--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -434,10 +434,10 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>53.32705710313409</v>
+        <v>53.26449181340857</v>
       </c>
       <c r="D2">
-        <v>25.97299879241849</v>
+        <v>25.93249319663132</v>
       </c>
       <c r="E2">
         <v>0.9262</v>
@@ -446,7 +446,7 @@
         <v>0.9262</v>
       </c>
       <c r="G2">
-        <v>0.3872030958911865</v>
+        <v>0.3892839481608621</v>
       </c>
       <c r="H2">
         <v>0.9262</v>
@@ -460,10 +460,10 @@
         <v>9</v>
       </c>
       <c r="C3">
-        <v>34.53148244944686</v>
+        <v>34.42170829708593</v>
       </c>
       <c r="D3">
-        <v>26.08589601670652</v>
+        <v>26.01477334208454</v>
       </c>
       <c r="E3">
         <v>0.9984</v>
@@ -472,7 +472,7 @@
         <v>0.9984</v>
       </c>
       <c r="G3">
-        <v>0.06748132491122871</v>
+        <v>0.06472843849581267</v>
       </c>
       <c r="H3">
         <v>0.9984</v>
@@ -486,10 +486,10 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>36.61274523339704</v>
+        <v>36.56347931591439</v>
       </c>
       <c r="D4">
-        <v>22.73265684308589</v>
+        <v>22.72964238966481</v>
       </c>
       <c r="E4">
         <v>0.9990740999999999</v>
@@ -498,7 +498,7 @@
         <v>0.9990740999999999</v>
       </c>
       <c r="G4">
-        <v>0.1662814267095185</v>
+        <v>0.1650893258330652</v>
       </c>
       <c r="H4">
         <v>0.9990740999999999</v>
@@ -512,10 +512,10 @@
         <v>11</v>
       </c>
       <c r="C5">
-        <v>54.62492179530582</v>
+        <v>54.66910192050099</v>
       </c>
       <c r="D5">
-        <v>22.52323336195511</v>
+        <v>22.56574131784717</v>
       </c>
       <c r="E5">
         <v>0.9999</v>
@@ -524,7 +524,7 @@
         <v>0.9999</v>
       </c>
       <c r="G5">
-        <v>0.545673771411969</v>
+        <v>0.5446150983617628</v>
       </c>
       <c r="H5">
         <v>0.9999</v>
@@ -538,10 +538,10 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>57.12305147755242</v>
+        <v>57.16392578808276</v>
       </c>
       <c r="D6">
-        <v>23.53933454639179</v>
+        <v>23.58706076165031</v>
       </c>
       <c r="E6">
         <v>0.9991</v>
@@ -550,7 +550,7 @@
         <v>0.9991</v>
       </c>
       <c r="G6">
-        <v>0.6981350019688173</v>
+        <v>0.6983902424541246</v>
       </c>
       <c r="H6">
         <v>0.9991</v>
@@ -564,10 +564,10 @@
         <v>13</v>
       </c>
       <c r="C7">
-        <v>35.88867319884837</v>
+        <v>35.91957141339604</v>
       </c>
       <c r="D7">
-        <v>19.04521398750263</v>
+        <v>19.10923935143763</v>
       </c>
       <c r="E7">
         <v>0.9996491399999999</v>
@@ -576,7 +576,7 @@
         <v>0.9996491399999999</v>
       </c>
       <c r="G7">
-        <v>0.2277471697384601</v>
+        <v>0.2290872260284964</v>
       </c>
       <c r="H7">
         <v>0.9985614899999999</v>
@@ -590,10 +590,10 @@
         <v>14</v>
       </c>
       <c r="C8">
-        <v>28.22738048024621</v>
+        <v>28.13794731775636</v>
       </c>
       <c r="D8">
-        <v>23.67423393518881</v>
+        <v>23.59847768192577</v>
       </c>
       <c r="E8">
         <v>0.9997295369999999</v>
@@ -602,7 +602,7 @@
         <v>0.9997295369999999</v>
       </c>
       <c r="G8">
-        <v>0.03956039626956498</v>
+        <v>0.03662381108768376</v>
       </c>
       <c r="H8">
         <v>0.9997295369999999</v>
@@ -616,10 +616,10 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>40.71619570965345</v>
+        <v>40.69797668816307</v>
       </c>
       <c r="D9">
-        <v>21.56447268795337</v>
+        <v>21.57531855713585</v>
       </c>
       <c r="E9">
         <v>0.99909852</v>
@@ -628,7 +628,7 @@
         <v>0.99909852</v>
       </c>
       <c r="G9">
-        <v>0.2359075884948187</v>
+        <v>0.2353178647851411</v>
       </c>
       <c r="H9">
         <v>0.9974930900000001</v>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -434,10 +434,10 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>53.26449181340857</v>
+        <v>53.1616507016645</v>
       </c>
       <c r="D2">
-        <v>25.93249319663132</v>
+        <v>25.87719523039523</v>
       </c>
       <c r="E2">
         <v>0.9262</v>
@@ -446,7 +446,7 @@
         <v>0.9262</v>
       </c>
       <c r="G2">
-        <v>0.3892839481608621</v>
+        <v>0.3865094784679615</v>
       </c>
       <c r="H2">
         <v>0.9262</v>
@@ -460,10 +460,10 @@
         <v>9</v>
       </c>
       <c r="C3">
-        <v>34.42170829708593</v>
+        <v>34.39169605853263</v>
       </c>
       <c r="D3">
-        <v>26.01477334208454</v>
+        <v>25.98461069124163</v>
       </c>
       <c r="E3">
         <v>0.9984</v>
@@ -472,7 +472,7 @@
         <v>0.9984</v>
       </c>
       <c r="G3">
-        <v>0.06472843849581267</v>
+        <v>0.06442232873409837</v>
       </c>
       <c r="H3">
         <v>0.9984</v>
@@ -486,10 +486,10 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>36.56347931591439</v>
+        <v>36.50320692850389</v>
       </c>
       <c r="D4">
-        <v>22.72964238966481</v>
+        <v>22.67174962584676</v>
       </c>
       <c r="E4">
         <v>0.9990740999999999</v>
@@ -498,7 +498,7 @@
         <v>0.9990740999999999</v>
       </c>
       <c r="G4">
-        <v>0.1650893258330652</v>
+        <v>0.1636113599638302</v>
       </c>
       <c r="H4">
         <v>0.9990740999999999</v>
@@ -512,10 +512,10 @@
         <v>11</v>
       </c>
       <c r="C5">
-        <v>54.66910192050099</v>
+        <v>54.55464008486201</v>
       </c>
       <c r="D5">
-        <v>22.56574131784717</v>
+        <v>22.50793492712612</v>
       </c>
       <c r="E5">
         <v>0.9999</v>
@@ -524,7 +524,7 @@
         <v>0.9999</v>
       </c>
       <c r="G5">
-        <v>0.5446150983617628</v>
+        <v>0.5417991097990287</v>
       </c>
       <c r="H5">
         <v>0.9999</v>
@@ -538,10 +538,10 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>57.16392578808276</v>
+        <v>57.06185053313492</v>
       </c>
       <c r="D6">
-        <v>23.58706076165031</v>
+        <v>23.51588978746457</v>
       </c>
       <c r="E6">
         <v>0.9991</v>
@@ -550,7 +550,7 @@
         <v>0.9991</v>
       </c>
       <c r="G6">
-        <v>0.6983902424541246</v>
+        <v>0.6950409655138174</v>
       </c>
       <c r="H6">
         <v>0.9991</v>
@@ -564,10 +564,10 @@
         <v>13</v>
       </c>
       <c r="C7">
-        <v>35.91957141339604</v>
+        <v>35.84954236955553</v>
       </c>
       <c r="D7">
-        <v>19.10923935143763</v>
+        <v>19.05244444540253</v>
       </c>
       <c r="E7">
         <v>0.9996491399999999</v>
@@ -576,7 +576,7 @@
         <v>0.9996491399999999</v>
       </c>
       <c r="G7">
-        <v>0.2290872260284964</v>
+        <v>0.2263126190211016</v>
       </c>
       <c r="H7">
         <v>0.9985614899999999</v>
@@ -590,10 +590,10 @@
         <v>14</v>
       </c>
       <c r="C8">
-        <v>28.13794731775636</v>
+        <v>28.12656681158764</v>
       </c>
       <c r="D8">
-        <v>23.59847768192577</v>
+        <v>23.58976500986843</v>
       </c>
       <c r="E8">
         <v>0.9997295369999999</v>
@@ -602,7 +602,7 @@
         <v>0.9997295369999999</v>
       </c>
       <c r="G8">
-        <v>0.03662381108768376</v>
+        <v>0.03344245601843587</v>
       </c>
       <c r="H8">
         <v>0.9997295369999999</v>
@@ -616,10 +616,10 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>40.69797668816307</v>
+        <v>40.62123437954348</v>
       </c>
       <c r="D9">
-        <v>21.57531855713585</v>
+        <v>21.52590685116699</v>
       </c>
       <c r="E9">
         <v>0.99909852</v>
@@ -628,7 +628,7 @@
         <v>0.99909852</v>
       </c>
       <c r="G9">
-        <v>0.2353178647851411</v>
+        <v>0.2326464269678006</v>
       </c>
       <c r="H9">
         <v>0.9974930900000001</v>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -434,10 +434,10 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>53.1616507016645</v>
+        <v>52.98393597476965</v>
       </c>
       <c r="D2">
-        <v>25.87719523039523</v>
+        <v>25.7807664399206</v>
       </c>
       <c r="E2">
         <v>0.9262</v>
@@ -446,7 +446,7 @@
         <v>0.9262</v>
       </c>
       <c r="G2">
-        <v>0.3865094784679615</v>
+        <v>0.3806139288115422</v>
       </c>
       <c r="H2">
         <v>0.9262</v>
@@ -460,10 +460,10 @@
         <v>9</v>
       </c>
       <c r="C3">
-        <v>34.39169605853263</v>
+        <v>34.39422833958157</v>
       </c>
       <c r="D3">
-        <v>25.98461069124163</v>
+        <v>25.97410596168422</v>
       </c>
       <c r="E3">
         <v>0.9984</v>
@@ -472,7 +472,7 @@
         <v>0.9984</v>
       </c>
       <c r="G3">
-        <v>0.06442232873409837</v>
+        <v>0.0640398666519566</v>
       </c>
       <c r="H3">
         <v>0.9984</v>
@@ -486,10 +486,10 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>36.50320692850389</v>
+        <v>36.51520309854606</v>
       </c>
       <c r="D4">
-        <v>22.67174962584676</v>
+        <v>22.64241706751066</v>
       </c>
       <c r="E4">
         <v>0.9990740999999999</v>
@@ -498,7 +498,7 @@
         <v>0.9990740999999999</v>
       </c>
       <c r="G4">
-        <v>0.1636113599638302</v>
+        <v>0.1634397213593777</v>
       </c>
       <c r="H4">
         <v>0.9990740999999999</v>
@@ -512,22 +512,22 @@
         <v>11</v>
       </c>
       <c r="C5">
-        <v>54.55464008486201</v>
+        <v>52.4369564088344</v>
       </c>
       <c r="D5">
-        <v>22.50793492712612</v>
+        <v>23.86853417172939</v>
       </c>
       <c r="E5">
-        <v>0.9999</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="F5">
-        <v>0.9999</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="G5">
-        <v>0.5417991097990287</v>
+        <v>0.53653909888039</v>
       </c>
       <c r="H5">
-        <v>0.9999</v>
+        <v>0.9994000000000002</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -538,10 +538,10 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>57.06185053313492</v>
+        <v>56.78897623973095</v>
       </c>
       <c r="D6">
-        <v>23.51588978746457</v>
+        <v>23.34061416628912</v>
       </c>
       <c r="E6">
         <v>0.9991</v>
@@ -550,7 +550,7 @@
         <v>0.9991</v>
       </c>
       <c r="G6">
-        <v>0.6950409655138174</v>
+        <v>0.687353379089068</v>
       </c>
       <c r="H6">
         <v>0.9991</v>
@@ -564,10 +564,10 @@
         <v>13</v>
       </c>
       <c r="C7">
-        <v>35.84954236955553</v>
+        <v>35.74666198786722</v>
       </c>
       <c r="D7">
-        <v>19.05244444540253</v>
+        <v>18.92986749993139</v>
       </c>
       <c r="E7">
         <v>0.9996491399999999</v>
@@ -576,7 +576,7 @@
         <v>0.9996491399999999</v>
       </c>
       <c r="G7">
-        <v>0.2263126190211016</v>
+        <v>0.2215460848299107</v>
       </c>
       <c r="H7">
         <v>0.9985614899999999</v>
@@ -590,10 +590,10 @@
         <v>14</v>
       </c>
       <c r="C8">
-        <v>28.12656681158764</v>
+        <v>28.13920778271748</v>
       </c>
       <c r="D8">
-        <v>23.58976500986843</v>
+        <v>23.59906077341354</v>
       </c>
       <c r="E8">
         <v>0.9997295369999999</v>
@@ -616,10 +616,10 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>40.62123437954348</v>
+        <v>40.57746751597755</v>
       </c>
       <c r="D9">
-        <v>21.52590685116699</v>
+        <v>21.44198776487845</v>
       </c>
       <c r="E9">
         <v>0.99909852</v>
@@ -628,7 +628,7 @@
         <v>0.99909852</v>
       </c>
       <c r="G9">
-        <v>0.2326464269678006</v>
+        <v>0.2305649246101233</v>
       </c>
       <c r="H9">
         <v>0.9974930900000001</v>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -434,10 +434,10 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>52.98393597476965</v>
+        <v>53.14054723588798</v>
       </c>
       <c r="D2">
-        <v>25.7807664399206</v>
+        <v>25.83744954013946</v>
       </c>
       <c r="E2">
         <v>0.9262</v>
@@ -446,7 +446,7 @@
         <v>0.9262</v>
       </c>
       <c r="G2">
-        <v>0.3806139288115422</v>
+        <v>0.3837351410690573</v>
       </c>
       <c r="H2">
         <v>0.9262</v>
@@ -460,10 +460,10 @@
         <v>9</v>
       </c>
       <c r="C3">
-        <v>34.39422833958157</v>
+        <v>34.36505002936617</v>
       </c>
       <c r="D3">
-        <v>25.97410596168422</v>
+        <v>25.95597699980606</v>
       </c>
       <c r="E3">
         <v>0.9984</v>
@@ -472,7 +472,7 @@
         <v>0.9984</v>
       </c>
       <c r="G3">
-        <v>0.0640398666519566</v>
+        <v>0.06228002738876826</v>
       </c>
       <c r="H3">
         <v>0.9984</v>
@@ -486,10 +486,10 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>36.51520309854606</v>
+        <v>36.55826420004409</v>
       </c>
       <c r="D4">
-        <v>22.64241706751066</v>
+        <v>22.67205262509598</v>
       </c>
       <c r="E4">
         <v>0.9990740999999999</v>
@@ -498,7 +498,7 @@
         <v>0.9990740999999999</v>
       </c>
       <c r="G4">
-        <v>0.1634397213593777</v>
+        <v>0.1648443271746771</v>
       </c>
       <c r="H4">
         <v>0.9990740999999999</v>
@@ -512,10 +512,10 @@
         <v>11</v>
       </c>
       <c r="C5">
-        <v>52.4369564088344</v>
+        <v>52.72318906915154</v>
       </c>
       <c r="D5">
-        <v>23.86853417172939</v>
+        <v>23.99556024590022</v>
       </c>
       <c r="E5">
         <v>0.9994000000000002</v>
@@ -524,7 +524,7 @@
         <v>0.9994000000000002</v>
       </c>
       <c r="G5">
-        <v>0.53653909888039</v>
+        <v>0.5439592933263377</v>
       </c>
       <c r="H5">
         <v>0.9994000000000002</v>
@@ -538,10 +538,10 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>56.78897623973095</v>
+        <v>57.20446192587175</v>
       </c>
       <c r="D6">
-        <v>23.34061416628912</v>
+        <v>23.51955704132281</v>
       </c>
       <c r="E6">
         <v>0.9991</v>
@@ -550,7 +550,7 @@
         <v>0.9991</v>
       </c>
       <c r="G6">
-        <v>0.687353379089068</v>
+        <v>0.6992832921155319</v>
       </c>
       <c r="H6">
         <v>0.9991</v>
@@ -564,10 +564,10 @@
         <v>13</v>
       </c>
       <c r="C7">
-        <v>35.74666198786722</v>
+        <v>35.79143357884439</v>
       </c>
       <c r="D7">
-        <v>18.92986749993139</v>
+        <v>18.98369797571865</v>
       </c>
       <c r="E7">
         <v>0.9996491399999999</v>
@@ -576,7 +576,7 @@
         <v>0.9996491399999999</v>
       </c>
       <c r="G7">
-        <v>0.2215460848299107</v>
+        <v>0.2245393460602025</v>
       </c>
       <c r="H7">
         <v>0.9985614899999999</v>
@@ -590,10 +590,10 @@
         <v>14</v>
       </c>
       <c r="C8">
-        <v>28.13920778271748</v>
+        <v>28.11545990436803</v>
       </c>
       <c r="D8">
-        <v>23.59906077341354</v>
+        <v>23.58100469397916</v>
       </c>
       <c r="E8">
         <v>0.9997295369999999</v>
@@ -602,7 +602,7 @@
         <v>0.9997295369999999</v>
       </c>
       <c r="G8">
-        <v>0.03344245601843587</v>
+        <v>0.03515547182056333</v>
       </c>
       <c r="H8">
         <v>0.9997295369999999</v>
@@ -616,10 +616,10 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>40.57746751597755</v>
+        <v>40.66761376561686</v>
       </c>
       <c r="D9">
-        <v>21.44198776487845</v>
+        <v>21.49162756482406</v>
       </c>
       <c r="E9">
         <v>0.99909852</v>
@@ -628,7 +628,7 @@
         <v>0.99909852</v>
       </c>
       <c r="G9">
-        <v>0.2305649246101233</v>
+        <v>0.233687284021632</v>
       </c>
       <c r="H9">
         <v>0.9974930900000001</v>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -434,10 +434,10 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>53.14054723588798</v>
+        <v>53.14119317027835</v>
       </c>
       <c r="D2">
-        <v>25.83744954013946</v>
+        <v>25.8460656801819</v>
       </c>
       <c r="E2">
         <v>0.9262</v>
@@ -446,7 +446,7 @@
         <v>0.9262</v>
       </c>
       <c r="G2">
-        <v>0.3837351410690573</v>
+        <v>0.3839084462043663</v>
       </c>
       <c r="H2">
         <v>0.9262</v>
@@ -460,10 +460,10 @@
         <v>9</v>
       </c>
       <c r="C3">
-        <v>34.36505002936617</v>
+        <v>34.36604773180467</v>
       </c>
       <c r="D3">
-        <v>25.95597699980606</v>
+        <v>25.95911191288482</v>
       </c>
       <c r="E3">
         <v>0.9984</v>
@@ -472,7 +472,7 @@
         <v>0.9984</v>
       </c>
       <c r="G3">
-        <v>0.06228002738876826</v>
+        <v>0.06266260621757724</v>
       </c>
       <c r="H3">
         <v>0.9984</v>
@@ -486,10 +486,10 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>36.55826420004409</v>
+        <v>36.55824432536258</v>
       </c>
       <c r="D4">
-        <v>22.67205262509598</v>
+        <v>22.67203467168659</v>
       </c>
       <c r="E4">
         <v>0.9990740999999999</v>
@@ -512,10 +512,10 @@
         <v>11</v>
       </c>
       <c r="C5">
-        <v>52.72318906915154</v>
+        <v>52.70713461718313</v>
       </c>
       <c r="D5">
-        <v>23.99556024590022</v>
+        <v>23.98886801805074</v>
       </c>
       <c r="E5">
         <v>0.9994000000000002</v>
@@ -524,7 +524,7 @@
         <v>0.9994000000000002</v>
       </c>
       <c r="G5">
-        <v>0.5439592933263377</v>
+        <v>0.5438253854918791</v>
       </c>
       <c r="H5">
         <v>0.9994000000000002</v>
@@ -538,10 +538,10 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>57.20446192587175</v>
+        <v>57.17173904720283</v>
       </c>
       <c r="D6">
-        <v>23.51955704132281</v>
+        <v>23.49978532445766</v>
       </c>
       <c r="E6">
         <v>0.9991</v>
@@ -550,7 +550,7 @@
         <v>0.9991</v>
       </c>
       <c r="G6">
-        <v>0.6992832921155319</v>
+        <v>0.6994110097039083</v>
       </c>
       <c r="H6">
         <v>0.9991</v>
@@ -564,10 +564,10 @@
         <v>13</v>
       </c>
       <c r="C7">
-        <v>35.79143357884439</v>
+        <v>35.78713940977861</v>
       </c>
       <c r="D7">
-        <v>18.98369797571865</v>
+        <v>18.96714341179282</v>
       </c>
       <c r="E7">
         <v>0.9996491399999999</v>
@@ -576,7 +576,7 @@
         <v>0.9996491399999999</v>
       </c>
       <c r="G7">
-        <v>0.2245393460602025</v>
+        <v>0.2243424293916285</v>
       </c>
       <c r="H7">
         <v>0.9985614899999999</v>
@@ -590,10 +590,10 @@
         <v>14</v>
       </c>
       <c r="C8">
-        <v>28.11545990436803</v>
+        <v>28.12253390077671</v>
       </c>
       <c r="D8">
-        <v>23.58100469397916</v>
+        <v>23.58699683751922</v>
       </c>
       <c r="E8">
         <v>0.9997295369999999</v>
@@ -602,7 +602,7 @@
         <v>0.9997295369999999</v>
       </c>
       <c r="G8">
-        <v>0.03515547182056333</v>
+        <v>0.03368732240295347</v>
       </c>
       <c r="H8">
         <v>0.9997295369999999</v>
@@ -616,10 +616,10 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>40.66761376561686</v>
+        <v>40.68906294966703</v>
       </c>
       <c r="D9">
-        <v>21.49162756482406</v>
+        <v>21.50438913887365</v>
       </c>
       <c r="E9">
         <v>0.99909852</v>
@@ -628,7 +628,7 @@
         <v>0.99909852</v>
       </c>
       <c r="G9">
-        <v>0.233687284021632</v>
+        <v>0.2342423866086769</v>
       </c>
       <c r="H9">
         <v>0.9974930900000001</v>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -434,10 +434,10 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>53.14119317027835</v>
+        <v>53.14833755912058</v>
       </c>
       <c r="D2">
-        <v>25.8460656801819</v>
+        <v>25.84885448407537</v>
       </c>
       <c r="E2">
         <v>0.9262</v>
@@ -460,22 +460,22 @@
         <v>9</v>
       </c>
       <c r="C3">
-        <v>34.36604773180467</v>
+        <v>34.64560932909123</v>
       </c>
       <c r="D3">
-        <v>25.95911191288482</v>
+        <v>26.08311546080494</v>
       </c>
       <c r="E3">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="F3">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="G3">
-        <v>0.06266260621757724</v>
+        <v>0.06258613715048233</v>
       </c>
       <c r="H3">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -486,10 +486,10 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>36.55824432536258</v>
+        <v>36.55790859258162</v>
       </c>
       <c r="D4">
-        <v>22.67203467168659</v>
+        <v>22.67181120908155</v>
       </c>
       <c r="E4">
         <v>0.9990740999999999</v>
@@ -512,10 +512,10 @@
         <v>11</v>
       </c>
       <c r="C5">
-        <v>52.70713461718313</v>
+        <v>52.70832779833182</v>
       </c>
       <c r="D5">
-        <v>23.98886801805074</v>
+        <v>23.99044674439659</v>
       </c>
       <c r="E5">
         <v>0.9994000000000002</v>
@@ -538,10 +538,10 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>57.17173904720283</v>
+        <v>57.1732166855686</v>
       </c>
       <c r="D6">
-        <v>23.49978532445766</v>
+        <v>23.50022751267814</v>
       </c>
       <c r="E6">
         <v>0.9991</v>
@@ -564,10 +564,10 @@
         <v>13</v>
       </c>
       <c r="C7">
-        <v>35.78713940977861</v>
+        <v>35.78646526282436</v>
       </c>
       <c r="D7">
-        <v>18.96714341179282</v>
+        <v>18.96635091925032</v>
       </c>
       <c r="E7">
         <v>0.9996491399999999</v>
@@ -576,7 +576,7 @@
         <v>0.9996491399999999</v>
       </c>
       <c r="G7">
-        <v>0.2243424293916285</v>
+        <v>0.2240600969213613</v>
       </c>
       <c r="H7">
         <v>0.9985614899999999</v>
@@ -616,10 +616,10 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>40.68906294966703</v>
+        <v>40.68830633303975</v>
       </c>
       <c r="D9">
-        <v>21.50438913887365</v>
+        <v>21.50431773660198</v>
       </c>
       <c r="E9">
         <v>0.99909852</v>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
   <si>
     <t>Date</t>
   </si>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -454,28 +454,28 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>34.64560932909123</v>
+        <v>53.11375783702195</v>
       </c>
       <c r="D3">
-        <v>26.08311546080494</v>
+        <v>25.85217106827631</v>
       </c>
       <c r="E3">
-        <v>0.9983000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="F3">
-        <v>0.9983000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="G3">
-        <v>0.06258613715048233</v>
+        <v>0.3839084462043663</v>
       </c>
       <c r="H3">
-        <v>0.9983000000000001</v>
+        <v>0.9262</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -483,51 +483,51 @@
         <v>46153</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>36.55790859258162</v>
+        <v>34.64560932909123</v>
       </c>
       <c r="D4">
-        <v>22.67181120908155</v>
+        <v>26.08311546080494</v>
       </c>
       <c r="E4">
-        <v>0.9990740999999999</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="F4">
-        <v>0.9990740999999999</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="G4">
-        <v>0.1648443271746771</v>
+        <v>0.06258613715048233</v>
       </c>
       <c r="H4">
-        <v>0.9990740999999999</v>
+        <v>0.9983000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>52.70832779833182</v>
+        <v>34.66668945999121</v>
       </c>
       <c r="D5">
-        <v>23.99044674439659</v>
+        <v>26.08311546080494</v>
       </c>
       <c r="E5">
-        <v>0.9994000000000002</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="F5">
-        <v>0.9994000000000002</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="G5">
-        <v>0.5438253854918791</v>
+        <v>0.06258613715048233</v>
       </c>
       <c r="H5">
-        <v>0.9994000000000002</v>
+        <v>0.9983000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -535,51 +535,51 @@
         <v>46153</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>57.1732166855686</v>
+        <v>36.55790859258162</v>
       </c>
       <c r="D6">
-        <v>23.50022751267814</v>
+        <v>22.67181120908155</v>
       </c>
       <c r="E6">
-        <v>0.9991</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="F6">
-        <v>0.9991</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="G6">
-        <v>0.6994110097039083</v>
+        <v>0.1648443271746771</v>
       </c>
       <c r="H6">
-        <v>0.9991</v>
+        <v>0.9990740999999999</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>35.78646526282436</v>
+        <v>36.53946284942268</v>
       </c>
       <c r="D7">
-        <v>18.96635091925032</v>
+        <v>22.48530121204493</v>
       </c>
       <c r="E7">
-        <v>0.9996491399999999</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="F7">
-        <v>0.9996491399999999</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="G7">
-        <v>0.2240600969213613</v>
+        <v>0.1548092499054095</v>
       </c>
       <c r="H7">
-        <v>0.9985614899999999</v>
+        <v>0.9990772499999999</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -587,51 +587,259 @@
         <v>46153</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C8">
-        <v>28.12253390077671</v>
+        <v>52.70832779833182</v>
       </c>
       <c r="D8">
-        <v>23.58699683751922</v>
+        <v>23.99044674439659</v>
       </c>
       <c r="E8">
-        <v>0.9997295369999999</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="F8">
-        <v>0.9997295369999999</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="G8">
-        <v>0.03368732240295347</v>
+        <v>0.5438253854918791</v>
       </c>
       <c r="H8">
-        <v>0.9997295369999999</v>
+        <v>0.9994000000000002</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>52.50191316731146</v>
+      </c>
+      <c r="D9">
+        <v>23.83967928437651</v>
+      </c>
+      <c r="E9">
+        <v>0.9996</v>
+      </c>
+      <c r="F9">
+        <v>0.9996</v>
+      </c>
+      <c r="G9">
+        <v>0.5438253854918791</v>
+      </c>
+      <c r="H9">
+        <v>0.9996</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1">
         <v>46153</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>57.1732166855686</v>
+      </c>
+      <c r="D10">
+        <v>23.50022751267814</v>
+      </c>
+      <c r="E10">
+        <v>0.9991</v>
+      </c>
+      <c r="F10">
+        <v>0.9991</v>
+      </c>
+      <c r="G10">
+        <v>0.6994110097039083</v>
+      </c>
+      <c r="H10">
+        <v>0.9991</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11">
+        <v>56.84378653790157</v>
+      </c>
+      <c r="D11">
+        <v>23.29782007210019</v>
+      </c>
+      <c r="E11">
+        <v>0.9990000000000001</v>
+      </c>
+      <c r="F11">
+        <v>0.9990000000000001</v>
+      </c>
+      <c r="G11">
+        <v>0.6994110097039083</v>
+      </c>
+      <c r="H11">
+        <v>0.9990000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12">
+        <v>35.78646526282436</v>
+      </c>
+      <c r="D12">
+        <v>18.96635091925032</v>
+      </c>
+      <c r="E12">
+        <v>0.9996491399999999</v>
+      </c>
+      <c r="F12">
+        <v>0.9996491399999999</v>
+      </c>
+      <c r="G12">
+        <v>0.2240600969213613</v>
+      </c>
+      <c r="H12">
+        <v>0.9985614899999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13">
+        <v>35.91440623436536</v>
+      </c>
+      <c r="D13">
+        <v>18.88616735108022</v>
+      </c>
+      <c r="E13">
+        <v>0.99965481</v>
+      </c>
+      <c r="F13">
+        <v>0.99965481</v>
+      </c>
+      <c r="G13">
+        <v>0.2240600969213613</v>
+      </c>
+      <c r="H13">
+        <v>0.9985622199999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14">
+        <v>28.12253390077671</v>
+      </c>
+      <c r="D14">
+        <v>23.58699683751922</v>
+      </c>
+      <c r="E14">
+        <v>0.9997295369999999</v>
+      </c>
+      <c r="F14">
+        <v>0.9997295369999999</v>
+      </c>
+      <c r="G14">
+        <v>0.03368732240295347</v>
+      </c>
+      <c r="H14">
+        <v>0.9997295369999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15">
+        <v>28.13810299106507</v>
+      </c>
+      <c r="D15">
+        <v>23.59691691522852</v>
+      </c>
+      <c r="E15">
+        <v>1.000319473</v>
+      </c>
+      <c r="F15">
+        <v>1.000319473</v>
+      </c>
+      <c r="G15">
+        <v>0.03368722590580253</v>
+      </c>
+      <c r="H15">
+        <v>1.000319473</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B16" t="s">
         <v>15</v>
       </c>
-      <c r="C9">
+      <c r="C16">
         <v>40.68830633303975</v>
       </c>
-      <c r="D9">
+      <c r="D16">
         <v>21.50431773660198</v>
       </c>
-      <c r="E9">
+      <c r="E16">
         <v>0.99909852</v>
       </c>
-      <c r="F9">
+      <c r="F16">
         <v>0.99909852</v>
       </c>
-      <c r="G9">
+      <c r="G16">
         <v>0.2342423866086769</v>
       </c>
-      <c r="H9">
+      <c r="H16">
         <v>0.9974930900000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17">
+        <v>40.95430127793534</v>
+      </c>
+      <c r="D17">
+        <v>21.48344363493026</v>
+      </c>
+      <c r="E17">
+        <v>0.9990972199999999</v>
+      </c>
+      <c r="F17">
+        <v>0.9990972199999999</v>
+      </c>
+      <c r="G17">
+        <v>0.2342423866086769</v>
+      </c>
+      <c r="H17">
+        <v>0.99752223</v>
       </c>
     </row>
   </sheetData>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -460,10 +460,10 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>53.11375783702195</v>
+        <v>52.53067808201381</v>
       </c>
       <c r="D3">
-        <v>25.85217106827631</v>
+        <v>25.65278023674941</v>
       </c>
       <c r="E3">
         <v>0.9262</v>
@@ -472,7 +472,7 @@
         <v>0.9262</v>
       </c>
       <c r="G3">
-        <v>0.3839084462043663</v>
+        <v>0.3683025172107874</v>
       </c>
       <c r="H3">
         <v>0.9262</v>
@@ -512,10 +512,10 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>34.66668945999121</v>
+        <v>34.47578302689066</v>
       </c>
       <c r="D5">
-        <v>26.08311546080494</v>
+        <v>25.98435318420949</v>
       </c>
       <c r="E5">
         <v>0.9983000000000001</v>
@@ -524,7 +524,7 @@
         <v>0.9983000000000001</v>
       </c>
       <c r="G5">
-        <v>0.06258613715048233</v>
+        <v>0.05876058235572601</v>
       </c>
       <c r="H5">
         <v>0.9983000000000001</v>
@@ -564,10 +564,10 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>36.53946284942268</v>
+        <v>36.4650104597748</v>
       </c>
       <c r="D7">
-        <v>22.48530121204493</v>
+        <v>22.48399453510068</v>
       </c>
       <c r="E7">
         <v>0.9990772499999999</v>
@@ -576,7 +576,7 @@
         <v>0.9990772499999999</v>
       </c>
       <c r="G7">
-        <v>0.1548092499054095</v>
+        <v>0.1580835403562029</v>
       </c>
       <c r="H7">
         <v>0.9990772499999999</v>
@@ -616,10 +616,10 @@
         <v>11</v>
       </c>
       <c r="C9">
-        <v>52.50191316731146</v>
+        <v>51.63153222454658</v>
       </c>
       <c r="D9">
-        <v>23.83967928437651</v>
+        <v>23.46464778500843</v>
       </c>
       <c r="E9">
         <v>0.9996</v>
@@ -628,7 +628,7 @@
         <v>0.9996</v>
       </c>
       <c r="G9">
-        <v>0.5438253854918791</v>
+        <v>0.5218859193541294</v>
       </c>
       <c r="H9">
         <v>0.9996</v>
@@ -668,10 +668,10 @@
         <v>12</v>
       </c>
       <c r="C11">
-        <v>56.84378653790157</v>
+        <v>55.64247719454313</v>
       </c>
       <c r="D11">
-        <v>23.29782007210019</v>
+        <v>22.81002793557051</v>
       </c>
       <c r="E11">
         <v>0.9990000000000001</v>
@@ -680,7 +680,7 @@
         <v>0.9990000000000001</v>
       </c>
       <c r="G11">
-        <v>0.6994110097039083</v>
+        <v>0.6687885762847323</v>
       </c>
       <c r="H11">
         <v>0.9990000000000001</v>
@@ -720,10 +720,10 @@
         <v>13</v>
       </c>
       <c r="C13">
-        <v>35.91440623436536</v>
+        <v>35.59061592483303</v>
       </c>
       <c r="D13">
-        <v>18.88616735108022</v>
+        <v>18.6391712483987</v>
       </c>
       <c r="E13">
         <v>0.99965481</v>
@@ -732,7 +732,7 @@
         <v>0.99965481</v>
       </c>
       <c r="G13">
-        <v>0.2240600969213613</v>
+        <v>0.2121613432887923</v>
       </c>
       <c r="H13">
         <v>0.9985622199999999</v>
@@ -772,10 +772,10 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>28.13810299106507</v>
+        <v>27.99868287903314</v>
       </c>
       <c r="D15">
-        <v>23.59691691522852</v>
+        <v>23.48500730715878</v>
       </c>
       <c r="E15">
         <v>1.000319473</v>
@@ -784,7 +784,7 @@
         <v>1.000319473</v>
       </c>
       <c r="G15">
-        <v>0.03368722590580253</v>
+        <v>0.03075054737156169</v>
       </c>
       <c r="H15">
         <v>1.000319473</v>
@@ -824,10 +824,10 @@
         <v>15</v>
       </c>
       <c r="C17">
-        <v>40.95430127793534</v>
+        <v>40.61418524967579</v>
       </c>
       <c r="D17">
-        <v>21.48344363493026</v>
+        <v>21.26549038316582</v>
       </c>
       <c r="E17">
         <v>0.9990972199999999</v>
@@ -836,7 +836,7 @@
         <v>0.9990972199999999</v>
       </c>
       <c r="G17">
-        <v>0.2342423866086769</v>
+        <v>0.2264710562650416</v>
       </c>
       <c r="H17">
         <v>0.99752223</v>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -460,10 +460,10 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>52.53067808201381</v>
+        <v>51.90076222475765</v>
       </c>
       <c r="D3">
-        <v>25.65278023674941</v>
+        <v>25.38353339891543</v>
       </c>
       <c r="E3">
         <v>0.9262</v>
@@ -472,7 +472,7 @@
         <v>0.9262</v>
       </c>
       <c r="G3">
-        <v>0.3683025172107874</v>
+        <v>0.3603259829906964</v>
       </c>
       <c r="H3">
         <v>0.9262</v>
@@ -512,10 +512,10 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>34.47578302689066</v>
+        <v>34.523173635569</v>
       </c>
       <c r="D5">
-        <v>25.98435318420949</v>
+        <v>25.99764476465155</v>
       </c>
       <c r="E5">
         <v>0.9983000000000001</v>
@@ -524,7 +524,7 @@
         <v>0.9983000000000001</v>
       </c>
       <c r="G5">
-        <v>0.05876058235572601</v>
+        <v>0.05692427402544253</v>
       </c>
       <c r="H5">
         <v>0.9983000000000001</v>
@@ -564,10 +564,10 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>36.4650104597748</v>
+        <v>36.3538848494011</v>
       </c>
       <c r="D7">
-        <v>22.48399453510068</v>
+        <v>22.3642673066391</v>
       </c>
       <c r="E7">
         <v>0.9990772499999999</v>
@@ -576,7 +576,7 @@
         <v>0.9990772499999999</v>
       </c>
       <c r="G7">
-        <v>0.1580835403562029</v>
+        <v>0.1532169579738591</v>
       </c>
       <c r="H7">
         <v>0.9990772499999999</v>
@@ -616,10 +616,10 @@
         <v>11</v>
       </c>
       <c r="C9">
-        <v>51.63153222454658</v>
+        <v>50.99680190559354</v>
       </c>
       <c r="D9">
-        <v>23.46464778500843</v>
+        <v>23.21419393228504</v>
       </c>
       <c r="E9">
         <v>0.9996</v>
@@ -628,7 +628,7 @@
         <v>0.9996</v>
       </c>
       <c r="G9">
-        <v>0.5218859193541294</v>
+        <v>0.50490235110438</v>
       </c>
       <c r="H9">
         <v>0.9996</v>
@@ -668,10 +668,10 @@
         <v>12</v>
       </c>
       <c r="C11">
-        <v>55.64247719454313</v>
+        <v>54.85570139405836</v>
       </c>
       <c r="D11">
-        <v>22.81002793557051</v>
+        <v>22.5218981340527</v>
       </c>
       <c r="E11">
         <v>0.9990000000000001</v>
@@ -680,7 +680,7 @@
         <v>0.9990000000000001</v>
       </c>
       <c r="G11">
-        <v>0.6687885762847323</v>
+        <v>0.6452795842169485</v>
       </c>
       <c r="H11">
         <v>0.9990000000000001</v>
@@ -720,10 +720,10 @@
         <v>13</v>
       </c>
       <c r="C13">
-        <v>35.59061592483303</v>
+        <v>35.50599331258434</v>
       </c>
       <c r="D13">
-        <v>18.6391712483987</v>
+        <v>18.57376843477372</v>
       </c>
       <c r="E13">
         <v>0.99965481</v>
@@ -732,7 +732,7 @@
         <v>0.99965481</v>
       </c>
       <c r="G13">
-        <v>0.2121613432887923</v>
+        <v>0.2067135285715218</v>
       </c>
       <c r="H13">
         <v>0.9985622199999999</v>
@@ -772,10 +772,10 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>27.99868287903314</v>
+        <v>28.06967993771944</v>
       </c>
       <c r="D15">
-        <v>23.48500730715878</v>
+        <v>23.54590989452407</v>
       </c>
       <c r="E15">
         <v>1.000319473</v>
@@ -824,10 +824,10 @@
         <v>15</v>
       </c>
       <c r="C17">
-        <v>40.61418524967579</v>
+        <v>40.39914472296738</v>
       </c>
       <c r="D17">
-        <v>21.26549038316582</v>
+        <v>21.13956631667561</v>
       </c>
       <c r="E17">
         <v>0.9990972199999999</v>
@@ -836,7 +836,7 @@
         <v>0.9990972199999999</v>
       </c>
       <c r="G17">
-        <v>0.2264710562650416</v>
+        <v>0.2191161322679345</v>
       </c>
       <c r="H17">
         <v>0.99752223</v>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -460,10 +460,10 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>51.90076222475765</v>
+        <v>52.01785360316035</v>
       </c>
       <c r="D3">
-        <v>25.38353339891543</v>
+        <v>25.45503980712668</v>
       </c>
       <c r="E3">
         <v>0.9262</v>
@@ -472,7 +472,7 @@
         <v>0.9262</v>
       </c>
       <c r="G3">
-        <v>0.3603259829906964</v>
+        <v>0.3646609926653563</v>
       </c>
       <c r="H3">
         <v>0.9262</v>
@@ -512,10 +512,10 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>34.523173635569</v>
+        <v>34.59502557202465</v>
       </c>
       <c r="D5">
-        <v>25.99764476465155</v>
+        <v>26.04796099512169</v>
       </c>
       <c r="E5">
         <v>0.9983000000000001</v>
@@ -524,7 +524,7 @@
         <v>0.9983000000000001</v>
       </c>
       <c r="G5">
-        <v>0.05692427402544253</v>
+        <v>0.05937268513248695</v>
       </c>
       <c r="H5">
         <v>0.9983000000000001</v>
@@ -564,10 +564,10 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>36.3538848494011</v>
+        <v>36.41161416903155</v>
       </c>
       <c r="D7">
-        <v>22.3642673066391</v>
+        <v>22.36334778970728</v>
       </c>
       <c r="E7">
         <v>0.9990772499999999</v>
@@ -576,7 +576,7 @@
         <v>0.9990772499999999</v>
       </c>
       <c r="G7">
-        <v>0.1532169579738591</v>
+        <v>0.1537232021504065</v>
       </c>
       <c r="H7">
         <v>0.9990772499999999</v>
@@ -616,10 +616,10 @@
         <v>11</v>
       </c>
       <c r="C9">
-        <v>50.99680190559354</v>
+        <v>51.06864794605255</v>
       </c>
       <c r="D9">
-        <v>23.21419393228504</v>
+        <v>23.24405448006081</v>
       </c>
       <c r="E9">
         <v>0.9996</v>
@@ -628,7 +628,7 @@
         <v>0.9996</v>
       </c>
       <c r="G9">
-        <v>0.50490235110438</v>
+        <v>0.5080096995706611</v>
       </c>
       <c r="H9">
         <v>0.9996</v>
@@ -668,10 +668,10 @@
         <v>12</v>
       </c>
       <c r="C11">
-        <v>54.85570139405836</v>
+        <v>55.11598462679832</v>
       </c>
       <c r="D11">
-        <v>22.5218981340527</v>
+        <v>22.63132237950178</v>
       </c>
       <c r="E11">
         <v>0.9990000000000001</v>
@@ -680,7 +680,7 @@
         <v>0.9990000000000001</v>
       </c>
       <c r="G11">
-        <v>0.6452795842169485</v>
+        <v>0.6530627641415347</v>
       </c>
       <c r="H11">
         <v>0.9990000000000001</v>
@@ -720,10 +720,10 @@
         <v>13</v>
       </c>
       <c r="C13">
-        <v>35.50599331258434</v>
+        <v>35.55253325775063</v>
       </c>
       <c r="D13">
-        <v>18.57376843477372</v>
+        <v>18.58012322989026</v>
       </c>
       <c r="E13">
         <v>0.99965481</v>
@@ -732,7 +732,7 @@
         <v>0.99965481</v>
       </c>
       <c r="G13">
-        <v>0.2067135285715218</v>
+        <v>0.2093112941810997</v>
       </c>
       <c r="H13">
         <v>0.9985622199999999</v>
@@ -772,10 +772,10 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>28.06967993771944</v>
+        <v>28.17914652889119</v>
       </c>
       <c r="D15">
-        <v>23.54590989452407</v>
+        <v>23.63965269874433</v>
       </c>
       <c r="E15">
         <v>1.000319473</v>
@@ -824,10 +824,10 @@
         <v>15</v>
       </c>
       <c r="C17">
-        <v>40.39914472296738</v>
+        <v>40.44575884225483</v>
       </c>
       <c r="D17">
-        <v>21.13956631667561</v>
+        <v>21.12949357071461</v>
       </c>
       <c r="E17">
         <v>0.9990972199999999</v>
@@ -836,7 +836,7 @@
         <v>0.9990972199999999</v>
       </c>
       <c r="G17">
-        <v>0.2191161322679345</v>
+        <v>0.218422333440373</v>
       </c>
       <c r="H17">
         <v>0.99752223</v>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -460,10 +460,10 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>52.01785360316035</v>
+        <v>51.56478316903839</v>
       </c>
       <c r="D3">
-        <v>25.45503980712668</v>
+        <v>25.22551174390981</v>
       </c>
       <c r="E3">
         <v>0.9262</v>
@@ -472,7 +472,7 @@
         <v>0.9262</v>
       </c>
       <c r="G3">
-        <v>0.3646609926653563</v>
+        <v>0.3495752436656974</v>
       </c>
       <c r="H3">
         <v>0.9262</v>
@@ -512,10 +512,10 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>34.59502557202465</v>
+        <v>34.52083917991418</v>
       </c>
       <c r="D5">
-        <v>26.04796099512169</v>
+        <v>25.97424315228389</v>
       </c>
       <c r="E5">
         <v>0.9983000000000001</v>
@@ -524,7 +524,7 @@
         <v>0.9983000000000001</v>
       </c>
       <c r="G5">
-        <v>0.05937268513248695</v>
+        <v>0.05547054452396849</v>
       </c>
       <c r="H5">
         <v>0.9983000000000001</v>
@@ -564,10 +564,10 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>36.41161416903155</v>
+        <v>36.36684428102582</v>
       </c>
       <c r="D7">
-        <v>22.36334778970728</v>
+        <v>22.33401381209434</v>
       </c>
       <c r="E7">
         <v>0.9990772499999999</v>
@@ -576,7 +576,7 @@
         <v>0.9990772499999999</v>
       </c>
       <c r="G7">
-        <v>0.1537232021504065</v>
+        <v>0.1523922554110018</v>
       </c>
       <c r="H7">
         <v>0.9990772499999999</v>
@@ -616,10 +616,10 @@
         <v>11</v>
       </c>
       <c r="C9">
-        <v>51.06864794605255</v>
+        <v>50.70834670626966</v>
       </c>
       <c r="D9">
-        <v>23.24405448006081</v>
+        <v>23.08855917397172</v>
       </c>
       <c r="E9">
         <v>0.9996</v>
@@ -628,7 +628,7 @@
         <v>0.9996</v>
       </c>
       <c r="G9">
-        <v>0.5080096995706611</v>
+        <v>0.4963701820770494</v>
       </c>
       <c r="H9">
         <v>0.9996</v>
@@ -668,10 +668,10 @@
         <v>12</v>
       </c>
       <c r="C11">
-        <v>55.11598462679832</v>
+        <v>54.46329494614861</v>
       </c>
       <c r="D11">
-        <v>22.63132237950178</v>
+        <v>22.36527736917794</v>
       </c>
       <c r="E11">
         <v>0.9990000000000001</v>
@@ -680,7 +680,7 @@
         <v>0.9990000000000001</v>
       </c>
       <c r="G11">
-        <v>0.6530627641415347</v>
+        <v>0.6374167754910727</v>
       </c>
       <c r="H11">
         <v>0.9990000000000001</v>
@@ -720,10 +720,10 @@
         <v>13</v>
       </c>
       <c r="C13">
-        <v>35.55253325775063</v>
+        <v>35.34861984342005</v>
       </c>
       <c r="D13">
-        <v>18.58012322989026</v>
+        <v>18.4210682696374</v>
       </c>
       <c r="E13">
         <v>0.99965481</v>
@@ -732,7 +732,7 @@
         <v>0.99965481</v>
       </c>
       <c r="G13">
-        <v>0.2093112941810997</v>
+        <v>0.1983335735119973</v>
       </c>
       <c r="H13">
         <v>0.9985622199999999</v>
@@ -772,10 +772,10 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>28.17914652889119</v>
+        <v>28.18683291196891</v>
       </c>
       <c r="D15">
-        <v>23.63965269874433</v>
+        <v>23.6483998882051</v>
       </c>
       <c r="E15">
         <v>1.000319473</v>
@@ -784,7 +784,7 @@
         <v>1.000319473</v>
       </c>
       <c r="G15">
-        <v>0.03075054737156169</v>
+        <v>0.03515556845477841</v>
       </c>
       <c r="H15">
         <v>1.000319473</v>
@@ -824,10 +824,10 @@
         <v>15</v>
       </c>
       <c r="C17">
-        <v>40.44575884225483</v>
+        <v>40.29323614420296</v>
       </c>
       <c r="D17">
-        <v>21.12949357071461</v>
+        <v>21.04019558141839</v>
       </c>
       <c r="E17">
         <v>0.9990972199999999</v>
@@ -836,7 +836,7 @@
         <v>0.9990972199999999</v>
       </c>
       <c r="G17">
-        <v>0.218422333440373</v>
+        <v>0.2127326113294077</v>
       </c>
       <c r="H17">
         <v>0.99752223</v>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -460,10 +460,10 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>51.56478316903839</v>
+        <v>51.34694149050806</v>
       </c>
       <c r="D3">
-        <v>25.22551174390981</v>
+        <v>25.13059807451218</v>
       </c>
       <c r="E3">
         <v>0.9262</v>
@@ -472,7 +472,7 @@
         <v>0.9262</v>
       </c>
       <c r="G3">
-        <v>0.3495752436656974</v>
+        <v>0.3474943913960218</v>
       </c>
       <c r="H3">
         <v>0.9262</v>
@@ -512,10 +512,10 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>34.52083917991418</v>
+        <v>34.47372961228716</v>
       </c>
       <c r="D5">
-        <v>25.97424315228389</v>
+        <v>25.93900921823723</v>
       </c>
       <c r="E5">
         <v>0.9983000000000001</v>
@@ -524,7 +524,7 @@
         <v>0.9983000000000001</v>
       </c>
       <c r="G5">
-        <v>0.05547054452396849</v>
+        <v>0.05377970254116637</v>
       </c>
       <c r="H5">
         <v>0.9983000000000001</v>
@@ -564,10 +564,10 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>36.36684428102582</v>
+        <v>36.27451305589771</v>
       </c>
       <c r="D7">
-        <v>22.33401381209434</v>
+        <v>22.23970770609628</v>
       </c>
       <c r="E7">
         <v>0.9990772499999999</v>
@@ -576,7 +576,7 @@
         <v>0.9990772499999999</v>
       </c>
       <c r="G7">
-        <v>0.1523922554110018</v>
+        <v>0.1477135584928815</v>
       </c>
       <c r="H7">
         <v>0.9990772499999999</v>
@@ -616,10 +616,10 @@
         <v>11</v>
       </c>
       <c r="C9">
-        <v>50.70834670626966</v>
+        <v>50.34760075742022</v>
       </c>
       <c r="D9">
-        <v>23.08855917397172</v>
+        <v>22.94525627489015</v>
       </c>
       <c r="E9">
         <v>0.9996</v>
@@ -628,7 +628,7 @@
         <v>0.9996</v>
       </c>
       <c r="G9">
-        <v>0.4963701820770494</v>
+        <v>0.4867399361068332</v>
       </c>
       <c r="H9">
         <v>0.9996</v>
@@ -668,10 +668,10 @@
         <v>12</v>
       </c>
       <c r="C11">
-        <v>54.46329494614861</v>
+        <v>54.16037128780655</v>
       </c>
       <c r="D11">
-        <v>22.36527736917794</v>
+        <v>22.25529157379935</v>
       </c>
       <c r="E11">
         <v>0.9990000000000001</v>
@@ -680,7 +680,7 @@
         <v>0.9990000000000001</v>
       </c>
       <c r="G11">
-        <v>0.6374167754910727</v>
+        <v>0.6262969735701496</v>
       </c>
       <c r="H11">
         <v>0.9990000000000001</v>
@@ -720,10 +720,10 @@
         <v>13</v>
       </c>
       <c r="C13">
-        <v>35.34861984342005</v>
+        <v>35.40871410092445</v>
       </c>
       <c r="D13">
-        <v>18.4210682696374</v>
+        <v>18.46760858956754</v>
       </c>
       <c r="E13">
         <v>0.99965481</v>
@@ -732,7 +732,7 @@
         <v>0.99965481</v>
       </c>
       <c r="G13">
-        <v>0.1983335735119973</v>
+        <v>0.2003028680657042</v>
       </c>
       <c r="H13">
         <v>0.9985622199999999</v>
@@ -772,10 +772,10 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>28.18683291196891</v>
+        <v>28.14893529114358</v>
       </c>
       <c r="D15">
-        <v>23.6483998882051</v>
+        <v>23.61483282101901</v>
       </c>
       <c r="E15">
         <v>1.000319473</v>
@@ -784,7 +784,7 @@
         <v>1.000319473</v>
       </c>
       <c r="G15">
-        <v>0.03515556845477841</v>
+        <v>0.03564491824293681</v>
       </c>
       <c r="H15">
         <v>1.000319473</v>
@@ -824,10 +824,10 @@
         <v>15</v>
       </c>
       <c r="C17">
-        <v>40.29323614420296</v>
+        <v>40.15360978689686</v>
       </c>
       <c r="D17">
-        <v>21.04019558141839</v>
+        <v>20.94424390550297</v>
       </c>
       <c r="E17">
         <v>0.9990972199999999</v>
@@ -836,7 +836,7 @@
         <v>0.9990972199999999</v>
       </c>
       <c r="G17">
-        <v>0.2127326113294077</v>
+        <v>0.2065572406266487</v>
       </c>
       <c r="H17">
         <v>0.99752223</v>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -460,10 +460,10 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>51.34694149050806</v>
+        <v>51.06151185025473</v>
       </c>
       <c r="D3">
-        <v>25.13059807451218</v>
+        <v>24.98793955767349</v>
       </c>
       <c r="E3">
         <v>0.9262</v>
@@ -472,7 +472,7 @@
         <v>0.9262</v>
       </c>
       <c r="G3">
-        <v>0.3474943913960218</v>
+        <v>0.3393445520406217</v>
       </c>
       <c r="H3">
         <v>0.9262</v>
@@ -512,10 +512,10 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>34.47372961228716</v>
+        <v>34.48700080215669</v>
       </c>
       <c r="D5">
-        <v>25.93900921823723</v>
+        <v>25.93236052401743</v>
       </c>
       <c r="E5">
         <v>0.9983000000000001</v>
@@ -524,7 +524,7 @@
         <v>0.9983000000000001</v>
       </c>
       <c r="G5">
-        <v>0.05377970254116637</v>
+        <v>0.05294566434982895</v>
       </c>
       <c r="H5">
         <v>0.9983000000000001</v>
@@ -564,10 +564,10 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>36.27451305589771</v>
+        <v>36.23625335408025</v>
       </c>
       <c r="D7">
-        <v>22.23970770609628</v>
+        <v>22.17038974430253</v>
       </c>
       <c r="E7">
         <v>0.9990772499999999</v>
@@ -576,7 +576,7 @@
         <v>0.9990772499999999</v>
       </c>
       <c r="G7">
-        <v>0.1477135584928815</v>
+        <v>0.1452803171387027</v>
       </c>
       <c r="H7">
         <v>0.9990772499999999</v>
@@ -616,10 +616,10 @@
         <v>11</v>
       </c>
       <c r="C9">
-        <v>50.34760075742022</v>
+        <v>49.97926409159241</v>
       </c>
       <c r="D9">
-        <v>22.94525627489015</v>
+        <v>22.76174235586557</v>
       </c>
       <c r="E9">
         <v>0.9996</v>
@@ -628,7 +628,7 @@
         <v>0.9996</v>
       </c>
       <c r="G9">
-        <v>0.4867399361068332</v>
+        <v>0.4752344899493095</v>
       </c>
       <c r="H9">
         <v>0.9996</v>
@@ -668,10 +668,10 @@
         <v>12</v>
       </c>
       <c r="C11">
-        <v>54.16037128780655</v>
+        <v>53.74603149660908</v>
       </c>
       <c r="D11">
-        <v>22.25529157379935</v>
+        <v>22.06505273076886</v>
       </c>
       <c r="E11">
         <v>0.9990000000000001</v>
@@ -680,7 +680,7 @@
         <v>0.9990000000000001</v>
       </c>
       <c r="G11">
-        <v>0.6262969735701496</v>
+        <v>0.6116908319311494</v>
       </c>
       <c r="H11">
         <v>0.9990000000000001</v>
@@ -720,10 +720,10 @@
         <v>13</v>
       </c>
       <c r="C13">
-        <v>35.40871410092445</v>
+        <v>35.31794589666234</v>
       </c>
       <c r="D13">
-        <v>18.46760858956754</v>
+        <v>18.36567109198903</v>
       </c>
       <c r="E13">
         <v>0.99965481</v>
@@ -732,7 +732,7 @@
         <v>0.99965481</v>
       </c>
       <c r="G13">
-        <v>0.2003028680657042</v>
+        <v>0.1954005380939772</v>
       </c>
       <c r="H13">
         <v>0.9985622199999999</v>
@@ -772,10 +772,10 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>28.14893529114358</v>
+        <v>28.20407200184371</v>
       </c>
       <c r="D15">
-        <v>23.61483282101901</v>
+        <v>23.6615166898851</v>
       </c>
       <c r="E15">
         <v>1.000319473</v>
@@ -824,10 +824,10 @@
         <v>15</v>
       </c>
       <c r="C17">
-        <v>40.15360978689686</v>
+        <v>40.00363082227965</v>
       </c>
       <c r="D17">
-        <v>20.94424390550297</v>
+        <v>20.83647107967932</v>
       </c>
       <c r="E17">
         <v>0.9990972199999999</v>
@@ -836,7 +836,7 @@
         <v>0.9990972199999999</v>
       </c>
       <c r="G17">
-        <v>0.2065572406266487</v>
+        <v>0.2001043715678636</v>
       </c>
       <c r="H17">
         <v>0.99752223</v>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -460,10 +460,10 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>51.06151185025473</v>
+        <v>50.74037438838347</v>
       </c>
       <c r="D3">
-        <v>24.98793955767349</v>
+        <v>24.82423654245297</v>
       </c>
       <c r="E3">
         <v>0.9262</v>
@@ -472,7 +472,7 @@
         <v>0.9262</v>
       </c>
       <c r="G3">
-        <v>0.3393445520406217</v>
+        <v>0.3282469378570119</v>
       </c>
       <c r="H3">
         <v>0.9262</v>
@@ -512,10 +512,10 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>34.48700080215669</v>
+        <v>34.43923968212547</v>
       </c>
       <c r="D5">
-        <v>25.93236052401743</v>
+        <v>25.88329416494999</v>
       </c>
       <c r="E5">
         <v>0.9983000000000001</v>
@@ -524,7 +524,7 @@
         <v>0.9983000000000001</v>
       </c>
       <c r="G5">
-        <v>0.05294566434982895</v>
+        <v>0.05087994881826097</v>
       </c>
       <c r="H5">
         <v>0.9983000000000001</v>
@@ -564,10 +564,10 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>36.23625335408025</v>
+        <v>36.22700140525382</v>
       </c>
       <c r="D7">
-        <v>22.17038974430253</v>
+        <v>22.20287279284432</v>
       </c>
       <c r="E7">
         <v>0.9990772499999999</v>
@@ -576,7 +576,7 @@
         <v>0.9990772499999999</v>
       </c>
       <c r="G7">
-        <v>0.1452803171387027</v>
+        <v>0.1456887811346648</v>
       </c>
       <c r="H7">
         <v>0.9990772499999999</v>
@@ -616,10 +616,10 @@
         <v>11</v>
       </c>
       <c r="C9">
-        <v>49.97926409159241</v>
+        <v>49.81400674461786</v>
       </c>
       <c r="D9">
-        <v>22.76174235586557</v>
+        <v>22.69857393603912</v>
       </c>
       <c r="E9">
         <v>0.9996</v>
@@ -628,7 +628,7 @@
         <v>0.9996</v>
       </c>
       <c r="G9">
-        <v>0.4752344899493095</v>
+        <v>0.4706670719327053</v>
       </c>
       <c r="H9">
         <v>0.9996</v>
@@ -668,10 +668,10 @@
         <v>12</v>
       </c>
       <c r="C11">
-        <v>53.74603149660908</v>
+        <v>53.46772993937179</v>
       </c>
       <c r="D11">
-        <v>22.06505273076886</v>
+        <v>21.96258284905942</v>
       </c>
       <c r="E11">
         <v>0.9990000000000001</v>
@@ -680,7 +680,7 @@
         <v>0.9990000000000001</v>
       </c>
       <c r="G11">
-        <v>0.6116908319311494</v>
+        <v>0.6061086388001555</v>
       </c>
       <c r="H11">
         <v>0.9990000000000001</v>
@@ -720,10 +720,10 @@
         <v>13</v>
       </c>
       <c r="C13">
-        <v>35.31794589666234</v>
+        <v>35.20286103862242</v>
       </c>
       <c r="D13">
-        <v>18.36567109198903</v>
+        <v>18.27955239205419</v>
       </c>
       <c r="E13">
         <v>0.99965481</v>
@@ -732,7 +732,7 @@
         <v>0.99965481</v>
       </c>
       <c r="G13">
-        <v>0.1954005380939772</v>
+        <v>0.1899536184524728</v>
       </c>
       <c r="H13">
         <v>0.9985622199999999</v>
@@ -772,10 +772,10 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>28.20407200184371</v>
+        <v>28.18458442796969</v>
       </c>
       <c r="D15">
-        <v>23.6615166898851</v>
+        <v>23.64533744556764</v>
       </c>
       <c r="E15">
         <v>1.000319473</v>
@@ -824,10 +824,10 @@
         <v>15</v>
       </c>
       <c r="C17">
-        <v>40.00363082227965</v>
+        <v>39.92516063883541</v>
       </c>
       <c r="D17">
-        <v>20.83647107967932</v>
+        <v>20.80502156866356</v>
       </c>
       <c r="E17">
         <v>0.9990972199999999</v>
@@ -836,7 +836,7 @@
         <v>0.9990972199999999</v>
       </c>
       <c r="G17">
-        <v>0.2001043715678636</v>
+        <v>0.1983697156864708</v>
       </c>
       <c r="H17">
         <v>0.99752223</v>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -460,10 +460,10 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>50.74037438838347</v>
+        <v>51.82921169635205</v>
       </c>
       <c r="D3">
-        <v>24.82423654245297</v>
+        <v>25.32805827181975</v>
       </c>
       <c r="E3">
         <v>0.9262</v>
@@ -472,7 +472,7 @@
         <v>0.9262</v>
       </c>
       <c r="G3">
-        <v>0.3282469378570119</v>
+        <v>0.3568580281685669</v>
       </c>
       <c r="H3">
         <v>0.9262</v>
@@ -512,22 +512,22 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>34.43923968212547</v>
+        <v>34.50204921141101</v>
       </c>
       <c r="D5">
-        <v>25.88329416494999</v>
+        <v>25.94535229304585</v>
       </c>
       <c r="E5">
-        <v>0.9983000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="F5">
-        <v>0.9983000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="G5">
-        <v>0.05087994881826097</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H5">
-        <v>0.9983000000000001</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -564,10 +564,10 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>36.22700140525382</v>
+        <v>36.44753722959613</v>
       </c>
       <c r="D7">
-        <v>22.20287279284432</v>
+        <v>22.40292401789388</v>
       </c>
       <c r="E7">
         <v>0.9990772499999999</v>
@@ -576,7 +576,7 @@
         <v>0.9990772499999999</v>
       </c>
       <c r="G7">
-        <v>0.1456887811346648</v>
+        <v>0.154964342628132</v>
       </c>
       <c r="H7">
         <v>0.9990772499999999</v>
@@ -616,10 +616,10 @@
         <v>11</v>
       </c>
       <c r="C9">
-        <v>49.81400674461786</v>
+        <v>50.89464485280568</v>
       </c>
       <c r="D9">
-        <v>22.69857393603912</v>
+        <v>23.21558303176282</v>
       </c>
       <c r="E9">
         <v>0.9996</v>
@@ -628,7 +628,7 @@
         <v>0.9996</v>
       </c>
       <c r="G9">
-        <v>0.4706670719327053</v>
+        <v>0.5034825029548833</v>
       </c>
       <c r="H9">
         <v>0.9996</v>
@@ -668,10 +668,10 @@
         <v>12</v>
       </c>
       <c r="C11">
-        <v>53.46772993937179</v>
+        <v>54.77380642078597</v>
       </c>
       <c r="D11">
-        <v>21.96258284905942</v>
+        <v>22.55192940254518</v>
       </c>
       <c r="E11">
         <v>0.9990000000000001</v>
@@ -680,7 +680,7 @@
         <v>0.9990000000000001</v>
       </c>
       <c r="G11">
-        <v>0.6061086388001555</v>
+        <v>0.6459175880844941</v>
       </c>
       <c r="H11">
         <v>0.9990000000000001</v>
@@ -720,10 +720,10 @@
         <v>13</v>
       </c>
       <c r="C13">
-        <v>35.20286103862242</v>
+        <v>35.71584102184062</v>
       </c>
       <c r="D13">
-        <v>18.27955239205419</v>
+        <v>18.62432950231353</v>
       </c>
       <c r="E13">
         <v>0.99965481</v>
@@ -732,7 +732,7 @@
         <v>0.99965481</v>
       </c>
       <c r="G13">
-        <v>0.1899536184524728</v>
+        <v>0.2104844827747143</v>
       </c>
       <c r="H13">
         <v>0.9985622199999999</v>
@@ -772,10 +772,10 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>28.18458442796969</v>
+        <v>28.17715727830483</v>
       </c>
       <c r="D15">
-        <v>23.64533744556764</v>
+        <v>23.63894513078866</v>
       </c>
       <c r="E15">
         <v>1.000319473</v>
@@ -784,7 +784,7 @@
         <v>1.000319473</v>
       </c>
       <c r="G15">
-        <v>0.03564491824293681</v>
+        <v>0.03515547182056333</v>
       </c>
       <c r="H15">
         <v>1.000319473</v>
@@ -824,10 +824,10 @@
         <v>15</v>
       </c>
       <c r="C17">
-        <v>39.92516063883541</v>
+        <v>40.32854894972581</v>
       </c>
       <c r="D17">
-        <v>20.80502156866356</v>
+        <v>21.09133998298594</v>
       </c>
       <c r="E17">
         <v>0.9990972199999999</v>
@@ -836,7 +836,7 @@
         <v>0.9990972199999999</v>
       </c>
       <c r="G17">
-        <v>0.1983697156864708</v>
+        <v>0.2156468205051487</v>
       </c>
       <c r="H17">
         <v>0.99752223</v>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="16">
   <si>
     <t>Date</t>
   </si>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -480,106 +480,106 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>34.64560932909123</v>
+        <v>52.28471716753184</v>
       </c>
       <c r="D4">
-        <v>26.08311546080494</v>
+        <v>25.54525144150689</v>
       </c>
       <c r="E4">
-        <v>0.9983000000000001</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="F4">
-        <v>0.9983000000000001</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="G4">
-        <v>0.06258613715048233</v>
+        <v>0.378012896547947</v>
       </c>
       <c r="H4">
-        <v>0.9983000000000001</v>
+        <v>0.9262000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
       <c r="C5">
-        <v>34.50204921141101</v>
+        <v>34.64560932909123</v>
       </c>
       <c r="D5">
-        <v>25.94535229304585</v>
+        <v>26.08311546080494</v>
       </c>
       <c r="E5">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="F5">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="G5">
-        <v>0.05768943168306073</v>
+        <v>0.06258613715048233</v>
       </c>
       <c r="H5">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>36.55790859258162</v>
+        <v>34.50204921141101</v>
       </c>
       <c r="D6">
-        <v>22.67181120908155</v>
+        <v>25.94535229304585</v>
       </c>
       <c r="E6">
-        <v>0.9990740999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F6">
-        <v>0.9990740999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G6">
-        <v>0.1648443271746771</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H6">
-        <v>0.9990740999999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>36.44753722959613</v>
+        <v>35.10429483281073</v>
       </c>
       <c r="D7">
-        <v>22.40292401789388</v>
+        <v>26.43864879939599</v>
       </c>
       <c r="E7">
-        <v>0.9990772499999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F7">
-        <v>0.9990772499999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G7">
-        <v>0.154964342628132</v>
+        <v>0.07926550001722021</v>
       </c>
       <c r="H7">
-        <v>0.9990772499999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -587,25 +587,25 @@
         <v>46153</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8">
-        <v>52.70832779833182</v>
+        <v>36.55790859258162</v>
       </c>
       <c r="D8">
-        <v>23.99044674439659</v>
+        <v>22.67181120908155</v>
       </c>
       <c r="E8">
-        <v>0.9994000000000002</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="F8">
-        <v>0.9994000000000002</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="G8">
-        <v>0.5438253854918791</v>
+        <v>0.1648443271746771</v>
       </c>
       <c r="H8">
-        <v>0.9994000000000002</v>
+        <v>0.9990740999999999</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -613,129 +613,129 @@
         <v>46154</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9">
-        <v>50.89464485280568</v>
+        <v>36.44753722959613</v>
       </c>
       <c r="D9">
-        <v>23.21558303176282</v>
+        <v>22.40292401789388</v>
       </c>
       <c r="E9">
-        <v>0.9996</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="F9">
-        <v>0.9996</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="G9">
-        <v>0.5034825029548833</v>
+        <v>0.154964342628132</v>
       </c>
       <c r="H9">
-        <v>0.9996</v>
+        <v>0.9990772499999999</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C10">
-        <v>57.1732166855686</v>
+        <v>36.63128514035871</v>
       </c>
       <c r="D10">
-        <v>23.50022751267814</v>
+        <v>22.65773388934668</v>
       </c>
       <c r="E10">
-        <v>0.9991</v>
+        <v>0.99907745</v>
       </c>
       <c r="F10">
-        <v>0.9991</v>
+        <v>0.99907745</v>
       </c>
       <c r="G10">
-        <v>0.6994110097039083</v>
+        <v>0.1671633421405267</v>
       </c>
       <c r="H10">
-        <v>0.9991</v>
+        <v>0.99907745</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11">
-        <v>54.77380642078597</v>
+        <v>52.70832779833182</v>
       </c>
       <c r="D11">
-        <v>22.55192940254518</v>
+        <v>23.99044674439659</v>
       </c>
       <c r="E11">
-        <v>0.9990000000000001</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="F11">
-        <v>0.9990000000000001</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="G11">
-        <v>0.6459175880844941</v>
+        <v>0.5438253854918791</v>
       </c>
       <c r="H11">
-        <v>0.9990000000000001</v>
+        <v>0.9994000000000002</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C12">
-        <v>35.78646526282436</v>
+        <v>50.89464485280568</v>
       </c>
       <c r="D12">
-        <v>18.96635091925032</v>
+        <v>23.21558303176282</v>
       </c>
       <c r="E12">
-        <v>0.9996491399999999</v>
+        <v>0.9996</v>
       </c>
       <c r="F12">
-        <v>0.9996491399999999</v>
+        <v>0.9996</v>
       </c>
       <c r="G12">
-        <v>0.2240600969213613</v>
+        <v>0.5034825029548833</v>
       </c>
       <c r="H12">
-        <v>0.9985614899999999</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C13">
-        <v>35.71584102184062</v>
+        <v>51.8659994471731</v>
       </c>
       <c r="D13">
-        <v>18.62432950231353</v>
+        <v>23.7009037279043</v>
       </c>
       <c r="E13">
-        <v>0.99965481</v>
+        <v>1.0002</v>
       </c>
       <c r="F13">
-        <v>0.99965481</v>
+        <v>1.0002</v>
       </c>
       <c r="G13">
-        <v>0.2104844827747143</v>
+        <v>0.533512029714132</v>
       </c>
       <c r="H13">
-        <v>0.9985622199999999</v>
+        <v>1.0002</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -743,25 +743,25 @@
         <v>46153</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C14">
-        <v>28.12253390077671</v>
+        <v>57.1732166855686</v>
       </c>
       <c r="D14">
-        <v>23.58699683751922</v>
+        <v>23.50022751267814</v>
       </c>
       <c r="E14">
-        <v>0.9997295369999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F14">
-        <v>0.9997295369999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G14">
-        <v>0.03368732240295347</v>
+        <v>0.6994110097039083</v>
       </c>
       <c r="H14">
-        <v>0.9997295369999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -769,77 +769,285 @@
         <v>46154</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C15">
-        <v>28.17715727830483</v>
+        <v>54.77380642078597</v>
       </c>
       <c r="D15">
-        <v>23.63894513078866</v>
+        <v>22.55192940254518</v>
       </c>
       <c r="E15">
-        <v>1.000319473</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F15">
-        <v>1.000319473</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G15">
-        <v>0.03515547182056333</v>
+        <v>0.6459175880844941</v>
       </c>
       <c r="H15">
-        <v>1.000319473</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C16">
-        <v>40.68830633303975</v>
+        <v>56.32187380830906</v>
       </c>
       <c r="D16">
-        <v>21.50431773660198</v>
+        <v>23.17121437414109</v>
       </c>
       <c r="E16">
-        <v>0.99909852</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F16">
-        <v>0.99909852</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G16">
-        <v>0.2342423866086769</v>
+        <v>0.6851523922954754</v>
       </c>
       <c r="H16">
-        <v>0.9974930900000001</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17">
+        <v>35.78646526282436</v>
+      </c>
+      <c r="D17">
+        <v>18.96635091925032</v>
+      </c>
+      <c r="E17">
+        <v>0.9996491399999999</v>
+      </c>
+      <c r="F17">
+        <v>0.9996491399999999</v>
+      </c>
+      <c r="G17">
+        <v>0.2240600969213613</v>
+      </c>
+      <c r="H17">
+        <v>0.9985614899999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="1">
         <v>46154</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18">
+        <v>35.71584102184062</v>
+      </c>
+      <c r="D18">
+        <v>18.62432950231353</v>
+      </c>
+      <c r="E18">
+        <v>0.99965481</v>
+      </c>
+      <c r="F18">
+        <v>0.99965481</v>
+      </c>
+      <c r="G18">
+        <v>0.2104844827747143</v>
+      </c>
+      <c r="H18">
+        <v>0.9985622199999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19">
+        <v>35.95182028203252</v>
+      </c>
+      <c r="D19">
+        <v>18.95670796791552</v>
+      </c>
+      <c r="E19">
+        <v>0.9996515200000001</v>
+      </c>
+      <c r="F19">
+        <v>0.9996515200000001</v>
+      </c>
+      <c r="G19">
+        <v>0.2259035693959275</v>
+      </c>
+      <c r="H19">
+        <v>0.99855193</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20">
+        <v>28.12253390077671</v>
+      </c>
+      <c r="D20">
+        <v>23.58699683751922</v>
+      </c>
+      <c r="E20">
+        <v>0.9997295369999999</v>
+      </c>
+      <c r="F20">
+        <v>0.9997295369999999</v>
+      </c>
+      <c r="G20">
+        <v>0.03368732240295347</v>
+      </c>
+      <c r="H20">
+        <v>0.9997295369999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21">
+        <v>28.17715727830483</v>
+      </c>
+      <c r="D21">
+        <v>23.63894513078866</v>
+      </c>
+      <c r="E21">
+        <v>1.000319473</v>
+      </c>
+      <c r="F21">
+        <v>1.000319473</v>
+      </c>
+      <c r="G21">
+        <v>0.03515547182056333</v>
+      </c>
+      <c r="H21">
+        <v>1.000319473</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22">
+        <v>28.59002627414054</v>
+      </c>
+      <c r="D22">
+        <v>23.96230704059692</v>
+      </c>
+      <c r="E22">
+        <v>0.9999999989999999</v>
+      </c>
+      <c r="F22">
+        <v>0.9999999989999999</v>
+      </c>
+      <c r="G22">
+        <v>0.05179637495949674</v>
+      </c>
+      <c r="H22">
+        <v>0.9999999989999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B23" t="s">
         <v>15</v>
       </c>
-      <c r="C17">
+      <c r="C23">
+        <v>40.68830633303975</v>
+      </c>
+      <c r="D23">
+        <v>21.50431773660198</v>
+      </c>
+      <c r="E23">
+        <v>0.99909852</v>
+      </c>
+      <c r="F23">
+        <v>0.99909852</v>
+      </c>
+      <c r="G23">
+        <v>0.2342423866086769</v>
+      </c>
+      <c r="H23">
+        <v>0.9974930900000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B24" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24">
         <v>40.32854894972581</v>
       </c>
-      <c r="D17">
+      <c r="D24">
         <v>21.09133998298594</v>
       </c>
-      <c r="E17">
+      <c r="E24">
         <v>0.9990972199999999</v>
       </c>
-      <c r="F17">
+      <c r="F24">
         <v>0.9990972199999999</v>
       </c>
-      <c r="G17">
+      <c r="G24">
         <v>0.2156468205051487</v>
       </c>
-      <c r="H17">
+      <c r="H24">
         <v>0.99752223</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25">
+        <v>40.47987921095815</v>
+      </c>
+      <c r="D25">
+        <v>21.35995364434454</v>
+      </c>
+      <c r="E25">
+        <v>0.9991780100000001</v>
+      </c>
+      <c r="F25">
+        <v>0.9991780100000001</v>
+      </c>
+      <c r="G25">
+        <v>0.2270956128473374</v>
+      </c>
+      <c r="H25">
+        <v>0.9975825700000001</v>
       </c>
     </row>
   </sheetData>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="16">
   <si>
     <t>Date</t>
   </si>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -506,68 +506,68 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>34.64560932909123</v>
+        <v>53.87287273813902</v>
       </c>
       <c r="D5">
-        <v>26.08311546080494</v>
+        <v>26.32154226438612</v>
       </c>
       <c r="E5">
-        <v>0.9983000000000001</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="F5">
-        <v>0.9983000000000001</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="G5">
-        <v>0.06258613715048233</v>
+        <v>0.4166811087612758</v>
       </c>
       <c r="H5">
-        <v>0.9983000000000001</v>
+        <v>0.9251999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
       </c>
       <c r="C6">
-        <v>34.50204921141101</v>
+        <v>34.64560932909123</v>
       </c>
       <c r="D6">
-        <v>25.94535229304585</v>
+        <v>26.08311546080494</v>
       </c>
       <c r="E6">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="F6">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="G6">
-        <v>0.05768943168306073</v>
+        <v>0.06258613715048233</v>
       </c>
       <c r="H6">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
       </c>
       <c r="C7">
-        <v>35.10429483281073</v>
+        <v>34.50204921141101</v>
       </c>
       <c r="D7">
-        <v>26.43864879939599</v>
+        <v>25.94535229304585</v>
       </c>
       <c r="E7">
         <v>0.9984</v>
@@ -576,7 +576,7 @@
         <v>0.9984</v>
       </c>
       <c r="G7">
-        <v>0.07926550001722021</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H7">
         <v>0.9984</v>
@@ -584,158 +584,158 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8">
-        <v>36.55790859258162</v>
+        <v>35.10429483281073</v>
       </c>
       <c r="D8">
-        <v>22.67181120908155</v>
+        <v>26.43864879939599</v>
       </c>
       <c r="E8">
-        <v>0.9990740999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F8">
-        <v>0.9990740999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G8">
-        <v>0.1648443271746771</v>
+        <v>0.07926550001722021</v>
       </c>
       <c r="H8">
-        <v>0.9990740999999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9">
-        <v>36.44753722959613</v>
+        <v>35.36860632820093</v>
       </c>
       <c r="D9">
-        <v>22.40292401789388</v>
+        <v>26.56575571102338</v>
       </c>
       <c r="E9">
-        <v>0.9990772499999999</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="F9">
-        <v>0.9990772499999999</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="G9">
-        <v>0.154964342628132</v>
+        <v>0.08553946591902095</v>
       </c>
       <c r="H9">
-        <v>0.9990772499999999</v>
+        <v>0.9985999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
       </c>
       <c r="C10">
-        <v>36.63128514035871</v>
+        <v>36.55790859258162</v>
       </c>
       <c r="D10">
-        <v>22.65773388934668</v>
+        <v>22.67181120908155</v>
       </c>
       <c r="E10">
-        <v>0.99907745</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="F10">
-        <v>0.99907745</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="G10">
-        <v>0.1671633421405267</v>
+        <v>0.1648443271746771</v>
       </c>
       <c r="H10">
-        <v>0.99907745</v>
+        <v>0.9990740999999999</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11">
-        <v>52.70832779833182</v>
+        <v>36.44753722959613</v>
       </c>
       <c r="D11">
-        <v>23.99044674439659</v>
+        <v>22.40292401789388</v>
       </c>
       <c r="E11">
-        <v>0.9994000000000002</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="F11">
-        <v>0.9994000000000002</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="G11">
-        <v>0.5438253854918791</v>
+        <v>0.154964342628132</v>
       </c>
       <c r="H11">
-        <v>0.9994000000000002</v>
+        <v>0.9990772499999999</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12">
-        <v>50.89464485280568</v>
+        <v>36.63128514035871</v>
       </c>
       <c r="D12">
-        <v>23.21558303176282</v>
+        <v>22.65773388934668</v>
       </c>
       <c r="E12">
-        <v>0.9996</v>
+        <v>0.99907745</v>
       </c>
       <c r="F12">
-        <v>0.9996</v>
+        <v>0.99907745</v>
       </c>
       <c r="G12">
-        <v>0.5034825029548833</v>
+        <v>0.1671633421405267</v>
       </c>
       <c r="H12">
-        <v>0.9996</v>
+        <v>0.99907745</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13">
-        <v>51.8659994471731</v>
+        <v>36.87865927427314</v>
       </c>
       <c r="D13">
-        <v>23.7009037279043</v>
+        <v>22.69755646854794</v>
       </c>
       <c r="E13">
-        <v>1.0002</v>
+        <v>0.99908601</v>
       </c>
       <c r="F13">
-        <v>1.0002</v>
+        <v>0.99908601</v>
       </c>
       <c r="G13">
-        <v>0.533512029714132</v>
+        <v>0.1754592080224002</v>
       </c>
       <c r="H13">
-        <v>1.0002</v>
+        <v>0.99908601</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -743,25 +743,25 @@
         <v>46153</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14">
-        <v>57.1732166855686</v>
+        <v>52.70832779833182</v>
       </c>
       <c r="D14">
-        <v>23.50022751267814</v>
+        <v>23.99044674439659</v>
       </c>
       <c r="E14">
-        <v>0.9991</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="F14">
-        <v>0.9991</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="G14">
-        <v>0.6994110097039083</v>
+        <v>0.5438253854918791</v>
       </c>
       <c r="H14">
-        <v>0.9991</v>
+        <v>0.9994000000000002</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -769,25 +769,25 @@
         <v>46154</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15">
-        <v>54.77380642078597</v>
+        <v>50.89464485280568</v>
       </c>
       <c r="D15">
-        <v>22.55192940254518</v>
+        <v>23.21558303176282</v>
       </c>
       <c r="E15">
-        <v>0.9990000000000001</v>
+        <v>0.9996</v>
       </c>
       <c r="F15">
-        <v>0.9990000000000001</v>
+        <v>0.9996</v>
       </c>
       <c r="G15">
-        <v>0.6459175880844941</v>
+        <v>0.5034825029548833</v>
       </c>
       <c r="H15">
-        <v>0.9990000000000001</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -795,259 +795,467 @@
         <v>46155</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C16">
-        <v>56.32187380830906</v>
+        <v>51.8659994471731</v>
       </c>
       <c r="D16">
-        <v>23.17121437414109</v>
+        <v>23.7009037279043</v>
       </c>
       <c r="E16">
-        <v>0.9990000000000001</v>
+        <v>1.0002</v>
       </c>
       <c r="F16">
-        <v>0.9990000000000001</v>
+        <v>1.0002</v>
       </c>
       <c r="G16">
-        <v>0.6851523922954754</v>
+        <v>0.533512029714132</v>
       </c>
       <c r="H16">
-        <v>0.9990000000000001</v>
+        <v>1.0002</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17">
-        <v>35.78646526282436</v>
+        <v>52.4470179952828</v>
       </c>
       <c r="D17">
-        <v>18.96635091925032</v>
+        <v>23.76861704536814</v>
       </c>
       <c r="E17">
-        <v>0.9996491399999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F17">
-        <v>0.9996491399999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G17">
-        <v>0.2240600969213613</v>
+        <v>0.5492634496849078</v>
       </c>
       <c r="H17">
-        <v>0.9985614899999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C18">
-        <v>35.71584102184062</v>
+        <v>57.1732166855686</v>
       </c>
       <c r="D18">
-        <v>18.62432950231353</v>
+        <v>23.50022751267814</v>
       </c>
       <c r="E18">
-        <v>0.99965481</v>
+        <v>0.9991</v>
       </c>
       <c r="F18">
-        <v>0.99965481</v>
+        <v>0.9991</v>
       </c>
       <c r="G18">
-        <v>0.2104844827747143</v>
+        <v>0.6994110097039083</v>
       </c>
       <c r="H18">
-        <v>0.9985622199999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C19">
-        <v>35.95182028203252</v>
+        <v>54.77380642078597</v>
       </c>
       <c r="D19">
-        <v>18.95670796791552</v>
+        <v>22.55192940254518</v>
       </c>
       <c r="E19">
-        <v>0.9996515200000001</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F19">
-        <v>0.9996515200000001</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G19">
-        <v>0.2259035693959275</v>
+        <v>0.6459175880844941</v>
       </c>
       <c r="H19">
-        <v>0.99855193</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C20">
-        <v>28.12253390077671</v>
+        <v>56.32187380830906</v>
       </c>
       <c r="D20">
-        <v>23.58699683751922</v>
+        <v>23.17121437414109</v>
       </c>
       <c r="E20">
-        <v>0.9997295369999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F20">
-        <v>0.9997295369999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G20">
-        <v>0.03368732240295347</v>
+        <v>0.6851523922954754</v>
       </c>
       <c r="H20">
-        <v>0.9997295369999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B21" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C21">
-        <v>28.17715727830483</v>
+        <v>56.15321618553139</v>
       </c>
       <c r="D21">
-        <v>23.63894513078866</v>
+        <v>22.95838347314443</v>
       </c>
       <c r="E21">
-        <v>1.000319473</v>
+        <v>0.9992</v>
       </c>
       <c r="F21">
-        <v>1.000319473</v>
+        <v>0.9992</v>
       </c>
       <c r="G21">
-        <v>0.03515547182056333</v>
+        <v>0.6907028507208208</v>
       </c>
       <c r="H21">
-        <v>1.000319473</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="B22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C22">
-        <v>28.59002627414054</v>
+        <v>35.78646526282436</v>
       </c>
       <c r="D22">
-        <v>23.96230704059692</v>
+        <v>18.96635091925032</v>
       </c>
       <c r="E22">
-        <v>0.9999999989999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="F22">
-        <v>0.9999999989999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="G22">
-        <v>0.05179637495949674</v>
+        <v>0.2240600969213613</v>
       </c>
       <c r="H22">
-        <v>0.9999999989999999</v>
+        <v>0.9985614899999999</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C23">
-        <v>40.68830633303975</v>
+        <v>35.71584102184062</v>
       </c>
       <c r="D23">
-        <v>21.50431773660198</v>
+        <v>18.62432950231353</v>
       </c>
       <c r="E23">
-        <v>0.99909852</v>
+        <v>0.99965481</v>
       </c>
       <c r="F23">
-        <v>0.99909852</v>
+        <v>0.99965481</v>
       </c>
       <c r="G23">
-        <v>0.2342423866086769</v>
+        <v>0.2104844827747143</v>
       </c>
       <c r="H23">
-        <v>0.9974930900000001</v>
+        <v>0.9985622199999999</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C24">
-        <v>40.32854894972581</v>
+        <v>35.95182028203252</v>
       </c>
       <c r="D24">
-        <v>21.09133998298594</v>
+        <v>18.95670796791552</v>
       </c>
       <c r="E24">
-        <v>0.9990972199999999</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="F24">
-        <v>0.9990972199999999</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="G24">
-        <v>0.2156468205051487</v>
+        <v>0.2259035693959275</v>
       </c>
       <c r="H24">
-        <v>0.99752223</v>
+        <v>0.99855193</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25">
+        <v>36.14451597805883</v>
+      </c>
+      <c r="D25">
+        <v>18.86297660538653</v>
+      </c>
+      <c r="E25">
+        <v>0.9996563399999999</v>
+      </c>
+      <c r="F25">
+        <v>0.9996563399999999</v>
+      </c>
+      <c r="G25">
+        <v>0.2362110061840785</v>
+      </c>
+      <c r="H25">
+        <v>0.99857265</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26">
+        <v>28.12253390077671</v>
+      </c>
+      <c r="D26">
+        <v>23.58699683751922</v>
+      </c>
+      <c r="E26">
+        <v>0.9997295369999999</v>
+      </c>
+      <c r="F26">
+        <v>0.9997295369999999</v>
+      </c>
+      <c r="G26">
+        <v>0.03368732240295347</v>
+      </c>
+      <c r="H26">
+        <v>0.9997295369999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27">
+        <v>28.17715727830483</v>
+      </c>
+      <c r="D27">
+        <v>23.63894513078866</v>
+      </c>
+      <c r="E27">
+        <v>1.000319473</v>
+      </c>
+      <c r="F27">
+        <v>1.000319473</v>
+      </c>
+      <c r="G27">
+        <v>0.03515547182056333</v>
+      </c>
+      <c r="H27">
+        <v>1.000319473</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="1">
         <v>46155</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28">
+        <v>28.59002627414054</v>
+      </c>
+      <c r="D28">
+        <v>23.96230704059692</v>
+      </c>
+      <c r="E28">
+        <v>0.9999999989999999</v>
+      </c>
+      <c r="F28">
+        <v>0.9999999989999999</v>
+      </c>
+      <c r="G28">
+        <v>0.05179637495949674</v>
+      </c>
+      <c r="H28">
+        <v>0.9999999989999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29">
+        <v>28.56217859389523</v>
+      </c>
+      <c r="D29">
+        <v>23.9411987302529</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>0.04837024516756849</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B30" t="s">
         <v>15</v>
       </c>
-      <c r="C25">
+      <c r="C30">
+        <v>40.68830633303975</v>
+      </c>
+      <c r="D30">
+        <v>21.50431773660198</v>
+      </c>
+      <c r="E30">
+        <v>0.99909852</v>
+      </c>
+      <c r="F30">
+        <v>0.99909852</v>
+      </c>
+      <c r="G30">
+        <v>0.2342423866086769</v>
+      </c>
+      <c r="H30">
+        <v>0.9974930900000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B31" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31">
+        <v>40.32854894972581</v>
+      </c>
+      <c r="D31">
+        <v>21.09133998298594</v>
+      </c>
+      <c r="E31">
+        <v>0.9990972199999999</v>
+      </c>
+      <c r="F31">
+        <v>0.9990972199999999</v>
+      </c>
+      <c r="G31">
+        <v>0.2156468205051487</v>
+      </c>
+      <c r="H31">
+        <v>0.99752223</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32">
         <v>40.47987921095815</v>
       </c>
-      <c r="D25">
+      <c r="D32">
         <v>21.35995364434454</v>
       </c>
-      <c r="E25">
+      <c r="E32">
         <v>0.9991780100000001</v>
       </c>
-      <c r="F25">
+      <c r="F32">
         <v>0.9991780100000001</v>
       </c>
-      <c r="G25">
+      <c r="G32">
         <v>0.2270956128473374</v>
       </c>
-      <c r="H25">
+      <c r="H32">
         <v>0.9975825700000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33">
+        <v>41.20436574895244</v>
+      </c>
+      <c r="D33">
+        <v>21.48149674387778</v>
+      </c>
+      <c r="E33">
+        <v>0.9991793299999999</v>
+      </c>
+      <c r="F33">
+        <v>0.9991793299999999</v>
+      </c>
+      <c r="G33">
+        <v>0.2454829228401052</v>
+      </c>
+      <c r="H33">
+        <v>0.99754722</v>
       </c>
     </row>
   </sheetData>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="16">
   <si>
     <t>Date</t>
   </si>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -532,68 +532,68 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>34.64560932909123</v>
+        <v>52.18747148214074</v>
       </c>
       <c r="D6">
-        <v>26.08311546080494</v>
+        <v>25.13616059644496</v>
       </c>
       <c r="E6">
-        <v>0.9983000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="F6">
-        <v>0.9983000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="G6">
-        <v>0.06258613715048233</v>
+        <v>0.3627535778249862</v>
       </c>
       <c r="H6">
-        <v>0.9983000000000001</v>
+        <v>0.9268</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
       </c>
       <c r="C7">
-        <v>34.50204921141101</v>
+        <v>34.64560932909123</v>
       </c>
       <c r="D7">
-        <v>25.94535229304585</v>
+        <v>26.08311546080494</v>
       </c>
       <c r="E7">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="F7">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="G7">
-        <v>0.05768943168306073</v>
+        <v>0.06258613715048233</v>
       </c>
       <c r="H7">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
       </c>
       <c r="C8">
-        <v>35.10429483281073</v>
+        <v>34.50204921141101</v>
       </c>
       <c r="D8">
-        <v>26.43864879939599</v>
+        <v>25.94535229304585</v>
       </c>
       <c r="E8">
         <v>0.9984</v>
@@ -602,7 +602,7 @@
         <v>0.9984</v>
       </c>
       <c r="G8">
-        <v>0.07926550001722021</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H8">
         <v>0.9984</v>
@@ -610,340 +610,340 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
       </c>
       <c r="C9">
-        <v>35.36860632820093</v>
+        <v>35.10429483281073</v>
       </c>
       <c r="D9">
-        <v>26.56575571102338</v>
+        <v>26.43864879939599</v>
       </c>
       <c r="E9">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F9">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G9">
-        <v>0.08553946591902095</v>
+        <v>0.07926550001722021</v>
       </c>
       <c r="H9">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10">
-        <v>36.55790859258162</v>
+        <v>35.36860632820093</v>
       </c>
       <c r="D10">
-        <v>22.67181120908155</v>
+        <v>26.56575571102338</v>
       </c>
       <c r="E10">
-        <v>0.9990740999999999</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="F10">
-        <v>0.9990740999999999</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="G10">
-        <v>0.1648443271746771</v>
+        <v>0.08553946591902095</v>
       </c>
       <c r="H10">
-        <v>0.9990740999999999</v>
+        <v>0.9985999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11">
-        <v>36.44753722959613</v>
+        <v>34.88080083527914</v>
       </c>
       <c r="D11">
-        <v>22.40292401789388</v>
+        <v>26.19322945679072</v>
       </c>
       <c r="E11">
-        <v>0.9990772499999999</v>
+        <v>0.9983</v>
       </c>
       <c r="F11">
-        <v>0.9990772499999999</v>
+        <v>0.9983</v>
       </c>
       <c r="G11">
-        <v>0.154964342628132</v>
+        <v>0.06870693142475881</v>
       </c>
       <c r="H11">
-        <v>0.9990772499999999</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
       </c>
       <c r="C12">
-        <v>36.63128514035871</v>
+        <v>36.55790859258162</v>
       </c>
       <c r="D12">
-        <v>22.65773388934668</v>
+        <v>22.67181120908155</v>
       </c>
       <c r="E12">
-        <v>0.99907745</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="F12">
-        <v>0.99907745</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="G12">
-        <v>0.1671633421405267</v>
+        <v>0.1648443271746771</v>
       </c>
       <c r="H12">
-        <v>0.99907745</v>
+        <v>0.9990740999999999</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
       </c>
       <c r="C13">
-        <v>36.87865927427314</v>
+        <v>36.44753722959613</v>
       </c>
       <c r="D13">
-        <v>22.69755646854794</v>
+        <v>22.40292401789388</v>
       </c>
       <c r="E13">
-        <v>0.99908601</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="F13">
-        <v>0.99908601</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="G13">
-        <v>0.1754592080224002</v>
+        <v>0.154964342628132</v>
       </c>
       <c r="H13">
-        <v>0.99908601</v>
+        <v>0.9990772499999999</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C14">
-        <v>52.70832779833182</v>
+        <v>36.63128514035871</v>
       </c>
       <c r="D14">
-        <v>23.99044674439659</v>
+        <v>22.65773388934668</v>
       </c>
       <c r="E14">
-        <v>0.9994000000000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="F14">
-        <v>0.9994000000000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="G14">
-        <v>0.5438253854918791</v>
+        <v>0.1671633421405267</v>
       </c>
       <c r="H14">
-        <v>0.9994000000000002</v>
+        <v>0.99907745</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C15">
-        <v>50.89464485280568</v>
+        <v>36.87865927427314</v>
       </c>
       <c r="D15">
-        <v>23.21558303176282</v>
+        <v>22.69755646854794</v>
       </c>
       <c r="E15">
-        <v>0.9996</v>
+        <v>0.99908601</v>
       </c>
       <c r="F15">
-        <v>0.9996</v>
+        <v>0.99908601</v>
       </c>
       <c r="G15">
-        <v>0.5034825029548833</v>
+        <v>0.1754592080224002</v>
       </c>
       <c r="H15">
-        <v>0.9996</v>
+        <v>0.99908601</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C16">
-        <v>51.8659994471731</v>
+        <v>36.52208783231286</v>
       </c>
       <c r="D16">
-        <v>23.7009037279043</v>
+        <v>22.32462309676992</v>
       </c>
       <c r="E16">
-        <v>1.0002</v>
+        <v>0.99915499</v>
       </c>
       <c r="F16">
-        <v>1.0002</v>
+        <v>0.99915499</v>
       </c>
       <c r="G16">
-        <v>0.533512029714132</v>
+        <v>0.1577242156354994</v>
       </c>
       <c r="H16">
-        <v>1.0002</v>
+        <v>0.99915499</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="B17" t="s">
         <v>11</v>
       </c>
       <c r="C17">
-        <v>52.4470179952828</v>
+        <v>52.70832779833182</v>
       </c>
       <c r="D17">
-        <v>23.76861704536814</v>
+        <v>23.99044674439659</v>
       </c>
       <c r="E17">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="F17">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="G17">
-        <v>0.5492634496849078</v>
+        <v>0.5438253854918791</v>
       </c>
       <c r="H17">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18">
-        <v>57.1732166855686</v>
+        <v>50.89464485280568</v>
       </c>
       <c r="D18">
-        <v>23.50022751267814</v>
+        <v>23.21558303176282</v>
       </c>
       <c r="E18">
-        <v>0.9991</v>
+        <v>0.9996</v>
       </c>
       <c r="F18">
-        <v>0.9991</v>
+        <v>0.9996</v>
       </c>
       <c r="G18">
-        <v>0.6994110097039083</v>
+        <v>0.5034825029548833</v>
       </c>
       <c r="H18">
-        <v>0.9991</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C19">
-        <v>54.77380642078597</v>
+        <v>51.8659994471731</v>
       </c>
       <c r="D19">
-        <v>22.55192940254518</v>
+        <v>23.7009037279043</v>
       </c>
       <c r="E19">
-        <v>0.9990000000000001</v>
+        <v>1.0002</v>
       </c>
       <c r="F19">
-        <v>0.9990000000000001</v>
+        <v>1.0002</v>
       </c>
       <c r="G19">
-        <v>0.6459175880844941</v>
+        <v>0.533512029714132</v>
       </c>
       <c r="H19">
-        <v>0.9990000000000001</v>
+        <v>1.0002</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C20">
-        <v>56.32187380830906</v>
+        <v>52.4470179952828</v>
       </c>
       <c r="D20">
-        <v>23.17121437414109</v>
+        <v>23.76861704536814</v>
       </c>
       <c r="E20">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
       <c r="F20">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
       <c r="G20">
-        <v>0.6851523922954754</v>
+        <v>0.5492634496849078</v>
       </c>
       <c r="H20">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C21">
-        <v>56.15321618553139</v>
+        <v>50.81077380018606</v>
       </c>
       <c r="D21">
-        <v>22.95838347314443</v>
+        <v>22.76900580927995</v>
       </c>
       <c r="E21">
-        <v>0.9992</v>
+        <v>0.9998</v>
       </c>
       <c r="F21">
-        <v>0.9992</v>
+        <v>0.9998</v>
       </c>
       <c r="G21">
-        <v>0.6907028507208208</v>
+        <v>0.4903296143797722</v>
       </c>
       <c r="H21">
-        <v>0.9992</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -951,25 +951,25 @@
         <v>46153</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C22">
-        <v>35.78646526282436</v>
+        <v>57.1732166855686</v>
       </c>
       <c r="D22">
-        <v>18.96635091925032</v>
+        <v>23.50022751267814</v>
       </c>
       <c r="E22">
-        <v>0.9996491399999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F22">
-        <v>0.9996491399999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G22">
-        <v>0.2240600969213613</v>
+        <v>0.6994110097039083</v>
       </c>
       <c r="H22">
-        <v>0.9985614899999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -977,25 +977,25 @@
         <v>46154</v>
       </c>
       <c r="B23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C23">
-        <v>35.71584102184062</v>
+        <v>54.77380642078597</v>
       </c>
       <c r="D23">
-        <v>18.62432950231353</v>
+        <v>22.55192940254518</v>
       </c>
       <c r="E23">
-        <v>0.99965481</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F23">
-        <v>0.99965481</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G23">
-        <v>0.2104844827747143</v>
+        <v>0.6459175880844941</v>
       </c>
       <c r="H23">
-        <v>0.9985622199999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1003,25 +1003,25 @@
         <v>46155</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C24">
-        <v>35.95182028203252</v>
+        <v>56.32187380830906</v>
       </c>
       <c r="D24">
-        <v>18.95670796791552</v>
+        <v>23.17121437414109</v>
       </c>
       <c r="E24">
-        <v>0.9996515200000001</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F24">
-        <v>0.9996515200000001</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G24">
-        <v>0.2259035693959275</v>
+        <v>0.6851523922954754</v>
       </c>
       <c r="H24">
-        <v>0.99855193</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1029,233 +1029,441 @@
         <v>46156</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C25">
-        <v>36.14451597805883</v>
+        <v>56.15321618553139</v>
       </c>
       <c r="D25">
-        <v>18.86297660538653</v>
+        <v>22.95838347314443</v>
       </c>
       <c r="E25">
-        <v>0.9996563399999999</v>
+        <v>0.9992</v>
       </c>
       <c r="F25">
-        <v>0.9996563399999999</v>
+        <v>0.9992</v>
       </c>
       <c r="G25">
-        <v>0.2362110061840785</v>
+        <v>0.6907028507208208</v>
       </c>
       <c r="H25">
-        <v>0.99857265</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C26">
-        <v>28.12253390077671</v>
+        <v>54.47755813049488</v>
       </c>
       <c r="D26">
-        <v>23.58699683751922</v>
+        <v>22.0083816089626</v>
       </c>
       <c r="E26">
-        <v>0.9997295369999999</v>
+        <v>0.9986</v>
       </c>
       <c r="F26">
-        <v>0.9997295369999999</v>
+        <v>0.9986</v>
       </c>
       <c r="G26">
-        <v>0.03368732240295347</v>
+        <v>0.6220895940829376</v>
       </c>
       <c r="H26">
-        <v>0.9997295369999999</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C27">
-        <v>28.17715727830483</v>
+        <v>35.78646526282436</v>
       </c>
       <c r="D27">
-        <v>23.63894513078866</v>
+        <v>18.96635091925032</v>
       </c>
       <c r="E27">
-        <v>1.000319473</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="F27">
-        <v>1.000319473</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="G27">
-        <v>0.03515547182056333</v>
+        <v>0.2240600969213613</v>
       </c>
       <c r="H27">
-        <v>1.000319473</v>
+        <v>0.9985614899999999</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C28">
-        <v>28.59002627414054</v>
+        <v>35.71584102184062</v>
       </c>
       <c r="D28">
-        <v>23.96230704059692</v>
+        <v>18.62432950231353</v>
       </c>
       <c r="E28">
-        <v>0.9999999989999999</v>
+        <v>0.99965481</v>
       </c>
       <c r="F28">
-        <v>0.9999999989999999</v>
+        <v>0.99965481</v>
       </c>
       <c r="G28">
-        <v>0.05179637495949674</v>
+        <v>0.2104844827747143</v>
       </c>
       <c r="H28">
-        <v>0.9999999989999999</v>
+        <v>0.9985622199999999</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C29">
-        <v>28.56217859389523</v>
+        <v>35.95182028203252</v>
       </c>
       <c r="D29">
-        <v>23.9411987302529</v>
+        <v>18.95670796791552</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="G29">
-        <v>0.04837024516756849</v>
+        <v>0.2259035693959275</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>0.99855193</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="B30" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C30">
-        <v>40.68830633303975</v>
+        <v>36.14451597805883</v>
       </c>
       <c r="D30">
-        <v>21.50431773660198</v>
+        <v>18.86297660538653</v>
       </c>
       <c r="E30">
-        <v>0.99909852</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="F30">
-        <v>0.99909852</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="G30">
-        <v>0.2342423866086769</v>
+        <v>0.2362110061840785</v>
       </c>
       <c r="H30">
-        <v>0.9974930900000001</v>
+        <v>0.99857265</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="B31" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C31">
-        <v>40.32854894972581</v>
+        <v>35.32805803135546</v>
       </c>
       <c r="D31">
-        <v>21.09133998298594</v>
+        <v>18.35643242381478</v>
       </c>
       <c r="E31">
-        <v>0.9990972199999999</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="F31">
-        <v>0.9990972199999999</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="G31">
-        <v>0.2156468205051487</v>
+        <v>0.2023559161375383</v>
       </c>
       <c r="H31">
-        <v>0.99752223</v>
+        <v>0.9986639900000002</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C32">
-        <v>40.47987921095815</v>
+        <v>28.12253390077671</v>
       </c>
       <c r="D32">
-        <v>21.35995364434454</v>
+        <v>23.58699683751922</v>
       </c>
       <c r="E32">
-        <v>0.9991780100000001</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="F32">
-        <v>0.9991780100000001</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="G32">
-        <v>0.2270956128473374</v>
+        <v>0.03368732240295347</v>
       </c>
       <c r="H32">
-        <v>0.9975825700000001</v>
+        <v>0.9997295369999999</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B33" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33">
+        <v>28.17715727830483</v>
+      </c>
+      <c r="D33">
+        <v>23.63894513078866</v>
+      </c>
+      <c r="E33">
+        <v>1.000319473</v>
+      </c>
+      <c r="F33">
+        <v>1.000319473</v>
+      </c>
+      <c r="G33">
+        <v>0.03515547182056333</v>
+      </c>
+      <c r="H33">
+        <v>1.000319473</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34">
+        <v>28.59002627414054</v>
+      </c>
+      <c r="D34">
+        <v>23.96230704059692</v>
+      </c>
+      <c r="E34">
+        <v>0.9999999989999999</v>
+      </c>
+      <c r="F34">
+        <v>0.9999999989999999</v>
+      </c>
+      <c r="G34">
+        <v>0.05179637495949674</v>
+      </c>
+      <c r="H34">
+        <v>0.9999999989999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="1">
         <v>46156</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35">
+        <v>28.56217859389523</v>
+      </c>
+      <c r="D35">
+        <v>23.9411987302529</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35">
+        <v>0.04837024516756849</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B36" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36">
+        <v>28.57618675936338</v>
+      </c>
+      <c r="D36">
+        <v>23.9576220541054</v>
+      </c>
+      <c r="E36">
+        <v>0.999503249</v>
+      </c>
+      <c r="F36">
+        <v>0.999503249</v>
+      </c>
+      <c r="G36">
+        <v>0.04983868243960732</v>
+      </c>
+      <c r="H36">
+        <v>0.999503249</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B37" t="s">
         <v>15</v>
       </c>
-      <c r="C33">
+      <c r="C37">
+        <v>40.68830633303975</v>
+      </c>
+      <c r="D37">
+        <v>21.50431773660198</v>
+      </c>
+      <c r="E37">
+        <v>0.99909852</v>
+      </c>
+      <c r="F37">
+        <v>0.99909852</v>
+      </c>
+      <c r="G37">
+        <v>0.2342423866086769</v>
+      </c>
+      <c r="H37">
+        <v>0.9974930900000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B38" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38">
+        <v>40.32854894972581</v>
+      </c>
+      <c r="D38">
+        <v>21.09133998298594</v>
+      </c>
+      <c r="E38">
+        <v>0.9990972199999999</v>
+      </c>
+      <c r="F38">
+        <v>0.9990972199999999</v>
+      </c>
+      <c r="G38">
+        <v>0.2156468205051487</v>
+      </c>
+      <c r="H38">
+        <v>0.99752223</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39">
+        <v>40.47987921095815</v>
+      </c>
+      <c r="D39">
+        <v>21.35995364434454</v>
+      </c>
+      <c r="E39">
+        <v>0.9991780100000001</v>
+      </c>
+      <c r="F39">
+        <v>0.9991780100000001</v>
+      </c>
+      <c r="G39">
+        <v>0.2270956128473374</v>
+      </c>
+      <c r="H39">
+        <v>0.9975825700000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B40" t="s">
+        <v>15</v>
+      </c>
+      <c r="C40">
         <v>41.20436574895244</v>
       </c>
-      <c r="D33">
+      <c r="D40">
         <v>21.48149674387778</v>
       </c>
-      <c r="E33">
+      <c r="E40">
         <v>0.9991793299999999</v>
       </c>
-      <c r="F33">
+      <c r="F40">
         <v>0.9991793299999999</v>
       </c>
-      <c r="G33">
+      <c r="G40">
         <v>0.2454829228401052</v>
       </c>
-      <c r="H33">
+      <c r="H40">
         <v>0.99754722</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B41" t="s">
+        <v>15</v>
+      </c>
+      <c r="C41">
+        <v>40.80613062958688</v>
+      </c>
+      <c r="D41">
+        <v>21.08912555803936</v>
+      </c>
+      <c r="E41">
+        <v>0.9991790600000001</v>
+      </c>
+      <c r="F41">
+        <v>0.9991790600000001</v>
+      </c>
+      <c r="G41">
+        <v>0.2230017445022556</v>
+      </c>
+      <c r="H41">
+        <v>0.9975824700000002</v>
       </c>
     </row>
   </sheetData>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="16">
   <si>
     <t>Date</t>
   </si>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -558,68 +558,68 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7">
-        <v>34.64560932909123</v>
+        <v>50.72035274995172</v>
       </c>
       <c r="D7">
-        <v>26.08311546080494</v>
+        <v>24.61756040386634</v>
       </c>
       <c r="E7">
-        <v>0.9983000000000001</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="F7">
-        <v>0.9983000000000001</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="G7">
-        <v>0.06258613715048233</v>
+        <v>0.3627535778249862</v>
       </c>
       <c r="H7">
-        <v>0.9983000000000001</v>
+        <v>0.9259000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
       </c>
       <c r="C8">
-        <v>34.50204921141101</v>
+        <v>34.64560932909123</v>
       </c>
       <c r="D8">
-        <v>25.94535229304585</v>
+        <v>26.08311546080494</v>
       </c>
       <c r="E8">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="F8">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="G8">
-        <v>0.05768943168306073</v>
+        <v>0.06258613715048233</v>
       </c>
       <c r="H8">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
       </c>
       <c r="C9">
-        <v>35.10429483281073</v>
+        <v>34.50204921141101</v>
       </c>
       <c r="D9">
-        <v>26.43864879939599</v>
+        <v>25.94535229304585</v>
       </c>
       <c r="E9">
         <v>0.9984</v>
@@ -628,7 +628,7 @@
         <v>0.9984</v>
       </c>
       <c r="G9">
-        <v>0.07926550001722021</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H9">
         <v>0.9984</v>
@@ -636,704 +636,704 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
       </c>
       <c r="C10">
-        <v>35.36860632820093</v>
+        <v>35.10429483281073</v>
       </c>
       <c r="D10">
-        <v>26.56575571102338</v>
+        <v>26.43864879939599</v>
       </c>
       <c r="E10">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F10">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G10">
-        <v>0.08553946591902095</v>
+        <v>0.07926550001722021</v>
       </c>
       <c r="H10">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
       </c>
       <c r="C11">
-        <v>34.88080083527914</v>
+        <v>35.36860632820093</v>
       </c>
       <c r="D11">
-        <v>26.19322945679072</v>
+        <v>26.56575571102338</v>
       </c>
       <c r="E11">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="F11">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="G11">
-        <v>0.06870693142475881</v>
+        <v>0.08553946591902095</v>
       </c>
       <c r="H11">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12">
-        <v>36.55790859258162</v>
+        <v>34.88080083527914</v>
       </c>
       <c r="D12">
-        <v>22.67181120908155</v>
+        <v>26.19322945679072</v>
       </c>
       <c r="E12">
-        <v>0.9990740999999999</v>
+        <v>0.9983</v>
       </c>
       <c r="F12">
-        <v>0.9990740999999999</v>
+        <v>0.9983</v>
       </c>
       <c r="G12">
-        <v>0.1648443271746771</v>
+        <v>0.06870693142475881</v>
       </c>
       <c r="H12">
-        <v>0.9990740999999999</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13">
-        <v>36.44753722959613</v>
+        <v>34.67638692539213</v>
       </c>
       <c r="D13">
-        <v>22.40292401789388</v>
+        <v>26.06707890342319</v>
       </c>
       <c r="E13">
-        <v>0.9990772499999999</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="F13">
-        <v>0.9990772499999999</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="G13">
-        <v>0.154964342628132</v>
+        <v>0.06289213016552919</v>
       </c>
       <c r="H13">
-        <v>0.9990772499999999</v>
+        <v>0.9985999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="B14" t="s">
         <v>10</v>
       </c>
       <c r="C14">
-        <v>36.63128514035871</v>
+        <v>36.55790859258162</v>
       </c>
       <c r="D14">
-        <v>22.65773388934668</v>
+        <v>22.67181120908155</v>
       </c>
       <c r="E14">
-        <v>0.99907745</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="F14">
-        <v>0.99907745</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="G14">
-        <v>0.1671633421405267</v>
+        <v>0.1648443271746771</v>
       </c>
       <c r="H14">
-        <v>0.99907745</v>
+        <v>0.9990740999999999</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="B15" t="s">
         <v>10</v>
       </c>
       <c r="C15">
-        <v>36.87865927427314</v>
+        <v>36.44753722959613</v>
       </c>
       <c r="D15">
-        <v>22.69755646854794</v>
+        <v>22.40292401789388</v>
       </c>
       <c r="E15">
-        <v>0.99908601</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="F15">
-        <v>0.99908601</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="G15">
-        <v>0.1754592080224002</v>
+        <v>0.154964342628132</v>
       </c>
       <c r="H15">
-        <v>0.99908601</v>
+        <v>0.9990772499999999</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="B16" t="s">
         <v>10</v>
       </c>
       <c r="C16">
-        <v>36.52208783231286</v>
+        <v>36.63128514035871</v>
       </c>
       <c r="D16">
-        <v>22.32462309676992</v>
+        <v>22.65773388934668</v>
       </c>
       <c r="E16">
-        <v>0.99915499</v>
+        <v>0.99907745</v>
       </c>
       <c r="F16">
-        <v>0.99915499</v>
+        <v>0.99907745</v>
       </c>
       <c r="G16">
-        <v>0.1577242156354994</v>
+        <v>0.1671633421405267</v>
       </c>
       <c r="H16">
-        <v>0.99915499</v>
+        <v>0.99907745</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C17">
-        <v>52.70832779833182</v>
+        <v>36.87865927427314</v>
       </c>
       <c r="D17">
-        <v>23.99044674439659</v>
+        <v>22.69755646854794</v>
       </c>
       <c r="E17">
-        <v>0.9994000000000002</v>
+        <v>0.99908601</v>
       </c>
       <c r="F17">
-        <v>0.9994000000000002</v>
+        <v>0.99908601</v>
       </c>
       <c r="G17">
-        <v>0.5438253854918791</v>
+        <v>0.1754592080224002</v>
       </c>
       <c r="H17">
-        <v>0.9994000000000002</v>
+        <v>0.99908601</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18">
-        <v>50.89464485280568</v>
+        <v>36.52208783231286</v>
       </c>
       <c r="D18">
-        <v>23.21558303176282</v>
+        <v>22.32462309676992</v>
       </c>
       <c r="E18">
-        <v>0.9996</v>
+        <v>0.99915499</v>
       </c>
       <c r="F18">
-        <v>0.9996</v>
+        <v>0.99915499</v>
       </c>
       <c r="G18">
-        <v>0.5034825029548833</v>
+        <v>0.1577242156354994</v>
       </c>
       <c r="H18">
-        <v>0.9996</v>
+        <v>0.99915499</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1">
-        <v>46155</v>
+        <v>46160</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C19">
-        <v>51.8659994471731</v>
+        <v>36.25604200674668</v>
       </c>
       <c r="D19">
-        <v>23.7009037279043</v>
+        <v>22.16555007468561</v>
       </c>
       <c r="E19">
-        <v>1.0002</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="F19">
-        <v>1.0002</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="G19">
-        <v>0.533512029714132</v>
+        <v>0.1527434068648266</v>
       </c>
       <c r="H19">
-        <v>1.0002</v>
+        <v>0.9991011900000002</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="B20" t="s">
         <v>11</v>
       </c>
       <c r="C20">
-        <v>52.4470179952828</v>
+        <v>52.70832779833182</v>
       </c>
       <c r="D20">
-        <v>23.76861704536814</v>
+        <v>23.99044674439659</v>
       </c>
       <c r="E20">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="F20">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="G20">
-        <v>0.5492634496849078</v>
+        <v>0.5438253854918791</v>
       </c>
       <c r="H20">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="B21" t="s">
         <v>11</v>
       </c>
       <c r="C21">
-        <v>50.81077380018606</v>
+        <v>50.89464485280568</v>
       </c>
       <c r="D21">
-        <v>22.76900580927995</v>
+        <v>23.21558303176282</v>
       </c>
       <c r="E21">
-        <v>0.9998</v>
+        <v>0.9996</v>
       </c>
       <c r="F21">
-        <v>0.9998</v>
+        <v>0.9996</v>
       </c>
       <c r="G21">
-        <v>0.4903296143797722</v>
+        <v>0.5034825029548833</v>
       </c>
       <c r="H21">
-        <v>0.9998</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C22">
-        <v>57.1732166855686</v>
+        <v>51.8659994471731</v>
       </c>
       <c r="D22">
-        <v>23.50022751267814</v>
+        <v>23.7009037279043</v>
       </c>
       <c r="E22">
-        <v>0.9991</v>
+        <v>1.0002</v>
       </c>
       <c r="F22">
-        <v>0.9991</v>
+        <v>1.0002</v>
       </c>
       <c r="G22">
-        <v>0.6994110097039083</v>
+        <v>0.533512029714132</v>
       </c>
       <c r="H22">
-        <v>0.9991</v>
+        <v>1.0002</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C23">
-        <v>54.77380642078597</v>
+        <v>52.4470179952828</v>
       </c>
       <c r="D23">
-        <v>22.55192940254518</v>
+        <v>23.76861704536814</v>
       </c>
       <c r="E23">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
       <c r="F23">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
       <c r="G23">
-        <v>0.6459175880844941</v>
+        <v>0.5492634496849078</v>
       </c>
       <c r="H23">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C24">
-        <v>56.32187380830906</v>
+        <v>50.81077380018606</v>
       </c>
       <c r="D24">
-        <v>23.17121437414109</v>
+        <v>22.76900580927995</v>
       </c>
       <c r="E24">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
       <c r="F24">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
       <c r="G24">
-        <v>0.6851523922954754</v>
+        <v>0.4903296143797722</v>
       </c>
       <c r="H24">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C25">
-        <v>56.15321618553139</v>
+        <v>49.50286387149169</v>
       </c>
       <c r="D25">
-        <v>22.95838347314443</v>
+        <v>22.24532119914133</v>
       </c>
       <c r="E25">
-        <v>0.9992</v>
+        <v>0.9996</v>
       </c>
       <c r="F25">
-        <v>0.9992</v>
+        <v>0.9996</v>
       </c>
       <c r="G25">
-        <v>0.6907028507208208</v>
+        <v>0.4630591776162345</v>
       </c>
       <c r="H25">
-        <v>0.9992</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="B26" t="s">
         <v>12</v>
       </c>
       <c r="C26">
-        <v>54.47755813049488</v>
+        <v>57.1732166855686</v>
       </c>
       <c r="D26">
-        <v>22.0083816089626</v>
+        <v>23.50022751267814</v>
       </c>
       <c r="E26">
-        <v>0.9986</v>
+        <v>0.9991</v>
       </c>
       <c r="F26">
-        <v>0.9986</v>
+        <v>0.9991</v>
       </c>
       <c r="G26">
-        <v>0.6220895940829376</v>
+        <v>0.6994110097039083</v>
       </c>
       <c r="H26">
-        <v>0.9986</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C27">
-        <v>35.78646526282436</v>
+        <v>54.77380642078597</v>
       </c>
       <c r="D27">
-        <v>18.96635091925032</v>
+        <v>22.55192940254518</v>
       </c>
       <c r="E27">
-        <v>0.9996491399999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F27">
-        <v>0.9996491399999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G27">
-        <v>0.2240600969213613</v>
+        <v>0.6459175880844941</v>
       </c>
       <c r="H27">
-        <v>0.9985614899999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C28">
-        <v>35.71584102184062</v>
+        <v>56.32187380830906</v>
       </c>
       <c r="D28">
-        <v>18.62432950231353</v>
+        <v>23.17121437414109</v>
       </c>
       <c r="E28">
-        <v>0.99965481</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F28">
-        <v>0.99965481</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G28">
-        <v>0.2104844827747143</v>
+        <v>0.6851523922954754</v>
       </c>
       <c r="H28">
-        <v>0.9985622199999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C29">
-        <v>35.95182028203252</v>
+        <v>56.15321618553139</v>
       </c>
       <c r="D29">
-        <v>18.95670796791552</v>
+        <v>22.95838347314443</v>
       </c>
       <c r="E29">
-        <v>0.9996515200000001</v>
+        <v>0.9992</v>
       </c>
       <c r="F29">
-        <v>0.9996515200000001</v>
+        <v>0.9992</v>
       </c>
       <c r="G29">
-        <v>0.2259035693959275</v>
+        <v>0.6907028507208208</v>
       </c>
       <c r="H29">
-        <v>0.99855193</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C30">
-        <v>36.14451597805883</v>
+        <v>54.47755813049488</v>
       </c>
       <c r="D30">
-        <v>18.86297660538653</v>
+        <v>22.0083816089626</v>
       </c>
       <c r="E30">
-        <v>0.9996563399999999</v>
+        <v>0.9986</v>
       </c>
       <c r="F30">
-        <v>0.9996563399999999</v>
+        <v>0.9986</v>
       </c>
       <c r="G30">
-        <v>0.2362110061840785</v>
+        <v>0.6220895940829376</v>
       </c>
       <c r="H30">
-        <v>0.99857265</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
       </c>
       <c r="C31">
-        <v>35.32805803135546</v>
+        <v>35.78646526282436</v>
       </c>
       <c r="D31">
-        <v>18.35643242381478</v>
+        <v>18.96635091925032</v>
       </c>
       <c r="E31">
-        <v>0.9997415800000001</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="F31">
-        <v>0.9997415800000001</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="G31">
-        <v>0.2023559161375383</v>
+        <v>0.2240600969213613</v>
       </c>
       <c r="H31">
-        <v>0.9986639900000002</v>
+        <v>0.9985614899999999</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C32">
-        <v>28.12253390077671</v>
+        <v>35.71584102184062</v>
       </c>
       <c r="D32">
-        <v>23.58699683751922</v>
+        <v>18.62432950231353</v>
       </c>
       <c r="E32">
-        <v>0.9997295369999999</v>
+        <v>0.99965481</v>
       </c>
       <c r="F32">
-        <v>0.9997295369999999</v>
+        <v>0.99965481</v>
       </c>
       <c r="G32">
-        <v>0.03368732240295347</v>
+        <v>0.2104844827747143</v>
       </c>
       <c r="H32">
-        <v>0.9997295369999999</v>
+        <v>0.9985622199999999</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C33">
-        <v>28.17715727830483</v>
+        <v>35.95182028203252</v>
       </c>
       <c r="D33">
-        <v>23.63894513078866</v>
+        <v>18.95670796791552</v>
       </c>
       <c r="E33">
-        <v>1.000319473</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="F33">
-        <v>1.000319473</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="G33">
-        <v>0.03515547182056333</v>
+        <v>0.2259035693959275</v>
       </c>
       <c r="H33">
-        <v>1.000319473</v>
+        <v>0.99855193</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B34" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C34">
-        <v>28.59002627414054</v>
+        <v>36.14451597805883</v>
       </c>
       <c r="D34">
-        <v>23.96230704059692</v>
+        <v>18.86297660538653</v>
       </c>
       <c r="E34">
-        <v>0.9999999989999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="F34">
-        <v>0.9999999989999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="G34">
-        <v>0.05179637495949674</v>
+        <v>0.2362110061840785</v>
       </c>
       <c r="H34">
-        <v>0.9999999989999999</v>
+        <v>0.99857265</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C35">
-        <v>28.56217859389523</v>
+        <v>35.32805803135546</v>
       </c>
       <c r="D35">
-        <v>23.9411987302529</v>
+        <v>18.35643242381478</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="G35">
-        <v>0.04837024516756849</v>
+        <v>0.2023559161375383</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>0.9986639900000002</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B36" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C36">
-        <v>28.57618675936338</v>
+        <v>34.83995455757461</v>
       </c>
       <c r="D36">
-        <v>23.9576220541054</v>
+        <v>18.02301281718857</v>
       </c>
       <c r="E36">
-        <v>0.999503249</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="F36">
-        <v>0.999503249</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="G36">
-        <v>0.04983868243960732</v>
+        <v>0.1850932291737926</v>
       </c>
       <c r="H36">
-        <v>0.999503249</v>
+        <v>0.99857724</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1341,25 +1341,25 @@
         <v>46153</v>
       </c>
       <c r="B37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C37">
-        <v>40.68830633303975</v>
+        <v>28.12253390077671</v>
       </c>
       <c r="D37">
-        <v>21.50431773660198</v>
+        <v>23.58699683751922</v>
       </c>
       <c r="E37">
-        <v>0.99909852</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="F37">
-        <v>0.99909852</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="G37">
-        <v>0.2342423866086769</v>
+        <v>0.03368732240295347</v>
       </c>
       <c r="H37">
-        <v>0.9974930900000001</v>
+        <v>0.9997295369999999</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1367,25 +1367,25 @@
         <v>46154</v>
       </c>
       <c r="B38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C38">
-        <v>40.32854894972581</v>
+        <v>28.17715727830483</v>
       </c>
       <c r="D38">
-        <v>21.09133998298594</v>
+        <v>23.63894513078866</v>
       </c>
       <c r="E38">
-        <v>0.9990972199999999</v>
+        <v>1.000319473</v>
       </c>
       <c r="F38">
-        <v>0.9990972199999999</v>
+        <v>1.000319473</v>
       </c>
       <c r="G38">
-        <v>0.2156468205051487</v>
+        <v>0.03515547182056333</v>
       </c>
       <c r="H38">
-        <v>0.99752223</v>
+        <v>1.000319473</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1393,25 +1393,25 @@
         <v>46155</v>
       </c>
       <c r="B39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C39">
-        <v>40.47987921095815</v>
+        <v>28.59002627414054</v>
       </c>
       <c r="D39">
-        <v>21.35995364434454</v>
+        <v>23.96230704059692</v>
       </c>
       <c r="E39">
-        <v>0.9991780100000001</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F39">
-        <v>0.9991780100000001</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G39">
-        <v>0.2270956128473374</v>
+        <v>0.05179637495949674</v>
       </c>
       <c r="H39">
-        <v>0.9975825700000001</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1419,25 +1419,25 @@
         <v>46156</v>
       </c>
       <c r="B40" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C40">
-        <v>41.20436574895244</v>
+        <v>28.56217859389523</v>
       </c>
       <c r="D40">
-        <v>21.48149674387778</v>
+        <v>23.9411987302529</v>
       </c>
       <c r="E40">
-        <v>0.9991793299999999</v>
+        <v>1</v>
       </c>
       <c r="F40">
-        <v>0.9991793299999999</v>
+        <v>1</v>
       </c>
       <c r="G40">
-        <v>0.2454829228401052</v>
+        <v>0.04837024516756849</v>
       </c>
       <c r="H40">
-        <v>0.99754722</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1445,25 +1445,207 @@
         <v>46157</v>
       </c>
       <c r="B41" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41">
+        <v>28.57618675936338</v>
+      </c>
+      <c r="D41">
+        <v>23.9576220541054</v>
+      </c>
+      <c r="E41">
+        <v>0.999503249</v>
+      </c>
+      <c r="F41">
+        <v>0.999503249</v>
+      </c>
+      <c r="G41">
+        <v>0.04983868243960732</v>
+      </c>
+      <c r="H41">
+        <v>0.999503249</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B42" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42">
+        <v>28.68951918518517</v>
+      </c>
+      <c r="D42">
+        <v>24.06134728453882</v>
+      </c>
+      <c r="E42">
+        <v>0.999503249</v>
+      </c>
+      <c r="F42">
+        <v>0.999503249</v>
+      </c>
+      <c r="G42">
+        <v>0.04983868243960732</v>
+      </c>
+      <c r="H42">
+        <v>0.999503249</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B43" t="s">
         <v>15</v>
       </c>
-      <c r="C41">
+      <c r="C43">
+        <v>40.68830633303975</v>
+      </c>
+      <c r="D43">
+        <v>21.50431773660198</v>
+      </c>
+      <c r="E43">
+        <v>0.99909852</v>
+      </c>
+      <c r="F43">
+        <v>0.99909852</v>
+      </c>
+      <c r="G43">
+        <v>0.2342423866086769</v>
+      </c>
+      <c r="H43">
+        <v>0.9974930900000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B44" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44">
+        <v>40.32854894972581</v>
+      </c>
+      <c r="D44">
+        <v>21.09133998298594</v>
+      </c>
+      <c r="E44">
+        <v>0.9990972199999999</v>
+      </c>
+      <c r="F44">
+        <v>0.9990972199999999</v>
+      </c>
+      <c r="G44">
+        <v>0.2156468205051487</v>
+      </c>
+      <c r="H44">
+        <v>0.99752223</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B45" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45">
+        <v>40.47987921095815</v>
+      </c>
+      <c r="D45">
+        <v>21.35995364434454</v>
+      </c>
+      <c r="E45">
+        <v>0.9991780100000001</v>
+      </c>
+      <c r="F45">
+        <v>0.9991780100000001</v>
+      </c>
+      <c r="G45">
+        <v>0.2270956128473374</v>
+      </c>
+      <c r="H45">
+        <v>0.9975825700000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B46" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46">
+        <v>41.20436574895244</v>
+      </c>
+      <c r="D46">
+        <v>21.48149674387778</v>
+      </c>
+      <c r="E46">
+        <v>0.9991793299999999</v>
+      </c>
+      <c r="F46">
+        <v>0.9991793299999999</v>
+      </c>
+      <c r="G46">
+        <v>0.2454829228401052</v>
+      </c>
+      <c r="H46">
+        <v>0.99754722</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B47" t="s">
+        <v>15</v>
+      </c>
+      <c r="C47">
         <v>40.80613062958688</v>
       </c>
-      <c r="D41">
+      <c r="D47">
         <v>21.08912555803936</v>
       </c>
-      <c r="E41">
+      <c r="E47">
         <v>0.9991790600000001</v>
       </c>
-      <c r="F41">
+      <c r="F47">
         <v>0.9991790600000001</v>
       </c>
-      <c r="G41">
+      <c r="G47">
         <v>0.2230017445022556</v>
       </c>
-      <c r="H41">
+      <c r="H47">
         <v>0.9975824700000002</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B48" t="s">
+        <v>15</v>
+      </c>
+      <c r="C48">
+        <v>40.11672876026724</v>
+      </c>
+      <c r="D48">
+        <v>20.79541439916316</v>
+      </c>
+      <c r="E48">
+        <v>0.999152</v>
+      </c>
+      <c r="F48">
+        <v>0.999152</v>
+      </c>
+      <c r="G48">
+        <v>0.2098184021536666</v>
+      </c>
+      <c r="H48">
+        <v>0.9975007899999999</v>
       </c>
     </row>
   </sheetData>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="16">
   <si>
     <t>Date</t>
   </si>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -584,68 +584,68 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1">
-        <v>46153</v>
+        <v>46161</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>34.64560932909123</v>
+        <v>50.13081250240213</v>
       </c>
       <c r="D8">
-        <v>26.08311546080494</v>
+        <v>24.12678679258809</v>
       </c>
       <c r="E8">
-        <v>0.9983000000000001</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="F8">
-        <v>0.9983000000000001</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="G8">
-        <v>0.06258613715048233</v>
+        <v>0.319576918507692</v>
       </c>
       <c r="H8">
-        <v>0.9983000000000001</v>
+        <v>0.9259000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
       </c>
       <c r="C9">
-        <v>34.50204921141101</v>
+        <v>34.64560932909123</v>
       </c>
       <c r="D9">
-        <v>25.94535229304585</v>
+        <v>26.08311546080494</v>
       </c>
       <c r="E9">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="F9">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="G9">
-        <v>0.05768943168306073</v>
+        <v>0.06258613715048233</v>
       </c>
       <c r="H9">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
       </c>
       <c r="C10">
-        <v>35.10429483281073</v>
+        <v>34.50204921141101</v>
       </c>
       <c r="D10">
-        <v>26.43864879939599</v>
+        <v>25.94535229304585</v>
       </c>
       <c r="E10">
         <v>0.9984</v>
@@ -654,7 +654,7 @@
         <v>0.9984</v>
       </c>
       <c r="G10">
-        <v>0.07926550001722021</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H10">
         <v>0.9984</v>
@@ -662,990 +662,1172 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
       </c>
       <c r="C11">
-        <v>35.36860632820093</v>
+        <v>35.10429483281073</v>
       </c>
       <c r="D11">
-        <v>26.56575571102338</v>
+        <v>26.43864879939599</v>
       </c>
       <c r="E11">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F11">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G11">
-        <v>0.08553946591902095</v>
+        <v>0.07926550001722021</v>
       </c>
       <c r="H11">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
       </c>
       <c r="C12">
-        <v>34.88080083527914</v>
+        <v>35.36860632820093</v>
       </c>
       <c r="D12">
-        <v>26.19322945679072</v>
+        <v>26.56575571102338</v>
       </c>
       <c r="E12">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="F12">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="G12">
-        <v>0.06870693142475881</v>
+        <v>0.08553946591902095</v>
       </c>
       <c r="H12">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="B13" t="s">
         <v>9</v>
       </c>
       <c r="C13">
-        <v>34.67638692539213</v>
+        <v>34.88080083527914</v>
       </c>
       <c r="D13">
-        <v>26.06707890342319</v>
+        <v>26.19322945679072</v>
       </c>
       <c r="E13">
-        <v>0.9985999999999999</v>
+        <v>0.9983</v>
       </c>
       <c r="F13">
-        <v>0.9985999999999999</v>
+        <v>0.9983</v>
       </c>
       <c r="G13">
-        <v>0.06289213016552919</v>
+        <v>0.06870693142475881</v>
       </c>
       <c r="H13">
-        <v>0.9985999999999999</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14">
-        <v>36.55790859258162</v>
+        <v>34.67638692539213</v>
       </c>
       <c r="D14">
-        <v>22.67181120908155</v>
+        <v>26.06707890342319</v>
       </c>
       <c r="E14">
-        <v>0.9990740999999999</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="F14">
-        <v>0.9990740999999999</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="G14">
-        <v>0.1648443271746771</v>
+        <v>0.06289213016552919</v>
       </c>
       <c r="H14">
-        <v>0.9990740999999999</v>
+        <v>0.9985999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C15">
-        <v>36.44753722959613</v>
+        <v>34.12713174867851</v>
       </c>
       <c r="D15">
-        <v>22.40292401789388</v>
+        <v>25.56917319151027</v>
       </c>
       <c r="E15">
-        <v>0.9990772499999999</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="F15">
-        <v>0.9990772499999999</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="G15">
-        <v>0.154964342628132</v>
+        <v>0.04514161662612648</v>
       </c>
       <c r="H15">
-        <v>0.9990772499999999</v>
+        <v>0.9985999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="B16" t="s">
         <v>10</v>
       </c>
       <c r="C16">
-        <v>36.63128514035871</v>
+        <v>36.55790859258162</v>
       </c>
       <c r="D16">
-        <v>22.65773388934668</v>
+        <v>22.67181120908155</v>
       </c>
       <c r="E16">
-        <v>0.99907745</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="F16">
-        <v>0.99907745</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="G16">
-        <v>0.1671633421405267</v>
+        <v>0.1648443271746771</v>
       </c>
       <c r="H16">
-        <v>0.99907745</v>
+        <v>0.9990740999999999</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
       </c>
       <c r="C17">
-        <v>36.87865927427314</v>
+        <v>36.44753722959613</v>
       </c>
       <c r="D17">
-        <v>22.69755646854794</v>
+        <v>22.40292401789388</v>
       </c>
       <c r="E17">
-        <v>0.99908601</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="F17">
-        <v>0.99908601</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="G17">
-        <v>0.1754592080224002</v>
+        <v>0.154964342628132</v>
       </c>
       <c r="H17">
-        <v>0.99908601</v>
+        <v>0.9990772499999999</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>
       </c>
       <c r="C18">
-        <v>36.52208783231286</v>
+        <v>36.63128514035871</v>
       </c>
       <c r="D18">
-        <v>22.32462309676992</v>
+        <v>22.65773388934668</v>
       </c>
       <c r="E18">
-        <v>0.99915499</v>
+        <v>0.99907745</v>
       </c>
       <c r="F18">
-        <v>0.99915499</v>
+        <v>0.99907745</v>
       </c>
       <c r="G18">
-        <v>0.1577242156354994</v>
+        <v>0.1671633421405267</v>
       </c>
       <c r="H18">
-        <v>0.99915499</v>
+        <v>0.99907745</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1">
-        <v>46160</v>
+        <v>46156</v>
       </c>
       <c r="B19" t="s">
         <v>10</v>
       </c>
       <c r="C19">
-        <v>36.25604200674668</v>
+        <v>36.87865927427314</v>
       </c>
       <c r="D19">
-        <v>22.16555007468561</v>
+        <v>22.69755646854794</v>
       </c>
       <c r="E19">
-        <v>0.9991011900000002</v>
+        <v>0.99908601</v>
       </c>
       <c r="F19">
-        <v>0.9991011900000002</v>
+        <v>0.99908601</v>
       </c>
       <c r="G19">
-        <v>0.1527434068648266</v>
+        <v>0.1754592080224002</v>
       </c>
       <c r="H19">
-        <v>0.9991011900000002</v>
+        <v>0.99908601</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C20">
-        <v>52.70832779833182</v>
+        <v>36.52208783231286</v>
       </c>
       <c r="D20">
-        <v>23.99044674439659</v>
+        <v>22.32462309676992</v>
       </c>
       <c r="E20">
-        <v>0.9994000000000002</v>
+        <v>0.99915499</v>
       </c>
       <c r="F20">
-        <v>0.9994000000000002</v>
+        <v>0.99915499</v>
       </c>
       <c r="G20">
-        <v>0.5438253854918791</v>
+        <v>0.1577242156354994</v>
       </c>
       <c r="H20">
-        <v>0.9994000000000002</v>
+        <v>0.99915499</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C21">
-        <v>50.89464485280568</v>
+        <v>36.25604200674668</v>
       </c>
       <c r="D21">
-        <v>23.21558303176282</v>
+        <v>22.16555007468561</v>
       </c>
       <c r="E21">
-        <v>0.9996</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="F21">
-        <v>0.9996</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="G21">
-        <v>0.5034825029548833</v>
+        <v>0.1527434068648266</v>
       </c>
       <c r="H21">
-        <v>0.9996</v>
+        <v>0.9991011900000002</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1">
-        <v>46155</v>
+        <v>46161</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C22">
-        <v>51.8659994471731</v>
+        <v>35.98205372592128</v>
       </c>
       <c r="D22">
-        <v>23.7009037279043</v>
+        <v>22.15980569372351</v>
       </c>
       <c r="E22">
-        <v>1.0002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="F22">
-        <v>1.0002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="G22">
-        <v>0.533512029714132</v>
+        <v>0.1413365165217606</v>
       </c>
       <c r="H22">
-        <v>1.0002</v>
+        <v>0.9993222199999999</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="B23" t="s">
         <v>11</v>
       </c>
       <c r="C23">
-        <v>52.4470179952828</v>
+        <v>52.70832779833182</v>
       </c>
       <c r="D23">
-        <v>23.76861704536814</v>
+        <v>23.99044674439659</v>
       </c>
       <c r="E23">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="F23">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="G23">
-        <v>0.5492634496849078</v>
+        <v>0.5438253854918791</v>
       </c>
       <c r="H23">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="B24" t="s">
         <v>11</v>
       </c>
       <c r="C24">
-        <v>50.81077380018606</v>
+        <v>50.89464485280568</v>
       </c>
       <c r="D24">
-        <v>22.76900580927995</v>
+        <v>23.21558303176282</v>
       </c>
       <c r="E24">
-        <v>0.9998</v>
+        <v>0.9996</v>
       </c>
       <c r="F24">
-        <v>0.9998</v>
+        <v>0.9996</v>
       </c>
       <c r="G24">
-        <v>0.4903296143797722</v>
+        <v>0.5034825029548833</v>
       </c>
       <c r="H24">
-        <v>0.9998</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="B25" t="s">
         <v>11</v>
       </c>
       <c r="C25">
-        <v>49.50286387149169</v>
+        <v>51.8659994471731</v>
       </c>
       <c r="D25">
-        <v>22.24532119914133</v>
+        <v>23.7009037279043</v>
       </c>
       <c r="E25">
-        <v>0.9996</v>
+        <v>1.0002</v>
       </c>
       <c r="F25">
-        <v>0.9996</v>
+        <v>1.0002</v>
       </c>
       <c r="G25">
-        <v>0.4630591776162345</v>
+        <v>0.533512029714132</v>
       </c>
       <c r="H25">
-        <v>0.9996</v>
+        <v>1.0002</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C26">
-        <v>57.1732166855686</v>
+        <v>52.4470179952828</v>
       </c>
       <c r="D26">
-        <v>23.50022751267814</v>
+        <v>23.76861704536814</v>
       </c>
       <c r="E26">
-        <v>0.9991</v>
+        <v>0.9998</v>
       </c>
       <c r="F26">
-        <v>0.9991</v>
+        <v>0.9998</v>
       </c>
       <c r="G26">
-        <v>0.6994110097039083</v>
+        <v>0.5492634496849078</v>
       </c>
       <c r="H26">
-        <v>0.9991</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="B27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C27">
-        <v>54.77380642078597</v>
+        <v>50.81077380018606</v>
       </c>
       <c r="D27">
-        <v>22.55192940254518</v>
+        <v>22.76900580927995</v>
       </c>
       <c r="E27">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
       <c r="F27">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
       <c r="G27">
-        <v>0.6459175880844941</v>
+        <v>0.4903296143797722</v>
       </c>
       <c r="H27">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1">
-        <v>46155</v>
+        <v>46160</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C28">
-        <v>56.32187380830906</v>
+        <v>49.50286387149169</v>
       </c>
       <c r="D28">
-        <v>23.17121437414109</v>
+        <v>22.24532119914133</v>
       </c>
       <c r="E28">
-        <v>0.9990000000000001</v>
+        <v>0.9996</v>
       </c>
       <c r="F28">
-        <v>0.9990000000000001</v>
+        <v>0.9996</v>
       </c>
       <c r="G28">
-        <v>0.6851523922954754</v>
+        <v>0.4630591776162345</v>
       </c>
       <c r="H28">
-        <v>0.9990000000000001</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1">
-        <v>46156</v>
+        <v>46161</v>
       </c>
       <c r="B29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C29">
-        <v>56.15321618553139</v>
+        <v>49.26275747752842</v>
       </c>
       <c r="D29">
-        <v>22.95838347314443</v>
+        <v>22.22547935840584</v>
       </c>
       <c r="E29">
-        <v>0.9992</v>
+        <v>0.9998</v>
       </c>
       <c r="F29">
-        <v>0.9992</v>
+        <v>0.9998</v>
       </c>
       <c r="G29">
-        <v>0.6907028507208208</v>
+        <v>0.4534691530468447</v>
       </c>
       <c r="H29">
-        <v>0.9992</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="B30" t="s">
         <v>12</v>
       </c>
       <c r="C30">
-        <v>54.47755813049488</v>
+        <v>57.1732166855686</v>
       </c>
       <c r="D30">
-        <v>22.0083816089626</v>
+        <v>23.50022751267814</v>
       </c>
       <c r="E30">
-        <v>0.9986</v>
+        <v>0.9991</v>
       </c>
       <c r="F30">
-        <v>0.9986</v>
+        <v>0.9991</v>
       </c>
       <c r="G30">
-        <v>0.6220895940829376</v>
+        <v>0.6994110097039083</v>
       </c>
       <c r="H30">
-        <v>0.9986</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C31">
-        <v>35.78646526282436</v>
+        <v>54.77380642078597</v>
       </c>
       <c r="D31">
-        <v>18.96635091925032</v>
+        <v>22.55192940254518</v>
       </c>
       <c r="E31">
-        <v>0.9996491399999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F31">
-        <v>0.9996491399999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G31">
-        <v>0.2240600969213613</v>
+        <v>0.6459175880844941</v>
       </c>
       <c r="H31">
-        <v>0.9985614899999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C32">
-        <v>35.71584102184062</v>
+        <v>56.32187380830906</v>
       </c>
       <c r="D32">
-        <v>18.62432950231353</v>
+        <v>23.17121437414109</v>
       </c>
       <c r="E32">
-        <v>0.99965481</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F32">
-        <v>0.99965481</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G32">
-        <v>0.2104844827747143</v>
+        <v>0.6851523922954754</v>
       </c>
       <c r="H32">
-        <v>0.9985622199999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C33">
-        <v>35.95182028203252</v>
+        <v>56.15321618553139</v>
       </c>
       <c r="D33">
-        <v>18.95670796791552</v>
+        <v>22.95838347314443</v>
       </c>
       <c r="E33">
-        <v>0.9996515200000001</v>
+        <v>0.9992</v>
       </c>
       <c r="F33">
-        <v>0.9996515200000001</v>
+        <v>0.9992</v>
       </c>
       <c r="G33">
-        <v>0.2259035693959275</v>
+        <v>0.6907028507208208</v>
       </c>
       <c r="H33">
-        <v>0.99855193</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C34">
-        <v>36.14451597805883</v>
+        <v>54.47755813049488</v>
       </c>
       <c r="D34">
-        <v>18.86297660538653</v>
+        <v>22.0083816089626</v>
       </c>
       <c r="E34">
-        <v>0.9996563399999999</v>
+        <v>0.9986</v>
       </c>
       <c r="F34">
-        <v>0.9996563399999999</v>
+        <v>0.9986</v>
       </c>
       <c r="G34">
-        <v>0.2362110061840785</v>
+        <v>0.6220895940829376</v>
       </c>
       <c r="H34">
-        <v>0.99857265</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
       </c>
       <c r="C35">
-        <v>35.32805803135546</v>
+        <v>35.78646526282436</v>
       </c>
       <c r="D35">
-        <v>18.35643242381478</v>
+        <v>18.96635091925032</v>
       </c>
       <c r="E35">
-        <v>0.9997415800000001</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="F35">
-        <v>0.9997415800000001</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="G35">
-        <v>0.2023559161375383</v>
+        <v>0.2240600969213613</v>
       </c>
       <c r="H35">
-        <v>0.9986639900000002</v>
+        <v>0.9985614899999999</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1">
-        <v>46160</v>
+        <v>46154</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
       </c>
       <c r="C36">
-        <v>34.83995455757461</v>
+        <v>35.71584102184062</v>
       </c>
       <c r="D36">
-        <v>18.02301281718857</v>
+        <v>18.62432950231353</v>
       </c>
       <c r="E36">
-        <v>0.9996851299999999</v>
+        <v>0.99965481</v>
       </c>
       <c r="F36">
-        <v>0.9996851299999999</v>
+        <v>0.99965481</v>
       </c>
       <c r="G36">
-        <v>0.1850932291737926</v>
+        <v>0.2104844827747143</v>
       </c>
       <c r="H36">
-        <v>0.99857724</v>
+        <v>0.9985622199999999</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C37">
-        <v>28.12253390077671</v>
+        <v>35.95182028203252</v>
       </c>
       <c r="D37">
-        <v>23.58699683751922</v>
+        <v>18.95670796791552</v>
       </c>
       <c r="E37">
-        <v>0.9997295369999999</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="F37">
-        <v>0.9997295369999999</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="G37">
-        <v>0.03368732240295347</v>
+        <v>0.2259035693959275</v>
       </c>
       <c r="H37">
-        <v>0.9997295369999999</v>
+        <v>0.99855193</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C38">
-        <v>28.17715727830483</v>
+        <v>36.14451597805883</v>
       </c>
       <c r="D38">
-        <v>23.63894513078866</v>
+        <v>18.86297660538653</v>
       </c>
       <c r="E38">
-        <v>1.000319473</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="F38">
-        <v>1.000319473</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="G38">
-        <v>0.03515547182056333</v>
+        <v>0.2362110061840785</v>
       </c>
       <c r="H38">
-        <v>1.000319473</v>
+        <v>0.99857265</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B39" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C39">
-        <v>28.59002627414054</v>
+        <v>35.32805803135546</v>
       </c>
       <c r="D39">
-        <v>23.96230704059692</v>
+        <v>18.35643242381478</v>
       </c>
       <c r="E39">
-        <v>0.9999999989999999</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="F39">
-        <v>0.9999999989999999</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="G39">
-        <v>0.05179637495949674</v>
+        <v>0.2023559161375383</v>
       </c>
       <c r="H39">
-        <v>0.9999999989999999</v>
+        <v>0.9986639900000002</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="B40" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C40">
-        <v>28.56217859389523</v>
+        <v>34.83995455757461</v>
       </c>
       <c r="D40">
-        <v>23.9411987302529</v>
+        <v>18.02301281718857</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="G40">
-        <v>0.04837024516756849</v>
+        <v>0.1850932291737926</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <v>0.99857724</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B41" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C41">
-        <v>28.57618675936338</v>
+        <v>34.39756871976165</v>
       </c>
       <c r="D41">
-        <v>23.9576220541054</v>
+        <v>18.04233141064392</v>
       </c>
       <c r="E41">
-        <v>0.999503249</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="F41">
-        <v>0.999503249</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="G41">
-        <v>0.04983868243960732</v>
+        <v>0.1745345318312599</v>
       </c>
       <c r="H41">
-        <v>0.999503249</v>
+        <v>0.9985337599999999</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1">
-        <v>46160</v>
+        <v>46153</v>
       </c>
       <c r="B42" t="s">
         <v>14</v>
       </c>
       <c r="C42">
-        <v>28.68951918518517</v>
+        <v>28.12253390077671</v>
       </c>
       <c r="D42">
-        <v>24.06134728453882</v>
+        <v>23.58699683751922</v>
       </c>
       <c r="E42">
-        <v>0.999503249</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="F42">
-        <v>0.999503249</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="G42">
-        <v>0.04983868243960732</v>
+        <v>0.03368732240295347</v>
       </c>
       <c r="H42">
-        <v>0.999503249</v>
+        <v>0.9997295369999999</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B43" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C43">
-        <v>40.68830633303975</v>
+        <v>28.17715727830483</v>
       </c>
       <c r="D43">
-        <v>21.50431773660198</v>
+        <v>23.63894513078866</v>
       </c>
       <c r="E43">
-        <v>0.99909852</v>
+        <v>1.000319473</v>
       </c>
       <c r="F43">
-        <v>0.99909852</v>
+        <v>1.000319473</v>
       </c>
       <c r="G43">
-        <v>0.2342423866086769</v>
+        <v>0.03515547182056333</v>
       </c>
       <c r="H43">
-        <v>0.9974930900000001</v>
+        <v>1.000319473</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C44">
-        <v>40.32854894972581</v>
+        <v>28.59002627414054</v>
       </c>
       <c r="D44">
-        <v>21.09133998298594</v>
+        <v>23.96230704059692</v>
       </c>
       <c r="E44">
-        <v>0.9990972199999999</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F44">
-        <v>0.9990972199999999</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G44">
-        <v>0.2156468205051487</v>
+        <v>0.05179637495949674</v>
       </c>
       <c r="H44">
-        <v>0.99752223</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C45">
-        <v>40.47987921095815</v>
+        <v>28.56217859389523</v>
       </c>
       <c r="D45">
-        <v>21.35995364434454</v>
+        <v>23.9411987302529</v>
       </c>
       <c r="E45">
-        <v>0.9991780100000001</v>
+        <v>1</v>
       </c>
       <c r="F45">
-        <v>0.9991780100000001</v>
+        <v>1</v>
       </c>
       <c r="G45">
-        <v>0.2270956128473374</v>
+        <v>0.04837024516756849</v>
       </c>
       <c r="H45">
-        <v>0.9975825700000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C46">
-        <v>41.20436574895244</v>
+        <v>28.57618675936338</v>
       </c>
       <c r="D46">
-        <v>21.48149674387778</v>
+        <v>23.9576220541054</v>
       </c>
       <c r="E46">
-        <v>0.9991793299999999</v>
+        <v>0.999503249</v>
       </c>
       <c r="F46">
-        <v>0.9991793299999999</v>
+        <v>0.999503249</v>
       </c>
       <c r="G46">
-        <v>0.2454829228401052</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H46">
-        <v>0.99754722</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B47" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C47">
-        <v>40.80613062958688</v>
+        <v>28.68951918518517</v>
       </c>
       <c r="D47">
-        <v>21.08912555803936</v>
+        <v>24.06134728453882</v>
       </c>
       <c r="E47">
-        <v>0.9991790600000001</v>
+        <v>0.999503249</v>
       </c>
       <c r="F47">
-        <v>0.9991790600000001</v>
+        <v>0.999503249</v>
       </c>
       <c r="G47">
-        <v>0.2230017445022556</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H47">
-        <v>0.9975824700000002</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B48" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48">
+        <v>28.27081472968482</v>
+      </c>
+      <c r="D48">
+        <v>23.71928084820412</v>
+      </c>
+      <c r="E48">
+        <v>1.000177331</v>
+      </c>
+      <c r="F48">
+        <v>1.000177331</v>
+      </c>
+      <c r="G48">
+        <v>0.04298642787381968</v>
+      </c>
+      <c r="H48">
+        <v>1.000177331</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B49" t="s">
+        <v>15</v>
+      </c>
+      <c r="C49">
+        <v>40.68830633303975</v>
+      </c>
+      <c r="D49">
+        <v>21.50431773660198</v>
+      </c>
+      <c r="E49">
+        <v>0.99909852</v>
+      </c>
+      <c r="F49">
+        <v>0.99909852</v>
+      </c>
+      <c r="G49">
+        <v>0.2342423866086769</v>
+      </c>
+      <c r="H49">
+        <v>0.9974930900000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B50" t="s">
+        <v>15</v>
+      </c>
+      <c r="C50">
+        <v>40.32854894972581</v>
+      </c>
+      <c r="D50">
+        <v>21.09133998298594</v>
+      </c>
+      <c r="E50">
+        <v>0.9990972199999999</v>
+      </c>
+      <c r="F50">
+        <v>0.9990972199999999</v>
+      </c>
+      <c r="G50">
+        <v>0.2156468205051487</v>
+      </c>
+      <c r="H50">
+        <v>0.99752223</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B51" t="s">
+        <v>15</v>
+      </c>
+      <c r="C51">
+        <v>40.47987921095815</v>
+      </c>
+      <c r="D51">
+        <v>21.35995364434454</v>
+      </c>
+      <c r="E51">
+        <v>0.9991780100000001</v>
+      </c>
+      <c r="F51">
+        <v>0.9991780100000001</v>
+      </c>
+      <c r="G51">
+        <v>0.2270956128473374</v>
+      </c>
+      <c r="H51">
+        <v>0.9975825700000001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B52" t="s">
+        <v>15</v>
+      </c>
+      <c r="C52">
+        <v>41.20436574895244</v>
+      </c>
+      <c r="D52">
+        <v>21.48149674387778</v>
+      </c>
+      <c r="E52">
+        <v>0.9991793299999999</v>
+      </c>
+      <c r="F52">
+        <v>0.9991793299999999</v>
+      </c>
+      <c r="G52">
+        <v>0.2454829228401052</v>
+      </c>
+      <c r="H52">
+        <v>0.99754722</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B53" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53">
+        <v>40.80613062958688</v>
+      </c>
+      <c r="D53">
+        <v>21.08912555803936</v>
+      </c>
+      <c r="E53">
+        <v>0.9991790600000001</v>
+      </c>
+      <c r="F53">
+        <v>0.9991790600000001</v>
+      </c>
+      <c r="G53">
+        <v>0.2230017445022556</v>
+      </c>
+      <c r="H53">
+        <v>0.9975824700000002</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="1">
         <v>46160</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B54" t="s">
         <v>15</v>
       </c>
-      <c r="C48">
+      <c r="C54">
         <v>40.11672876026724</v>
       </c>
-      <c r="D48">
+      <c r="D54">
         <v>20.79541439916316</v>
       </c>
-      <c r="E48">
+      <c r="E54">
         <v>0.999152</v>
       </c>
-      <c r="F48">
+      <c r="F54">
         <v>0.999152</v>
       </c>
-      <c r="G48">
+      <c r="G54">
         <v>0.2098184021536666</v>
       </c>
-      <c r="H48">
+      <c r="H54">
         <v>0.9975007899999999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C55">
+        <v>39.6906260794726</v>
+      </c>
+      <c r="D55">
+        <v>20.73623051383995</v>
+      </c>
+      <c r="E55">
+        <v>0.99914989</v>
+      </c>
+      <c r="F55">
+        <v>0.99914989</v>
+      </c>
+      <c r="G55">
+        <v>0.1987860161580062</v>
+      </c>
+      <c r="H55">
+        <v>0.9974417</v>
       </c>
     </row>
   </sheetData>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="16">
   <si>
     <t>Date</t>
   </si>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -590,10 +590,10 @@
         <v>8</v>
       </c>
       <c r="C8">
-        <v>50.13081250240213</v>
+        <v>50.41417290445963</v>
       </c>
       <c r="D8">
-        <v>24.12678679258809</v>
+        <v>24.2763908467475</v>
       </c>
       <c r="E8">
         <v>0.9259000000000001</v>
@@ -602,7 +602,7 @@
         <v>0.9259000000000001</v>
       </c>
       <c r="G8">
-        <v>0.319576918507692</v>
+        <v>0.3424657642981368</v>
       </c>
       <c r="H8">
         <v>0.9259000000000001</v>
@@ -772,10 +772,10 @@
         <v>9</v>
       </c>
       <c r="C15">
-        <v>34.12713174867851</v>
+        <v>34.25540193117895</v>
       </c>
       <c r="D15">
-        <v>25.56917319151027</v>
+        <v>25.6645407902341</v>
       </c>
       <c r="E15">
         <v>0.9985999999999999</v>
@@ -784,7 +784,7 @@
         <v>0.9985999999999999</v>
       </c>
       <c r="G15">
-        <v>0.04514161662612648</v>
+        <v>0.05034431510859494</v>
       </c>
       <c r="H15">
         <v>0.9985999999999999</v>
@@ -954,10 +954,10 @@
         <v>10</v>
       </c>
       <c r="C22">
-        <v>35.98205372592128</v>
+        <v>36.18806580365983</v>
       </c>
       <c r="D22">
-        <v>22.15980569372351</v>
+        <v>22.36877300491099</v>
       </c>
       <c r="E22">
         <v>0.9993222199999999</v>
@@ -966,7 +966,7 @@
         <v>0.9993222199999999</v>
       </c>
       <c r="G22">
-        <v>0.1413365165217606</v>
+        <v>0.1520248570974059</v>
       </c>
       <c r="H22">
         <v>0.9993222199999999</v>
@@ -1136,10 +1136,10 @@
         <v>11</v>
       </c>
       <c r="C29">
-        <v>49.26275747752842</v>
+        <v>49.82623808958123</v>
       </c>
       <c r="D29">
-        <v>22.22547935840584</v>
+        <v>22.50598722801563</v>
       </c>
       <c r="E29">
         <v>0.9998</v>
@@ -1148,7 +1148,7 @@
         <v>0.9998</v>
       </c>
       <c r="G29">
-        <v>0.4534691530468447</v>
+        <v>0.4722742929494663</v>
       </c>
       <c r="H29">
         <v>0.9998</v>
@@ -1286,328 +1286,328 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1">
-        <v>46153</v>
+        <v>46161</v>
       </c>
       <c r="B35" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C35">
-        <v>35.78646526282436</v>
+        <v>53.27576798661448</v>
       </c>
       <c r="D35">
-        <v>18.96635091925032</v>
+        <v>21.85720371153168</v>
       </c>
       <c r="E35">
-        <v>0.9996491399999999</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="F35">
-        <v>0.9996491399999999</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="G35">
-        <v>0.2240600969213613</v>
+        <v>0.602312739683422</v>
       </c>
       <c r="H35">
-        <v>0.9985614899999999</v>
+        <v>0.9988999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
       </c>
       <c r="C36">
-        <v>35.71584102184062</v>
+        <v>35.78646526282436</v>
       </c>
       <c r="D36">
-        <v>18.62432950231353</v>
+        <v>18.96635091925032</v>
       </c>
       <c r="E36">
-        <v>0.99965481</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="F36">
-        <v>0.99965481</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="G36">
-        <v>0.2104844827747143</v>
+        <v>0.2240600969213613</v>
       </c>
       <c r="H36">
-        <v>0.9985622199999999</v>
+        <v>0.9985614899999999</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
       </c>
       <c r="C37">
-        <v>35.95182028203252</v>
+        <v>35.71584102184062</v>
       </c>
       <c r="D37">
-        <v>18.95670796791552</v>
+        <v>18.62432950231353</v>
       </c>
       <c r="E37">
-        <v>0.9996515200000001</v>
+        <v>0.99965481</v>
       </c>
       <c r="F37">
-        <v>0.9996515200000001</v>
+        <v>0.99965481</v>
       </c>
       <c r="G37">
-        <v>0.2259035693959275</v>
+        <v>0.2104844827747143</v>
       </c>
       <c r="H37">
-        <v>0.99855193</v>
+        <v>0.9985622199999999</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
       </c>
       <c r="C38">
-        <v>36.14451597805883</v>
+        <v>35.95182028203252</v>
       </c>
       <c r="D38">
-        <v>18.86297660538653</v>
+        <v>18.95670796791552</v>
       </c>
       <c r="E38">
-        <v>0.9996563399999999</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="F38">
-        <v>0.9996563399999999</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="G38">
-        <v>0.2362110061840785</v>
+        <v>0.2259035693959275</v>
       </c>
       <c r="H38">
-        <v>0.99857265</v>
+        <v>0.99855193</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
       </c>
       <c r="C39">
-        <v>35.32805803135546</v>
+        <v>36.14451597805883</v>
       </c>
       <c r="D39">
-        <v>18.35643242381478</v>
+        <v>18.86297660538653</v>
       </c>
       <c r="E39">
-        <v>0.9997415800000001</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="F39">
-        <v>0.9997415800000001</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="G39">
-        <v>0.2023559161375383</v>
+        <v>0.2362110061840785</v>
       </c>
       <c r="H39">
-        <v>0.9986639900000002</v>
+        <v>0.99857265</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
       </c>
       <c r="C40">
-        <v>34.83995455757461</v>
+        <v>35.32805803135546</v>
       </c>
       <c r="D40">
-        <v>18.02301281718857</v>
+        <v>18.35643242381478</v>
       </c>
       <c r="E40">
-        <v>0.9996851299999999</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="F40">
-        <v>0.9996851299999999</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="G40">
-        <v>0.1850932291737926</v>
+        <v>0.2023559161375383</v>
       </c>
       <c r="H40">
-        <v>0.99857724</v>
+        <v>0.9986639900000002</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
       </c>
       <c r="C41">
-        <v>34.39756871976165</v>
+        <v>34.83995455757461</v>
       </c>
       <c r="D41">
-        <v>18.04233141064392</v>
+        <v>18.02301281718857</v>
       </c>
       <c r="E41">
-        <v>0.9996803099999999</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="F41">
-        <v>0.9996803099999999</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="G41">
-        <v>0.1745345318312599</v>
+        <v>0.1850932291737926</v>
       </c>
       <c r="H41">
-        <v>0.9985337599999999</v>
+        <v>0.99857724</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1">
-        <v>46153</v>
+        <v>46161</v>
       </c>
       <c r="B42" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C42">
-        <v>28.12253390077671</v>
+        <v>34.67094791506609</v>
       </c>
       <c r="D42">
-        <v>23.58699683751922</v>
+        <v>18.25363286935865</v>
       </c>
       <c r="E42">
-        <v>0.9997295369999999</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="F42">
-        <v>0.9997295369999999</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="G42">
-        <v>0.03368732240295347</v>
+        <v>0.1855960060184894</v>
       </c>
       <c r="H42">
-        <v>0.9997295369999999</v>
+        <v>0.9985337599999999</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B43" t="s">
         <v>14</v>
       </c>
       <c r="C43">
-        <v>28.17715727830483</v>
+        <v>28.12253390077671</v>
       </c>
       <c r="D43">
-        <v>23.63894513078866</v>
+        <v>23.58699683751922</v>
       </c>
       <c r="E43">
-        <v>1.000319473</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="F43">
-        <v>1.000319473</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="G43">
-        <v>0.03515547182056333</v>
+        <v>0.03368732240295347</v>
       </c>
       <c r="H43">
-        <v>1.000319473</v>
+        <v>0.9997295369999999</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B44" t="s">
         <v>14</v>
       </c>
       <c r="C44">
-        <v>28.59002627414054</v>
+        <v>28.17715727830483</v>
       </c>
       <c r="D44">
-        <v>23.96230704059692</v>
+        <v>23.63894513078866</v>
       </c>
       <c r="E44">
-        <v>0.9999999989999999</v>
+        <v>1.000319473</v>
       </c>
       <c r="F44">
-        <v>0.9999999989999999</v>
+        <v>1.000319473</v>
       </c>
       <c r="G44">
-        <v>0.05179637495949674</v>
+        <v>0.03515547182056333</v>
       </c>
       <c r="H44">
-        <v>0.9999999989999999</v>
+        <v>1.000319473</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B45" t="s">
         <v>14</v>
       </c>
       <c r="C45">
-        <v>28.56217859389523</v>
+        <v>28.59002627414054</v>
       </c>
       <c r="D45">
-        <v>23.9411987302529</v>
+        <v>23.96230704059692</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G45">
-        <v>0.04837024516756849</v>
+        <v>0.05179637495949674</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="B46" t="s">
         <v>14</v>
       </c>
       <c r="C46">
-        <v>28.57618675936338</v>
+        <v>28.56217859389523</v>
       </c>
       <c r="D46">
-        <v>23.9576220541054</v>
+        <v>23.9411987302529</v>
       </c>
       <c r="E46">
-        <v>0.999503249</v>
+        <v>1</v>
       </c>
       <c r="F46">
-        <v>0.999503249</v>
+        <v>1</v>
       </c>
       <c r="G46">
-        <v>0.04983868243960732</v>
+        <v>0.04837024516756849</v>
       </c>
       <c r="H46">
-        <v>0.999503249</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="B47" t="s">
         <v>14</v>
       </c>
       <c r="C47">
-        <v>28.68951918518517</v>
+        <v>28.57618675936338</v>
       </c>
       <c r="D47">
-        <v>24.06134728453882</v>
+        <v>23.9576220541054</v>
       </c>
       <c r="E47">
         <v>0.999503249</v>
@@ -1624,209 +1624,235 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="B48" t="s">
         <v>14</v>
       </c>
       <c r="C48">
-        <v>28.27081472968482</v>
+        <v>28.68951918518517</v>
       </c>
       <c r="D48">
-        <v>23.71928084820412</v>
+        <v>24.06134728453882</v>
       </c>
       <c r="E48">
-        <v>1.000177331</v>
+        <v>0.999503249</v>
       </c>
       <c r="F48">
-        <v>1.000177331</v>
+        <v>0.999503249</v>
       </c>
       <c r="G48">
-        <v>0.04298642787381968</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H48">
-        <v>1.000177331</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1">
-        <v>46153</v>
+        <v>46161</v>
       </c>
       <c r="B49" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C49">
-        <v>40.68830633303975</v>
+        <v>28.32991568770565</v>
       </c>
       <c r="D49">
-        <v>21.50431773660198</v>
+        <v>23.76389398471357</v>
       </c>
       <c r="E49">
-        <v>0.99909852</v>
+        <v>1.000177331</v>
       </c>
       <c r="F49">
-        <v>0.99909852</v>
+        <v>1.000177331</v>
       </c>
       <c r="G49">
-        <v>0.2342423866086769</v>
+        <v>0.03760270393243093</v>
       </c>
       <c r="H49">
-        <v>0.9974930900000001</v>
+        <v>1.000177331</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B50" t="s">
         <v>15</v>
       </c>
       <c r="C50">
-        <v>40.32854894972581</v>
+        <v>40.68830633303975</v>
       </c>
       <c r="D50">
-        <v>21.09133998298594</v>
+        <v>21.50431773660198</v>
       </c>
       <c r="E50">
-        <v>0.9990972199999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="F50">
-        <v>0.9990972199999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="G50">
-        <v>0.2156468205051487</v>
+        <v>0.2342423866086769</v>
       </c>
       <c r="H50">
-        <v>0.99752223</v>
+        <v>0.9974930900000001</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B51" t="s">
         <v>15</v>
       </c>
       <c r="C51">
-        <v>40.47987921095815</v>
+        <v>40.32854894972581</v>
       </c>
       <c r="D51">
-        <v>21.35995364434454</v>
+        <v>21.09133998298594</v>
       </c>
       <c r="E51">
-        <v>0.9991780100000001</v>
+        <v>0.9990972199999999</v>
       </c>
       <c r="F51">
-        <v>0.9991780100000001</v>
+        <v>0.9990972199999999</v>
       </c>
       <c r="G51">
-        <v>0.2270956128473374</v>
+        <v>0.2156468205051487</v>
       </c>
       <c r="H51">
-        <v>0.9975825700000001</v>
+        <v>0.99752223</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B52" t="s">
         <v>15</v>
       </c>
       <c r="C52">
-        <v>41.20436574895244</v>
+        <v>40.47987921095815</v>
       </c>
       <c r="D52">
-        <v>21.48149674387778</v>
+        <v>21.35995364434454</v>
       </c>
       <c r="E52">
-        <v>0.9991793299999999</v>
+        <v>0.9991780100000001</v>
       </c>
       <c r="F52">
-        <v>0.9991793299999999</v>
+        <v>0.9991780100000001</v>
       </c>
       <c r="G52">
-        <v>0.2454829228401052</v>
+        <v>0.2270956128473374</v>
       </c>
       <c r="H52">
-        <v>0.99754722</v>
+        <v>0.9975825700000001</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="B53" t="s">
         <v>15</v>
       </c>
       <c r="C53">
-        <v>40.80613062958688</v>
+        <v>41.20436574895244</v>
       </c>
       <c r="D53">
-        <v>21.08912555803936</v>
+        <v>21.48149674387778</v>
       </c>
       <c r="E53">
-        <v>0.9991790600000001</v>
+        <v>0.9991793299999999</v>
       </c>
       <c r="F53">
-        <v>0.9991790600000001</v>
+        <v>0.9991793299999999</v>
       </c>
       <c r="G53">
-        <v>0.2230017445022556</v>
+        <v>0.2454829228401052</v>
       </c>
       <c r="H53">
-        <v>0.9975824700000002</v>
+        <v>0.99754722</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="B54" t="s">
         <v>15</v>
       </c>
       <c r="C54">
-        <v>40.11672876026724</v>
+        <v>40.80613062958688</v>
       </c>
       <c r="D54">
-        <v>20.79541439916316</v>
+        <v>21.08912555803936</v>
       </c>
       <c r="E54">
-        <v>0.999152</v>
+        <v>0.9991790600000001</v>
       </c>
       <c r="F54">
-        <v>0.999152</v>
+        <v>0.9991790600000001</v>
       </c>
       <c r="G54">
-        <v>0.2098184021536666</v>
+        <v>0.2230017445022556</v>
       </c>
       <c r="H54">
-        <v>0.9975007899999999</v>
+        <v>0.9975824700000002</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="B55" t="s">
         <v>15</v>
       </c>
       <c r="C55">
-        <v>39.6906260794726</v>
+        <v>40.11672876026724</v>
       </c>
       <c r="D55">
-        <v>20.73623051383995</v>
+        <v>20.79541439916316</v>
       </c>
       <c r="E55">
+        <v>0.999152</v>
+      </c>
+      <c r="F55">
+        <v>0.999152</v>
+      </c>
+      <c r="G55">
+        <v>0.2098184021536666</v>
+      </c>
+      <c r="H55">
+        <v>0.9975007899999999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B56" t="s">
+        <v>15</v>
+      </c>
+      <c r="C56">
+        <v>39.94139653421203</v>
+      </c>
+      <c r="D56">
+        <v>20.93911458867925</v>
+      </c>
+      <c r="E56">
         <v>0.99914989</v>
       </c>
-      <c r="F55">
+      <c r="F56">
         <v>0.99914989</v>
       </c>
-      <c r="G55">
-        <v>0.1987860161580062</v>
-      </c>
-      <c r="H55">
+      <c r="G56">
+        <v>0.210789805212247</v>
+      </c>
+      <c r="H56">
         <v>0.9974417</v>
       </c>
     </row>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -590,10 +590,10 @@
         <v>8</v>
       </c>
       <c r="C8">
-        <v>50.41417290445963</v>
+        <v>50.11981086673613</v>
       </c>
       <c r="D8">
-        <v>24.2763908467475</v>
+        <v>24.13061679021705</v>
       </c>
       <c r="E8">
         <v>0.9259000000000001</v>
@@ -602,7 +602,7 @@
         <v>0.9259000000000001</v>
       </c>
       <c r="G8">
-        <v>0.3424657642981368</v>
+        <v>0.3258193430227221</v>
       </c>
       <c r="H8">
         <v>0.9259000000000001</v>
@@ -772,22 +772,22 @@
         <v>9</v>
       </c>
       <c r="C15">
-        <v>34.25540193117895</v>
+        <v>34.21212662725402</v>
       </c>
       <c r="D15">
-        <v>25.6645407902341</v>
+        <v>25.60349394367002</v>
       </c>
       <c r="E15">
-        <v>0.9985999999999999</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="F15">
-        <v>0.9985999999999999</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="G15">
-        <v>0.05034431510859494</v>
+        <v>0.0486610616591685</v>
       </c>
       <c r="H15">
-        <v>0.9985999999999999</v>
+        <v>0.9984999999999998</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -954,10 +954,10 @@
         <v>10</v>
       </c>
       <c r="C22">
-        <v>36.18806580365983</v>
+        <v>36.01040085730018</v>
       </c>
       <c r="D22">
-        <v>22.36877300491099</v>
+        <v>22.19475589056387</v>
       </c>
       <c r="E22">
         <v>0.9993222199999999</v>
@@ -966,7 +966,7 @@
         <v>0.9993222199999999</v>
       </c>
       <c r="G22">
-        <v>0.1520248570974059</v>
+        <v>0.1456396418594061</v>
       </c>
       <c r="H22">
         <v>0.9993222199999999</v>
@@ -1136,10 +1136,10 @@
         <v>11</v>
       </c>
       <c r="C29">
-        <v>49.82623808958123</v>
+        <v>49.29146729279496</v>
       </c>
       <c r="D29">
-        <v>22.50598722801563</v>
+        <v>22.22167836589682</v>
       </c>
       <c r="E29">
         <v>0.9998</v>
@@ -1148,7 +1148,7 @@
         <v>0.9998</v>
       </c>
       <c r="G29">
-        <v>0.4722742929494663</v>
+        <v>0.4571659248870246</v>
       </c>
       <c r="H29">
         <v>0.9998</v>
@@ -1292,10 +1292,10 @@
         <v>12</v>
       </c>
       <c r="C35">
-        <v>53.27576798661448</v>
+        <v>52.6278781150669</v>
       </c>
       <c r="D35">
-        <v>21.85720371153168</v>
+        <v>21.5357353870778</v>
       </c>
       <c r="E35">
         <v>0.9988999999999999</v>
@@ -1304,7 +1304,7 @@
         <v>0.9988999999999999</v>
       </c>
       <c r="G35">
-        <v>0.602312739683422</v>
+        <v>0.5845134636435627</v>
       </c>
       <c r="H35">
         <v>0.9988999999999999</v>
@@ -1474,10 +1474,10 @@
         <v>13</v>
       </c>
       <c r="C42">
-        <v>34.67094791506609</v>
+        <v>34.45479308705605</v>
       </c>
       <c r="D42">
-        <v>18.25363286935865</v>
+        <v>18.09576834566068</v>
       </c>
       <c r="E42">
         <v>0.9996803099999999</v>
@@ -1486,7 +1486,7 @@
         <v>0.9996803099999999</v>
       </c>
       <c r="G42">
-        <v>0.1855960060184894</v>
+        <v>0.1784731209386736</v>
       </c>
       <c r="H42">
         <v>0.9985337599999999</v>
@@ -1656,10 +1656,10 @@
         <v>14</v>
       </c>
       <c r="C49">
-        <v>28.32991568770565</v>
+        <v>28.31167386654059</v>
       </c>
       <c r="D49">
-        <v>23.76389398471357</v>
+        <v>23.75157719455474</v>
       </c>
       <c r="E49">
         <v>1.000177331</v>
@@ -1668,7 +1668,7 @@
         <v>1.000177331</v>
       </c>
       <c r="G49">
-        <v>0.03760270393243093</v>
+        <v>0.04053938625111919</v>
       </c>
       <c r="H49">
         <v>1.000177331</v>
@@ -1838,10 +1838,10 @@
         <v>15</v>
       </c>
       <c r="C56">
-        <v>39.94139653421203</v>
+        <v>39.69086941528401</v>
       </c>
       <c r="D56">
-        <v>20.93911458867925</v>
+        <v>20.74924328599426</v>
       </c>
       <c r="E56">
         <v>0.99914989</v>
@@ -1850,7 +1850,7 @@
         <v>0.99914989</v>
       </c>
       <c r="G56">
-        <v>0.210789805212247</v>
+        <v>0.2020471776850241</v>
       </c>
       <c r="H56">
         <v>0.9974417</v>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="17">
   <si>
     <t>Date</t>
   </si>
@@ -38,6 +38,9 @@
   </si>
   <si>
     <t>Covered Weight</t>
+  </si>
+  <si>
+    <t>CHAT</t>
   </si>
   <si>
     <t>CHPS.TO</t>
@@ -397,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -428,42 +431,42 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1">
-        <v>46153</v>
+        <v>46162</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2">
-        <v>53.14833755912058</v>
+        <v>22.37524618271185</v>
       </c>
       <c r="D2">
-        <v>25.84885448407537</v>
+        <v>15.26948688081125</v>
       </c>
       <c r="E2">
-        <v>0.9262</v>
+        <v>0.8598999999999999</v>
       </c>
       <c r="F2">
-        <v>0.9262</v>
+        <v>0.8598999999999999</v>
       </c>
       <c r="G2">
-        <v>0.3839084462043663</v>
+        <v>0.4234128294606059</v>
       </c>
       <c r="H2">
-        <v>0.9262</v>
+        <v>0.9087</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>51.82921169635205</v>
+        <v>53.14833755912058</v>
       </c>
       <c r="D3">
-        <v>25.32805827181975</v>
+        <v>25.84885448407537</v>
       </c>
       <c r="E3">
         <v>0.9262</v>
@@ -472,7 +475,7 @@
         <v>0.9262</v>
       </c>
       <c r="G3">
-        <v>0.3568580281685669</v>
+        <v>0.3839084462043663</v>
       </c>
       <c r="H3">
         <v>0.9262</v>
@@ -480,120 +483,120 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>52.28471716753184</v>
+        <v>51.82921169635205</v>
       </c>
       <c r="D4">
-        <v>25.54525144150689</v>
+        <v>25.32805827181975</v>
       </c>
       <c r="E4">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="F4">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="G4">
-        <v>0.378012896547947</v>
+        <v>0.3568580281685669</v>
       </c>
       <c r="H4">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>53.87287273813902</v>
+        <v>52.28471716753184</v>
       </c>
       <c r="D5">
-        <v>26.32154226438612</v>
+        <v>25.54525144150689</v>
       </c>
       <c r="E5">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="F5">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="G5">
-        <v>0.4166811087612758</v>
+        <v>0.378012896547947</v>
       </c>
       <c r="H5">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>52.18747148214074</v>
+        <v>53.87287273813902</v>
       </c>
       <c r="D6">
-        <v>25.13616059644496</v>
+        <v>26.32154226438612</v>
       </c>
       <c r="E6">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="F6">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="G6">
-        <v>0.3627535778249862</v>
+        <v>0.4166811087612758</v>
       </c>
       <c r="H6">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>50.72035274995172</v>
+        <v>52.18747148214074</v>
       </c>
       <c r="D7">
-        <v>24.61756040386634</v>
+        <v>25.13616059644496</v>
       </c>
       <c r="E7">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="F7">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="G7">
         <v>0.3627535778249862</v>
       </c>
       <c r="H7">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8">
-        <v>50.11981086673613</v>
+        <v>50.72035274995172</v>
       </c>
       <c r="D8">
-        <v>24.13061679021705</v>
+        <v>24.61756040386634</v>
       </c>
       <c r="E8">
         <v>0.9259000000000001</v>
@@ -602,7 +605,7 @@
         <v>0.9259000000000001</v>
       </c>
       <c r="G8">
-        <v>0.3258193430227221</v>
+        <v>0.3627535778249862</v>
       </c>
       <c r="H8">
         <v>0.9259000000000001</v>
@@ -610,146 +613,146 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1">
-        <v>46153</v>
+        <v>46161</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
       </c>
       <c r="C9">
-        <v>34.64560932909123</v>
+        <v>50.11981086673613</v>
       </c>
       <c r="D9">
-        <v>26.08311546080494</v>
+        <v>24.13061679021705</v>
       </c>
       <c r="E9">
-        <v>0.9983000000000001</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="F9">
-        <v>0.9983000000000001</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="G9">
-        <v>0.06258613715048233</v>
+        <v>0.3258193430227221</v>
       </c>
       <c r="H9">
-        <v>0.9983000000000001</v>
+        <v>0.9259000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1">
-        <v>46154</v>
+        <v>46162</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
       </c>
       <c r="C10">
-        <v>34.50204921141101</v>
+        <v>51.95937354089963</v>
       </c>
       <c r="D10">
-        <v>25.94535229304585</v>
+        <v>24.96489538254654</v>
       </c>
       <c r="E10">
-        <v>0.9984</v>
+        <v>0.9252</v>
       </c>
       <c r="F10">
-        <v>0.9984</v>
+        <v>0.9252</v>
       </c>
       <c r="G10">
-        <v>0.05768943168306073</v>
+        <v>0.3794001313943973</v>
       </c>
       <c r="H10">
-        <v>0.9984</v>
+        <v>0.9252</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11">
-        <v>35.10429483281073</v>
+        <v>34.64560932909123</v>
       </c>
       <c r="D11">
-        <v>26.43864879939599</v>
+        <v>26.08311546080494</v>
       </c>
       <c r="E11">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="F11">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="G11">
-        <v>0.07926550001722021</v>
+        <v>0.06258613715048233</v>
       </c>
       <c r="H11">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12">
-        <v>35.36860632820093</v>
+        <v>34.50204921141101</v>
       </c>
       <c r="D12">
-        <v>26.56575571102338</v>
+        <v>25.94535229304585</v>
       </c>
       <c r="E12">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F12">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G12">
-        <v>0.08553946591902095</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H12">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13">
-        <v>34.88080083527914</v>
+        <v>35.10429483281073</v>
       </c>
       <c r="D13">
-        <v>26.19322945679072</v>
+        <v>26.43864879939599</v>
       </c>
       <c r="E13">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="F13">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="G13">
-        <v>0.06870693142475881</v>
+        <v>0.07926550001722021</v>
       </c>
       <c r="H13">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1">
-        <v>46160</v>
+        <v>46156</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14">
-        <v>34.67638692539213</v>
+        <v>35.36860632820093</v>
       </c>
       <c r="D14">
-        <v>26.06707890342319</v>
+        <v>26.56575571102338</v>
       </c>
       <c r="E14">
         <v>0.9985999999999999</v>
@@ -758,7 +761,7 @@
         <v>0.9985999999999999</v>
       </c>
       <c r="G14">
-        <v>0.06289213016552919</v>
+        <v>0.08553946591902095</v>
       </c>
       <c r="H14">
         <v>0.9985999999999999</v>
@@ -766,354 +769,354 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15">
-        <v>34.21212662725402</v>
+        <v>34.88080083527914</v>
       </c>
       <c r="D15">
-        <v>25.60349394367002</v>
+        <v>26.19322945679072</v>
       </c>
       <c r="E15">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="F15">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="G15">
-        <v>0.0486610616591685</v>
+        <v>0.06870693142475881</v>
       </c>
       <c r="H15">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="B16" t="s">
         <v>10</v>
       </c>
       <c r="C16">
-        <v>36.55790859258162</v>
+        <v>34.67638692539213</v>
       </c>
       <c r="D16">
-        <v>22.67181120908155</v>
+        <v>26.06707890342319</v>
       </c>
       <c r="E16">
-        <v>0.9990740999999999</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="F16">
-        <v>0.9990740999999999</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="G16">
-        <v>0.1648443271746771</v>
+        <v>0.06289213016552919</v>
       </c>
       <c r="H16">
-        <v>0.9990740999999999</v>
+        <v>0.9985999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
       </c>
       <c r="C17">
-        <v>36.44753722959613</v>
+        <v>34.21212662725402</v>
       </c>
       <c r="D17">
-        <v>22.40292401789388</v>
+        <v>25.60349394367002</v>
       </c>
       <c r="E17">
-        <v>0.9990772499999999</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="F17">
-        <v>0.9990772499999999</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="G17">
-        <v>0.154964342628132</v>
+        <v>0.0486610616591685</v>
       </c>
       <c r="H17">
-        <v>0.9990772499999999</v>
+        <v>0.9984999999999998</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1">
-        <v>46155</v>
+        <v>46162</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>
       </c>
       <c r="C18">
-        <v>36.63128514035871</v>
+        <v>34.55565809375118</v>
       </c>
       <c r="D18">
-        <v>22.65773388934668</v>
+        <v>25.81704570991075</v>
       </c>
       <c r="E18">
-        <v>0.99907745</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="F18">
-        <v>0.99907745</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="G18">
-        <v>0.1671633421405267</v>
+        <v>0.05937268513248695</v>
       </c>
       <c r="H18">
-        <v>0.99907745</v>
+        <v>0.9984999999999998</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="B19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C19">
-        <v>36.87865927427314</v>
+        <v>36.55790859258162</v>
       </c>
       <c r="D19">
-        <v>22.69755646854794</v>
+        <v>22.67181120908155</v>
       </c>
       <c r="E19">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="F19">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="G19">
-        <v>0.1754592080224002</v>
+        <v>0.1648443271746771</v>
       </c>
       <c r="H19">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="B20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C20">
-        <v>36.52208783231286</v>
+        <v>36.44753722959613</v>
       </c>
       <c r="D20">
-        <v>22.32462309676992</v>
+        <v>22.40292401789388</v>
       </c>
       <c r="E20">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="F20">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="G20">
-        <v>0.1577242156354994</v>
+        <v>0.154964342628132</v>
       </c>
       <c r="H20">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="B21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C21">
-        <v>36.25604200674668</v>
+        <v>36.63128514035871</v>
       </c>
       <c r="D21">
-        <v>22.16555007468561</v>
+        <v>22.65773388934668</v>
       </c>
       <c r="E21">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="F21">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="G21">
-        <v>0.1527434068648266</v>
+        <v>0.1671633421405267</v>
       </c>
       <c r="H21">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1">
-        <v>46161</v>
+        <v>46156</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C22">
-        <v>36.01040085730018</v>
+        <v>36.87865927427314</v>
       </c>
       <c r="D22">
-        <v>22.19475589056387</v>
+        <v>22.69755646854794</v>
       </c>
       <c r="E22">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="F22">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="G22">
-        <v>0.1456396418594061</v>
+        <v>0.1754592080224002</v>
       </c>
       <c r="H22">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="B23" t="s">
         <v>11</v>
       </c>
       <c r="C23">
-        <v>52.70832779833182</v>
+        <v>36.52208783231286</v>
       </c>
       <c r="D23">
-        <v>23.99044674439659</v>
+        <v>22.32462309676992</v>
       </c>
       <c r="E23">
-        <v>0.9994000000000002</v>
+        <v>0.99915499</v>
       </c>
       <c r="F23">
-        <v>0.9994000000000002</v>
+        <v>0.99915499</v>
       </c>
       <c r="G23">
-        <v>0.5438253854918791</v>
+        <v>0.1577242156354994</v>
       </c>
       <c r="H23">
-        <v>0.9994000000000002</v>
+        <v>0.99915499</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="B24" t="s">
         <v>11</v>
       </c>
       <c r="C24">
-        <v>50.89464485280568</v>
+        <v>36.25604200674668</v>
       </c>
       <c r="D24">
-        <v>23.21558303176282</v>
+        <v>22.16555007468561</v>
       </c>
       <c r="E24">
-        <v>0.9996</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="F24">
-        <v>0.9996</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="G24">
-        <v>0.5034825029548833</v>
+        <v>0.1527434068648266</v>
       </c>
       <c r="H24">
-        <v>0.9996</v>
+        <v>0.9991011900000002</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1">
-        <v>46155</v>
+        <v>46161</v>
       </c>
       <c r="B25" t="s">
         <v>11</v>
       </c>
       <c r="C25">
-        <v>51.8659994471731</v>
+        <v>36.01040085730018</v>
       </c>
       <c r="D25">
-        <v>23.7009037279043</v>
+        <v>22.19475589056387</v>
       </c>
       <c r="E25">
-        <v>1.0002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="F25">
-        <v>1.0002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="G25">
-        <v>0.533512029714132</v>
+        <v>0.1456396418594061</v>
       </c>
       <c r="H25">
-        <v>1.0002</v>
+        <v>0.9993222199999999</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1">
-        <v>46156</v>
+        <v>46162</v>
       </c>
       <c r="B26" t="s">
         <v>11</v>
       </c>
       <c r="C26">
-        <v>52.4470179952828</v>
+        <v>36.39687441295362</v>
       </c>
       <c r="D26">
-        <v>23.76861704536814</v>
+        <v>22.40139717894661</v>
       </c>
       <c r="E26">
-        <v>0.9998</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="F26">
-        <v>0.9998</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="G26">
-        <v>0.5492634496849078</v>
+        <v>0.1613479630823502</v>
       </c>
       <c r="H26">
-        <v>0.9998</v>
+        <v>0.9992557700000001</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C27">
-        <v>50.81077380018606</v>
+        <v>52.70832779833182</v>
       </c>
       <c r="D27">
-        <v>22.76900580927995</v>
+        <v>23.99044674439659</v>
       </c>
       <c r="E27">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="F27">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="G27">
-        <v>0.4903296143797722</v>
+        <v>0.5438253854918791</v>
       </c>
       <c r="H27">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1">
-        <v>46160</v>
+        <v>46154</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C28">
-        <v>49.50286387149169</v>
+        <v>50.89464485280568</v>
       </c>
       <c r="D28">
-        <v>22.24532119914133</v>
+        <v>23.21558303176282</v>
       </c>
       <c r="E28">
         <v>0.9996</v>
@@ -1122,7 +1125,7 @@
         <v>0.9996</v>
       </c>
       <c r="G28">
-        <v>0.4630591776162345</v>
+        <v>0.5034825029548833</v>
       </c>
       <c r="H28">
         <v>0.9996</v>
@@ -1130,548 +1133,548 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1">
-        <v>46161</v>
+        <v>46155</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C29">
-        <v>49.29146729279496</v>
+        <v>51.8659994471731</v>
       </c>
       <c r="D29">
-        <v>22.22167836589682</v>
+        <v>23.7009037279043</v>
       </c>
       <c r="E29">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="F29">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="G29">
-        <v>0.4571659248870246</v>
+        <v>0.533512029714132</v>
       </c>
       <c r="H29">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="B30" t="s">
         <v>12</v>
       </c>
       <c r="C30">
-        <v>57.1732166855686</v>
+        <v>52.4470179952828</v>
       </c>
       <c r="D30">
-        <v>23.50022751267814</v>
+        <v>23.76861704536814</v>
       </c>
       <c r="E30">
-        <v>0.9991</v>
+        <v>0.9998</v>
       </c>
       <c r="F30">
-        <v>0.9991</v>
+        <v>0.9998</v>
       </c>
       <c r="G30">
-        <v>0.6994110097039083</v>
+        <v>0.5492634496849078</v>
       </c>
       <c r="H30">
-        <v>0.9991</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="B31" t="s">
         <v>12</v>
       </c>
       <c r="C31">
-        <v>54.77380642078597</v>
+        <v>50.81077380018606</v>
       </c>
       <c r="D31">
-        <v>22.55192940254518</v>
+        <v>22.76900580927995</v>
       </c>
       <c r="E31">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
       <c r="F31">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
       <c r="G31">
-        <v>0.6459175880844941</v>
+        <v>0.4903296143797722</v>
       </c>
       <c r="H31">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1">
-        <v>46155</v>
+        <v>46160</v>
       </c>
       <c r="B32" t="s">
         <v>12</v>
       </c>
       <c r="C32">
-        <v>56.32187380830906</v>
+        <v>49.50286387149169</v>
       </c>
       <c r="D32">
-        <v>23.17121437414109</v>
+        <v>22.24532119914133</v>
       </c>
       <c r="E32">
-        <v>0.9990000000000001</v>
+        <v>0.9996</v>
       </c>
       <c r="F32">
-        <v>0.9990000000000001</v>
+        <v>0.9996</v>
       </c>
       <c r="G32">
-        <v>0.6851523922954754</v>
+        <v>0.4630591776162345</v>
       </c>
       <c r="H32">
-        <v>0.9990000000000001</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1">
-        <v>46156</v>
+        <v>46161</v>
       </c>
       <c r="B33" t="s">
         <v>12</v>
       </c>
       <c r="C33">
-        <v>56.15321618553139</v>
+        <v>49.29146729279496</v>
       </c>
       <c r="D33">
-        <v>22.95838347314443</v>
+        <v>22.22167836589682</v>
       </c>
       <c r="E33">
-        <v>0.9992</v>
+        <v>0.9998</v>
       </c>
       <c r="F33">
-        <v>0.9992</v>
+        <v>0.9998</v>
       </c>
       <c r="G33">
-        <v>0.6907028507208208</v>
+        <v>0.4571659248870246</v>
       </c>
       <c r="H33">
-        <v>0.9992</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1">
-        <v>46157</v>
+        <v>46162</v>
       </c>
       <c r="B34" t="s">
         <v>12</v>
       </c>
       <c r="C34">
-        <v>54.47755813049488</v>
+        <v>50.83441153904246</v>
       </c>
       <c r="D34">
-        <v>22.0083816089626</v>
+        <v>22.82073918527218</v>
       </c>
       <c r="E34">
-        <v>0.9986</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F34">
-        <v>0.9986</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G34">
-        <v>0.6220895940829376</v>
+        <v>0.5021430976070391</v>
       </c>
       <c r="H34">
-        <v>0.9986</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C35">
-        <v>52.6278781150669</v>
+        <v>57.1732166855686</v>
       </c>
       <c r="D35">
-        <v>21.5357353870778</v>
+        <v>23.50022751267814</v>
       </c>
       <c r="E35">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F35">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G35">
-        <v>0.5845134636435627</v>
+        <v>0.6994110097039083</v>
       </c>
       <c r="H35">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
       </c>
       <c r="C36">
-        <v>35.78646526282436</v>
+        <v>54.77380642078597</v>
       </c>
       <c r="D36">
-        <v>18.96635091925032</v>
+        <v>22.55192940254518</v>
       </c>
       <c r="E36">
-        <v>0.9996491399999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F36">
-        <v>0.9996491399999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G36">
-        <v>0.2240600969213613</v>
+        <v>0.6459175880844941</v>
       </c>
       <c r="H36">
-        <v>0.9985614899999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
       </c>
       <c r="C37">
-        <v>35.71584102184062</v>
+        <v>56.32187380830906</v>
       </c>
       <c r="D37">
-        <v>18.62432950231353</v>
+        <v>23.17121437414109</v>
       </c>
       <c r="E37">
-        <v>0.99965481</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F37">
-        <v>0.99965481</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G37">
-        <v>0.2104844827747143</v>
+        <v>0.6851523922954754</v>
       </c>
       <c r="H37">
-        <v>0.9985622199999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
       </c>
       <c r="C38">
-        <v>35.95182028203252</v>
+        <v>56.15321618553139</v>
       </c>
       <c r="D38">
-        <v>18.95670796791552</v>
+        <v>22.95838347314443</v>
       </c>
       <c r="E38">
-        <v>0.9996515200000001</v>
+        <v>0.9992</v>
       </c>
       <c r="F38">
-        <v>0.9996515200000001</v>
+        <v>0.9992</v>
       </c>
       <c r="G38">
-        <v>0.2259035693959275</v>
+        <v>0.6907028507208208</v>
       </c>
       <c r="H38">
-        <v>0.99855193</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
       </c>
       <c r="C39">
-        <v>36.14451597805883</v>
+        <v>54.47755813049488</v>
       </c>
       <c r="D39">
-        <v>18.86297660538653</v>
+        <v>22.0083816089626</v>
       </c>
       <c r="E39">
-        <v>0.9996563399999999</v>
+        <v>0.9986</v>
       </c>
       <c r="F39">
-        <v>0.9996563399999999</v>
+        <v>0.9986</v>
       </c>
       <c r="G39">
-        <v>0.2362110061840785</v>
+        <v>0.6220895940829376</v>
       </c>
       <c r="H39">
-        <v>0.99857265</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
       </c>
       <c r="C40">
-        <v>35.32805803135546</v>
+        <v>52.6278781150669</v>
       </c>
       <c r="D40">
-        <v>18.35643242381478</v>
+        <v>21.5357353870778</v>
       </c>
       <c r="E40">
-        <v>0.9997415800000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="F40">
-        <v>0.9997415800000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="G40">
-        <v>0.2023559161375383</v>
+        <v>0.5845134636435627</v>
       </c>
       <c r="H40">
-        <v>0.9986639900000002</v>
+        <v>0.9988999999999999</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
       </c>
       <c r="C41">
-        <v>34.83995455757461</v>
+        <v>54.56468576204723</v>
       </c>
       <c r="D41">
-        <v>18.02301281718857</v>
+        <v>22.20904610919571</v>
       </c>
       <c r="E41">
-        <v>0.9996851299999999</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="F41">
-        <v>0.9996851299999999</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="G41">
-        <v>0.1850932291737926</v>
+        <v>0.6447373685406854</v>
       </c>
       <c r="H41">
-        <v>0.99857724</v>
+        <v>0.9990999999999999</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B42" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C42">
-        <v>34.45479308705605</v>
+        <v>35.78646526282436</v>
       </c>
       <c r="D42">
-        <v>18.09576834566068</v>
+        <v>18.96635091925032</v>
       </c>
       <c r="E42">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="F42">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="G42">
-        <v>0.1784731209386736</v>
+        <v>0.2240600969213613</v>
       </c>
       <c r="H42">
-        <v>0.9985337599999999</v>
+        <v>0.9985614899999999</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B43" t="s">
         <v>14</v>
       </c>
       <c r="C43">
-        <v>28.12253390077671</v>
+        <v>35.71584102184062</v>
       </c>
       <c r="D43">
-        <v>23.58699683751922</v>
+        <v>18.62432950231353</v>
       </c>
       <c r="E43">
-        <v>0.9997295369999999</v>
+        <v>0.99965481</v>
       </c>
       <c r="F43">
-        <v>0.9997295369999999</v>
+        <v>0.99965481</v>
       </c>
       <c r="G43">
-        <v>0.03368732240295347</v>
+        <v>0.2104844827747143</v>
       </c>
       <c r="H43">
-        <v>0.9997295369999999</v>
+        <v>0.9985622199999999</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B44" t="s">
         <v>14</v>
       </c>
       <c r="C44">
-        <v>28.17715727830483</v>
+        <v>35.95182028203252</v>
       </c>
       <c r="D44">
-        <v>23.63894513078866</v>
+        <v>18.95670796791552</v>
       </c>
       <c r="E44">
-        <v>1.000319473</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="F44">
-        <v>1.000319473</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="G44">
-        <v>0.03515547182056333</v>
+        <v>0.2259035693959275</v>
       </c>
       <c r="H44">
-        <v>1.000319473</v>
+        <v>0.99855193</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B45" t="s">
         <v>14</v>
       </c>
       <c r="C45">
-        <v>28.59002627414054</v>
+        <v>36.14451597805883</v>
       </c>
       <c r="D45">
-        <v>23.96230704059692</v>
+        <v>18.86297660538653</v>
       </c>
       <c r="E45">
-        <v>0.9999999989999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="F45">
-        <v>0.9999999989999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="G45">
-        <v>0.05179637495949674</v>
+        <v>0.2362110061840785</v>
       </c>
       <c r="H45">
-        <v>0.9999999989999999</v>
+        <v>0.99857265</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B46" t="s">
         <v>14</v>
       </c>
       <c r="C46">
-        <v>28.56217859389523</v>
+        <v>35.32805803135546</v>
       </c>
       <c r="D46">
-        <v>23.9411987302529</v>
+        <v>18.35643242381478</v>
       </c>
       <c r="E46">
-        <v>1</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="F46">
-        <v>1</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="G46">
-        <v>0.04837024516756849</v>
+        <v>0.2023559161375383</v>
       </c>
       <c r="H46">
-        <v>1</v>
+        <v>0.9986639900000002</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B47" t="s">
         <v>14</v>
       </c>
       <c r="C47">
-        <v>28.57618675936338</v>
+        <v>34.83995455757461</v>
       </c>
       <c r="D47">
-        <v>23.9576220541054</v>
+        <v>18.02301281718857</v>
       </c>
       <c r="E47">
-        <v>0.999503249</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="F47">
-        <v>0.999503249</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="G47">
-        <v>0.04983868243960732</v>
+        <v>0.1850932291737926</v>
       </c>
       <c r="H47">
-        <v>0.999503249</v>
+        <v>0.99857724</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B48" t="s">
         <v>14</v>
       </c>
       <c r="C48">
-        <v>28.68951918518517</v>
+        <v>34.45479308705605</v>
       </c>
       <c r="D48">
-        <v>24.06134728453882</v>
+        <v>18.09576834566068</v>
       </c>
       <c r="E48">
-        <v>0.999503249</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="F48">
-        <v>0.999503249</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="G48">
-        <v>0.04983868243960732</v>
+        <v>0.1784731209386736</v>
       </c>
       <c r="H48">
-        <v>0.999503249</v>
+        <v>0.9985337599999999</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B49" t="s">
         <v>14</v>
       </c>
       <c r="C49">
-        <v>28.31167386654059</v>
+        <v>34.91466438419509</v>
       </c>
       <c r="D49">
-        <v>23.75157719455474</v>
+        <v>18.30346103715894</v>
       </c>
       <c r="E49">
-        <v>1.000177331</v>
+        <v>0.99963413</v>
       </c>
       <c r="F49">
-        <v>1.000177331</v>
+        <v>0.99963413</v>
       </c>
       <c r="G49">
-        <v>0.04053938625111919</v>
+        <v>0.1986679482446734</v>
       </c>
       <c r="H49">
-        <v>1.000177331</v>
+        <v>0.99848777</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1682,22 +1685,22 @@
         <v>15</v>
       </c>
       <c r="C50">
-        <v>40.68830633303975</v>
+        <v>28.12253390077671</v>
       </c>
       <c r="D50">
-        <v>21.50431773660198</v>
+        <v>23.58699683751922</v>
       </c>
       <c r="E50">
-        <v>0.99909852</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="F50">
-        <v>0.99909852</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="G50">
-        <v>0.2342423866086769</v>
+        <v>0.03368732240295347</v>
       </c>
       <c r="H50">
-        <v>0.9974930900000001</v>
+        <v>0.9997295369999999</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1708,22 +1711,22 @@
         <v>15</v>
       </c>
       <c r="C51">
-        <v>40.32854894972581</v>
+        <v>28.17715727830483</v>
       </c>
       <c r="D51">
-        <v>21.09133998298594</v>
+        <v>23.63894513078866</v>
       </c>
       <c r="E51">
-        <v>0.9990972199999999</v>
+        <v>1.000319473</v>
       </c>
       <c r="F51">
-        <v>0.9990972199999999</v>
+        <v>1.000319473</v>
       </c>
       <c r="G51">
-        <v>0.2156468205051487</v>
+        <v>0.03515547182056333</v>
       </c>
       <c r="H51">
-        <v>0.99752223</v>
+        <v>1.000319473</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -1734,22 +1737,22 @@
         <v>15</v>
       </c>
       <c r="C52">
-        <v>40.47987921095815</v>
+        <v>28.59002627414054</v>
       </c>
       <c r="D52">
-        <v>21.35995364434454</v>
+        <v>23.96230704059692</v>
       </c>
       <c r="E52">
-        <v>0.9991780100000001</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F52">
-        <v>0.9991780100000001</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G52">
-        <v>0.2270956128473374</v>
+        <v>0.05179637495949674</v>
       </c>
       <c r="H52">
-        <v>0.9975825700000001</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -1760,22 +1763,22 @@
         <v>15</v>
       </c>
       <c r="C53">
-        <v>41.20436574895244</v>
+        <v>28.56217859389523</v>
       </c>
       <c r="D53">
-        <v>21.48149674387778</v>
+        <v>23.9411987302529</v>
       </c>
       <c r="E53">
-        <v>0.9991793299999999</v>
+        <v>1</v>
       </c>
       <c r="F53">
-        <v>0.9991793299999999</v>
+        <v>1</v>
       </c>
       <c r="G53">
-        <v>0.2454829228401052</v>
+        <v>0.04837024516756849</v>
       </c>
       <c r="H53">
-        <v>0.99754722</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -1786,22 +1789,22 @@
         <v>15</v>
       </c>
       <c r="C54">
-        <v>40.80613062958688</v>
+        <v>28.57618675936338</v>
       </c>
       <c r="D54">
-        <v>21.08912555803936</v>
+        <v>23.9576220541054</v>
       </c>
       <c r="E54">
-        <v>0.9991790600000001</v>
+        <v>0.999503249</v>
       </c>
       <c r="F54">
-        <v>0.9991790600000001</v>
+        <v>0.999503249</v>
       </c>
       <c r="G54">
-        <v>0.2230017445022556</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H54">
-        <v>0.9975824700000002</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -1812,22 +1815,22 @@
         <v>15</v>
       </c>
       <c r="C55">
-        <v>40.11672876026724</v>
+        <v>28.68951918518517</v>
       </c>
       <c r="D55">
-        <v>20.79541439916316</v>
+        <v>24.06134728453882</v>
       </c>
       <c r="E55">
-        <v>0.999152</v>
+        <v>0.999503249</v>
       </c>
       <c r="F55">
-        <v>0.999152</v>
+        <v>0.999503249</v>
       </c>
       <c r="G55">
-        <v>0.2098184021536666</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H55">
-        <v>0.9975007899999999</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -1838,22 +1841,256 @@
         <v>15</v>
       </c>
       <c r="C56">
+        <v>28.31167386654059</v>
+      </c>
+      <c r="D56">
+        <v>23.75157719455474</v>
+      </c>
+      <c r="E56">
+        <v>1.000177331</v>
+      </c>
+      <c r="F56">
+        <v>1.000177331</v>
+      </c>
+      <c r="G56">
+        <v>0.04053938625111919</v>
+      </c>
+      <c r="H56">
+        <v>1.000177331</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B57" t="s">
+        <v>15</v>
+      </c>
+      <c r="C57">
+        <v>28.4769960549547</v>
+      </c>
+      <c r="D57">
+        <v>23.80617361075545</v>
+      </c>
+      <c r="E57">
+        <v>0.999503734</v>
+      </c>
+      <c r="F57">
+        <v>0.999503734</v>
+      </c>
+      <c r="G57">
+        <v>0.04200762838143257</v>
+      </c>
+      <c r="H57">
+        <v>0.999503734</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58">
+        <v>40.68830633303975</v>
+      </c>
+      <c r="D58">
+        <v>21.50431773660198</v>
+      </c>
+      <c r="E58">
+        <v>0.99909852</v>
+      </c>
+      <c r="F58">
+        <v>0.99909852</v>
+      </c>
+      <c r="G58">
+        <v>0.2342423866086769</v>
+      </c>
+      <c r="H58">
+        <v>0.9974930900000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59">
+        <v>40.32854894972581</v>
+      </c>
+      <c r="D59">
+        <v>21.09133998298594</v>
+      </c>
+      <c r="E59">
+        <v>0.9990972199999999</v>
+      </c>
+      <c r="F59">
+        <v>0.9990972199999999</v>
+      </c>
+      <c r="G59">
+        <v>0.2156468205051487</v>
+      </c>
+      <c r="H59">
+        <v>0.99752223</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60">
+        <v>40.47987921095815</v>
+      </c>
+      <c r="D60">
+        <v>21.35995364434454</v>
+      </c>
+      <c r="E60">
+        <v>0.9991780100000001</v>
+      </c>
+      <c r="F60">
+        <v>0.9991780100000001</v>
+      </c>
+      <c r="G60">
+        <v>0.2270956128473374</v>
+      </c>
+      <c r="H60">
+        <v>0.9975825700000001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61">
+        <v>41.20436574895244</v>
+      </c>
+      <c r="D61">
+        <v>21.48149674387778</v>
+      </c>
+      <c r="E61">
+        <v>0.9991793299999999</v>
+      </c>
+      <c r="F61">
+        <v>0.9991793299999999</v>
+      </c>
+      <c r="G61">
+        <v>0.2454829228401052</v>
+      </c>
+      <c r="H61">
+        <v>0.99754722</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62">
+        <v>40.80613062958688</v>
+      </c>
+      <c r="D62">
+        <v>21.08912555803936</v>
+      </c>
+      <c r="E62">
+        <v>0.9991790600000001</v>
+      </c>
+      <c r="F62">
+        <v>0.9991790600000001</v>
+      </c>
+      <c r="G62">
+        <v>0.2230017445022556</v>
+      </c>
+      <c r="H62">
+        <v>0.9975824700000002</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63">
+        <v>40.11672876026724</v>
+      </c>
+      <c r="D63">
+        <v>20.79541439916316</v>
+      </c>
+      <c r="E63">
+        <v>0.999152</v>
+      </c>
+      <c r="F63">
+        <v>0.999152</v>
+      </c>
+      <c r="G63">
+        <v>0.2098184021536666</v>
+      </c>
+      <c r="H63">
+        <v>0.9975007899999999</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64">
         <v>39.69086941528401</v>
       </c>
-      <c r="D56">
+      <c r="D64">
         <v>20.74924328599426</v>
       </c>
-      <c r="E56">
+      <c r="E64">
         <v>0.99914989</v>
       </c>
-      <c r="F56">
+      <c r="F64">
         <v>0.99914989</v>
       </c>
-      <c r="G56">
+      <c r="G64">
         <v>0.2020471776850241</v>
       </c>
-      <c r="H56">
+      <c r="H64">
         <v>0.9974417</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65">
+        <v>40.2667184266821</v>
+      </c>
+      <c r="D65">
+        <v>21.02916053406821</v>
+      </c>
+      <c r="E65">
+        <v>0.99915058</v>
+      </c>
+      <c r="F65">
+        <v>0.99915058</v>
+      </c>
+      <c r="G65">
+        <v>0.2235568470893006</v>
+      </c>
+      <c r="H65">
+        <v>0.9974415600000001</v>
       </c>
     </row>
   </sheetData>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -437,22 +437,22 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>22.37524618271185</v>
+        <v>22.82058997660883</v>
       </c>
       <c r="D2">
-        <v>15.26948688081125</v>
+        <v>15.48555269621395</v>
       </c>
       <c r="E2">
-        <v>0.8598999999999999</v>
+        <v>0.8658</v>
       </c>
       <c r="F2">
-        <v>0.8598999999999999</v>
+        <v>0.8658</v>
       </c>
       <c r="G2">
-        <v>0.4234128294606059</v>
+        <v>0.4290446087759137</v>
       </c>
       <c r="H2">
-        <v>0.9087</v>
+        <v>0.9148000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -645,10 +645,10 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>51.95937354089963</v>
+        <v>51.74165648409151</v>
       </c>
       <c r="D10">
-        <v>24.96489538254654</v>
+        <v>24.98091384114761</v>
       </c>
       <c r="E10">
         <v>0.9252</v>
@@ -657,7 +657,7 @@
         <v>0.9252</v>
       </c>
       <c r="G10">
-        <v>0.3794001313943973</v>
+        <v>0.3818277262286871</v>
       </c>
       <c r="H10">
         <v>0.9252</v>
@@ -853,22 +853,22 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>34.55565809375118</v>
+        <v>34.78598436564941</v>
       </c>
       <c r="D18">
-        <v>25.81704570991075</v>
+        <v>25.95505316769806</v>
       </c>
       <c r="E18">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="F18">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="G18">
-        <v>0.05937268513248695</v>
+        <v>0.06335117806143331</v>
       </c>
       <c r="H18">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1061,10 +1061,10 @@
         <v>11</v>
       </c>
       <c r="C26">
-        <v>36.39687441295362</v>
+        <v>36.45290912796982</v>
       </c>
       <c r="D26">
-        <v>22.40139717894661</v>
+        <v>22.46357594746874</v>
       </c>
       <c r="E26">
         <v>0.9992557700000001</v>
@@ -1073,7 +1073,7 @@
         <v>0.9992557700000001</v>
       </c>
       <c r="G26">
-        <v>0.1613479630823502</v>
+        <v>0.1646157747240327</v>
       </c>
       <c r="H26">
         <v>0.9992557700000001</v>
@@ -1269,10 +1269,10 @@
         <v>12</v>
       </c>
       <c r="C34">
-        <v>50.83441153904246</v>
+        <v>50.88652370817657</v>
       </c>
       <c r="D34">
-        <v>22.82073918527218</v>
+        <v>22.93254398967657</v>
       </c>
       <c r="E34">
         <v>0.9998999999999999</v>
@@ -1281,7 +1281,7 @@
         <v>0.9998999999999999</v>
       </c>
       <c r="G34">
-        <v>0.5021430976070391</v>
+        <v>0.5126171754864624</v>
       </c>
       <c r="H34">
         <v>0.9998999999999999</v>
@@ -1451,10 +1451,10 @@
         <v>13</v>
       </c>
       <c r="C41">
-        <v>54.56468576204723</v>
+        <v>54.91583234840245</v>
       </c>
       <c r="D41">
-        <v>22.20904610919571</v>
+        <v>22.38321645985006</v>
       </c>
       <c r="E41">
         <v>0.9990999999999999</v>
@@ -1463,7 +1463,7 @@
         <v>0.9990999999999999</v>
       </c>
       <c r="G41">
-        <v>0.6447373685406854</v>
+        <v>0.6596976539194066</v>
       </c>
       <c r="H41">
         <v>0.9990999999999999</v>
@@ -1659,10 +1659,10 @@
         <v>14</v>
       </c>
       <c r="C49">
-        <v>34.91466438419509</v>
+        <v>34.96336277390787</v>
       </c>
       <c r="D49">
-        <v>18.30346103715894</v>
+        <v>18.34938420029253</v>
       </c>
       <c r="E49">
         <v>0.99963413</v>
@@ -1671,7 +1671,7 @@
         <v>0.99963413</v>
       </c>
       <c r="G49">
-        <v>0.1986679482446734</v>
+        <v>0.2009313391215752</v>
       </c>
       <c r="H49">
         <v>0.99848777</v>
@@ -1867,10 +1867,10 @@
         <v>15</v>
       </c>
       <c r="C57">
-        <v>28.4769960549547</v>
+        <v>28.57911382310097</v>
       </c>
       <c r="D57">
-        <v>23.80617361075545</v>
+        <v>23.89431741541233</v>
       </c>
       <c r="E57">
         <v>0.999503734</v>
@@ -1879,7 +1879,7 @@
         <v>0.999503734</v>
       </c>
       <c r="G57">
-        <v>0.04200762838143257</v>
+        <v>0.04690190590044785</v>
       </c>
       <c r="H57">
         <v>0.999503734</v>
@@ -2075,10 +2075,10 @@
         <v>16</v>
       </c>
       <c r="C65">
-        <v>40.2667184266821</v>
+        <v>40.37836787855562</v>
       </c>
       <c r="D65">
-        <v>21.02916053406821</v>
+        <v>21.11271132314188</v>
       </c>
       <c r="E65">
         <v>0.99915058</v>
@@ -2087,7 +2087,7 @@
         <v>0.99915058</v>
       </c>
       <c r="G65">
-        <v>0.2235568470893006</v>
+        <v>0.2291077670847563</v>
       </c>
       <c r="H65">
         <v>0.9974415600000001</v>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="17">
   <si>
     <t>Date</t>
   </si>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -457,42 +457,42 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1">
-        <v>46153</v>
+        <v>46163</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>53.14833755912058</v>
+        <v>23.22061873427279</v>
       </c>
       <c r="D3">
-        <v>25.84885448407537</v>
+        <v>16.00384870003266</v>
       </c>
       <c r="E3">
-        <v>0.9262</v>
+        <v>0.867</v>
       </c>
       <c r="F3">
-        <v>0.9262</v>
+        <v>0.867</v>
       </c>
       <c r="G3">
-        <v>0.3839084462043663</v>
+        <v>0.469448563680241</v>
       </c>
       <c r="H3">
-        <v>0.9262</v>
+        <v>0.9137999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
       <c r="C4">
-        <v>51.82921169635205</v>
+        <v>53.14833755912058</v>
       </c>
       <c r="D4">
-        <v>25.32805827181975</v>
+        <v>25.84885448407537</v>
       </c>
       <c r="E4">
         <v>0.9262</v>
@@ -501,7 +501,7 @@
         <v>0.9262</v>
       </c>
       <c r="G4">
-        <v>0.3568580281685669</v>
+        <v>0.3839084462043663</v>
       </c>
       <c r="H4">
         <v>0.9262</v>
@@ -509,120 +509,120 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
       <c r="C5">
-        <v>52.28471716753184</v>
+        <v>51.82921169635205</v>
       </c>
       <c r="D5">
-        <v>25.54525144150689</v>
+        <v>25.32805827181975</v>
       </c>
       <c r="E5">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="F5">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="G5">
-        <v>0.378012896547947</v>
+        <v>0.3568580281685669</v>
       </c>
       <c r="H5">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
       </c>
       <c r="C6">
-        <v>53.87287273813902</v>
+        <v>52.28471716753184</v>
       </c>
       <c r="D6">
-        <v>26.32154226438612</v>
+        <v>25.54525144150689</v>
       </c>
       <c r="E6">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="F6">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="G6">
-        <v>0.4166811087612758</v>
+        <v>0.378012896547947</v>
       </c>
       <c r="H6">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
       </c>
       <c r="C7">
-        <v>52.18747148214074</v>
+        <v>53.87287273813902</v>
       </c>
       <c r="D7">
-        <v>25.13616059644496</v>
+        <v>26.32154226438612</v>
       </c>
       <c r="E7">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="F7">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="G7">
-        <v>0.3627535778249862</v>
+        <v>0.4166811087612758</v>
       </c>
       <c r="H7">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
       </c>
       <c r="C8">
-        <v>50.72035274995172</v>
+        <v>52.18747148214074</v>
       </c>
       <c r="D8">
-        <v>24.61756040386634</v>
+        <v>25.13616059644496</v>
       </c>
       <c r="E8">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="F8">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="G8">
         <v>0.3627535778249862</v>
       </c>
       <c r="H8">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
       </c>
       <c r="C9">
-        <v>50.11981086673613</v>
+        <v>50.72035274995172</v>
       </c>
       <c r="D9">
-        <v>24.13061679021705</v>
+        <v>24.61756040386634</v>
       </c>
       <c r="E9">
         <v>0.9259000000000001</v>
@@ -631,7 +631,7 @@
         <v>0.9259000000000001</v>
       </c>
       <c r="G9">
-        <v>0.3258193430227221</v>
+        <v>0.3627535778249862</v>
       </c>
       <c r="H9">
         <v>0.9259000000000001</v>
@@ -639,172 +639,172 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
       </c>
       <c r="C10">
-        <v>51.74165648409151</v>
+        <v>50.11981086673613</v>
       </c>
       <c r="D10">
-        <v>24.98091384114761</v>
+        <v>24.13061679021705</v>
       </c>
       <c r="E10">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="F10">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="G10">
-        <v>0.3818277262286871</v>
+        <v>0.3258193430227221</v>
       </c>
       <c r="H10">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1">
-        <v>46153</v>
+        <v>46162</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11">
-        <v>34.64560932909123</v>
+        <v>51.74165648409151</v>
       </c>
       <c r="D11">
-        <v>26.08311546080494</v>
+        <v>24.98091384114761</v>
       </c>
       <c r="E11">
-        <v>0.9983000000000001</v>
+        <v>0.9252</v>
       </c>
       <c r="F11">
-        <v>0.9983000000000001</v>
+        <v>0.9252</v>
       </c>
       <c r="G11">
-        <v>0.06258613715048233</v>
+        <v>0.3818277262286871</v>
       </c>
       <c r="H11">
-        <v>0.9983000000000001</v>
+        <v>0.9252</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1">
-        <v>46154</v>
+        <v>46163</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12">
-        <v>34.50204921141101</v>
+        <v>49.13455894175823</v>
       </c>
       <c r="D12">
-        <v>25.94535229304585</v>
+        <v>25.30005057653127</v>
       </c>
       <c r="E12">
-        <v>0.9984</v>
+        <v>0.9247</v>
       </c>
       <c r="F12">
-        <v>0.9984</v>
+        <v>0.9247</v>
       </c>
       <c r="G12">
-        <v>0.05768943168306073</v>
+        <v>0.4028091571787618</v>
       </c>
       <c r="H12">
-        <v>0.9984</v>
+        <v>0.9247</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
       </c>
       <c r="C13">
-        <v>35.10429483281073</v>
+        <v>34.64560932909123</v>
       </c>
       <c r="D13">
-        <v>26.43864879939599</v>
+        <v>26.08311546080494</v>
       </c>
       <c r="E13">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="F13">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="G13">
-        <v>0.07926550001722021</v>
+        <v>0.06258613715048233</v>
       </c>
       <c r="H13">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="B14" t="s">
         <v>10</v>
       </c>
       <c r="C14">
-        <v>35.36860632820093</v>
+        <v>34.50204921141101</v>
       </c>
       <c r="D14">
-        <v>26.56575571102338</v>
+        <v>25.94535229304585</v>
       </c>
       <c r="E14">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F14">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G14">
-        <v>0.08553946591902095</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H14">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="B15" t="s">
         <v>10</v>
       </c>
       <c r="C15">
-        <v>34.88080083527914</v>
+        <v>35.10429483281073</v>
       </c>
       <c r="D15">
-        <v>26.19322945679072</v>
+        <v>26.43864879939599</v>
       </c>
       <c r="E15">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="F15">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="G15">
-        <v>0.06870693142475881</v>
+        <v>0.07926550001722021</v>
       </c>
       <c r="H15">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1">
-        <v>46160</v>
+        <v>46156</v>
       </c>
       <c r="B16" t="s">
         <v>10</v>
       </c>
       <c r="C16">
-        <v>34.67638692539213</v>
+        <v>35.36860632820093</v>
       </c>
       <c r="D16">
-        <v>26.06707890342319</v>
+        <v>26.56575571102338</v>
       </c>
       <c r="E16">
         <v>0.9985999999999999</v>
@@ -813,7 +813,7 @@
         <v>0.9985999999999999</v>
       </c>
       <c r="G16">
-        <v>0.06289213016552919</v>
+        <v>0.08553946591902095</v>
       </c>
       <c r="H16">
         <v>0.9985999999999999</v>
@@ -821,406 +821,406 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
       </c>
       <c r="C17">
-        <v>34.21212662725402</v>
+        <v>34.88080083527914</v>
       </c>
       <c r="D17">
-        <v>25.60349394367002</v>
+        <v>26.19322945679072</v>
       </c>
       <c r="E17">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="F17">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="G17">
-        <v>0.0486610616591685</v>
+        <v>0.06870693142475881</v>
       </c>
       <c r="H17">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>
       </c>
       <c r="C18">
-        <v>34.78598436564941</v>
+        <v>34.67638692539213</v>
       </c>
       <c r="D18">
-        <v>25.95505316769806</v>
+        <v>26.06707890342319</v>
       </c>
       <c r="E18">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="F18">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="G18">
-        <v>0.06335117806143331</v>
+        <v>0.06289213016552919</v>
       </c>
       <c r="H18">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1">
-        <v>46153</v>
+        <v>46161</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C19">
-        <v>36.55790859258162</v>
+        <v>34.21212662725402</v>
       </c>
       <c r="D19">
-        <v>22.67181120908155</v>
+        <v>25.60349394367002</v>
       </c>
       <c r="E19">
-        <v>0.9990740999999999</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="F19">
-        <v>0.9990740999999999</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="G19">
-        <v>0.1648443271746771</v>
+        <v>0.0486610616591685</v>
       </c>
       <c r="H19">
-        <v>0.9990740999999999</v>
+        <v>0.9984999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1">
-        <v>46154</v>
+        <v>46162</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C20">
-        <v>36.44753722959613</v>
+        <v>34.78598436564941</v>
       </c>
       <c r="D20">
-        <v>22.40292401789388</v>
+        <v>25.95505316769806</v>
       </c>
       <c r="E20">
-        <v>0.9990772499999999</v>
+        <v>0.9983</v>
       </c>
       <c r="F20">
-        <v>0.9990772499999999</v>
+        <v>0.9983</v>
       </c>
       <c r="G20">
-        <v>0.154964342628132</v>
+        <v>0.06335117806143331</v>
       </c>
       <c r="H20">
-        <v>0.9990772499999999</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1">
-        <v>46155</v>
+        <v>46163</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C21">
-        <v>36.63128514035871</v>
+        <v>33.4539909056227</v>
       </c>
       <c r="D21">
-        <v>22.65773388934668</v>
+        <v>25.96014535427112</v>
       </c>
       <c r="E21">
-        <v>0.99907745</v>
+        <v>0.9984</v>
       </c>
       <c r="F21">
-        <v>0.99907745</v>
+        <v>0.9984</v>
       </c>
       <c r="G21">
-        <v>0.1671633421405267</v>
+        <v>0.06350423294229035</v>
       </c>
       <c r="H21">
-        <v>0.99907745</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="B22" t="s">
         <v>11</v>
       </c>
       <c r="C22">
-        <v>36.87865927427314</v>
+        <v>36.55790859258162</v>
       </c>
       <c r="D22">
-        <v>22.69755646854794</v>
+        <v>22.67181120908155</v>
       </c>
       <c r="E22">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="F22">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="G22">
-        <v>0.1754592080224002</v>
+        <v>0.1648443271746771</v>
       </c>
       <c r="H22">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="B23" t="s">
         <v>11</v>
       </c>
       <c r="C23">
-        <v>36.52208783231286</v>
+        <v>36.44753722959613</v>
       </c>
       <c r="D23">
-        <v>22.32462309676992</v>
+        <v>22.40292401789388</v>
       </c>
       <c r="E23">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="F23">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="G23">
-        <v>0.1577242156354994</v>
+        <v>0.154964342628132</v>
       </c>
       <c r="H23">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="B24" t="s">
         <v>11</v>
       </c>
       <c r="C24">
-        <v>36.25604200674668</v>
+        <v>36.63128514035871</v>
       </c>
       <c r="D24">
-        <v>22.16555007468561</v>
+        <v>22.65773388934668</v>
       </c>
       <c r="E24">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="F24">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="G24">
-        <v>0.1527434068648266</v>
+        <v>0.1671633421405267</v>
       </c>
       <c r="H24">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1">
-        <v>46161</v>
+        <v>46156</v>
       </c>
       <c r="B25" t="s">
         <v>11</v>
       </c>
       <c r="C25">
-        <v>36.01040085730018</v>
+        <v>36.87865927427314</v>
       </c>
       <c r="D25">
-        <v>22.19475589056387</v>
+        <v>22.69755646854794</v>
       </c>
       <c r="E25">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="F25">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="G25">
-        <v>0.1456396418594061</v>
+        <v>0.1754592080224002</v>
       </c>
       <c r="H25">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1">
-        <v>46162</v>
+        <v>46157</v>
       </c>
       <c r="B26" t="s">
         <v>11</v>
       </c>
       <c r="C26">
-        <v>36.45290912796982</v>
+        <v>36.52208783231286</v>
       </c>
       <c r="D26">
-        <v>22.46357594746874</v>
+        <v>22.32462309676992</v>
       </c>
       <c r="E26">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="F26">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="G26">
-        <v>0.1646157747240327</v>
+        <v>0.1577242156354994</v>
       </c>
       <c r="H26">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="B27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C27">
-        <v>52.70832779833182</v>
+        <v>36.25604200674668</v>
       </c>
       <c r="D27">
-        <v>23.99044674439659</v>
+        <v>22.16555007468561</v>
       </c>
       <c r="E27">
-        <v>0.9994000000000002</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="F27">
-        <v>0.9994000000000002</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="G27">
-        <v>0.5438253854918791</v>
+        <v>0.1527434068648266</v>
       </c>
       <c r="H27">
-        <v>0.9994000000000002</v>
+        <v>0.9991011900000002</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C28">
-        <v>50.89464485280568</v>
+        <v>36.01040085730018</v>
       </c>
       <c r="D28">
-        <v>23.21558303176282</v>
+        <v>22.19475589056387</v>
       </c>
       <c r="E28">
-        <v>0.9996</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="F28">
-        <v>0.9996</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="G28">
-        <v>0.5034825029548833</v>
+        <v>0.1456396418594061</v>
       </c>
       <c r="H28">
-        <v>0.9996</v>
+        <v>0.9993222199999999</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1">
-        <v>46155</v>
+        <v>46162</v>
       </c>
       <c r="B29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C29">
-        <v>51.8659994471731</v>
+        <v>36.45290912796982</v>
       </c>
       <c r="D29">
-        <v>23.7009037279043</v>
+        <v>22.46357594746874</v>
       </c>
       <c r="E29">
-        <v>1.0002</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="F29">
-        <v>1.0002</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="G29">
-        <v>0.533512029714132</v>
+        <v>0.1646157747240327</v>
       </c>
       <c r="H29">
-        <v>1.0002</v>
+        <v>0.9992557700000001</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1">
-        <v>46156</v>
+        <v>46163</v>
       </c>
       <c r="B30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C30">
-        <v>52.4470179952828</v>
+        <v>35.75282090566891</v>
       </c>
       <c r="D30">
-        <v>23.76861704536814</v>
+        <v>22.57615417310648</v>
       </c>
       <c r="E30">
-        <v>0.9998</v>
+        <v>0.99926856</v>
       </c>
       <c r="F30">
-        <v>0.9998</v>
+        <v>0.99926856</v>
       </c>
       <c r="G30">
-        <v>0.5492634496849078</v>
+        <v>0.1668367104873381</v>
       </c>
       <c r="H30">
-        <v>0.9998</v>
+        <v>0.99926856</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="B31" t="s">
         <v>12</v>
       </c>
       <c r="C31">
-        <v>50.81077380018606</v>
+        <v>52.70832779833182</v>
       </c>
       <c r="D31">
-        <v>22.76900580927995</v>
+        <v>23.99044674439659</v>
       </c>
       <c r="E31">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="F31">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="G31">
-        <v>0.4903296143797722</v>
+        <v>0.5438253854918791</v>
       </c>
       <c r="H31">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1">
-        <v>46160</v>
+        <v>46154</v>
       </c>
       <c r="B32" t="s">
         <v>12</v>
       </c>
       <c r="C32">
-        <v>49.50286387149169</v>
+        <v>50.89464485280568</v>
       </c>
       <c r="D32">
-        <v>22.24532119914133</v>
+        <v>23.21558303176282</v>
       </c>
       <c r="E32">
         <v>0.9996</v>
@@ -1229,7 +1229,7 @@
         <v>0.9996</v>
       </c>
       <c r="G32">
-        <v>0.4630591776162345</v>
+        <v>0.5034825029548833</v>
       </c>
       <c r="H32">
         <v>0.9996</v>
@@ -1237,860 +1237,1094 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1">
-        <v>46161</v>
+        <v>46155</v>
       </c>
       <c r="B33" t="s">
         <v>12</v>
       </c>
       <c r="C33">
-        <v>49.29146729279496</v>
+        <v>51.8659994471731</v>
       </c>
       <c r="D33">
-        <v>22.22167836589682</v>
+        <v>23.7009037279043</v>
       </c>
       <c r="E33">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="F33">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="G33">
-        <v>0.4571659248870246</v>
+        <v>0.533512029714132</v>
       </c>
       <c r="H33">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1">
-        <v>46162</v>
+        <v>46156</v>
       </c>
       <c r="B34" t="s">
         <v>12</v>
       </c>
       <c r="C34">
-        <v>50.88652370817657</v>
+        <v>52.4470179952828</v>
       </c>
       <c r="D34">
-        <v>22.93254398967657</v>
+        <v>23.76861704536814</v>
       </c>
       <c r="E34">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F34">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G34">
-        <v>0.5126171754864624</v>
+        <v>0.5492634496849078</v>
       </c>
       <c r="H34">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="B35" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C35">
-        <v>57.1732166855686</v>
+        <v>50.81077380018606</v>
       </c>
       <c r="D35">
-        <v>23.50022751267814</v>
+        <v>22.76900580927995</v>
       </c>
       <c r="E35">
-        <v>0.9991</v>
+        <v>0.9998</v>
       </c>
       <c r="F35">
-        <v>0.9991</v>
+        <v>0.9998</v>
       </c>
       <c r="G35">
-        <v>0.6994110097039083</v>
+        <v>0.4903296143797722</v>
       </c>
       <c r="H35">
-        <v>0.9991</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C36">
-        <v>54.77380642078597</v>
+        <v>49.50286387149169</v>
       </c>
       <c r="D36">
-        <v>22.55192940254518</v>
+        <v>22.24532119914133</v>
       </c>
       <c r="E36">
-        <v>0.9990000000000001</v>
+        <v>0.9996</v>
       </c>
       <c r="F36">
-        <v>0.9990000000000001</v>
+        <v>0.9996</v>
       </c>
       <c r="G36">
-        <v>0.6459175880844941</v>
+        <v>0.4630591776162345</v>
       </c>
       <c r="H36">
-        <v>0.9990000000000001</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1">
-        <v>46155</v>
+        <v>46161</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C37">
-        <v>56.32187380830906</v>
+        <v>49.29146729279496</v>
       </c>
       <c r="D37">
-        <v>23.17121437414109</v>
+        <v>22.22167836589682</v>
       </c>
       <c r="E37">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
       <c r="F37">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
       <c r="G37">
-        <v>0.6851523922954754</v>
+        <v>0.4571659248870246</v>
       </c>
       <c r="H37">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1">
-        <v>46156</v>
+        <v>46162</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C38">
-        <v>56.15321618553139</v>
+        <v>50.88652370817657</v>
       </c>
       <c r="D38">
-        <v>22.95838347314443</v>
+        <v>22.93254398967657</v>
       </c>
       <c r="E38">
-        <v>0.9992</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F38">
-        <v>0.9992</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G38">
-        <v>0.6907028507208208</v>
+        <v>0.5126171754864624</v>
       </c>
       <c r="H38">
-        <v>0.9992</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1">
-        <v>46157</v>
+        <v>46163</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C39">
-        <v>54.47755813049488</v>
+        <v>48.26646764818586</v>
       </c>
       <c r="D39">
-        <v>22.0083816089626</v>
+        <v>23.11655387625012</v>
       </c>
       <c r="E39">
-        <v>0.9986</v>
+        <v>0.9999</v>
       </c>
       <c r="F39">
-        <v>0.9986</v>
+        <v>0.9999</v>
       </c>
       <c r="G39">
-        <v>0.6220895940829376</v>
+        <v>0.521243030947425</v>
       </c>
       <c r="H39">
-        <v>0.9986</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
       </c>
       <c r="C40">
-        <v>52.6278781150669</v>
+        <v>57.1732166855686</v>
       </c>
       <c r="D40">
-        <v>21.5357353870778</v>
+        <v>23.50022751267814</v>
       </c>
       <c r="E40">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F40">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G40">
-        <v>0.5845134636435627</v>
+        <v>0.6994110097039083</v>
       </c>
       <c r="H40">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
       </c>
       <c r="C41">
-        <v>54.91583234840245</v>
+        <v>54.77380642078597</v>
       </c>
       <c r="D41">
-        <v>22.38321645985006</v>
+        <v>22.55192940254518</v>
       </c>
       <c r="E41">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F41">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G41">
-        <v>0.6596976539194066</v>
+        <v>0.6459175880844941</v>
       </c>
       <c r="H41">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B42" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C42">
-        <v>35.78646526282436</v>
+        <v>56.32187380830906</v>
       </c>
       <c r="D42">
-        <v>18.96635091925032</v>
+        <v>23.17121437414109</v>
       </c>
       <c r="E42">
-        <v>0.9996491399999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F42">
-        <v>0.9996491399999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G42">
-        <v>0.2240600969213613</v>
+        <v>0.6851523922954754</v>
       </c>
       <c r="H42">
-        <v>0.9985614899999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B43" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C43">
-        <v>35.71584102184062</v>
+        <v>56.15321618553139</v>
       </c>
       <c r="D43">
-        <v>18.62432950231353</v>
+        <v>22.95838347314443</v>
       </c>
       <c r="E43">
-        <v>0.99965481</v>
+        <v>0.9992</v>
       </c>
       <c r="F43">
-        <v>0.99965481</v>
+        <v>0.9992</v>
       </c>
       <c r="G43">
-        <v>0.2104844827747143</v>
+        <v>0.6907028507208208</v>
       </c>
       <c r="H43">
-        <v>0.9985622199999999</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B44" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C44">
-        <v>35.95182028203252</v>
+        <v>54.47755813049488</v>
       </c>
       <c r="D44">
-        <v>18.95670796791552</v>
+        <v>22.0083816089626</v>
       </c>
       <c r="E44">
-        <v>0.9996515200000001</v>
+        <v>0.9986</v>
       </c>
       <c r="F44">
-        <v>0.9996515200000001</v>
+        <v>0.9986</v>
       </c>
       <c r="G44">
-        <v>0.2259035693959275</v>
+        <v>0.6220895940829376</v>
       </c>
       <c r="H44">
-        <v>0.99855193</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1">
-        <v>46156</v>
+        <v>46161</v>
       </c>
       <c r="B45" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C45">
-        <v>36.14451597805883</v>
+        <v>52.6278781150669</v>
       </c>
       <c r="D45">
-        <v>18.86297660538653</v>
+        <v>21.5357353870778</v>
       </c>
       <c r="E45">
-        <v>0.9996563399999999</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="F45">
-        <v>0.9996563399999999</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="G45">
-        <v>0.2362110061840785</v>
+        <v>0.5845134636435627</v>
       </c>
       <c r="H45">
-        <v>0.99857265</v>
+        <v>0.9988999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1">
-        <v>46157</v>
+        <v>46162</v>
       </c>
       <c r="B46" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C46">
-        <v>35.32805803135546</v>
+        <v>54.91583234840245</v>
       </c>
       <c r="D46">
-        <v>18.35643242381478</v>
+        <v>22.38321645985006</v>
       </c>
       <c r="E46">
-        <v>0.9997415800000001</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="F46">
-        <v>0.9997415800000001</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="G46">
-        <v>0.2023559161375383</v>
+        <v>0.6596976539194066</v>
       </c>
       <c r="H46">
-        <v>0.9986639900000002</v>
+        <v>0.9990999999999999</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1">
-        <v>46160</v>
+        <v>46163</v>
       </c>
       <c r="B47" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C47">
-        <v>34.83995455757461</v>
+        <v>53.91712298548793</v>
       </c>
       <c r="D47">
-        <v>18.02301281718857</v>
+        <v>22.73711181201267</v>
       </c>
       <c r="E47">
-        <v>0.9996851299999999</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="F47">
-        <v>0.9996851299999999</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="G47">
-        <v>0.1850932291737926</v>
+        <v>0.6737329602396263</v>
       </c>
       <c r="H47">
-        <v>0.99857724</v>
+        <v>0.9991999999999999</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B48" t="s">
         <v>14</v>
       </c>
       <c r="C48">
-        <v>34.45479308705605</v>
+        <v>35.78646526282436</v>
       </c>
       <c r="D48">
-        <v>18.09576834566068</v>
+        <v>18.96635091925032</v>
       </c>
       <c r="E48">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="F48">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="G48">
-        <v>0.1784731209386736</v>
+        <v>0.2240600969213613</v>
       </c>
       <c r="H48">
-        <v>0.9985337599999999</v>
+        <v>0.9985614899999999</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B49" t="s">
         <v>14</v>
       </c>
       <c r="C49">
-        <v>34.96336277390787</v>
+        <v>35.71584102184062</v>
       </c>
       <c r="D49">
-        <v>18.34938420029253</v>
+        <v>18.62432950231353</v>
       </c>
       <c r="E49">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="F49">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="G49">
-        <v>0.2009313391215752</v>
+        <v>0.2104844827747143</v>
       </c>
       <c r="H49">
-        <v>0.99848777</v>
+        <v>0.9985622199999999</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B50" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C50">
-        <v>28.12253390077671</v>
+        <v>35.95182028203252</v>
       </c>
       <c r="D50">
-        <v>23.58699683751922</v>
+        <v>18.95670796791552</v>
       </c>
       <c r="E50">
-        <v>0.9997295369999999</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="F50">
-        <v>0.9997295369999999</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="G50">
-        <v>0.03368732240295347</v>
+        <v>0.2259035693959275</v>
       </c>
       <c r="H50">
-        <v>0.9997295369999999</v>
+        <v>0.99855193</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B51" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C51">
-        <v>28.17715727830483</v>
+        <v>36.14451597805883</v>
       </c>
       <c r="D51">
-        <v>23.63894513078866</v>
+        <v>18.86297660538653</v>
       </c>
       <c r="E51">
-        <v>1.000319473</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="F51">
-        <v>1.000319473</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="G51">
-        <v>0.03515547182056333</v>
+        <v>0.2362110061840785</v>
       </c>
       <c r="H51">
-        <v>1.000319473</v>
+        <v>0.99857265</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B52" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C52">
-        <v>28.59002627414054</v>
+        <v>35.32805803135546</v>
       </c>
       <c r="D52">
-        <v>23.96230704059692</v>
+        <v>18.35643242381478</v>
       </c>
       <c r="E52">
-        <v>0.9999999989999999</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="F52">
-        <v>0.9999999989999999</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="G52">
-        <v>0.05179637495949674</v>
+        <v>0.2023559161375383</v>
       </c>
       <c r="H52">
-        <v>0.9999999989999999</v>
+        <v>0.9986639900000002</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="B53" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C53">
-        <v>28.56217859389523</v>
+        <v>34.83995455757461</v>
       </c>
       <c r="D53">
-        <v>23.9411987302529</v>
+        <v>18.02301281718857</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="G53">
-        <v>0.04837024516756849</v>
+        <v>0.1850932291737926</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>0.99857724</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C54">
-        <v>28.57618675936338</v>
+        <v>34.45479308705605</v>
       </c>
       <c r="D54">
-        <v>23.9576220541054</v>
+        <v>18.09576834566068</v>
       </c>
       <c r="E54">
-        <v>0.999503249</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="F54">
-        <v>0.999503249</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="G54">
-        <v>0.04983868243960732</v>
+        <v>0.1784731209386736</v>
       </c>
       <c r="H54">
-        <v>0.999503249</v>
+        <v>0.9985337599999999</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="B55" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C55">
-        <v>28.68951918518517</v>
+        <v>34.96336277390787</v>
       </c>
       <c r="D55">
-        <v>24.06134728453882</v>
+        <v>18.34938420029253</v>
       </c>
       <c r="E55">
-        <v>0.999503249</v>
+        <v>0.99963413</v>
       </c>
       <c r="F55">
-        <v>0.999503249</v>
+        <v>0.99963413</v>
       </c>
       <c r="G55">
-        <v>0.04983868243960732</v>
+        <v>0.2009313391215752</v>
       </c>
       <c r="H55">
-        <v>0.999503249</v>
+        <v>0.99848777</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="B56" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C56">
-        <v>28.31167386654059</v>
+        <v>34.44616924817128</v>
       </c>
       <c r="D56">
-        <v>23.75157719455474</v>
+        <v>18.60085625074367</v>
       </c>
       <c r="E56">
-        <v>1.000177331</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="F56">
-        <v>1.000177331</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="G56">
-        <v>0.04053938625111919</v>
+        <v>0.2124957180214682</v>
       </c>
       <c r="H56">
-        <v>1.000177331</v>
+        <v>0.9985085200000001</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1">
-        <v>46162</v>
+        <v>46153</v>
       </c>
       <c r="B57" t="s">
         <v>15</v>
       </c>
       <c r="C57">
-        <v>28.57911382310097</v>
+        <v>28.12253390077671</v>
       </c>
       <c r="D57">
-        <v>23.89431741541233</v>
+        <v>23.58699683751922</v>
       </c>
       <c r="E57">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="F57">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="G57">
-        <v>0.04690190590044785</v>
+        <v>0.03368732240295347</v>
       </c>
       <c r="H57">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B58" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C58">
-        <v>40.68830633303975</v>
+        <v>28.17715727830483</v>
       </c>
       <c r="D58">
-        <v>21.50431773660198</v>
+        <v>23.63894513078866</v>
       </c>
       <c r="E58">
-        <v>0.99909852</v>
+        <v>1.000319473</v>
       </c>
       <c r="F58">
-        <v>0.99909852</v>
+        <v>1.000319473</v>
       </c>
       <c r="G58">
-        <v>0.2342423866086769</v>
+        <v>0.03515547182056333</v>
       </c>
       <c r="H58">
-        <v>0.9974930900000001</v>
+        <v>1.000319473</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B59" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C59">
-        <v>40.32854894972581</v>
+        <v>28.59002627414054</v>
       </c>
       <c r="D59">
-        <v>21.09133998298594</v>
+        <v>23.96230704059692</v>
       </c>
       <c r="E59">
-        <v>0.9990972199999999</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F59">
-        <v>0.9990972199999999</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G59">
-        <v>0.2156468205051487</v>
+        <v>0.05179637495949674</v>
       </c>
       <c r="H59">
-        <v>0.99752223</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B60" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C60">
-        <v>40.47987921095815</v>
+        <v>28.56217859389523</v>
       </c>
       <c r="D60">
-        <v>21.35995364434454</v>
+        <v>23.9411987302529</v>
       </c>
       <c r="E60">
-        <v>0.9991780100000001</v>
+        <v>1</v>
       </c>
       <c r="F60">
-        <v>0.9991780100000001</v>
+        <v>1</v>
       </c>
       <c r="G60">
-        <v>0.2270956128473374</v>
+        <v>0.04837024516756849</v>
       </c>
       <c r="H60">
-        <v>0.9975825700000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B61" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C61">
-        <v>41.20436574895244</v>
+        <v>28.57618675936338</v>
       </c>
       <c r="D61">
-        <v>21.48149674387778</v>
+        <v>23.9576220541054</v>
       </c>
       <c r="E61">
-        <v>0.9991793299999999</v>
+        <v>0.999503249</v>
       </c>
       <c r="F61">
-        <v>0.9991793299999999</v>
+        <v>0.999503249</v>
       </c>
       <c r="G61">
-        <v>0.2454829228401052</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H61">
-        <v>0.99754722</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B62" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C62">
-        <v>40.80613062958688</v>
+        <v>28.68951918518517</v>
       </c>
       <c r="D62">
-        <v>21.08912555803936</v>
+        <v>24.06134728453882</v>
       </c>
       <c r="E62">
-        <v>0.9991790600000001</v>
+        <v>0.999503249</v>
       </c>
       <c r="F62">
-        <v>0.9991790600000001</v>
+        <v>0.999503249</v>
       </c>
       <c r="G62">
-        <v>0.2230017445022556</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H62">
-        <v>0.9975824700000002</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B63" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C63">
-        <v>40.11672876026724</v>
+        <v>28.31167386654059</v>
       </c>
       <c r="D63">
-        <v>20.79541439916316</v>
+        <v>23.75157719455474</v>
       </c>
       <c r="E63">
-        <v>0.999152</v>
+        <v>1.000177331</v>
       </c>
       <c r="F63">
-        <v>0.999152</v>
+        <v>1.000177331</v>
       </c>
       <c r="G63">
-        <v>0.2098184021536666</v>
+        <v>0.04053938625111919</v>
       </c>
       <c r="H63">
-        <v>0.9975007899999999</v>
+        <v>1.000177331</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B64" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C64">
-        <v>39.69086941528401</v>
+        <v>28.57911382310097</v>
       </c>
       <c r="D64">
-        <v>20.74924328599426</v>
+        <v>23.89431741541233</v>
       </c>
       <c r="E64">
-        <v>0.99914989</v>
+        <v>0.999503734</v>
       </c>
       <c r="F64">
-        <v>0.99914989</v>
+        <v>0.999503734</v>
       </c>
       <c r="G64">
-        <v>0.2020471776850241</v>
+        <v>0.04690190590044785</v>
       </c>
       <c r="H64">
-        <v>0.9974417</v>
+        <v>0.999503734</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B65" t="s">
+        <v>15</v>
+      </c>
+      <c r="C65">
+        <v>28.55785065378643</v>
+      </c>
+      <c r="D65">
+        <v>24.04274714970193</v>
+      </c>
+      <c r="E65">
+        <v>1.000229282</v>
+      </c>
+      <c r="F65">
+        <v>1.000229282</v>
+      </c>
+      <c r="G65">
+        <v>0.05228572319419666</v>
+      </c>
+      <c r="H65">
+        <v>1.000229282</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66">
+        <v>40.68830633303975</v>
+      </c>
+      <c r="D66">
+        <v>21.50431773660198</v>
+      </c>
+      <c r="E66">
+        <v>0.99909852</v>
+      </c>
+      <c r="F66">
+        <v>0.99909852</v>
+      </c>
+      <c r="G66">
+        <v>0.2342423866086769</v>
+      </c>
+      <c r="H66">
+        <v>0.9974930900000001</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67">
+        <v>40.32854894972581</v>
+      </c>
+      <c r="D67">
+        <v>21.09133998298594</v>
+      </c>
+      <c r="E67">
+        <v>0.9990972199999999</v>
+      </c>
+      <c r="F67">
+        <v>0.9990972199999999</v>
+      </c>
+      <c r="G67">
+        <v>0.2156468205051487</v>
+      </c>
+      <c r="H67">
+        <v>0.99752223</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68">
+        <v>40.47987921095815</v>
+      </c>
+      <c r="D68">
+        <v>21.35995364434454</v>
+      </c>
+      <c r="E68">
+        <v>0.9991780100000001</v>
+      </c>
+      <c r="F68">
+        <v>0.9991780100000001</v>
+      </c>
+      <c r="G68">
+        <v>0.2270956128473374</v>
+      </c>
+      <c r="H68">
+        <v>0.9975825700000001</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69">
+        <v>41.20436574895244</v>
+      </c>
+      <c r="D69">
+        <v>21.48149674387778</v>
+      </c>
+      <c r="E69">
+        <v>0.9991793299999999</v>
+      </c>
+      <c r="F69">
+        <v>0.9991793299999999</v>
+      </c>
+      <c r="G69">
+        <v>0.2454829228401052</v>
+      </c>
+      <c r="H69">
+        <v>0.99754722</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70">
+        <v>40.80613062958688</v>
+      </c>
+      <c r="D70">
+        <v>21.08912555803936</v>
+      </c>
+      <c r="E70">
+        <v>0.9991790600000001</v>
+      </c>
+      <c r="F70">
+        <v>0.9991790600000001</v>
+      </c>
+      <c r="G70">
+        <v>0.2230017445022556</v>
+      </c>
+      <c r="H70">
+        <v>0.9975824700000002</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71">
+        <v>40.11672876026724</v>
+      </c>
+      <c r="D71">
+        <v>20.79541439916316</v>
+      </c>
+      <c r="E71">
+        <v>0.999152</v>
+      </c>
+      <c r="F71">
+        <v>0.999152</v>
+      </c>
+      <c r="G71">
+        <v>0.2098184021536666</v>
+      </c>
+      <c r="H71">
+        <v>0.9975007899999999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72">
+        <v>39.69086941528401</v>
+      </c>
+      <c r="D72">
+        <v>20.74924328599426</v>
+      </c>
+      <c r="E72">
+        <v>0.99914989</v>
+      </c>
+      <c r="F72">
+        <v>0.99914989</v>
+      </c>
+      <c r="G72">
+        <v>0.2020471776850241</v>
+      </c>
+      <c r="H72">
+        <v>0.9974417</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="1">
         <v>46162</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B73" t="s">
         <v>16</v>
       </c>
-      <c r="C65">
+      <c r="C73">
         <v>40.37836787855562</v>
       </c>
-      <c r="D65">
+      <c r="D73">
         <v>21.11271132314188</v>
       </c>
-      <c r="E65">
+      <c r="E73">
         <v>0.99915058</v>
       </c>
-      <c r="F65">
+      <c r="F73">
         <v>0.99915058</v>
       </c>
-      <c r="G65">
+      <c r="G73">
         <v>0.2291077670847563</v>
       </c>
-      <c r="H65">
+      <c r="H73">
         <v>0.9974415600000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74">
+        <v>38.9123066967842</v>
+      </c>
+      <c r="D74">
+        <v>21.28910644207464</v>
+      </c>
+      <c r="E74">
+        <v>0.9989350699999999</v>
+      </c>
+      <c r="F74">
+        <v>0.9989350699999999</v>
+      </c>
+      <c r="G74">
+        <v>0.2392382040170877</v>
+      </c>
+      <c r="H74">
+        <v>0.99726191</v>
       </c>
     </row>
   </sheetData>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="17">
   <si>
     <t>Date</t>
   </si>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -483,42 +483,42 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1">
-        <v>46153</v>
+        <v>46164</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>53.14833755912058</v>
+        <v>23.47456054103265</v>
       </c>
       <c r="D4">
-        <v>25.84885448407537</v>
+        <v>16.04707182251085</v>
       </c>
       <c r="E4">
-        <v>0.9262</v>
+        <v>0.8545999999999999</v>
       </c>
       <c r="F4">
-        <v>0.9262</v>
+        <v>0.8545999999999999</v>
       </c>
       <c r="G4">
-        <v>0.3839084462043663</v>
+        <v>0.4876634748449802</v>
       </c>
       <c r="H4">
-        <v>0.9262</v>
+        <v>0.9083</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
       <c r="C5">
-        <v>51.82921169635205</v>
+        <v>53.14833755912058</v>
       </c>
       <c r="D5">
-        <v>25.32805827181975</v>
+        <v>25.84885448407537</v>
       </c>
       <c r="E5">
         <v>0.9262</v>
@@ -527,7 +527,7 @@
         <v>0.9262</v>
       </c>
       <c r="G5">
-        <v>0.3568580281685669</v>
+        <v>0.3839084462043663</v>
       </c>
       <c r="H5">
         <v>0.9262</v>
@@ -535,120 +535,120 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
       </c>
       <c r="C6">
-        <v>52.28471716753184</v>
+        <v>51.82921169635205</v>
       </c>
       <c r="D6">
-        <v>25.54525144150689</v>
+        <v>25.32805827181975</v>
       </c>
       <c r="E6">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="F6">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="G6">
-        <v>0.378012896547947</v>
+        <v>0.3568580281685669</v>
       </c>
       <c r="H6">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
       </c>
       <c r="C7">
-        <v>53.87287273813902</v>
+        <v>52.28471716753184</v>
       </c>
       <c r="D7">
-        <v>26.32154226438612</v>
+        <v>25.54525144150689</v>
       </c>
       <c r="E7">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="F7">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="G7">
-        <v>0.4166811087612758</v>
+        <v>0.378012896547947</v>
       </c>
       <c r="H7">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
       </c>
       <c r="C8">
-        <v>52.18747148214074</v>
+        <v>53.87287273813902</v>
       </c>
       <c r="D8">
-        <v>25.13616059644496</v>
+        <v>26.32154226438612</v>
       </c>
       <c r="E8">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="F8">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="G8">
-        <v>0.3627535778249862</v>
+        <v>0.4166811087612758</v>
       </c>
       <c r="H8">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
       </c>
       <c r="C9">
-        <v>50.72035274995172</v>
+        <v>52.18747148214074</v>
       </c>
       <c r="D9">
-        <v>24.61756040386634</v>
+        <v>25.13616059644496</v>
       </c>
       <c r="E9">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="F9">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="G9">
         <v>0.3627535778249862</v>
       </c>
       <c r="H9">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
       </c>
       <c r="C10">
-        <v>50.11981086673613</v>
+        <v>50.72035274995172</v>
       </c>
       <c r="D10">
-        <v>24.13061679021705</v>
+        <v>24.61756040386634</v>
       </c>
       <c r="E10">
         <v>0.9259000000000001</v>
@@ -657,7 +657,7 @@
         <v>0.9259000000000001</v>
       </c>
       <c r="G10">
-        <v>0.3258193430227221</v>
+        <v>0.3627535778249862</v>
       </c>
       <c r="H10">
         <v>0.9259000000000001</v>
@@ -665,198 +665,198 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
       </c>
       <c r="C11">
-        <v>51.74165648409151</v>
+        <v>50.11981086673613</v>
       </c>
       <c r="D11">
-        <v>24.98091384114761</v>
+        <v>24.13061679021705</v>
       </c>
       <c r="E11">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="F11">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="G11">
-        <v>0.3818277262286871</v>
+        <v>0.3258193430227221</v>
       </c>
       <c r="H11">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
       </c>
       <c r="C12">
-        <v>49.13455894175823</v>
+        <v>51.74165648409151</v>
       </c>
       <c r="D12">
-        <v>25.30005057653127</v>
+        <v>24.98091384114761</v>
       </c>
       <c r="E12">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="F12">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="G12">
-        <v>0.4028091571787618</v>
+        <v>0.3818277262286871</v>
       </c>
       <c r="H12">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1">
-        <v>46153</v>
+        <v>46163</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13">
-        <v>34.64560932909123</v>
+        <v>49.13455894175823</v>
       </c>
       <c r="D13">
-        <v>26.08311546080494</v>
+        <v>25.30005057653127</v>
       </c>
       <c r="E13">
-        <v>0.9983000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="F13">
-        <v>0.9983000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="G13">
-        <v>0.06258613715048233</v>
+        <v>0.4028091571787618</v>
       </c>
       <c r="H13">
-        <v>0.9983000000000001</v>
+        <v>0.9247</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1">
-        <v>46154</v>
+        <v>46164</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14">
-        <v>34.50204921141101</v>
+        <v>49.57776597479297</v>
       </c>
       <c r="D14">
-        <v>25.94535229304585</v>
+        <v>25.04906725563518</v>
       </c>
       <c r="E14">
-        <v>0.9984</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="F14">
-        <v>0.9984</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="G14">
-        <v>0.05768943168306073</v>
+        <v>0.4256980029692063</v>
       </c>
       <c r="H14">
-        <v>0.9984</v>
+        <v>0.9245000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="B15" t="s">
         <v>10</v>
       </c>
       <c r="C15">
-        <v>35.10429483281073</v>
+        <v>34.64560932909123</v>
       </c>
       <c r="D15">
-        <v>26.43864879939599</v>
+        <v>26.08311546080494</v>
       </c>
       <c r="E15">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="F15">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="G15">
-        <v>0.07926550001722021</v>
+        <v>0.06258613715048233</v>
       </c>
       <c r="H15">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="B16" t="s">
         <v>10</v>
       </c>
       <c r="C16">
-        <v>35.36860632820093</v>
+        <v>34.50204921141101</v>
       </c>
       <c r="D16">
-        <v>26.56575571102338</v>
+        <v>25.94535229304585</v>
       </c>
       <c r="E16">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F16">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G16">
-        <v>0.08553946591902095</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H16">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
       </c>
       <c r="C17">
-        <v>34.88080083527914</v>
+        <v>35.10429483281073</v>
       </c>
       <c r="D17">
-        <v>26.19322945679072</v>
+        <v>26.43864879939599</v>
       </c>
       <c r="E17">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="F17">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="G17">
-        <v>0.06870693142475881</v>
+        <v>0.07926550001722021</v>
       </c>
       <c r="H17">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1">
-        <v>46160</v>
+        <v>46156</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>
       </c>
       <c r="C18">
-        <v>34.67638692539213</v>
+        <v>35.36860632820093</v>
       </c>
       <c r="D18">
-        <v>26.06707890342319</v>
+        <v>26.56575571102338</v>
       </c>
       <c r="E18">
         <v>0.9985999999999999</v>
@@ -865,7 +865,7 @@
         <v>0.9985999999999999</v>
       </c>
       <c r="G18">
-        <v>0.06289213016552919</v>
+        <v>0.08553946591902095</v>
       </c>
       <c r="H18">
         <v>0.9985999999999999</v>
@@ -873,458 +873,458 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="B19" t="s">
         <v>10</v>
       </c>
       <c r="C19">
-        <v>34.21212662725402</v>
+        <v>34.88080083527914</v>
       </c>
       <c r="D19">
-        <v>25.60349394367002</v>
+        <v>26.19322945679072</v>
       </c>
       <c r="E19">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="F19">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="G19">
-        <v>0.0486610616591685</v>
+        <v>0.06870693142475881</v>
       </c>
       <c r="H19">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="B20" t="s">
         <v>10</v>
       </c>
       <c r="C20">
-        <v>34.78598436564941</v>
+        <v>34.67638692539213</v>
       </c>
       <c r="D20">
-        <v>25.95505316769806</v>
+        <v>26.06707890342319</v>
       </c>
       <c r="E20">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="F20">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="G20">
-        <v>0.06335117806143331</v>
+        <v>0.06289213016552919</v>
       </c>
       <c r="H20">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1">
-        <v>46163</v>
+        <v>46161</v>
       </c>
       <c r="B21" t="s">
         <v>10</v>
       </c>
       <c r="C21">
-        <v>33.4539909056227</v>
+        <v>34.21212662725402</v>
       </c>
       <c r="D21">
-        <v>25.96014535427112</v>
+        <v>25.60349394367002</v>
       </c>
       <c r="E21">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="F21">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="G21">
-        <v>0.06350423294229035</v>
+        <v>0.0486610616591685</v>
       </c>
       <c r="H21">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1">
-        <v>46153</v>
+        <v>46162</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C22">
-        <v>36.55790859258162</v>
+        <v>34.78598436564941</v>
       </c>
       <c r="D22">
-        <v>22.67181120908155</v>
+        <v>25.95505316769806</v>
       </c>
       <c r="E22">
-        <v>0.9990740999999999</v>
+        <v>0.9983</v>
       </c>
       <c r="F22">
-        <v>0.9990740999999999</v>
+        <v>0.9983</v>
       </c>
       <c r="G22">
-        <v>0.1648443271746771</v>
+        <v>0.06335117806143331</v>
       </c>
       <c r="H22">
-        <v>0.9990740999999999</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1">
-        <v>46154</v>
+        <v>46163</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C23">
-        <v>36.44753722959613</v>
+        <v>33.4539909056227</v>
       </c>
       <c r="D23">
-        <v>22.40292401789388</v>
+        <v>25.96014535427112</v>
       </c>
       <c r="E23">
-        <v>0.9990772499999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F23">
-        <v>0.9990772499999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G23">
-        <v>0.154964342628132</v>
+        <v>0.06350423294229035</v>
       </c>
       <c r="H23">
-        <v>0.9990772499999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1">
-        <v>46155</v>
+        <v>46164</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C24">
-        <v>36.63128514035871</v>
+        <v>33.24951933563993</v>
       </c>
       <c r="D24">
-        <v>22.65773388934668</v>
+        <v>25.46629530314992</v>
       </c>
       <c r="E24">
-        <v>0.99907745</v>
+        <v>0.9984</v>
       </c>
       <c r="F24">
-        <v>0.99907745</v>
+        <v>0.9984</v>
       </c>
       <c r="G24">
-        <v>0.1671633421405267</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H24">
-        <v>0.99907745</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="B25" t="s">
         <v>11</v>
       </c>
       <c r="C25">
-        <v>36.87865927427314</v>
+        <v>36.55790859258162</v>
       </c>
       <c r="D25">
-        <v>22.69755646854794</v>
+        <v>22.67181120908155</v>
       </c>
       <c r="E25">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="F25">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="G25">
-        <v>0.1754592080224002</v>
+        <v>0.1648443271746771</v>
       </c>
       <c r="H25">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="B26" t="s">
         <v>11</v>
       </c>
       <c r="C26">
-        <v>36.52208783231286</v>
+        <v>36.44753722959613</v>
       </c>
       <c r="D26">
-        <v>22.32462309676992</v>
+        <v>22.40292401789388</v>
       </c>
       <c r="E26">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="F26">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="G26">
-        <v>0.1577242156354994</v>
+        <v>0.154964342628132</v>
       </c>
       <c r="H26">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="B27" t="s">
         <v>11</v>
       </c>
       <c r="C27">
-        <v>36.25604200674668</v>
+        <v>36.63128514035871</v>
       </c>
       <c r="D27">
-        <v>22.16555007468561</v>
+        <v>22.65773388934668</v>
       </c>
       <c r="E27">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="F27">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="G27">
-        <v>0.1527434068648266</v>
+        <v>0.1671633421405267</v>
       </c>
       <c r="H27">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1">
-        <v>46161</v>
+        <v>46156</v>
       </c>
       <c r="B28" t="s">
         <v>11</v>
       </c>
       <c r="C28">
-        <v>36.01040085730018</v>
+        <v>36.87865927427314</v>
       </c>
       <c r="D28">
-        <v>22.19475589056387</v>
+        <v>22.69755646854794</v>
       </c>
       <c r="E28">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="F28">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="G28">
-        <v>0.1456396418594061</v>
+        <v>0.1754592080224002</v>
       </c>
       <c r="H28">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1">
-        <v>46162</v>
+        <v>46157</v>
       </c>
       <c r="B29" t="s">
         <v>11</v>
       </c>
       <c r="C29">
-        <v>36.45290912796982</v>
+        <v>36.52208783231286</v>
       </c>
       <c r="D29">
-        <v>22.46357594746874</v>
+        <v>22.32462309676992</v>
       </c>
       <c r="E29">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="F29">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="G29">
-        <v>0.1646157747240327</v>
+        <v>0.1577242156354994</v>
       </c>
       <c r="H29">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1">
-        <v>46163</v>
+        <v>46160</v>
       </c>
       <c r="B30" t="s">
         <v>11</v>
       </c>
       <c r="C30">
-        <v>35.75282090566891</v>
+        <v>36.25604200674668</v>
       </c>
       <c r="D30">
-        <v>22.57615417310648</v>
+        <v>22.16555007468561</v>
       </c>
       <c r="E30">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="F30">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="G30">
-        <v>0.1668367104873381</v>
+        <v>0.1527434068648266</v>
       </c>
       <c r="H30">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1">
-        <v>46153</v>
+        <v>46161</v>
       </c>
       <c r="B31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C31">
-        <v>52.70832779833182</v>
+        <v>36.01040085730018</v>
       </c>
       <c r="D31">
-        <v>23.99044674439659</v>
+        <v>22.19475589056387</v>
       </c>
       <c r="E31">
-        <v>0.9994000000000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="F31">
-        <v>0.9994000000000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="G31">
-        <v>0.5438253854918791</v>
+        <v>0.1456396418594061</v>
       </c>
       <c r="H31">
-        <v>0.9994000000000002</v>
+        <v>0.9993222199999999</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1">
-        <v>46154</v>
+        <v>46162</v>
       </c>
       <c r="B32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C32">
-        <v>50.89464485280568</v>
+        <v>36.45290912796982</v>
       </c>
       <c r="D32">
-        <v>23.21558303176282</v>
+        <v>22.46357594746874</v>
       </c>
       <c r="E32">
-        <v>0.9996</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="F32">
-        <v>0.9996</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="G32">
-        <v>0.5034825029548833</v>
+        <v>0.1646157747240327</v>
       </c>
       <c r="H32">
-        <v>0.9996</v>
+        <v>0.9992557700000001</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1">
-        <v>46155</v>
+        <v>46163</v>
       </c>
       <c r="B33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C33">
-        <v>51.8659994471731</v>
+        <v>35.75282090566891</v>
       </c>
       <c r="D33">
-        <v>23.7009037279043</v>
+        <v>22.57615417310648</v>
       </c>
       <c r="E33">
-        <v>1.0002</v>
+        <v>0.99926856</v>
       </c>
       <c r="F33">
-        <v>1.0002</v>
+        <v>0.99926856</v>
       </c>
       <c r="G33">
-        <v>0.533512029714132</v>
+        <v>0.1668367104873381</v>
       </c>
       <c r="H33">
-        <v>1.0002</v>
+        <v>0.99926856</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1">
-        <v>46156</v>
+        <v>46164</v>
       </c>
       <c r="B34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C34">
-        <v>52.4470179952828</v>
+        <v>35.75514940724808</v>
       </c>
       <c r="D34">
-        <v>23.76861704536814</v>
+        <v>22.28880693466429</v>
       </c>
       <c r="E34">
-        <v>0.9998</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="F34">
-        <v>0.9998</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="G34">
-        <v>0.5492634496849078</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H34">
-        <v>0.9998</v>
+        <v>0.9992573500000002</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="B35" t="s">
         <v>12</v>
       </c>
       <c r="C35">
-        <v>50.81077380018606</v>
+        <v>52.70832779833182</v>
       </c>
       <c r="D35">
-        <v>22.76900580927995</v>
+        <v>23.99044674439659</v>
       </c>
       <c r="E35">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="F35">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="G35">
-        <v>0.4903296143797722</v>
+        <v>0.5438253854918791</v>
       </c>
       <c r="H35">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1">
-        <v>46160</v>
+        <v>46154</v>
       </c>
       <c r="B36" t="s">
         <v>12</v>
       </c>
       <c r="C36">
-        <v>49.50286387149169</v>
+        <v>50.89464485280568</v>
       </c>
       <c r="D36">
-        <v>22.24532119914133</v>
+        <v>23.21558303176282</v>
       </c>
       <c r="E36">
         <v>0.9996</v>
@@ -1333,7 +1333,7 @@
         <v>0.9996</v>
       </c>
       <c r="G36">
-        <v>0.4630591776162345</v>
+        <v>0.5034825029548833</v>
       </c>
       <c r="H36">
         <v>0.9996</v>
@@ -1341,990 +1341,1224 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1">
-        <v>46161</v>
+        <v>46155</v>
       </c>
       <c r="B37" t="s">
         <v>12</v>
       </c>
       <c r="C37">
-        <v>49.29146729279496</v>
+        <v>51.8659994471731</v>
       </c>
       <c r="D37">
-        <v>22.22167836589682</v>
+        <v>23.7009037279043</v>
       </c>
       <c r="E37">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="F37">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="G37">
-        <v>0.4571659248870246</v>
+        <v>0.533512029714132</v>
       </c>
       <c r="H37">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1">
-        <v>46162</v>
+        <v>46156</v>
       </c>
       <c r="B38" t="s">
         <v>12</v>
       </c>
       <c r="C38">
-        <v>50.88652370817657</v>
+        <v>52.4470179952828</v>
       </c>
       <c r="D38">
-        <v>22.93254398967657</v>
+        <v>23.76861704536814</v>
       </c>
       <c r="E38">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F38">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G38">
-        <v>0.5126171754864624</v>
+        <v>0.5492634496849078</v>
       </c>
       <c r="H38">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1">
-        <v>46163</v>
+        <v>46157</v>
       </c>
       <c r="B39" t="s">
         <v>12</v>
       </c>
       <c r="C39">
-        <v>48.26646764818586</v>
+        <v>50.81077380018606</v>
       </c>
       <c r="D39">
-        <v>23.11655387625012</v>
+        <v>22.76900580927995</v>
       </c>
       <c r="E39">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="F39">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="G39">
-        <v>0.521243030947425</v>
+        <v>0.4903296143797722</v>
       </c>
       <c r="H39">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="B40" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C40">
-        <v>57.1732166855686</v>
+        <v>49.50286387149169</v>
       </c>
       <c r="D40">
-        <v>23.50022751267814</v>
+        <v>22.24532119914133</v>
       </c>
       <c r="E40">
-        <v>0.9991</v>
+        <v>0.9996</v>
       </c>
       <c r="F40">
-        <v>0.9991</v>
+        <v>0.9996</v>
       </c>
       <c r="G40">
-        <v>0.6994110097039083</v>
+        <v>0.4630591776162345</v>
       </c>
       <c r="H40">
-        <v>0.9991</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="B41" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C41">
-        <v>54.77380642078597</v>
+        <v>49.29146729279496</v>
       </c>
       <c r="D41">
-        <v>22.55192940254518</v>
+        <v>22.22167836589682</v>
       </c>
       <c r="E41">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
       <c r="F41">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
       <c r="G41">
-        <v>0.6459175880844941</v>
+        <v>0.4571659248870246</v>
       </c>
       <c r="H41">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1">
-        <v>46155</v>
+        <v>46162</v>
       </c>
       <c r="B42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C42">
-        <v>56.32187380830906</v>
+        <v>50.88652370817657</v>
       </c>
       <c r="D42">
-        <v>23.17121437414109</v>
+        <v>22.93254398967657</v>
       </c>
       <c r="E42">
-        <v>0.9990000000000001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F42">
-        <v>0.9990000000000001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G42">
-        <v>0.6851523922954754</v>
+        <v>0.5126171754864624</v>
       </c>
       <c r="H42">
-        <v>0.9990000000000001</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1">
-        <v>46156</v>
+        <v>46163</v>
       </c>
       <c r="B43" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C43">
-        <v>56.15321618553139</v>
+        <v>48.26646764818586</v>
       </c>
       <c r="D43">
-        <v>22.95838347314443</v>
+        <v>23.11655387625012</v>
       </c>
       <c r="E43">
-        <v>0.9992</v>
+        <v>0.9999</v>
       </c>
       <c r="F43">
-        <v>0.9992</v>
+        <v>0.9999</v>
       </c>
       <c r="G43">
-        <v>0.6907028507208208</v>
+        <v>0.521243030947425</v>
       </c>
       <c r="H43">
-        <v>0.9992</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1">
-        <v>46157</v>
+        <v>46164</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C44">
-        <v>54.47755813049488</v>
+        <v>48.84737503703267</v>
       </c>
       <c r="D44">
-        <v>22.0083816089626</v>
+        <v>22.83557604744466</v>
       </c>
       <c r="E44">
-        <v>0.9986</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F44">
-        <v>0.9986</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G44">
-        <v>0.6220895940829376</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H44">
-        <v>0.9986</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
       </c>
       <c r="C45">
-        <v>52.6278781150669</v>
+        <v>57.1732166855686</v>
       </c>
       <c r="D45">
-        <v>21.5357353870778</v>
+        <v>23.50022751267814</v>
       </c>
       <c r="E45">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F45">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G45">
-        <v>0.5845134636435627</v>
+        <v>0.6994110097039083</v>
       </c>
       <c r="H45">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
       </c>
       <c r="C46">
-        <v>54.91583234840245</v>
+        <v>54.77380642078597</v>
       </c>
       <c r="D46">
-        <v>22.38321645985006</v>
+        <v>22.55192940254518</v>
       </c>
       <c r="E46">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F46">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G46">
-        <v>0.6596976539194066</v>
+        <v>0.6459175880844941</v>
       </c>
       <c r="H46">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
       </c>
       <c r="C47">
-        <v>53.91712298548793</v>
+        <v>56.32187380830906</v>
       </c>
       <c r="D47">
-        <v>22.73711181201267</v>
+        <v>23.17121437414109</v>
       </c>
       <c r="E47">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F47">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G47">
-        <v>0.6737329602396263</v>
+        <v>0.6851523922954754</v>
       </c>
       <c r="H47">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="B48" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C48">
-        <v>35.78646526282436</v>
+        <v>56.15321618553139</v>
       </c>
       <c r="D48">
-        <v>18.96635091925032</v>
+        <v>22.95838347314443</v>
       </c>
       <c r="E48">
-        <v>0.9996491399999999</v>
+        <v>0.9992</v>
       </c>
       <c r="F48">
-        <v>0.9996491399999999</v>
+        <v>0.9992</v>
       </c>
       <c r="G48">
-        <v>0.2240600969213613</v>
+        <v>0.6907028507208208</v>
       </c>
       <c r="H48">
-        <v>0.9985614899999999</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="B49" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C49">
-        <v>35.71584102184062</v>
+        <v>54.47755813049488</v>
       </c>
       <c r="D49">
-        <v>18.62432950231353</v>
+        <v>22.0083816089626</v>
       </c>
       <c r="E49">
-        <v>0.99965481</v>
+        <v>0.9986</v>
       </c>
       <c r="F49">
-        <v>0.99965481</v>
+        <v>0.9986</v>
       </c>
       <c r="G49">
-        <v>0.2104844827747143</v>
+        <v>0.6220895940829376</v>
       </c>
       <c r="H49">
-        <v>0.9985622199999999</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1">
-        <v>46155</v>
+        <v>46161</v>
       </c>
       <c r="B50" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C50">
-        <v>35.95182028203252</v>
+        <v>52.6278781150669</v>
       </c>
       <c r="D50">
-        <v>18.95670796791552</v>
+        <v>21.5357353870778</v>
       </c>
       <c r="E50">
-        <v>0.9996515200000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="F50">
-        <v>0.9996515200000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="G50">
-        <v>0.2259035693959275</v>
+        <v>0.5845134636435627</v>
       </c>
       <c r="H50">
-        <v>0.99855193</v>
+        <v>0.9988999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1">
-        <v>46156</v>
+        <v>46162</v>
       </c>
       <c r="B51" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C51">
-        <v>36.14451597805883</v>
+        <v>54.91583234840245</v>
       </c>
       <c r="D51">
-        <v>18.86297660538653</v>
+        <v>22.38321645985006</v>
       </c>
       <c r="E51">
-        <v>0.9996563399999999</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="F51">
-        <v>0.9996563399999999</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="G51">
-        <v>0.2362110061840785</v>
+        <v>0.6596976539194066</v>
       </c>
       <c r="H51">
-        <v>0.99857265</v>
+        <v>0.9990999999999999</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1">
-        <v>46157</v>
+        <v>46163</v>
       </c>
       <c r="B52" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C52">
-        <v>35.32805803135546</v>
+        <v>53.91712298548793</v>
       </c>
       <c r="D52">
-        <v>18.35643242381478</v>
+        <v>22.73711181201267</v>
       </c>
       <c r="E52">
-        <v>0.9997415800000001</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="F52">
-        <v>0.9997415800000001</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="G52">
-        <v>0.2023559161375383</v>
+        <v>0.6737329602396263</v>
       </c>
       <c r="H52">
-        <v>0.9986639900000002</v>
+        <v>0.9991999999999999</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1">
-        <v>46160</v>
+        <v>46164</v>
       </c>
       <c r="B53" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C53">
-        <v>34.83995455757461</v>
+        <v>55.19651747515625</v>
       </c>
       <c r="D53">
-        <v>18.02301281718857</v>
+        <v>22.79462037330554</v>
       </c>
       <c r="E53">
-        <v>0.9996851299999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F53">
-        <v>0.9996851299999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G53">
-        <v>0.1850932291737926</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H53">
-        <v>0.99857724</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B54" t="s">
         <v>14</v>
       </c>
       <c r="C54">
-        <v>34.45479308705605</v>
+        <v>35.78646526282436</v>
       </c>
       <c r="D54">
-        <v>18.09576834566068</v>
+        <v>18.96635091925032</v>
       </c>
       <c r="E54">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="F54">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="G54">
-        <v>0.1784731209386736</v>
+        <v>0.2240600969213613</v>
       </c>
       <c r="H54">
-        <v>0.9985337599999999</v>
+        <v>0.9985614899999999</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B55" t="s">
         <v>14</v>
       </c>
       <c r="C55">
-        <v>34.96336277390787</v>
+        <v>35.71584102184062</v>
       </c>
       <c r="D55">
-        <v>18.34938420029253</v>
+        <v>18.62432950231353</v>
       </c>
       <c r="E55">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="F55">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="G55">
-        <v>0.2009313391215752</v>
+        <v>0.2104844827747143</v>
       </c>
       <c r="H55">
-        <v>0.99848777</v>
+        <v>0.9985622199999999</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B56" t="s">
         <v>14</v>
       </c>
       <c r="C56">
-        <v>34.44616924817128</v>
+        <v>35.95182028203252</v>
       </c>
       <c r="D56">
-        <v>18.60085625074367</v>
+        <v>18.95670796791552</v>
       </c>
       <c r="E56">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="F56">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="G56">
-        <v>0.2124957180214682</v>
+        <v>0.2259035693959275</v>
       </c>
       <c r="H56">
-        <v>0.9985085200000001</v>
+        <v>0.99855193</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="B57" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C57">
-        <v>28.12253390077671</v>
+        <v>36.14451597805883</v>
       </c>
       <c r="D57">
-        <v>23.58699683751922</v>
+        <v>18.86297660538653</v>
       </c>
       <c r="E57">
-        <v>0.9997295369999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="F57">
-        <v>0.9997295369999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="G57">
-        <v>0.03368732240295347</v>
+        <v>0.2362110061840785</v>
       </c>
       <c r="H57">
-        <v>0.9997295369999999</v>
+        <v>0.99857265</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="B58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C58">
-        <v>28.17715727830483</v>
+        <v>35.32805803135546</v>
       </c>
       <c r="D58">
-        <v>23.63894513078866</v>
+        <v>18.35643242381478</v>
       </c>
       <c r="E58">
-        <v>1.000319473</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="F58">
-        <v>1.000319473</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="G58">
-        <v>0.03515547182056333</v>
+        <v>0.2023559161375383</v>
       </c>
       <c r="H58">
-        <v>1.000319473</v>
+        <v>0.9986639900000002</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1">
-        <v>46155</v>
+        <v>46160</v>
       </c>
       <c r="B59" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C59">
-        <v>28.59002627414054</v>
+        <v>34.83995455757461</v>
       </c>
       <c r="D59">
-        <v>23.96230704059692</v>
+        <v>18.02301281718857</v>
       </c>
       <c r="E59">
-        <v>0.9999999989999999</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="F59">
-        <v>0.9999999989999999</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="G59">
-        <v>0.05179637495949674</v>
+        <v>0.1850932291737926</v>
       </c>
       <c r="H59">
-        <v>0.9999999989999999</v>
+        <v>0.99857724</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1">
-        <v>46156</v>
+        <v>46161</v>
       </c>
       <c r="B60" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C60">
-        <v>28.56217859389523</v>
+        <v>34.45479308705605</v>
       </c>
       <c r="D60">
-        <v>23.9411987302529</v>
+        <v>18.09576834566068</v>
       </c>
       <c r="E60">
-        <v>1</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="F60">
-        <v>1</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="G60">
-        <v>0.04837024516756849</v>
+        <v>0.1784731209386736</v>
       </c>
       <c r="H60">
-        <v>1</v>
+        <v>0.9985337599999999</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1">
-        <v>46157</v>
+        <v>46162</v>
       </c>
       <c r="B61" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C61">
-        <v>28.57618675936338</v>
+        <v>34.96336277390787</v>
       </c>
       <c r="D61">
-        <v>23.9576220541054</v>
+        <v>18.34938420029253</v>
       </c>
       <c r="E61">
-        <v>0.999503249</v>
+        <v>0.99963413</v>
       </c>
       <c r="F61">
-        <v>0.999503249</v>
+        <v>0.99963413</v>
       </c>
       <c r="G61">
-        <v>0.04983868243960732</v>
+        <v>0.2009313391215752</v>
       </c>
       <c r="H61">
-        <v>0.999503249</v>
+        <v>0.99848777</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1">
-        <v>46160</v>
+        <v>46163</v>
       </c>
       <c r="B62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C62">
-        <v>28.68951918518517</v>
+        <v>34.44616924817128</v>
       </c>
       <c r="D62">
-        <v>24.06134728453882</v>
+        <v>18.60085625074367</v>
       </c>
       <c r="E62">
-        <v>0.999503249</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="F62">
-        <v>0.999503249</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="G62">
-        <v>0.04983868243960732</v>
+        <v>0.2124957180214682</v>
       </c>
       <c r="H62">
-        <v>0.999503249</v>
+        <v>0.9985085200000001</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1">
-        <v>46161</v>
+        <v>46164</v>
       </c>
       <c r="B63" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C63">
-        <v>28.31167386654059</v>
+        <v>34.62137220937314</v>
       </c>
       <c r="D63">
-        <v>23.75157719455474</v>
+        <v>18.28780484745949</v>
       </c>
       <c r="E63">
-        <v>1.000177331</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="F63">
-        <v>1.000177331</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="G63">
-        <v>0.04053938625111919</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H63">
-        <v>1.000177331</v>
+        <v>0.9932939299999999</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1">
-        <v>46162</v>
+        <v>46153</v>
       </c>
       <c r="B64" t="s">
         <v>15</v>
       </c>
       <c r="C64">
-        <v>28.57911382310097</v>
+        <v>28.12253390077671</v>
       </c>
       <c r="D64">
-        <v>23.89431741541233</v>
+        <v>23.58699683751922</v>
       </c>
       <c r="E64">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="F64">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="G64">
-        <v>0.04690190590044785</v>
+        <v>0.03368732240295347</v>
       </c>
       <c r="H64">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1">
-        <v>46163</v>
+        <v>46154</v>
       </c>
       <c r="B65" t="s">
         <v>15</v>
       </c>
       <c r="C65">
-        <v>28.55785065378643</v>
+        <v>28.17715727830483</v>
       </c>
       <c r="D65">
-        <v>24.04274714970193</v>
+        <v>23.63894513078866</v>
       </c>
       <c r="E65">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="F65">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="G65">
-        <v>0.05228572319419666</v>
+        <v>0.03515547182056333</v>
       </c>
       <c r="H65">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B66" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C66">
-        <v>40.68830633303975</v>
+        <v>28.59002627414054</v>
       </c>
       <c r="D66">
-        <v>21.50431773660198</v>
+        <v>23.96230704059692</v>
       </c>
       <c r="E66">
-        <v>0.99909852</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F66">
-        <v>0.99909852</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G66">
-        <v>0.2342423866086769</v>
+        <v>0.05179637495949674</v>
       </c>
       <c r="H66">
-        <v>0.9974930900000001</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B67" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C67">
-        <v>40.32854894972581</v>
+        <v>28.56217859389523</v>
       </c>
       <c r="D67">
-        <v>21.09133998298594</v>
+        <v>23.9411987302529</v>
       </c>
       <c r="E67">
-        <v>0.9990972199999999</v>
+        <v>1</v>
       </c>
       <c r="F67">
-        <v>0.9990972199999999</v>
+        <v>1</v>
       </c>
       <c r="G67">
-        <v>0.2156468205051487</v>
+        <v>0.04837024516756849</v>
       </c>
       <c r="H67">
-        <v>0.99752223</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B68" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C68">
-        <v>40.47987921095815</v>
+        <v>28.57618675936338</v>
       </c>
       <c r="D68">
-        <v>21.35995364434454</v>
+        <v>23.9576220541054</v>
       </c>
       <c r="E68">
-        <v>0.9991780100000001</v>
+        <v>0.999503249</v>
       </c>
       <c r="F68">
-        <v>0.9991780100000001</v>
+        <v>0.999503249</v>
       </c>
       <c r="G68">
-        <v>0.2270956128473374</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H68">
-        <v>0.9975825700000001</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="B69" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C69">
-        <v>41.20436574895244</v>
+        <v>28.68951918518517</v>
       </c>
       <c r="D69">
-        <v>21.48149674387778</v>
+        <v>24.06134728453882</v>
       </c>
       <c r="E69">
-        <v>0.9991793299999999</v>
+        <v>0.999503249</v>
       </c>
       <c r="F69">
-        <v>0.9991793299999999</v>
+        <v>0.999503249</v>
       </c>
       <c r="G69">
-        <v>0.2454829228401052</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H69">
-        <v>0.99754722</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B70" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C70">
-        <v>40.80613062958688</v>
+        <v>28.31167386654059</v>
       </c>
       <c r="D70">
-        <v>21.08912555803936</v>
+        <v>23.75157719455474</v>
       </c>
       <c r="E70">
-        <v>0.9991790600000001</v>
+        <v>1.000177331</v>
       </c>
       <c r="F70">
-        <v>0.9991790600000001</v>
+        <v>1.000177331</v>
       </c>
       <c r="G70">
-        <v>0.2230017445022556</v>
+        <v>0.04053938625111919</v>
       </c>
       <c r="H70">
-        <v>0.9975824700000002</v>
+        <v>1.000177331</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="B71" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C71">
-        <v>40.11672876026724</v>
+        <v>28.57911382310097</v>
       </c>
       <c r="D71">
-        <v>20.79541439916316</v>
+        <v>23.89431741541233</v>
       </c>
       <c r="E71">
-        <v>0.999152</v>
+        <v>0.999503734</v>
       </c>
       <c r="F71">
-        <v>0.999152</v>
+        <v>0.999503734</v>
       </c>
       <c r="G71">
-        <v>0.2098184021536666</v>
+        <v>0.04690190590044785</v>
       </c>
       <c r="H71">
-        <v>0.9975007899999999</v>
+        <v>0.999503734</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="B72" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C72">
-        <v>39.69086941528401</v>
+        <v>28.55785065378643</v>
       </c>
       <c r="D72">
-        <v>20.74924328599426</v>
+        <v>24.04274714970193</v>
       </c>
       <c r="E72">
-        <v>0.99914989</v>
+        <v>1.000229282</v>
       </c>
       <c r="F72">
-        <v>0.99914989</v>
+        <v>1.000229282</v>
       </c>
       <c r="G72">
-        <v>0.2020471776850241</v>
+        <v>0.05228572319419666</v>
       </c>
       <c r="H72">
-        <v>0.9974417</v>
+        <v>1.000229282</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="B73" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C73">
-        <v>40.37836787855562</v>
+        <v>28.50194638163107</v>
       </c>
       <c r="D73">
-        <v>21.11271132314188</v>
+        <v>23.99272397156045</v>
       </c>
       <c r="E73">
-        <v>0.99915058</v>
+        <v>1</v>
       </c>
       <c r="F73">
-        <v>0.99915058</v>
+        <v>1</v>
       </c>
       <c r="G73">
-        <v>0.2291077670847563</v>
+        <v>0.04934923597154284</v>
       </c>
       <c r="H73">
-        <v>0.9974415600000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1">
-        <v>46163</v>
+        <v>46153</v>
       </c>
       <c r="B74" t="s">
         <v>16</v>
       </c>
       <c r="C74">
+        <v>40.68830633303975</v>
+      </c>
+      <c r="D74">
+        <v>21.50431773660198</v>
+      </c>
+      <c r="E74">
+        <v>0.99909852</v>
+      </c>
+      <c r="F74">
+        <v>0.99909852</v>
+      </c>
+      <c r="G74">
+        <v>0.2342423866086769</v>
+      </c>
+      <c r="H74">
+        <v>0.9974930900000001</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75">
+        <v>40.32854894972581</v>
+      </c>
+      <c r="D75">
+        <v>21.09133998298594</v>
+      </c>
+      <c r="E75">
+        <v>0.9990972199999999</v>
+      </c>
+      <c r="F75">
+        <v>0.9990972199999999</v>
+      </c>
+      <c r="G75">
+        <v>0.2156468205051487</v>
+      </c>
+      <c r="H75">
+        <v>0.99752223</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76">
+        <v>40.47987921095815</v>
+      </c>
+      <c r="D76">
+        <v>21.35995364434454</v>
+      </c>
+      <c r="E76">
+        <v>0.9991780100000001</v>
+      </c>
+      <c r="F76">
+        <v>0.9991780100000001</v>
+      </c>
+      <c r="G76">
+        <v>0.2270956128473374</v>
+      </c>
+      <c r="H76">
+        <v>0.9975825700000001</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77">
+        <v>41.20436574895244</v>
+      </c>
+      <c r="D77">
+        <v>21.48149674387778</v>
+      </c>
+      <c r="E77">
+        <v>0.9991793299999999</v>
+      </c>
+      <c r="F77">
+        <v>0.9991793299999999</v>
+      </c>
+      <c r="G77">
+        <v>0.2454829228401052</v>
+      </c>
+      <c r="H77">
+        <v>0.99754722</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78">
+        <v>40.80613062958688</v>
+      </c>
+      <c r="D78">
+        <v>21.08912555803936</v>
+      </c>
+      <c r="E78">
+        <v>0.9991790600000001</v>
+      </c>
+      <c r="F78">
+        <v>0.9991790600000001</v>
+      </c>
+      <c r="G78">
+        <v>0.2230017445022556</v>
+      </c>
+      <c r="H78">
+        <v>0.9975824700000002</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79">
+        <v>40.11672876026724</v>
+      </c>
+      <c r="D79">
+        <v>20.79541439916316</v>
+      </c>
+      <c r="E79">
+        <v>0.999152</v>
+      </c>
+      <c r="F79">
+        <v>0.999152</v>
+      </c>
+      <c r="G79">
+        <v>0.2098184021536666</v>
+      </c>
+      <c r="H79">
+        <v>0.9975007899999999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80">
+        <v>39.69086941528401</v>
+      </c>
+      <c r="D80">
+        <v>20.74924328599426</v>
+      </c>
+      <c r="E80">
+        <v>0.99914989</v>
+      </c>
+      <c r="F80">
+        <v>0.99914989</v>
+      </c>
+      <c r="G80">
+        <v>0.2020471776850241</v>
+      </c>
+      <c r="H80">
+        <v>0.9974417</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81">
+        <v>40.37836787855562</v>
+      </c>
+      <c r="D81">
+        <v>21.11271132314188</v>
+      </c>
+      <c r="E81">
+        <v>0.99915058</v>
+      </c>
+      <c r="F81">
+        <v>0.99915058</v>
+      </c>
+      <c r="G81">
+        <v>0.2291077670847563</v>
+      </c>
+      <c r="H81">
+        <v>0.9974415600000001</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82">
         <v>38.9123066967842</v>
       </c>
-      <c r="D74">
+      <c r="D82">
         <v>21.28910644207464</v>
       </c>
-      <c r="E74">
+      <c r="E82">
         <v>0.9989350699999999</v>
       </c>
-      <c r="F74">
+      <c r="F82">
         <v>0.9989350699999999</v>
       </c>
-      <c r="G74">
+      <c r="G82">
         <v>0.2392382040170877</v>
       </c>
-      <c r="H74">
+      <c r="H82">
         <v>0.99726191</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" s="1">
+        <v>46164</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83">
+        <v>39.43913909150694</v>
+      </c>
+      <c r="D83">
+        <v>21.05297617141148</v>
+      </c>
+      <c r="E83">
+        <v>0.999144</v>
+      </c>
+      <c r="F83">
+        <v>0.999144</v>
+      </c>
+      <c r="G83">
+        <v>0.2516582935428642</v>
+      </c>
+      <c r="H83">
+        <v>0.9974678400000001</v>
       </c>
     </row>
   </sheetData>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="17">
   <si>
     <t>Date</t>
   </si>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -509,42 +509,42 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>53.14833755912058</v>
+        <v>23.50043035988074</v>
       </c>
       <c r="D5">
-        <v>25.84885448407537</v>
+        <v>16.05971703883154</v>
       </c>
       <c r="E5">
-        <v>0.9262</v>
+        <v>0.8545999999999999</v>
       </c>
       <c r="F5">
-        <v>0.9262</v>
+        <v>0.8545999999999999</v>
       </c>
       <c r="G5">
-        <v>0.3839084462043663</v>
+        <v>0.4876634748449802</v>
       </c>
       <c r="H5">
-        <v>0.9262</v>
+        <v>0.9083</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
       </c>
       <c r="C6">
-        <v>51.82921169635205</v>
+        <v>53.14833755912058</v>
       </c>
       <c r="D6">
-        <v>25.32805827181975</v>
+        <v>25.84885448407537</v>
       </c>
       <c r="E6">
         <v>0.9262</v>
@@ -553,7 +553,7 @@
         <v>0.9262</v>
       </c>
       <c r="G6">
-        <v>0.3568580281685669</v>
+        <v>0.3839084462043663</v>
       </c>
       <c r="H6">
         <v>0.9262</v>
@@ -561,120 +561,120 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
       </c>
       <c r="C7">
-        <v>52.28471716753184</v>
+        <v>51.82921169635205</v>
       </c>
       <c r="D7">
-        <v>25.54525144150689</v>
+        <v>25.32805827181975</v>
       </c>
       <c r="E7">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="F7">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="G7">
-        <v>0.378012896547947</v>
+        <v>0.3568580281685669</v>
       </c>
       <c r="H7">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
       </c>
       <c r="C8">
-        <v>53.87287273813902</v>
+        <v>52.28471716753184</v>
       </c>
       <c r="D8">
-        <v>26.32154226438612</v>
+        <v>25.54525144150689</v>
       </c>
       <c r="E8">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="F8">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="G8">
-        <v>0.4166811087612758</v>
+        <v>0.378012896547947</v>
       </c>
       <c r="H8">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
       </c>
       <c r="C9">
-        <v>52.18747148214074</v>
+        <v>53.87287273813902</v>
       </c>
       <c r="D9">
-        <v>25.13616059644496</v>
+        <v>26.32154226438612</v>
       </c>
       <c r="E9">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="F9">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="G9">
-        <v>0.3627535778249862</v>
+        <v>0.4166811087612758</v>
       </c>
       <c r="H9">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
       </c>
       <c r="C10">
-        <v>50.72035274995172</v>
+        <v>52.18747148214074</v>
       </c>
       <c r="D10">
-        <v>24.61756040386634</v>
+        <v>25.13616059644496</v>
       </c>
       <c r="E10">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="F10">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="G10">
         <v>0.3627535778249862</v>
       </c>
       <c r="H10">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
       </c>
       <c r="C11">
-        <v>50.11981086673613</v>
+        <v>50.72035274995172</v>
       </c>
       <c r="D11">
-        <v>24.13061679021705</v>
+        <v>24.61756040386634</v>
       </c>
       <c r="E11">
         <v>0.9259000000000001</v>
@@ -683,7 +683,7 @@
         <v>0.9259000000000001</v>
       </c>
       <c r="G11">
-        <v>0.3258193430227221</v>
+        <v>0.3627535778249862</v>
       </c>
       <c r="H11">
         <v>0.9259000000000001</v>
@@ -691,224 +691,224 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
       </c>
       <c r="C12">
-        <v>51.74165648409151</v>
+        <v>50.11981086673613</v>
       </c>
       <c r="D12">
-        <v>24.98091384114761</v>
+        <v>24.13061679021705</v>
       </c>
       <c r="E12">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="F12">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="G12">
-        <v>0.3818277262286871</v>
+        <v>0.3258193430227221</v>
       </c>
       <c r="H12">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="B13" t="s">
         <v>9</v>
       </c>
       <c r="C13">
-        <v>49.13455894175823</v>
+        <v>51.74165648409151</v>
       </c>
       <c r="D13">
-        <v>25.30005057653127</v>
+        <v>24.98091384114761</v>
       </c>
       <c r="E13">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="F13">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="G13">
-        <v>0.4028091571787618</v>
+        <v>0.3818277262286871</v>
       </c>
       <c r="H13">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
       </c>
       <c r="C14">
-        <v>49.57776597479297</v>
+        <v>49.13455894175823</v>
       </c>
       <c r="D14">
-        <v>25.04906725563518</v>
+        <v>25.30005057653127</v>
       </c>
       <c r="E14">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="F14">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="G14">
-        <v>0.4256980029692063</v>
+        <v>0.4028091571787618</v>
       </c>
       <c r="H14">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1">
-        <v>46153</v>
+        <v>46164</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C15">
-        <v>34.64560932909123</v>
+        <v>49.57776597479297</v>
       </c>
       <c r="D15">
-        <v>26.08311546080494</v>
+        <v>25.04906725563518</v>
       </c>
       <c r="E15">
-        <v>0.9983000000000001</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="F15">
-        <v>0.9983000000000001</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="G15">
-        <v>0.06258613715048233</v>
+        <v>0.4256980029692063</v>
       </c>
       <c r="H15">
-        <v>0.9983000000000001</v>
+        <v>0.9245000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1">
-        <v>46154</v>
+        <v>46167</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C16">
-        <v>34.50204921141101</v>
+        <v>49.71239596645896</v>
       </c>
       <c r="D16">
-        <v>25.94535229304585</v>
+        <v>25.18778610744295</v>
       </c>
       <c r="E16">
-        <v>0.9984</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="F16">
-        <v>0.9984</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="G16">
-        <v>0.05768943168306073</v>
+        <v>0.4525749835757003</v>
       </c>
       <c r="H16">
-        <v>0.9984</v>
+        <v>0.9231999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
       </c>
       <c r="C17">
-        <v>35.10429483281073</v>
+        <v>34.64560932909123</v>
       </c>
       <c r="D17">
-        <v>26.43864879939599</v>
+        <v>26.08311546080494</v>
       </c>
       <c r="E17">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="F17">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="G17">
-        <v>0.07926550001722021</v>
+        <v>0.06258613715048233</v>
       </c>
       <c r="H17">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>
       </c>
       <c r="C18">
-        <v>35.36860632820093</v>
+        <v>34.50204921141101</v>
       </c>
       <c r="D18">
-        <v>26.56575571102338</v>
+        <v>25.94535229304585</v>
       </c>
       <c r="E18">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F18">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G18">
-        <v>0.08553946591902095</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H18">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="B19" t="s">
         <v>10</v>
       </c>
       <c r="C19">
-        <v>34.88080083527914</v>
+        <v>35.10429483281073</v>
       </c>
       <c r="D19">
-        <v>26.19322945679072</v>
+        <v>26.43864879939599</v>
       </c>
       <c r="E19">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="F19">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="G19">
-        <v>0.06870693142475881</v>
+        <v>0.07926550001722021</v>
       </c>
       <c r="H19">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1">
-        <v>46160</v>
+        <v>46156</v>
       </c>
       <c r="B20" t="s">
         <v>10</v>
       </c>
       <c r="C20">
-        <v>34.67638692539213</v>
+        <v>35.36860632820093</v>
       </c>
       <c r="D20">
-        <v>26.06707890342319</v>
+        <v>26.56575571102338</v>
       </c>
       <c r="E20">
         <v>0.9985999999999999</v>
@@ -917,7 +917,7 @@
         <v>0.9985999999999999</v>
       </c>
       <c r="G20">
-        <v>0.06289213016552919</v>
+        <v>0.08553946591902095</v>
       </c>
       <c r="H20">
         <v>0.9985999999999999</v>
@@ -925,510 +925,510 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="B21" t="s">
         <v>10</v>
       </c>
       <c r="C21">
-        <v>34.21212662725402</v>
+        <v>34.88080083527914</v>
       </c>
       <c r="D21">
-        <v>25.60349394367002</v>
+        <v>26.19322945679072</v>
       </c>
       <c r="E21">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="F21">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="G21">
-        <v>0.0486610616591685</v>
+        <v>0.06870693142475881</v>
       </c>
       <c r="H21">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="B22" t="s">
         <v>10</v>
       </c>
       <c r="C22">
-        <v>34.78598436564941</v>
+        <v>34.67638692539213</v>
       </c>
       <c r="D22">
-        <v>25.95505316769806</v>
+        <v>26.06707890342319</v>
       </c>
       <c r="E22">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="F22">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="G22">
-        <v>0.06335117806143331</v>
+        <v>0.06289213016552919</v>
       </c>
       <c r="H22">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1">
-        <v>46163</v>
+        <v>46161</v>
       </c>
       <c r="B23" t="s">
         <v>10</v>
       </c>
       <c r="C23">
-        <v>33.4539909056227</v>
+        <v>34.21212662725402</v>
       </c>
       <c r="D23">
-        <v>25.96014535427112</v>
+        <v>25.60349394367002</v>
       </c>
       <c r="E23">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="F23">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="G23">
-        <v>0.06350423294229035</v>
+        <v>0.0486610616591685</v>
       </c>
       <c r="H23">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1">
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="B24" t="s">
         <v>10</v>
       </c>
       <c r="C24">
-        <v>33.24951933563993</v>
+        <v>34.78598436564941</v>
       </c>
       <c r="D24">
-        <v>25.46629530314992</v>
+        <v>25.95505316769806</v>
       </c>
       <c r="E24">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="F24">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="G24">
-        <v>0.06136193159696024</v>
+        <v>0.06335117806143331</v>
       </c>
       <c r="H24">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1">
-        <v>46153</v>
+        <v>46163</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C25">
-        <v>36.55790859258162</v>
+        <v>33.4539909056227</v>
       </c>
       <c r="D25">
-        <v>22.67181120908155</v>
+        <v>25.96014535427112</v>
       </c>
       <c r="E25">
-        <v>0.9990740999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F25">
-        <v>0.9990740999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G25">
-        <v>0.1648443271746771</v>
+        <v>0.06350423294229035</v>
       </c>
       <c r="H25">
-        <v>0.9990740999999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1">
-        <v>46154</v>
+        <v>46164</v>
       </c>
       <c r="B26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C26">
-        <v>36.44753722959613</v>
+        <v>33.24951933563993</v>
       </c>
       <c r="D26">
-        <v>22.40292401789388</v>
+        <v>25.46629530314992</v>
       </c>
       <c r="E26">
-        <v>0.9990772499999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F26">
-        <v>0.9990772499999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G26">
-        <v>0.154964342628132</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H26">
-        <v>0.9990772499999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1">
-        <v>46155</v>
+        <v>46167</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C27">
-        <v>36.63128514035871</v>
+        <v>33.29896419867477</v>
       </c>
       <c r="D27">
-        <v>22.65773388934668</v>
+        <v>25.45090185337973</v>
       </c>
       <c r="E27">
-        <v>0.99907745</v>
+        <v>0.9984</v>
       </c>
       <c r="F27">
-        <v>0.99907745</v>
+        <v>0.9984</v>
       </c>
       <c r="G27">
-        <v>0.1671633421405267</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H27">
-        <v>0.99907745</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="B28" t="s">
         <v>11</v>
       </c>
       <c r="C28">
-        <v>36.87865927427314</v>
+        <v>36.55790859258162</v>
       </c>
       <c r="D28">
-        <v>22.69755646854794</v>
+        <v>22.67181120908155</v>
       </c>
       <c r="E28">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="F28">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="G28">
-        <v>0.1754592080224002</v>
+        <v>0.1648443271746771</v>
       </c>
       <c r="H28">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="B29" t="s">
         <v>11</v>
       </c>
       <c r="C29">
-        <v>36.52208783231286</v>
+        <v>36.44753722959613</v>
       </c>
       <c r="D29">
-        <v>22.32462309676992</v>
+        <v>22.40292401789388</v>
       </c>
       <c r="E29">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="F29">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="G29">
-        <v>0.1577242156354994</v>
+        <v>0.154964342628132</v>
       </c>
       <c r="H29">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="B30" t="s">
         <v>11</v>
       </c>
       <c r="C30">
-        <v>36.25604200674668</v>
+        <v>36.63128514035871</v>
       </c>
       <c r="D30">
-        <v>22.16555007468561</v>
+        <v>22.65773388934668</v>
       </c>
       <c r="E30">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="F30">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="G30">
-        <v>0.1527434068648266</v>
+        <v>0.1671633421405267</v>
       </c>
       <c r="H30">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1">
-        <v>46161</v>
+        <v>46156</v>
       </c>
       <c r="B31" t="s">
         <v>11</v>
       </c>
       <c r="C31">
-        <v>36.01040085730018</v>
+        <v>36.87865927427314</v>
       </c>
       <c r="D31">
-        <v>22.19475589056387</v>
+        <v>22.69755646854794</v>
       </c>
       <c r="E31">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="F31">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="G31">
-        <v>0.1456396418594061</v>
+        <v>0.1754592080224002</v>
       </c>
       <c r="H31">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1">
-        <v>46162</v>
+        <v>46157</v>
       </c>
       <c r="B32" t="s">
         <v>11</v>
       </c>
       <c r="C32">
-        <v>36.45290912796982</v>
+        <v>36.52208783231286</v>
       </c>
       <c r="D32">
-        <v>22.46357594746874</v>
+        <v>22.32462309676992</v>
       </c>
       <c r="E32">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="F32">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="G32">
-        <v>0.1646157747240327</v>
+        <v>0.1577242156354994</v>
       </c>
       <c r="H32">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1">
-        <v>46163</v>
+        <v>46160</v>
       </c>
       <c r="B33" t="s">
         <v>11</v>
       </c>
       <c r="C33">
-        <v>35.75282090566891</v>
+        <v>36.25604200674668</v>
       </c>
       <c r="D33">
-        <v>22.57615417310648</v>
+        <v>22.16555007468561</v>
       </c>
       <c r="E33">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="F33">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="G33">
-        <v>0.1668367104873381</v>
+        <v>0.1527434068648266</v>
       </c>
       <c r="H33">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1">
-        <v>46164</v>
+        <v>46161</v>
       </c>
       <c r="B34" t="s">
         <v>11</v>
       </c>
       <c r="C34">
-        <v>35.75514940724808</v>
+        <v>36.01040085730018</v>
       </c>
       <c r="D34">
-        <v>22.28880693466429</v>
+        <v>22.19475589056387</v>
       </c>
       <c r="E34">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="F34">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="G34">
-        <v>0.1717848261904962</v>
+        <v>0.1456396418594061</v>
       </c>
       <c r="H34">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1">
-        <v>46153</v>
+        <v>46162</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C35">
-        <v>52.70832779833182</v>
+        <v>36.45290912796982</v>
       </c>
       <c r="D35">
-        <v>23.99044674439659</v>
+        <v>22.46357594746874</v>
       </c>
       <c r="E35">
-        <v>0.9994000000000002</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="F35">
-        <v>0.9994000000000002</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="G35">
-        <v>0.5438253854918791</v>
+        <v>0.1646157747240327</v>
       </c>
       <c r="H35">
-        <v>0.9994000000000002</v>
+        <v>0.9992557700000001</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1">
-        <v>46154</v>
+        <v>46163</v>
       </c>
       <c r="B36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C36">
-        <v>50.89464485280568</v>
+        <v>35.75282090566891</v>
       </c>
       <c r="D36">
-        <v>23.21558303176282</v>
+        <v>22.57615417310648</v>
       </c>
       <c r="E36">
-        <v>0.9996</v>
+        <v>0.99926856</v>
       </c>
       <c r="F36">
-        <v>0.9996</v>
+        <v>0.99926856</v>
       </c>
       <c r="G36">
-        <v>0.5034825029548833</v>
+        <v>0.1668367104873381</v>
       </c>
       <c r="H36">
-        <v>0.9996</v>
+        <v>0.99926856</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1">
-        <v>46155</v>
+        <v>46164</v>
       </c>
       <c r="B37" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C37">
-        <v>51.8659994471731</v>
+        <v>35.75514940724808</v>
       </c>
       <c r="D37">
-        <v>23.7009037279043</v>
+        <v>22.28880693466429</v>
       </c>
       <c r="E37">
-        <v>1.0002</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="F37">
-        <v>1.0002</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="G37">
-        <v>0.533512029714132</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H37">
-        <v>1.0002</v>
+        <v>0.9992573500000002</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1">
-        <v>46156</v>
+        <v>46167</v>
       </c>
       <c r="B38" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C38">
-        <v>52.4470179952828</v>
+        <v>35.84133099010302</v>
       </c>
       <c r="D38">
-        <v>23.76861704536814</v>
+        <v>22.37458514769363</v>
       </c>
       <c r="E38">
-        <v>0.9998</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="F38">
-        <v>0.9998</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="G38">
-        <v>0.5492634496849078</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H38">
-        <v>0.9998</v>
+        <v>0.9992609200000001</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="B39" t="s">
         <v>12</v>
       </c>
       <c r="C39">
-        <v>50.81077380018606</v>
+        <v>52.70832779833182</v>
       </c>
       <c r="D39">
-        <v>22.76900580927995</v>
+        <v>23.99044674439659</v>
       </c>
       <c r="E39">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="F39">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="G39">
-        <v>0.4903296143797722</v>
+        <v>0.5438253854918791</v>
       </c>
       <c r="H39">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1">
-        <v>46160</v>
+        <v>46154</v>
       </c>
       <c r="B40" t="s">
         <v>12</v>
       </c>
       <c r="C40">
-        <v>49.50286387149169</v>
+        <v>50.89464485280568</v>
       </c>
       <c r="D40">
-        <v>22.24532119914133</v>
+        <v>23.21558303176282</v>
       </c>
       <c r="E40">
         <v>0.9996</v>
@@ -1437,7 +1437,7 @@
         <v>0.9996</v>
       </c>
       <c r="G40">
-        <v>0.4630591776162345</v>
+        <v>0.5034825029548833</v>
       </c>
       <c r="H40">
         <v>0.9996</v>
@@ -1445,1119 +1445,1353 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1">
-        <v>46161</v>
+        <v>46155</v>
       </c>
       <c r="B41" t="s">
         <v>12</v>
       </c>
       <c r="C41">
-        <v>49.29146729279496</v>
+        <v>51.8659994471731</v>
       </c>
       <c r="D41">
-        <v>22.22167836589682</v>
+        <v>23.7009037279043</v>
       </c>
       <c r="E41">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="F41">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="G41">
-        <v>0.4571659248870246</v>
+        <v>0.533512029714132</v>
       </c>
       <c r="H41">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1">
-        <v>46162</v>
+        <v>46156</v>
       </c>
       <c r="B42" t="s">
         <v>12</v>
       </c>
       <c r="C42">
-        <v>50.88652370817657</v>
+        <v>52.4470179952828</v>
       </c>
       <c r="D42">
-        <v>22.93254398967657</v>
+        <v>23.76861704536814</v>
       </c>
       <c r="E42">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F42">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G42">
-        <v>0.5126171754864624</v>
+        <v>0.5492634496849078</v>
       </c>
       <c r="H42">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1">
-        <v>46163</v>
+        <v>46157</v>
       </c>
       <c r="B43" t="s">
         <v>12</v>
       </c>
       <c r="C43">
-        <v>48.26646764818586</v>
+        <v>50.81077380018606</v>
       </c>
       <c r="D43">
-        <v>23.11655387625012</v>
+        <v>22.76900580927995</v>
       </c>
       <c r="E43">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="F43">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="G43">
-        <v>0.521243030947425</v>
+        <v>0.4903296143797722</v>
       </c>
       <c r="H43">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1">
-        <v>46164</v>
+        <v>46160</v>
       </c>
       <c r="B44" t="s">
         <v>12</v>
       </c>
       <c r="C44">
-        <v>48.84737503703267</v>
+        <v>49.50286387149169</v>
       </c>
       <c r="D44">
-        <v>22.83557604744466</v>
+        <v>22.24532119914133</v>
       </c>
       <c r="E44">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="F44">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="G44">
-        <v>0.5438521997590966</v>
+        <v>0.4630591776162345</v>
       </c>
       <c r="H44">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1">
-        <v>46153</v>
+        <v>46161</v>
       </c>
       <c r="B45" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C45">
-        <v>57.1732166855686</v>
+        <v>49.29146729279496</v>
       </c>
       <c r="D45">
-        <v>23.50022751267814</v>
+        <v>22.22167836589682</v>
       </c>
       <c r="E45">
-        <v>0.9991</v>
+        <v>0.9998</v>
       </c>
       <c r="F45">
-        <v>0.9991</v>
+        <v>0.9998</v>
       </c>
       <c r="G45">
-        <v>0.6994110097039083</v>
+        <v>0.4571659248870246</v>
       </c>
       <c r="H45">
-        <v>0.9991</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1">
-        <v>46154</v>
+        <v>46162</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C46">
-        <v>54.77380642078597</v>
+        <v>50.88652370817657</v>
       </c>
       <c r="D46">
-        <v>22.55192940254518</v>
+        <v>22.93254398967657</v>
       </c>
       <c r="E46">
-        <v>0.9990000000000001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F46">
-        <v>0.9990000000000001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G46">
-        <v>0.6459175880844941</v>
+        <v>0.5126171754864624</v>
       </c>
       <c r="H46">
-        <v>0.9990000000000001</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1">
-        <v>46155</v>
+        <v>46163</v>
       </c>
       <c r="B47" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C47">
-        <v>56.32187380830906</v>
+        <v>48.26646764818586</v>
       </c>
       <c r="D47">
-        <v>23.17121437414109</v>
+        <v>23.11655387625012</v>
       </c>
       <c r="E47">
-        <v>0.9990000000000001</v>
+        <v>0.9999</v>
       </c>
       <c r="F47">
-        <v>0.9990000000000001</v>
+        <v>0.9999</v>
       </c>
       <c r="G47">
-        <v>0.6851523922954754</v>
+        <v>0.521243030947425</v>
       </c>
       <c r="H47">
-        <v>0.9990000000000001</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1">
-        <v>46156</v>
+        <v>46164</v>
       </c>
       <c r="B48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C48">
-        <v>56.15321618553139</v>
+        <v>48.84737503703267</v>
       </c>
       <c r="D48">
-        <v>22.95838347314443</v>
+        <v>22.83557604744466</v>
       </c>
       <c r="E48">
-        <v>0.9992</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F48">
-        <v>0.9992</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G48">
-        <v>0.6907028507208208</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H48">
-        <v>0.9992</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1">
-        <v>46157</v>
+        <v>46167</v>
       </c>
       <c r="B49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C49">
-        <v>54.47755813049488</v>
+        <v>48.85151560750146</v>
       </c>
       <c r="D49">
-        <v>22.0083816089626</v>
+        <v>22.83513820206554</v>
       </c>
       <c r="E49">
-        <v>0.9986</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F49">
-        <v>0.9986</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G49">
-        <v>0.6220895940829376</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H49">
-        <v>0.9986</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
       </c>
       <c r="C50">
-        <v>52.6278781150669</v>
+        <v>57.1732166855686</v>
       </c>
       <c r="D50">
-        <v>21.5357353870778</v>
+        <v>23.50022751267814</v>
       </c>
       <c r="E50">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F50">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G50">
-        <v>0.5845134636435627</v>
+        <v>0.6994110097039083</v>
       </c>
       <c r="H50">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
       </c>
       <c r="C51">
-        <v>54.91583234840245</v>
+        <v>54.77380642078597</v>
       </c>
       <c r="D51">
-        <v>22.38321645985006</v>
+        <v>22.55192940254518</v>
       </c>
       <c r="E51">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F51">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G51">
-        <v>0.6596976539194066</v>
+        <v>0.6459175880844941</v>
       </c>
       <c r="H51">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
       </c>
       <c r="C52">
-        <v>53.91712298548793</v>
+        <v>56.32187380830906</v>
       </c>
       <c r="D52">
-        <v>22.73711181201267</v>
+        <v>23.17121437414109</v>
       </c>
       <c r="E52">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F52">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G52">
-        <v>0.6737329602396263</v>
+        <v>0.6851523922954754</v>
       </c>
       <c r="H52">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
       </c>
       <c r="C53">
-        <v>55.19651747515625</v>
+        <v>56.15321618553139</v>
       </c>
       <c r="D53">
-        <v>22.79462037330554</v>
+        <v>22.95838347314443</v>
       </c>
       <c r="E53">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
       <c r="F53">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
       <c r="G53">
-        <v>0.7139885317003913</v>
+        <v>0.6907028507208208</v>
       </c>
       <c r="H53">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="B54" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C54">
-        <v>35.78646526282436</v>
+        <v>54.47755813049488</v>
       </c>
       <c r="D54">
-        <v>18.96635091925032</v>
+        <v>22.0083816089626</v>
       </c>
       <c r="E54">
-        <v>0.9996491399999999</v>
+        <v>0.9986</v>
       </c>
       <c r="F54">
-        <v>0.9996491399999999</v>
+        <v>0.9986</v>
       </c>
       <c r="G54">
-        <v>0.2240600969213613</v>
+        <v>0.6220895940829376</v>
       </c>
       <c r="H54">
-        <v>0.9985614899999999</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="B55" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C55">
-        <v>35.71584102184062</v>
+        <v>52.6278781150669</v>
       </c>
       <c r="D55">
-        <v>18.62432950231353</v>
+        <v>21.5357353870778</v>
       </c>
       <c r="E55">
-        <v>0.99965481</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="F55">
-        <v>0.99965481</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="G55">
-        <v>0.2104844827747143</v>
+        <v>0.5845134636435627</v>
       </c>
       <c r="H55">
-        <v>0.9985622199999999</v>
+        <v>0.9988999999999999</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1">
-        <v>46155</v>
+        <v>46162</v>
       </c>
       <c r="B56" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C56">
-        <v>35.95182028203252</v>
+        <v>54.91583234840245</v>
       </c>
       <c r="D56">
-        <v>18.95670796791552</v>
+        <v>22.38321645985006</v>
       </c>
       <c r="E56">
-        <v>0.9996515200000001</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="F56">
-        <v>0.9996515200000001</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="G56">
-        <v>0.2259035693959275</v>
+        <v>0.6596976539194066</v>
       </c>
       <c r="H56">
-        <v>0.99855193</v>
+        <v>0.9990999999999999</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1">
-        <v>46156</v>
+        <v>46163</v>
       </c>
       <c r="B57" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C57">
-        <v>36.14451597805883</v>
+        <v>53.91712298548793</v>
       </c>
       <c r="D57">
-        <v>18.86297660538653</v>
+        <v>22.73711181201267</v>
       </c>
       <c r="E57">
-        <v>0.9996563399999999</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="F57">
-        <v>0.9996563399999999</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="G57">
-        <v>0.2362110061840785</v>
+        <v>0.6737329602396263</v>
       </c>
       <c r="H57">
-        <v>0.99857265</v>
+        <v>0.9991999999999999</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1">
-        <v>46157</v>
+        <v>46164</v>
       </c>
       <c r="B58" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C58">
-        <v>35.32805803135546</v>
+        <v>55.19651747515625</v>
       </c>
       <c r="D58">
-        <v>18.35643242381478</v>
+        <v>22.79462037330554</v>
       </c>
       <c r="E58">
-        <v>0.9997415800000001</v>
+        <v>0.9991</v>
       </c>
       <c r="F58">
-        <v>0.9997415800000001</v>
+        <v>0.9991</v>
       </c>
       <c r="G58">
-        <v>0.2023559161375383</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H58">
-        <v>0.9986639900000002</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="B59" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C59">
-        <v>34.83995455757461</v>
+        <v>55.28054997487197</v>
       </c>
       <c r="D59">
-        <v>18.02301281718857</v>
+        <v>23.00160891539877</v>
       </c>
       <c r="E59">
-        <v>0.9996851299999999</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="F59">
-        <v>0.9996851299999999</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="G59">
-        <v>0.1850932291737926</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H59">
-        <v>0.99857724</v>
+        <v>0.9989000000000001</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B60" t="s">
         <v>14</v>
       </c>
       <c r="C60">
-        <v>34.45479308705605</v>
+        <v>35.78646526282436</v>
       </c>
       <c r="D60">
-        <v>18.09576834566068</v>
+        <v>18.96635091925032</v>
       </c>
       <c r="E60">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="F60">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="G60">
-        <v>0.1784731209386736</v>
+        <v>0.2240600969213613</v>
       </c>
       <c r="H60">
-        <v>0.9985337599999999</v>
+        <v>0.9985614899999999</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B61" t="s">
         <v>14</v>
       </c>
       <c r="C61">
-        <v>34.96336277390787</v>
+        <v>35.71584102184062</v>
       </c>
       <c r="D61">
-        <v>18.34938420029253</v>
+        <v>18.62432950231353</v>
       </c>
       <c r="E61">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="F61">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="G61">
-        <v>0.2009313391215752</v>
+        <v>0.2104844827747143</v>
       </c>
       <c r="H61">
-        <v>0.99848777</v>
+        <v>0.9985622199999999</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B62" t="s">
         <v>14</v>
       </c>
       <c r="C62">
-        <v>34.44616924817128</v>
+        <v>35.95182028203252</v>
       </c>
       <c r="D62">
-        <v>18.60085625074367</v>
+        <v>18.95670796791552</v>
       </c>
       <c r="E62">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="F62">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="G62">
-        <v>0.2124957180214682</v>
+        <v>0.2259035693959275</v>
       </c>
       <c r="H62">
-        <v>0.9985085200000001</v>
+        <v>0.99855193</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="B63" t="s">
         <v>14</v>
       </c>
       <c r="C63">
-        <v>34.62137220937314</v>
+        <v>36.14451597805883</v>
       </c>
       <c r="D63">
-        <v>18.28780484745949</v>
+        <v>18.86297660538653</v>
       </c>
       <c r="E63">
-        <v>0.9996106299999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="F63">
-        <v>0.9996106299999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="G63">
-        <v>0.2145907067863493</v>
+        <v>0.2362110061840785</v>
       </c>
       <c r="H63">
-        <v>0.9932939299999999</v>
+        <v>0.99857265</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="B64" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C64">
-        <v>28.12253390077671</v>
+        <v>35.32805803135546</v>
       </c>
       <c r="D64">
-        <v>23.58699683751922</v>
+        <v>18.35643242381478</v>
       </c>
       <c r="E64">
-        <v>0.9997295369999999</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="F64">
-        <v>0.9997295369999999</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="G64">
-        <v>0.03368732240295347</v>
+        <v>0.2023559161375383</v>
       </c>
       <c r="H64">
-        <v>0.9997295369999999</v>
+        <v>0.9986639900000002</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="B65" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C65">
-        <v>28.17715727830483</v>
+        <v>34.83995455757461</v>
       </c>
       <c r="D65">
-        <v>23.63894513078866</v>
+        <v>18.02301281718857</v>
       </c>
       <c r="E65">
-        <v>1.000319473</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="F65">
-        <v>1.000319473</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="G65">
-        <v>0.03515547182056333</v>
+        <v>0.1850932291737926</v>
       </c>
       <c r="H65">
-        <v>1.000319473</v>
+        <v>0.99857724</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1">
-        <v>46155</v>
+        <v>46161</v>
       </c>
       <c r="B66" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C66">
-        <v>28.59002627414054</v>
+        <v>34.45479308705605</v>
       </c>
       <c r="D66">
-        <v>23.96230704059692</v>
+        <v>18.09576834566068</v>
       </c>
       <c r="E66">
-        <v>0.9999999989999999</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="F66">
-        <v>0.9999999989999999</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="G66">
-        <v>0.05179637495949674</v>
+        <v>0.1784731209386736</v>
       </c>
       <c r="H66">
-        <v>0.9999999989999999</v>
+        <v>0.9985337599999999</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1">
-        <v>46156</v>
+        <v>46162</v>
       </c>
       <c r="B67" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C67">
-        <v>28.56217859389523</v>
+        <v>34.96336277390787</v>
       </c>
       <c r="D67">
-        <v>23.9411987302529</v>
+        <v>18.34938420029253</v>
       </c>
       <c r="E67">
-        <v>1</v>
+        <v>0.99963413</v>
       </c>
       <c r="F67">
-        <v>1</v>
+        <v>0.99963413</v>
       </c>
       <c r="G67">
-        <v>0.04837024516756849</v>
+        <v>0.2009313391215752</v>
       </c>
       <c r="H67">
-        <v>1</v>
+        <v>0.99848777</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1">
-        <v>46157</v>
+        <v>46163</v>
       </c>
       <c r="B68" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C68">
-        <v>28.57618675936338</v>
+        <v>34.44616924817128</v>
       </c>
       <c r="D68">
-        <v>23.9576220541054</v>
+        <v>18.60085625074367</v>
       </c>
       <c r="E68">
-        <v>0.999503249</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="F68">
-        <v>0.999503249</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="G68">
-        <v>0.04983868243960732</v>
+        <v>0.2124957180214682</v>
       </c>
       <c r="H68">
-        <v>0.999503249</v>
+        <v>0.9985085200000001</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1">
-        <v>46160</v>
+        <v>46164</v>
       </c>
       <c r="B69" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C69">
-        <v>28.68951918518517</v>
+        <v>34.62137220937314</v>
       </c>
       <c r="D69">
-        <v>24.06134728453882</v>
+        <v>18.28780484745949</v>
       </c>
       <c r="E69">
-        <v>0.999503249</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="F69">
-        <v>0.999503249</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="G69">
-        <v>0.04983868243960732</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H69">
-        <v>0.999503249</v>
+        <v>0.9932939299999999</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1">
-        <v>46161</v>
+        <v>46167</v>
       </c>
       <c r="B70" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C70">
-        <v>28.31167386654059</v>
+        <v>34.6540695486741</v>
       </c>
       <c r="D70">
-        <v>23.75157719455474</v>
+        <v>18.36409048915342</v>
       </c>
       <c r="E70">
-        <v>1.000177331</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="F70">
-        <v>1.000177331</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="G70">
-        <v>0.04053938625111919</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H70">
-        <v>1.000177331</v>
+        <v>0.9984302600000001</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1">
-        <v>46162</v>
+        <v>46153</v>
       </c>
       <c r="B71" t="s">
         <v>15</v>
       </c>
       <c r="C71">
-        <v>28.57911382310097</v>
+        <v>28.12253390077671</v>
       </c>
       <c r="D71">
-        <v>23.89431741541233</v>
+        <v>23.58699683751922</v>
       </c>
       <c r="E71">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="F71">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="G71">
-        <v>0.04690190590044785</v>
+        <v>0.03368732240295347</v>
       </c>
       <c r="H71">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1">
-        <v>46163</v>
+        <v>46154</v>
       </c>
       <c r="B72" t="s">
         <v>15</v>
       </c>
       <c r="C72">
-        <v>28.55785065378643</v>
+        <v>28.17715727830483</v>
       </c>
       <c r="D72">
-        <v>24.04274714970193</v>
+        <v>23.63894513078866</v>
       </c>
       <c r="E72">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="F72">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="G72">
-        <v>0.05228572319419666</v>
+        <v>0.03515547182056333</v>
       </c>
       <c r="H72">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1">
-        <v>46164</v>
+        <v>46155</v>
       </c>
       <c r="B73" t="s">
         <v>15</v>
       </c>
       <c r="C73">
-        <v>28.50194638163107</v>
+        <v>28.59002627414054</v>
       </c>
       <c r="D73">
-        <v>23.99272397156045</v>
+        <v>23.96230704059692</v>
       </c>
       <c r="E73">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F73">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G73">
-        <v>0.04934923597154284</v>
+        <v>0.05179637495949674</v>
       </c>
       <c r="H73">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="B74" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C74">
-        <v>40.68830633303975</v>
+        <v>28.56217859389523</v>
       </c>
       <c r="D74">
-        <v>21.50431773660198</v>
+        <v>23.9411987302529</v>
       </c>
       <c r="E74">
-        <v>0.99909852</v>
+        <v>1</v>
       </c>
       <c r="F74">
-        <v>0.99909852</v>
+        <v>1</v>
       </c>
       <c r="G74">
-        <v>0.2342423866086769</v>
+        <v>0.04837024516756849</v>
       </c>
       <c r="H74">
-        <v>0.9974930900000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="B75" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C75">
-        <v>40.32854894972581</v>
+        <v>28.57618675936338</v>
       </c>
       <c r="D75">
-        <v>21.09133998298594</v>
+        <v>23.9576220541054</v>
       </c>
       <c r="E75">
-        <v>0.9990972199999999</v>
+        <v>0.999503249</v>
       </c>
       <c r="F75">
-        <v>0.9990972199999999</v>
+        <v>0.999503249</v>
       </c>
       <c r="G75">
-        <v>0.2156468205051487</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H75">
-        <v>0.99752223</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1">
-        <v>46155</v>
+        <v>46160</v>
       </c>
       <c r="B76" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C76">
-        <v>40.47987921095815</v>
+        <v>28.68951918518517</v>
       </c>
       <c r="D76">
-        <v>21.35995364434454</v>
+        <v>24.06134728453882</v>
       </c>
       <c r="E76">
-        <v>0.9991780100000001</v>
+        <v>0.999503249</v>
       </c>
       <c r="F76">
-        <v>0.9991780100000001</v>
+        <v>0.999503249</v>
       </c>
       <c r="G76">
-        <v>0.2270956128473374</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H76">
-        <v>0.9975825700000001</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1">
-        <v>46156</v>
+        <v>46161</v>
       </c>
       <c r="B77" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C77">
-        <v>41.20436574895244</v>
+        <v>28.31167386654059</v>
       </c>
       <c r="D77">
-        <v>21.48149674387778</v>
+        <v>23.75157719455474</v>
       </c>
       <c r="E77">
-        <v>0.9991793299999999</v>
+        <v>1.000177331</v>
       </c>
       <c r="F77">
-        <v>0.9991793299999999</v>
+        <v>1.000177331</v>
       </c>
       <c r="G77">
-        <v>0.2454829228401052</v>
+        <v>0.04053938625111919</v>
       </c>
       <c r="H77">
-        <v>0.99754722</v>
+        <v>1.000177331</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="1">
-        <v>46157</v>
+        <v>46162</v>
       </c>
       <c r="B78" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C78">
-        <v>40.80613062958688</v>
+        <v>28.57911382310097</v>
       </c>
       <c r="D78">
-        <v>21.08912555803936</v>
+        <v>23.89431741541233</v>
       </c>
       <c r="E78">
-        <v>0.9991790600000001</v>
+        <v>0.999503734</v>
       </c>
       <c r="F78">
-        <v>0.9991790600000001</v>
+        <v>0.999503734</v>
       </c>
       <c r="G78">
-        <v>0.2230017445022556</v>
+        <v>0.04690190590044785</v>
       </c>
       <c r="H78">
-        <v>0.9975824700000002</v>
+        <v>0.999503734</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1">
-        <v>46160</v>
+        <v>46163</v>
       </c>
       <c r="B79" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C79">
-        <v>40.11672876026724</v>
+        <v>28.55785065378643</v>
       </c>
       <c r="D79">
-        <v>20.79541439916316</v>
+        <v>24.04274714970193</v>
       </c>
       <c r="E79">
-        <v>0.999152</v>
+        <v>1.000229282</v>
       </c>
       <c r="F79">
-        <v>0.999152</v>
+        <v>1.000229282</v>
       </c>
       <c r="G79">
-        <v>0.2098184021536666</v>
+        <v>0.05228572319419666</v>
       </c>
       <c r="H79">
-        <v>0.9975007899999999</v>
+        <v>1.000229282</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1">
-        <v>46161</v>
+        <v>46164</v>
       </c>
       <c r="B80" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C80">
-        <v>39.69086941528401</v>
+        <v>28.50194638163107</v>
       </c>
       <c r="D80">
-        <v>20.74924328599426</v>
+        <v>23.99272397156045</v>
       </c>
       <c r="E80">
-        <v>0.99914989</v>
+        <v>1</v>
       </c>
       <c r="F80">
-        <v>0.99914989</v>
+        <v>1</v>
       </c>
       <c r="G80">
-        <v>0.2020471776850241</v>
+        <v>0.04934923597154284</v>
       </c>
       <c r="H80">
-        <v>0.9974417</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="1">
-        <v>46162</v>
+        <v>46167</v>
       </c>
       <c r="B81" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C81">
-        <v>40.37836787855562</v>
+        <v>28.55106858744498</v>
       </c>
       <c r="D81">
-        <v>21.11271132314188</v>
+        <v>23.9768329565351</v>
       </c>
       <c r="E81">
-        <v>0.99915058</v>
+        <v>1</v>
       </c>
       <c r="F81">
-        <v>0.99915058</v>
+        <v>1</v>
       </c>
       <c r="G81">
-        <v>0.2291077670847563</v>
+        <v>0.05571185335164408</v>
       </c>
       <c r="H81">
-        <v>0.9974415600000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="1">
-        <v>46163</v>
+        <v>46153</v>
       </c>
       <c r="B82" t="s">
         <v>16</v>
       </c>
       <c r="C82">
-        <v>38.9123066967842</v>
+        <v>40.68830633303975</v>
       </c>
       <c r="D82">
-        <v>21.28910644207464</v>
+        <v>21.50431773660198</v>
       </c>
       <c r="E82">
-        <v>0.9989350699999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="F82">
-        <v>0.9989350699999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="G82">
-        <v>0.2392382040170877</v>
+        <v>0.2342423866086769</v>
       </c>
       <c r="H82">
-        <v>0.99726191</v>
+        <v>0.9974930900000001</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="1">
-        <v>46164</v>
+        <v>46154</v>
       </c>
       <c r="B83" t="s">
         <v>16</v>
       </c>
       <c r="C83">
+        <v>40.32854894972581</v>
+      </c>
+      <c r="D83">
+        <v>21.09133998298594</v>
+      </c>
+      <c r="E83">
+        <v>0.9990972199999999</v>
+      </c>
+      <c r="F83">
+        <v>0.9990972199999999</v>
+      </c>
+      <c r="G83">
+        <v>0.2156468205051487</v>
+      </c>
+      <c r="H83">
+        <v>0.99752223</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84">
+        <v>40.47987921095815</v>
+      </c>
+      <c r="D84">
+        <v>21.35995364434454</v>
+      </c>
+      <c r="E84">
+        <v>0.9991780100000001</v>
+      </c>
+      <c r="F84">
+        <v>0.9991780100000001</v>
+      </c>
+      <c r="G84">
+        <v>0.2270956128473374</v>
+      </c>
+      <c r="H84">
+        <v>0.9975825700000001</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85">
+        <v>41.20436574895244</v>
+      </c>
+      <c r="D85">
+        <v>21.48149674387778</v>
+      </c>
+      <c r="E85">
+        <v>0.9991793299999999</v>
+      </c>
+      <c r="F85">
+        <v>0.9991793299999999</v>
+      </c>
+      <c r="G85">
+        <v>0.2454829228401052</v>
+      </c>
+      <c r="H85">
+        <v>0.99754722</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86">
+        <v>40.80613062958688</v>
+      </c>
+      <c r="D86">
+        <v>21.08912555803936</v>
+      </c>
+      <c r="E86">
+        <v>0.9991790600000001</v>
+      </c>
+      <c r="F86">
+        <v>0.9991790600000001</v>
+      </c>
+      <c r="G86">
+        <v>0.2230017445022556</v>
+      </c>
+      <c r="H86">
+        <v>0.9975824700000002</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87">
+        <v>40.11672876026724</v>
+      </c>
+      <c r="D87">
+        <v>20.79541439916316</v>
+      </c>
+      <c r="E87">
+        <v>0.999152</v>
+      </c>
+      <c r="F87">
+        <v>0.999152</v>
+      </c>
+      <c r="G87">
+        <v>0.2098184021536666</v>
+      </c>
+      <c r="H87">
+        <v>0.9975007899999999</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88">
+        <v>39.69086941528401</v>
+      </c>
+      <c r="D88">
+        <v>20.74924328599426</v>
+      </c>
+      <c r="E88">
+        <v>0.99914989</v>
+      </c>
+      <c r="F88">
+        <v>0.99914989</v>
+      </c>
+      <c r="G88">
+        <v>0.2020471776850241</v>
+      </c>
+      <c r="H88">
+        <v>0.9974417</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89">
+        <v>40.37836787855562</v>
+      </c>
+      <c r="D89">
+        <v>21.11271132314188</v>
+      </c>
+      <c r="E89">
+        <v>0.99915058</v>
+      </c>
+      <c r="F89">
+        <v>0.99915058</v>
+      </c>
+      <c r="G89">
+        <v>0.2291077670847563</v>
+      </c>
+      <c r="H89">
+        <v>0.9974415600000001</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90">
+        <v>38.9123066967842</v>
+      </c>
+      <c r="D90">
+        <v>21.28910644207464</v>
+      </c>
+      <c r="E90">
+        <v>0.9989350699999999</v>
+      </c>
+      <c r="F90">
+        <v>0.9989350699999999</v>
+      </c>
+      <c r="G90">
+        <v>0.2392382040170877</v>
+      </c>
+      <c r="H90">
+        <v>0.99726191</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" s="1">
+        <v>46164</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91">
         <v>39.43913909150694</v>
       </c>
-      <c r="D83">
+      <c r="D91">
         <v>21.05297617141148</v>
       </c>
-      <c r="E83">
+      <c r="E91">
         <v>0.999144</v>
       </c>
-      <c r="F83">
+      <c r="F91">
         <v>0.999144</v>
       </c>
-      <c r="G83">
+      <c r="G91">
         <v>0.2516582935428642</v>
       </c>
-      <c r="H83">
+      <c r="H91">
+        <v>0.9974678400000001</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92">
+        <v>39.45782844313628</v>
+      </c>
+      <c r="D92">
+        <v>21.0518901572272</v>
+      </c>
+      <c r="E92">
+        <v>0.999144</v>
+      </c>
+      <c r="F92">
+        <v>0.999144</v>
+      </c>
+      <c r="G92">
+        <v>0.2516582935428642</v>
+      </c>
+      <c r="H92">
         <v>0.9974678400000001</v>
       </c>
     </row>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="17">
   <si>
     <t>Date</t>
   </si>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -535,42 +535,42 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1">
-        <v>46153</v>
+        <v>46168</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>53.14833755912058</v>
+        <v>24.14090233899204</v>
       </c>
       <c r="D6">
-        <v>25.84885448407537</v>
+        <v>16.4877384097279</v>
       </c>
       <c r="E6">
-        <v>0.9262</v>
+        <v>0.8517</v>
       </c>
       <c r="F6">
-        <v>0.9262</v>
+        <v>0.8517</v>
       </c>
       <c r="G6">
-        <v>0.3839084462043663</v>
+        <v>0.55952974427947</v>
       </c>
       <c r="H6">
-        <v>0.9262</v>
+        <v>0.9055000000000003</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
       </c>
       <c r="C7">
-        <v>51.82921169635205</v>
+        <v>53.14833755912058</v>
       </c>
       <c r="D7">
-        <v>25.32805827181975</v>
+        <v>25.84885448407537</v>
       </c>
       <c r="E7">
         <v>0.9262</v>
@@ -579,7 +579,7 @@
         <v>0.9262</v>
       </c>
       <c r="G7">
-        <v>0.3568580281685669</v>
+        <v>0.3839084462043663</v>
       </c>
       <c r="H7">
         <v>0.9262</v>
@@ -587,120 +587,120 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
       </c>
       <c r="C8">
-        <v>52.28471716753184</v>
+        <v>51.82921169635205</v>
       </c>
       <c r="D8">
-        <v>25.54525144150689</v>
+        <v>25.32805827181975</v>
       </c>
       <c r="E8">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="F8">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="G8">
-        <v>0.378012896547947</v>
+        <v>0.3568580281685669</v>
       </c>
       <c r="H8">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
       </c>
       <c r="C9">
-        <v>53.87287273813902</v>
+        <v>52.28471716753184</v>
       </c>
       <c r="D9">
-        <v>26.32154226438612</v>
+        <v>25.54525144150689</v>
       </c>
       <c r="E9">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="F9">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="G9">
-        <v>0.4166811087612758</v>
+        <v>0.378012896547947</v>
       </c>
       <c r="H9">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
       </c>
       <c r="C10">
-        <v>52.18747148214074</v>
+        <v>53.87287273813902</v>
       </c>
       <c r="D10">
-        <v>25.13616059644496</v>
+        <v>26.32154226438612</v>
       </c>
       <c r="E10">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="F10">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="G10">
-        <v>0.3627535778249862</v>
+        <v>0.4166811087612758</v>
       </c>
       <c r="H10">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
       </c>
       <c r="C11">
-        <v>50.72035274995172</v>
+        <v>52.18747148214074</v>
       </c>
       <c r="D11">
-        <v>24.61756040386634</v>
+        <v>25.13616059644496</v>
       </c>
       <c r="E11">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="F11">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="G11">
         <v>0.3627535778249862</v>
       </c>
       <c r="H11">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
       </c>
       <c r="C12">
-        <v>50.11981086673613</v>
+        <v>50.72035274995172</v>
       </c>
       <c r="D12">
-        <v>24.13061679021705</v>
+        <v>24.61756040386634</v>
       </c>
       <c r="E12">
         <v>0.9259000000000001</v>
@@ -709,7 +709,7 @@
         <v>0.9259000000000001</v>
       </c>
       <c r="G12">
-        <v>0.3258193430227221</v>
+        <v>0.3627535778249862</v>
       </c>
       <c r="H12">
         <v>0.9259000000000001</v>
@@ -717,250 +717,250 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="B13" t="s">
         <v>9</v>
       </c>
       <c r="C13">
-        <v>51.74165648409151</v>
+        <v>50.11981086673613</v>
       </c>
       <c r="D13">
-        <v>24.98091384114761</v>
+        <v>24.13061679021705</v>
       </c>
       <c r="E13">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="F13">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="G13">
-        <v>0.3818277262286871</v>
+        <v>0.3258193430227221</v>
       </c>
       <c r="H13">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
       </c>
       <c r="C14">
-        <v>49.13455894175823</v>
+        <v>51.74165648409151</v>
       </c>
       <c r="D14">
-        <v>25.30005057653127</v>
+        <v>24.98091384114761</v>
       </c>
       <c r="E14">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="F14">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="G14">
-        <v>0.4028091571787618</v>
+        <v>0.3818277262286871</v>
       </c>
       <c r="H14">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
       </c>
       <c r="C15">
-        <v>49.57776597479297</v>
+        <v>49.13455894175823</v>
       </c>
       <c r="D15">
-        <v>25.04906725563518</v>
+        <v>25.30005057653127</v>
       </c>
       <c r="E15">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="F15">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="G15">
-        <v>0.4256980029692063</v>
+        <v>0.4028091571787618</v>
       </c>
       <c r="H15">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
       </c>
       <c r="C16">
-        <v>49.71239596645896</v>
+        <v>49.57776597479297</v>
       </c>
       <c r="D16">
-        <v>25.18778610744295</v>
+        <v>25.04906725563518</v>
       </c>
       <c r="E16">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="F16">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="G16">
-        <v>0.4525749835757003</v>
+        <v>0.4256980029692063</v>
       </c>
       <c r="H16">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C17">
-        <v>34.64560932909123</v>
+        <v>49.71239596645896</v>
       </c>
       <c r="D17">
-        <v>26.08311546080494</v>
+        <v>25.18778610744295</v>
       </c>
       <c r="E17">
-        <v>0.9983000000000001</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="F17">
-        <v>0.9983000000000001</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="G17">
-        <v>0.06258613715048233</v>
+        <v>0.4525749835757003</v>
       </c>
       <c r="H17">
-        <v>0.9983000000000001</v>
+        <v>0.9231999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1">
-        <v>46154</v>
+        <v>46168</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18">
-        <v>34.50204921141101</v>
+        <v>50.77166277510776</v>
       </c>
       <c r="D18">
-        <v>25.94535229304585</v>
+        <v>25.7431782858765</v>
       </c>
       <c r="E18">
-        <v>0.9984</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="F18">
-        <v>0.9984</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="G18">
-        <v>0.05768943168306073</v>
+        <v>0.4700884597036457</v>
       </c>
       <c r="H18">
-        <v>0.9984</v>
+        <v>0.9231999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="B19" t="s">
         <v>10</v>
       </c>
       <c r="C19">
-        <v>35.10429483281073</v>
+        <v>34.64560932909123</v>
       </c>
       <c r="D19">
-        <v>26.43864879939599</v>
+        <v>26.08311546080494</v>
       </c>
       <c r="E19">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="F19">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="G19">
-        <v>0.07926550001722021</v>
+        <v>0.06258613715048233</v>
       </c>
       <c r="H19">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="B20" t="s">
         <v>10</v>
       </c>
       <c r="C20">
-        <v>35.36860632820093</v>
+        <v>34.50204921141101</v>
       </c>
       <c r="D20">
-        <v>26.56575571102338</v>
+        <v>25.94535229304585</v>
       </c>
       <c r="E20">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F20">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G20">
-        <v>0.08553946591902095</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H20">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="B21" t="s">
         <v>10</v>
       </c>
       <c r="C21">
-        <v>34.88080083527914</v>
+        <v>35.10429483281073</v>
       </c>
       <c r="D21">
-        <v>26.19322945679072</v>
+        <v>26.43864879939599</v>
       </c>
       <c r="E21">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="F21">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="G21">
-        <v>0.06870693142475881</v>
+        <v>0.07926550001722021</v>
       </c>
       <c r="H21">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1">
-        <v>46160</v>
+        <v>46156</v>
       </c>
       <c r="B22" t="s">
         <v>10</v>
       </c>
       <c r="C22">
-        <v>34.67638692539213</v>
+        <v>35.36860632820093</v>
       </c>
       <c r="D22">
-        <v>26.06707890342319</v>
+        <v>26.56575571102338</v>
       </c>
       <c r="E22">
         <v>0.9985999999999999</v>
@@ -969,7 +969,7 @@
         <v>0.9985999999999999</v>
       </c>
       <c r="G22">
-        <v>0.06289213016552919</v>
+        <v>0.08553946591902095</v>
       </c>
       <c r="H22">
         <v>0.9985999999999999</v>
@@ -977,120 +977,120 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="B23" t="s">
         <v>10</v>
       </c>
       <c r="C23">
-        <v>34.21212662725402</v>
+        <v>34.88080083527914</v>
       </c>
       <c r="D23">
-        <v>25.60349394367002</v>
+        <v>26.19322945679072</v>
       </c>
       <c r="E23">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="F23">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="G23">
-        <v>0.0486610616591685</v>
+        <v>0.06870693142475881</v>
       </c>
       <c r="H23">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="B24" t="s">
         <v>10</v>
       </c>
       <c r="C24">
-        <v>34.78598436564941</v>
+        <v>34.67638692539213</v>
       </c>
       <c r="D24">
-        <v>25.95505316769806</v>
+        <v>26.06707890342319</v>
       </c>
       <c r="E24">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="F24">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="G24">
-        <v>0.06335117806143331</v>
+        <v>0.06289213016552919</v>
       </c>
       <c r="H24">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1">
-        <v>46163</v>
+        <v>46161</v>
       </c>
       <c r="B25" t="s">
         <v>10</v>
       </c>
       <c r="C25">
-        <v>33.4539909056227</v>
+        <v>34.21212662725402</v>
       </c>
       <c r="D25">
-        <v>25.96014535427112</v>
+        <v>25.60349394367002</v>
       </c>
       <c r="E25">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="F25">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="G25">
-        <v>0.06350423294229035</v>
+        <v>0.0486610616591685</v>
       </c>
       <c r="H25">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1">
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="B26" t="s">
         <v>10</v>
       </c>
       <c r="C26">
-        <v>33.24951933563993</v>
+        <v>34.78598436564941</v>
       </c>
       <c r="D26">
-        <v>25.46629530314992</v>
+        <v>25.95505316769806</v>
       </c>
       <c r="E26">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="F26">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="G26">
-        <v>0.06136193159696024</v>
+        <v>0.06335117806143331</v>
       </c>
       <c r="H26">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1">
-        <v>46167</v>
+        <v>46163</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
       </c>
       <c r="C27">
-        <v>33.29896419867477</v>
+        <v>33.4539909056227</v>
       </c>
       <c r="D27">
-        <v>25.45090185337973</v>
+        <v>25.96014535427112</v>
       </c>
       <c r="E27">
         <v>0.9984</v>
@@ -1099,7 +1099,7 @@
         <v>0.9984</v>
       </c>
       <c r="G27">
-        <v>0.06136193159696024</v>
+        <v>0.06350423294229035</v>
       </c>
       <c r="H27">
         <v>0.9984</v>
@@ -1107,432 +1107,432 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1">
-        <v>46153</v>
+        <v>46164</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C28">
-        <v>36.55790859258162</v>
+        <v>33.24951933563993</v>
       </c>
       <c r="D28">
-        <v>22.67181120908155</v>
+        <v>25.46629530314992</v>
       </c>
       <c r="E28">
-        <v>0.9990740999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F28">
-        <v>0.9990740999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G28">
-        <v>0.1648443271746771</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H28">
-        <v>0.9990740999999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1">
-        <v>46154</v>
+        <v>46167</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C29">
-        <v>36.44753722959613</v>
+        <v>33.29896419867477</v>
       </c>
       <c r="D29">
-        <v>22.40292401789388</v>
+        <v>25.45090185337973</v>
       </c>
       <c r="E29">
-        <v>0.9990772499999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F29">
-        <v>0.9990772499999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G29">
-        <v>0.154964342628132</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H29">
-        <v>0.9990772499999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1">
-        <v>46155</v>
+        <v>46168</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C30">
-        <v>36.63128514035871</v>
+        <v>33.41270923608511</v>
       </c>
       <c r="D30">
-        <v>22.65773388934668</v>
+        <v>25.54156152389702</v>
       </c>
       <c r="E30">
-        <v>0.99907745</v>
+        <v>0.9984</v>
       </c>
       <c r="F30">
-        <v>0.99907745</v>
+        <v>0.9984</v>
       </c>
       <c r="G30">
-        <v>0.1671633421405267</v>
+        <v>0.06549347940676342</v>
       </c>
       <c r="H30">
-        <v>0.99907745</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="B31" t="s">
         <v>11</v>
       </c>
       <c r="C31">
-        <v>36.87865927427314</v>
+        <v>36.55790859258162</v>
       </c>
       <c r="D31">
-        <v>22.69755646854794</v>
+        <v>22.67181120908155</v>
       </c>
       <c r="E31">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="F31">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="G31">
-        <v>0.1754592080224002</v>
+        <v>0.1648443271746771</v>
       </c>
       <c r="H31">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="B32" t="s">
         <v>11</v>
       </c>
       <c r="C32">
-        <v>36.52208783231286</v>
+        <v>36.44753722959613</v>
       </c>
       <c r="D32">
-        <v>22.32462309676992</v>
+        <v>22.40292401789388</v>
       </c>
       <c r="E32">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="F32">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="G32">
-        <v>0.1577242156354994</v>
+        <v>0.154964342628132</v>
       </c>
       <c r="H32">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="B33" t="s">
         <v>11</v>
       </c>
       <c r="C33">
-        <v>36.25604200674668</v>
+        <v>36.63128514035871</v>
       </c>
       <c r="D33">
-        <v>22.16555007468561</v>
+        <v>22.65773388934668</v>
       </c>
       <c r="E33">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="F33">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="G33">
-        <v>0.1527434068648266</v>
+        <v>0.1671633421405267</v>
       </c>
       <c r="H33">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1">
-        <v>46161</v>
+        <v>46156</v>
       </c>
       <c r="B34" t="s">
         <v>11</v>
       </c>
       <c r="C34">
-        <v>36.01040085730018</v>
+        <v>36.87865927427314</v>
       </c>
       <c r="D34">
-        <v>22.19475589056387</v>
+        <v>22.69755646854794</v>
       </c>
       <c r="E34">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="F34">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="G34">
-        <v>0.1456396418594061</v>
+        <v>0.1754592080224002</v>
       </c>
       <c r="H34">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1">
-        <v>46162</v>
+        <v>46157</v>
       </c>
       <c r="B35" t="s">
         <v>11</v>
       </c>
       <c r="C35">
-        <v>36.45290912796982</v>
+        <v>36.52208783231286</v>
       </c>
       <c r="D35">
-        <v>22.46357594746874</v>
+        <v>22.32462309676992</v>
       </c>
       <c r="E35">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="F35">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="G35">
-        <v>0.1646157747240327</v>
+        <v>0.1577242156354994</v>
       </c>
       <c r="H35">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1">
-        <v>46163</v>
+        <v>46160</v>
       </c>
       <c r="B36" t="s">
         <v>11</v>
       </c>
       <c r="C36">
-        <v>35.75282090566891</v>
+        <v>36.25604200674668</v>
       </c>
       <c r="D36">
-        <v>22.57615417310648</v>
+        <v>22.16555007468561</v>
       </c>
       <c r="E36">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="F36">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="G36">
-        <v>0.1668367104873381</v>
+        <v>0.1527434068648266</v>
       </c>
       <c r="H36">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1">
-        <v>46164</v>
+        <v>46161</v>
       </c>
       <c r="B37" t="s">
         <v>11</v>
       </c>
       <c r="C37">
-        <v>35.75514940724808</v>
+        <v>36.01040085730018</v>
       </c>
       <c r="D37">
-        <v>22.28880693466429</v>
+        <v>22.19475589056387</v>
       </c>
       <c r="E37">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="F37">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="G37">
-        <v>0.1717848261904962</v>
+        <v>0.1456396418594061</v>
       </c>
       <c r="H37">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1">
-        <v>46167</v>
+        <v>46162</v>
       </c>
       <c r="B38" t="s">
         <v>11</v>
       </c>
       <c r="C38">
-        <v>35.84133099010302</v>
+        <v>36.45290912796982</v>
       </c>
       <c r="D38">
-        <v>22.37458514769363</v>
+        <v>22.46357594746874</v>
       </c>
       <c r="E38">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="F38">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="G38">
-        <v>0.1717848261904962</v>
+        <v>0.1646157747240327</v>
       </c>
       <c r="H38">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1">
-        <v>46153</v>
+        <v>46163</v>
       </c>
       <c r="B39" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C39">
-        <v>52.70832779833182</v>
+        <v>35.75282090566891</v>
       </c>
       <c r="D39">
-        <v>23.99044674439659</v>
+        <v>22.57615417310648</v>
       </c>
       <c r="E39">
-        <v>0.9994000000000002</v>
+        <v>0.99926856</v>
       </c>
       <c r="F39">
-        <v>0.9994000000000002</v>
+        <v>0.99926856</v>
       </c>
       <c r="G39">
-        <v>0.5438253854918791</v>
+        <v>0.1668367104873381</v>
       </c>
       <c r="H39">
-        <v>0.9994000000000002</v>
+        <v>0.99926856</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1">
-        <v>46154</v>
+        <v>46164</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C40">
-        <v>50.89464485280568</v>
+        <v>35.75514940724808</v>
       </c>
       <c r="D40">
-        <v>23.21558303176282</v>
+        <v>22.28880693466429</v>
       </c>
       <c r="E40">
-        <v>0.9996</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="F40">
-        <v>0.9996</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="G40">
-        <v>0.5034825029548833</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H40">
-        <v>0.9996</v>
+        <v>0.9992573500000002</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1">
-        <v>46155</v>
+        <v>46167</v>
       </c>
       <c r="B41" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C41">
-        <v>51.8659994471731</v>
+        <v>35.84133099010302</v>
       </c>
       <c r="D41">
-        <v>23.7009037279043</v>
+        <v>22.37458514769363</v>
       </c>
       <c r="E41">
-        <v>1.0002</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="F41">
-        <v>1.0002</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="G41">
-        <v>0.533512029714132</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H41">
-        <v>1.0002</v>
+        <v>0.9992609200000001</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1">
-        <v>46156</v>
+        <v>46168</v>
       </c>
       <c r="B42" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C42">
-        <v>52.4470179952828</v>
+        <v>36.23214279739292</v>
       </c>
       <c r="D42">
-        <v>23.76861704536814</v>
+        <v>22.93484792820123</v>
       </c>
       <c r="E42">
-        <v>0.9998</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="F42">
-        <v>0.9998</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="G42">
-        <v>0.5492634496849078</v>
+        <v>0.1925900763781823</v>
       </c>
       <c r="H42">
-        <v>0.9998</v>
+        <v>0.9992609200000001</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="B43" t="s">
         <v>12</v>
       </c>
       <c r="C43">
-        <v>50.81077380018606</v>
+        <v>52.70832779833182</v>
       </c>
       <c r="D43">
-        <v>22.76900580927995</v>
+        <v>23.99044674439659</v>
       </c>
       <c r="E43">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="F43">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="G43">
-        <v>0.4903296143797722</v>
+        <v>0.5438253854918791</v>
       </c>
       <c r="H43">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1">
-        <v>46160</v>
+        <v>46154</v>
       </c>
       <c r="B44" t="s">
         <v>12</v>
       </c>
       <c r="C44">
-        <v>49.50286387149169</v>
+        <v>50.89464485280568</v>
       </c>
       <c r="D44">
-        <v>22.24532119914133</v>
+        <v>23.21558303176282</v>
       </c>
       <c r="E44">
         <v>0.9996</v>
@@ -1541,7 +1541,7 @@
         <v>0.9996</v>
       </c>
       <c r="G44">
-        <v>0.4630591776162345</v>
+        <v>0.5034825029548833</v>
       </c>
       <c r="H44">
         <v>0.9996</v>
@@ -1549,952 +1549,952 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1">
-        <v>46161</v>
+        <v>46155</v>
       </c>
       <c r="B45" t="s">
         <v>12</v>
       </c>
       <c r="C45">
-        <v>49.29146729279496</v>
+        <v>51.8659994471731</v>
       </c>
       <c r="D45">
-        <v>22.22167836589682</v>
+        <v>23.7009037279043</v>
       </c>
       <c r="E45">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="F45">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="G45">
-        <v>0.4571659248870246</v>
+        <v>0.533512029714132</v>
       </c>
       <c r="H45">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1">
-        <v>46162</v>
+        <v>46156</v>
       </c>
       <c r="B46" t="s">
         <v>12</v>
       </c>
       <c r="C46">
-        <v>50.88652370817657</v>
+        <v>52.4470179952828</v>
       </c>
       <c r="D46">
-        <v>22.93254398967657</v>
+        <v>23.76861704536814</v>
       </c>
       <c r="E46">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F46">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G46">
-        <v>0.5126171754864624</v>
+        <v>0.5492634496849078</v>
       </c>
       <c r="H46">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1">
-        <v>46163</v>
+        <v>46157</v>
       </c>
       <c r="B47" t="s">
         <v>12</v>
       </c>
       <c r="C47">
-        <v>48.26646764818586</v>
+        <v>50.81077380018606</v>
       </c>
       <c r="D47">
-        <v>23.11655387625012</v>
+        <v>22.76900580927995</v>
       </c>
       <c r="E47">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="F47">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="G47">
-        <v>0.521243030947425</v>
+        <v>0.4903296143797722</v>
       </c>
       <c r="H47">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1">
-        <v>46164</v>
+        <v>46160</v>
       </c>
       <c r="B48" t="s">
         <v>12</v>
       </c>
       <c r="C48">
-        <v>48.84737503703267</v>
+        <v>49.50286387149169</v>
       </c>
       <c r="D48">
-        <v>22.83557604744466</v>
+        <v>22.24532119914133</v>
       </c>
       <c r="E48">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="F48">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="G48">
-        <v>0.5438521997590966</v>
+        <v>0.4630591776162345</v>
       </c>
       <c r="H48">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1">
-        <v>46167</v>
+        <v>46161</v>
       </c>
       <c r="B49" t="s">
         <v>12</v>
       </c>
       <c r="C49">
-        <v>48.85151560750146</v>
+        <v>49.29146729279496</v>
       </c>
       <c r="D49">
-        <v>22.83513820206554</v>
+        <v>22.22167836589682</v>
       </c>
       <c r="E49">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F49">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G49">
-        <v>0.5438521997590966</v>
+        <v>0.4571659248870246</v>
       </c>
       <c r="H49">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1">
-        <v>46153</v>
+        <v>46162</v>
       </c>
       <c r="B50" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C50">
-        <v>57.1732166855686</v>
+        <v>50.88652370817657</v>
       </c>
       <c r="D50">
-        <v>23.50022751267814</v>
+        <v>22.93254398967657</v>
       </c>
       <c r="E50">
-        <v>0.9991</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F50">
-        <v>0.9991</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G50">
-        <v>0.6994110097039083</v>
+        <v>0.5126171754864624</v>
       </c>
       <c r="H50">
-        <v>0.9991</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1">
-        <v>46154</v>
+        <v>46163</v>
       </c>
       <c r="B51" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C51">
-        <v>54.77380642078597</v>
+        <v>48.26646764818586</v>
       </c>
       <c r="D51">
-        <v>22.55192940254518</v>
+        <v>23.11655387625012</v>
       </c>
       <c r="E51">
-        <v>0.9990000000000001</v>
+        <v>0.9999</v>
       </c>
       <c r="F51">
-        <v>0.9990000000000001</v>
+        <v>0.9999</v>
       </c>
       <c r="G51">
-        <v>0.6459175880844941</v>
+        <v>0.521243030947425</v>
       </c>
       <c r="H51">
-        <v>0.9990000000000001</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1">
-        <v>46155</v>
+        <v>46164</v>
       </c>
       <c r="B52" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C52">
-        <v>56.32187380830906</v>
+        <v>48.84737503703267</v>
       </c>
       <c r="D52">
-        <v>23.17121437414109</v>
+        <v>22.83557604744466</v>
       </c>
       <c r="E52">
-        <v>0.9990000000000001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F52">
-        <v>0.9990000000000001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G52">
-        <v>0.6851523922954754</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H52">
-        <v>0.9990000000000001</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1">
-        <v>46156</v>
+        <v>46167</v>
       </c>
       <c r="B53" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C53">
-        <v>56.15321618553139</v>
+        <v>48.85151560750146</v>
       </c>
       <c r="D53">
-        <v>22.95838347314443</v>
+        <v>22.83513820206554</v>
       </c>
       <c r="E53">
-        <v>0.9992</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F53">
-        <v>0.9992</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G53">
-        <v>0.6907028507208208</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H53">
-        <v>0.9992</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1">
-        <v>46157</v>
+        <v>46168</v>
       </c>
       <c r="B54" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C54">
-        <v>54.47755813049488</v>
+        <v>50.90437883274981</v>
       </c>
       <c r="D54">
-        <v>22.0083816089626</v>
+        <v>24.25672473501501</v>
       </c>
       <c r="E54">
-        <v>0.9986</v>
+        <v>0.9996999999999999</v>
       </c>
       <c r="F54">
-        <v>0.9986</v>
+        <v>0.9996999999999999</v>
       </c>
       <c r="G54">
-        <v>0.6220895940829376</v>
+        <v>0.6130191115419561</v>
       </c>
       <c r="H54">
-        <v>0.9986</v>
+        <v>0.9996999999999999</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
       </c>
       <c r="C55">
-        <v>52.6278781150669</v>
+        <v>57.1732166855686</v>
       </c>
       <c r="D55">
-        <v>21.5357353870778</v>
+        <v>23.50022751267814</v>
       </c>
       <c r="E55">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F55">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G55">
-        <v>0.5845134636435627</v>
+        <v>0.6994110097039083</v>
       </c>
       <c r="H55">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
       </c>
       <c r="C56">
-        <v>54.91583234840245</v>
+        <v>54.77380642078597</v>
       </c>
       <c r="D56">
-        <v>22.38321645985006</v>
+        <v>22.55192940254518</v>
       </c>
       <c r="E56">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F56">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G56">
-        <v>0.6596976539194066</v>
+        <v>0.6459175880844941</v>
       </c>
       <c r="H56">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
       </c>
       <c r="C57">
-        <v>53.91712298548793</v>
+        <v>56.32187380830906</v>
       </c>
       <c r="D57">
-        <v>22.73711181201267</v>
+        <v>23.17121437414109</v>
       </c>
       <c r="E57">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F57">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G57">
-        <v>0.6737329602396263</v>
+        <v>0.6851523922954754</v>
       </c>
       <c r="H57">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
       </c>
       <c r="C58">
-        <v>55.19651747515625</v>
+        <v>56.15321618553139</v>
       </c>
       <c r="D58">
-        <v>22.79462037330554</v>
+        <v>22.95838347314443</v>
       </c>
       <c r="E58">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
       <c r="F58">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
       <c r="G58">
-        <v>0.7139885317003913</v>
+        <v>0.6907028507208208</v>
       </c>
       <c r="H58">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
       </c>
       <c r="C59">
-        <v>55.28054997487197</v>
+        <v>54.47755813049488</v>
       </c>
       <c r="D59">
-        <v>23.00160891539877</v>
+        <v>22.0083816089626</v>
       </c>
       <c r="E59">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="F59">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="G59">
-        <v>0.7139885317003913</v>
+        <v>0.6220895940829376</v>
       </c>
       <c r="H59">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1">
-        <v>46153</v>
+        <v>46161</v>
       </c>
       <c r="B60" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C60">
-        <v>35.78646526282436</v>
+        <v>52.6278781150669</v>
       </c>
       <c r="D60">
-        <v>18.96635091925032</v>
+        <v>21.5357353870778</v>
       </c>
       <c r="E60">
-        <v>0.9996491399999999</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="F60">
-        <v>0.9996491399999999</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="G60">
-        <v>0.2240600969213613</v>
+        <v>0.5845134636435627</v>
       </c>
       <c r="H60">
-        <v>0.9985614899999999</v>
+        <v>0.9988999999999999</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1">
-        <v>46154</v>
+        <v>46162</v>
       </c>
       <c r="B61" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C61">
-        <v>35.71584102184062</v>
+        <v>54.91583234840245</v>
       </c>
       <c r="D61">
-        <v>18.62432950231353</v>
+        <v>22.38321645985006</v>
       </c>
       <c r="E61">
-        <v>0.99965481</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="F61">
-        <v>0.99965481</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="G61">
-        <v>0.2104844827747143</v>
+        <v>0.6596976539194066</v>
       </c>
       <c r="H61">
-        <v>0.9985622199999999</v>
+        <v>0.9990999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1">
-        <v>46155</v>
+        <v>46163</v>
       </c>
       <c r="B62" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C62">
-        <v>35.95182028203252</v>
+        <v>53.91712298548793</v>
       </c>
       <c r="D62">
-        <v>18.95670796791552</v>
+        <v>22.73711181201267</v>
       </c>
       <c r="E62">
-        <v>0.9996515200000001</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="F62">
-        <v>0.9996515200000001</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="G62">
-        <v>0.2259035693959275</v>
+        <v>0.6737329602396263</v>
       </c>
       <c r="H62">
-        <v>0.99855193</v>
+        <v>0.9991999999999999</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1">
-        <v>46156</v>
+        <v>46164</v>
       </c>
       <c r="B63" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C63">
-        <v>36.14451597805883</v>
+        <v>55.19651747515625</v>
       </c>
       <c r="D63">
-        <v>18.86297660538653</v>
+        <v>22.79462037330554</v>
       </c>
       <c r="E63">
-        <v>0.9996563399999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F63">
-        <v>0.9996563399999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G63">
-        <v>0.2362110061840785</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H63">
-        <v>0.99857265</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1">
-        <v>46157</v>
+        <v>46167</v>
       </c>
       <c r="B64" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C64">
-        <v>35.32805803135546</v>
+        <v>55.28054997487197</v>
       </c>
       <c r="D64">
-        <v>18.35643242381478</v>
+        <v>23.00160891539877</v>
       </c>
       <c r="E64">
-        <v>0.9997415800000001</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="F64">
-        <v>0.9997415800000001</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="G64">
-        <v>0.2023559161375383</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H64">
-        <v>0.9986639900000002</v>
+        <v>0.9989000000000001</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1">
-        <v>46160</v>
+        <v>46168</v>
       </c>
       <c r="B65" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C65">
-        <v>34.83995455757461</v>
+        <v>58.75156728873073</v>
       </c>
       <c r="D65">
-        <v>18.02301281718857</v>
+        <v>24.84249654093248</v>
       </c>
       <c r="E65">
-        <v>0.9996851299999999</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="F65">
-        <v>0.9996851299999999</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="G65">
-        <v>0.1850932291737926</v>
+        <v>0.8184872182632257</v>
       </c>
       <c r="H65">
-        <v>0.99857724</v>
+        <v>0.9989000000000001</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B66" t="s">
         <v>14</v>
       </c>
       <c r="C66">
-        <v>34.45479308705605</v>
+        <v>35.78646526282436</v>
       </c>
       <c r="D66">
-        <v>18.09576834566068</v>
+        <v>18.96635091925032</v>
       </c>
       <c r="E66">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="F66">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="G66">
-        <v>0.1784731209386736</v>
+        <v>0.2240600969213613</v>
       </c>
       <c r="H66">
-        <v>0.9985337599999999</v>
+        <v>0.9985614899999999</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B67" t="s">
         <v>14</v>
       </c>
       <c r="C67">
-        <v>34.96336277390787</v>
+        <v>35.71584102184062</v>
       </c>
       <c r="D67">
-        <v>18.34938420029253</v>
+        <v>18.62432950231353</v>
       </c>
       <c r="E67">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="F67">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="G67">
-        <v>0.2009313391215752</v>
+        <v>0.2104844827747143</v>
       </c>
       <c r="H67">
-        <v>0.99848777</v>
+        <v>0.9985622199999999</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B68" t="s">
         <v>14</v>
       </c>
       <c r="C68">
-        <v>34.44616924817128</v>
+        <v>35.95182028203252</v>
       </c>
       <c r="D68">
-        <v>18.60085625074367</v>
+        <v>18.95670796791552</v>
       </c>
       <c r="E68">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="F68">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="G68">
-        <v>0.2124957180214682</v>
+        <v>0.2259035693959275</v>
       </c>
       <c r="H68">
-        <v>0.9985085200000001</v>
+        <v>0.99855193</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="B69" t="s">
         <v>14</v>
       </c>
       <c r="C69">
-        <v>34.62137220937314</v>
+        <v>36.14451597805883</v>
       </c>
       <c r="D69">
-        <v>18.28780484745949</v>
+        <v>18.86297660538653</v>
       </c>
       <c r="E69">
-        <v>0.9996106299999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="F69">
-        <v>0.9996106299999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="G69">
-        <v>0.2145907067863493</v>
+        <v>0.2362110061840785</v>
       </c>
       <c r="H69">
-        <v>0.9932939299999999</v>
+        <v>0.99857265</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="B70" t="s">
         <v>14</v>
       </c>
       <c r="C70">
-        <v>34.6540695486741</v>
+        <v>35.32805803135546</v>
       </c>
       <c r="D70">
-        <v>18.36409048915342</v>
+        <v>18.35643242381478</v>
       </c>
       <c r="E70">
-        <v>0.9995448900000001</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="F70">
-        <v>0.9995448900000001</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="G70">
-        <v>0.2145907067863493</v>
+        <v>0.2023559161375383</v>
       </c>
       <c r="H70">
-        <v>0.9984302600000001</v>
+        <v>0.9986639900000002</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="B71" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C71">
-        <v>28.12253390077671</v>
+        <v>34.83995455757461</v>
       </c>
       <c r="D71">
-        <v>23.58699683751922</v>
+        <v>18.02301281718857</v>
       </c>
       <c r="E71">
-        <v>0.9997295369999999</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="F71">
-        <v>0.9997295369999999</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="G71">
-        <v>0.03368732240295347</v>
+        <v>0.1850932291737926</v>
       </c>
       <c r="H71">
-        <v>0.9997295369999999</v>
+        <v>0.99857724</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="B72" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C72">
-        <v>28.17715727830483</v>
+        <v>34.45479308705605</v>
       </c>
       <c r="D72">
-        <v>23.63894513078866</v>
+        <v>18.09576834566068</v>
       </c>
       <c r="E72">
-        <v>1.000319473</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="F72">
-        <v>1.000319473</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="G72">
-        <v>0.03515547182056333</v>
+        <v>0.1784731209386736</v>
       </c>
       <c r="H72">
-        <v>1.000319473</v>
+        <v>0.9985337599999999</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1">
-        <v>46155</v>
+        <v>46162</v>
       </c>
       <c r="B73" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C73">
-        <v>28.59002627414054</v>
+        <v>34.96336277390787</v>
       </c>
       <c r="D73">
-        <v>23.96230704059692</v>
+        <v>18.34938420029253</v>
       </c>
       <c r="E73">
-        <v>0.9999999989999999</v>
+        <v>0.99963413</v>
       </c>
       <c r="F73">
-        <v>0.9999999989999999</v>
+        <v>0.99963413</v>
       </c>
       <c r="G73">
-        <v>0.05179637495949674</v>
+        <v>0.2009313391215752</v>
       </c>
       <c r="H73">
-        <v>0.9999999989999999</v>
+        <v>0.99848777</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1">
-        <v>46156</v>
+        <v>46163</v>
       </c>
       <c r="B74" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C74">
-        <v>28.56217859389523</v>
+        <v>34.44616924817128</v>
       </c>
       <c r="D74">
-        <v>23.9411987302529</v>
+        <v>18.60085625074367</v>
       </c>
       <c r="E74">
-        <v>1</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="F74">
-        <v>1</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="G74">
-        <v>0.04837024516756849</v>
+        <v>0.2124957180214682</v>
       </c>
       <c r="H74">
-        <v>1</v>
+        <v>0.9985085200000001</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1">
-        <v>46157</v>
+        <v>46164</v>
       </c>
       <c r="B75" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C75">
-        <v>28.57618675936338</v>
+        <v>34.62137220937314</v>
       </c>
       <c r="D75">
-        <v>23.9576220541054</v>
+        <v>18.28780484745949</v>
       </c>
       <c r="E75">
-        <v>0.999503249</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="F75">
-        <v>0.999503249</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="G75">
-        <v>0.04983868243960732</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H75">
-        <v>0.999503249</v>
+        <v>0.9932939299999999</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="B76" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C76">
-        <v>28.68951918518517</v>
+        <v>34.6540695486741</v>
       </c>
       <c r="D76">
-        <v>24.06134728453882</v>
+        <v>18.36409048915342</v>
       </c>
       <c r="E76">
-        <v>0.999503249</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="F76">
-        <v>0.999503249</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="G76">
-        <v>0.04983868243960732</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H76">
-        <v>0.999503249</v>
+        <v>0.9984302600000001</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1">
-        <v>46161</v>
+        <v>46168</v>
       </c>
       <c r="B77" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C77">
-        <v>28.31167386654059</v>
+        <v>35.4820130509417</v>
       </c>
       <c r="D77">
-        <v>23.75157719455474</v>
+        <v>19.20292041814603</v>
       </c>
       <c r="E77">
-        <v>1.000177331</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="F77">
-        <v>1.000177331</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="G77">
-        <v>0.04053938625111919</v>
+        <v>0.2553172934903569</v>
       </c>
       <c r="H77">
-        <v>1.000177331</v>
+        <v>0.9984302600000001</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="1">
-        <v>46162</v>
+        <v>46153</v>
       </c>
       <c r="B78" t="s">
         <v>15</v>
       </c>
       <c r="C78">
-        <v>28.57911382310097</v>
+        <v>28.12253390077671</v>
       </c>
       <c r="D78">
-        <v>23.89431741541233</v>
+        <v>23.58699683751922</v>
       </c>
       <c r="E78">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="F78">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="G78">
-        <v>0.04690190590044785</v>
+        <v>0.03368732240295347</v>
       </c>
       <c r="H78">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1">
-        <v>46163</v>
+        <v>46154</v>
       </c>
       <c r="B79" t="s">
         <v>15</v>
       </c>
       <c r="C79">
-        <v>28.55785065378643</v>
+        <v>28.17715727830483</v>
       </c>
       <c r="D79">
-        <v>24.04274714970193</v>
+        <v>23.63894513078866</v>
       </c>
       <c r="E79">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="F79">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="G79">
-        <v>0.05228572319419666</v>
+        <v>0.03515547182056333</v>
       </c>
       <c r="H79">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1">
-        <v>46164</v>
+        <v>46155</v>
       </c>
       <c r="B80" t="s">
         <v>15</v>
       </c>
       <c r="C80">
-        <v>28.50194638163107</v>
+        <v>28.59002627414054</v>
       </c>
       <c r="D80">
-        <v>23.99272397156045</v>
+        <v>23.96230704059692</v>
       </c>
       <c r="E80">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F80">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G80">
-        <v>0.04934923597154284</v>
+        <v>0.05179637495949674</v>
       </c>
       <c r="H80">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="1">
-        <v>46167</v>
+        <v>46156</v>
       </c>
       <c r="B81" t="s">
         <v>15</v>
       </c>
       <c r="C81">
-        <v>28.55106858744498</v>
+        <v>28.56217859389523</v>
       </c>
       <c r="D81">
-        <v>23.9768329565351</v>
+        <v>23.9411987302529</v>
       </c>
       <c r="E81">
         <v>1</v>
@@ -2503,7 +2503,7 @@
         <v>1</v>
       </c>
       <c r="G81">
-        <v>0.05571185335164408</v>
+        <v>0.04837024516756849</v>
       </c>
       <c r="H81">
         <v>1</v>
@@ -2511,288 +2511,522 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="1">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="B82" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C82">
-        <v>40.68830633303975</v>
+        <v>28.57618675936338</v>
       </c>
       <c r="D82">
-        <v>21.50431773660198</v>
+        <v>23.9576220541054</v>
       </c>
       <c r="E82">
-        <v>0.99909852</v>
+        <v>0.999503249</v>
       </c>
       <c r="F82">
-        <v>0.99909852</v>
+        <v>0.999503249</v>
       </c>
       <c r="G82">
-        <v>0.2342423866086769</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H82">
-        <v>0.9974930900000001</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="1">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="B83" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C83">
-        <v>40.32854894972581</v>
+        <v>28.68951918518517</v>
       </c>
       <c r="D83">
-        <v>21.09133998298594</v>
+        <v>24.06134728453882</v>
       </c>
       <c r="E83">
-        <v>0.9990972199999999</v>
+        <v>0.999503249</v>
       </c>
       <c r="F83">
-        <v>0.9990972199999999</v>
+        <v>0.999503249</v>
       </c>
       <c r="G83">
-        <v>0.2156468205051487</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H83">
-        <v>0.99752223</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="1">
-        <v>46155</v>
+        <v>46161</v>
       </c>
       <c r="B84" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C84">
-        <v>40.47987921095815</v>
+        <v>28.31167386654059</v>
       </c>
       <c r="D84">
-        <v>21.35995364434454</v>
+        <v>23.75157719455474</v>
       </c>
       <c r="E84">
-        <v>0.9991780100000001</v>
+        <v>1.000177331</v>
       </c>
       <c r="F84">
-        <v>0.9991780100000001</v>
+        <v>1.000177331</v>
       </c>
       <c r="G84">
-        <v>0.2270956128473374</v>
+        <v>0.04053938625111919</v>
       </c>
       <c r="H84">
-        <v>0.9975825700000001</v>
+        <v>1.000177331</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1">
-        <v>46156</v>
+        <v>46162</v>
       </c>
       <c r="B85" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C85">
-        <v>41.20436574895244</v>
+        <v>28.57911382310097</v>
       </c>
       <c r="D85">
-        <v>21.48149674387778</v>
+        <v>23.89431741541233</v>
       </c>
       <c r="E85">
-        <v>0.9991793299999999</v>
+        <v>0.999503734</v>
       </c>
       <c r="F85">
-        <v>0.9991793299999999</v>
+        <v>0.999503734</v>
       </c>
       <c r="G85">
-        <v>0.2454829228401052</v>
+        <v>0.04690190590044785</v>
       </c>
       <c r="H85">
-        <v>0.99754722</v>
+        <v>0.999503734</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="1">
-        <v>46157</v>
+        <v>46163</v>
       </c>
       <c r="B86" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C86">
-        <v>40.80613062958688</v>
+        <v>28.55785065378643</v>
       </c>
       <c r="D86">
-        <v>21.08912555803936</v>
+        <v>24.04274714970193</v>
       </c>
       <c r="E86">
-        <v>0.9991790600000001</v>
+        <v>1.000229282</v>
       </c>
       <c r="F86">
-        <v>0.9991790600000001</v>
+        <v>1.000229282</v>
       </c>
       <c r="G86">
-        <v>0.2230017445022556</v>
+        <v>0.05228572319419666</v>
       </c>
       <c r="H86">
-        <v>0.9975824700000002</v>
+        <v>1.000229282</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="1">
-        <v>46160</v>
+        <v>46164</v>
       </c>
       <c r="B87" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C87">
-        <v>40.11672876026724</v>
+        <v>28.50194638163107</v>
       </c>
       <c r="D87">
-        <v>20.79541439916316</v>
+        <v>23.99272397156045</v>
       </c>
       <c r="E87">
-        <v>0.999152</v>
+        <v>1</v>
       </c>
       <c r="F87">
-        <v>0.999152</v>
+        <v>1</v>
       </c>
       <c r="G87">
-        <v>0.2098184021536666</v>
+        <v>0.04934923597154284</v>
       </c>
       <c r="H87">
-        <v>0.9975007899999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1">
-        <v>46161</v>
+        <v>46167</v>
       </c>
       <c r="B88" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C88">
-        <v>39.69086941528401</v>
+        <v>28.55106858744498</v>
       </c>
       <c r="D88">
-        <v>20.74924328599426</v>
+        <v>23.9768329565351</v>
       </c>
       <c r="E88">
-        <v>0.99914989</v>
+        <v>1</v>
       </c>
       <c r="F88">
-        <v>0.99914989</v>
+        <v>1</v>
       </c>
       <c r="G88">
-        <v>0.2020471776850241</v>
+        <v>0.05571185335164408</v>
       </c>
       <c r="H88">
-        <v>0.9974417</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="1">
-        <v>46162</v>
+        <v>46168</v>
       </c>
       <c r="B89" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C89">
-        <v>40.37836787855562</v>
+        <v>28.54681541456266</v>
       </c>
       <c r="D89">
-        <v>21.11271132314188</v>
+        <v>23.97386168967948</v>
       </c>
       <c r="E89">
-        <v>0.99915058</v>
+        <v>1</v>
       </c>
       <c r="F89">
-        <v>0.99915058</v>
+        <v>1</v>
       </c>
       <c r="G89">
-        <v>0.2291077670847563</v>
+        <v>0.04837034303541388</v>
       </c>
       <c r="H89">
-        <v>0.9974415600000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="1">
-        <v>46163</v>
+        <v>46153</v>
       </c>
       <c r="B90" t="s">
         <v>16</v>
       </c>
       <c r="C90">
-        <v>38.9123066967842</v>
+        <v>40.68830633303975</v>
       </c>
       <c r="D90">
-        <v>21.28910644207464</v>
+        <v>21.50431773660198</v>
       </c>
       <c r="E90">
-        <v>0.9989350699999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="F90">
-        <v>0.9989350699999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="G90">
-        <v>0.2392382040170877</v>
+        <v>0.2342423866086769</v>
       </c>
       <c r="H90">
-        <v>0.99726191</v>
+        <v>0.9974930900000001</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="1">
-        <v>46164</v>
+        <v>46154</v>
       </c>
       <c r="B91" t="s">
         <v>16</v>
       </c>
       <c r="C91">
-        <v>39.43913909150694</v>
+        <v>40.32854894972581</v>
       </c>
       <c r="D91">
-        <v>21.05297617141148</v>
+        <v>21.09133998298594</v>
       </c>
       <c r="E91">
-        <v>0.999144</v>
+        <v>0.9990972199999999</v>
       </c>
       <c r="F91">
-        <v>0.999144</v>
+        <v>0.9990972199999999</v>
       </c>
       <c r="G91">
-        <v>0.2516582935428642</v>
+        <v>0.2156468205051487</v>
       </c>
       <c r="H91">
-        <v>0.9974678400000001</v>
+        <v>0.99752223</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="1">
-        <v>46167</v>
+        <v>46155</v>
       </c>
       <c r="B92" t="s">
         <v>16</v>
       </c>
       <c r="C92">
+        <v>40.47987921095815</v>
+      </c>
+      <c r="D92">
+        <v>21.35995364434454</v>
+      </c>
+      <c r="E92">
+        <v>0.9991780100000001</v>
+      </c>
+      <c r="F92">
+        <v>0.9991780100000001</v>
+      </c>
+      <c r="G92">
+        <v>0.2270956128473374</v>
+      </c>
+      <c r="H92">
+        <v>0.9975825700000001</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93">
+        <v>41.20436574895244</v>
+      </c>
+      <c r="D93">
+        <v>21.48149674387778</v>
+      </c>
+      <c r="E93">
+        <v>0.9991793299999999</v>
+      </c>
+      <c r="F93">
+        <v>0.9991793299999999</v>
+      </c>
+      <c r="G93">
+        <v>0.2454829228401052</v>
+      </c>
+      <c r="H93">
+        <v>0.99754722</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94">
+        <v>40.80613062958688</v>
+      </c>
+      <c r="D94">
+        <v>21.08912555803936</v>
+      </c>
+      <c r="E94">
+        <v>0.9991790600000001</v>
+      </c>
+      <c r="F94">
+        <v>0.9991790600000001</v>
+      </c>
+      <c r="G94">
+        <v>0.2230017445022556</v>
+      </c>
+      <c r="H94">
+        <v>0.9975824700000002</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95">
+        <v>40.11672876026724</v>
+      </c>
+      <c r="D95">
+        <v>20.79541439916316</v>
+      </c>
+      <c r="E95">
+        <v>0.999152</v>
+      </c>
+      <c r="F95">
+        <v>0.999152</v>
+      </c>
+      <c r="G95">
+        <v>0.2098184021536666</v>
+      </c>
+      <c r="H95">
+        <v>0.9975007899999999</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96">
+        <v>39.69086941528401</v>
+      </c>
+      <c r="D96">
+        <v>20.74924328599426</v>
+      </c>
+      <c r="E96">
+        <v>0.99914989</v>
+      </c>
+      <c r="F96">
+        <v>0.99914989</v>
+      </c>
+      <c r="G96">
+        <v>0.2020471776850241</v>
+      </c>
+      <c r="H96">
+        <v>0.9974417</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97">
+        <v>40.37836787855562</v>
+      </c>
+      <c r="D97">
+        <v>21.11271132314188</v>
+      </c>
+      <c r="E97">
+        <v>0.99915058</v>
+      </c>
+      <c r="F97">
+        <v>0.99915058</v>
+      </c>
+      <c r="G97">
+        <v>0.2291077670847563</v>
+      </c>
+      <c r="H97">
+        <v>0.9974415600000001</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98">
+        <v>38.9123066967842</v>
+      </c>
+      <c r="D98">
+        <v>21.28910644207464</v>
+      </c>
+      <c r="E98">
+        <v>0.9989350699999999</v>
+      </c>
+      <c r="F98">
+        <v>0.9989350699999999</v>
+      </c>
+      <c r="G98">
+        <v>0.2392382040170877</v>
+      </c>
+      <c r="H98">
+        <v>0.99726191</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" s="1">
+        <v>46164</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99">
+        <v>39.43913909150694</v>
+      </c>
+      <c r="D99">
+        <v>21.05297617141148</v>
+      </c>
+      <c r="E99">
+        <v>0.999144</v>
+      </c>
+      <c r="F99">
+        <v>0.999144</v>
+      </c>
+      <c r="G99">
+        <v>0.2516582935428642</v>
+      </c>
+      <c r="H99">
+        <v>0.9974678400000001</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100">
         <v>39.45782844313628</v>
       </c>
-      <c r="D92">
+      <c r="D100">
         <v>21.0518901572272</v>
       </c>
-      <c r="E92">
+      <c r="E100">
         <v>0.999144</v>
       </c>
-      <c r="F92">
+      <c r="F100">
         <v>0.999144</v>
       </c>
-      <c r="G92">
+      <c r="G100">
         <v>0.2516582935428642</v>
       </c>
-      <c r="H92">
+      <c r="H100">
         <v>0.9974678400000001</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101">
+        <v>40.20219297984542</v>
+      </c>
+      <c r="D101">
+        <v>21.93106024403281</v>
+      </c>
+      <c r="E101">
+        <v>0.9991421799999999</v>
+      </c>
+      <c r="F101">
+        <v>0.9991421799999999</v>
+      </c>
+      <c r="G101">
+        <v>0.2846167552893293</v>
+      </c>
+      <c r="H101">
+        <v>0.9974609800000001</v>
       </c>
     </row>
   </sheetData>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="17">
   <si>
     <t>Date</t>
   </si>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -561,42 +561,42 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1">
-        <v>46153</v>
+        <v>46169</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7">
-        <v>53.14833755912058</v>
+        <v>24.14012495989505</v>
       </c>
       <c r="D7">
-        <v>25.84885448407537</v>
+        <v>16.46578274225799</v>
       </c>
       <c r="E7">
-        <v>0.9262</v>
+        <v>0.8513000000000001</v>
       </c>
       <c r="F7">
-        <v>0.9262</v>
+        <v>0.8513000000000001</v>
       </c>
       <c r="G7">
-        <v>0.3839084462043663</v>
+        <v>0.5532373571746756</v>
       </c>
       <c r="H7">
-        <v>0.9262</v>
+        <v>0.907</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
       </c>
       <c r="C8">
-        <v>51.82921169635205</v>
+        <v>53.14833755912058</v>
       </c>
       <c r="D8">
-        <v>25.32805827181975</v>
+        <v>25.84885448407537</v>
       </c>
       <c r="E8">
         <v>0.9262</v>
@@ -605,7 +605,7 @@
         <v>0.9262</v>
       </c>
       <c r="G8">
-        <v>0.3568580281685669</v>
+        <v>0.3839084462043663</v>
       </c>
       <c r="H8">
         <v>0.9262</v>
@@ -613,120 +613,120 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
       </c>
       <c r="C9">
-        <v>52.28471716753184</v>
+        <v>51.82921169635205</v>
       </c>
       <c r="D9">
-        <v>25.54525144150689</v>
+        <v>25.32805827181975</v>
       </c>
       <c r="E9">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="F9">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="G9">
-        <v>0.378012896547947</v>
+        <v>0.3568580281685669</v>
       </c>
       <c r="H9">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
       </c>
       <c r="C10">
-        <v>53.87287273813902</v>
+        <v>52.28471716753184</v>
       </c>
       <c r="D10">
-        <v>26.32154226438612</v>
+        <v>25.54525144150689</v>
       </c>
       <c r="E10">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="F10">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="G10">
-        <v>0.4166811087612758</v>
+        <v>0.378012896547947</v>
       </c>
       <c r="H10">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
       </c>
       <c r="C11">
-        <v>52.18747148214074</v>
+        <v>53.87287273813902</v>
       </c>
       <c r="D11">
-        <v>25.13616059644496</v>
+        <v>26.32154226438612</v>
       </c>
       <c r="E11">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="F11">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="G11">
-        <v>0.3627535778249862</v>
+        <v>0.4166811087612758</v>
       </c>
       <c r="H11">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
       </c>
       <c r="C12">
-        <v>50.72035274995172</v>
+        <v>52.18747148214074</v>
       </c>
       <c r="D12">
-        <v>24.61756040386634</v>
+        <v>25.13616059644496</v>
       </c>
       <c r="E12">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="F12">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="G12">
         <v>0.3627535778249862</v>
       </c>
       <c r="H12">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="B13" t="s">
         <v>9</v>
       </c>
       <c r="C13">
-        <v>50.11981086673613</v>
+        <v>50.72035274995172</v>
       </c>
       <c r="D13">
-        <v>24.13061679021705</v>
+        <v>24.61756040386634</v>
       </c>
       <c r="E13">
         <v>0.9259000000000001</v>
@@ -735,7 +735,7 @@
         <v>0.9259000000000001</v>
       </c>
       <c r="G13">
-        <v>0.3258193430227221</v>
+        <v>0.3627535778249862</v>
       </c>
       <c r="H13">
         <v>0.9259000000000001</v>
@@ -743,120 +743,120 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
       </c>
       <c r="C14">
-        <v>51.74165648409151</v>
+        <v>50.11981086673613</v>
       </c>
       <c r="D14">
-        <v>24.98091384114761</v>
+        <v>24.13061679021705</v>
       </c>
       <c r="E14">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="F14">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="G14">
-        <v>0.3818277262286871</v>
+        <v>0.3258193430227221</v>
       </c>
       <c r="H14">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
       </c>
       <c r="C15">
-        <v>49.13455894175823</v>
+        <v>51.74165648409151</v>
       </c>
       <c r="D15">
-        <v>25.30005057653127</v>
+        <v>24.98091384114761</v>
       </c>
       <c r="E15">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="F15">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="G15">
-        <v>0.4028091571787618</v>
+        <v>0.3818277262286871</v>
       </c>
       <c r="H15">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
       </c>
       <c r="C16">
-        <v>49.57776597479297</v>
+        <v>49.13455894175823</v>
       </c>
       <c r="D16">
-        <v>25.04906725563518</v>
+        <v>25.30005057653127</v>
       </c>
       <c r="E16">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="F16">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="G16">
-        <v>0.4256980029692063</v>
+        <v>0.4028091571787618</v>
       </c>
       <c r="H16">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
       </c>
       <c r="C17">
-        <v>49.71239596645896</v>
+        <v>49.57776597479297</v>
       </c>
       <c r="D17">
-        <v>25.18778610744295</v>
+        <v>25.04906725563518</v>
       </c>
       <c r="E17">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="F17">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="G17">
-        <v>0.4525749835757003</v>
+        <v>0.4256980029692063</v>
       </c>
       <c r="H17">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="B18" t="s">
         <v>9</v>
       </c>
       <c r="C18">
-        <v>50.77166277510776</v>
+        <v>49.71239596645896</v>
       </c>
       <c r="D18">
-        <v>25.7431782858765</v>
+        <v>25.18778610744295</v>
       </c>
       <c r="E18">
         <v>0.9231999999999999</v>
@@ -865,7 +865,7 @@
         <v>0.9231999999999999</v>
       </c>
       <c r="G18">
-        <v>0.4700884597036457</v>
+        <v>0.4525749835757003</v>
       </c>
       <c r="H18">
         <v>0.9231999999999999</v>
@@ -873,146 +873,146 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1">
-        <v>46153</v>
+        <v>46168</v>
       </c>
       <c r="B19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C19">
-        <v>34.64560932909123</v>
+        <v>50.77166277510776</v>
       </c>
       <c r="D19">
-        <v>26.08311546080494</v>
+        <v>25.7431782858765</v>
       </c>
       <c r="E19">
-        <v>0.9983000000000001</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="F19">
-        <v>0.9983000000000001</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="G19">
-        <v>0.06258613715048233</v>
+        <v>0.4700884597036457</v>
       </c>
       <c r="H19">
-        <v>0.9983000000000001</v>
+        <v>0.9231999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1">
-        <v>46154</v>
+        <v>46169</v>
       </c>
       <c r="B20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C20">
-        <v>34.50204921141101</v>
+        <v>50.57689164833899</v>
       </c>
       <c r="D20">
-        <v>25.94535229304585</v>
+        <v>25.70244067238947</v>
       </c>
       <c r="E20">
-        <v>0.9984</v>
+        <v>0.9217</v>
       </c>
       <c r="F20">
-        <v>0.9984</v>
+        <v>0.9217</v>
       </c>
       <c r="G20">
-        <v>0.05768943168306073</v>
+        <v>0.4518814984464716</v>
       </c>
       <c r="H20">
-        <v>0.9984</v>
+        <v>0.9217</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="B21" t="s">
         <v>10</v>
       </c>
       <c r="C21">
-        <v>35.10429483281073</v>
+        <v>34.64560932909123</v>
       </c>
       <c r="D21">
-        <v>26.43864879939599</v>
+        <v>26.08311546080494</v>
       </c>
       <c r="E21">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="F21">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="G21">
-        <v>0.07926550001722021</v>
+        <v>0.06258613715048233</v>
       </c>
       <c r="H21">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="B22" t="s">
         <v>10</v>
       </c>
       <c r="C22">
-        <v>35.36860632820093</v>
+        <v>34.50204921141101</v>
       </c>
       <c r="D22">
-        <v>26.56575571102338</v>
+        <v>25.94535229304585</v>
       </c>
       <c r="E22">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F22">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G22">
-        <v>0.08553946591902095</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H22">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="B23" t="s">
         <v>10</v>
       </c>
       <c r="C23">
-        <v>34.88080083527914</v>
+        <v>35.10429483281073</v>
       </c>
       <c r="D23">
-        <v>26.19322945679072</v>
+        <v>26.43864879939599</v>
       </c>
       <c r="E23">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="F23">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="G23">
-        <v>0.06870693142475881</v>
+        <v>0.07926550001722021</v>
       </c>
       <c r="H23">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1">
-        <v>46160</v>
+        <v>46156</v>
       </c>
       <c r="B24" t="s">
         <v>10</v>
       </c>
       <c r="C24">
-        <v>34.67638692539213</v>
+        <v>35.36860632820093</v>
       </c>
       <c r="D24">
-        <v>26.06707890342319</v>
+        <v>26.56575571102338</v>
       </c>
       <c r="E24">
         <v>0.9985999999999999</v>
@@ -1021,7 +1021,7 @@
         <v>0.9985999999999999</v>
       </c>
       <c r="G24">
-        <v>0.06289213016552919</v>
+        <v>0.08553946591902095</v>
       </c>
       <c r="H24">
         <v>0.9985999999999999</v>
@@ -1029,120 +1029,120 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="B25" t="s">
         <v>10</v>
       </c>
       <c r="C25">
-        <v>34.21212662725402</v>
+        <v>34.88080083527914</v>
       </c>
       <c r="D25">
-        <v>25.60349394367002</v>
+        <v>26.19322945679072</v>
       </c>
       <c r="E25">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="F25">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="G25">
-        <v>0.0486610616591685</v>
+        <v>0.06870693142475881</v>
       </c>
       <c r="H25">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="B26" t="s">
         <v>10</v>
       </c>
       <c r="C26">
-        <v>34.78598436564941</v>
+        <v>34.67638692539213</v>
       </c>
       <c r="D26">
-        <v>25.95505316769806</v>
+        <v>26.06707890342319</v>
       </c>
       <c r="E26">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="F26">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="G26">
-        <v>0.06335117806143331</v>
+        <v>0.06289213016552919</v>
       </c>
       <c r="H26">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1">
-        <v>46163</v>
+        <v>46161</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
       </c>
       <c r="C27">
-        <v>33.4539909056227</v>
+        <v>34.21212662725402</v>
       </c>
       <c r="D27">
-        <v>25.96014535427112</v>
+        <v>25.60349394367002</v>
       </c>
       <c r="E27">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="F27">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="G27">
-        <v>0.06350423294229035</v>
+        <v>0.0486610616591685</v>
       </c>
       <c r="H27">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1">
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
       </c>
       <c r="C28">
-        <v>33.24951933563993</v>
+        <v>34.78598436564941</v>
       </c>
       <c r="D28">
-        <v>25.46629530314992</v>
+        <v>25.95505316769806</v>
       </c>
       <c r="E28">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="F28">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="G28">
-        <v>0.06136193159696024</v>
+        <v>0.06335117806143331</v>
       </c>
       <c r="H28">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1">
-        <v>46167</v>
+        <v>46163</v>
       </c>
       <c r="B29" t="s">
         <v>10</v>
       </c>
       <c r="C29">
-        <v>33.29896419867477</v>
+        <v>33.4539909056227</v>
       </c>
       <c r="D29">
-        <v>25.45090185337973</v>
+        <v>25.96014535427112</v>
       </c>
       <c r="E29">
         <v>0.9984</v>
@@ -1151,7 +1151,7 @@
         <v>0.9984</v>
       </c>
       <c r="G29">
-        <v>0.06136193159696024</v>
+        <v>0.06350423294229035</v>
       </c>
       <c r="H29">
         <v>0.9984</v>
@@ -1159,16 +1159,16 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1">
-        <v>46168</v>
+        <v>46164</v>
       </c>
       <c r="B30" t="s">
         <v>10</v>
       </c>
       <c r="C30">
-        <v>33.41270923608511</v>
+        <v>33.24951933563993</v>
       </c>
       <c r="D30">
-        <v>25.54156152389702</v>
+        <v>25.46629530314992</v>
       </c>
       <c r="E30">
         <v>0.9984</v>
@@ -1177,7 +1177,7 @@
         <v>0.9984</v>
       </c>
       <c r="G30">
-        <v>0.06549347940676342</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H30">
         <v>0.9984</v>
@@ -1185,458 +1185,458 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C31">
-        <v>36.55790859258162</v>
+        <v>33.29896419867477</v>
       </c>
       <c r="D31">
-        <v>22.67181120908155</v>
+        <v>25.45090185337973</v>
       </c>
       <c r="E31">
-        <v>0.9990740999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F31">
-        <v>0.9990740999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G31">
-        <v>0.1648443271746771</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H31">
-        <v>0.9990740999999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1">
-        <v>46154</v>
+        <v>46168</v>
       </c>
       <c r="B32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C32">
-        <v>36.44753722959613</v>
+        <v>33.41270923608511</v>
       </c>
       <c r="D32">
-        <v>22.40292401789388</v>
+        <v>25.54156152389702</v>
       </c>
       <c r="E32">
-        <v>0.9990772499999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F32">
-        <v>0.9990772499999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G32">
-        <v>0.154964342628132</v>
+        <v>0.06549347940676342</v>
       </c>
       <c r="H32">
-        <v>0.9990772499999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1">
-        <v>46155</v>
+        <v>46169</v>
       </c>
       <c r="B33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C33">
-        <v>36.63128514035871</v>
+        <v>33.73350746548562</v>
       </c>
       <c r="D33">
-        <v>22.65773388934668</v>
+        <v>25.75393367034243</v>
       </c>
       <c r="E33">
-        <v>0.99907745</v>
+        <v>0.9987000000000001</v>
       </c>
       <c r="F33">
-        <v>0.99907745</v>
+        <v>0.9987000000000001</v>
       </c>
       <c r="G33">
-        <v>0.1671633421405267</v>
+        <v>0.07620510288008187</v>
       </c>
       <c r="H33">
-        <v>0.99907745</v>
+        <v>0.9987000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="B34" t="s">
         <v>11</v>
       </c>
       <c r="C34">
-        <v>36.87865927427314</v>
+        <v>36.55790859258162</v>
       </c>
       <c r="D34">
-        <v>22.69755646854794</v>
+        <v>22.67181120908155</v>
       </c>
       <c r="E34">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="F34">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="G34">
-        <v>0.1754592080224002</v>
+        <v>0.1648443271746771</v>
       </c>
       <c r="H34">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="B35" t="s">
         <v>11</v>
       </c>
       <c r="C35">
-        <v>36.52208783231286</v>
+        <v>36.44753722959613</v>
       </c>
       <c r="D35">
-        <v>22.32462309676992</v>
+        <v>22.40292401789388</v>
       </c>
       <c r="E35">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="F35">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="G35">
-        <v>0.1577242156354994</v>
+        <v>0.154964342628132</v>
       </c>
       <c r="H35">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="B36" t="s">
         <v>11</v>
       </c>
       <c r="C36">
-        <v>36.25604200674668</v>
+        <v>36.63128514035871</v>
       </c>
       <c r="D36">
-        <v>22.16555007468561</v>
+        <v>22.65773388934668</v>
       </c>
       <c r="E36">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="F36">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="G36">
-        <v>0.1527434068648266</v>
+        <v>0.1671633421405267</v>
       </c>
       <c r="H36">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1">
-        <v>46161</v>
+        <v>46156</v>
       </c>
       <c r="B37" t="s">
         <v>11</v>
       </c>
       <c r="C37">
-        <v>36.01040085730018</v>
+        <v>36.87865927427314</v>
       </c>
       <c r="D37">
-        <v>22.19475589056387</v>
+        <v>22.69755646854794</v>
       </c>
       <c r="E37">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="F37">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="G37">
-        <v>0.1456396418594061</v>
+        <v>0.1754592080224002</v>
       </c>
       <c r="H37">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1">
-        <v>46162</v>
+        <v>46157</v>
       </c>
       <c r="B38" t="s">
         <v>11</v>
       </c>
       <c r="C38">
-        <v>36.45290912796982</v>
+        <v>36.52208783231286</v>
       </c>
       <c r="D38">
-        <v>22.46357594746874</v>
+        <v>22.32462309676992</v>
       </c>
       <c r="E38">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="F38">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="G38">
-        <v>0.1646157747240327</v>
+        <v>0.1577242156354994</v>
       </c>
       <c r="H38">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1">
-        <v>46163</v>
+        <v>46160</v>
       </c>
       <c r="B39" t="s">
         <v>11</v>
       </c>
       <c r="C39">
-        <v>35.75282090566891</v>
+        <v>36.25604200674668</v>
       </c>
       <c r="D39">
-        <v>22.57615417310648</v>
+        <v>22.16555007468561</v>
       </c>
       <c r="E39">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="F39">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="G39">
-        <v>0.1668367104873381</v>
+        <v>0.1527434068648266</v>
       </c>
       <c r="H39">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1">
-        <v>46164</v>
+        <v>46161</v>
       </c>
       <c r="B40" t="s">
         <v>11</v>
       </c>
       <c r="C40">
-        <v>35.75514940724808</v>
+        <v>36.01040085730018</v>
       </c>
       <c r="D40">
-        <v>22.28880693466429</v>
+        <v>22.19475589056387</v>
       </c>
       <c r="E40">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="F40">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="G40">
-        <v>0.1717848261904962</v>
+        <v>0.1456396418594061</v>
       </c>
       <c r="H40">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1">
-        <v>46167</v>
+        <v>46162</v>
       </c>
       <c r="B41" t="s">
         <v>11</v>
       </c>
       <c r="C41">
-        <v>35.84133099010302</v>
+        <v>36.45290912796982</v>
       </c>
       <c r="D41">
-        <v>22.37458514769363</v>
+        <v>22.46357594746874</v>
       </c>
       <c r="E41">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="F41">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="G41">
-        <v>0.1717848261904962</v>
+        <v>0.1646157747240327</v>
       </c>
       <c r="H41">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1">
-        <v>46168</v>
+        <v>46163</v>
       </c>
       <c r="B42" t="s">
         <v>11</v>
       </c>
       <c r="C42">
-        <v>36.23214279739292</v>
+        <v>35.75282090566891</v>
       </c>
       <c r="D42">
-        <v>22.93484792820123</v>
+        <v>22.57615417310648</v>
       </c>
       <c r="E42">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
       <c r="F42">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
       <c r="G42">
-        <v>0.1925900763781823</v>
+        <v>0.1668367104873381</v>
       </c>
       <c r="H42">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1">
-        <v>46153</v>
+        <v>46164</v>
       </c>
       <c r="B43" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C43">
-        <v>52.70832779833182</v>
+        <v>35.75514940724808</v>
       </c>
       <c r="D43">
-        <v>23.99044674439659</v>
+        <v>22.28880693466429</v>
       </c>
       <c r="E43">
-        <v>0.9994000000000002</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="F43">
-        <v>0.9994000000000002</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="G43">
-        <v>0.5438253854918791</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H43">
-        <v>0.9994000000000002</v>
+        <v>0.9992573500000002</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1">
-        <v>46154</v>
+        <v>46167</v>
       </c>
       <c r="B44" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C44">
-        <v>50.89464485280568</v>
+        <v>35.84133099010302</v>
       </c>
       <c r="D44">
-        <v>23.21558303176282</v>
+        <v>22.37458514769363</v>
       </c>
       <c r="E44">
-        <v>0.9996</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="F44">
-        <v>0.9996</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="G44">
-        <v>0.5034825029548833</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H44">
-        <v>0.9996</v>
+        <v>0.9992609200000001</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1">
-        <v>46155</v>
+        <v>46168</v>
       </c>
       <c r="B45" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C45">
-        <v>51.8659994471731</v>
+        <v>36.23214279739292</v>
       </c>
       <c r="D45">
-        <v>23.7009037279043</v>
+        <v>22.93484792820123</v>
       </c>
       <c r="E45">
-        <v>1.0002</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="F45">
-        <v>1.0002</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="G45">
-        <v>0.533512029714132</v>
+        <v>0.1925900763781823</v>
       </c>
       <c r="H45">
-        <v>1.0002</v>
+        <v>0.9992609200000001</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1">
-        <v>46156</v>
+        <v>46169</v>
       </c>
       <c r="B46" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C46">
-        <v>52.4470179952828</v>
+        <v>36.4336692499184</v>
       </c>
       <c r="D46">
-        <v>23.76861704536814</v>
+        <v>22.75940954009856</v>
       </c>
       <c r="E46">
-        <v>0.9998</v>
+        <v>0.9992099400000001</v>
       </c>
       <c r="F46">
-        <v>0.9998</v>
+        <v>0.9992099400000001</v>
       </c>
       <c r="G46">
-        <v>0.5492634496849078</v>
+        <v>0.1912346098381414</v>
       </c>
       <c r="H46">
-        <v>0.9998</v>
+        <v>0.9992099400000001</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="B47" t="s">
         <v>12</v>
       </c>
       <c r="C47">
-        <v>50.81077380018606</v>
+        <v>52.70832779833182</v>
       </c>
       <c r="D47">
-        <v>22.76900580927995</v>
+        <v>23.99044674439659</v>
       </c>
       <c r="E47">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="F47">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="G47">
-        <v>0.4903296143797722</v>
+        <v>0.5438253854918791</v>
       </c>
       <c r="H47">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1">
-        <v>46160</v>
+        <v>46154</v>
       </c>
       <c r="B48" t="s">
         <v>12</v>
       </c>
       <c r="C48">
-        <v>49.50286387149169</v>
+        <v>50.89464485280568</v>
       </c>
       <c r="D48">
-        <v>22.24532119914133</v>
+        <v>23.21558303176282</v>
       </c>
       <c r="E48">
         <v>0.9996</v>
@@ -1645,7 +1645,7 @@
         <v>0.9996</v>
       </c>
       <c r="G48">
-        <v>0.4630591776162345</v>
+        <v>0.5034825029548833</v>
       </c>
       <c r="H48">
         <v>0.9996</v>
@@ -1653,1030 +1653,1030 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1">
-        <v>46161</v>
+        <v>46155</v>
       </c>
       <c r="B49" t="s">
         <v>12</v>
       </c>
       <c r="C49">
-        <v>49.29146729279496</v>
+        <v>51.8659994471731</v>
       </c>
       <c r="D49">
-        <v>22.22167836589682</v>
+        <v>23.7009037279043</v>
       </c>
       <c r="E49">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="F49">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="G49">
-        <v>0.4571659248870246</v>
+        <v>0.533512029714132</v>
       </c>
       <c r="H49">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1">
-        <v>46162</v>
+        <v>46156</v>
       </c>
       <c r="B50" t="s">
         <v>12</v>
       </c>
       <c r="C50">
-        <v>50.88652370817657</v>
+        <v>52.4470179952828</v>
       </c>
       <c r="D50">
-        <v>22.93254398967657</v>
+        <v>23.76861704536814</v>
       </c>
       <c r="E50">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F50">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G50">
-        <v>0.5126171754864624</v>
+        <v>0.5492634496849078</v>
       </c>
       <c r="H50">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1">
-        <v>46163</v>
+        <v>46157</v>
       </c>
       <c r="B51" t="s">
         <v>12</v>
       </c>
       <c r="C51">
-        <v>48.26646764818586</v>
+        <v>50.81077380018606</v>
       </c>
       <c r="D51">
-        <v>23.11655387625012</v>
+        <v>22.76900580927995</v>
       </c>
       <c r="E51">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="F51">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="G51">
-        <v>0.521243030947425</v>
+        <v>0.4903296143797722</v>
       </c>
       <c r="H51">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1">
-        <v>46164</v>
+        <v>46160</v>
       </c>
       <c r="B52" t="s">
         <v>12</v>
       </c>
       <c r="C52">
-        <v>48.84737503703267</v>
+        <v>49.50286387149169</v>
       </c>
       <c r="D52">
-        <v>22.83557604744466</v>
+        <v>22.24532119914133</v>
       </c>
       <c r="E52">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="F52">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="G52">
-        <v>0.5438521997590966</v>
+        <v>0.4630591776162345</v>
       </c>
       <c r="H52">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1">
-        <v>46167</v>
+        <v>46161</v>
       </c>
       <c r="B53" t="s">
         <v>12</v>
       </c>
       <c r="C53">
-        <v>48.85151560750146</v>
+        <v>49.29146729279496</v>
       </c>
       <c r="D53">
-        <v>22.83513820206554</v>
+        <v>22.22167836589682</v>
       </c>
       <c r="E53">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F53">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G53">
-        <v>0.5438521997590966</v>
+        <v>0.4571659248870246</v>
       </c>
       <c r="H53">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1">
-        <v>46168</v>
+        <v>46162</v>
       </c>
       <c r="B54" t="s">
         <v>12</v>
       </c>
       <c r="C54">
-        <v>50.90437883274981</v>
+        <v>50.88652370817657</v>
       </c>
       <c r="D54">
-        <v>24.25672473501501</v>
+        <v>22.93254398967657</v>
       </c>
       <c r="E54">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F54">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G54">
-        <v>0.6130191115419561</v>
+        <v>0.5126171754864624</v>
       </c>
       <c r="H54">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1">
-        <v>46153</v>
+        <v>46163</v>
       </c>
       <c r="B55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C55">
-        <v>57.1732166855686</v>
+        <v>48.26646764818586</v>
       </c>
       <c r="D55">
-        <v>23.50022751267814</v>
+        <v>23.11655387625012</v>
       </c>
       <c r="E55">
-        <v>0.9991</v>
+        <v>0.9999</v>
       </c>
       <c r="F55">
-        <v>0.9991</v>
+        <v>0.9999</v>
       </c>
       <c r="G55">
-        <v>0.6994110097039083</v>
+        <v>0.521243030947425</v>
       </c>
       <c r="H55">
-        <v>0.9991</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1">
-        <v>46154</v>
+        <v>46164</v>
       </c>
       <c r="B56" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C56">
-        <v>54.77380642078597</v>
+        <v>48.84737503703267</v>
       </c>
       <c r="D56">
-        <v>22.55192940254518</v>
+        <v>22.83557604744466</v>
       </c>
       <c r="E56">
-        <v>0.9990000000000001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F56">
-        <v>0.9990000000000001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G56">
-        <v>0.6459175880844941</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H56">
-        <v>0.9990000000000001</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1">
-        <v>46155</v>
+        <v>46167</v>
       </c>
       <c r="B57" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C57">
-        <v>56.32187380830906</v>
+        <v>48.85151560750146</v>
       </c>
       <c r="D57">
-        <v>23.17121437414109</v>
+        <v>22.83513820206554</v>
       </c>
       <c r="E57">
-        <v>0.9990000000000001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F57">
-        <v>0.9990000000000001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G57">
-        <v>0.6851523922954754</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H57">
-        <v>0.9990000000000001</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1">
-        <v>46156</v>
+        <v>46168</v>
       </c>
       <c r="B58" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C58">
-        <v>56.15321618553139</v>
+        <v>50.90437883274981</v>
       </c>
       <c r="D58">
-        <v>22.95838347314443</v>
+        <v>24.25672473501501</v>
       </c>
       <c r="E58">
-        <v>0.9992</v>
+        <v>0.9996999999999999</v>
       </c>
       <c r="F58">
-        <v>0.9992</v>
+        <v>0.9996999999999999</v>
       </c>
       <c r="G58">
-        <v>0.6907028507208208</v>
+        <v>0.6130191115419561</v>
       </c>
       <c r="H58">
-        <v>0.9992</v>
+        <v>0.9996999999999999</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1">
-        <v>46157</v>
+        <v>46169</v>
       </c>
       <c r="B59" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C59">
-        <v>54.47755813049488</v>
+        <v>50.47312432255841</v>
       </c>
       <c r="D59">
-        <v>22.0083816089626</v>
+        <v>23.84499305142194</v>
       </c>
       <c r="E59">
-        <v>0.9986</v>
+        <v>0.9998</v>
       </c>
       <c r="F59">
-        <v>0.9986</v>
+        <v>0.9998</v>
       </c>
       <c r="G59">
-        <v>0.6220895940829376</v>
+        <v>0.5952317692821967</v>
       </c>
       <c r="H59">
-        <v>0.9986</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
       </c>
       <c r="C60">
-        <v>52.6278781150669</v>
+        <v>57.1732166855686</v>
       </c>
       <c r="D60">
-        <v>21.5357353870778</v>
+        <v>23.50022751267814</v>
       </c>
       <c r="E60">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F60">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G60">
-        <v>0.5845134636435627</v>
+        <v>0.6994110097039083</v>
       </c>
       <c r="H60">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
       </c>
       <c r="C61">
-        <v>54.91583234840245</v>
+        <v>54.77380642078597</v>
       </c>
       <c r="D61">
-        <v>22.38321645985006</v>
+        <v>22.55192940254518</v>
       </c>
       <c r="E61">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F61">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G61">
-        <v>0.6596976539194066</v>
+        <v>0.6459175880844941</v>
       </c>
       <c r="H61">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
       </c>
       <c r="C62">
-        <v>53.91712298548793</v>
+        <v>56.32187380830906</v>
       </c>
       <c r="D62">
-        <v>22.73711181201267</v>
+        <v>23.17121437414109</v>
       </c>
       <c r="E62">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F62">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G62">
-        <v>0.6737329602396263</v>
+        <v>0.6851523922954754</v>
       </c>
       <c r="H62">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
       </c>
       <c r="C63">
-        <v>55.19651747515625</v>
+        <v>56.15321618553139</v>
       </c>
       <c r="D63">
-        <v>22.79462037330554</v>
+        <v>22.95838347314443</v>
       </c>
       <c r="E63">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
       <c r="F63">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
       <c r="G63">
-        <v>0.7139885317003913</v>
+        <v>0.6907028507208208</v>
       </c>
       <c r="H63">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
       </c>
       <c r="C64">
-        <v>55.28054997487197</v>
+        <v>54.47755813049488</v>
       </c>
       <c r="D64">
-        <v>23.00160891539877</v>
+        <v>22.0083816089626</v>
       </c>
       <c r="E64">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="F64">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="G64">
-        <v>0.7139885317003913</v>
+        <v>0.6220895940829376</v>
       </c>
       <c r="H64">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1">
-        <v>46168</v>
+        <v>46161</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
       </c>
       <c r="C65">
-        <v>58.75156728873073</v>
+        <v>52.6278781150669</v>
       </c>
       <c r="D65">
-        <v>24.84249654093248</v>
+        <v>21.5357353870778</v>
       </c>
       <c r="E65">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="F65">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="G65">
-        <v>0.8184872182632257</v>
+        <v>0.5845134636435627</v>
       </c>
       <c r="H65">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1">
-        <v>46153</v>
+        <v>46162</v>
       </c>
       <c r="B66" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C66">
-        <v>35.78646526282436</v>
+        <v>54.91583234840245</v>
       </c>
       <c r="D66">
-        <v>18.96635091925032</v>
+        <v>22.38321645985006</v>
       </c>
       <c r="E66">
-        <v>0.9996491399999999</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="F66">
-        <v>0.9996491399999999</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="G66">
-        <v>0.2240600969213613</v>
+        <v>0.6596976539194066</v>
       </c>
       <c r="H66">
-        <v>0.9985614899999999</v>
+        <v>0.9990999999999999</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1">
-        <v>46154</v>
+        <v>46163</v>
       </c>
       <c r="B67" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C67">
-        <v>35.71584102184062</v>
+        <v>53.91712298548793</v>
       </c>
       <c r="D67">
-        <v>18.62432950231353</v>
+        <v>22.73711181201267</v>
       </c>
       <c r="E67">
-        <v>0.99965481</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="F67">
-        <v>0.99965481</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="G67">
-        <v>0.2104844827747143</v>
+        <v>0.6737329602396263</v>
       </c>
       <c r="H67">
-        <v>0.9985622199999999</v>
+        <v>0.9991999999999999</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1">
-        <v>46155</v>
+        <v>46164</v>
       </c>
       <c r="B68" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C68">
-        <v>35.95182028203252</v>
+        <v>55.19651747515625</v>
       </c>
       <c r="D68">
-        <v>18.95670796791552</v>
+        <v>22.79462037330554</v>
       </c>
       <c r="E68">
-        <v>0.9996515200000001</v>
+        <v>0.9991</v>
       </c>
       <c r="F68">
-        <v>0.9996515200000001</v>
+        <v>0.9991</v>
       </c>
       <c r="G68">
-        <v>0.2259035693959275</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H68">
-        <v>0.99855193</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1">
-        <v>46156</v>
+        <v>46167</v>
       </c>
       <c r="B69" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C69">
-        <v>36.14451597805883</v>
+        <v>55.28054997487197</v>
       </c>
       <c r="D69">
-        <v>18.86297660538653</v>
+        <v>23.00160891539877</v>
       </c>
       <c r="E69">
-        <v>0.9996563399999999</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="F69">
-        <v>0.9996563399999999</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="G69">
-        <v>0.2362110061840785</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H69">
-        <v>0.99857265</v>
+        <v>0.9989000000000001</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1">
-        <v>46157</v>
+        <v>46168</v>
       </c>
       <c r="B70" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C70">
-        <v>35.32805803135546</v>
+        <v>58.75156728873073</v>
       </c>
       <c r="D70">
-        <v>18.35643242381478</v>
+        <v>24.84249654093248</v>
       </c>
       <c r="E70">
-        <v>0.9997415800000001</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="F70">
-        <v>0.9997415800000001</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="G70">
-        <v>0.2023559161375383</v>
+        <v>0.8184872182632257</v>
       </c>
       <c r="H70">
-        <v>0.9986639900000002</v>
+        <v>0.9989000000000001</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1">
-        <v>46160</v>
+        <v>46169</v>
       </c>
       <c r="B71" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C71">
-        <v>34.83995455757461</v>
+        <v>57.86771234337395</v>
       </c>
       <c r="D71">
-        <v>18.02301281718857</v>
+        <v>24.21066615243091</v>
       </c>
       <c r="E71">
-        <v>0.9996851299999999</v>
+        <v>0.9986999999999999</v>
       </c>
       <c r="F71">
-        <v>0.9996851299999999</v>
+        <v>0.9986999999999999</v>
       </c>
       <c r="G71">
-        <v>0.1850932291737926</v>
+        <v>0.798997241708943</v>
       </c>
       <c r="H71">
-        <v>0.99857724</v>
+        <v>0.9986999999999999</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B72" t="s">
         <v>14</v>
       </c>
       <c r="C72">
-        <v>34.45479308705605</v>
+        <v>35.78646526282436</v>
       </c>
       <c r="D72">
-        <v>18.09576834566068</v>
+        <v>18.96635091925032</v>
       </c>
       <c r="E72">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="F72">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="G72">
-        <v>0.1784731209386736</v>
+        <v>0.2240600969213613</v>
       </c>
       <c r="H72">
-        <v>0.9985337599999999</v>
+        <v>0.9985614899999999</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B73" t="s">
         <v>14</v>
       </c>
       <c r="C73">
-        <v>34.96336277390787</v>
+        <v>35.71584102184062</v>
       </c>
       <c r="D73">
-        <v>18.34938420029253</v>
+        <v>18.62432950231353</v>
       </c>
       <c r="E73">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="F73">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="G73">
-        <v>0.2009313391215752</v>
+        <v>0.2104844827747143</v>
       </c>
       <c r="H73">
-        <v>0.99848777</v>
+        <v>0.9985622199999999</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B74" t="s">
         <v>14</v>
       </c>
       <c r="C74">
-        <v>34.44616924817128</v>
+        <v>35.95182028203252</v>
       </c>
       <c r="D74">
-        <v>18.60085625074367</v>
+        <v>18.95670796791552</v>
       </c>
       <c r="E74">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="F74">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="G74">
-        <v>0.2124957180214682</v>
+        <v>0.2259035693959275</v>
       </c>
       <c r="H74">
-        <v>0.9985085200000001</v>
+        <v>0.99855193</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="B75" t="s">
         <v>14</v>
       </c>
       <c r="C75">
-        <v>34.62137220937314</v>
+        <v>36.14451597805883</v>
       </c>
       <c r="D75">
-        <v>18.28780484745949</v>
+        <v>18.86297660538653</v>
       </c>
       <c r="E75">
-        <v>0.9996106299999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="F75">
-        <v>0.9996106299999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="G75">
-        <v>0.2145907067863493</v>
+        <v>0.2362110061840785</v>
       </c>
       <c r="H75">
-        <v>0.9932939299999999</v>
+        <v>0.99857265</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="B76" t="s">
         <v>14</v>
       </c>
       <c r="C76">
-        <v>34.6540695486741</v>
+        <v>35.32805803135546</v>
       </c>
       <c r="D76">
-        <v>18.36409048915342</v>
+        <v>18.35643242381478</v>
       </c>
       <c r="E76">
-        <v>0.9995448900000001</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="F76">
-        <v>0.9995448900000001</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="G76">
-        <v>0.2145907067863493</v>
+        <v>0.2023559161375383</v>
       </c>
       <c r="H76">
-        <v>0.9984302600000001</v>
+        <v>0.9986639900000002</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1">
-        <v>46168</v>
+        <v>46160</v>
       </c>
       <c r="B77" t="s">
         <v>14</v>
       </c>
       <c r="C77">
-        <v>35.4820130509417</v>
+        <v>34.83995455757461</v>
       </c>
       <c r="D77">
-        <v>19.20292041814603</v>
+        <v>18.02301281718857</v>
       </c>
       <c r="E77">
-        <v>0.9995448900000001</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="F77">
-        <v>0.9995448900000001</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="G77">
-        <v>0.2553172934903569</v>
+        <v>0.1850932291737926</v>
       </c>
       <c r="H77">
-        <v>0.9984302600000001</v>
+        <v>0.99857724</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="1">
-        <v>46153</v>
+        <v>46161</v>
       </c>
       <c r="B78" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C78">
-        <v>28.12253390077671</v>
+        <v>34.45479308705605</v>
       </c>
       <c r="D78">
-        <v>23.58699683751922</v>
+        <v>18.09576834566068</v>
       </c>
       <c r="E78">
-        <v>0.9997295369999999</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="F78">
-        <v>0.9997295369999999</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="G78">
-        <v>0.03368732240295347</v>
+        <v>0.1784731209386736</v>
       </c>
       <c r="H78">
-        <v>0.9997295369999999</v>
+        <v>0.9985337599999999</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1">
-        <v>46154</v>
+        <v>46162</v>
       </c>
       <c r="B79" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C79">
-        <v>28.17715727830483</v>
+        <v>34.96336277390787</v>
       </c>
       <c r="D79">
-        <v>23.63894513078866</v>
+        <v>18.34938420029253</v>
       </c>
       <c r="E79">
-        <v>1.000319473</v>
+        <v>0.99963413</v>
       </c>
       <c r="F79">
-        <v>1.000319473</v>
+        <v>0.99963413</v>
       </c>
       <c r="G79">
-        <v>0.03515547182056333</v>
+        <v>0.2009313391215752</v>
       </c>
       <c r="H79">
-        <v>1.000319473</v>
+        <v>0.99848777</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1">
-        <v>46155</v>
+        <v>46163</v>
       </c>
       <c r="B80" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C80">
-        <v>28.59002627414054</v>
+        <v>34.44616924817128</v>
       </c>
       <c r="D80">
-        <v>23.96230704059692</v>
+        <v>18.60085625074367</v>
       </c>
       <c r="E80">
-        <v>0.9999999989999999</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="F80">
-        <v>0.9999999989999999</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="G80">
-        <v>0.05179637495949674</v>
+        <v>0.2124957180214682</v>
       </c>
       <c r="H80">
-        <v>0.9999999989999999</v>
+        <v>0.9985085200000001</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="1">
-        <v>46156</v>
+        <v>46164</v>
       </c>
       <c r="B81" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C81">
-        <v>28.56217859389523</v>
+        <v>34.62137220937314</v>
       </c>
       <c r="D81">
-        <v>23.9411987302529</v>
+        <v>18.28780484745949</v>
       </c>
       <c r="E81">
-        <v>1</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="F81">
-        <v>1</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="G81">
-        <v>0.04837024516756849</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H81">
-        <v>1</v>
+        <v>0.9932939299999999</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="1">
-        <v>46157</v>
+        <v>46167</v>
       </c>
       <c r="B82" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C82">
-        <v>28.57618675936338</v>
+        <v>34.6540695486741</v>
       </c>
       <c r="D82">
-        <v>23.9576220541054</v>
+        <v>18.36409048915342</v>
       </c>
       <c r="E82">
-        <v>0.999503249</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="F82">
-        <v>0.999503249</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="G82">
-        <v>0.04983868243960732</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H82">
-        <v>0.999503249</v>
+        <v>0.9984302600000001</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="1">
-        <v>46160</v>
+        <v>46168</v>
       </c>
       <c r="B83" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C83">
-        <v>28.68951918518517</v>
+        <v>35.4820130509417</v>
       </c>
       <c r="D83">
-        <v>24.06134728453882</v>
+        <v>19.20292041814603</v>
       </c>
       <c r="E83">
-        <v>0.999503249</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="F83">
-        <v>0.999503249</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="G83">
-        <v>0.04983868243960732</v>
+        <v>0.2553172934903569</v>
       </c>
       <c r="H83">
-        <v>0.999503249</v>
+        <v>0.9984302600000001</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="1">
-        <v>46161</v>
+        <v>46169</v>
       </c>
       <c r="B84" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C84">
-        <v>28.31167386654059</v>
+        <v>35.71913468603401</v>
       </c>
       <c r="D84">
-        <v>23.75157719455474</v>
+        <v>18.96318693998171</v>
       </c>
       <c r="E84">
-        <v>1.000177331</v>
+        <v>0.99955466</v>
       </c>
       <c r="F84">
-        <v>1.000177331</v>
+        <v>0.99955466</v>
       </c>
       <c r="G84">
-        <v>0.04053938625111919</v>
+        <v>0.2536413280520453</v>
       </c>
       <c r="H84">
-        <v>1.000177331</v>
+        <v>0.9984700500000001</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1">
-        <v>46162</v>
+        <v>46153</v>
       </c>
       <c r="B85" t="s">
         <v>15</v>
       </c>
       <c r="C85">
-        <v>28.57911382310097</v>
+        <v>28.12253390077671</v>
       </c>
       <c r="D85">
-        <v>23.89431741541233</v>
+        <v>23.58699683751922</v>
       </c>
       <c r="E85">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="F85">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="G85">
-        <v>0.04690190590044785</v>
+        <v>0.03368732240295347</v>
       </c>
       <c r="H85">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="1">
-        <v>46163</v>
+        <v>46154</v>
       </c>
       <c r="B86" t="s">
         <v>15</v>
       </c>
       <c r="C86">
-        <v>28.55785065378643</v>
+        <v>28.17715727830483</v>
       </c>
       <c r="D86">
-        <v>24.04274714970193</v>
+        <v>23.63894513078866</v>
       </c>
       <c r="E86">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="F86">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="G86">
-        <v>0.05228572319419666</v>
+        <v>0.03515547182056333</v>
       </c>
       <c r="H86">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="1">
-        <v>46164</v>
+        <v>46155</v>
       </c>
       <c r="B87" t="s">
         <v>15</v>
       </c>
       <c r="C87">
-        <v>28.50194638163107</v>
+        <v>28.59002627414054</v>
       </c>
       <c r="D87">
-        <v>23.99272397156045</v>
+        <v>23.96230704059692</v>
       </c>
       <c r="E87">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F87">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G87">
-        <v>0.04934923597154284</v>
+        <v>0.05179637495949674</v>
       </c>
       <c r="H87">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1">
-        <v>46167</v>
+        <v>46156</v>
       </c>
       <c r="B88" t="s">
         <v>15</v>
       </c>
       <c r="C88">
-        <v>28.55106858744498</v>
+        <v>28.56217859389523</v>
       </c>
       <c r="D88">
-        <v>23.9768329565351</v>
+        <v>23.9411987302529</v>
       </c>
       <c r="E88">
         <v>1</v>
@@ -2685,7 +2685,7 @@
         <v>1</v>
       </c>
       <c r="G88">
-        <v>0.05571185335164408</v>
+        <v>0.04837024516756849</v>
       </c>
       <c r="H88">
         <v>1</v>
@@ -2693,340 +2693,574 @@
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="1">
-        <v>46168</v>
+        <v>46157</v>
       </c>
       <c r="B89" t="s">
         <v>15</v>
       </c>
       <c r="C89">
-        <v>28.54681541456266</v>
+        <v>28.57618675936338</v>
       </c>
       <c r="D89">
-        <v>23.97386168967948</v>
+        <v>23.9576220541054</v>
       </c>
       <c r="E89">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="F89">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="G89">
-        <v>0.04837034303541388</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H89">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="B90" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C90">
-        <v>40.68830633303975</v>
+        <v>28.68951918518517</v>
       </c>
       <c r="D90">
-        <v>21.50431773660198</v>
+        <v>24.06134728453882</v>
       </c>
       <c r="E90">
-        <v>0.99909852</v>
+        <v>0.999503249</v>
       </c>
       <c r="F90">
-        <v>0.99909852</v>
+        <v>0.999503249</v>
       </c>
       <c r="G90">
-        <v>0.2342423866086769</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H90">
-        <v>0.9974930900000001</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="1">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="B91" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C91">
-        <v>40.32854894972581</v>
+        <v>28.31167386654059</v>
       </c>
       <c r="D91">
-        <v>21.09133998298594</v>
+        <v>23.75157719455474</v>
       </c>
       <c r="E91">
-        <v>0.9990972199999999</v>
+        <v>1.000177331</v>
       </c>
       <c r="F91">
-        <v>0.9990972199999999</v>
+        <v>1.000177331</v>
       </c>
       <c r="G91">
-        <v>0.2156468205051487</v>
+        <v>0.04053938625111919</v>
       </c>
       <c r="H91">
-        <v>0.99752223</v>
+        <v>1.000177331</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="1">
-        <v>46155</v>
+        <v>46162</v>
       </c>
       <c r="B92" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C92">
-        <v>40.47987921095815</v>
+        <v>28.57911382310097</v>
       </c>
       <c r="D92">
-        <v>21.35995364434454</v>
+        <v>23.89431741541233</v>
       </c>
       <c r="E92">
-        <v>0.9991780100000001</v>
+        <v>0.999503734</v>
       </c>
       <c r="F92">
-        <v>0.9991780100000001</v>
+        <v>0.999503734</v>
       </c>
       <c r="G92">
-        <v>0.2270956128473374</v>
+        <v>0.04690190590044785</v>
       </c>
       <c r="H92">
-        <v>0.9975825700000001</v>
+        <v>0.999503734</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="1">
-        <v>46156</v>
+        <v>46163</v>
       </c>
       <c r="B93" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C93">
-        <v>41.20436574895244</v>
+        <v>28.55785065378643</v>
       </c>
       <c r="D93">
-        <v>21.48149674387778</v>
+        <v>24.04274714970193</v>
       </c>
       <c r="E93">
-        <v>0.9991793299999999</v>
+        <v>1.000229282</v>
       </c>
       <c r="F93">
-        <v>0.9991793299999999</v>
+        <v>1.000229282</v>
       </c>
       <c r="G93">
-        <v>0.2454829228401052</v>
+        <v>0.05228572319419666</v>
       </c>
       <c r="H93">
-        <v>0.99754722</v>
+        <v>1.000229282</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="1">
-        <v>46157</v>
+        <v>46164</v>
       </c>
       <c r="B94" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C94">
-        <v>40.80613062958688</v>
+        <v>28.50194638163107</v>
       </c>
       <c r="D94">
-        <v>21.08912555803936</v>
+        <v>23.99272397156045</v>
       </c>
       <c r="E94">
-        <v>0.9991790600000001</v>
+        <v>1</v>
       </c>
       <c r="F94">
-        <v>0.9991790600000001</v>
+        <v>1</v>
       </c>
       <c r="G94">
-        <v>0.2230017445022556</v>
+        <v>0.04934923597154284</v>
       </c>
       <c r="H94">
-        <v>0.9975824700000002</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="1">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="B95" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C95">
-        <v>40.11672876026724</v>
+        <v>28.55106858744498</v>
       </c>
       <c r="D95">
-        <v>20.79541439916316</v>
+        <v>23.9768329565351</v>
       </c>
       <c r="E95">
-        <v>0.999152</v>
+        <v>1</v>
       </c>
       <c r="F95">
-        <v>0.999152</v>
+        <v>1</v>
       </c>
       <c r="G95">
-        <v>0.2098184021536666</v>
+        <v>0.05571185335164408</v>
       </c>
       <c r="H95">
-        <v>0.9975007899999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="1">
-        <v>46161</v>
+        <v>46168</v>
       </c>
       <c r="B96" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C96">
-        <v>39.69086941528401</v>
+        <v>28.54681541456266</v>
       </c>
       <c r="D96">
-        <v>20.74924328599426</v>
+        <v>23.97386168967948</v>
       </c>
       <c r="E96">
-        <v>0.99914989</v>
+        <v>1</v>
       </c>
       <c r="F96">
-        <v>0.99914989</v>
+        <v>1</v>
       </c>
       <c r="G96">
-        <v>0.2020471776850241</v>
+        <v>0.04837034303541388</v>
       </c>
       <c r="H96">
-        <v>0.9974417</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="1">
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="B97" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C97">
-        <v>40.37836787855562</v>
+        <v>28.83672936868491</v>
       </c>
       <c r="D97">
-        <v>21.11271132314188</v>
+        <v>24.203511281145</v>
       </c>
       <c r="E97">
-        <v>0.99915058</v>
+        <v>1</v>
       </c>
       <c r="F97">
-        <v>0.99915058</v>
+        <v>1</v>
       </c>
       <c r="G97">
-        <v>0.2291077670847563</v>
+        <v>0.05962723282507953</v>
       </c>
       <c r="H97">
-        <v>0.9974415600000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="1">
-        <v>46163</v>
+        <v>46153</v>
       </c>
       <c r="B98" t="s">
         <v>16</v>
       </c>
       <c r="C98">
-        <v>38.9123066967842</v>
+        <v>40.68830633303975</v>
       </c>
       <c r="D98">
-        <v>21.28910644207464</v>
+        <v>21.50431773660198</v>
       </c>
       <c r="E98">
-        <v>0.9989350699999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="F98">
-        <v>0.9989350699999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="G98">
-        <v>0.2392382040170877</v>
+        <v>0.2342423866086769</v>
       </c>
       <c r="H98">
-        <v>0.99726191</v>
+        <v>0.9974930900000001</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="1">
-        <v>46164</v>
+        <v>46154</v>
       </c>
       <c r="B99" t="s">
         <v>16</v>
       </c>
       <c r="C99">
-        <v>39.43913909150694</v>
+        <v>40.32854894972581</v>
       </c>
       <c r="D99">
-        <v>21.05297617141148</v>
+        <v>21.09133998298594</v>
       </c>
       <c r="E99">
-        <v>0.999144</v>
+        <v>0.9990972199999999</v>
       </c>
       <c r="F99">
-        <v>0.999144</v>
+        <v>0.9990972199999999</v>
       </c>
       <c r="G99">
-        <v>0.2516582935428642</v>
+        <v>0.2156468205051487</v>
       </c>
       <c r="H99">
-        <v>0.9974678400000001</v>
+        <v>0.99752223</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="1">
-        <v>46167</v>
+        <v>46155</v>
       </c>
       <c r="B100" t="s">
         <v>16</v>
       </c>
       <c r="C100">
-        <v>39.45782844313628</v>
+        <v>40.47987921095815</v>
       </c>
       <c r="D100">
-        <v>21.0518901572272</v>
+        <v>21.35995364434454</v>
       </c>
       <c r="E100">
-        <v>0.999144</v>
+        <v>0.9991780100000001</v>
       </c>
       <c r="F100">
-        <v>0.999144</v>
+        <v>0.9991780100000001</v>
       </c>
       <c r="G100">
-        <v>0.2516582935428642</v>
+        <v>0.2270956128473374</v>
       </c>
       <c r="H100">
-        <v>0.9974678400000001</v>
+        <v>0.9975825700000001</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="1">
-        <v>46168</v>
+        <v>46156</v>
       </c>
       <c r="B101" t="s">
         <v>16</v>
       </c>
       <c r="C101">
+        <v>41.20436574895244</v>
+      </c>
+      <c r="D101">
+        <v>21.48149674387778</v>
+      </c>
+      <c r="E101">
+        <v>0.9991793299999999</v>
+      </c>
+      <c r="F101">
+        <v>0.9991793299999999</v>
+      </c>
+      <c r="G101">
+        <v>0.2454829228401052</v>
+      </c>
+      <c r="H101">
+        <v>0.99754722</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102">
+        <v>40.80613062958688</v>
+      </c>
+      <c r="D102">
+        <v>21.08912555803936</v>
+      </c>
+      <c r="E102">
+        <v>0.9991790600000001</v>
+      </c>
+      <c r="F102">
+        <v>0.9991790600000001</v>
+      </c>
+      <c r="G102">
+        <v>0.2230017445022556</v>
+      </c>
+      <c r="H102">
+        <v>0.9975824700000002</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103">
+        <v>40.11672876026724</v>
+      </c>
+      <c r="D103">
+        <v>20.79541439916316</v>
+      </c>
+      <c r="E103">
+        <v>0.999152</v>
+      </c>
+      <c r="F103">
+        <v>0.999152</v>
+      </c>
+      <c r="G103">
+        <v>0.2098184021536666</v>
+      </c>
+      <c r="H103">
+        <v>0.9975007899999999</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104">
+        <v>39.69086941528401</v>
+      </c>
+      <c r="D104">
+        <v>20.74924328599426</v>
+      </c>
+      <c r="E104">
+        <v>0.99914989</v>
+      </c>
+      <c r="F104">
+        <v>0.99914989</v>
+      </c>
+      <c r="G104">
+        <v>0.2020471776850241</v>
+      </c>
+      <c r="H104">
+        <v>0.9974417</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105">
+        <v>40.37836787855562</v>
+      </c>
+      <c r="D105">
+        <v>21.11271132314188</v>
+      </c>
+      <c r="E105">
+        <v>0.99915058</v>
+      </c>
+      <c r="F105">
+        <v>0.99915058</v>
+      </c>
+      <c r="G105">
+        <v>0.2291077670847563</v>
+      </c>
+      <c r="H105">
+        <v>0.9974415600000001</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106">
+        <v>38.9123066967842</v>
+      </c>
+      <c r="D106">
+        <v>21.28910644207464</v>
+      </c>
+      <c r="E106">
+        <v>0.9989350699999999</v>
+      </c>
+      <c r="F106">
+        <v>0.9989350699999999</v>
+      </c>
+      <c r="G106">
+        <v>0.2392382040170877</v>
+      </c>
+      <c r="H106">
+        <v>0.99726191</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" s="1">
+        <v>46164</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107">
+        <v>39.43913909150694</v>
+      </c>
+      <c r="D107">
+        <v>21.05297617141148</v>
+      </c>
+      <c r="E107">
+        <v>0.999144</v>
+      </c>
+      <c r="F107">
+        <v>0.999144</v>
+      </c>
+      <c r="G107">
+        <v>0.2516582935428642</v>
+      </c>
+      <c r="H107">
+        <v>0.9974678400000001</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108">
+        <v>39.45782844313628</v>
+      </c>
+      <c r="D108">
+        <v>21.0518901572272</v>
+      </c>
+      <c r="E108">
+        <v>0.999144</v>
+      </c>
+      <c r="F108">
+        <v>0.999144</v>
+      </c>
+      <c r="G108">
+        <v>0.2516582935428642</v>
+      </c>
+      <c r="H108">
+        <v>0.9974678400000001</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109">
         <v>40.20219297984542</v>
       </c>
-      <c r="D101">
+      <c r="D109">
         <v>21.93106024403281</v>
       </c>
-      <c r="E101">
+      <c r="E109">
         <v>0.9991421799999999</v>
       </c>
-      <c r="F101">
+      <c r="F109">
         <v>0.9991421799999999</v>
       </c>
-      <c r="G101">
+      <c r="G109">
         <v>0.2846167552893293</v>
       </c>
-      <c r="H101">
+      <c r="H109">
         <v>0.9974609800000001</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110">
+        <v>40.34993865302093</v>
+      </c>
+      <c r="D110">
+        <v>21.65366031776487</v>
+      </c>
+      <c r="E110">
+        <v>0.9991434600000001</v>
+      </c>
+      <c r="F110">
+        <v>0.9991434600000001</v>
+      </c>
+      <c r="G110">
+        <v>0.2796902860011767</v>
+      </c>
+      <c r="H110">
+        <v>0.9991434600000001</v>
       </c>
     </row>
   </sheetData>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="17">
   <si>
     <t>Date</t>
   </si>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H110"/>
+  <dimension ref="A1:H119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -587,42 +587,42 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1">
-        <v>46153</v>
+        <v>46170</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>53.14833755912058</v>
+        <v>24.60711544306017</v>
       </c>
       <c r="D8">
-        <v>25.84885448407537</v>
+        <v>16.81224929344452</v>
       </c>
       <c r="E8">
-        <v>0.9262</v>
+        <v>0.8501999999999998</v>
       </c>
       <c r="F8">
-        <v>0.9262</v>
+        <v>0.8501999999999998</v>
       </c>
       <c r="G8">
-        <v>0.3839084462043663</v>
+        <v>0.6039079580940436</v>
       </c>
       <c r="H8">
-        <v>0.9262</v>
+        <v>0.9105</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
       </c>
       <c r="C9">
-        <v>51.82921169635205</v>
+        <v>53.14833755912058</v>
       </c>
       <c r="D9">
-        <v>25.32805827181975</v>
+        <v>25.84885448407537</v>
       </c>
       <c r="E9">
         <v>0.9262</v>
@@ -631,7 +631,7 @@
         <v>0.9262</v>
       </c>
       <c r="G9">
-        <v>0.3568580281685669</v>
+        <v>0.3839084462043663</v>
       </c>
       <c r="H9">
         <v>0.9262</v>
@@ -639,120 +639,120 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
       </c>
       <c r="C10">
-        <v>52.28471716753184</v>
+        <v>51.82921169635205</v>
       </c>
       <c r="D10">
-        <v>25.54525144150689</v>
+        <v>25.32805827181975</v>
       </c>
       <c r="E10">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="F10">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="G10">
-        <v>0.378012896547947</v>
+        <v>0.3568580281685669</v>
       </c>
       <c r="H10">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
       </c>
       <c r="C11">
-        <v>53.87287273813902</v>
+        <v>52.28471716753184</v>
       </c>
       <c r="D11">
-        <v>26.32154226438612</v>
+        <v>25.54525144150689</v>
       </c>
       <c r="E11">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="F11">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="G11">
-        <v>0.4166811087612758</v>
+        <v>0.378012896547947</v>
       </c>
       <c r="H11">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
       </c>
       <c r="C12">
-        <v>52.18747148214074</v>
+        <v>53.87287273813902</v>
       </c>
       <c r="D12">
-        <v>25.13616059644496</v>
+        <v>26.32154226438612</v>
       </c>
       <c r="E12">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="F12">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="G12">
-        <v>0.3627535778249862</v>
+        <v>0.4166811087612758</v>
       </c>
       <c r="H12">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="B13" t="s">
         <v>9</v>
       </c>
       <c r="C13">
-        <v>50.72035274995172</v>
+        <v>52.18747148214074</v>
       </c>
       <c r="D13">
-        <v>24.61756040386634</v>
+        <v>25.13616059644496</v>
       </c>
       <c r="E13">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="F13">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="G13">
         <v>0.3627535778249862</v>
       </c>
       <c r="H13">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
       </c>
       <c r="C14">
-        <v>50.11981086673613</v>
+        <v>50.72035274995172</v>
       </c>
       <c r="D14">
-        <v>24.13061679021705</v>
+        <v>24.61756040386634</v>
       </c>
       <c r="E14">
         <v>0.9259000000000001</v>
@@ -761,7 +761,7 @@
         <v>0.9259000000000001</v>
       </c>
       <c r="G14">
-        <v>0.3258193430227221</v>
+        <v>0.3627535778249862</v>
       </c>
       <c r="H14">
         <v>0.9259000000000001</v>
@@ -769,120 +769,120 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
       </c>
       <c r="C15">
-        <v>51.74165648409151</v>
+        <v>50.11981086673613</v>
       </c>
       <c r="D15">
-        <v>24.98091384114761</v>
+        <v>24.13061679021705</v>
       </c>
       <c r="E15">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="F15">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="G15">
-        <v>0.3818277262286871</v>
+        <v>0.3258193430227221</v>
       </c>
       <c r="H15">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
       </c>
       <c r="C16">
-        <v>49.13455894175823</v>
+        <v>51.74165648409151</v>
       </c>
       <c r="D16">
-        <v>25.30005057653127</v>
+        <v>24.98091384114761</v>
       </c>
       <c r="E16">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="F16">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="G16">
-        <v>0.4028091571787618</v>
+        <v>0.3818277262286871</v>
       </c>
       <c r="H16">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
       </c>
       <c r="C17">
-        <v>49.57776597479297</v>
+        <v>49.13455894175823</v>
       </c>
       <c r="D17">
-        <v>25.04906725563518</v>
+        <v>25.30005057653127</v>
       </c>
       <c r="E17">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="F17">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="G17">
-        <v>0.4256980029692063</v>
+        <v>0.4028091571787618</v>
       </c>
       <c r="H17">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="B18" t="s">
         <v>9</v>
       </c>
       <c r="C18">
-        <v>49.71239596645896</v>
+        <v>49.57776597479297</v>
       </c>
       <c r="D18">
-        <v>25.18778610744295</v>
+        <v>25.04906725563518</v>
       </c>
       <c r="E18">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="F18">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="G18">
-        <v>0.4525749835757003</v>
+        <v>0.4256980029692063</v>
       </c>
       <c r="H18">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="B19" t="s">
         <v>9</v>
       </c>
       <c r="C19">
-        <v>50.77166277510776</v>
+        <v>49.71239596645896</v>
       </c>
       <c r="D19">
-        <v>25.7431782858765</v>
+        <v>25.18778610744295</v>
       </c>
       <c r="E19">
         <v>0.9231999999999999</v>
@@ -891,7 +891,7 @@
         <v>0.9231999999999999</v>
       </c>
       <c r="G19">
-        <v>0.4700884597036457</v>
+        <v>0.4525749835757003</v>
       </c>
       <c r="H19">
         <v>0.9231999999999999</v>
@@ -899,172 +899,172 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1">
-        <v>46169</v>
+        <v>46168</v>
       </c>
       <c r="B20" t="s">
         <v>9</v>
       </c>
       <c r="C20">
-        <v>50.57689164833899</v>
+        <v>50.77166277510776</v>
       </c>
       <c r="D20">
-        <v>25.70244067238947</v>
+        <v>25.7431782858765</v>
       </c>
       <c r="E20">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="F20">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="G20">
-        <v>0.4518814984464716</v>
+        <v>0.4700884597036457</v>
       </c>
       <c r="H20">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1">
-        <v>46153</v>
+        <v>46169</v>
       </c>
       <c r="B21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C21">
-        <v>34.64560932909123</v>
+        <v>50.57689164833899</v>
       </c>
       <c r="D21">
-        <v>26.08311546080494</v>
+        <v>25.70244067238947</v>
       </c>
       <c r="E21">
-        <v>0.9983000000000001</v>
+        <v>0.9217</v>
       </c>
       <c r="F21">
-        <v>0.9983000000000001</v>
+        <v>0.9217</v>
       </c>
       <c r="G21">
-        <v>0.06258613715048233</v>
+        <v>0.4518814984464716</v>
       </c>
       <c r="H21">
-        <v>0.9983000000000001</v>
+        <v>0.9217</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1">
-        <v>46154</v>
+        <v>46170</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C22">
-        <v>34.50204921141101</v>
+        <v>50.80027854822009</v>
       </c>
       <c r="D22">
-        <v>25.94535229304585</v>
+        <v>25.90068415792015</v>
       </c>
       <c r="E22">
-        <v>0.9984</v>
+        <v>0.9231</v>
       </c>
       <c r="F22">
-        <v>0.9984</v>
+        <v>0.9231</v>
       </c>
       <c r="G22">
-        <v>0.05768943168306073</v>
+        <v>0.4699150222743402</v>
       </c>
       <c r="H22">
-        <v>0.9984</v>
+        <v>0.9231</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="B23" t="s">
         <v>10</v>
       </c>
       <c r="C23">
-        <v>35.10429483281073</v>
+        <v>34.64560932909123</v>
       </c>
       <c r="D23">
-        <v>26.43864879939599</v>
+        <v>26.08311546080494</v>
       </c>
       <c r="E23">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="F23">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="G23">
-        <v>0.07926550001722021</v>
+        <v>0.06258613715048233</v>
       </c>
       <c r="H23">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="B24" t="s">
         <v>10</v>
       </c>
       <c r="C24">
-        <v>35.36860632820093</v>
+        <v>34.50204921141101</v>
       </c>
       <c r="D24">
-        <v>26.56575571102338</v>
+        <v>25.94535229304585</v>
       </c>
       <c r="E24">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F24">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G24">
-        <v>0.08553946591902095</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H24">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="B25" t="s">
         <v>10</v>
       </c>
       <c r="C25">
-        <v>34.88080083527914</v>
+        <v>35.10429483281073</v>
       </c>
       <c r="D25">
-        <v>26.19322945679072</v>
+        <v>26.43864879939599</v>
       </c>
       <c r="E25">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="F25">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="G25">
-        <v>0.06870693142475881</v>
+        <v>0.07926550001722021</v>
       </c>
       <c r="H25">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1">
-        <v>46160</v>
+        <v>46156</v>
       </c>
       <c r="B26" t="s">
         <v>10</v>
       </c>
       <c r="C26">
-        <v>34.67638692539213</v>
+        <v>35.36860632820093</v>
       </c>
       <c r="D26">
-        <v>26.06707890342319</v>
+        <v>26.56575571102338</v>
       </c>
       <c r="E26">
         <v>0.9985999999999999</v>
@@ -1073,7 +1073,7 @@
         <v>0.9985999999999999</v>
       </c>
       <c r="G26">
-        <v>0.06289213016552919</v>
+        <v>0.08553946591902095</v>
       </c>
       <c r="H26">
         <v>0.9985999999999999</v>
@@ -1081,120 +1081,120 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
       </c>
       <c r="C27">
-        <v>34.21212662725402</v>
+        <v>34.88080083527914</v>
       </c>
       <c r="D27">
-        <v>25.60349394367002</v>
+        <v>26.19322945679072</v>
       </c>
       <c r="E27">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="F27">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="G27">
-        <v>0.0486610616591685</v>
+        <v>0.06870693142475881</v>
       </c>
       <c r="H27">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
       </c>
       <c r="C28">
-        <v>34.78598436564941</v>
+        <v>34.67638692539213</v>
       </c>
       <c r="D28">
-        <v>25.95505316769806</v>
+        <v>26.06707890342319</v>
       </c>
       <c r="E28">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="F28">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="G28">
-        <v>0.06335117806143331</v>
+        <v>0.06289213016552919</v>
       </c>
       <c r="H28">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1">
-        <v>46163</v>
+        <v>46161</v>
       </c>
       <c r="B29" t="s">
         <v>10</v>
       </c>
       <c r="C29">
-        <v>33.4539909056227</v>
+        <v>34.21212662725402</v>
       </c>
       <c r="D29">
-        <v>25.96014535427112</v>
+        <v>25.60349394367002</v>
       </c>
       <c r="E29">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="F29">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="G29">
-        <v>0.06350423294229035</v>
+        <v>0.0486610616591685</v>
       </c>
       <c r="H29">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1">
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="B30" t="s">
         <v>10</v>
       </c>
       <c r="C30">
-        <v>33.24951933563993</v>
+        <v>34.78598436564941</v>
       </c>
       <c r="D30">
-        <v>25.46629530314992</v>
+        <v>25.95505316769806</v>
       </c>
       <c r="E30">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="F30">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="G30">
-        <v>0.06136193159696024</v>
+        <v>0.06335117806143331</v>
       </c>
       <c r="H30">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1">
-        <v>46167</v>
+        <v>46163</v>
       </c>
       <c r="B31" t="s">
         <v>10</v>
       </c>
       <c r="C31">
-        <v>33.29896419867477</v>
+        <v>33.4539909056227</v>
       </c>
       <c r="D31">
-        <v>25.45090185337973</v>
+        <v>25.96014535427112</v>
       </c>
       <c r="E31">
         <v>0.9984</v>
@@ -1203,7 +1203,7 @@
         <v>0.9984</v>
       </c>
       <c r="G31">
-        <v>0.06136193159696024</v>
+        <v>0.06350423294229035</v>
       </c>
       <c r="H31">
         <v>0.9984</v>
@@ -1211,16 +1211,16 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1">
-        <v>46168</v>
+        <v>46164</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
       </c>
       <c r="C32">
-        <v>33.41270923608511</v>
+        <v>33.24951933563993</v>
       </c>
       <c r="D32">
-        <v>25.54156152389702</v>
+        <v>25.46629530314992</v>
       </c>
       <c r="E32">
         <v>0.9984</v>
@@ -1229,7 +1229,7 @@
         <v>0.9984</v>
       </c>
       <c r="G32">
-        <v>0.06549347940676342</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H32">
         <v>0.9984</v>
@@ -1237,510 +1237,510 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1">
-        <v>46169</v>
+        <v>46167</v>
       </c>
       <c r="B33" t="s">
         <v>10</v>
       </c>
       <c r="C33">
-        <v>33.73350746548562</v>
+        <v>33.29896419867477</v>
       </c>
       <c r="D33">
-        <v>25.75393367034243</v>
+        <v>25.45090185337973</v>
       </c>
       <c r="E33">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="F33">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="G33">
-        <v>0.07620510288008187</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H33">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1">
-        <v>46153</v>
+        <v>46168</v>
       </c>
       <c r="B34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C34">
-        <v>36.55790859258162</v>
+        <v>33.41270923608511</v>
       </c>
       <c r="D34">
-        <v>22.67181120908155</v>
+        <v>25.54156152389702</v>
       </c>
       <c r="E34">
-        <v>0.9990740999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F34">
-        <v>0.9990740999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G34">
-        <v>0.1648443271746771</v>
+        <v>0.06549347940676342</v>
       </c>
       <c r="H34">
-        <v>0.9990740999999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1">
-        <v>46154</v>
+        <v>46169</v>
       </c>
       <c r="B35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C35">
-        <v>36.44753722959613</v>
+        <v>33.73350746548562</v>
       </c>
       <c r="D35">
-        <v>22.40292401789388</v>
+        <v>25.75393367034243</v>
       </c>
       <c r="E35">
-        <v>0.9990772499999999</v>
+        <v>0.9987000000000001</v>
       </c>
       <c r="F35">
-        <v>0.9990772499999999</v>
+        <v>0.9987000000000001</v>
       </c>
       <c r="G35">
-        <v>0.154964342628132</v>
+        <v>0.07620510288008187</v>
       </c>
       <c r="H35">
-        <v>0.9990772499999999</v>
+        <v>0.9987000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1">
-        <v>46155</v>
+        <v>46170</v>
       </c>
       <c r="B36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C36">
-        <v>36.63128514035871</v>
+        <v>33.84336414535104</v>
       </c>
       <c r="D36">
-        <v>22.65773388934668</v>
+        <v>25.97168203877208</v>
       </c>
       <c r="E36">
-        <v>0.99907745</v>
+        <v>0.9988</v>
       </c>
       <c r="F36">
-        <v>0.99907745</v>
+        <v>0.9988</v>
       </c>
       <c r="G36">
-        <v>0.1671633421405267</v>
+        <v>0.0844683152463559</v>
       </c>
       <c r="H36">
-        <v>0.99907745</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="B37" t="s">
         <v>11</v>
       </c>
       <c r="C37">
-        <v>36.87865927427314</v>
+        <v>36.55790859258162</v>
       </c>
       <c r="D37">
-        <v>22.69755646854794</v>
+        <v>22.67181120908155</v>
       </c>
       <c r="E37">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="F37">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="G37">
-        <v>0.1754592080224002</v>
+        <v>0.1648443271746771</v>
       </c>
       <c r="H37">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="B38" t="s">
         <v>11</v>
       </c>
       <c r="C38">
-        <v>36.52208783231286</v>
+        <v>36.44753722959613</v>
       </c>
       <c r="D38">
-        <v>22.32462309676992</v>
+        <v>22.40292401789388</v>
       </c>
       <c r="E38">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="F38">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="G38">
-        <v>0.1577242156354994</v>
+        <v>0.154964342628132</v>
       </c>
       <c r="H38">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="B39" t="s">
         <v>11</v>
       </c>
       <c r="C39">
-        <v>36.25604200674668</v>
+        <v>36.63128514035871</v>
       </c>
       <c r="D39">
-        <v>22.16555007468561</v>
+        <v>22.65773388934668</v>
       </c>
       <c r="E39">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="F39">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="G39">
-        <v>0.1527434068648266</v>
+        <v>0.1671633421405267</v>
       </c>
       <c r="H39">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1">
-        <v>46161</v>
+        <v>46156</v>
       </c>
       <c r="B40" t="s">
         <v>11</v>
       </c>
       <c r="C40">
-        <v>36.01040085730018</v>
+        <v>36.87865927427314</v>
       </c>
       <c r="D40">
-        <v>22.19475589056387</v>
+        <v>22.69755646854794</v>
       </c>
       <c r="E40">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="F40">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="G40">
-        <v>0.1456396418594061</v>
+        <v>0.1754592080224002</v>
       </c>
       <c r="H40">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1">
-        <v>46162</v>
+        <v>46157</v>
       </c>
       <c r="B41" t="s">
         <v>11</v>
       </c>
       <c r="C41">
-        <v>36.45290912796982</v>
+        <v>36.52208783231286</v>
       </c>
       <c r="D41">
-        <v>22.46357594746874</v>
+        <v>22.32462309676992</v>
       </c>
       <c r="E41">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="F41">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="G41">
-        <v>0.1646157747240327</v>
+        <v>0.1577242156354994</v>
       </c>
       <c r="H41">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1">
-        <v>46163</v>
+        <v>46160</v>
       </c>
       <c r="B42" t="s">
         <v>11</v>
       </c>
       <c r="C42">
-        <v>35.75282090566891</v>
+        <v>36.25604200674668</v>
       </c>
       <c r="D42">
-        <v>22.57615417310648</v>
+        <v>22.16555007468561</v>
       </c>
       <c r="E42">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="F42">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="G42">
-        <v>0.1668367104873381</v>
+        <v>0.1527434068648266</v>
       </c>
       <c r="H42">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1">
-        <v>46164</v>
+        <v>46161</v>
       </c>
       <c r="B43" t="s">
         <v>11</v>
       </c>
       <c r="C43">
-        <v>35.75514940724808</v>
+        <v>36.01040085730018</v>
       </c>
       <c r="D43">
-        <v>22.28880693466429</v>
+        <v>22.19475589056387</v>
       </c>
       <c r="E43">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="F43">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="G43">
-        <v>0.1717848261904962</v>
+        <v>0.1456396418594061</v>
       </c>
       <c r="H43">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1">
-        <v>46167</v>
+        <v>46162</v>
       </c>
       <c r="B44" t="s">
         <v>11</v>
       </c>
       <c r="C44">
-        <v>35.84133099010302</v>
+        <v>36.45290912796982</v>
       </c>
       <c r="D44">
-        <v>22.37458514769363</v>
+        <v>22.46357594746874</v>
       </c>
       <c r="E44">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="F44">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="G44">
-        <v>0.1717848261904962</v>
+        <v>0.1646157747240327</v>
       </c>
       <c r="H44">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1">
-        <v>46168</v>
+        <v>46163</v>
       </c>
       <c r="B45" t="s">
         <v>11</v>
       </c>
       <c r="C45">
-        <v>36.23214279739292</v>
+        <v>35.75282090566891</v>
       </c>
       <c r="D45">
-        <v>22.93484792820123</v>
+        <v>22.57615417310648</v>
       </c>
       <c r="E45">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
       <c r="F45">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
       <c r="G45">
-        <v>0.1925900763781823</v>
+        <v>0.1668367104873381</v>
       </c>
       <c r="H45">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="B46" t="s">
         <v>11</v>
       </c>
       <c r="C46">
-        <v>36.4336692499184</v>
+        <v>35.75514940724808</v>
       </c>
       <c r="D46">
-        <v>22.75940954009856</v>
+        <v>22.28880693466429</v>
       </c>
       <c r="E46">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="F46">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="G46">
-        <v>0.1912346098381414</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H46">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="B47" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C47">
-        <v>52.70832779833182</v>
+        <v>35.84133099010302</v>
       </c>
       <c r="D47">
-        <v>23.99044674439659</v>
+        <v>22.37458514769363</v>
       </c>
       <c r="E47">
-        <v>0.9994000000000002</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="F47">
-        <v>0.9994000000000002</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="G47">
-        <v>0.5438253854918791</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H47">
-        <v>0.9994000000000002</v>
+        <v>0.9992609200000001</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1">
-        <v>46154</v>
+        <v>46168</v>
       </c>
       <c r="B48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C48">
-        <v>50.89464485280568</v>
+        <v>36.23214279739292</v>
       </c>
       <c r="D48">
-        <v>23.21558303176282</v>
+        <v>22.93484792820123</v>
       </c>
       <c r="E48">
-        <v>0.9996</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="F48">
-        <v>0.9996</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="G48">
-        <v>0.5034825029548833</v>
+        <v>0.1925900763781823</v>
       </c>
       <c r="H48">
-        <v>0.9996</v>
+        <v>0.9992609200000001</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1">
-        <v>46155</v>
+        <v>46169</v>
       </c>
       <c r="B49" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C49">
-        <v>51.8659994471731</v>
+        <v>36.4336692499184</v>
       </c>
       <c r="D49">
-        <v>23.7009037279043</v>
+        <v>22.75940954009856</v>
       </c>
       <c r="E49">
-        <v>1.0002</v>
+        <v>0.9992099400000001</v>
       </c>
       <c r="F49">
-        <v>1.0002</v>
+        <v>0.9992099400000001</v>
       </c>
       <c r="G49">
-        <v>0.533512029714132</v>
+        <v>0.1912346098381414</v>
       </c>
       <c r="H49">
-        <v>1.0002</v>
+        <v>0.9992099400000001</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1">
-        <v>46156</v>
+        <v>46170</v>
       </c>
       <c r="B50" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C50">
-        <v>52.4470179952828</v>
+        <v>36.57358557066742</v>
       </c>
       <c r="D50">
-        <v>23.76861704536814</v>
+        <v>22.83069636955243</v>
       </c>
       <c r="E50">
-        <v>0.9998</v>
+        <v>0.9994435600000001</v>
       </c>
       <c r="F50">
-        <v>0.9998</v>
+        <v>0.9994435600000001</v>
       </c>
       <c r="G50">
-        <v>0.5492634496849078</v>
+        <v>0.2012778603742877</v>
       </c>
       <c r="H50">
-        <v>0.9998</v>
+        <v>0.9994435600000001</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="B51" t="s">
         <v>12</v>
       </c>
       <c r="C51">
-        <v>50.81077380018606</v>
+        <v>52.70832779833182</v>
       </c>
       <c r="D51">
-        <v>22.76900580927995</v>
+        <v>23.99044674439659</v>
       </c>
       <c r="E51">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="F51">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="G51">
-        <v>0.4903296143797722</v>
+        <v>0.5438253854918791</v>
       </c>
       <c r="H51">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1">
-        <v>46160</v>
+        <v>46154</v>
       </c>
       <c r="B52" t="s">
         <v>12</v>
       </c>
       <c r="C52">
-        <v>49.50286387149169</v>
+        <v>50.89464485280568</v>
       </c>
       <c r="D52">
-        <v>22.24532119914133</v>
+        <v>23.21558303176282</v>
       </c>
       <c r="E52">
         <v>0.9996</v>
@@ -1749,7 +1749,7 @@
         <v>0.9996</v>
       </c>
       <c r="G52">
-        <v>0.4630591776162345</v>
+        <v>0.5034825029548833</v>
       </c>
       <c r="H52">
         <v>0.9996</v>
@@ -1757,1108 +1757,1108 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1">
-        <v>46161</v>
+        <v>46155</v>
       </c>
       <c r="B53" t="s">
         <v>12</v>
       </c>
       <c r="C53">
-        <v>49.29146729279496</v>
+        <v>51.8659994471731</v>
       </c>
       <c r="D53">
-        <v>22.22167836589682</v>
+        <v>23.7009037279043</v>
       </c>
       <c r="E53">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="F53">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="G53">
-        <v>0.4571659248870246</v>
+        <v>0.533512029714132</v>
       </c>
       <c r="H53">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1">
-        <v>46162</v>
+        <v>46156</v>
       </c>
       <c r="B54" t="s">
         <v>12</v>
       </c>
       <c r="C54">
-        <v>50.88652370817657</v>
+        <v>52.4470179952828</v>
       </c>
       <c r="D54">
-        <v>22.93254398967657</v>
+        <v>23.76861704536814</v>
       </c>
       <c r="E54">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F54">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G54">
-        <v>0.5126171754864624</v>
+        <v>0.5492634496849078</v>
       </c>
       <c r="H54">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1">
-        <v>46163</v>
+        <v>46157</v>
       </c>
       <c r="B55" t="s">
         <v>12</v>
       </c>
       <c r="C55">
-        <v>48.26646764818586</v>
+        <v>50.81077380018606</v>
       </c>
       <c r="D55">
-        <v>23.11655387625012</v>
+        <v>22.76900580927995</v>
       </c>
       <c r="E55">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="F55">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="G55">
-        <v>0.521243030947425</v>
+        <v>0.4903296143797722</v>
       </c>
       <c r="H55">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1">
-        <v>46164</v>
+        <v>46160</v>
       </c>
       <c r="B56" t="s">
         <v>12</v>
       </c>
       <c r="C56">
-        <v>48.84737503703267</v>
+        <v>49.50286387149169</v>
       </c>
       <c r="D56">
-        <v>22.83557604744466</v>
+        <v>22.24532119914133</v>
       </c>
       <c r="E56">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="F56">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="G56">
-        <v>0.5438521997590966</v>
+        <v>0.4630591776162345</v>
       </c>
       <c r="H56">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1">
-        <v>46167</v>
+        <v>46161</v>
       </c>
       <c r="B57" t="s">
         <v>12</v>
       </c>
       <c r="C57">
-        <v>48.85151560750146</v>
+        <v>49.29146729279496</v>
       </c>
       <c r="D57">
-        <v>22.83513820206554</v>
+        <v>22.22167836589682</v>
       </c>
       <c r="E57">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F57">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G57">
-        <v>0.5438521997590966</v>
+        <v>0.4571659248870246</v>
       </c>
       <c r="H57">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1">
-        <v>46168</v>
+        <v>46162</v>
       </c>
       <c r="B58" t="s">
         <v>12</v>
       </c>
       <c r="C58">
-        <v>50.90437883274981</v>
+        <v>50.88652370817657</v>
       </c>
       <c r="D58">
-        <v>24.25672473501501</v>
+        <v>22.93254398967657</v>
       </c>
       <c r="E58">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F58">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G58">
-        <v>0.6130191115419561</v>
+        <v>0.5126171754864624</v>
       </c>
       <c r="H58">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1">
-        <v>46169</v>
+        <v>46163</v>
       </c>
       <c r="B59" t="s">
         <v>12</v>
       </c>
       <c r="C59">
-        <v>50.47312432255841</v>
+        <v>48.26646764818586</v>
       </c>
       <c r="D59">
-        <v>23.84499305142194</v>
+        <v>23.11655387625012</v>
       </c>
       <c r="E59">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="F59">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="G59">
-        <v>0.5952317692821967</v>
+        <v>0.521243030947425</v>
       </c>
       <c r="H59">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1">
-        <v>46153</v>
+        <v>46164</v>
       </c>
       <c r="B60" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C60">
-        <v>57.1732166855686</v>
+        <v>48.84737503703267</v>
       </c>
       <c r="D60">
-        <v>23.50022751267814</v>
+        <v>22.83557604744466</v>
       </c>
       <c r="E60">
-        <v>0.9991</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F60">
-        <v>0.9991</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G60">
-        <v>0.6994110097039083</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H60">
-        <v>0.9991</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1">
-        <v>46154</v>
+        <v>46167</v>
       </c>
       <c r="B61" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C61">
-        <v>54.77380642078597</v>
+        <v>48.85151560750146</v>
       </c>
       <c r="D61">
-        <v>22.55192940254518</v>
+        <v>22.83513820206554</v>
       </c>
       <c r="E61">
-        <v>0.9990000000000001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F61">
-        <v>0.9990000000000001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G61">
-        <v>0.6459175880844941</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H61">
-        <v>0.9990000000000001</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1">
-        <v>46155</v>
+        <v>46168</v>
       </c>
       <c r="B62" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C62">
-        <v>56.32187380830906</v>
+        <v>50.90437883274981</v>
       </c>
       <c r="D62">
-        <v>23.17121437414109</v>
+        <v>24.25672473501501</v>
       </c>
       <c r="E62">
-        <v>0.9990000000000001</v>
+        <v>0.9996999999999999</v>
       </c>
       <c r="F62">
-        <v>0.9990000000000001</v>
+        <v>0.9996999999999999</v>
       </c>
       <c r="G62">
-        <v>0.6851523922954754</v>
+        <v>0.6130191115419561</v>
       </c>
       <c r="H62">
-        <v>0.9990000000000001</v>
+        <v>0.9996999999999999</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1">
-        <v>46156</v>
+        <v>46169</v>
       </c>
       <c r="B63" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C63">
-        <v>56.15321618553139</v>
+        <v>50.47312432255841</v>
       </c>
       <c r="D63">
-        <v>22.95838347314443</v>
+        <v>23.84499305142194</v>
       </c>
       <c r="E63">
-        <v>0.9992</v>
+        <v>0.9998</v>
       </c>
       <c r="F63">
-        <v>0.9992</v>
+        <v>0.9998</v>
       </c>
       <c r="G63">
-        <v>0.6907028507208208</v>
+        <v>0.5952317692821967</v>
       </c>
       <c r="H63">
-        <v>0.9992</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1">
-        <v>46157</v>
+        <v>46170</v>
       </c>
       <c r="B64" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C64">
-        <v>54.47755813049488</v>
+        <v>50.84596269629946</v>
       </c>
       <c r="D64">
-        <v>22.0083816089626</v>
+        <v>23.7680603326165</v>
       </c>
       <c r="E64">
-        <v>0.9986</v>
+        <v>0.9998</v>
       </c>
       <c r="F64">
-        <v>0.9986</v>
+        <v>0.9998</v>
       </c>
       <c r="G64">
-        <v>0.6220895940829376</v>
+        <v>0.606831065374982</v>
       </c>
       <c r="H64">
-        <v>0.9986</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
       </c>
       <c r="C65">
-        <v>52.6278781150669</v>
+        <v>57.1732166855686</v>
       </c>
       <c r="D65">
-        <v>21.5357353870778</v>
+        <v>23.50022751267814</v>
       </c>
       <c r="E65">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F65">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G65">
-        <v>0.5845134636435627</v>
+        <v>0.6994110097039083</v>
       </c>
       <c r="H65">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
       </c>
       <c r="C66">
-        <v>54.91583234840245</v>
+        <v>54.77380642078597</v>
       </c>
       <c r="D66">
-        <v>22.38321645985006</v>
+        <v>22.55192940254518</v>
       </c>
       <c r="E66">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F66">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G66">
-        <v>0.6596976539194066</v>
+        <v>0.6459175880844941</v>
       </c>
       <c r="H66">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
       </c>
       <c r="C67">
-        <v>53.91712298548793</v>
+        <v>56.32187380830906</v>
       </c>
       <c r="D67">
-        <v>22.73711181201267</v>
+        <v>23.17121437414109</v>
       </c>
       <c r="E67">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F67">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G67">
-        <v>0.6737329602396263</v>
+        <v>0.6851523922954754</v>
       </c>
       <c r="H67">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
       </c>
       <c r="C68">
-        <v>55.19651747515625</v>
+        <v>56.15321618553139</v>
       </c>
       <c r="D68">
-        <v>22.79462037330554</v>
+        <v>22.95838347314443</v>
       </c>
       <c r="E68">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
       <c r="F68">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
       <c r="G68">
-        <v>0.7139885317003913</v>
+        <v>0.6907028507208208</v>
       </c>
       <c r="H68">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
       </c>
       <c r="C69">
-        <v>55.28054997487197</v>
+        <v>54.47755813049488</v>
       </c>
       <c r="D69">
-        <v>23.00160891539877</v>
+        <v>22.0083816089626</v>
       </c>
       <c r="E69">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="F69">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="G69">
-        <v>0.7139885317003913</v>
+        <v>0.6220895940829376</v>
       </c>
       <c r="H69">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1">
-        <v>46168</v>
+        <v>46161</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
       </c>
       <c r="C70">
-        <v>58.75156728873073</v>
+        <v>52.6278781150669</v>
       </c>
       <c r="D70">
-        <v>24.84249654093248</v>
+        <v>21.5357353870778</v>
       </c>
       <c r="E70">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="F70">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="G70">
-        <v>0.8184872182632257</v>
+        <v>0.5845134636435627</v>
       </c>
       <c r="H70">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1">
-        <v>46169</v>
+        <v>46162</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
       </c>
       <c r="C71">
-        <v>57.86771234337395</v>
+        <v>54.91583234840245</v>
       </c>
       <c r="D71">
-        <v>24.21066615243091</v>
+        <v>22.38321645985006</v>
       </c>
       <c r="E71">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="F71">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="G71">
-        <v>0.798997241708943</v>
+        <v>0.6596976539194066</v>
       </c>
       <c r="H71">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1">
-        <v>46153</v>
+        <v>46163</v>
       </c>
       <c r="B72" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C72">
-        <v>35.78646526282436</v>
+        <v>53.91712298548793</v>
       </c>
       <c r="D72">
-        <v>18.96635091925032</v>
+        <v>22.73711181201267</v>
       </c>
       <c r="E72">
-        <v>0.9996491399999999</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="F72">
-        <v>0.9996491399999999</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="G72">
-        <v>0.2240600969213613</v>
+        <v>0.6737329602396263</v>
       </c>
       <c r="H72">
-        <v>0.9985614899999999</v>
+        <v>0.9991999999999999</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1">
-        <v>46154</v>
+        <v>46164</v>
       </c>
       <c r="B73" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C73">
-        <v>35.71584102184062</v>
+        <v>55.19651747515625</v>
       </c>
       <c r="D73">
-        <v>18.62432950231353</v>
+        <v>22.79462037330554</v>
       </c>
       <c r="E73">
-        <v>0.99965481</v>
+        <v>0.9991</v>
       </c>
       <c r="F73">
-        <v>0.99965481</v>
+        <v>0.9991</v>
       </c>
       <c r="G73">
-        <v>0.2104844827747143</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H73">
-        <v>0.9985622199999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1">
-        <v>46155</v>
+        <v>46167</v>
       </c>
       <c r="B74" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C74">
-        <v>35.95182028203252</v>
+        <v>55.28054997487197</v>
       </c>
       <c r="D74">
-        <v>18.95670796791552</v>
+        <v>23.00160891539877</v>
       </c>
       <c r="E74">
-        <v>0.9996515200000001</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="F74">
-        <v>0.9996515200000001</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="G74">
-        <v>0.2259035693959275</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H74">
-        <v>0.99855193</v>
+        <v>0.9989000000000001</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1">
-        <v>46156</v>
+        <v>46168</v>
       </c>
       <c r="B75" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C75">
-        <v>36.14451597805883</v>
+        <v>58.75156728873073</v>
       </c>
       <c r="D75">
-        <v>18.86297660538653</v>
+        <v>24.84249654093248</v>
       </c>
       <c r="E75">
-        <v>0.9996563399999999</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="F75">
-        <v>0.9996563399999999</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="G75">
-        <v>0.2362110061840785</v>
+        <v>0.8184872182632257</v>
       </c>
       <c r="H75">
-        <v>0.99857265</v>
+        <v>0.9989000000000001</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1">
-        <v>46157</v>
+        <v>46169</v>
       </c>
       <c r="B76" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C76">
-        <v>35.32805803135546</v>
+        <v>57.86771234337395</v>
       </c>
       <c r="D76">
-        <v>18.35643242381478</v>
+        <v>24.21066615243091</v>
       </c>
       <c r="E76">
-        <v>0.9997415800000001</v>
+        <v>0.9986999999999999</v>
       </c>
       <c r="F76">
-        <v>0.9997415800000001</v>
+        <v>0.9986999999999999</v>
       </c>
       <c r="G76">
-        <v>0.2023559161375383</v>
+        <v>0.798997241708943</v>
       </c>
       <c r="H76">
-        <v>0.9986639900000002</v>
+        <v>0.9986999999999999</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1">
-        <v>46160</v>
+        <v>46170</v>
       </c>
       <c r="B77" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C77">
-        <v>34.83995455757461</v>
+        <v>58.18666682631797</v>
       </c>
       <c r="D77">
-        <v>18.02301281718857</v>
+        <v>24.09552344282839</v>
       </c>
       <c r="E77">
-        <v>0.9996851299999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F77">
-        <v>0.9996851299999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G77">
-        <v>0.1850932291737926</v>
+        <v>0.8165093478664007</v>
       </c>
       <c r="H77">
-        <v>0.99857724</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B78" t="s">
         <v>14</v>
       </c>
       <c r="C78">
-        <v>34.45479308705605</v>
+        <v>35.78646526282436</v>
       </c>
       <c r="D78">
-        <v>18.09576834566068</v>
+        <v>18.96635091925032</v>
       </c>
       <c r="E78">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="F78">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="G78">
-        <v>0.1784731209386736</v>
+        <v>0.2240600969213613</v>
       </c>
       <c r="H78">
-        <v>0.9985337599999999</v>
+        <v>0.9985614899999999</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B79" t="s">
         <v>14</v>
       </c>
       <c r="C79">
-        <v>34.96336277390787</v>
+        <v>35.71584102184062</v>
       </c>
       <c r="D79">
-        <v>18.34938420029253</v>
+        <v>18.62432950231353</v>
       </c>
       <c r="E79">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="F79">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="G79">
-        <v>0.2009313391215752</v>
+        <v>0.2104844827747143</v>
       </c>
       <c r="H79">
-        <v>0.99848777</v>
+        <v>0.9985622199999999</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B80" t="s">
         <v>14</v>
       </c>
       <c r="C80">
-        <v>34.44616924817128</v>
+        <v>35.95182028203252</v>
       </c>
       <c r="D80">
-        <v>18.60085625074367</v>
+        <v>18.95670796791552</v>
       </c>
       <c r="E80">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="F80">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="G80">
-        <v>0.2124957180214682</v>
+        <v>0.2259035693959275</v>
       </c>
       <c r="H80">
-        <v>0.9985085200000001</v>
+        <v>0.99855193</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="1">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="B81" t="s">
         <v>14</v>
       </c>
       <c r="C81">
-        <v>34.62137220937314</v>
+        <v>36.14451597805883</v>
       </c>
       <c r="D81">
-        <v>18.28780484745949</v>
+        <v>18.86297660538653</v>
       </c>
       <c r="E81">
-        <v>0.9996106299999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="F81">
-        <v>0.9996106299999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="G81">
-        <v>0.2145907067863493</v>
+        <v>0.2362110061840785</v>
       </c>
       <c r="H81">
-        <v>0.9932939299999999</v>
+        <v>0.99857265</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="1">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="B82" t="s">
         <v>14</v>
       </c>
       <c r="C82">
-        <v>34.6540695486741</v>
+        <v>35.32805803135546</v>
       </c>
       <c r="D82">
-        <v>18.36409048915342</v>
+        <v>18.35643242381478</v>
       </c>
       <c r="E82">
-        <v>0.9995448900000001</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="F82">
-        <v>0.9995448900000001</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="G82">
-        <v>0.2145907067863493</v>
+        <v>0.2023559161375383</v>
       </c>
       <c r="H82">
-        <v>0.9984302600000001</v>
+        <v>0.9986639900000002</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="1">
-        <v>46168</v>
+        <v>46160</v>
       </c>
       <c r="B83" t="s">
         <v>14</v>
       </c>
       <c r="C83">
-        <v>35.4820130509417</v>
+        <v>34.83995455757461</v>
       </c>
       <c r="D83">
-        <v>19.20292041814603</v>
+        <v>18.02301281718857</v>
       </c>
       <c r="E83">
-        <v>0.9995448900000001</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="F83">
-        <v>0.9995448900000001</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="G83">
-        <v>0.2553172934903569</v>
+        <v>0.1850932291737926</v>
       </c>
       <c r="H83">
-        <v>0.9984302600000001</v>
+        <v>0.99857724</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="1">
-        <v>46169</v>
+        <v>46161</v>
       </c>
       <c r="B84" t="s">
         <v>14</v>
       </c>
       <c r="C84">
-        <v>35.71913468603401</v>
+        <v>34.45479308705605</v>
       </c>
       <c r="D84">
-        <v>18.96318693998171</v>
+        <v>18.09576834566068</v>
       </c>
       <c r="E84">
-        <v>0.99955466</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="F84">
-        <v>0.99955466</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="G84">
-        <v>0.2536413280520453</v>
+        <v>0.1784731209386736</v>
       </c>
       <c r="H84">
-        <v>0.9984700500000001</v>
+        <v>0.9985337599999999</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1">
-        <v>46153</v>
+        <v>46162</v>
       </c>
       <c r="B85" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C85">
-        <v>28.12253390077671</v>
+        <v>34.96336277390787</v>
       </c>
       <c r="D85">
-        <v>23.58699683751922</v>
+        <v>18.34938420029253</v>
       </c>
       <c r="E85">
-        <v>0.9997295369999999</v>
+        <v>0.99963413</v>
       </c>
       <c r="F85">
-        <v>0.9997295369999999</v>
+        <v>0.99963413</v>
       </c>
       <c r="G85">
-        <v>0.03368732240295347</v>
+        <v>0.2009313391215752</v>
       </c>
       <c r="H85">
-        <v>0.9997295369999999</v>
+        <v>0.99848777</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="1">
-        <v>46154</v>
+        <v>46163</v>
       </c>
       <c r="B86" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C86">
-        <v>28.17715727830483</v>
+        <v>34.44616924817128</v>
       </c>
       <c r="D86">
-        <v>23.63894513078866</v>
+        <v>18.60085625074367</v>
       </c>
       <c r="E86">
-        <v>1.000319473</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="F86">
-        <v>1.000319473</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="G86">
-        <v>0.03515547182056333</v>
+        <v>0.2124957180214682</v>
       </c>
       <c r="H86">
-        <v>1.000319473</v>
+        <v>0.9985085200000001</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="1">
-        <v>46155</v>
+        <v>46164</v>
       </c>
       <c r="B87" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C87">
-        <v>28.59002627414054</v>
+        <v>34.62137220937314</v>
       </c>
       <c r="D87">
-        <v>23.96230704059692</v>
+        <v>18.28780484745949</v>
       </c>
       <c r="E87">
-        <v>0.9999999989999999</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="F87">
-        <v>0.9999999989999999</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="G87">
-        <v>0.05179637495949674</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H87">
-        <v>0.9999999989999999</v>
+        <v>0.9932939299999999</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1">
-        <v>46156</v>
+        <v>46167</v>
       </c>
       <c r="B88" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C88">
-        <v>28.56217859389523</v>
+        <v>34.6540695486741</v>
       </c>
       <c r="D88">
-        <v>23.9411987302529</v>
+        <v>18.36409048915342</v>
       </c>
       <c r="E88">
-        <v>1</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="F88">
-        <v>1</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="G88">
-        <v>0.04837024516756849</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H88">
-        <v>1</v>
+        <v>0.9984302600000001</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="1">
-        <v>46157</v>
+        <v>46168</v>
       </c>
       <c r="B89" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C89">
-        <v>28.57618675936338</v>
+        <v>35.4820130509417</v>
       </c>
       <c r="D89">
-        <v>23.9576220541054</v>
+        <v>19.20292041814603</v>
       </c>
       <c r="E89">
-        <v>0.999503249</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="F89">
-        <v>0.999503249</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="G89">
-        <v>0.04983868243960732</v>
+        <v>0.2553172934903569</v>
       </c>
       <c r="H89">
-        <v>0.999503249</v>
+        <v>0.9984302600000001</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="1">
-        <v>46160</v>
+        <v>46169</v>
       </c>
       <c r="B90" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C90">
-        <v>28.68951918518517</v>
+        <v>35.71913468603401</v>
       </c>
       <c r="D90">
-        <v>24.06134728453882</v>
+        <v>18.96318693998171</v>
       </c>
       <c r="E90">
-        <v>0.999503249</v>
+        <v>0.99955466</v>
       </c>
       <c r="F90">
-        <v>0.999503249</v>
+        <v>0.99955466</v>
       </c>
       <c r="G90">
-        <v>0.04983868243960732</v>
+        <v>0.2536413280520453</v>
       </c>
       <c r="H90">
-        <v>0.999503249</v>
+        <v>0.9984700500000001</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="1">
-        <v>46161</v>
+        <v>46170</v>
       </c>
       <c r="B91" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C91">
-        <v>28.31167386654059</v>
+        <v>35.76226417354731</v>
       </c>
       <c r="D91">
-        <v>23.75157719455474</v>
+        <v>18.89050847207122</v>
       </c>
       <c r="E91">
-        <v>1.000177331</v>
+        <v>0.9995525399999999</v>
       </c>
       <c r="F91">
-        <v>1.000177331</v>
+        <v>0.9995525399999999</v>
       </c>
       <c r="G91">
-        <v>0.04053938625111919</v>
+        <v>0.2580826940041561</v>
       </c>
       <c r="H91">
-        <v>1.000177331</v>
+        <v>0.99847732</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="1">
-        <v>46162</v>
+        <v>46153</v>
       </c>
       <c r="B92" t="s">
         <v>15</v>
       </c>
       <c r="C92">
-        <v>28.57911382310097</v>
+        <v>28.12253390077671</v>
       </c>
       <c r="D92">
-        <v>23.89431741541233</v>
+        <v>23.58699683751922</v>
       </c>
       <c r="E92">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="F92">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="G92">
-        <v>0.04690190590044785</v>
+        <v>0.03368732240295347</v>
       </c>
       <c r="H92">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="1">
-        <v>46163</v>
+        <v>46154</v>
       </c>
       <c r="B93" t="s">
         <v>15</v>
       </c>
       <c r="C93">
-        <v>28.55785065378643</v>
+        <v>28.17715727830483</v>
       </c>
       <c r="D93">
-        <v>24.04274714970193</v>
+        <v>23.63894513078866</v>
       </c>
       <c r="E93">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="F93">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="G93">
-        <v>0.05228572319419666</v>
+        <v>0.03515547182056333</v>
       </c>
       <c r="H93">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="1">
-        <v>46164</v>
+        <v>46155</v>
       </c>
       <c r="B94" t="s">
         <v>15</v>
       </c>
       <c r="C94">
-        <v>28.50194638163107</v>
+        <v>28.59002627414054</v>
       </c>
       <c r="D94">
-        <v>23.99272397156045</v>
+        <v>23.96230704059692</v>
       </c>
       <c r="E94">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F94">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G94">
-        <v>0.04934923597154284</v>
+        <v>0.05179637495949674</v>
       </c>
       <c r="H94">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="1">
-        <v>46167</v>
+        <v>46156</v>
       </c>
       <c r="B95" t="s">
         <v>15</v>
       </c>
       <c r="C95">
-        <v>28.55106858744498</v>
+        <v>28.56217859389523</v>
       </c>
       <c r="D95">
-        <v>23.9768329565351</v>
+        <v>23.9411987302529</v>
       </c>
       <c r="E95">
         <v>1</v>
@@ -2867,7 +2867,7 @@
         <v>1</v>
       </c>
       <c r="G95">
-        <v>0.05571185335164408</v>
+        <v>0.04837024516756849</v>
       </c>
       <c r="H95">
         <v>1</v>
@@ -2875,392 +2875,626 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="1">
-        <v>46168</v>
+        <v>46157</v>
       </c>
       <c r="B96" t="s">
         <v>15</v>
       </c>
       <c r="C96">
-        <v>28.54681541456266</v>
+        <v>28.57618675936338</v>
       </c>
       <c r="D96">
-        <v>23.97386168967948</v>
+        <v>23.9576220541054</v>
       </c>
       <c r="E96">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="F96">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="G96">
-        <v>0.04837034303541388</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H96">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="1">
-        <v>46169</v>
+        <v>46160</v>
       </c>
       <c r="B97" t="s">
         <v>15</v>
       </c>
       <c r="C97">
-        <v>28.83672936868491</v>
+        <v>28.68951918518517</v>
       </c>
       <c r="D97">
-        <v>24.203511281145</v>
+        <v>24.06134728453882</v>
       </c>
       <c r="E97">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="F97">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="G97">
-        <v>0.05962723282507953</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H97">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="1">
-        <v>46153</v>
+        <v>46161</v>
       </c>
       <c r="B98" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C98">
-        <v>40.68830633303975</v>
+        <v>28.31167386654059</v>
       </c>
       <c r="D98">
-        <v>21.50431773660198</v>
+        <v>23.75157719455474</v>
       </c>
       <c r="E98">
-        <v>0.99909852</v>
+        <v>1.000177331</v>
       </c>
       <c r="F98">
-        <v>0.99909852</v>
+        <v>1.000177331</v>
       </c>
       <c r="G98">
-        <v>0.2342423866086769</v>
+        <v>0.04053938625111919</v>
       </c>
       <c r="H98">
-        <v>0.9974930900000001</v>
+        <v>1.000177331</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="1">
-        <v>46154</v>
+        <v>46162</v>
       </c>
       <c r="B99" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C99">
-        <v>40.32854894972581</v>
+        <v>28.57911382310097</v>
       </c>
       <c r="D99">
-        <v>21.09133998298594</v>
+        <v>23.89431741541233</v>
       </c>
       <c r="E99">
-        <v>0.9990972199999999</v>
+        <v>0.999503734</v>
       </c>
       <c r="F99">
-        <v>0.9990972199999999</v>
+        <v>0.999503734</v>
       </c>
       <c r="G99">
-        <v>0.2156468205051487</v>
+        <v>0.04690190590044785</v>
       </c>
       <c r="H99">
-        <v>0.99752223</v>
+        <v>0.999503734</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="1">
-        <v>46155</v>
+        <v>46163</v>
       </c>
       <c r="B100" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C100">
-        <v>40.47987921095815</v>
+        <v>28.55785065378643</v>
       </c>
       <c r="D100">
-        <v>21.35995364434454</v>
+        <v>24.04274714970193</v>
       </c>
       <c r="E100">
-        <v>0.9991780100000001</v>
+        <v>1.000229282</v>
       </c>
       <c r="F100">
-        <v>0.9991780100000001</v>
+        <v>1.000229282</v>
       </c>
       <c r="G100">
-        <v>0.2270956128473374</v>
+        <v>0.05228572319419666</v>
       </c>
       <c r="H100">
-        <v>0.9975825700000001</v>
+        <v>1.000229282</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="1">
-        <v>46156</v>
+        <v>46164</v>
       </c>
       <c r="B101" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C101">
-        <v>41.20436574895244</v>
+        <v>28.50194638163107</v>
       </c>
       <c r="D101">
-        <v>21.48149674387778</v>
+        <v>23.99272397156045</v>
       </c>
       <c r="E101">
-        <v>0.9991793299999999</v>
+        <v>1</v>
       </c>
       <c r="F101">
-        <v>0.9991793299999999</v>
+        <v>1</v>
       </c>
       <c r="G101">
-        <v>0.2454829228401052</v>
+        <v>0.04934923597154284</v>
       </c>
       <c r="H101">
-        <v>0.99754722</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="1">
-        <v>46157</v>
+        <v>46167</v>
       </c>
       <c r="B102" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C102">
-        <v>40.80613062958688</v>
+        <v>28.55106858744498</v>
       </c>
       <c r="D102">
-        <v>21.08912555803936</v>
+        <v>23.9768329565351</v>
       </c>
       <c r="E102">
-        <v>0.9991790600000001</v>
+        <v>1</v>
       </c>
       <c r="F102">
-        <v>0.9991790600000001</v>
+        <v>1</v>
       </c>
       <c r="G102">
-        <v>0.2230017445022556</v>
+        <v>0.05571185335164408</v>
       </c>
       <c r="H102">
-        <v>0.9975824700000002</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="1">
-        <v>46160</v>
+        <v>46168</v>
       </c>
       <c r="B103" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C103">
-        <v>40.11672876026724</v>
+        <v>28.54681541456266</v>
       </c>
       <c r="D103">
-        <v>20.79541439916316</v>
+        <v>23.97386168967948</v>
       </c>
       <c r="E103">
-        <v>0.999152</v>
+        <v>1</v>
       </c>
       <c r="F103">
-        <v>0.999152</v>
+        <v>1</v>
       </c>
       <c r="G103">
-        <v>0.2098184021536666</v>
+        <v>0.04837034303541388</v>
       </c>
       <c r="H103">
-        <v>0.9975007899999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="1">
-        <v>46161</v>
+        <v>46169</v>
       </c>
       <c r="B104" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C104">
-        <v>39.69086941528401</v>
+        <v>28.83672936868491</v>
       </c>
       <c r="D104">
-        <v>20.74924328599426</v>
+        <v>24.203511281145</v>
       </c>
       <c r="E104">
-        <v>0.99914989</v>
+        <v>1</v>
       </c>
       <c r="F104">
-        <v>0.99914989</v>
+        <v>1</v>
       </c>
       <c r="G104">
-        <v>0.2020471776850241</v>
+        <v>0.05962723282507953</v>
       </c>
       <c r="H104">
-        <v>0.9974417</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="1">
-        <v>46162</v>
+        <v>46170</v>
       </c>
       <c r="B105" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C105">
-        <v>40.37836787855562</v>
+        <v>28.88109630394224</v>
       </c>
       <c r="D105">
-        <v>21.11271132314188</v>
+        <v>24.34085451035401</v>
       </c>
       <c r="E105">
-        <v>0.99915058</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F105">
-        <v>0.99915058</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G105">
-        <v>0.2291077670847563</v>
+        <v>0.06647938938594877</v>
       </c>
       <c r="H105">
-        <v>0.9974415600000001</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="1">
-        <v>46163</v>
+        <v>46153</v>
       </c>
       <c r="B106" t="s">
         <v>16</v>
       </c>
       <c r="C106">
-        <v>38.9123066967842</v>
+        <v>40.68830633303975</v>
       </c>
       <c r="D106">
-        <v>21.28910644207464</v>
+        <v>21.50431773660198</v>
       </c>
       <c r="E106">
-        <v>0.9989350699999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="F106">
-        <v>0.9989350699999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="G106">
-        <v>0.2392382040170877</v>
+        <v>0.2342423866086769</v>
       </c>
       <c r="H106">
-        <v>0.99726191</v>
+        <v>0.9974930900000001</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="1">
-        <v>46164</v>
+        <v>46154</v>
       </c>
       <c r="B107" t="s">
         <v>16</v>
       </c>
       <c r="C107">
-        <v>39.43913909150694</v>
+        <v>40.32854894972581</v>
       </c>
       <c r="D107">
-        <v>21.05297617141148</v>
+        <v>21.09133998298594</v>
       </c>
       <c r="E107">
-        <v>0.999144</v>
+        <v>0.9990972199999999</v>
       </c>
       <c r="F107">
-        <v>0.999144</v>
+        <v>0.9990972199999999</v>
       </c>
       <c r="G107">
-        <v>0.2516582935428642</v>
+        <v>0.2156468205051487</v>
       </c>
       <c r="H107">
-        <v>0.9974678400000001</v>
+        <v>0.99752223</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="1">
-        <v>46167</v>
+        <v>46155</v>
       </c>
       <c r="B108" t="s">
         <v>16</v>
       </c>
       <c r="C108">
-        <v>39.45782844313628</v>
+        <v>40.47987921095815</v>
       </c>
       <c r="D108">
-        <v>21.0518901572272</v>
+        <v>21.35995364434454</v>
       </c>
       <c r="E108">
-        <v>0.999144</v>
+        <v>0.9991780100000001</v>
       </c>
       <c r="F108">
-        <v>0.999144</v>
+        <v>0.9991780100000001</v>
       </c>
       <c r="G108">
-        <v>0.2516582935428642</v>
+        <v>0.2270956128473374</v>
       </c>
       <c r="H108">
-        <v>0.9974678400000001</v>
+        <v>0.9975825700000001</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="1">
-        <v>46168</v>
+        <v>46156</v>
       </c>
       <c r="B109" t="s">
         <v>16</v>
       </c>
       <c r="C109">
-        <v>40.20219297984542</v>
+        <v>41.20436574895244</v>
       </c>
       <c r="D109">
-        <v>21.93106024403281</v>
+        <v>21.48149674387778</v>
       </c>
       <c r="E109">
-        <v>0.9991421799999999</v>
+        <v>0.9991793299999999</v>
       </c>
       <c r="F109">
-        <v>0.9991421799999999</v>
+        <v>0.9991793299999999</v>
       </c>
       <c r="G109">
-        <v>0.2846167552893293</v>
+        <v>0.2454829228401052</v>
       </c>
       <c r="H109">
-        <v>0.9974609800000001</v>
+        <v>0.99754722</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="1">
-        <v>46169</v>
+        <v>46157</v>
       </c>
       <c r="B110" t="s">
         <v>16</v>
       </c>
       <c r="C110">
+        <v>40.80613062958688</v>
+      </c>
+      <c r="D110">
+        <v>21.08912555803936</v>
+      </c>
+      <c r="E110">
+        <v>0.9991790600000001</v>
+      </c>
+      <c r="F110">
+        <v>0.9991790600000001</v>
+      </c>
+      <c r="G110">
+        <v>0.2230017445022556</v>
+      </c>
+      <c r="H110">
+        <v>0.9975824700000002</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111">
+        <v>40.11672876026724</v>
+      </c>
+      <c r="D111">
+        <v>20.79541439916316</v>
+      </c>
+      <c r="E111">
+        <v>0.999152</v>
+      </c>
+      <c r="F111">
+        <v>0.999152</v>
+      </c>
+      <c r="G111">
+        <v>0.2098184021536666</v>
+      </c>
+      <c r="H111">
+        <v>0.9975007899999999</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112">
+        <v>39.69086941528401</v>
+      </c>
+      <c r="D112">
+        <v>20.74924328599426</v>
+      </c>
+      <c r="E112">
+        <v>0.99914989</v>
+      </c>
+      <c r="F112">
+        <v>0.99914989</v>
+      </c>
+      <c r="G112">
+        <v>0.2020471776850241</v>
+      </c>
+      <c r="H112">
+        <v>0.9974417</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113">
+        <v>40.37836787855562</v>
+      </c>
+      <c r="D113">
+        <v>21.11271132314188</v>
+      </c>
+      <c r="E113">
+        <v>0.99915058</v>
+      </c>
+      <c r="F113">
+        <v>0.99915058</v>
+      </c>
+      <c r="G113">
+        <v>0.2291077670847563</v>
+      </c>
+      <c r="H113">
+        <v>0.9974415600000001</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114">
+        <v>38.9123066967842</v>
+      </c>
+      <c r="D114">
+        <v>21.28910644207464</v>
+      </c>
+      <c r="E114">
+        <v>0.9989350699999999</v>
+      </c>
+      <c r="F114">
+        <v>0.9989350699999999</v>
+      </c>
+      <c r="G114">
+        <v>0.2392382040170877</v>
+      </c>
+      <c r="H114">
+        <v>0.99726191</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115" s="1">
+        <v>46164</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115">
+        <v>39.43913909150694</v>
+      </c>
+      <c r="D115">
+        <v>21.05297617141148</v>
+      </c>
+      <c r="E115">
+        <v>0.999144</v>
+      </c>
+      <c r="F115">
+        <v>0.999144</v>
+      </c>
+      <c r="G115">
+        <v>0.2516582935428642</v>
+      </c>
+      <c r="H115">
+        <v>0.9974678400000001</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116">
+        <v>39.45782844313628</v>
+      </c>
+      <c r="D116">
+        <v>21.0518901572272</v>
+      </c>
+      <c r="E116">
+        <v>0.999144</v>
+      </c>
+      <c r="F116">
+        <v>0.999144</v>
+      </c>
+      <c r="G116">
+        <v>0.2516582935428642</v>
+      </c>
+      <c r="H116">
+        <v>0.9974678400000001</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117">
+        <v>40.20219297984542</v>
+      </c>
+      <c r="D117">
+        <v>21.93106024403281</v>
+      </c>
+      <c r="E117">
+        <v>0.9991421799999999</v>
+      </c>
+      <c r="F117">
+        <v>0.9991421799999999</v>
+      </c>
+      <c r="G117">
+        <v>0.2846167552893293</v>
+      </c>
+      <c r="H117">
+        <v>0.9974609800000001</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118">
         <v>40.34993865302093</v>
       </c>
-      <c r="D110">
+      <c r="D118">
         <v>21.65366031776487</v>
       </c>
-      <c r="E110">
+      <c r="E118">
         <v>0.9991434600000001</v>
       </c>
-      <c r="F110">
+      <c r="F118">
         <v>0.9991434600000001</v>
       </c>
-      <c r="G110">
+      <c r="G118">
         <v>0.2796902860011767</v>
       </c>
-      <c r="H110">
+      <c r="H118">
         <v>0.9991434600000001</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119">
+        <v>40.5850485390846</v>
+      </c>
+      <c r="D119">
+        <v>21.75450977746074</v>
+      </c>
+      <c r="E119">
+        <v>0.99914592</v>
+      </c>
+      <c r="F119">
+        <v>0.99914592</v>
+      </c>
+      <c r="G119">
+        <v>0.2964818481030536</v>
+      </c>
+      <c r="H119">
+        <v>0.99914592</v>
       </c>
     </row>
   </sheetData>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="17">
   <si>
     <t>Date</t>
   </si>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H119"/>
+  <dimension ref="A1:H128"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -613,42 +613,42 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1">
-        <v>46153</v>
+        <v>46171</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>53.14833755912058</v>
+        <v>30.17828919906164</v>
       </c>
       <c r="D9">
-        <v>25.84885448407537</v>
+        <v>18.97854592273499</v>
       </c>
       <c r="E9">
-        <v>0.9262</v>
+        <v>0.8119</v>
       </c>
       <c r="F9">
-        <v>0.9262</v>
+        <v>0.8119</v>
       </c>
       <c r="G9">
-        <v>0.3839084462043663</v>
+        <v>0.6264282532438508</v>
       </c>
       <c r="H9">
-        <v>0.9262</v>
+        <v>0.9109999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
       </c>
       <c r="C10">
-        <v>51.82921169635205</v>
+        <v>53.14833755912058</v>
       </c>
       <c r="D10">
-        <v>25.32805827181975</v>
+        <v>25.84885448407537</v>
       </c>
       <c r="E10">
         <v>0.9262</v>
@@ -657,7 +657,7 @@
         <v>0.9262</v>
       </c>
       <c r="G10">
-        <v>0.3568580281685669</v>
+        <v>0.3839084462043663</v>
       </c>
       <c r="H10">
         <v>0.9262</v>
@@ -665,120 +665,120 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
       </c>
       <c r="C11">
-        <v>52.28471716753184</v>
+        <v>51.82921169635205</v>
       </c>
       <c r="D11">
-        <v>25.54525144150689</v>
+        <v>25.32805827181975</v>
       </c>
       <c r="E11">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="F11">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="G11">
-        <v>0.378012896547947</v>
+        <v>0.3568580281685669</v>
       </c>
       <c r="H11">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
       </c>
       <c r="C12">
-        <v>53.87287273813902</v>
+        <v>52.28471716753184</v>
       </c>
       <c r="D12">
-        <v>26.32154226438612</v>
+        <v>25.54525144150689</v>
       </c>
       <c r="E12">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="F12">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="G12">
-        <v>0.4166811087612758</v>
+        <v>0.378012896547947</v>
       </c>
       <c r="H12">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="B13" t="s">
         <v>9</v>
       </c>
       <c r="C13">
-        <v>52.18747148214074</v>
+        <v>53.87287273813902</v>
       </c>
       <c r="D13">
-        <v>25.13616059644496</v>
+        <v>26.32154226438612</v>
       </c>
       <c r="E13">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="F13">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="G13">
-        <v>0.3627535778249862</v>
+        <v>0.4166811087612758</v>
       </c>
       <c r="H13">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
       </c>
       <c r="C14">
-        <v>50.72035274995172</v>
+        <v>52.18747148214074</v>
       </c>
       <c r="D14">
-        <v>24.61756040386634</v>
+        <v>25.13616059644496</v>
       </c>
       <c r="E14">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="F14">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="G14">
         <v>0.3627535778249862</v>
       </c>
       <c r="H14">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
       </c>
       <c r="C15">
-        <v>50.11981086673613</v>
+        <v>50.72035274995172</v>
       </c>
       <c r="D15">
-        <v>24.13061679021705</v>
+        <v>24.61756040386634</v>
       </c>
       <c r="E15">
         <v>0.9259000000000001</v>
@@ -787,7 +787,7 @@
         <v>0.9259000000000001</v>
       </c>
       <c r="G15">
-        <v>0.3258193430227221</v>
+        <v>0.3627535778249862</v>
       </c>
       <c r="H15">
         <v>0.9259000000000001</v>
@@ -795,120 +795,120 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
       </c>
       <c r="C16">
-        <v>51.74165648409151</v>
+        <v>50.11981086673613</v>
       </c>
       <c r="D16">
-        <v>24.98091384114761</v>
+        <v>24.13061679021705</v>
       </c>
       <c r="E16">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="F16">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="G16">
-        <v>0.3818277262286871</v>
+        <v>0.3258193430227221</v>
       </c>
       <c r="H16">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
       </c>
       <c r="C17">
-        <v>49.13455894175823</v>
+        <v>51.74165648409151</v>
       </c>
       <c r="D17">
-        <v>25.30005057653127</v>
+        <v>24.98091384114761</v>
       </c>
       <c r="E17">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="F17">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="G17">
-        <v>0.4028091571787618</v>
+        <v>0.3818277262286871</v>
       </c>
       <c r="H17">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="B18" t="s">
         <v>9</v>
       </c>
       <c r="C18">
-        <v>49.57776597479297</v>
+        <v>49.13455894175823</v>
       </c>
       <c r="D18">
-        <v>25.04906725563518</v>
+        <v>25.30005057653127</v>
       </c>
       <c r="E18">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="F18">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="G18">
-        <v>0.4256980029692063</v>
+        <v>0.4028091571787618</v>
       </c>
       <c r="H18">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="B19" t="s">
         <v>9</v>
       </c>
       <c r="C19">
-        <v>49.71239596645896</v>
+        <v>49.57776597479297</v>
       </c>
       <c r="D19">
-        <v>25.18778610744295</v>
+        <v>25.04906725563518</v>
       </c>
       <c r="E19">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="F19">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="G19">
-        <v>0.4525749835757003</v>
+        <v>0.4256980029692063</v>
       </c>
       <c r="H19">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="B20" t="s">
         <v>9</v>
       </c>
       <c r="C20">
-        <v>50.77166277510776</v>
+        <v>49.71239596645896</v>
       </c>
       <c r="D20">
-        <v>25.7431782858765</v>
+        <v>25.18778610744295</v>
       </c>
       <c r="E20">
         <v>0.9231999999999999</v>
@@ -917,7 +917,7 @@
         <v>0.9231999999999999</v>
       </c>
       <c r="G20">
-        <v>0.4700884597036457</v>
+        <v>0.4525749835757003</v>
       </c>
       <c r="H20">
         <v>0.9231999999999999</v>
@@ -925,198 +925,198 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1">
-        <v>46169</v>
+        <v>46168</v>
       </c>
       <c r="B21" t="s">
         <v>9</v>
       </c>
       <c r="C21">
-        <v>50.57689164833899</v>
+        <v>50.77166277510776</v>
       </c>
       <c r="D21">
-        <v>25.70244067238947</v>
+        <v>25.7431782858765</v>
       </c>
       <c r="E21">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="F21">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="G21">
-        <v>0.4518814984464716</v>
+        <v>0.4700884597036457</v>
       </c>
       <c r="H21">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="B22" t="s">
         <v>9</v>
       </c>
       <c r="C22">
-        <v>50.80027854822009</v>
+        <v>50.57689164833899</v>
       </c>
       <c r="D22">
-        <v>25.90068415792015</v>
+        <v>25.70244067238947</v>
       </c>
       <c r="E22">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
       <c r="F22">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
       <c r="G22">
-        <v>0.4699150222743402</v>
+        <v>0.4518814984464716</v>
       </c>
       <c r="H22">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1">
-        <v>46153</v>
+        <v>46170</v>
       </c>
       <c r="B23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C23">
-        <v>34.64560932909123</v>
+        <v>50.80027854822009</v>
       </c>
       <c r="D23">
-        <v>26.08311546080494</v>
+        <v>25.90068415792015</v>
       </c>
       <c r="E23">
-        <v>0.9983000000000001</v>
+        <v>0.9231</v>
       </c>
       <c r="F23">
-        <v>0.9983000000000001</v>
+        <v>0.9231</v>
       </c>
       <c r="G23">
-        <v>0.06258613715048233</v>
+        <v>0.4699150222743402</v>
       </c>
       <c r="H23">
-        <v>0.9983000000000001</v>
+        <v>0.9231</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1">
-        <v>46154</v>
+        <v>46171</v>
       </c>
       <c r="B24" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C24">
-        <v>34.50204921141101</v>
+        <v>51.44563447241545</v>
       </c>
       <c r="D24">
-        <v>25.94535229304585</v>
+        <v>26.0970978996374</v>
       </c>
       <c r="E24">
-        <v>0.9984</v>
+        <v>0.9246</v>
       </c>
       <c r="F24">
-        <v>0.9984</v>
+        <v>0.9246</v>
       </c>
       <c r="G24">
-        <v>0.05768943168306073</v>
+        <v>0.4791053539115764</v>
       </c>
       <c r="H24">
-        <v>0.9984</v>
+        <v>0.9246</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="B25" t="s">
         <v>10</v>
       </c>
       <c r="C25">
-        <v>35.10429483281073</v>
+        <v>34.64560932909123</v>
       </c>
       <c r="D25">
-        <v>26.43864879939599</v>
+        <v>26.08311546080494</v>
       </c>
       <c r="E25">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="F25">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="G25">
-        <v>0.07926550001722021</v>
+        <v>0.06258613715048233</v>
       </c>
       <c r="H25">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="B26" t="s">
         <v>10</v>
       </c>
       <c r="C26">
-        <v>35.36860632820093</v>
+        <v>34.50204921141101</v>
       </c>
       <c r="D26">
-        <v>26.56575571102338</v>
+        <v>25.94535229304585</v>
       </c>
       <c r="E26">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F26">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G26">
-        <v>0.08553946591902095</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H26">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
       </c>
       <c r="C27">
-        <v>34.88080083527914</v>
+        <v>35.10429483281073</v>
       </c>
       <c r="D27">
-        <v>26.19322945679072</v>
+        <v>26.43864879939599</v>
       </c>
       <c r="E27">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="F27">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="G27">
-        <v>0.06870693142475881</v>
+        <v>0.07926550001722021</v>
       </c>
       <c r="H27">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1">
-        <v>46160</v>
+        <v>46156</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
       </c>
       <c r="C28">
-        <v>34.67638692539213</v>
+        <v>35.36860632820093</v>
       </c>
       <c r="D28">
-        <v>26.06707890342319</v>
+        <v>26.56575571102338</v>
       </c>
       <c r="E28">
         <v>0.9985999999999999</v>
@@ -1125,7 +1125,7 @@
         <v>0.9985999999999999</v>
       </c>
       <c r="G28">
-        <v>0.06289213016552919</v>
+        <v>0.08553946591902095</v>
       </c>
       <c r="H28">
         <v>0.9985999999999999</v>
@@ -1133,120 +1133,120 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="B29" t="s">
         <v>10</v>
       </c>
       <c r="C29">
-        <v>34.21212662725402</v>
+        <v>34.88080083527914</v>
       </c>
       <c r="D29">
-        <v>25.60349394367002</v>
+        <v>26.19322945679072</v>
       </c>
       <c r="E29">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="F29">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="G29">
-        <v>0.0486610616591685</v>
+        <v>0.06870693142475881</v>
       </c>
       <c r="H29">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="B30" t="s">
         <v>10</v>
       </c>
       <c r="C30">
-        <v>34.78598436564941</v>
+        <v>34.67638692539213</v>
       </c>
       <c r="D30">
-        <v>25.95505316769806</v>
+        <v>26.06707890342319</v>
       </c>
       <c r="E30">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="F30">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="G30">
-        <v>0.06335117806143331</v>
+        <v>0.06289213016552919</v>
       </c>
       <c r="H30">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1">
-        <v>46163</v>
+        <v>46161</v>
       </c>
       <c r="B31" t="s">
         <v>10</v>
       </c>
       <c r="C31">
-        <v>33.4539909056227</v>
+        <v>34.21212662725402</v>
       </c>
       <c r="D31">
-        <v>25.96014535427112</v>
+        <v>25.60349394367002</v>
       </c>
       <c r="E31">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="F31">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="G31">
-        <v>0.06350423294229035</v>
+        <v>0.0486610616591685</v>
       </c>
       <c r="H31">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1">
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
       </c>
       <c r="C32">
-        <v>33.24951933563993</v>
+        <v>34.78598436564941</v>
       </c>
       <c r="D32">
-        <v>25.46629530314992</v>
+        <v>25.95505316769806</v>
       </c>
       <c r="E32">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="F32">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="G32">
-        <v>0.06136193159696024</v>
+        <v>0.06335117806143331</v>
       </c>
       <c r="H32">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1">
-        <v>46167</v>
+        <v>46163</v>
       </c>
       <c r="B33" t="s">
         <v>10</v>
       </c>
       <c r="C33">
-        <v>33.29896419867477</v>
+        <v>33.4539909056227</v>
       </c>
       <c r="D33">
-        <v>25.45090185337973</v>
+        <v>25.96014535427112</v>
       </c>
       <c r="E33">
         <v>0.9984</v>
@@ -1255,7 +1255,7 @@
         <v>0.9984</v>
       </c>
       <c r="G33">
-        <v>0.06136193159696024</v>
+        <v>0.06350423294229035</v>
       </c>
       <c r="H33">
         <v>0.9984</v>
@@ -1263,16 +1263,16 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1">
-        <v>46168</v>
+        <v>46164</v>
       </c>
       <c r="B34" t="s">
         <v>10</v>
       </c>
       <c r="C34">
-        <v>33.41270923608511</v>
+        <v>33.24951933563993</v>
       </c>
       <c r="D34">
-        <v>25.54156152389702</v>
+        <v>25.46629530314992</v>
       </c>
       <c r="E34">
         <v>0.9984</v>
@@ -1281,7 +1281,7 @@
         <v>0.9984</v>
       </c>
       <c r="G34">
-        <v>0.06549347940676342</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H34">
         <v>0.9984</v>
@@ -1289,562 +1289,562 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1">
-        <v>46169</v>
+        <v>46167</v>
       </c>
       <c r="B35" t="s">
         <v>10</v>
       </c>
       <c r="C35">
-        <v>33.73350746548562</v>
+        <v>33.29896419867477</v>
       </c>
       <c r="D35">
-        <v>25.75393367034243</v>
+        <v>25.45090185337973</v>
       </c>
       <c r="E35">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="F35">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="G35">
-        <v>0.07620510288008187</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H35">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1">
-        <v>46170</v>
+        <v>46168</v>
       </c>
       <c r="B36" t="s">
         <v>10</v>
       </c>
       <c r="C36">
-        <v>33.84336414535104</v>
+        <v>33.41270923608511</v>
       </c>
       <c r="D36">
-        <v>25.97168203877208</v>
+        <v>25.54156152389702</v>
       </c>
       <c r="E36">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
       <c r="F36">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
       <c r="G36">
-        <v>0.0844683152463559</v>
+        <v>0.06549347940676342</v>
       </c>
       <c r="H36">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1">
-        <v>46153</v>
+        <v>46169</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C37">
-        <v>36.55790859258162</v>
+        <v>33.73350746548562</v>
       </c>
       <c r="D37">
-        <v>22.67181120908155</v>
+        <v>25.75393367034243</v>
       </c>
       <c r="E37">
-        <v>0.9990740999999999</v>
+        <v>0.9987000000000001</v>
       </c>
       <c r="F37">
-        <v>0.9990740999999999</v>
+        <v>0.9987000000000001</v>
       </c>
       <c r="G37">
-        <v>0.1648443271746771</v>
+        <v>0.07620510288008187</v>
       </c>
       <c r="H37">
-        <v>0.9990740999999999</v>
+        <v>0.9987000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1">
-        <v>46154</v>
+        <v>46170</v>
       </c>
       <c r="B38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C38">
-        <v>36.44753722959613</v>
+        <v>33.84336414535104</v>
       </c>
       <c r="D38">
-        <v>22.40292401789388</v>
+        <v>25.97168203877208</v>
       </c>
       <c r="E38">
-        <v>0.9990772499999999</v>
+        <v>0.9988</v>
       </c>
       <c r="F38">
-        <v>0.9990772499999999</v>
+        <v>0.9988</v>
       </c>
       <c r="G38">
-        <v>0.154964342628132</v>
+        <v>0.0844683152463559</v>
       </c>
       <c r="H38">
-        <v>0.9990772499999999</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1">
-        <v>46155</v>
+        <v>46171</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C39">
-        <v>36.63128514035871</v>
+        <v>33.73370320039719</v>
       </c>
       <c r="D39">
-        <v>22.65773388934668</v>
+        <v>25.880209881309</v>
       </c>
       <c r="E39">
-        <v>0.99907745</v>
+        <v>0.9988</v>
       </c>
       <c r="F39">
-        <v>0.99907745</v>
+        <v>0.9988</v>
       </c>
       <c r="G39">
-        <v>0.1671633421405267</v>
+        <v>0.08201990413931148</v>
       </c>
       <c r="H39">
-        <v>0.99907745</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="B40" t="s">
         <v>11</v>
       </c>
       <c r="C40">
-        <v>36.87865927427314</v>
+        <v>36.55790859258162</v>
       </c>
       <c r="D40">
-        <v>22.69755646854794</v>
+        <v>22.67181120908155</v>
       </c>
       <c r="E40">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="F40">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="G40">
-        <v>0.1754592080224002</v>
+        <v>0.1648443271746771</v>
       </c>
       <c r="H40">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="B41" t="s">
         <v>11</v>
       </c>
       <c r="C41">
-        <v>36.52208783231286</v>
+        <v>36.44753722959613</v>
       </c>
       <c r="D41">
-        <v>22.32462309676992</v>
+        <v>22.40292401789388</v>
       </c>
       <c r="E41">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="F41">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="G41">
-        <v>0.1577242156354994</v>
+        <v>0.154964342628132</v>
       </c>
       <c r="H41">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="B42" t="s">
         <v>11</v>
       </c>
       <c r="C42">
-        <v>36.25604200674668</v>
+        <v>36.63128514035871</v>
       </c>
       <c r="D42">
-        <v>22.16555007468561</v>
+        <v>22.65773388934668</v>
       </c>
       <c r="E42">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="F42">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="G42">
-        <v>0.1527434068648266</v>
+        <v>0.1671633421405267</v>
       </c>
       <c r="H42">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1">
-        <v>46161</v>
+        <v>46156</v>
       </c>
       <c r="B43" t="s">
         <v>11</v>
       </c>
       <c r="C43">
-        <v>36.01040085730018</v>
+        <v>36.87865927427314</v>
       </c>
       <c r="D43">
-        <v>22.19475589056387</v>
+        <v>22.69755646854794</v>
       </c>
       <c r="E43">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="F43">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="G43">
-        <v>0.1456396418594061</v>
+        <v>0.1754592080224002</v>
       </c>
       <c r="H43">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1">
-        <v>46162</v>
+        <v>46157</v>
       </c>
       <c r="B44" t="s">
         <v>11</v>
       </c>
       <c r="C44">
-        <v>36.45290912796982</v>
+        <v>36.52208783231286</v>
       </c>
       <c r="D44">
-        <v>22.46357594746874</v>
+        <v>22.32462309676992</v>
       </c>
       <c r="E44">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="F44">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="G44">
-        <v>0.1646157747240327</v>
+        <v>0.1577242156354994</v>
       </c>
       <c r="H44">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1">
-        <v>46163</v>
+        <v>46160</v>
       </c>
       <c r="B45" t="s">
         <v>11</v>
       </c>
       <c r="C45">
-        <v>35.75282090566891</v>
+        <v>36.25604200674668</v>
       </c>
       <c r="D45">
-        <v>22.57615417310648</v>
+        <v>22.16555007468561</v>
       </c>
       <c r="E45">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="F45">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="G45">
-        <v>0.1668367104873381</v>
+        <v>0.1527434068648266</v>
       </c>
       <c r="H45">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1">
-        <v>46164</v>
+        <v>46161</v>
       </c>
       <c r="B46" t="s">
         <v>11</v>
       </c>
       <c r="C46">
-        <v>35.75514940724808</v>
+        <v>36.01040085730018</v>
       </c>
       <c r="D46">
-        <v>22.28880693466429</v>
+        <v>22.19475589056387</v>
       </c>
       <c r="E46">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="F46">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="G46">
-        <v>0.1717848261904962</v>
+        <v>0.1456396418594061</v>
       </c>
       <c r="H46">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1">
-        <v>46167</v>
+        <v>46162</v>
       </c>
       <c r="B47" t="s">
         <v>11</v>
       </c>
       <c r="C47">
-        <v>35.84133099010302</v>
+        <v>36.45290912796982</v>
       </c>
       <c r="D47">
-        <v>22.37458514769363</v>
+        <v>22.46357594746874</v>
       </c>
       <c r="E47">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="F47">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="G47">
-        <v>0.1717848261904962</v>
+        <v>0.1646157747240327</v>
       </c>
       <c r="H47">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1">
-        <v>46168</v>
+        <v>46163</v>
       </c>
       <c r="B48" t="s">
         <v>11</v>
       </c>
       <c r="C48">
-        <v>36.23214279739292</v>
+        <v>35.75282090566891</v>
       </c>
       <c r="D48">
-        <v>22.93484792820123</v>
+        <v>22.57615417310648</v>
       </c>
       <c r="E48">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
       <c r="F48">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
       <c r="G48">
-        <v>0.1925900763781823</v>
+        <v>0.1668367104873381</v>
       </c>
       <c r="H48">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="B49" t="s">
         <v>11</v>
       </c>
       <c r="C49">
-        <v>36.4336692499184</v>
+        <v>35.75514940724808</v>
       </c>
       <c r="D49">
-        <v>22.75940954009856</v>
+        <v>22.28880693466429</v>
       </c>
       <c r="E49">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="F49">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="G49">
-        <v>0.1912346098381414</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H49">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="B50" t="s">
         <v>11</v>
       </c>
       <c r="C50">
-        <v>36.57358557066742</v>
+        <v>35.84133099010302</v>
       </c>
       <c r="D50">
-        <v>22.83069636955243</v>
+        <v>22.37458514769363</v>
       </c>
       <c r="E50">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="F50">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="G50">
-        <v>0.2012778603742877</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H50">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1">
-        <v>46153</v>
+        <v>46168</v>
       </c>
       <c r="B51" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C51">
-        <v>52.70832779833182</v>
+        <v>36.23214279739292</v>
       </c>
       <c r="D51">
-        <v>23.99044674439659</v>
+        <v>22.93484792820123</v>
       </c>
       <c r="E51">
-        <v>0.9994000000000002</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="F51">
-        <v>0.9994000000000002</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="G51">
-        <v>0.5438253854918791</v>
+        <v>0.1925900763781823</v>
       </c>
       <c r="H51">
-        <v>0.9994000000000002</v>
+        <v>0.9992609200000001</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1">
-        <v>46154</v>
+        <v>46169</v>
       </c>
       <c r="B52" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C52">
-        <v>50.89464485280568</v>
+        <v>36.4336692499184</v>
       </c>
       <c r="D52">
-        <v>23.21558303176282</v>
+        <v>22.75940954009856</v>
       </c>
       <c r="E52">
-        <v>0.9996</v>
+        <v>0.9992099400000001</v>
       </c>
       <c r="F52">
-        <v>0.9996</v>
+        <v>0.9992099400000001</v>
       </c>
       <c r="G52">
-        <v>0.5034825029548833</v>
+        <v>0.1912346098381414</v>
       </c>
       <c r="H52">
-        <v>0.9996</v>
+        <v>0.9992099400000001</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1">
-        <v>46155</v>
+        <v>46170</v>
       </c>
       <c r="B53" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C53">
-        <v>51.8659994471731</v>
+        <v>36.57358557066742</v>
       </c>
       <c r="D53">
-        <v>23.7009037279043</v>
+        <v>22.83069636955243</v>
       </c>
       <c r="E53">
-        <v>1.0002</v>
+        <v>0.9994435600000001</v>
       </c>
       <c r="F53">
-        <v>1.0002</v>
+        <v>0.9994435600000001</v>
       </c>
       <c r="G53">
-        <v>0.533512029714132</v>
+        <v>0.2012778603742877</v>
       </c>
       <c r="H53">
-        <v>1.0002</v>
+        <v>0.9994435600000001</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1">
-        <v>46156</v>
+        <v>46171</v>
       </c>
       <c r="B54" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C54">
-        <v>52.4470179952828</v>
+        <v>36.67481300942</v>
       </c>
       <c r="D54">
-        <v>23.76861704536814</v>
+        <v>22.95852861681004</v>
       </c>
       <c r="E54">
-        <v>0.9998</v>
+        <v>0.9964953299999998</v>
       </c>
       <c r="F54">
-        <v>0.9998</v>
+        <v>0.9964953299999998</v>
       </c>
       <c r="G54">
-        <v>0.5492634496849078</v>
+        <v>0.2057034850411275</v>
       </c>
       <c r="H54">
-        <v>0.9998</v>
+        <v>0.9994474899999999</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="B55" t="s">
         <v>12</v>
       </c>
       <c r="C55">
-        <v>50.81077380018606</v>
+        <v>52.70832779833182</v>
       </c>
       <c r="D55">
-        <v>22.76900580927995</v>
+        <v>23.99044674439659</v>
       </c>
       <c r="E55">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="F55">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="G55">
-        <v>0.4903296143797722</v>
+        <v>0.5438253854918791</v>
       </c>
       <c r="H55">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1">
-        <v>46160</v>
+        <v>46154</v>
       </c>
       <c r="B56" t="s">
         <v>12</v>
       </c>
       <c r="C56">
-        <v>49.50286387149169</v>
+        <v>50.89464485280568</v>
       </c>
       <c r="D56">
-        <v>22.24532119914133</v>
+        <v>23.21558303176282</v>
       </c>
       <c r="E56">
         <v>0.9996</v>
@@ -1853,7 +1853,7 @@
         <v>0.9996</v>
       </c>
       <c r="G56">
-        <v>0.4630591776162345</v>
+        <v>0.5034825029548833</v>
       </c>
       <c r="H56">
         <v>0.9996</v>
@@ -1861,1186 +1861,1186 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1">
-        <v>46161</v>
+        <v>46155</v>
       </c>
       <c r="B57" t="s">
         <v>12</v>
       </c>
       <c r="C57">
-        <v>49.29146729279496</v>
+        <v>51.8659994471731</v>
       </c>
       <c r="D57">
-        <v>22.22167836589682</v>
+        <v>23.7009037279043</v>
       </c>
       <c r="E57">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="F57">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="G57">
-        <v>0.4571659248870246</v>
+        <v>0.533512029714132</v>
       </c>
       <c r="H57">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1">
-        <v>46162</v>
+        <v>46156</v>
       </c>
       <c r="B58" t="s">
         <v>12</v>
       </c>
       <c r="C58">
-        <v>50.88652370817657</v>
+        <v>52.4470179952828</v>
       </c>
       <c r="D58">
-        <v>22.93254398967657</v>
+        <v>23.76861704536814</v>
       </c>
       <c r="E58">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F58">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G58">
-        <v>0.5126171754864624</v>
+        <v>0.5492634496849078</v>
       </c>
       <c r="H58">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1">
-        <v>46163</v>
+        <v>46157</v>
       </c>
       <c r="B59" t="s">
         <v>12</v>
       </c>
       <c r="C59">
-        <v>48.26646764818586</v>
+        <v>50.81077380018606</v>
       </c>
       <c r="D59">
-        <v>23.11655387625012</v>
+        <v>22.76900580927995</v>
       </c>
       <c r="E59">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="F59">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="G59">
-        <v>0.521243030947425</v>
+        <v>0.4903296143797722</v>
       </c>
       <c r="H59">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1">
-        <v>46164</v>
+        <v>46160</v>
       </c>
       <c r="B60" t="s">
         <v>12</v>
       </c>
       <c r="C60">
-        <v>48.84737503703267</v>
+        <v>49.50286387149169</v>
       </c>
       <c r="D60">
-        <v>22.83557604744466</v>
+        <v>22.24532119914133</v>
       </c>
       <c r="E60">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="F60">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="G60">
-        <v>0.5438521997590966</v>
+        <v>0.4630591776162345</v>
       </c>
       <c r="H60">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1">
-        <v>46167</v>
+        <v>46161</v>
       </c>
       <c r="B61" t="s">
         <v>12</v>
       </c>
       <c r="C61">
-        <v>48.85151560750146</v>
+        <v>49.29146729279496</v>
       </c>
       <c r="D61">
-        <v>22.83513820206554</v>
+        <v>22.22167836589682</v>
       </c>
       <c r="E61">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F61">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G61">
-        <v>0.5438521997590966</v>
+        <v>0.4571659248870246</v>
       </c>
       <c r="H61">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1">
-        <v>46168</v>
+        <v>46162</v>
       </c>
       <c r="B62" t="s">
         <v>12</v>
       </c>
       <c r="C62">
-        <v>50.90437883274981</v>
+        <v>50.88652370817657</v>
       </c>
       <c r="D62">
-        <v>24.25672473501501</v>
+        <v>22.93254398967657</v>
       </c>
       <c r="E62">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F62">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G62">
-        <v>0.6130191115419561</v>
+        <v>0.5126171754864624</v>
       </c>
       <c r="H62">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1">
-        <v>46169</v>
+        <v>46163</v>
       </c>
       <c r="B63" t="s">
         <v>12</v>
       </c>
       <c r="C63">
-        <v>50.47312432255841</v>
+        <v>48.26646764818586</v>
       </c>
       <c r="D63">
-        <v>23.84499305142194</v>
+        <v>23.11655387625012</v>
       </c>
       <c r="E63">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="F63">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="G63">
-        <v>0.5952317692821967</v>
+        <v>0.521243030947425</v>
       </c>
       <c r="H63">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1">
-        <v>46170</v>
+        <v>46164</v>
       </c>
       <c r="B64" t="s">
         <v>12</v>
       </c>
       <c r="C64">
-        <v>50.84596269629946</v>
+        <v>48.84737503703267</v>
       </c>
       <c r="D64">
-        <v>23.7680603326165</v>
+        <v>22.83557604744466</v>
       </c>
       <c r="E64">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F64">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G64">
-        <v>0.606831065374982</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H64">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="B65" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C65">
-        <v>57.1732166855686</v>
+        <v>48.85151560750146</v>
       </c>
       <c r="D65">
-        <v>23.50022751267814</v>
+        <v>22.83513820206554</v>
       </c>
       <c r="E65">
-        <v>0.9991</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F65">
-        <v>0.9991</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G65">
-        <v>0.6994110097039083</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H65">
-        <v>0.9991</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1">
-        <v>46154</v>
+        <v>46168</v>
       </c>
       <c r="B66" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C66">
-        <v>54.77380642078597</v>
+        <v>50.90437883274981</v>
       </c>
       <c r="D66">
-        <v>22.55192940254518</v>
+        <v>24.25672473501501</v>
       </c>
       <c r="E66">
-        <v>0.9990000000000001</v>
+        <v>0.9996999999999999</v>
       </c>
       <c r="F66">
-        <v>0.9990000000000001</v>
+        <v>0.9996999999999999</v>
       </c>
       <c r="G66">
-        <v>0.6459175880844941</v>
+        <v>0.6130191115419561</v>
       </c>
       <c r="H66">
-        <v>0.9990000000000001</v>
+        <v>0.9996999999999999</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1">
-        <v>46155</v>
+        <v>46169</v>
       </c>
       <c r="B67" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C67">
-        <v>56.32187380830906</v>
+        <v>50.47312432255841</v>
       </c>
       <c r="D67">
-        <v>23.17121437414109</v>
+        <v>23.84499305142194</v>
       </c>
       <c r="E67">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
       <c r="F67">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
       <c r="G67">
-        <v>0.6851523922954754</v>
+        <v>0.5952317692821967</v>
       </c>
       <c r="H67">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1">
-        <v>46156</v>
+        <v>46170</v>
       </c>
       <c r="B68" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C68">
-        <v>56.15321618553139</v>
+        <v>50.84596269629946</v>
       </c>
       <c r="D68">
-        <v>22.95838347314443</v>
+        <v>23.7680603326165</v>
       </c>
       <c r="E68">
-        <v>0.9992</v>
+        <v>0.9998</v>
       </c>
       <c r="F68">
-        <v>0.9992</v>
+        <v>0.9998</v>
       </c>
       <c r="G68">
-        <v>0.6907028507208208</v>
+        <v>0.606831065374982</v>
       </c>
       <c r="H68">
-        <v>0.9992</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1">
-        <v>46157</v>
+        <v>46171</v>
       </c>
       <c r="B69" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C69">
-        <v>54.47755813049488</v>
+        <v>51.08372269965196</v>
       </c>
       <c r="D69">
-        <v>22.0083816089626</v>
+        <v>23.88880359436525</v>
       </c>
       <c r="E69">
-        <v>0.9986</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F69">
-        <v>0.9986</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G69">
-        <v>0.6220895940829376</v>
+        <v>0.604420070348211</v>
       </c>
       <c r="H69">
-        <v>0.9986</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
       </c>
       <c r="C70">
-        <v>52.6278781150669</v>
+        <v>57.1732166855686</v>
       </c>
       <c r="D70">
-        <v>21.5357353870778</v>
+        <v>23.50022751267814</v>
       </c>
       <c r="E70">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F70">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G70">
-        <v>0.5845134636435627</v>
+        <v>0.6994110097039083</v>
       </c>
       <c r="H70">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
       </c>
       <c r="C71">
-        <v>54.91583234840245</v>
+        <v>54.77380642078597</v>
       </c>
       <c r="D71">
-        <v>22.38321645985006</v>
+        <v>22.55192940254518</v>
       </c>
       <c r="E71">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F71">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G71">
-        <v>0.6596976539194066</v>
+        <v>0.6459175880844941</v>
       </c>
       <c r="H71">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
       </c>
       <c r="C72">
-        <v>53.91712298548793</v>
+        <v>56.32187380830906</v>
       </c>
       <c r="D72">
-        <v>22.73711181201267</v>
+        <v>23.17121437414109</v>
       </c>
       <c r="E72">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F72">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G72">
-        <v>0.6737329602396263</v>
+        <v>0.6851523922954754</v>
       </c>
       <c r="H72">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
       </c>
       <c r="C73">
-        <v>55.19651747515625</v>
+        <v>56.15321618553139</v>
       </c>
       <c r="D73">
-        <v>22.79462037330554</v>
+        <v>22.95838347314443</v>
       </c>
       <c r="E73">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
       <c r="F73">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
       <c r="G73">
-        <v>0.7139885317003913</v>
+        <v>0.6907028507208208</v>
       </c>
       <c r="H73">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
       </c>
       <c r="C74">
-        <v>55.28054997487197</v>
+        <v>54.47755813049488</v>
       </c>
       <c r="D74">
-        <v>23.00160891539877</v>
+        <v>22.0083816089626</v>
       </c>
       <c r="E74">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="F74">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="G74">
-        <v>0.7139885317003913</v>
+        <v>0.6220895940829376</v>
       </c>
       <c r="H74">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1">
-        <v>46168</v>
+        <v>46161</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
       </c>
       <c r="C75">
-        <v>58.75156728873073</v>
+        <v>52.6278781150669</v>
       </c>
       <c r="D75">
-        <v>24.84249654093248</v>
+        <v>21.5357353870778</v>
       </c>
       <c r="E75">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="F75">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="G75">
-        <v>0.8184872182632257</v>
+        <v>0.5845134636435627</v>
       </c>
       <c r="H75">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1">
-        <v>46169</v>
+        <v>46162</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
       </c>
       <c r="C76">
-        <v>57.86771234337395</v>
+        <v>54.91583234840245</v>
       </c>
       <c r="D76">
-        <v>24.21066615243091</v>
+        <v>22.38321645985006</v>
       </c>
       <c r="E76">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="F76">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="G76">
-        <v>0.798997241708943</v>
+        <v>0.6596976539194066</v>
       </c>
       <c r="H76">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1">
-        <v>46170</v>
+        <v>46163</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
       </c>
       <c r="C77">
-        <v>58.18666682631797</v>
+        <v>53.91712298548793</v>
       </c>
       <c r="D77">
-        <v>24.09552344282839</v>
+        <v>22.73711181201267</v>
       </c>
       <c r="E77">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="F77">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="G77">
-        <v>0.8165093478664007</v>
+        <v>0.6737329602396263</v>
       </c>
       <c r="H77">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="1">
-        <v>46153</v>
+        <v>46164</v>
       </c>
       <c r="B78" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C78">
-        <v>35.78646526282436</v>
+        <v>55.19651747515625</v>
       </c>
       <c r="D78">
-        <v>18.96635091925032</v>
+        <v>22.79462037330554</v>
       </c>
       <c r="E78">
-        <v>0.9996491399999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F78">
-        <v>0.9996491399999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G78">
-        <v>0.2240600969213613</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H78">
-        <v>0.9985614899999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1">
-        <v>46154</v>
+        <v>46167</v>
       </c>
       <c r="B79" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C79">
-        <v>35.71584102184062</v>
+        <v>55.28054997487197</v>
       </c>
       <c r="D79">
-        <v>18.62432950231353</v>
+        <v>23.00160891539877</v>
       </c>
       <c r="E79">
-        <v>0.99965481</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="F79">
-        <v>0.99965481</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="G79">
-        <v>0.2104844827747143</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H79">
-        <v>0.9985622199999999</v>
+        <v>0.9989000000000001</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1">
-        <v>46155</v>
+        <v>46168</v>
       </c>
       <c r="B80" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C80">
-        <v>35.95182028203252</v>
+        <v>58.75156728873073</v>
       </c>
       <c r="D80">
-        <v>18.95670796791552</v>
+        <v>24.84249654093248</v>
       </c>
       <c r="E80">
-        <v>0.9996515200000001</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="F80">
-        <v>0.9996515200000001</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="G80">
-        <v>0.2259035693959275</v>
+        <v>0.8184872182632257</v>
       </c>
       <c r="H80">
-        <v>0.99855193</v>
+        <v>0.9989000000000001</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="1">
-        <v>46156</v>
+        <v>46169</v>
       </c>
       <c r="B81" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C81">
-        <v>36.14451597805883</v>
+        <v>57.86771234337395</v>
       </c>
       <c r="D81">
-        <v>18.86297660538653</v>
+        <v>24.21066615243091</v>
       </c>
       <c r="E81">
-        <v>0.9996563399999999</v>
+        <v>0.9986999999999999</v>
       </c>
       <c r="F81">
-        <v>0.9996563399999999</v>
+        <v>0.9986999999999999</v>
       </c>
       <c r="G81">
-        <v>0.2362110061840785</v>
+        <v>0.798997241708943</v>
       </c>
       <c r="H81">
-        <v>0.99857265</v>
+        <v>0.9986999999999999</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="1">
-        <v>46157</v>
+        <v>46170</v>
       </c>
       <c r="B82" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C82">
-        <v>35.32805803135546</v>
+        <v>58.18666682631797</v>
       </c>
       <c r="D82">
-        <v>18.35643242381478</v>
+        <v>24.09552344282839</v>
       </c>
       <c r="E82">
-        <v>0.9997415800000001</v>
+        <v>0.9991</v>
       </c>
       <c r="F82">
-        <v>0.9997415800000001</v>
+        <v>0.9991</v>
       </c>
       <c r="G82">
-        <v>0.2023559161375383</v>
+        <v>0.8165093478664007</v>
       </c>
       <c r="H82">
-        <v>0.9986639900000002</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="1">
-        <v>46160</v>
+        <v>46171</v>
       </c>
       <c r="B83" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C83">
-        <v>34.83995455757461</v>
+        <v>58.79256019733606</v>
       </c>
       <c r="D83">
-        <v>18.02301281718857</v>
+        <v>24.33854853448823</v>
       </c>
       <c r="E83">
-        <v>0.9996851299999999</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="F83">
-        <v>0.9996851299999999</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="G83">
-        <v>0.1850932291737926</v>
+        <v>0.8152654642198496</v>
       </c>
       <c r="H83">
-        <v>0.99857724</v>
+        <v>0.9989999999999999</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B84" t="s">
         <v>14</v>
       </c>
       <c r="C84">
-        <v>34.45479308705605</v>
+        <v>35.78646526282436</v>
       </c>
       <c r="D84">
-        <v>18.09576834566068</v>
+        <v>18.96635091925032</v>
       </c>
       <c r="E84">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="F84">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="G84">
-        <v>0.1784731209386736</v>
+        <v>0.2240600969213613</v>
       </c>
       <c r="H84">
-        <v>0.9985337599999999</v>
+        <v>0.9985614899999999</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B85" t="s">
         <v>14</v>
       </c>
       <c r="C85">
-        <v>34.96336277390787</v>
+        <v>35.71584102184062</v>
       </c>
       <c r="D85">
-        <v>18.34938420029253</v>
+        <v>18.62432950231353</v>
       </c>
       <c r="E85">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="F85">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="G85">
-        <v>0.2009313391215752</v>
+        <v>0.2104844827747143</v>
       </c>
       <c r="H85">
-        <v>0.99848777</v>
+        <v>0.9985622199999999</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B86" t="s">
         <v>14</v>
       </c>
       <c r="C86">
-        <v>34.44616924817128</v>
+        <v>35.95182028203252</v>
       </c>
       <c r="D86">
-        <v>18.60085625074367</v>
+        <v>18.95670796791552</v>
       </c>
       <c r="E86">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="F86">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="G86">
-        <v>0.2124957180214682</v>
+        <v>0.2259035693959275</v>
       </c>
       <c r="H86">
-        <v>0.9985085200000001</v>
+        <v>0.99855193</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="1">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="B87" t="s">
         <v>14</v>
       </c>
       <c r="C87">
-        <v>34.62137220937314</v>
+        <v>36.14451597805883</v>
       </c>
       <c r="D87">
-        <v>18.28780484745949</v>
+        <v>18.86297660538653</v>
       </c>
       <c r="E87">
-        <v>0.9996106299999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="F87">
-        <v>0.9996106299999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="G87">
-        <v>0.2145907067863493</v>
+        <v>0.2362110061840785</v>
       </c>
       <c r="H87">
-        <v>0.9932939299999999</v>
+        <v>0.99857265</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="B88" t="s">
         <v>14</v>
       </c>
       <c r="C88">
-        <v>34.6540695486741</v>
+        <v>35.32805803135546</v>
       </c>
       <c r="D88">
-        <v>18.36409048915342</v>
+        <v>18.35643242381478</v>
       </c>
       <c r="E88">
-        <v>0.9995448900000001</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="F88">
-        <v>0.9995448900000001</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="G88">
-        <v>0.2145907067863493</v>
+        <v>0.2023559161375383</v>
       </c>
       <c r="H88">
-        <v>0.9984302600000001</v>
+        <v>0.9986639900000002</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="1">
-        <v>46168</v>
+        <v>46160</v>
       </c>
       <c r="B89" t="s">
         <v>14</v>
       </c>
       <c r="C89">
-        <v>35.4820130509417</v>
+        <v>34.83995455757461</v>
       </c>
       <c r="D89">
-        <v>19.20292041814603</v>
+        <v>18.02301281718857</v>
       </c>
       <c r="E89">
-        <v>0.9995448900000001</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="F89">
-        <v>0.9995448900000001</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="G89">
-        <v>0.2553172934903569</v>
+        <v>0.1850932291737926</v>
       </c>
       <c r="H89">
-        <v>0.9984302600000001</v>
+        <v>0.99857724</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="1">
-        <v>46169</v>
+        <v>46161</v>
       </c>
       <c r="B90" t="s">
         <v>14</v>
       </c>
       <c r="C90">
-        <v>35.71913468603401</v>
+        <v>34.45479308705605</v>
       </c>
       <c r="D90">
-        <v>18.96318693998171</v>
+        <v>18.09576834566068</v>
       </c>
       <c r="E90">
-        <v>0.99955466</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="F90">
-        <v>0.99955466</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="G90">
-        <v>0.2536413280520453</v>
+        <v>0.1784731209386736</v>
       </c>
       <c r="H90">
-        <v>0.9984700500000001</v>
+        <v>0.9985337599999999</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="1">
-        <v>46170</v>
+        <v>46162</v>
       </c>
       <c r="B91" t="s">
         <v>14</v>
       </c>
       <c r="C91">
-        <v>35.76226417354731</v>
+        <v>34.96336277390787</v>
       </c>
       <c r="D91">
-        <v>18.89050847207122</v>
+        <v>18.34938420029253</v>
       </c>
       <c r="E91">
-        <v>0.9995525399999999</v>
+        <v>0.99963413</v>
       </c>
       <c r="F91">
-        <v>0.9995525399999999</v>
+        <v>0.99963413</v>
       </c>
       <c r="G91">
-        <v>0.2580826940041561</v>
+        <v>0.2009313391215752</v>
       </c>
       <c r="H91">
-        <v>0.99847732</v>
+        <v>0.99848777</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="1">
-        <v>46153</v>
+        <v>46163</v>
       </c>
       <c r="B92" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C92">
-        <v>28.12253390077671</v>
+        <v>34.44616924817128</v>
       </c>
       <c r="D92">
-        <v>23.58699683751922</v>
+        <v>18.60085625074367</v>
       </c>
       <c r="E92">
-        <v>0.9997295369999999</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="F92">
-        <v>0.9997295369999999</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="G92">
-        <v>0.03368732240295347</v>
+        <v>0.2124957180214682</v>
       </c>
       <c r="H92">
-        <v>0.9997295369999999</v>
+        <v>0.9985085200000001</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="1">
-        <v>46154</v>
+        <v>46164</v>
       </c>
       <c r="B93" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C93">
-        <v>28.17715727830483</v>
+        <v>34.62137220937314</v>
       </c>
       <c r="D93">
-        <v>23.63894513078866</v>
+        <v>18.28780484745949</v>
       </c>
       <c r="E93">
-        <v>1.000319473</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="F93">
-        <v>1.000319473</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="G93">
-        <v>0.03515547182056333</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H93">
-        <v>1.000319473</v>
+        <v>0.9932939299999999</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="1">
-        <v>46155</v>
+        <v>46167</v>
       </c>
       <c r="B94" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C94">
-        <v>28.59002627414054</v>
+        <v>34.6540695486741</v>
       </c>
       <c r="D94">
-        <v>23.96230704059692</v>
+        <v>18.36409048915342</v>
       </c>
       <c r="E94">
-        <v>0.9999999989999999</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="F94">
-        <v>0.9999999989999999</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="G94">
-        <v>0.05179637495949674</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H94">
-        <v>0.9999999989999999</v>
+        <v>0.9984302600000001</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="1">
-        <v>46156</v>
+        <v>46168</v>
       </c>
       <c r="B95" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C95">
-        <v>28.56217859389523</v>
+        <v>35.4820130509417</v>
       </c>
       <c r="D95">
-        <v>23.9411987302529</v>
+        <v>19.20292041814603</v>
       </c>
       <c r="E95">
-        <v>1</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="F95">
-        <v>1</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="G95">
-        <v>0.04837024516756849</v>
+        <v>0.2553172934903569</v>
       </c>
       <c r="H95">
-        <v>1</v>
+        <v>0.9984302600000001</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="1">
-        <v>46157</v>
+        <v>46169</v>
       </c>
       <c r="B96" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C96">
-        <v>28.57618675936338</v>
+        <v>35.71913468603401</v>
       </c>
       <c r="D96">
-        <v>23.9576220541054</v>
+        <v>18.96318693998171</v>
       </c>
       <c r="E96">
-        <v>0.999503249</v>
+        <v>0.99955466</v>
       </c>
       <c r="F96">
-        <v>0.999503249</v>
+        <v>0.99955466</v>
       </c>
       <c r="G96">
-        <v>0.04983868243960732</v>
+        <v>0.2536413280520453</v>
       </c>
       <c r="H96">
-        <v>0.999503249</v>
+        <v>0.9984700500000001</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="1">
-        <v>46160</v>
+        <v>46170</v>
       </c>
       <c r="B97" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C97">
-        <v>28.68951918518517</v>
+        <v>35.76226417354731</v>
       </c>
       <c r="D97">
-        <v>24.06134728453882</v>
+        <v>18.89050847207122</v>
       </c>
       <c r="E97">
-        <v>0.999503249</v>
+        <v>0.9995525399999999</v>
       </c>
       <c r="F97">
-        <v>0.999503249</v>
+        <v>0.9995525399999999</v>
       </c>
       <c r="G97">
-        <v>0.04983868243960732</v>
+        <v>0.2580826940041561</v>
       </c>
       <c r="H97">
-        <v>0.999503249</v>
+        <v>0.99847732</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="1">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="B98" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C98">
-        <v>28.31167386654059</v>
+        <v>35.84309020154227</v>
       </c>
       <c r="D98">
-        <v>23.75157719455474</v>
+        <v>19.06511612333149</v>
       </c>
       <c r="E98">
-        <v>1.000177331</v>
+        <v>0.9995533299999999</v>
       </c>
       <c r="F98">
-        <v>1.000177331</v>
+        <v>0.9995533299999999</v>
       </c>
       <c r="G98">
-        <v>0.04053938625111919</v>
+        <v>0.2619374017254759</v>
       </c>
       <c r="H98">
-        <v>1.000177331</v>
+        <v>0.99849382</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="1">
-        <v>46162</v>
+        <v>46153</v>
       </c>
       <c r="B99" t="s">
         <v>15</v>
       </c>
       <c r="C99">
-        <v>28.57911382310097</v>
+        <v>28.12253390077671</v>
       </c>
       <c r="D99">
-        <v>23.89431741541233</v>
+        <v>23.58699683751922</v>
       </c>
       <c r="E99">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="F99">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="G99">
-        <v>0.04690190590044785</v>
+        <v>0.03368732240295347</v>
       </c>
       <c r="H99">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="1">
-        <v>46163</v>
+        <v>46154</v>
       </c>
       <c r="B100" t="s">
         <v>15</v>
       </c>
       <c r="C100">
-        <v>28.55785065378643</v>
+        <v>28.17715727830483</v>
       </c>
       <c r="D100">
-        <v>24.04274714970193</v>
+        <v>23.63894513078866</v>
       </c>
       <c r="E100">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="F100">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="G100">
-        <v>0.05228572319419666</v>
+        <v>0.03515547182056333</v>
       </c>
       <c r="H100">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="1">
-        <v>46164</v>
+        <v>46155</v>
       </c>
       <c r="B101" t="s">
         <v>15</v>
       </c>
       <c r="C101">
-        <v>28.50194638163107</v>
+        <v>28.59002627414054</v>
       </c>
       <c r="D101">
-        <v>23.99272397156045</v>
+        <v>23.96230704059692</v>
       </c>
       <c r="E101">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F101">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G101">
-        <v>0.04934923597154284</v>
+        <v>0.05179637495949674</v>
       </c>
       <c r="H101">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="1">
-        <v>46167</v>
+        <v>46156</v>
       </c>
       <c r="B102" t="s">
         <v>15</v>
       </c>
       <c r="C102">
-        <v>28.55106858744498</v>
+        <v>28.56217859389523</v>
       </c>
       <c r="D102">
-        <v>23.9768329565351</v>
+        <v>23.9411987302529</v>
       </c>
       <c r="E102">
         <v>1</v>
@@ -3049,7 +3049,7 @@
         <v>1</v>
       </c>
       <c r="G102">
-        <v>0.05571185335164408</v>
+        <v>0.04837024516756849</v>
       </c>
       <c r="H102">
         <v>1</v>
@@ -3057,444 +3057,678 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="1">
-        <v>46168</v>
+        <v>46157</v>
       </c>
       <c r="B103" t="s">
         <v>15</v>
       </c>
       <c r="C103">
-        <v>28.54681541456266</v>
+        <v>28.57618675936338</v>
       </c>
       <c r="D103">
-        <v>23.97386168967948</v>
+        <v>23.9576220541054</v>
       </c>
       <c r="E103">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="F103">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="G103">
-        <v>0.04837034303541388</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H103">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="1">
-        <v>46169</v>
+        <v>46160</v>
       </c>
       <c r="B104" t="s">
         <v>15</v>
       </c>
       <c r="C104">
-        <v>28.83672936868491</v>
+        <v>28.68951918518517</v>
       </c>
       <c r="D104">
-        <v>24.203511281145</v>
+        <v>24.06134728453882</v>
       </c>
       <c r="E104">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="F104">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="G104">
-        <v>0.05962723282507953</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H104">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="1">
-        <v>46170</v>
+        <v>46161</v>
       </c>
       <c r="B105" t="s">
         <v>15</v>
       </c>
       <c r="C105">
-        <v>28.88109630394224</v>
+        <v>28.31167386654059</v>
       </c>
       <c r="D105">
-        <v>24.34085451035401</v>
+        <v>23.75157719455474</v>
       </c>
       <c r="E105">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
       <c r="F105">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
       <c r="G105">
-        <v>0.06647938938594877</v>
+        <v>0.04053938625111919</v>
       </c>
       <c r="H105">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="1">
-        <v>46153</v>
+        <v>46162</v>
       </c>
       <c r="B106" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C106">
-        <v>40.68830633303975</v>
+        <v>28.57911382310097</v>
       </c>
       <c r="D106">
-        <v>21.50431773660198</v>
+        <v>23.89431741541233</v>
       </c>
       <c r="E106">
-        <v>0.99909852</v>
+        <v>0.999503734</v>
       </c>
       <c r="F106">
-        <v>0.99909852</v>
+        <v>0.999503734</v>
       </c>
       <c r="G106">
-        <v>0.2342423866086769</v>
+        <v>0.04690190590044785</v>
       </c>
       <c r="H106">
-        <v>0.9974930900000001</v>
+        <v>0.999503734</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="1">
-        <v>46154</v>
+        <v>46163</v>
       </c>
       <c r="B107" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C107">
-        <v>40.32854894972581</v>
+        <v>28.55785065378643</v>
       </c>
       <c r="D107">
-        <v>21.09133998298594</v>
+        <v>24.04274714970193</v>
       </c>
       <c r="E107">
-        <v>0.9990972199999999</v>
+        <v>1.000229282</v>
       </c>
       <c r="F107">
-        <v>0.9990972199999999</v>
+        <v>1.000229282</v>
       </c>
       <c r="G107">
-        <v>0.2156468205051487</v>
+        <v>0.05228572319419666</v>
       </c>
       <c r="H107">
-        <v>0.99752223</v>
+        <v>1.000229282</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="1">
-        <v>46155</v>
+        <v>46164</v>
       </c>
       <c r="B108" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C108">
-        <v>40.47987921095815</v>
+        <v>28.50194638163107</v>
       </c>
       <c r="D108">
-        <v>21.35995364434454</v>
+        <v>23.99272397156045</v>
       </c>
       <c r="E108">
-        <v>0.9991780100000001</v>
+        <v>1</v>
       </c>
       <c r="F108">
-        <v>0.9991780100000001</v>
+        <v>1</v>
       </c>
       <c r="G108">
-        <v>0.2270956128473374</v>
+        <v>0.04934923597154284</v>
       </c>
       <c r="H108">
-        <v>0.9975825700000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="1">
-        <v>46156</v>
+        <v>46167</v>
       </c>
       <c r="B109" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C109">
-        <v>41.20436574895244</v>
+        <v>28.55106858744498</v>
       </c>
       <c r="D109">
-        <v>21.48149674387778</v>
+        <v>23.9768329565351</v>
       </c>
       <c r="E109">
-        <v>0.9991793299999999</v>
+        <v>1</v>
       </c>
       <c r="F109">
-        <v>0.9991793299999999</v>
+        <v>1</v>
       </c>
       <c r="G109">
-        <v>0.2454829228401052</v>
+        <v>0.05571185335164408</v>
       </c>
       <c r="H109">
-        <v>0.99754722</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="1">
-        <v>46157</v>
+        <v>46168</v>
       </c>
       <c r="B110" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C110">
-        <v>40.80613062958688</v>
+        <v>28.54681541456266</v>
       </c>
       <c r="D110">
-        <v>21.08912555803936</v>
+        <v>23.97386168967948</v>
       </c>
       <c r="E110">
-        <v>0.9991790600000001</v>
+        <v>1</v>
       </c>
       <c r="F110">
-        <v>0.9991790600000001</v>
+        <v>1</v>
       </c>
       <c r="G110">
-        <v>0.2230017445022556</v>
+        <v>0.04837034303541388</v>
       </c>
       <c r="H110">
-        <v>0.9975824700000002</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="1">
-        <v>46160</v>
+        <v>46169</v>
       </c>
       <c r="B111" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C111">
-        <v>40.11672876026724</v>
+        <v>28.83672936868491</v>
       </c>
       <c r="D111">
-        <v>20.79541439916316</v>
+        <v>24.203511281145</v>
       </c>
       <c r="E111">
-        <v>0.999152</v>
+        <v>1</v>
       </c>
       <c r="F111">
-        <v>0.999152</v>
+        <v>1</v>
       </c>
       <c r="G111">
-        <v>0.2098184021536666</v>
+        <v>0.05962723282507953</v>
       </c>
       <c r="H111">
-        <v>0.9975007899999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="1">
-        <v>46161</v>
+        <v>46170</v>
       </c>
       <c r="B112" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C112">
-        <v>39.69086941528401</v>
+        <v>28.88109630394224</v>
       </c>
       <c r="D112">
-        <v>20.74924328599426</v>
+        <v>24.34085451035401</v>
       </c>
       <c r="E112">
-        <v>0.99914989</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F112">
-        <v>0.99914989</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G112">
-        <v>0.2020471776850241</v>
+        <v>0.06647938938594877</v>
       </c>
       <c r="H112">
-        <v>0.9974417</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="1">
-        <v>46162</v>
+        <v>46171</v>
       </c>
       <c r="B113" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C113">
-        <v>40.37836787855562</v>
+        <v>28.92588622185229</v>
       </c>
       <c r="D113">
-        <v>21.11271132314188</v>
+        <v>24.37463012178961</v>
       </c>
       <c r="E113">
-        <v>0.99915058</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F113">
-        <v>0.99915058</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G113">
-        <v>0.2291077670847563</v>
+        <v>0.0669687424559624</v>
       </c>
       <c r="H113">
-        <v>0.9974415600000001</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="1">
-        <v>46163</v>
+        <v>46153</v>
       </c>
       <c r="B114" t="s">
         <v>16</v>
       </c>
       <c r="C114">
-        <v>38.9123066967842</v>
+        <v>40.68830633303975</v>
       </c>
       <c r="D114">
-        <v>21.28910644207464</v>
+        <v>21.50431773660198</v>
       </c>
       <c r="E114">
-        <v>0.9989350699999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="F114">
-        <v>0.9989350699999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="G114">
-        <v>0.2392382040170877</v>
+        <v>0.2342423866086769</v>
       </c>
       <c r="H114">
-        <v>0.99726191</v>
+        <v>0.9974930900000001</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="1">
-        <v>46164</v>
+        <v>46154</v>
       </c>
       <c r="B115" t="s">
         <v>16</v>
       </c>
       <c r="C115">
-        <v>39.43913909150694</v>
+        <v>40.32854894972581</v>
       </c>
       <c r="D115">
-        <v>21.05297617141148</v>
+        <v>21.09133998298594</v>
       </c>
       <c r="E115">
-        <v>0.999144</v>
+        <v>0.9990972199999999</v>
       </c>
       <c r="F115">
-        <v>0.999144</v>
+        <v>0.9990972199999999</v>
       </c>
       <c r="G115">
-        <v>0.2516582935428642</v>
+        <v>0.2156468205051487</v>
       </c>
       <c r="H115">
-        <v>0.9974678400000001</v>
+        <v>0.99752223</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="1">
-        <v>46167</v>
+        <v>46155</v>
       </c>
       <c r="B116" t="s">
         <v>16</v>
       </c>
       <c r="C116">
-        <v>39.45782844313628</v>
+        <v>40.47987921095815</v>
       </c>
       <c r="D116">
-        <v>21.0518901572272</v>
+        <v>21.35995364434454</v>
       </c>
       <c r="E116">
-        <v>0.999144</v>
+        <v>0.9991780100000001</v>
       </c>
       <c r="F116">
-        <v>0.999144</v>
+        <v>0.9991780100000001</v>
       </c>
       <c r="G116">
-        <v>0.2516582935428642</v>
+        <v>0.2270956128473374</v>
       </c>
       <c r="H116">
-        <v>0.9974678400000001</v>
+        <v>0.9975825700000001</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="1">
-        <v>46168</v>
+        <v>46156</v>
       </c>
       <c r="B117" t="s">
         <v>16</v>
       </c>
       <c r="C117">
-        <v>40.20219297984542</v>
+        <v>41.20436574895244</v>
       </c>
       <c r="D117">
-        <v>21.93106024403281</v>
+        <v>21.48149674387778</v>
       </c>
       <c r="E117">
-        <v>0.9991421799999999</v>
+        <v>0.9991793299999999</v>
       </c>
       <c r="F117">
-        <v>0.9991421799999999</v>
+        <v>0.9991793299999999</v>
       </c>
       <c r="G117">
-        <v>0.2846167552893293</v>
+        <v>0.2454829228401052</v>
       </c>
       <c r="H117">
-        <v>0.9974609800000001</v>
+        <v>0.99754722</v>
       </c>
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="1">
-        <v>46169</v>
+        <v>46157</v>
       </c>
       <c r="B118" t="s">
         <v>16</v>
       </c>
       <c r="C118">
-        <v>40.34993865302093</v>
+        <v>40.80613062958688</v>
       </c>
       <c r="D118">
-        <v>21.65366031776487</v>
+        <v>21.08912555803936</v>
       </c>
       <c r="E118">
-        <v>0.9991434600000001</v>
+        <v>0.9991790600000001</v>
       </c>
       <c r="F118">
-        <v>0.9991434600000001</v>
+        <v>0.9991790600000001</v>
       </c>
       <c r="G118">
-        <v>0.2796902860011767</v>
+        <v>0.2230017445022556</v>
       </c>
       <c r="H118">
-        <v>0.9991434600000001</v>
+        <v>0.9975824700000002</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="1">
-        <v>46170</v>
+        <v>46160</v>
       </c>
       <c r="B119" t="s">
         <v>16</v>
       </c>
       <c r="C119">
+        <v>40.11672876026724</v>
+      </c>
+      <c r="D119">
+        <v>20.79541439916316</v>
+      </c>
+      <c r="E119">
+        <v>0.999152</v>
+      </c>
+      <c r="F119">
+        <v>0.999152</v>
+      </c>
+      <c r="G119">
+        <v>0.2098184021536666</v>
+      </c>
+      <c r="H119">
+        <v>0.9975007899999999</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120">
+        <v>39.69086941528401</v>
+      </c>
+      <c r="D120">
+        <v>20.74924328599426</v>
+      </c>
+      <c r="E120">
+        <v>0.99914989</v>
+      </c>
+      <c r="F120">
+        <v>0.99914989</v>
+      </c>
+      <c r="G120">
+        <v>0.2020471776850241</v>
+      </c>
+      <c r="H120">
+        <v>0.9974417</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121">
+        <v>40.37836787855562</v>
+      </c>
+      <c r="D121">
+        <v>21.11271132314188</v>
+      </c>
+      <c r="E121">
+        <v>0.99915058</v>
+      </c>
+      <c r="F121">
+        <v>0.99915058</v>
+      </c>
+      <c r="G121">
+        <v>0.2291077670847563</v>
+      </c>
+      <c r="H121">
+        <v>0.9974415600000001</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122">
+        <v>38.9123066967842</v>
+      </c>
+      <c r="D122">
+        <v>21.28910644207464</v>
+      </c>
+      <c r="E122">
+        <v>0.9989350699999999</v>
+      </c>
+      <c r="F122">
+        <v>0.9989350699999999</v>
+      </c>
+      <c r="G122">
+        <v>0.2392382040170877</v>
+      </c>
+      <c r="H122">
+        <v>0.99726191</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123" s="1">
+        <v>46164</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123">
+        <v>39.43913909150694</v>
+      </c>
+      <c r="D123">
+        <v>21.05297617141148</v>
+      </c>
+      <c r="E123">
+        <v>0.999144</v>
+      </c>
+      <c r="F123">
+        <v>0.999144</v>
+      </c>
+      <c r="G123">
+        <v>0.2516582935428642</v>
+      </c>
+      <c r="H123">
+        <v>0.9974678400000001</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124">
+        <v>39.45782844313628</v>
+      </c>
+      <c r="D124">
+        <v>21.0518901572272</v>
+      </c>
+      <c r="E124">
+        <v>0.999144</v>
+      </c>
+      <c r="F124">
+        <v>0.999144</v>
+      </c>
+      <c r="G124">
+        <v>0.2516582935428642</v>
+      </c>
+      <c r="H124">
+        <v>0.9974678400000001</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125">
+        <v>40.20219297984542</v>
+      </c>
+      <c r="D125">
+        <v>21.93106024403281</v>
+      </c>
+      <c r="E125">
+        <v>0.9991421799999999</v>
+      </c>
+      <c r="F125">
+        <v>0.9991421799999999</v>
+      </c>
+      <c r="G125">
+        <v>0.2846167552893293</v>
+      </c>
+      <c r="H125">
+        <v>0.9974609800000001</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126">
+        <v>40.34993865302093</v>
+      </c>
+      <c r="D126">
+        <v>21.65366031776487</v>
+      </c>
+      <c r="E126">
+        <v>0.9991434600000001</v>
+      </c>
+      <c r="F126">
+        <v>0.9991434600000001</v>
+      </c>
+      <c r="G126">
+        <v>0.2796902860011767</v>
+      </c>
+      <c r="H126">
+        <v>0.9991434600000001</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127">
         <v>40.5850485390846</v>
       </c>
-      <c r="D119">
+      <c r="D127">
         <v>21.75450977746074</v>
       </c>
-      <c r="E119">
+      <c r="E127">
         <v>0.99914592</v>
       </c>
-      <c r="F119">
+      <c r="F127">
         <v>0.99914592</v>
       </c>
-      <c r="G119">
+      <c r="G127">
         <v>0.2964818481030536</v>
       </c>
-      <c r="H119">
+      <c r="H127">
         <v>0.99914592</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128">
+        <v>41.86785805184477</v>
+      </c>
+      <c r="D128">
+        <v>22.33589392797469</v>
+      </c>
+      <c r="E128">
+        <v>0.9991336999999999</v>
+      </c>
+      <c r="F128">
+        <v>0.9991336999999999</v>
+      </c>
+      <c r="G128">
+        <v>0.3254158954996882</v>
+      </c>
+      <c r="H128">
+        <v>0.9991336999999999</v>
       </c>
     </row>
   </sheetData>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="17">
   <si>
     <t>Date</t>
   </si>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H128"/>
+  <dimension ref="A1:H137"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -639,42 +639,42 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1">
-        <v>46153</v>
+        <v>46174</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10">
-        <v>53.14833755912058</v>
+        <v>26.08061528964706</v>
       </c>
       <c r="D10">
-        <v>25.84885448407537</v>
+        <v>17.76801553767955</v>
       </c>
       <c r="E10">
-        <v>0.9262</v>
+        <v>0.8565</v>
       </c>
       <c r="F10">
-        <v>0.9262</v>
+        <v>0.8565</v>
       </c>
       <c r="G10">
-        <v>0.3839084462043663</v>
+        <v>0.6895181290030949</v>
       </c>
       <c r="H10">
-        <v>0.9262</v>
+        <v>0.9117</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
       </c>
       <c r="C11">
-        <v>51.82921169635205</v>
+        <v>53.14833755912058</v>
       </c>
       <c r="D11">
-        <v>25.32805827181975</v>
+        <v>25.84885448407537</v>
       </c>
       <c r="E11">
         <v>0.9262</v>
@@ -683,7 +683,7 @@
         <v>0.9262</v>
       </c>
       <c r="G11">
-        <v>0.3568580281685669</v>
+        <v>0.3839084462043663</v>
       </c>
       <c r="H11">
         <v>0.9262</v>
@@ -691,120 +691,120 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
       </c>
       <c r="C12">
-        <v>52.28471716753184</v>
+        <v>51.82921169635205</v>
       </c>
       <c r="D12">
-        <v>25.54525144150689</v>
+        <v>25.32805827181975</v>
       </c>
       <c r="E12">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="F12">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="G12">
-        <v>0.378012896547947</v>
+        <v>0.3568580281685669</v>
       </c>
       <c r="H12">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B13" t="s">
         <v>9</v>
       </c>
       <c r="C13">
-        <v>53.87287273813902</v>
+        <v>52.28471716753184</v>
       </c>
       <c r="D13">
-        <v>26.32154226438612</v>
+        <v>25.54525144150689</v>
       </c>
       <c r="E13">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="F13">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="G13">
-        <v>0.4166811087612758</v>
+        <v>0.378012896547947</v>
       </c>
       <c r="H13">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
       </c>
       <c r="C14">
-        <v>52.18747148214074</v>
+        <v>53.87287273813902</v>
       </c>
       <c r="D14">
-        <v>25.13616059644496</v>
+        <v>26.32154226438612</v>
       </c>
       <c r="E14">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="F14">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="G14">
-        <v>0.3627535778249862</v>
+        <v>0.4166811087612758</v>
       </c>
       <c r="H14">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
       </c>
       <c r="C15">
-        <v>50.72035274995172</v>
+        <v>52.18747148214074</v>
       </c>
       <c r="D15">
-        <v>24.61756040386634</v>
+        <v>25.13616059644496</v>
       </c>
       <c r="E15">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="F15">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="G15">
         <v>0.3627535778249862</v>
       </c>
       <c r="H15">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
       </c>
       <c r="C16">
-        <v>50.11981086673613</v>
+        <v>50.72035274995172</v>
       </c>
       <c r="D16">
-        <v>24.13061679021705</v>
+        <v>24.61756040386634</v>
       </c>
       <c r="E16">
         <v>0.9259000000000001</v>
@@ -813,7 +813,7 @@
         <v>0.9259000000000001</v>
       </c>
       <c r="G16">
-        <v>0.3258193430227221</v>
+        <v>0.3627535778249862</v>
       </c>
       <c r="H16">
         <v>0.9259000000000001</v>
@@ -821,120 +821,120 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
       </c>
       <c r="C17">
-        <v>51.74165648409151</v>
+        <v>50.11981086673613</v>
       </c>
       <c r="D17">
-        <v>24.98091384114761</v>
+        <v>24.13061679021705</v>
       </c>
       <c r="E17">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="F17">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="G17">
-        <v>0.3818277262286871</v>
+        <v>0.3258193430227221</v>
       </c>
       <c r="H17">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="B18" t="s">
         <v>9</v>
       </c>
       <c r="C18">
-        <v>49.13455894175823</v>
+        <v>51.74165648409151</v>
       </c>
       <c r="D18">
-        <v>25.30005057653127</v>
+        <v>24.98091384114761</v>
       </c>
       <c r="E18">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="F18">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="G18">
-        <v>0.4028091571787618</v>
+        <v>0.3818277262286871</v>
       </c>
       <c r="H18">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="B19" t="s">
         <v>9</v>
       </c>
       <c r="C19">
-        <v>49.57776597479297</v>
+        <v>49.13455894175823</v>
       </c>
       <c r="D19">
-        <v>25.04906725563518</v>
+        <v>25.30005057653127</v>
       </c>
       <c r="E19">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="F19">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="G19">
-        <v>0.4256980029692063</v>
+        <v>0.4028091571787618</v>
       </c>
       <c r="H19">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="B20" t="s">
         <v>9</v>
       </c>
       <c r="C20">
-        <v>49.71239596645896</v>
+        <v>49.57776597479297</v>
       </c>
       <c r="D20">
-        <v>25.18778610744295</v>
+        <v>25.04906725563518</v>
       </c>
       <c r="E20">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="F20">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="G20">
-        <v>0.4525749835757003</v>
+        <v>0.4256980029692063</v>
       </c>
       <c r="H20">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="B21" t="s">
         <v>9</v>
       </c>
       <c r="C21">
-        <v>50.77166277510776</v>
+        <v>49.71239596645896</v>
       </c>
       <c r="D21">
-        <v>25.7431782858765</v>
+        <v>25.18778610744295</v>
       </c>
       <c r="E21">
         <v>0.9231999999999999</v>
@@ -943,7 +943,7 @@
         <v>0.9231999999999999</v>
       </c>
       <c r="G21">
-        <v>0.4700884597036457</v>
+        <v>0.4525749835757003</v>
       </c>
       <c r="H21">
         <v>0.9231999999999999</v>
@@ -951,224 +951,224 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1">
-        <v>46169</v>
+        <v>46168</v>
       </c>
       <c r="B22" t="s">
         <v>9</v>
       </c>
       <c r="C22">
-        <v>50.57689164833899</v>
+        <v>50.77166277510776</v>
       </c>
       <c r="D22">
-        <v>25.70244067238947</v>
+        <v>25.7431782858765</v>
       </c>
       <c r="E22">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="F22">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="G22">
-        <v>0.4518814984464716</v>
+        <v>0.4700884597036457</v>
       </c>
       <c r="H22">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="B23" t="s">
         <v>9</v>
       </c>
       <c r="C23">
-        <v>50.80027854822009</v>
+        <v>50.57689164833899</v>
       </c>
       <c r="D23">
-        <v>25.90068415792015</v>
+        <v>25.70244067238947</v>
       </c>
       <c r="E23">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
       <c r="F23">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
       <c r="G23">
-        <v>0.4699150222743402</v>
+        <v>0.4518814984464716</v>
       </c>
       <c r="H23">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="B24" t="s">
         <v>9</v>
       </c>
       <c r="C24">
-        <v>51.44563447241545</v>
+        <v>50.80027854822009</v>
       </c>
       <c r="D24">
-        <v>26.0970978996374</v>
+        <v>25.90068415792015</v>
       </c>
       <c r="E24">
-        <v>0.9246</v>
+        <v>0.9231</v>
       </c>
       <c r="F24">
-        <v>0.9246</v>
+        <v>0.9231</v>
       </c>
       <c r="G24">
-        <v>0.4791053539115764</v>
+        <v>0.4699150222743402</v>
       </c>
       <c r="H24">
-        <v>0.9246</v>
+        <v>0.9231</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1">
-        <v>46153</v>
+        <v>46171</v>
       </c>
       <c r="B25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C25">
-        <v>34.64560932909123</v>
+        <v>51.44563447241545</v>
       </c>
       <c r="D25">
-        <v>26.08311546080494</v>
+        <v>26.0970978996374</v>
       </c>
       <c r="E25">
-        <v>0.9983000000000001</v>
+        <v>0.9246</v>
       </c>
       <c r="F25">
-        <v>0.9983000000000001</v>
+        <v>0.9246</v>
       </c>
       <c r="G25">
-        <v>0.06258613715048233</v>
+        <v>0.4791053539115764</v>
       </c>
       <c r="H25">
-        <v>0.9983000000000001</v>
+        <v>0.9246</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1">
-        <v>46154</v>
+        <v>46174</v>
       </c>
       <c r="B26" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C26">
-        <v>34.50204921141101</v>
+        <v>53.05792083471825</v>
       </c>
       <c r="D26">
-        <v>25.94535229304585</v>
+        <v>26.86242981002239</v>
       </c>
       <c r="E26">
-        <v>0.9984</v>
+        <v>0.9254999999999999</v>
       </c>
       <c r="F26">
-        <v>0.9984</v>
+        <v>0.9254999999999999</v>
       </c>
       <c r="G26">
-        <v>0.05768943168306073</v>
+        <v>0.5306051577195796</v>
       </c>
       <c r="H26">
-        <v>0.9984</v>
+        <v>0.9254999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
       </c>
       <c r="C27">
-        <v>35.10429483281073</v>
+        <v>34.64560932909123</v>
       </c>
       <c r="D27">
-        <v>26.43864879939599</v>
+        <v>26.08311546080494</v>
       </c>
       <c r="E27">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="F27">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="G27">
-        <v>0.07926550001722021</v>
+        <v>0.06258613715048233</v>
       </c>
       <c r="H27">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
       </c>
       <c r="C28">
-        <v>35.36860632820093</v>
+        <v>34.50204921141101</v>
       </c>
       <c r="D28">
-        <v>26.56575571102338</v>
+        <v>25.94535229304585</v>
       </c>
       <c r="E28">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F28">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G28">
-        <v>0.08553946591902095</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H28">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="B29" t="s">
         <v>10</v>
       </c>
       <c r="C29">
-        <v>34.88080083527914</v>
+        <v>35.10429483281073</v>
       </c>
       <c r="D29">
-        <v>26.19322945679072</v>
+        <v>26.43864879939599</v>
       </c>
       <c r="E29">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="F29">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="G29">
-        <v>0.06870693142475881</v>
+        <v>0.07926550001722021</v>
       </c>
       <c r="H29">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1">
-        <v>46160</v>
+        <v>46156</v>
       </c>
       <c r="B30" t="s">
         <v>10</v>
       </c>
       <c r="C30">
-        <v>34.67638692539213</v>
+        <v>35.36860632820093</v>
       </c>
       <c r="D30">
-        <v>26.06707890342319</v>
+        <v>26.56575571102338</v>
       </c>
       <c r="E30">
         <v>0.9985999999999999</v>
@@ -1177,7 +1177,7 @@
         <v>0.9985999999999999</v>
       </c>
       <c r="G30">
-        <v>0.06289213016552919</v>
+        <v>0.08553946591902095</v>
       </c>
       <c r="H30">
         <v>0.9985999999999999</v>
@@ -1185,120 +1185,120 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="B31" t="s">
         <v>10</v>
       </c>
       <c r="C31">
-        <v>34.21212662725402</v>
+        <v>34.88080083527914</v>
       </c>
       <c r="D31">
-        <v>25.60349394367002</v>
+        <v>26.19322945679072</v>
       </c>
       <c r="E31">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="F31">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="G31">
-        <v>0.0486610616591685</v>
+        <v>0.06870693142475881</v>
       </c>
       <c r="H31">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
       </c>
       <c r="C32">
-        <v>34.78598436564941</v>
+        <v>34.67638692539213</v>
       </c>
       <c r="D32">
-        <v>25.95505316769806</v>
+        <v>26.06707890342319</v>
       </c>
       <c r="E32">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="F32">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="G32">
-        <v>0.06335117806143331</v>
+        <v>0.06289213016552919</v>
       </c>
       <c r="H32">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1">
-        <v>46163</v>
+        <v>46161</v>
       </c>
       <c r="B33" t="s">
         <v>10</v>
       </c>
       <c r="C33">
-        <v>33.4539909056227</v>
+        <v>34.21212662725402</v>
       </c>
       <c r="D33">
-        <v>25.96014535427112</v>
+        <v>25.60349394367002</v>
       </c>
       <c r="E33">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="F33">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="G33">
-        <v>0.06350423294229035</v>
+        <v>0.0486610616591685</v>
       </c>
       <c r="H33">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1">
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="B34" t="s">
         <v>10</v>
       </c>
       <c r="C34">
-        <v>33.24951933563993</v>
+        <v>34.78598436564941</v>
       </c>
       <c r="D34">
-        <v>25.46629530314992</v>
+        <v>25.95505316769806</v>
       </c>
       <c r="E34">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="F34">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="G34">
-        <v>0.06136193159696024</v>
+        <v>0.06335117806143331</v>
       </c>
       <c r="H34">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1">
-        <v>46167</v>
+        <v>46163</v>
       </c>
       <c r="B35" t="s">
         <v>10</v>
       </c>
       <c r="C35">
-        <v>33.29896419867477</v>
+        <v>33.4539909056227</v>
       </c>
       <c r="D35">
-        <v>25.45090185337973</v>
+        <v>25.96014535427112</v>
       </c>
       <c r="E35">
         <v>0.9984</v>
@@ -1307,7 +1307,7 @@
         <v>0.9984</v>
       </c>
       <c r="G35">
-        <v>0.06136193159696024</v>
+        <v>0.06350423294229035</v>
       </c>
       <c r="H35">
         <v>0.9984</v>
@@ -1315,16 +1315,16 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1">
-        <v>46168</v>
+        <v>46164</v>
       </c>
       <c r="B36" t="s">
         <v>10</v>
       </c>
       <c r="C36">
-        <v>33.41270923608511</v>
+        <v>33.24951933563993</v>
       </c>
       <c r="D36">
-        <v>25.54156152389702</v>
+        <v>25.46629530314992</v>
       </c>
       <c r="E36">
         <v>0.9984</v>
@@ -1333,7 +1333,7 @@
         <v>0.9984</v>
       </c>
       <c r="G36">
-        <v>0.06549347940676342</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H36">
         <v>0.9984</v>
@@ -1341,614 +1341,614 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1">
-        <v>46169</v>
+        <v>46167</v>
       </c>
       <c r="B37" t="s">
         <v>10</v>
       </c>
       <c r="C37">
-        <v>33.73350746548562</v>
+        <v>33.29896419867477</v>
       </c>
       <c r="D37">
-        <v>25.75393367034243</v>
+        <v>25.45090185337973</v>
       </c>
       <c r="E37">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="F37">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="G37">
-        <v>0.07620510288008187</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H37">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1">
-        <v>46170</v>
+        <v>46168</v>
       </c>
       <c r="B38" t="s">
         <v>10</v>
       </c>
       <c r="C38">
-        <v>33.84336414535104</v>
+        <v>33.41270923608511</v>
       </c>
       <c r="D38">
-        <v>25.97168203877208</v>
+        <v>25.54156152389702</v>
       </c>
       <c r="E38">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
       <c r="F38">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
       <c r="G38">
-        <v>0.0844683152463559</v>
+        <v>0.06549347940676342</v>
       </c>
       <c r="H38">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1">
-        <v>46171</v>
+        <v>46169</v>
       </c>
       <c r="B39" t="s">
         <v>10</v>
       </c>
       <c r="C39">
-        <v>33.73370320039719</v>
+        <v>33.73350746548562</v>
       </c>
       <c r="D39">
-        <v>25.880209881309</v>
+        <v>25.75393367034243</v>
       </c>
       <c r="E39">
-        <v>0.9988</v>
+        <v>0.9987000000000001</v>
       </c>
       <c r="F39">
-        <v>0.9988</v>
+        <v>0.9987000000000001</v>
       </c>
       <c r="G39">
-        <v>0.08201990413931148</v>
+        <v>0.07620510288008187</v>
       </c>
       <c r="H39">
-        <v>0.9988</v>
+        <v>0.9987000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1">
-        <v>46153</v>
+        <v>46170</v>
       </c>
       <c r="B40" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C40">
-        <v>36.55790859258162</v>
+        <v>33.84336414535104</v>
       </c>
       <c r="D40">
-        <v>22.67181120908155</v>
+        <v>25.97168203877208</v>
       </c>
       <c r="E40">
-        <v>0.9990740999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="F40">
-        <v>0.9990740999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="G40">
-        <v>0.1648443271746771</v>
+        <v>0.0844683152463559</v>
       </c>
       <c r="H40">
-        <v>0.9990740999999999</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1">
-        <v>46154</v>
+        <v>46171</v>
       </c>
       <c r="B41" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C41">
-        <v>36.44753722959613</v>
+        <v>33.73370320039719</v>
       </c>
       <c r="D41">
-        <v>22.40292401789388</v>
+        <v>25.880209881309</v>
       </c>
       <c r="E41">
-        <v>0.9990772499999999</v>
+        <v>0.9988</v>
       </c>
       <c r="F41">
-        <v>0.9990772499999999</v>
+        <v>0.9988</v>
       </c>
       <c r="G41">
-        <v>0.154964342628132</v>
+        <v>0.08201990413931148</v>
       </c>
       <c r="H41">
-        <v>0.9990772499999999</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1">
-        <v>46155</v>
+        <v>46174</v>
       </c>
       <c r="B42" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C42">
-        <v>36.63128514035871</v>
+        <v>33.45546240777382</v>
       </c>
       <c r="D42">
-        <v>22.65773388934668</v>
+        <v>25.61350381215703</v>
       </c>
       <c r="E42">
-        <v>0.99907745</v>
+        <v>0.999</v>
       </c>
       <c r="F42">
-        <v>0.99907745</v>
+        <v>0.999</v>
       </c>
       <c r="G42">
-        <v>0.1671633421405267</v>
+        <v>0.06901304118647311</v>
       </c>
       <c r="H42">
-        <v>0.99907745</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="B43" t="s">
         <v>11</v>
       </c>
       <c r="C43">
-        <v>36.87865927427314</v>
+        <v>36.55790859258162</v>
       </c>
       <c r="D43">
-        <v>22.69755646854794</v>
+        <v>22.67181120908155</v>
       </c>
       <c r="E43">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="F43">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="G43">
-        <v>0.1754592080224002</v>
+        <v>0.1648443271746771</v>
       </c>
       <c r="H43">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="B44" t="s">
         <v>11</v>
       </c>
       <c r="C44">
-        <v>36.52208783231286</v>
+        <v>36.44753722959613</v>
       </c>
       <c r="D44">
-        <v>22.32462309676992</v>
+        <v>22.40292401789388</v>
       </c>
       <c r="E44">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="F44">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="G44">
-        <v>0.1577242156354994</v>
+        <v>0.154964342628132</v>
       </c>
       <c r="H44">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="B45" t="s">
         <v>11</v>
       </c>
       <c r="C45">
-        <v>36.25604200674668</v>
+        <v>36.63128514035871</v>
       </c>
       <c r="D45">
-        <v>22.16555007468561</v>
+        <v>22.65773388934668</v>
       </c>
       <c r="E45">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="F45">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="G45">
-        <v>0.1527434068648266</v>
+        <v>0.1671633421405267</v>
       </c>
       <c r="H45">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1">
-        <v>46161</v>
+        <v>46156</v>
       </c>
       <c r="B46" t="s">
         <v>11</v>
       </c>
       <c r="C46">
-        <v>36.01040085730018</v>
+        <v>36.87865927427314</v>
       </c>
       <c r="D46">
-        <v>22.19475589056387</v>
+        <v>22.69755646854794</v>
       </c>
       <c r="E46">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="F46">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="G46">
-        <v>0.1456396418594061</v>
+        <v>0.1754592080224002</v>
       </c>
       <c r="H46">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1">
-        <v>46162</v>
+        <v>46157</v>
       </c>
       <c r="B47" t="s">
         <v>11</v>
       </c>
       <c r="C47">
-        <v>36.45290912796982</v>
+        <v>36.52208783231286</v>
       </c>
       <c r="D47">
-        <v>22.46357594746874</v>
+        <v>22.32462309676992</v>
       </c>
       <c r="E47">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="F47">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="G47">
-        <v>0.1646157747240327</v>
+        <v>0.1577242156354994</v>
       </c>
       <c r="H47">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1">
-        <v>46163</v>
+        <v>46160</v>
       </c>
       <c r="B48" t="s">
         <v>11</v>
       </c>
       <c r="C48">
-        <v>35.75282090566891</v>
+        <v>36.25604200674668</v>
       </c>
       <c r="D48">
-        <v>22.57615417310648</v>
+        <v>22.16555007468561</v>
       </c>
       <c r="E48">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="F48">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="G48">
-        <v>0.1668367104873381</v>
+        <v>0.1527434068648266</v>
       </c>
       <c r="H48">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1">
-        <v>46164</v>
+        <v>46161</v>
       </c>
       <c r="B49" t="s">
         <v>11</v>
       </c>
       <c r="C49">
-        <v>35.75514940724808</v>
+        <v>36.01040085730018</v>
       </c>
       <c r="D49">
-        <v>22.28880693466429</v>
+        <v>22.19475589056387</v>
       </c>
       <c r="E49">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="F49">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="G49">
-        <v>0.1717848261904962</v>
+        <v>0.1456396418594061</v>
       </c>
       <c r="H49">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1">
-        <v>46167</v>
+        <v>46162</v>
       </c>
       <c r="B50" t="s">
         <v>11</v>
       </c>
       <c r="C50">
-        <v>35.84133099010302</v>
+        <v>36.45290912796982</v>
       </c>
       <c r="D50">
-        <v>22.37458514769363</v>
+        <v>22.46357594746874</v>
       </c>
       <c r="E50">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="F50">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="G50">
-        <v>0.1717848261904962</v>
+        <v>0.1646157747240327</v>
       </c>
       <c r="H50">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1">
-        <v>46168</v>
+        <v>46163</v>
       </c>
       <c r="B51" t="s">
         <v>11</v>
       </c>
       <c r="C51">
-        <v>36.23214279739292</v>
+        <v>35.75282090566891</v>
       </c>
       <c r="D51">
-        <v>22.93484792820123</v>
+        <v>22.57615417310648</v>
       </c>
       <c r="E51">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
       <c r="F51">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
       <c r="G51">
-        <v>0.1925900763781823</v>
+        <v>0.1668367104873381</v>
       </c>
       <c r="H51">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="B52" t="s">
         <v>11</v>
       </c>
       <c r="C52">
-        <v>36.4336692499184</v>
+        <v>35.75514940724808</v>
       </c>
       <c r="D52">
-        <v>22.75940954009856</v>
+        <v>22.28880693466429</v>
       </c>
       <c r="E52">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="F52">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="G52">
-        <v>0.1912346098381414</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H52">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="B53" t="s">
         <v>11</v>
       </c>
       <c r="C53">
-        <v>36.57358557066742</v>
+        <v>35.84133099010302</v>
       </c>
       <c r="D53">
-        <v>22.83069636955243</v>
+        <v>22.37458514769363</v>
       </c>
       <c r="E53">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="F53">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="G53">
-        <v>0.2012778603742877</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H53">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1">
-        <v>46171</v>
+        <v>46168</v>
       </c>
       <c r="B54" t="s">
         <v>11</v>
       </c>
       <c r="C54">
-        <v>36.67481300942</v>
+        <v>36.23214279739292</v>
       </c>
       <c r="D54">
-        <v>22.95852861681004</v>
+        <v>22.93484792820123</v>
       </c>
       <c r="E54">
-        <v>0.9964953299999998</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="F54">
-        <v>0.9964953299999998</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="G54">
-        <v>0.2057034850411275</v>
+        <v>0.1925900763781823</v>
       </c>
       <c r="H54">
-        <v>0.9994474899999999</v>
+        <v>0.9992609200000001</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1">
-        <v>46153</v>
+        <v>46169</v>
       </c>
       <c r="B55" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C55">
-        <v>52.70832779833182</v>
+        <v>36.4336692499184</v>
       </c>
       <c r="D55">
-        <v>23.99044674439659</v>
+        <v>22.75940954009856</v>
       </c>
       <c r="E55">
-        <v>0.9994000000000002</v>
+        <v>0.9992099400000001</v>
       </c>
       <c r="F55">
-        <v>0.9994000000000002</v>
+        <v>0.9992099400000001</v>
       </c>
       <c r="G55">
-        <v>0.5438253854918791</v>
+        <v>0.1912346098381414</v>
       </c>
       <c r="H55">
-        <v>0.9994000000000002</v>
+        <v>0.9992099400000001</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1">
-        <v>46154</v>
+        <v>46170</v>
       </c>
       <c r="B56" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C56">
-        <v>50.89464485280568</v>
+        <v>36.57358557066742</v>
       </c>
       <c r="D56">
-        <v>23.21558303176282</v>
+        <v>22.83069636955243</v>
       </c>
       <c r="E56">
-        <v>0.9996</v>
+        <v>0.9994435600000001</v>
       </c>
       <c r="F56">
-        <v>0.9996</v>
+        <v>0.9994435600000001</v>
       </c>
       <c r="G56">
-        <v>0.5034825029548833</v>
+        <v>0.2012778603742877</v>
       </c>
       <c r="H56">
-        <v>0.9996</v>
+        <v>0.9994435600000001</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1">
-        <v>46155</v>
+        <v>46171</v>
       </c>
       <c r="B57" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C57">
-        <v>51.8659994471731</v>
+        <v>36.67481300942</v>
       </c>
       <c r="D57">
-        <v>23.7009037279043</v>
+        <v>22.95852861681004</v>
       </c>
       <c r="E57">
-        <v>1.0002</v>
+        <v>0.9964953299999998</v>
       </c>
       <c r="F57">
-        <v>1.0002</v>
+        <v>0.9964953299999998</v>
       </c>
       <c r="G57">
-        <v>0.533512029714132</v>
+        <v>0.2057034850411275</v>
       </c>
       <c r="H57">
-        <v>1.0002</v>
+        <v>0.9994474899999999</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1">
-        <v>46156</v>
+        <v>46174</v>
       </c>
       <c r="B58" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C58">
-        <v>52.4470179952828</v>
+        <v>36.84565507982974</v>
       </c>
       <c r="D58">
-        <v>23.76861704536814</v>
+        <v>23.15960292175205</v>
       </c>
       <c r="E58">
-        <v>0.9998</v>
+        <v>0.99646052</v>
       </c>
       <c r="F58">
-        <v>0.9998</v>
+        <v>0.99646052</v>
       </c>
       <c r="G58">
-        <v>0.5492634496849078</v>
+        <v>0.2129379226426205</v>
       </c>
       <c r="H58">
-        <v>0.9998</v>
+        <v>0.9993986199999999</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="B59" t="s">
         <v>12</v>
       </c>
       <c r="C59">
-        <v>50.81077380018606</v>
+        <v>52.70832779833182</v>
       </c>
       <c r="D59">
-        <v>22.76900580927995</v>
+        <v>23.99044674439659</v>
       </c>
       <c r="E59">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="F59">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="G59">
-        <v>0.4903296143797722</v>
+        <v>0.5438253854918791</v>
       </c>
       <c r="H59">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1">
-        <v>46160</v>
+        <v>46154</v>
       </c>
       <c r="B60" t="s">
         <v>12</v>
       </c>
       <c r="C60">
-        <v>49.50286387149169</v>
+        <v>50.89464485280568</v>
       </c>
       <c r="D60">
-        <v>22.24532119914133</v>
+        <v>23.21558303176282</v>
       </c>
       <c r="E60">
         <v>0.9996</v>
@@ -1957,7 +1957,7 @@
         <v>0.9996</v>
       </c>
       <c r="G60">
-        <v>0.4630591776162345</v>
+        <v>0.5034825029548833</v>
       </c>
       <c r="H60">
         <v>0.9996</v>
@@ -1965,224 +1965,224 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1">
-        <v>46161</v>
+        <v>46155</v>
       </c>
       <c r="B61" t="s">
         <v>12</v>
       </c>
       <c r="C61">
-        <v>49.29146729279496</v>
+        <v>51.8659994471731</v>
       </c>
       <c r="D61">
-        <v>22.22167836589682</v>
+        <v>23.7009037279043</v>
       </c>
       <c r="E61">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="F61">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="G61">
-        <v>0.4571659248870246</v>
+        <v>0.533512029714132</v>
       </c>
       <c r="H61">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1">
-        <v>46162</v>
+        <v>46156</v>
       </c>
       <c r="B62" t="s">
         <v>12</v>
       </c>
       <c r="C62">
-        <v>50.88652370817657</v>
+        <v>52.4470179952828</v>
       </c>
       <c r="D62">
-        <v>22.93254398967657</v>
+        <v>23.76861704536814</v>
       </c>
       <c r="E62">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F62">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G62">
-        <v>0.5126171754864624</v>
+        <v>0.5492634496849078</v>
       </c>
       <c r="H62">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1">
-        <v>46163</v>
+        <v>46157</v>
       </c>
       <c r="B63" t="s">
         <v>12</v>
       </c>
       <c r="C63">
-        <v>48.26646764818586</v>
+        <v>50.81077380018606</v>
       </c>
       <c r="D63">
-        <v>23.11655387625012</v>
+        <v>22.76900580927995</v>
       </c>
       <c r="E63">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="F63">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="G63">
-        <v>0.521243030947425</v>
+        <v>0.4903296143797722</v>
       </c>
       <c r="H63">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1">
-        <v>46164</v>
+        <v>46160</v>
       </c>
       <c r="B64" t="s">
         <v>12</v>
       </c>
       <c r="C64">
-        <v>48.84737503703267</v>
+        <v>49.50286387149169</v>
       </c>
       <c r="D64">
-        <v>22.83557604744466</v>
+        <v>22.24532119914133</v>
       </c>
       <c r="E64">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="F64">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="G64">
-        <v>0.5438521997590966</v>
+        <v>0.4630591776162345</v>
       </c>
       <c r="H64">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1">
-        <v>46167</v>
+        <v>46161</v>
       </c>
       <c r="B65" t="s">
         <v>12</v>
       </c>
       <c r="C65">
-        <v>48.85151560750146</v>
+        <v>49.29146729279496</v>
       </c>
       <c r="D65">
-        <v>22.83513820206554</v>
+        <v>22.22167836589682</v>
       </c>
       <c r="E65">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F65">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G65">
-        <v>0.5438521997590966</v>
+        <v>0.4571659248870246</v>
       </c>
       <c r="H65">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1">
-        <v>46168</v>
+        <v>46162</v>
       </c>
       <c r="B66" t="s">
         <v>12</v>
       </c>
       <c r="C66">
-        <v>50.90437883274981</v>
+        <v>50.88652370817657</v>
       </c>
       <c r="D66">
-        <v>24.25672473501501</v>
+        <v>22.93254398967657</v>
       </c>
       <c r="E66">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F66">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G66">
-        <v>0.6130191115419561</v>
+        <v>0.5126171754864624</v>
       </c>
       <c r="H66">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1">
-        <v>46169</v>
+        <v>46163</v>
       </c>
       <c r="B67" t="s">
         <v>12</v>
       </c>
       <c r="C67">
-        <v>50.47312432255841</v>
+        <v>48.26646764818586</v>
       </c>
       <c r="D67">
-        <v>23.84499305142194</v>
+        <v>23.11655387625012</v>
       </c>
       <c r="E67">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="F67">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="G67">
-        <v>0.5952317692821967</v>
+        <v>0.521243030947425</v>
       </c>
       <c r="H67">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1">
-        <v>46170</v>
+        <v>46164</v>
       </c>
       <c r="B68" t="s">
         <v>12</v>
       </c>
       <c r="C68">
-        <v>50.84596269629946</v>
+        <v>48.84737503703267</v>
       </c>
       <c r="D68">
-        <v>23.7680603326165</v>
+        <v>22.83557604744466</v>
       </c>
       <c r="E68">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F68">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G68">
-        <v>0.606831065374982</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H68">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1">
-        <v>46171</v>
+        <v>46167</v>
       </c>
       <c r="B69" t="s">
         <v>12</v>
       </c>
       <c r="C69">
-        <v>51.08372269965196</v>
+        <v>48.85151560750146</v>
       </c>
       <c r="D69">
-        <v>23.88880359436525</v>
+        <v>22.83513820206554</v>
       </c>
       <c r="E69">
         <v>0.9998999999999999</v>
@@ -2191,7 +2191,7 @@
         <v>0.9998999999999999</v>
       </c>
       <c r="G69">
-        <v>0.604420070348211</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H69">
         <v>0.9998999999999999</v>
@@ -2199,1030 +2199,1030 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1">
-        <v>46153</v>
+        <v>46168</v>
       </c>
       <c r="B70" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C70">
-        <v>57.1732166855686</v>
+        <v>50.90437883274981</v>
       </c>
       <c r="D70">
-        <v>23.50022751267814</v>
+        <v>24.25672473501501</v>
       </c>
       <c r="E70">
-        <v>0.9991</v>
+        <v>0.9996999999999999</v>
       </c>
       <c r="F70">
-        <v>0.9991</v>
+        <v>0.9996999999999999</v>
       </c>
       <c r="G70">
-        <v>0.6994110097039083</v>
+        <v>0.6130191115419561</v>
       </c>
       <c r="H70">
-        <v>0.9991</v>
+        <v>0.9996999999999999</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1">
-        <v>46154</v>
+        <v>46169</v>
       </c>
       <c r="B71" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C71">
-        <v>54.77380642078597</v>
+        <v>50.47312432255841</v>
       </c>
       <c r="D71">
-        <v>22.55192940254518</v>
+        <v>23.84499305142194</v>
       </c>
       <c r="E71">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
       <c r="F71">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
       <c r="G71">
-        <v>0.6459175880844941</v>
+        <v>0.5952317692821967</v>
       </c>
       <c r="H71">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1">
-        <v>46155</v>
+        <v>46170</v>
       </c>
       <c r="B72" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C72">
-        <v>56.32187380830906</v>
+        <v>50.84596269629946</v>
       </c>
       <c r="D72">
-        <v>23.17121437414109</v>
+        <v>23.7680603326165</v>
       </c>
       <c r="E72">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
       <c r="F72">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
       <c r="G72">
-        <v>0.6851523922954754</v>
+        <v>0.606831065374982</v>
       </c>
       <c r="H72">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1">
-        <v>46156</v>
+        <v>46171</v>
       </c>
       <c r="B73" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C73">
-        <v>56.15321618553139</v>
+        <v>51.08372269965196</v>
       </c>
       <c r="D73">
-        <v>22.95838347314443</v>
+        <v>23.88880359436525</v>
       </c>
       <c r="E73">
-        <v>0.9992</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F73">
-        <v>0.9992</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G73">
-        <v>0.6907028507208208</v>
+        <v>0.604420070348211</v>
       </c>
       <c r="H73">
-        <v>0.9992</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1">
-        <v>46157</v>
+        <v>46174</v>
       </c>
       <c r="B74" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C74">
-        <v>54.47755813049488</v>
+        <v>51.84875713649351</v>
       </c>
       <c r="D74">
-        <v>22.0083816089626</v>
+        <v>24.29466650399529</v>
       </c>
       <c r="E74">
-        <v>0.9986</v>
+        <v>0.9998</v>
       </c>
       <c r="F74">
-        <v>0.9986</v>
+        <v>0.9998</v>
       </c>
       <c r="G74">
-        <v>0.6220895940829376</v>
+        <v>0.6282079224060508</v>
       </c>
       <c r="H74">
-        <v>0.9986</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
       </c>
       <c r="C75">
-        <v>52.6278781150669</v>
+        <v>57.1732166855686</v>
       </c>
       <c r="D75">
-        <v>21.5357353870778</v>
+        <v>23.50022751267814</v>
       </c>
       <c r="E75">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F75">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G75">
-        <v>0.5845134636435627</v>
+        <v>0.6994110097039083</v>
       </c>
       <c r="H75">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
       </c>
       <c r="C76">
-        <v>54.91583234840245</v>
+        <v>54.77380642078597</v>
       </c>
       <c r="D76">
-        <v>22.38321645985006</v>
+        <v>22.55192940254518</v>
       </c>
       <c r="E76">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F76">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G76">
-        <v>0.6596976539194066</v>
+        <v>0.6459175880844941</v>
       </c>
       <c r="H76">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
       </c>
       <c r="C77">
-        <v>53.91712298548793</v>
+        <v>56.32187380830906</v>
       </c>
       <c r="D77">
-        <v>22.73711181201267</v>
+        <v>23.17121437414109</v>
       </c>
       <c r="E77">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F77">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G77">
-        <v>0.6737329602396263</v>
+        <v>0.6851523922954754</v>
       </c>
       <c r="H77">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="1">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
       </c>
       <c r="C78">
-        <v>55.19651747515625</v>
+        <v>56.15321618553139</v>
       </c>
       <c r="D78">
-        <v>22.79462037330554</v>
+        <v>22.95838347314443</v>
       </c>
       <c r="E78">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
       <c r="F78">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
       <c r="G78">
-        <v>0.7139885317003913</v>
+        <v>0.6907028507208208</v>
       </c>
       <c r="H78">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
       </c>
       <c r="C79">
-        <v>55.28054997487197</v>
+        <v>54.47755813049488</v>
       </c>
       <c r="D79">
-        <v>23.00160891539877</v>
+        <v>22.0083816089626</v>
       </c>
       <c r="E79">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="F79">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="G79">
-        <v>0.7139885317003913</v>
+        <v>0.6220895940829376</v>
       </c>
       <c r="H79">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1">
-        <v>46168</v>
+        <v>46161</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
       </c>
       <c r="C80">
-        <v>58.75156728873073</v>
+        <v>52.6278781150669</v>
       </c>
       <c r="D80">
-        <v>24.84249654093248</v>
+        <v>21.5357353870778</v>
       </c>
       <c r="E80">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="F80">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="G80">
-        <v>0.8184872182632257</v>
+        <v>0.5845134636435627</v>
       </c>
       <c r="H80">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="1">
-        <v>46169</v>
+        <v>46162</v>
       </c>
       <c r="B81" t="s">
         <v>13</v>
       </c>
       <c r="C81">
-        <v>57.86771234337395</v>
+        <v>54.91583234840245</v>
       </c>
       <c r="D81">
-        <v>24.21066615243091</v>
+        <v>22.38321645985006</v>
       </c>
       <c r="E81">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="F81">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="G81">
-        <v>0.798997241708943</v>
+        <v>0.6596976539194066</v>
       </c>
       <c r="H81">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="1">
-        <v>46170</v>
+        <v>46163</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
       </c>
       <c r="C82">
-        <v>58.18666682631797</v>
+        <v>53.91712298548793</v>
       </c>
       <c r="D82">
-        <v>24.09552344282839</v>
+        <v>22.73711181201267</v>
       </c>
       <c r="E82">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="F82">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="G82">
-        <v>0.8165093478664007</v>
+        <v>0.6737329602396263</v>
       </c>
       <c r="H82">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="1">
-        <v>46171</v>
+        <v>46164</v>
       </c>
       <c r="B83" t="s">
         <v>13</v>
       </c>
       <c r="C83">
-        <v>58.79256019733606</v>
+        <v>55.19651747515625</v>
       </c>
       <c r="D83">
-        <v>24.33854853448823</v>
+        <v>22.79462037330554</v>
       </c>
       <c r="E83">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F83">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G83">
-        <v>0.8152654642198496</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H83">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="1">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="B84" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C84">
-        <v>35.78646526282436</v>
+        <v>55.28054997487197</v>
       </c>
       <c r="D84">
-        <v>18.96635091925032</v>
+        <v>23.00160891539877</v>
       </c>
       <c r="E84">
-        <v>0.9996491399999999</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="F84">
-        <v>0.9996491399999999</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="G84">
-        <v>0.2240600969213613</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H84">
-        <v>0.9985614899999999</v>
+        <v>0.9989000000000001</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1">
-        <v>46154</v>
+        <v>46168</v>
       </c>
       <c r="B85" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C85">
-        <v>35.71584102184062</v>
+        <v>58.75156728873073</v>
       </c>
       <c r="D85">
-        <v>18.62432950231353</v>
+        <v>24.84249654093248</v>
       </c>
       <c r="E85">
-        <v>0.99965481</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="F85">
-        <v>0.99965481</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="G85">
-        <v>0.2104844827747143</v>
+        <v>0.8184872182632257</v>
       </c>
       <c r="H85">
-        <v>0.9985622199999999</v>
+        <v>0.9989000000000001</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="1">
-        <v>46155</v>
+        <v>46169</v>
       </c>
       <c r="B86" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C86">
-        <v>35.95182028203252</v>
+        <v>57.86771234337395</v>
       </c>
       <c r="D86">
-        <v>18.95670796791552</v>
+        <v>24.21066615243091</v>
       </c>
       <c r="E86">
-        <v>0.9996515200000001</v>
+        <v>0.9986999999999999</v>
       </c>
       <c r="F86">
-        <v>0.9996515200000001</v>
+        <v>0.9986999999999999</v>
       </c>
       <c r="G86">
-        <v>0.2259035693959275</v>
+        <v>0.798997241708943</v>
       </c>
       <c r="H86">
-        <v>0.99855193</v>
+        <v>0.9986999999999999</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="1">
-        <v>46156</v>
+        <v>46170</v>
       </c>
       <c r="B87" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C87">
-        <v>36.14451597805883</v>
+        <v>58.18666682631797</v>
       </c>
       <c r="D87">
-        <v>18.86297660538653</v>
+        <v>24.09552344282839</v>
       </c>
       <c r="E87">
-        <v>0.9996563399999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F87">
-        <v>0.9996563399999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G87">
-        <v>0.2362110061840785</v>
+        <v>0.8165093478664007</v>
       </c>
       <c r="H87">
-        <v>0.99857265</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1">
-        <v>46157</v>
+        <v>46171</v>
       </c>
       <c r="B88" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C88">
-        <v>35.32805803135546</v>
+        <v>58.79256019733606</v>
       </c>
       <c r="D88">
-        <v>18.35643242381478</v>
+        <v>24.33854853448823</v>
       </c>
       <c r="E88">
-        <v>0.9997415800000001</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="F88">
-        <v>0.9997415800000001</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="G88">
-        <v>0.2023559161375383</v>
+        <v>0.8152654642198496</v>
       </c>
       <c r="H88">
-        <v>0.9986639900000002</v>
+        <v>0.9989999999999999</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="1">
-        <v>46160</v>
+        <v>46174</v>
       </c>
       <c r="B89" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C89">
-        <v>34.83995455757461</v>
+        <v>58.97156722185718</v>
       </c>
       <c r="D89">
-        <v>18.02301281718857</v>
+        <v>24.48296361348067</v>
       </c>
       <c r="E89">
-        <v>0.9996851299999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F89">
-        <v>0.9996851299999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G89">
-        <v>0.1850932291737926</v>
+        <v>0.8243563865851753</v>
       </c>
       <c r="H89">
-        <v>0.99857724</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B90" t="s">
         <v>14</v>
       </c>
       <c r="C90">
-        <v>34.45479308705605</v>
+        <v>35.78646526282436</v>
       </c>
       <c r="D90">
-        <v>18.09576834566068</v>
+        <v>18.96635091925032</v>
       </c>
       <c r="E90">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="F90">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="G90">
-        <v>0.1784731209386736</v>
+        <v>0.2240600969213613</v>
       </c>
       <c r="H90">
-        <v>0.9985337599999999</v>
+        <v>0.9985614899999999</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B91" t="s">
         <v>14</v>
       </c>
       <c r="C91">
-        <v>34.96336277390787</v>
+        <v>35.71584102184062</v>
       </c>
       <c r="D91">
-        <v>18.34938420029253</v>
+        <v>18.62432950231353</v>
       </c>
       <c r="E91">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="F91">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="G91">
-        <v>0.2009313391215752</v>
+        <v>0.2104844827747143</v>
       </c>
       <c r="H91">
-        <v>0.99848777</v>
+        <v>0.9985622199999999</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B92" t="s">
         <v>14</v>
       </c>
       <c r="C92">
-        <v>34.44616924817128</v>
+        <v>35.95182028203252</v>
       </c>
       <c r="D92">
-        <v>18.60085625074367</v>
+        <v>18.95670796791552</v>
       </c>
       <c r="E92">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="F92">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="G92">
-        <v>0.2124957180214682</v>
+        <v>0.2259035693959275</v>
       </c>
       <c r="H92">
-        <v>0.9985085200000001</v>
+        <v>0.99855193</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="1">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="B93" t="s">
         <v>14</v>
       </c>
       <c r="C93">
-        <v>34.62137220937314</v>
+        <v>36.14451597805883</v>
       </c>
       <c r="D93">
-        <v>18.28780484745949</v>
+        <v>18.86297660538653</v>
       </c>
       <c r="E93">
-        <v>0.9996106299999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="F93">
-        <v>0.9996106299999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="G93">
-        <v>0.2145907067863493</v>
+        <v>0.2362110061840785</v>
       </c>
       <c r="H93">
-        <v>0.9932939299999999</v>
+        <v>0.99857265</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="1">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="B94" t="s">
         <v>14</v>
       </c>
       <c r="C94">
-        <v>34.6540695486741</v>
+        <v>35.32805803135546</v>
       </c>
       <c r="D94">
-        <v>18.36409048915342</v>
+        <v>18.35643242381478</v>
       </c>
       <c r="E94">
-        <v>0.9995448900000001</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="F94">
-        <v>0.9995448900000001</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="G94">
-        <v>0.2145907067863493</v>
+        <v>0.2023559161375383</v>
       </c>
       <c r="H94">
-        <v>0.9984302600000001</v>
+        <v>0.9986639900000002</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="1">
-        <v>46168</v>
+        <v>46160</v>
       </c>
       <c r="B95" t="s">
         <v>14</v>
       </c>
       <c r="C95">
-        <v>35.4820130509417</v>
+        <v>34.83995455757461</v>
       </c>
       <c r="D95">
-        <v>19.20292041814603</v>
+        <v>18.02301281718857</v>
       </c>
       <c r="E95">
-        <v>0.9995448900000001</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="F95">
-        <v>0.9995448900000001</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="G95">
-        <v>0.2553172934903569</v>
+        <v>0.1850932291737926</v>
       </c>
       <c r="H95">
-        <v>0.9984302600000001</v>
+        <v>0.99857724</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="1">
-        <v>46169</v>
+        <v>46161</v>
       </c>
       <c r="B96" t="s">
         <v>14</v>
       </c>
       <c r="C96">
-        <v>35.71913468603401</v>
+        <v>34.45479308705605</v>
       </c>
       <c r="D96">
-        <v>18.96318693998171</v>
+        <v>18.09576834566068</v>
       </c>
       <c r="E96">
-        <v>0.99955466</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="F96">
-        <v>0.99955466</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="G96">
-        <v>0.2536413280520453</v>
+        <v>0.1784731209386736</v>
       </c>
       <c r="H96">
-        <v>0.9984700500000001</v>
+        <v>0.9985337599999999</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="1">
-        <v>46170</v>
+        <v>46162</v>
       </c>
       <c r="B97" t="s">
         <v>14</v>
       </c>
       <c r="C97">
-        <v>35.76226417354731</v>
+        <v>34.96336277390787</v>
       </c>
       <c r="D97">
-        <v>18.89050847207122</v>
+        <v>18.34938420029253</v>
       </c>
       <c r="E97">
-        <v>0.9995525399999999</v>
+        <v>0.99963413</v>
       </c>
       <c r="F97">
-        <v>0.9995525399999999</v>
+        <v>0.99963413</v>
       </c>
       <c r="G97">
-        <v>0.2580826940041561</v>
+        <v>0.2009313391215752</v>
       </c>
       <c r="H97">
-        <v>0.99847732</v>
+        <v>0.99848777</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="1">
-        <v>46171</v>
+        <v>46163</v>
       </c>
       <c r="B98" t="s">
         <v>14</v>
       </c>
       <c r="C98">
-        <v>35.84309020154227</v>
+        <v>34.44616924817128</v>
       </c>
       <c r="D98">
-        <v>19.06511612333149</v>
+        <v>18.60085625074367</v>
       </c>
       <c r="E98">
-        <v>0.9995533299999999</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="F98">
-        <v>0.9995533299999999</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="G98">
-        <v>0.2619374017254759</v>
+        <v>0.2124957180214682</v>
       </c>
       <c r="H98">
-        <v>0.99849382</v>
+        <v>0.9985085200000001</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="1">
-        <v>46153</v>
+        <v>46164</v>
       </c>
       <c r="B99" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C99">
-        <v>28.12253390077671</v>
+        <v>34.62137220937314</v>
       </c>
       <c r="D99">
-        <v>23.58699683751922</v>
+        <v>18.28780484745949</v>
       </c>
       <c r="E99">
-        <v>0.9997295369999999</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="F99">
-        <v>0.9997295369999999</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="G99">
-        <v>0.03368732240295347</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H99">
-        <v>0.9997295369999999</v>
+        <v>0.9932939299999999</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="1">
-        <v>46154</v>
+        <v>46167</v>
       </c>
       <c r="B100" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C100">
-        <v>28.17715727830483</v>
+        <v>34.6540695486741</v>
       </c>
       <c r="D100">
-        <v>23.63894513078866</v>
+        <v>18.36409048915342</v>
       </c>
       <c r="E100">
-        <v>1.000319473</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="F100">
-        <v>1.000319473</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="G100">
-        <v>0.03515547182056333</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H100">
-        <v>1.000319473</v>
+        <v>0.9984302600000001</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="1">
-        <v>46155</v>
+        <v>46168</v>
       </c>
       <c r="B101" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C101">
-        <v>28.59002627414054</v>
+        <v>35.4820130509417</v>
       </c>
       <c r="D101">
-        <v>23.96230704059692</v>
+        <v>19.20292041814603</v>
       </c>
       <c r="E101">
-        <v>0.9999999989999999</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="F101">
-        <v>0.9999999989999999</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="G101">
-        <v>0.05179637495949674</v>
+        <v>0.2553172934903569</v>
       </c>
       <c r="H101">
-        <v>0.9999999989999999</v>
+        <v>0.9984302600000001</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="1">
-        <v>46156</v>
+        <v>46169</v>
       </c>
       <c r="B102" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C102">
-        <v>28.56217859389523</v>
+        <v>35.71913468603401</v>
       </c>
       <c r="D102">
-        <v>23.9411987302529</v>
+        <v>18.96318693998171</v>
       </c>
       <c r="E102">
-        <v>1</v>
+        <v>0.99955466</v>
       </c>
       <c r="F102">
-        <v>1</v>
+        <v>0.99955466</v>
       </c>
       <c r="G102">
-        <v>0.04837024516756849</v>
+        <v>0.2536413280520453</v>
       </c>
       <c r="H102">
-        <v>1</v>
+        <v>0.9984700500000001</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="1">
-        <v>46157</v>
+        <v>46170</v>
       </c>
       <c r="B103" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C103">
-        <v>28.57618675936338</v>
+        <v>35.76226417354731</v>
       </c>
       <c r="D103">
-        <v>23.9576220541054</v>
+        <v>18.89050847207122</v>
       </c>
       <c r="E103">
-        <v>0.999503249</v>
+        <v>0.9995525399999999</v>
       </c>
       <c r="F103">
-        <v>0.999503249</v>
+        <v>0.9995525399999999</v>
       </c>
       <c r="G103">
-        <v>0.04983868243960732</v>
+        <v>0.2580826940041561</v>
       </c>
       <c r="H103">
-        <v>0.999503249</v>
+        <v>0.99847732</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="1">
-        <v>46160</v>
+        <v>46171</v>
       </c>
       <c r="B104" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C104">
-        <v>28.68951918518517</v>
+        <v>35.84309020154227</v>
       </c>
       <c r="D104">
-        <v>24.06134728453882</v>
+        <v>19.06511612333149</v>
       </c>
       <c r="E104">
-        <v>0.999503249</v>
+        <v>0.9995533299999999</v>
       </c>
       <c r="F104">
-        <v>0.999503249</v>
+        <v>0.9995533299999999</v>
       </c>
       <c r="G104">
-        <v>0.04983868243960732</v>
+        <v>0.2619374017254759</v>
       </c>
       <c r="H104">
-        <v>0.999503249</v>
+        <v>0.99849382</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="1">
-        <v>46161</v>
+        <v>46174</v>
       </c>
       <c r="B105" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C105">
-        <v>28.31167386654059</v>
+        <v>36.27022125574057</v>
       </c>
       <c r="D105">
-        <v>23.75157719455474</v>
+        <v>19.32711369104533</v>
       </c>
       <c r="E105">
-        <v>1.000177331</v>
+        <v>0.9995550400000001</v>
       </c>
       <c r="F105">
-        <v>1.000177331</v>
+        <v>0.9995550400000001</v>
       </c>
       <c r="G105">
-        <v>0.04053938625111919</v>
+        <v>0.2764348160433892</v>
       </c>
       <c r="H105">
-        <v>1.000177331</v>
+        <v>0.9985177199999999</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="1">
-        <v>46162</v>
+        <v>46153</v>
       </c>
       <c r="B106" t="s">
         <v>15</v>
       </c>
       <c r="C106">
-        <v>28.57911382310097</v>
+        <v>28.12253390077671</v>
       </c>
       <c r="D106">
-        <v>23.89431741541233</v>
+        <v>23.58699683751922</v>
       </c>
       <c r="E106">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="F106">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="G106">
-        <v>0.04690190590044785</v>
+        <v>0.03368732240295347</v>
       </c>
       <c r="H106">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="1">
-        <v>46163</v>
+        <v>46154</v>
       </c>
       <c r="B107" t="s">
         <v>15</v>
       </c>
       <c r="C107">
-        <v>28.55785065378643</v>
+        <v>28.17715727830483</v>
       </c>
       <c r="D107">
-        <v>24.04274714970193</v>
+        <v>23.63894513078866</v>
       </c>
       <c r="E107">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="F107">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="G107">
-        <v>0.05228572319419666</v>
+        <v>0.03515547182056333</v>
       </c>
       <c r="H107">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="1">
-        <v>46164</v>
+        <v>46155</v>
       </c>
       <c r="B108" t="s">
         <v>15</v>
       </c>
       <c r="C108">
-        <v>28.50194638163107</v>
+        <v>28.59002627414054</v>
       </c>
       <c r="D108">
-        <v>23.99272397156045</v>
+        <v>23.96230704059692</v>
       </c>
       <c r="E108">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F108">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G108">
-        <v>0.04934923597154284</v>
+        <v>0.05179637495949674</v>
       </c>
       <c r="H108">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="1">
-        <v>46167</v>
+        <v>46156</v>
       </c>
       <c r="B109" t="s">
         <v>15</v>
       </c>
       <c r="C109">
-        <v>28.55106858744498</v>
+        <v>28.56217859389523</v>
       </c>
       <c r="D109">
-        <v>23.9768329565351</v>
+        <v>23.9411987302529</v>
       </c>
       <c r="E109">
         <v>1</v>
@@ -3231,7 +3231,7 @@
         <v>1</v>
       </c>
       <c r="G109">
-        <v>0.05571185335164408</v>
+        <v>0.04837024516756849</v>
       </c>
       <c r="H109">
         <v>1</v>
@@ -3239,496 +3239,730 @@
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="1">
-        <v>46168</v>
+        <v>46157</v>
       </c>
       <c r="B110" t="s">
         <v>15</v>
       </c>
       <c r="C110">
-        <v>28.54681541456266</v>
+        <v>28.57618675936338</v>
       </c>
       <c r="D110">
-        <v>23.97386168967948</v>
+        <v>23.9576220541054</v>
       </c>
       <c r="E110">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="F110">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="G110">
-        <v>0.04837034303541388</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H110">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="1">
-        <v>46169</v>
+        <v>46160</v>
       </c>
       <c r="B111" t="s">
         <v>15</v>
       </c>
       <c r="C111">
-        <v>28.83672936868491</v>
+        <v>28.68951918518517</v>
       </c>
       <c r="D111">
-        <v>24.203511281145</v>
+        <v>24.06134728453882</v>
       </c>
       <c r="E111">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="F111">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="G111">
-        <v>0.05962723282507953</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H111">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="1">
-        <v>46170</v>
+        <v>46161</v>
       </c>
       <c r="B112" t="s">
         <v>15</v>
       </c>
       <c r="C112">
-        <v>28.88109630394224</v>
+        <v>28.31167386654059</v>
       </c>
       <c r="D112">
-        <v>24.34085451035401</v>
+        <v>23.75157719455474</v>
       </c>
       <c r="E112">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
       <c r="F112">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
       <c r="G112">
-        <v>0.06647938938594877</v>
+        <v>0.04053938625111919</v>
       </c>
       <c r="H112">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="1">
-        <v>46171</v>
+        <v>46162</v>
       </c>
       <c r="B113" t="s">
         <v>15</v>
       </c>
       <c r="C113">
-        <v>28.92588622185229</v>
+        <v>28.57911382310097</v>
       </c>
       <c r="D113">
-        <v>24.37463012178961</v>
+        <v>23.89431741541233</v>
       </c>
       <c r="E113">
-        <v>0.9999999989999999</v>
+        <v>0.999503734</v>
       </c>
       <c r="F113">
-        <v>0.9999999989999999</v>
+        <v>0.999503734</v>
       </c>
       <c r="G113">
-        <v>0.0669687424559624</v>
+        <v>0.04690190590044785</v>
       </c>
       <c r="H113">
-        <v>0.9999999989999999</v>
+        <v>0.999503734</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="1">
-        <v>46153</v>
+        <v>46163</v>
       </c>
       <c r="B114" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C114">
-        <v>40.68830633303975</v>
+        <v>28.55785065378643</v>
       </c>
       <c r="D114">
-        <v>21.50431773660198</v>
+        <v>24.04274714970193</v>
       </c>
       <c r="E114">
-        <v>0.99909852</v>
+        <v>1.000229282</v>
       </c>
       <c r="F114">
-        <v>0.99909852</v>
+        <v>1.000229282</v>
       </c>
       <c r="G114">
-        <v>0.2342423866086769</v>
+        <v>0.05228572319419666</v>
       </c>
       <c r="H114">
-        <v>0.9974930900000001</v>
+        <v>1.000229282</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="1">
-        <v>46154</v>
+        <v>46164</v>
       </c>
       <c r="B115" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C115">
-        <v>40.32854894972581</v>
+        <v>28.50194638163107</v>
       </c>
       <c r="D115">
-        <v>21.09133998298594</v>
+        <v>23.99272397156045</v>
       </c>
       <c r="E115">
-        <v>0.9990972199999999</v>
+        <v>1</v>
       </c>
       <c r="F115">
-        <v>0.9990972199999999</v>
+        <v>1</v>
       </c>
       <c r="G115">
-        <v>0.2156468205051487</v>
+        <v>0.04934923597154284</v>
       </c>
       <c r="H115">
-        <v>0.99752223</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="1">
-        <v>46155</v>
+        <v>46167</v>
       </c>
       <c r="B116" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C116">
-        <v>40.47987921095815</v>
+        <v>28.55106858744498</v>
       </c>
       <c r="D116">
-        <v>21.35995364434454</v>
+        <v>23.9768329565351</v>
       </c>
       <c r="E116">
-        <v>0.9991780100000001</v>
+        <v>1</v>
       </c>
       <c r="F116">
-        <v>0.9991780100000001</v>
+        <v>1</v>
       </c>
       <c r="G116">
-        <v>0.2270956128473374</v>
+        <v>0.05571185335164408</v>
       </c>
       <c r="H116">
-        <v>0.9975825700000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="1">
-        <v>46156</v>
+        <v>46168</v>
       </c>
       <c r="B117" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C117">
-        <v>41.20436574895244</v>
+        <v>28.54681541456266</v>
       </c>
       <c r="D117">
-        <v>21.48149674387778</v>
+        <v>23.97386168967948</v>
       </c>
       <c r="E117">
-        <v>0.9991793299999999</v>
+        <v>1</v>
       </c>
       <c r="F117">
-        <v>0.9991793299999999</v>
+        <v>1</v>
       </c>
       <c r="G117">
-        <v>0.2454829228401052</v>
+        <v>0.04837034303541388</v>
       </c>
       <c r="H117">
-        <v>0.99754722</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="1">
-        <v>46157</v>
+        <v>46169</v>
       </c>
       <c r="B118" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C118">
-        <v>40.80613062958688</v>
+        <v>28.83672936868491</v>
       </c>
       <c r="D118">
-        <v>21.08912555803936</v>
+        <v>24.203511281145</v>
       </c>
       <c r="E118">
-        <v>0.9991790600000001</v>
+        <v>1</v>
       </c>
       <c r="F118">
-        <v>0.9991790600000001</v>
+        <v>1</v>
       </c>
       <c r="G118">
-        <v>0.2230017445022556</v>
+        <v>0.05962723282507953</v>
       </c>
       <c r="H118">
-        <v>0.9975824700000002</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="1">
-        <v>46160</v>
+        <v>46170</v>
       </c>
       <c r="B119" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C119">
-        <v>40.11672876026724</v>
+        <v>28.88109630394224</v>
       </c>
       <c r="D119">
-        <v>20.79541439916316</v>
+        <v>24.34085451035401</v>
       </c>
       <c r="E119">
-        <v>0.999152</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F119">
-        <v>0.999152</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G119">
-        <v>0.2098184021536666</v>
+        <v>0.06647938938594877</v>
       </c>
       <c r="H119">
-        <v>0.9975007899999999</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="1">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="B120" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C120">
-        <v>39.69086941528401</v>
+        <v>28.92588622185229</v>
       </c>
       <c r="D120">
-        <v>20.74924328599426</v>
+        <v>24.37463012178961</v>
       </c>
       <c r="E120">
-        <v>0.99914989</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F120">
-        <v>0.99914989</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G120">
-        <v>0.2020471776850241</v>
+        <v>0.0669687424559624</v>
       </c>
       <c r="H120">
-        <v>0.9974417</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="1">
-        <v>46162</v>
+        <v>46174</v>
       </c>
       <c r="B121" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C121">
-        <v>40.37836787855562</v>
+        <v>28.479823472488</v>
       </c>
       <c r="D121">
-        <v>21.11271132314188</v>
+        <v>23.940843604634</v>
       </c>
       <c r="E121">
-        <v>0.99915058</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F121">
-        <v>0.99915058</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G121">
-        <v>0.2291077670847563</v>
+        <v>0.05385076946675693</v>
       </c>
       <c r="H121">
-        <v>0.9974415600000001</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="1">
-        <v>46163</v>
+        <v>46153</v>
       </c>
       <c r="B122" t="s">
         <v>16</v>
       </c>
       <c r="C122">
-        <v>38.9123066967842</v>
+        <v>40.68830633303975</v>
       </c>
       <c r="D122">
-        <v>21.28910644207464</v>
+        <v>21.50431773660198</v>
       </c>
       <c r="E122">
-        <v>0.9989350699999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="F122">
-        <v>0.9989350699999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="G122">
-        <v>0.2392382040170877</v>
+        <v>0.2342423866086769</v>
       </c>
       <c r="H122">
-        <v>0.99726191</v>
+        <v>0.9974930900000001</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="1">
-        <v>46164</v>
+        <v>46154</v>
       </c>
       <c r="B123" t="s">
         <v>16</v>
       </c>
       <c r="C123">
-        <v>39.43913909150694</v>
+        <v>40.32854894972581</v>
       </c>
       <c r="D123">
-        <v>21.05297617141148</v>
+        <v>21.09133998298594</v>
       </c>
       <c r="E123">
-        <v>0.999144</v>
+        <v>0.9990972199999999</v>
       </c>
       <c r="F123">
-        <v>0.999144</v>
+        <v>0.9990972199999999</v>
       </c>
       <c r="G123">
-        <v>0.2516582935428642</v>
+        <v>0.2156468205051487</v>
       </c>
       <c r="H123">
-        <v>0.9974678400000001</v>
+        <v>0.99752223</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="1">
-        <v>46167</v>
+        <v>46155</v>
       </c>
       <c r="B124" t="s">
         <v>16</v>
       </c>
       <c r="C124">
-        <v>39.45782844313628</v>
+        <v>40.47987921095815</v>
       </c>
       <c r="D124">
-        <v>21.0518901572272</v>
+        <v>21.35995364434454</v>
       </c>
       <c r="E124">
-        <v>0.999144</v>
+        <v>0.9991780100000001</v>
       </c>
       <c r="F124">
-        <v>0.999144</v>
+        <v>0.9991780100000001</v>
       </c>
       <c r="G124">
-        <v>0.2516582935428642</v>
+        <v>0.2270956128473374</v>
       </c>
       <c r="H124">
-        <v>0.9974678400000001</v>
+        <v>0.9975825700000001</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="1">
-        <v>46168</v>
+        <v>46156</v>
       </c>
       <c r="B125" t="s">
         <v>16</v>
       </c>
       <c r="C125">
-        <v>40.20219297984542</v>
+        <v>41.20436574895244</v>
       </c>
       <c r="D125">
-        <v>21.93106024403281</v>
+        <v>21.48149674387778</v>
       </c>
       <c r="E125">
-        <v>0.9991421799999999</v>
+        <v>0.9991793299999999</v>
       </c>
       <c r="F125">
-        <v>0.9991421799999999</v>
+        <v>0.9991793299999999</v>
       </c>
       <c r="G125">
-        <v>0.2846167552893293</v>
+        <v>0.2454829228401052</v>
       </c>
       <c r="H125">
-        <v>0.9974609800000001</v>
+        <v>0.99754722</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" s="1">
-        <v>46169</v>
+        <v>46157</v>
       </c>
       <c r="B126" t="s">
         <v>16</v>
       </c>
       <c r="C126">
-        <v>40.34993865302093</v>
+        <v>40.80613062958688</v>
       </c>
       <c r="D126">
-        <v>21.65366031776487</v>
+        <v>21.08912555803936</v>
       </c>
       <c r="E126">
-        <v>0.9991434600000001</v>
+        <v>0.9991790600000001</v>
       </c>
       <c r="F126">
-        <v>0.9991434600000001</v>
+        <v>0.9991790600000001</v>
       </c>
       <c r="G126">
-        <v>0.2796902860011767</v>
+        <v>0.2230017445022556</v>
       </c>
       <c r="H126">
-        <v>0.9991434600000001</v>
+        <v>0.9975824700000002</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" s="1">
-        <v>46170</v>
+        <v>46160</v>
       </c>
       <c r="B127" t="s">
         <v>16</v>
       </c>
       <c r="C127">
-        <v>40.5850485390846</v>
+        <v>40.11672876026724</v>
       </c>
       <c r="D127">
-        <v>21.75450977746074</v>
+        <v>20.79541439916316</v>
       </c>
       <c r="E127">
-        <v>0.99914592</v>
+        <v>0.999152</v>
       </c>
       <c r="F127">
-        <v>0.99914592</v>
+        <v>0.999152</v>
       </c>
       <c r="G127">
-        <v>0.2964818481030536</v>
+        <v>0.2098184021536666</v>
       </c>
       <c r="H127">
-        <v>0.99914592</v>
+        <v>0.9975007899999999</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="1">
-        <v>46171</v>
+        <v>46161</v>
       </c>
       <c r="B128" t="s">
         <v>16</v>
       </c>
       <c r="C128">
+        <v>39.69086941528401</v>
+      </c>
+      <c r="D128">
+        <v>20.74924328599426</v>
+      </c>
+      <c r="E128">
+        <v>0.99914989</v>
+      </c>
+      <c r="F128">
+        <v>0.99914989</v>
+      </c>
+      <c r="G128">
+        <v>0.2020471776850241</v>
+      </c>
+      <c r="H128">
+        <v>0.9974417</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129">
+        <v>40.37836787855562</v>
+      </c>
+      <c r="D129">
+        <v>21.11271132314188</v>
+      </c>
+      <c r="E129">
+        <v>0.99915058</v>
+      </c>
+      <c r="F129">
+        <v>0.99915058</v>
+      </c>
+      <c r="G129">
+        <v>0.2291077670847563</v>
+      </c>
+      <c r="H129">
+        <v>0.9974415600000001</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130">
+        <v>38.9123066967842</v>
+      </c>
+      <c r="D130">
+        <v>21.28910644207464</v>
+      </c>
+      <c r="E130">
+        <v>0.9989350699999999</v>
+      </c>
+      <c r="F130">
+        <v>0.9989350699999999</v>
+      </c>
+      <c r="G130">
+        <v>0.2392382040170877</v>
+      </c>
+      <c r="H130">
+        <v>0.99726191</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="A131" s="1">
+        <v>46164</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131">
+        <v>39.43913909150694</v>
+      </c>
+      <c r="D131">
+        <v>21.05297617141148</v>
+      </c>
+      <c r="E131">
+        <v>0.999144</v>
+      </c>
+      <c r="F131">
+        <v>0.999144</v>
+      </c>
+      <c r="G131">
+        <v>0.2516582935428642</v>
+      </c>
+      <c r="H131">
+        <v>0.9974678400000001</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
+      <c r="A132" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132">
+        <v>39.45782844313628</v>
+      </c>
+      <c r="D132">
+        <v>21.0518901572272</v>
+      </c>
+      <c r="E132">
+        <v>0.999144</v>
+      </c>
+      <c r="F132">
+        <v>0.999144</v>
+      </c>
+      <c r="G132">
+        <v>0.2516582935428642</v>
+      </c>
+      <c r="H132">
+        <v>0.9974678400000001</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
+      <c r="A133" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133">
+        <v>40.20219297984542</v>
+      </c>
+      <c r="D133">
+        <v>21.93106024403281</v>
+      </c>
+      <c r="E133">
+        <v>0.9991421799999999</v>
+      </c>
+      <c r="F133">
+        <v>0.9991421799999999</v>
+      </c>
+      <c r="G133">
+        <v>0.2846167552893293</v>
+      </c>
+      <c r="H133">
+        <v>0.9974609800000001</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
+      <c r="A134" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134">
+        <v>40.34993865302093</v>
+      </c>
+      <c r="D134">
+        <v>21.65366031776487</v>
+      </c>
+      <c r="E134">
+        <v>0.9991434600000001</v>
+      </c>
+      <c r="F134">
+        <v>0.9991434600000001</v>
+      </c>
+      <c r="G134">
+        <v>0.2796902860011767</v>
+      </c>
+      <c r="H134">
+        <v>0.9991434600000001</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
+      <c r="A135" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135">
+        <v>40.5850485390846</v>
+      </c>
+      <c r="D135">
+        <v>21.75450977746074</v>
+      </c>
+      <c r="E135">
+        <v>0.99914592</v>
+      </c>
+      <c r="F135">
+        <v>0.99914592</v>
+      </c>
+      <c r="G135">
+        <v>0.2964818481030536</v>
+      </c>
+      <c r="H135">
+        <v>0.99914592</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136">
         <v>41.86785805184477</v>
       </c>
-      <c r="D128">
+      <c r="D136">
         <v>22.33589392797469</v>
       </c>
-      <c r="E128">
+      <c r="E136">
         <v>0.9991336999999999</v>
       </c>
-      <c r="F128">
+      <c r="F136">
         <v>0.9991336999999999</v>
       </c>
-      <c r="G128">
+      <c r="G136">
         <v>0.3254158954996882</v>
       </c>
-      <c r="H128">
+      <c r="H136">
         <v>0.9991336999999999</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
+      <c r="A137" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137">
+        <v>42.82932322850974</v>
+      </c>
+      <c r="D137">
+        <v>22.98998911430362</v>
+      </c>
+      <c r="E137">
+        <v>0.99914238</v>
+      </c>
+      <c r="F137">
+        <v>0.99914238</v>
+      </c>
+      <c r="G137">
+        <v>0.3583049032509023</v>
+      </c>
+      <c r="H137">
+        <v>0.99914238</v>
       </c>
     </row>
   </sheetData>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="17">
   <si>
     <t>Date</t>
   </si>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H137"/>
+  <dimension ref="A1:H146"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -665,42 +665,42 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1">
-        <v>46153</v>
+        <v>46175</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11">
-        <v>53.14833755912058</v>
+        <v>26.90315455444875</v>
       </c>
       <c r="D11">
-        <v>25.84885448407537</v>
+        <v>17.99426887002218</v>
       </c>
       <c r="E11">
-        <v>0.9262</v>
+        <v>0.8596999999999999</v>
       </c>
       <c r="F11">
-        <v>0.9262</v>
+        <v>0.8596999999999999</v>
       </c>
       <c r="G11">
-        <v>0.3839084462043663</v>
+        <v>0.7130319257127653</v>
       </c>
       <c r="H11">
-        <v>0.9262</v>
+        <v>0.9119999999999998</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
       </c>
       <c r="C12">
-        <v>51.82921169635205</v>
+        <v>53.14833755912058</v>
       </c>
       <c r="D12">
-        <v>25.32805827181975</v>
+        <v>25.84885448407537</v>
       </c>
       <c r="E12">
         <v>0.9262</v>
@@ -709,7 +709,7 @@
         <v>0.9262</v>
       </c>
       <c r="G12">
-        <v>0.3568580281685669</v>
+        <v>0.3839084462043663</v>
       </c>
       <c r="H12">
         <v>0.9262</v>
@@ -717,120 +717,120 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B13" t="s">
         <v>9</v>
       </c>
       <c r="C13">
-        <v>52.28471716753184</v>
+        <v>51.82921169635205</v>
       </c>
       <c r="D13">
-        <v>25.54525144150689</v>
+        <v>25.32805827181975</v>
       </c>
       <c r="E13">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="F13">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="G13">
-        <v>0.378012896547947</v>
+        <v>0.3568580281685669</v>
       </c>
       <c r="H13">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
       </c>
       <c r="C14">
-        <v>53.87287273813902</v>
+        <v>52.28471716753184</v>
       </c>
       <c r="D14">
-        <v>26.32154226438612</v>
+        <v>25.54525144150689</v>
       </c>
       <c r="E14">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="F14">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="G14">
-        <v>0.4166811087612758</v>
+        <v>0.378012896547947</v>
       </c>
       <c r="H14">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
       </c>
       <c r="C15">
-        <v>52.18747148214074</v>
+        <v>53.87287273813902</v>
       </c>
       <c r="D15">
-        <v>25.13616059644496</v>
+        <v>26.32154226438612</v>
       </c>
       <c r="E15">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="F15">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="G15">
-        <v>0.3627535778249862</v>
+        <v>0.4166811087612758</v>
       </c>
       <c r="H15">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
       </c>
       <c r="C16">
-        <v>50.72035274995172</v>
+        <v>52.18747148214074</v>
       </c>
       <c r="D16">
-        <v>24.61756040386634</v>
+        <v>25.13616059644496</v>
       </c>
       <c r="E16">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="F16">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="G16">
         <v>0.3627535778249862</v>
       </c>
       <c r="H16">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
       </c>
       <c r="C17">
-        <v>50.11981086673613</v>
+        <v>50.72035274995172</v>
       </c>
       <c r="D17">
-        <v>24.13061679021705</v>
+        <v>24.61756040386634</v>
       </c>
       <c r="E17">
         <v>0.9259000000000001</v>
@@ -839,7 +839,7 @@
         <v>0.9259000000000001</v>
       </c>
       <c r="G17">
-        <v>0.3258193430227221</v>
+        <v>0.3627535778249862</v>
       </c>
       <c r="H17">
         <v>0.9259000000000001</v>
@@ -847,120 +847,120 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="B18" t="s">
         <v>9</v>
       </c>
       <c r="C18">
-        <v>51.74165648409151</v>
+        <v>50.11981086673613</v>
       </c>
       <c r="D18">
-        <v>24.98091384114761</v>
+        <v>24.13061679021705</v>
       </c>
       <c r="E18">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="F18">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="G18">
-        <v>0.3818277262286871</v>
+        <v>0.3258193430227221</v>
       </c>
       <c r="H18">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="B19" t="s">
         <v>9</v>
       </c>
       <c r="C19">
-        <v>49.13455894175823</v>
+        <v>51.74165648409151</v>
       </c>
       <c r="D19">
-        <v>25.30005057653127</v>
+        <v>24.98091384114761</v>
       </c>
       <c r="E19">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="F19">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="G19">
-        <v>0.4028091571787618</v>
+        <v>0.3818277262286871</v>
       </c>
       <c r="H19">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="B20" t="s">
         <v>9</v>
       </c>
       <c r="C20">
-        <v>49.57776597479297</v>
+        <v>49.13455894175823</v>
       </c>
       <c r="D20">
-        <v>25.04906725563518</v>
+        <v>25.30005057653127</v>
       </c>
       <c r="E20">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="F20">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="G20">
-        <v>0.4256980029692063</v>
+        <v>0.4028091571787618</v>
       </c>
       <c r="H20">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="B21" t="s">
         <v>9</v>
       </c>
       <c r="C21">
-        <v>49.71239596645896</v>
+        <v>49.57776597479297</v>
       </c>
       <c r="D21">
-        <v>25.18778610744295</v>
+        <v>25.04906725563518</v>
       </c>
       <c r="E21">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="F21">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="G21">
-        <v>0.4525749835757003</v>
+        <v>0.4256980029692063</v>
       </c>
       <c r="H21">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="B22" t="s">
         <v>9</v>
       </c>
       <c r="C22">
-        <v>50.77166277510776</v>
+        <v>49.71239596645896</v>
       </c>
       <c r="D22">
-        <v>25.7431782858765</v>
+        <v>25.18778610744295</v>
       </c>
       <c r="E22">
         <v>0.9231999999999999</v>
@@ -969,7 +969,7 @@
         <v>0.9231999999999999</v>
       </c>
       <c r="G22">
-        <v>0.4700884597036457</v>
+        <v>0.4525749835757003</v>
       </c>
       <c r="H22">
         <v>0.9231999999999999</v>
@@ -977,250 +977,250 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1">
-        <v>46169</v>
+        <v>46168</v>
       </c>
       <c r="B23" t="s">
         <v>9</v>
       </c>
       <c r="C23">
-        <v>50.57689164833899</v>
+        <v>50.77166277510776</v>
       </c>
       <c r="D23">
-        <v>25.70244067238947</v>
+        <v>25.7431782858765</v>
       </c>
       <c r="E23">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="F23">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="G23">
-        <v>0.4518814984464716</v>
+        <v>0.4700884597036457</v>
       </c>
       <c r="H23">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="B24" t="s">
         <v>9</v>
       </c>
       <c r="C24">
-        <v>50.80027854822009</v>
+        <v>50.57689164833899</v>
       </c>
       <c r="D24">
-        <v>25.90068415792015</v>
+        <v>25.70244067238947</v>
       </c>
       <c r="E24">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
       <c r="F24">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
       <c r="G24">
-        <v>0.4699150222743402</v>
+        <v>0.4518814984464716</v>
       </c>
       <c r="H24">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
       </c>
       <c r="C25">
-        <v>51.44563447241545</v>
+        <v>50.80027854822009</v>
       </c>
       <c r="D25">
-        <v>26.0970978996374</v>
+        <v>25.90068415792015</v>
       </c>
       <c r="E25">
-        <v>0.9246</v>
+        <v>0.9231</v>
       </c>
       <c r="F25">
-        <v>0.9246</v>
+        <v>0.9231</v>
       </c>
       <c r="G25">
-        <v>0.4791053539115764</v>
+        <v>0.4699150222743402</v>
       </c>
       <c r="H25">
-        <v>0.9246</v>
+        <v>0.9231</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1">
-        <v>46174</v>
+        <v>46171</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
       </c>
       <c r="C26">
-        <v>53.05792083471825</v>
+        <v>51.44563447241545</v>
       </c>
       <c r="D26">
-        <v>26.86242981002239</v>
+        <v>26.0970978996374</v>
       </c>
       <c r="E26">
-        <v>0.9254999999999999</v>
+        <v>0.9246</v>
       </c>
       <c r="F26">
-        <v>0.9254999999999999</v>
+        <v>0.9246</v>
       </c>
       <c r="G26">
-        <v>0.5306051577195796</v>
+        <v>0.4791053539115764</v>
       </c>
       <c r="H26">
-        <v>0.9254999999999999</v>
+        <v>0.9246</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1">
-        <v>46153</v>
+        <v>46174</v>
       </c>
       <c r="B27" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C27">
-        <v>34.64560932909123</v>
+        <v>53.05792083471825</v>
       </c>
       <c r="D27">
-        <v>26.08311546080494</v>
+        <v>26.86242981002239</v>
       </c>
       <c r="E27">
-        <v>0.9983000000000001</v>
+        <v>0.9254999999999999</v>
       </c>
       <c r="F27">
-        <v>0.9983000000000001</v>
+        <v>0.9254999999999999</v>
       </c>
       <c r="G27">
-        <v>0.06258613715048233</v>
+        <v>0.5306051577195796</v>
       </c>
       <c r="H27">
-        <v>0.9983000000000001</v>
+        <v>0.9254999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1">
-        <v>46154</v>
+        <v>46175</v>
       </c>
       <c r="B28" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C28">
-        <v>34.50204921141101</v>
+        <v>54.38946369031042</v>
       </c>
       <c r="D28">
-        <v>25.94535229304585</v>
+        <v>27.57160808325711</v>
       </c>
       <c r="E28">
-        <v>0.9984</v>
+        <v>0.9254999999999999</v>
       </c>
       <c r="F28">
-        <v>0.9984</v>
+        <v>0.9254999999999999</v>
       </c>
       <c r="G28">
-        <v>0.05768943168306073</v>
+        <v>0.5845326886558693</v>
       </c>
       <c r="H28">
-        <v>0.9984</v>
+        <v>0.9254999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="B29" t="s">
         <v>10</v>
       </c>
       <c r="C29">
-        <v>35.10429483281073</v>
+        <v>34.64560932909123</v>
       </c>
       <c r="D29">
-        <v>26.43864879939599</v>
+        <v>26.08311546080494</v>
       </c>
       <c r="E29">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="F29">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="G29">
-        <v>0.07926550001722021</v>
+        <v>0.06258613715048233</v>
       </c>
       <c r="H29">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="B30" t="s">
         <v>10</v>
       </c>
       <c r="C30">
-        <v>35.36860632820093</v>
+        <v>34.50204921141101</v>
       </c>
       <c r="D30">
-        <v>26.56575571102338</v>
+        <v>25.94535229304585</v>
       </c>
       <c r="E30">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F30">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G30">
-        <v>0.08553946591902095</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H30">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="B31" t="s">
         <v>10</v>
       </c>
       <c r="C31">
-        <v>34.88080083527914</v>
+        <v>35.10429483281073</v>
       </c>
       <c r="D31">
-        <v>26.19322945679072</v>
+        <v>26.43864879939599</v>
       </c>
       <c r="E31">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="F31">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="G31">
-        <v>0.06870693142475881</v>
+        <v>0.07926550001722021</v>
       </c>
       <c r="H31">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1">
-        <v>46160</v>
+        <v>46156</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
       </c>
       <c r="C32">
-        <v>34.67638692539213</v>
+        <v>35.36860632820093</v>
       </c>
       <c r="D32">
-        <v>26.06707890342319</v>
+        <v>26.56575571102338</v>
       </c>
       <c r="E32">
         <v>0.9985999999999999</v>
@@ -1229,7 +1229,7 @@
         <v>0.9985999999999999</v>
       </c>
       <c r="G32">
-        <v>0.06289213016552919</v>
+        <v>0.08553946591902095</v>
       </c>
       <c r="H32">
         <v>0.9985999999999999</v>
@@ -1237,120 +1237,120 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="B33" t="s">
         <v>10</v>
       </c>
       <c r="C33">
-        <v>34.21212662725402</v>
+        <v>34.88080083527914</v>
       </c>
       <c r="D33">
-        <v>25.60349394367002</v>
+        <v>26.19322945679072</v>
       </c>
       <c r="E33">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="F33">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="G33">
-        <v>0.0486610616591685</v>
+        <v>0.06870693142475881</v>
       </c>
       <c r="H33">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="B34" t="s">
         <v>10</v>
       </c>
       <c r="C34">
-        <v>34.78598436564941</v>
+        <v>34.67638692539213</v>
       </c>
       <c r="D34">
-        <v>25.95505316769806</v>
+        <v>26.06707890342319</v>
       </c>
       <c r="E34">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="F34">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="G34">
-        <v>0.06335117806143331</v>
+        <v>0.06289213016552919</v>
       </c>
       <c r="H34">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1">
-        <v>46163</v>
+        <v>46161</v>
       </c>
       <c r="B35" t="s">
         <v>10</v>
       </c>
       <c r="C35">
-        <v>33.4539909056227</v>
+        <v>34.21212662725402</v>
       </c>
       <c r="D35">
-        <v>25.96014535427112</v>
+        <v>25.60349394367002</v>
       </c>
       <c r="E35">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="F35">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="G35">
-        <v>0.06350423294229035</v>
+        <v>0.0486610616591685</v>
       </c>
       <c r="H35">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1">
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="B36" t="s">
         <v>10</v>
       </c>
       <c r="C36">
-        <v>33.24951933563993</v>
+        <v>34.78598436564941</v>
       </c>
       <c r="D36">
-        <v>25.46629530314992</v>
+        <v>25.95505316769806</v>
       </c>
       <c r="E36">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="F36">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="G36">
-        <v>0.06136193159696024</v>
+        <v>0.06335117806143331</v>
       </c>
       <c r="H36">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1">
-        <v>46167</v>
+        <v>46163</v>
       </c>
       <c r="B37" t="s">
         <v>10</v>
       </c>
       <c r="C37">
-        <v>33.29896419867477</v>
+        <v>33.4539909056227</v>
       </c>
       <c r="D37">
-        <v>25.45090185337973</v>
+        <v>25.96014535427112</v>
       </c>
       <c r="E37">
         <v>0.9984</v>
@@ -1359,7 +1359,7 @@
         <v>0.9984</v>
       </c>
       <c r="G37">
-        <v>0.06136193159696024</v>
+        <v>0.06350423294229035</v>
       </c>
       <c r="H37">
         <v>0.9984</v>
@@ -1367,16 +1367,16 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1">
-        <v>46168</v>
+        <v>46164</v>
       </c>
       <c r="B38" t="s">
         <v>10</v>
       </c>
       <c r="C38">
-        <v>33.41270923608511</v>
+        <v>33.24951933563993</v>
       </c>
       <c r="D38">
-        <v>25.54156152389702</v>
+        <v>25.46629530314992</v>
       </c>
       <c r="E38">
         <v>0.9984</v>
@@ -1385,7 +1385,7 @@
         <v>0.9984</v>
       </c>
       <c r="G38">
-        <v>0.06549347940676342</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H38">
         <v>0.9984</v>
@@ -1393,666 +1393,666 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1">
-        <v>46169</v>
+        <v>46167</v>
       </c>
       <c r="B39" t="s">
         <v>10</v>
       </c>
       <c r="C39">
-        <v>33.73350746548562</v>
+        <v>33.29896419867477</v>
       </c>
       <c r="D39">
-        <v>25.75393367034243</v>
+        <v>25.45090185337973</v>
       </c>
       <c r="E39">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="F39">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="G39">
-        <v>0.07620510288008187</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H39">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1">
-        <v>46170</v>
+        <v>46168</v>
       </c>
       <c r="B40" t="s">
         <v>10</v>
       </c>
       <c r="C40">
-        <v>33.84336414535104</v>
+        <v>33.41270923608511</v>
       </c>
       <c r="D40">
-        <v>25.97168203877208</v>
+        <v>25.54156152389702</v>
       </c>
       <c r="E40">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
       <c r="F40">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
       <c r="G40">
-        <v>0.0844683152463559</v>
+        <v>0.06549347940676342</v>
       </c>
       <c r="H40">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1">
-        <v>46171</v>
+        <v>46169</v>
       </c>
       <c r="B41" t="s">
         <v>10</v>
       </c>
       <c r="C41">
-        <v>33.73370320039719</v>
+        <v>33.73350746548562</v>
       </c>
       <c r="D41">
-        <v>25.880209881309</v>
+        <v>25.75393367034243</v>
       </c>
       <c r="E41">
-        <v>0.9988</v>
+        <v>0.9987000000000001</v>
       </c>
       <c r="F41">
-        <v>0.9988</v>
+        <v>0.9987000000000001</v>
       </c>
       <c r="G41">
-        <v>0.08201990413931148</v>
+        <v>0.07620510288008187</v>
       </c>
       <c r="H41">
-        <v>0.9988</v>
+        <v>0.9987000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1">
-        <v>46174</v>
+        <v>46170</v>
       </c>
       <c r="B42" t="s">
         <v>10</v>
       </c>
       <c r="C42">
-        <v>33.45546240777382</v>
+        <v>33.84336414535104</v>
       </c>
       <c r="D42">
-        <v>25.61350381215703</v>
+        <v>25.97168203877208</v>
       </c>
       <c r="E42">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
       <c r="F42">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
       <c r="G42">
-        <v>0.06901304118647311</v>
+        <v>0.0844683152463559</v>
       </c>
       <c r="H42">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1">
-        <v>46153</v>
+        <v>46171</v>
       </c>
       <c r="B43" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C43">
-        <v>36.55790859258162</v>
+        <v>33.73370320039719</v>
       </c>
       <c r="D43">
-        <v>22.67181120908155</v>
+        <v>25.880209881309</v>
       </c>
       <c r="E43">
-        <v>0.9990740999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="F43">
-        <v>0.9990740999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="G43">
-        <v>0.1648443271746771</v>
+        <v>0.08201990413931148</v>
       </c>
       <c r="H43">
-        <v>0.9990740999999999</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1">
-        <v>46154</v>
+        <v>46174</v>
       </c>
       <c r="B44" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C44">
-        <v>36.44753722959613</v>
+        <v>33.45546240777382</v>
       </c>
       <c r="D44">
-        <v>22.40292401789388</v>
+        <v>25.61350381215703</v>
       </c>
       <c r="E44">
-        <v>0.9990772499999999</v>
+        <v>0.999</v>
       </c>
       <c r="F44">
-        <v>0.9990772499999999</v>
+        <v>0.999</v>
       </c>
       <c r="G44">
-        <v>0.154964342628132</v>
+        <v>0.06901304118647311</v>
       </c>
       <c r="H44">
-        <v>0.9990772499999999</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1">
-        <v>46155</v>
+        <v>46175</v>
       </c>
       <c r="B45" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C45">
-        <v>36.63128514035871</v>
+        <v>33.31245255516097</v>
       </c>
       <c r="D45">
-        <v>22.65773388934668</v>
+        <v>25.36461330330757</v>
       </c>
       <c r="E45">
-        <v>0.99907745</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="F45">
-        <v>0.99907745</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="G45">
-        <v>0.1671633421405267</v>
+        <v>0.05845447259401171</v>
       </c>
       <c r="H45">
-        <v>0.99907745</v>
+        <v>0.9989999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="B46" t="s">
         <v>11</v>
       </c>
       <c r="C46">
-        <v>36.87865927427314</v>
+        <v>36.55790859258162</v>
       </c>
       <c r="D46">
-        <v>22.69755646854794</v>
+        <v>22.67181120908155</v>
       </c>
       <c r="E46">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="F46">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="G46">
-        <v>0.1754592080224002</v>
+        <v>0.1648443271746771</v>
       </c>
       <c r="H46">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="B47" t="s">
         <v>11</v>
       </c>
       <c r="C47">
-        <v>36.52208783231286</v>
+        <v>36.44753722959613</v>
       </c>
       <c r="D47">
-        <v>22.32462309676992</v>
+        <v>22.40292401789388</v>
       </c>
       <c r="E47">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="F47">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="G47">
-        <v>0.1577242156354994</v>
+        <v>0.154964342628132</v>
       </c>
       <c r="H47">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="B48" t="s">
         <v>11</v>
       </c>
       <c r="C48">
-        <v>36.25604200674668</v>
+        <v>36.63128514035871</v>
       </c>
       <c r="D48">
-        <v>22.16555007468561</v>
+        <v>22.65773388934668</v>
       </c>
       <c r="E48">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="F48">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="G48">
-        <v>0.1527434068648266</v>
+        <v>0.1671633421405267</v>
       </c>
       <c r="H48">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1">
-        <v>46161</v>
+        <v>46156</v>
       </c>
       <c r="B49" t="s">
         <v>11</v>
       </c>
       <c r="C49">
-        <v>36.01040085730018</v>
+        <v>36.87865927427314</v>
       </c>
       <c r="D49">
-        <v>22.19475589056387</v>
+        <v>22.69755646854794</v>
       </c>
       <c r="E49">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="F49">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="G49">
-        <v>0.1456396418594061</v>
+        <v>0.1754592080224002</v>
       </c>
       <c r="H49">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1">
-        <v>46162</v>
+        <v>46157</v>
       </c>
       <c r="B50" t="s">
         <v>11</v>
       </c>
       <c r="C50">
-        <v>36.45290912796982</v>
+        <v>36.52208783231286</v>
       </c>
       <c r="D50">
-        <v>22.46357594746874</v>
+        <v>22.32462309676992</v>
       </c>
       <c r="E50">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="F50">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="G50">
-        <v>0.1646157747240327</v>
+        <v>0.1577242156354994</v>
       </c>
       <c r="H50">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1">
-        <v>46163</v>
+        <v>46160</v>
       </c>
       <c r="B51" t="s">
         <v>11</v>
       </c>
       <c r="C51">
-        <v>35.75282090566891</v>
+        <v>36.25604200674668</v>
       </c>
       <c r="D51">
-        <v>22.57615417310648</v>
+        <v>22.16555007468561</v>
       </c>
       <c r="E51">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="F51">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="G51">
-        <v>0.1668367104873381</v>
+        <v>0.1527434068648266</v>
       </c>
       <c r="H51">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1">
-        <v>46164</v>
+        <v>46161</v>
       </c>
       <c r="B52" t="s">
         <v>11</v>
       </c>
       <c r="C52">
-        <v>35.75514940724808</v>
+        <v>36.01040085730018</v>
       </c>
       <c r="D52">
-        <v>22.28880693466429</v>
+        <v>22.19475589056387</v>
       </c>
       <c r="E52">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="F52">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="G52">
-        <v>0.1717848261904962</v>
+        <v>0.1456396418594061</v>
       </c>
       <c r="H52">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1">
-        <v>46167</v>
+        <v>46162</v>
       </c>
       <c r="B53" t="s">
         <v>11</v>
       </c>
       <c r="C53">
-        <v>35.84133099010302</v>
+        <v>36.45290912796982</v>
       </c>
       <c r="D53">
-        <v>22.37458514769363</v>
+        <v>22.46357594746874</v>
       </c>
       <c r="E53">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="F53">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="G53">
-        <v>0.1717848261904962</v>
+        <v>0.1646157747240327</v>
       </c>
       <c r="H53">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1">
-        <v>46168</v>
+        <v>46163</v>
       </c>
       <c r="B54" t="s">
         <v>11</v>
       </c>
       <c r="C54">
-        <v>36.23214279739292</v>
+        <v>35.75282090566891</v>
       </c>
       <c r="D54">
-        <v>22.93484792820123</v>
+        <v>22.57615417310648</v>
       </c>
       <c r="E54">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
       <c r="F54">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
       <c r="G54">
-        <v>0.1925900763781823</v>
+        <v>0.1668367104873381</v>
       </c>
       <c r="H54">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="B55" t="s">
         <v>11</v>
       </c>
       <c r="C55">
-        <v>36.4336692499184</v>
+        <v>35.75514940724808</v>
       </c>
       <c r="D55">
-        <v>22.75940954009856</v>
+        <v>22.28880693466429</v>
       </c>
       <c r="E55">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="F55">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="G55">
-        <v>0.1912346098381414</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H55">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="B56" t="s">
         <v>11</v>
       </c>
       <c r="C56">
-        <v>36.57358557066742</v>
+        <v>35.84133099010302</v>
       </c>
       <c r="D56">
-        <v>22.83069636955243</v>
+        <v>22.37458514769363</v>
       </c>
       <c r="E56">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="F56">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="G56">
-        <v>0.2012778603742877</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H56">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1">
-        <v>46171</v>
+        <v>46168</v>
       </c>
       <c r="B57" t="s">
         <v>11</v>
       </c>
       <c r="C57">
-        <v>36.67481300942</v>
+        <v>36.23214279739292</v>
       </c>
       <c r="D57">
-        <v>22.95852861681004</v>
+        <v>22.93484792820123</v>
       </c>
       <c r="E57">
-        <v>0.9964953299999998</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="F57">
-        <v>0.9964953299999998</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="G57">
-        <v>0.2057034850411275</v>
+        <v>0.1925900763781823</v>
       </c>
       <c r="H57">
-        <v>0.9994474899999999</v>
+        <v>0.9992609200000001</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1">
-        <v>46174</v>
+        <v>46169</v>
       </c>
       <c r="B58" t="s">
         <v>11</v>
       </c>
       <c r="C58">
-        <v>36.84565507982974</v>
+        <v>36.4336692499184</v>
       </c>
       <c r="D58">
-        <v>23.15960292175205</v>
+        <v>22.75940954009856</v>
       </c>
       <c r="E58">
-        <v>0.99646052</v>
+        <v>0.9992099400000001</v>
       </c>
       <c r="F58">
-        <v>0.99646052</v>
+        <v>0.9992099400000001</v>
       </c>
       <c r="G58">
-        <v>0.2129379226426205</v>
+        <v>0.1912346098381414</v>
       </c>
       <c r="H58">
-        <v>0.9993986199999999</v>
+        <v>0.9992099400000001</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1">
-        <v>46153</v>
+        <v>46170</v>
       </c>
       <c r="B59" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C59">
-        <v>52.70832779833182</v>
+        <v>36.57358557066742</v>
       </c>
       <c r="D59">
-        <v>23.99044674439659</v>
+        <v>22.83069636955243</v>
       </c>
       <c r="E59">
-        <v>0.9994000000000002</v>
+        <v>0.9994435600000001</v>
       </c>
       <c r="F59">
-        <v>0.9994000000000002</v>
+        <v>0.9994435600000001</v>
       </c>
       <c r="G59">
-        <v>0.5438253854918791</v>
+        <v>0.2012778603742877</v>
       </c>
       <c r="H59">
-        <v>0.9994000000000002</v>
+        <v>0.9994435600000001</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1">
-        <v>46154</v>
+        <v>46171</v>
       </c>
       <c r="B60" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C60">
-        <v>50.89464485280568</v>
+        <v>36.67481300942</v>
       </c>
       <c r="D60">
-        <v>23.21558303176282</v>
+        <v>22.95852861681004</v>
       </c>
       <c r="E60">
-        <v>0.9996</v>
+        <v>0.9964953299999998</v>
       </c>
       <c r="F60">
-        <v>0.9996</v>
+        <v>0.9964953299999998</v>
       </c>
       <c r="G60">
-        <v>0.5034825029548833</v>
+        <v>0.2057034850411275</v>
       </c>
       <c r="H60">
-        <v>0.9996</v>
+        <v>0.9994474899999999</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1">
-        <v>46155</v>
+        <v>46174</v>
       </c>
       <c r="B61" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C61">
-        <v>51.8659994471731</v>
+        <v>36.84565507982974</v>
       </c>
       <c r="D61">
-        <v>23.7009037279043</v>
+        <v>23.15960292175205</v>
       </c>
       <c r="E61">
-        <v>1.0002</v>
+        <v>0.99646052</v>
       </c>
       <c r="F61">
-        <v>1.0002</v>
+        <v>0.99646052</v>
       </c>
       <c r="G61">
-        <v>0.533512029714132</v>
+        <v>0.2129379226426205</v>
       </c>
       <c r="H61">
-        <v>1.0002</v>
+        <v>0.9993986199999999</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1">
-        <v>46156</v>
+        <v>46175</v>
       </c>
       <c r="B62" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C62">
-        <v>52.4470179952828</v>
+        <v>36.88482057171844</v>
       </c>
       <c r="D62">
-        <v>23.76861704536814</v>
+        <v>23.03898938038424</v>
       </c>
       <c r="E62">
-        <v>0.9998</v>
+        <v>0.99645675</v>
       </c>
       <c r="F62">
-        <v>0.9998</v>
+        <v>0.99645675</v>
       </c>
       <c r="G62">
-        <v>0.5492634496849078</v>
+        <v>0.2185229551183987</v>
       </c>
       <c r="H62">
-        <v>0.9998</v>
+        <v>0.9994034199999998</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="B63" t="s">
         <v>12</v>
       </c>
       <c r="C63">
-        <v>50.81077380018606</v>
+        <v>52.70832779833182</v>
       </c>
       <c r="D63">
-        <v>22.76900580927995</v>
+        <v>23.99044674439659</v>
       </c>
       <c r="E63">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="F63">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="G63">
-        <v>0.4903296143797722</v>
+        <v>0.5438253854918791</v>
       </c>
       <c r="H63">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1">
-        <v>46160</v>
+        <v>46154</v>
       </c>
       <c r="B64" t="s">
         <v>12</v>
       </c>
       <c r="C64">
-        <v>49.50286387149169</v>
+        <v>50.89464485280568</v>
       </c>
       <c r="D64">
-        <v>22.24532119914133</v>
+        <v>23.21558303176282</v>
       </c>
       <c r="E64">
         <v>0.9996</v>
@@ -2061,7 +2061,7 @@
         <v>0.9996</v>
       </c>
       <c r="G64">
-        <v>0.4630591776162345</v>
+        <v>0.5034825029548833</v>
       </c>
       <c r="H64">
         <v>0.9996</v>
@@ -2069,224 +2069,224 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1">
-        <v>46161</v>
+        <v>46155</v>
       </c>
       <c r="B65" t="s">
         <v>12</v>
       </c>
       <c r="C65">
-        <v>49.29146729279496</v>
+        <v>51.8659994471731</v>
       </c>
       <c r="D65">
-        <v>22.22167836589682</v>
+        <v>23.7009037279043</v>
       </c>
       <c r="E65">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="F65">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="G65">
-        <v>0.4571659248870246</v>
+        <v>0.533512029714132</v>
       </c>
       <c r="H65">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1">
-        <v>46162</v>
+        <v>46156</v>
       </c>
       <c r="B66" t="s">
         <v>12</v>
       </c>
       <c r="C66">
-        <v>50.88652370817657</v>
+        <v>52.4470179952828</v>
       </c>
       <c r="D66">
-        <v>22.93254398967657</v>
+        <v>23.76861704536814</v>
       </c>
       <c r="E66">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F66">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G66">
-        <v>0.5126171754864624</v>
+        <v>0.5492634496849078</v>
       </c>
       <c r="H66">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1">
-        <v>46163</v>
+        <v>46157</v>
       </c>
       <c r="B67" t="s">
         <v>12</v>
       </c>
       <c r="C67">
-        <v>48.26646764818586</v>
+        <v>50.81077380018606</v>
       </c>
       <c r="D67">
-        <v>23.11655387625012</v>
+        <v>22.76900580927995</v>
       </c>
       <c r="E67">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="F67">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="G67">
-        <v>0.521243030947425</v>
+        <v>0.4903296143797722</v>
       </c>
       <c r="H67">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1">
-        <v>46164</v>
+        <v>46160</v>
       </c>
       <c r="B68" t="s">
         <v>12</v>
       </c>
       <c r="C68">
-        <v>48.84737503703267</v>
+        <v>49.50286387149169</v>
       </c>
       <c r="D68">
-        <v>22.83557604744466</v>
+        <v>22.24532119914133</v>
       </c>
       <c r="E68">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="F68">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="G68">
-        <v>0.5438521997590966</v>
+        <v>0.4630591776162345</v>
       </c>
       <c r="H68">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1">
-        <v>46167</v>
+        <v>46161</v>
       </c>
       <c r="B69" t="s">
         <v>12</v>
       </c>
       <c r="C69">
-        <v>48.85151560750146</v>
+        <v>49.29146729279496</v>
       </c>
       <c r="D69">
-        <v>22.83513820206554</v>
+        <v>22.22167836589682</v>
       </c>
       <c r="E69">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F69">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G69">
-        <v>0.5438521997590966</v>
+        <v>0.4571659248870246</v>
       </c>
       <c r="H69">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1">
-        <v>46168</v>
+        <v>46162</v>
       </c>
       <c r="B70" t="s">
         <v>12</v>
       </c>
       <c r="C70">
-        <v>50.90437883274981</v>
+        <v>50.88652370817657</v>
       </c>
       <c r="D70">
-        <v>24.25672473501501</v>
+        <v>22.93254398967657</v>
       </c>
       <c r="E70">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F70">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G70">
-        <v>0.6130191115419561</v>
+        <v>0.5126171754864624</v>
       </c>
       <c r="H70">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1">
-        <v>46169</v>
+        <v>46163</v>
       </c>
       <c r="B71" t="s">
         <v>12</v>
       </c>
       <c r="C71">
-        <v>50.47312432255841</v>
+        <v>48.26646764818586</v>
       </c>
       <c r="D71">
-        <v>23.84499305142194</v>
+        <v>23.11655387625012</v>
       </c>
       <c r="E71">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="F71">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="G71">
-        <v>0.5952317692821967</v>
+        <v>0.521243030947425</v>
       </c>
       <c r="H71">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1">
-        <v>46170</v>
+        <v>46164</v>
       </c>
       <c r="B72" t="s">
         <v>12</v>
       </c>
       <c r="C72">
-        <v>50.84596269629946</v>
+        <v>48.84737503703267</v>
       </c>
       <c r="D72">
-        <v>23.7680603326165</v>
+        <v>22.83557604744466</v>
       </c>
       <c r="E72">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F72">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G72">
-        <v>0.606831065374982</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H72">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1">
-        <v>46171</v>
+        <v>46167</v>
       </c>
       <c r="B73" t="s">
         <v>12</v>
       </c>
       <c r="C73">
-        <v>51.08372269965196</v>
+        <v>48.85151560750146</v>
       </c>
       <c r="D73">
-        <v>23.88880359436525</v>
+        <v>22.83513820206554</v>
       </c>
       <c r="E73">
         <v>0.9998999999999999</v>
@@ -2295,7 +2295,7 @@
         <v>0.9998999999999999</v>
       </c>
       <c r="G73">
-        <v>0.604420070348211</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H73">
         <v>0.9998999999999999</v>
@@ -2303,1108 +2303,1108 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1">
-        <v>46174</v>
+        <v>46168</v>
       </c>
       <c r="B74" t="s">
         <v>12</v>
       </c>
       <c r="C74">
-        <v>51.84875713649351</v>
+        <v>50.90437883274981</v>
       </c>
       <c r="D74">
-        <v>24.29466650399529</v>
+        <v>24.25672473501501</v>
       </c>
       <c r="E74">
-        <v>0.9998</v>
+        <v>0.9996999999999999</v>
       </c>
       <c r="F74">
-        <v>0.9998</v>
+        <v>0.9996999999999999</v>
       </c>
       <c r="G74">
-        <v>0.6282079224060508</v>
+        <v>0.6130191115419561</v>
       </c>
       <c r="H74">
-        <v>0.9998</v>
+        <v>0.9996999999999999</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1">
-        <v>46153</v>
+        <v>46169</v>
       </c>
       <c r="B75" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C75">
-        <v>57.1732166855686</v>
+        <v>50.47312432255841</v>
       </c>
       <c r="D75">
-        <v>23.50022751267814</v>
+        <v>23.84499305142194</v>
       </c>
       <c r="E75">
-        <v>0.9991</v>
+        <v>0.9998</v>
       </c>
       <c r="F75">
-        <v>0.9991</v>
+        <v>0.9998</v>
       </c>
       <c r="G75">
-        <v>0.6994110097039083</v>
+        <v>0.5952317692821967</v>
       </c>
       <c r="H75">
-        <v>0.9991</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1">
-        <v>46154</v>
+        <v>46170</v>
       </c>
       <c r="B76" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C76">
-        <v>54.77380642078597</v>
+        <v>50.84596269629946</v>
       </c>
       <c r="D76">
-        <v>22.55192940254518</v>
+        <v>23.7680603326165</v>
       </c>
       <c r="E76">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
       <c r="F76">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
       <c r="G76">
-        <v>0.6459175880844941</v>
+        <v>0.606831065374982</v>
       </c>
       <c r="H76">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1">
-        <v>46155</v>
+        <v>46171</v>
       </c>
       <c r="B77" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C77">
-        <v>56.32187380830906</v>
+        <v>51.08372269965196</v>
       </c>
       <c r="D77">
-        <v>23.17121437414109</v>
+        <v>23.88880359436525</v>
       </c>
       <c r="E77">
-        <v>0.9990000000000001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F77">
-        <v>0.9990000000000001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G77">
-        <v>0.6851523922954754</v>
+        <v>0.604420070348211</v>
       </c>
       <c r="H77">
-        <v>0.9990000000000001</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="1">
-        <v>46156</v>
+        <v>46174</v>
       </c>
       <c r="B78" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C78">
-        <v>56.15321618553139</v>
+        <v>51.84875713649351</v>
       </c>
       <c r="D78">
-        <v>22.95838347314443</v>
+        <v>24.29466650399529</v>
       </c>
       <c r="E78">
-        <v>0.9992</v>
+        <v>0.9998</v>
       </c>
       <c r="F78">
-        <v>0.9992</v>
+        <v>0.9998</v>
       </c>
       <c r="G78">
-        <v>0.6907028507208208</v>
+        <v>0.6282079224060508</v>
       </c>
       <c r="H78">
-        <v>0.9992</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1">
-        <v>46157</v>
+        <v>46175</v>
       </c>
       <c r="B79" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C79">
-        <v>54.47755813049488</v>
+        <v>53.42858844634741</v>
       </c>
       <c r="D79">
-        <v>22.0083816089626</v>
+        <v>24.82449061140869</v>
       </c>
       <c r="E79">
-        <v>0.9986</v>
+        <v>1</v>
       </c>
       <c r="F79">
-        <v>0.9986</v>
+        <v>1</v>
       </c>
       <c r="G79">
-        <v>0.6220895940829376</v>
+        <v>0.6935709687814895</v>
       </c>
       <c r="H79">
-        <v>0.9986</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
       </c>
       <c r="C80">
-        <v>52.6278781150669</v>
+        <v>57.1732166855686</v>
       </c>
       <c r="D80">
-        <v>21.5357353870778</v>
+        <v>23.50022751267814</v>
       </c>
       <c r="E80">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F80">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G80">
-        <v>0.5845134636435627</v>
+        <v>0.6994110097039083</v>
       </c>
       <c r="H80">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B81" t="s">
         <v>13</v>
       </c>
       <c r="C81">
-        <v>54.91583234840245</v>
+        <v>54.77380642078597</v>
       </c>
       <c r="D81">
-        <v>22.38321645985006</v>
+        <v>22.55192940254518</v>
       </c>
       <c r="E81">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F81">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G81">
-        <v>0.6596976539194066</v>
+        <v>0.6459175880844941</v>
       </c>
       <c r="H81">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
       </c>
       <c r="C82">
-        <v>53.91712298548793</v>
+        <v>56.32187380830906</v>
       </c>
       <c r="D82">
-        <v>22.73711181201267</v>
+        <v>23.17121437414109</v>
       </c>
       <c r="E82">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F82">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G82">
-        <v>0.6737329602396263</v>
+        <v>0.6851523922954754</v>
       </c>
       <c r="H82">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="1">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="B83" t="s">
         <v>13</v>
       </c>
       <c r="C83">
-        <v>55.19651747515625</v>
+        <v>56.15321618553139</v>
       </c>
       <c r="D83">
-        <v>22.79462037330554</v>
+        <v>22.95838347314443</v>
       </c>
       <c r="E83">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
       <c r="F83">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
       <c r="G83">
-        <v>0.7139885317003913</v>
+        <v>0.6907028507208208</v>
       </c>
       <c r="H83">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="1">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
       </c>
       <c r="C84">
-        <v>55.28054997487197</v>
+        <v>54.47755813049488</v>
       </c>
       <c r="D84">
-        <v>23.00160891539877</v>
+        <v>22.0083816089626</v>
       </c>
       <c r="E84">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="F84">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="G84">
-        <v>0.7139885317003913</v>
+        <v>0.6220895940829376</v>
       </c>
       <c r="H84">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1">
-        <v>46168</v>
+        <v>46161</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
       </c>
       <c r="C85">
-        <v>58.75156728873073</v>
+        <v>52.6278781150669</v>
       </c>
       <c r="D85">
-        <v>24.84249654093248</v>
+        <v>21.5357353870778</v>
       </c>
       <c r="E85">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="F85">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="G85">
-        <v>0.8184872182632257</v>
+        <v>0.5845134636435627</v>
       </c>
       <c r="H85">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="1">
-        <v>46169</v>
+        <v>46162</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
       </c>
       <c r="C86">
-        <v>57.86771234337395</v>
+        <v>54.91583234840245</v>
       </c>
       <c r="D86">
-        <v>24.21066615243091</v>
+        <v>22.38321645985006</v>
       </c>
       <c r="E86">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="F86">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="G86">
-        <v>0.798997241708943</v>
+        <v>0.6596976539194066</v>
       </c>
       <c r="H86">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="1">
-        <v>46170</v>
+        <v>46163</v>
       </c>
       <c r="B87" t="s">
         <v>13</v>
       </c>
       <c r="C87">
-        <v>58.18666682631797</v>
+        <v>53.91712298548793</v>
       </c>
       <c r="D87">
-        <v>24.09552344282839</v>
+        <v>22.73711181201267</v>
       </c>
       <c r="E87">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="F87">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="G87">
-        <v>0.8165093478664007</v>
+        <v>0.6737329602396263</v>
       </c>
       <c r="H87">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1">
-        <v>46171</v>
+        <v>46164</v>
       </c>
       <c r="B88" t="s">
         <v>13</v>
       </c>
       <c r="C88">
-        <v>58.79256019733606</v>
+        <v>55.19651747515625</v>
       </c>
       <c r="D88">
-        <v>24.33854853448823</v>
+        <v>22.79462037330554</v>
       </c>
       <c r="E88">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F88">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G88">
-        <v>0.8152654642198496</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H88">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="1">
-        <v>46174</v>
+        <v>46167</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
       </c>
       <c r="C89">
-        <v>58.97156722185718</v>
+        <v>55.28054997487197</v>
       </c>
       <c r="D89">
-        <v>24.48296361348067</v>
+        <v>23.00160891539877</v>
       </c>
       <c r="E89">
-        <v>0.9990000000000001</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="F89">
-        <v>0.9990000000000001</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="G89">
-        <v>0.8243563865851753</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H89">
-        <v>0.9990000000000001</v>
+        <v>0.9989000000000001</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="1">
-        <v>46153</v>
+        <v>46168</v>
       </c>
       <c r="B90" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C90">
-        <v>35.78646526282436</v>
+        <v>58.75156728873073</v>
       </c>
       <c r="D90">
-        <v>18.96635091925032</v>
+        <v>24.84249654093248</v>
       </c>
       <c r="E90">
-        <v>0.9996491399999999</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="F90">
-        <v>0.9996491399999999</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="G90">
-        <v>0.2240600969213613</v>
+        <v>0.8184872182632257</v>
       </c>
       <c r="H90">
-        <v>0.9985614899999999</v>
+        <v>0.9989000000000001</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="1">
-        <v>46154</v>
+        <v>46169</v>
       </c>
       <c r="B91" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C91">
-        <v>35.71584102184062</v>
+        <v>57.86771234337395</v>
       </c>
       <c r="D91">
-        <v>18.62432950231353</v>
+        <v>24.21066615243091</v>
       </c>
       <c r="E91">
-        <v>0.99965481</v>
+        <v>0.9986999999999999</v>
       </c>
       <c r="F91">
-        <v>0.99965481</v>
+        <v>0.9986999999999999</v>
       </c>
       <c r="G91">
-        <v>0.2104844827747143</v>
+        <v>0.798997241708943</v>
       </c>
       <c r="H91">
-        <v>0.9985622199999999</v>
+        <v>0.9986999999999999</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="1">
-        <v>46155</v>
+        <v>46170</v>
       </c>
       <c r="B92" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C92">
-        <v>35.95182028203252</v>
+        <v>58.18666682631797</v>
       </c>
       <c r="D92">
-        <v>18.95670796791552</v>
+        <v>24.09552344282839</v>
       </c>
       <c r="E92">
-        <v>0.9996515200000001</v>
+        <v>0.9991</v>
       </c>
       <c r="F92">
-        <v>0.9996515200000001</v>
+        <v>0.9991</v>
       </c>
       <c r="G92">
-        <v>0.2259035693959275</v>
+        <v>0.8165093478664007</v>
       </c>
       <c r="H92">
-        <v>0.99855193</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="1">
-        <v>46156</v>
+        <v>46171</v>
       </c>
       <c r="B93" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C93">
-        <v>36.14451597805883</v>
+        <v>58.79256019733606</v>
       </c>
       <c r="D93">
-        <v>18.86297660538653</v>
+        <v>24.33854853448823</v>
       </c>
       <c r="E93">
-        <v>0.9996563399999999</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="F93">
-        <v>0.9996563399999999</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="G93">
-        <v>0.2362110061840785</v>
+        <v>0.8152654642198496</v>
       </c>
       <c r="H93">
-        <v>0.99857265</v>
+        <v>0.9989999999999999</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="1">
-        <v>46157</v>
+        <v>46174</v>
       </c>
       <c r="B94" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C94">
-        <v>35.32805803135546</v>
+        <v>58.97156722185718</v>
       </c>
       <c r="D94">
-        <v>18.35643242381478</v>
+        <v>24.48296361348067</v>
       </c>
       <c r="E94">
-        <v>0.9997415800000001</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F94">
-        <v>0.9997415800000001</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G94">
-        <v>0.2023559161375383</v>
+        <v>0.8243563865851753</v>
       </c>
       <c r="H94">
-        <v>0.9986639900000002</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="1">
-        <v>46160</v>
+        <v>46175</v>
       </c>
       <c r="B95" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C95">
-        <v>34.83995455757461</v>
+        <v>61.6542902214027</v>
       </c>
       <c r="D95">
-        <v>18.02301281718857</v>
+        <v>25.06517348653028</v>
       </c>
       <c r="E95">
-        <v>0.9996851299999999</v>
+        <v>0.9988</v>
       </c>
       <c r="F95">
-        <v>0.9996851299999999</v>
+        <v>0.9988</v>
       </c>
       <c r="G95">
-        <v>0.1850932291737926</v>
+        <v>0.9299077697948877</v>
       </c>
       <c r="H95">
-        <v>0.99857724</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B96" t="s">
         <v>14</v>
       </c>
       <c r="C96">
-        <v>34.45479308705605</v>
+        <v>35.78646526282436</v>
       </c>
       <c r="D96">
-        <v>18.09576834566068</v>
+        <v>18.96635091925032</v>
       </c>
       <c r="E96">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="F96">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="G96">
-        <v>0.1784731209386736</v>
+        <v>0.2240600969213613</v>
       </c>
       <c r="H96">
-        <v>0.9985337599999999</v>
+        <v>0.9985614899999999</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B97" t="s">
         <v>14</v>
       </c>
       <c r="C97">
-        <v>34.96336277390787</v>
+        <v>35.71584102184062</v>
       </c>
       <c r="D97">
-        <v>18.34938420029253</v>
+        <v>18.62432950231353</v>
       </c>
       <c r="E97">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="F97">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="G97">
-        <v>0.2009313391215752</v>
+        <v>0.2104844827747143</v>
       </c>
       <c r="H97">
-        <v>0.99848777</v>
+        <v>0.9985622199999999</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B98" t="s">
         <v>14</v>
       </c>
       <c r="C98">
-        <v>34.44616924817128</v>
+        <v>35.95182028203252</v>
       </c>
       <c r="D98">
-        <v>18.60085625074367</v>
+        <v>18.95670796791552</v>
       </c>
       <c r="E98">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="F98">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="G98">
-        <v>0.2124957180214682</v>
+        <v>0.2259035693959275</v>
       </c>
       <c r="H98">
-        <v>0.9985085200000001</v>
+        <v>0.99855193</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="1">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="B99" t="s">
         <v>14</v>
       </c>
       <c r="C99">
-        <v>34.62137220937314</v>
+        <v>36.14451597805883</v>
       </c>
       <c r="D99">
-        <v>18.28780484745949</v>
+        <v>18.86297660538653</v>
       </c>
       <c r="E99">
-        <v>0.9996106299999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="F99">
-        <v>0.9996106299999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="G99">
-        <v>0.2145907067863493</v>
+        <v>0.2362110061840785</v>
       </c>
       <c r="H99">
-        <v>0.9932939299999999</v>
+        <v>0.99857265</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="1">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="B100" t="s">
         <v>14</v>
       </c>
       <c r="C100">
-        <v>34.6540695486741</v>
+        <v>35.32805803135546</v>
       </c>
       <c r="D100">
-        <v>18.36409048915342</v>
+        <v>18.35643242381478</v>
       </c>
       <c r="E100">
-        <v>0.9995448900000001</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="F100">
-        <v>0.9995448900000001</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="G100">
-        <v>0.2145907067863493</v>
+        <v>0.2023559161375383</v>
       </c>
       <c r="H100">
-        <v>0.9984302600000001</v>
+        <v>0.9986639900000002</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="1">
-        <v>46168</v>
+        <v>46160</v>
       </c>
       <c r="B101" t="s">
         <v>14</v>
       </c>
       <c r="C101">
-        <v>35.4820130509417</v>
+        <v>34.83995455757461</v>
       </c>
       <c r="D101">
-        <v>19.20292041814603</v>
+        <v>18.02301281718857</v>
       </c>
       <c r="E101">
-        <v>0.9995448900000001</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="F101">
-        <v>0.9995448900000001</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="G101">
-        <v>0.2553172934903569</v>
+        <v>0.1850932291737926</v>
       </c>
       <c r="H101">
-        <v>0.9984302600000001</v>
+        <v>0.99857724</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="1">
-        <v>46169</v>
+        <v>46161</v>
       </c>
       <c r="B102" t="s">
         <v>14</v>
       </c>
       <c r="C102">
-        <v>35.71913468603401</v>
+        <v>34.45479308705605</v>
       </c>
       <c r="D102">
-        <v>18.96318693998171</v>
+        <v>18.09576834566068</v>
       </c>
       <c r="E102">
-        <v>0.99955466</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="F102">
-        <v>0.99955466</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="G102">
-        <v>0.2536413280520453</v>
+        <v>0.1784731209386736</v>
       </c>
       <c r="H102">
-        <v>0.9984700500000001</v>
+        <v>0.9985337599999999</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="1">
-        <v>46170</v>
+        <v>46162</v>
       </c>
       <c r="B103" t="s">
         <v>14</v>
       </c>
       <c r="C103">
-        <v>35.76226417354731</v>
+        <v>34.96336277390787</v>
       </c>
       <c r="D103">
-        <v>18.89050847207122</v>
+        <v>18.34938420029253</v>
       </c>
       <c r="E103">
-        <v>0.9995525399999999</v>
+        <v>0.99963413</v>
       </c>
       <c r="F103">
-        <v>0.9995525399999999</v>
+        <v>0.99963413</v>
       </c>
       <c r="G103">
-        <v>0.2580826940041561</v>
+        <v>0.2009313391215752</v>
       </c>
       <c r="H103">
-        <v>0.99847732</v>
+        <v>0.99848777</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="1">
-        <v>46171</v>
+        <v>46163</v>
       </c>
       <c r="B104" t="s">
         <v>14</v>
       </c>
       <c r="C104">
-        <v>35.84309020154227</v>
+        <v>34.44616924817128</v>
       </c>
       <c r="D104">
-        <v>19.06511612333149</v>
+        <v>18.60085625074367</v>
       </c>
       <c r="E104">
-        <v>0.9995533299999999</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="F104">
-        <v>0.9995533299999999</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="G104">
-        <v>0.2619374017254759</v>
+        <v>0.2124957180214682</v>
       </c>
       <c r="H104">
-        <v>0.99849382</v>
+        <v>0.9985085200000001</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="1">
-        <v>46174</v>
+        <v>46164</v>
       </c>
       <c r="B105" t="s">
         <v>14</v>
       </c>
       <c r="C105">
-        <v>36.27022125574057</v>
+        <v>34.62137220937314</v>
       </c>
       <c r="D105">
-        <v>19.32711369104533</v>
+        <v>18.28780484745949</v>
       </c>
       <c r="E105">
-        <v>0.9995550400000001</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="F105">
-        <v>0.9995550400000001</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="G105">
-        <v>0.2764348160433892</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H105">
-        <v>0.9985177199999999</v>
+        <v>0.9932939299999999</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="1">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="B106" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C106">
-        <v>28.12253390077671</v>
+        <v>34.6540695486741</v>
       </c>
       <c r="D106">
-        <v>23.58699683751922</v>
+        <v>18.36409048915342</v>
       </c>
       <c r="E106">
-        <v>0.9997295369999999</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="F106">
-        <v>0.9997295369999999</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="G106">
-        <v>0.03368732240295347</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H106">
-        <v>0.9997295369999999</v>
+        <v>0.9984302600000001</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="1">
-        <v>46154</v>
+        <v>46168</v>
       </c>
       <c r="B107" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C107">
-        <v>28.17715727830483</v>
+        <v>35.4820130509417</v>
       </c>
       <c r="D107">
-        <v>23.63894513078866</v>
+        <v>19.20292041814603</v>
       </c>
       <c r="E107">
-        <v>1.000319473</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="F107">
-        <v>1.000319473</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="G107">
-        <v>0.03515547182056333</v>
+        <v>0.2553172934903569</v>
       </c>
       <c r="H107">
-        <v>1.000319473</v>
+        <v>0.9984302600000001</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="1">
-        <v>46155</v>
+        <v>46169</v>
       </c>
       <c r="B108" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C108">
-        <v>28.59002627414054</v>
+        <v>35.71913468603401</v>
       </c>
       <c r="D108">
-        <v>23.96230704059692</v>
+        <v>18.96318693998171</v>
       </c>
       <c r="E108">
-        <v>0.9999999989999999</v>
+        <v>0.99955466</v>
       </c>
       <c r="F108">
-        <v>0.9999999989999999</v>
+        <v>0.99955466</v>
       </c>
       <c r="G108">
-        <v>0.05179637495949674</v>
+        <v>0.2536413280520453</v>
       </c>
       <c r="H108">
-        <v>0.9999999989999999</v>
+        <v>0.9984700500000001</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="1">
-        <v>46156</v>
+        <v>46170</v>
       </c>
       <c r="B109" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C109">
-        <v>28.56217859389523</v>
+        <v>35.76226417354731</v>
       </c>
       <c r="D109">
-        <v>23.9411987302529</v>
+        <v>18.89050847207122</v>
       </c>
       <c r="E109">
-        <v>1</v>
+        <v>0.9995525399999999</v>
       </c>
       <c r="F109">
-        <v>1</v>
+        <v>0.9995525399999999</v>
       </c>
       <c r="G109">
-        <v>0.04837024516756849</v>
+        <v>0.2580826940041561</v>
       </c>
       <c r="H109">
-        <v>1</v>
+        <v>0.99847732</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="1">
-        <v>46157</v>
+        <v>46171</v>
       </c>
       <c r="B110" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C110">
-        <v>28.57618675936338</v>
+        <v>35.84309020154227</v>
       </c>
       <c r="D110">
-        <v>23.9576220541054</v>
+        <v>19.06511612333149</v>
       </c>
       <c r="E110">
-        <v>0.999503249</v>
+        <v>0.9995533299999999</v>
       </c>
       <c r="F110">
-        <v>0.999503249</v>
+        <v>0.9995533299999999</v>
       </c>
       <c r="G110">
-        <v>0.04983868243960732</v>
+        <v>0.2619374017254759</v>
       </c>
       <c r="H110">
-        <v>0.999503249</v>
+        <v>0.99849382</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="1">
-        <v>46160</v>
+        <v>46174</v>
       </c>
       <c r="B111" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C111">
-        <v>28.68951918518517</v>
+        <v>36.27022125574057</v>
       </c>
       <c r="D111">
-        <v>24.06134728453882</v>
+        <v>19.32711369104533</v>
       </c>
       <c r="E111">
-        <v>0.999503249</v>
+        <v>0.9995550400000001</v>
       </c>
       <c r="F111">
-        <v>0.999503249</v>
+        <v>0.9995550400000001</v>
       </c>
       <c r="G111">
-        <v>0.04983868243960732</v>
+        <v>0.2764348160433892</v>
       </c>
       <c r="H111">
-        <v>0.999503249</v>
+        <v>0.9985177199999999</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="1">
-        <v>46161</v>
+        <v>46175</v>
       </c>
       <c r="B112" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C112">
-        <v>28.31167386654059</v>
+        <v>36.57133692946976</v>
       </c>
       <c r="D112">
-        <v>23.75157719455474</v>
+        <v>19.33857330565742</v>
       </c>
       <c r="E112">
-        <v>1.000177331</v>
+        <v>0.9994989200000002</v>
       </c>
       <c r="F112">
-        <v>1.000177331</v>
+        <v>0.9994989200000002</v>
       </c>
       <c r="G112">
-        <v>0.04053938625111919</v>
+        <v>0.2931947261624381</v>
       </c>
       <c r="H112">
-        <v>1.000177331</v>
+        <v>0.9984577800000001</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="1">
-        <v>46162</v>
+        <v>46153</v>
       </c>
       <c r="B113" t="s">
         <v>15</v>
       </c>
       <c r="C113">
-        <v>28.57911382310097</v>
+        <v>28.12253390077671</v>
       </c>
       <c r="D113">
-        <v>23.89431741541233</v>
+        <v>23.58699683751922</v>
       </c>
       <c r="E113">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="F113">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="G113">
-        <v>0.04690190590044785</v>
+        <v>0.03368732240295347</v>
       </c>
       <c r="H113">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="1">
-        <v>46163</v>
+        <v>46154</v>
       </c>
       <c r="B114" t="s">
         <v>15</v>
       </c>
       <c r="C114">
-        <v>28.55785065378643</v>
+        <v>28.17715727830483</v>
       </c>
       <c r="D114">
-        <v>24.04274714970193</v>
+        <v>23.63894513078866</v>
       </c>
       <c r="E114">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="F114">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="G114">
-        <v>0.05228572319419666</v>
+        <v>0.03515547182056333</v>
       </c>
       <c r="H114">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="1">
-        <v>46164</v>
+        <v>46155</v>
       </c>
       <c r="B115" t="s">
         <v>15</v>
       </c>
       <c r="C115">
-        <v>28.50194638163107</v>
+        <v>28.59002627414054</v>
       </c>
       <c r="D115">
-        <v>23.99272397156045</v>
+        <v>23.96230704059692</v>
       </c>
       <c r="E115">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F115">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G115">
-        <v>0.04934923597154284</v>
+        <v>0.05179637495949674</v>
       </c>
       <c r="H115">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="1">
-        <v>46167</v>
+        <v>46156</v>
       </c>
       <c r="B116" t="s">
         <v>15</v>
       </c>
       <c r="C116">
-        <v>28.55106858744498</v>
+        <v>28.56217859389523</v>
       </c>
       <c r="D116">
-        <v>23.9768329565351</v>
+        <v>23.9411987302529</v>
       </c>
       <c r="E116">
         <v>1</v>
@@ -3413,7 +3413,7 @@
         <v>1</v>
       </c>
       <c r="G116">
-        <v>0.05571185335164408</v>
+        <v>0.04837024516756849</v>
       </c>
       <c r="H116">
         <v>1</v>
@@ -3421,548 +3421,782 @@
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="1">
-        <v>46168</v>
+        <v>46157</v>
       </c>
       <c r="B117" t="s">
         <v>15</v>
       </c>
       <c r="C117">
-        <v>28.54681541456266</v>
+        <v>28.57618675936338</v>
       </c>
       <c r="D117">
-        <v>23.97386168967948</v>
+        <v>23.9576220541054</v>
       </c>
       <c r="E117">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="F117">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="G117">
-        <v>0.04837034303541388</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H117">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="1">
-        <v>46169</v>
+        <v>46160</v>
       </c>
       <c r="B118" t="s">
         <v>15</v>
       </c>
       <c r="C118">
-        <v>28.83672936868491</v>
+        <v>28.68951918518517</v>
       </c>
       <c r="D118">
-        <v>24.203511281145</v>
+        <v>24.06134728453882</v>
       </c>
       <c r="E118">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="F118">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="G118">
-        <v>0.05962723282507953</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H118">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="1">
-        <v>46170</v>
+        <v>46161</v>
       </c>
       <c r="B119" t="s">
         <v>15</v>
       </c>
       <c r="C119">
-        <v>28.88109630394224</v>
+        <v>28.31167386654059</v>
       </c>
       <c r="D119">
-        <v>24.34085451035401</v>
+        <v>23.75157719455474</v>
       </c>
       <c r="E119">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
       <c r="F119">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
       <c r="G119">
-        <v>0.06647938938594877</v>
+        <v>0.04053938625111919</v>
       </c>
       <c r="H119">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="1">
-        <v>46171</v>
+        <v>46162</v>
       </c>
       <c r="B120" t="s">
         <v>15</v>
       </c>
       <c r="C120">
-        <v>28.92588622185229</v>
+        <v>28.57911382310097</v>
       </c>
       <c r="D120">
-        <v>24.37463012178961</v>
+        <v>23.89431741541233</v>
       </c>
       <c r="E120">
-        <v>0.9999999989999999</v>
+        <v>0.999503734</v>
       </c>
       <c r="F120">
-        <v>0.9999999989999999</v>
+        <v>0.999503734</v>
       </c>
       <c r="G120">
-        <v>0.0669687424559624</v>
+        <v>0.04690190590044785</v>
       </c>
       <c r="H120">
-        <v>0.9999999989999999</v>
+        <v>0.999503734</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="1">
-        <v>46174</v>
+        <v>46163</v>
       </c>
       <c r="B121" t="s">
         <v>15</v>
       </c>
       <c r="C121">
-        <v>28.479823472488</v>
+        <v>28.55785065378643</v>
       </c>
       <c r="D121">
-        <v>23.940843604634</v>
+        <v>24.04274714970193</v>
       </c>
       <c r="E121">
-        <v>0.9999999999999999</v>
+        <v>1.000229282</v>
       </c>
       <c r="F121">
-        <v>0.9999999999999999</v>
+        <v>1.000229282</v>
       </c>
       <c r="G121">
-        <v>0.05385076946675693</v>
+        <v>0.05228572319419666</v>
       </c>
       <c r="H121">
-        <v>0.9999999999999999</v>
+        <v>1.000229282</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="1">
-        <v>46153</v>
+        <v>46164</v>
       </c>
       <c r="B122" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C122">
-        <v>40.68830633303975</v>
+        <v>28.50194638163107</v>
       </c>
       <c r="D122">
-        <v>21.50431773660198</v>
+        <v>23.99272397156045</v>
       </c>
       <c r="E122">
-        <v>0.99909852</v>
+        <v>1</v>
       </c>
       <c r="F122">
-        <v>0.99909852</v>
+        <v>1</v>
       </c>
       <c r="G122">
-        <v>0.2342423866086769</v>
+        <v>0.04934923597154284</v>
       </c>
       <c r="H122">
-        <v>0.9974930900000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="1">
-        <v>46154</v>
+        <v>46167</v>
       </c>
       <c r="B123" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C123">
-        <v>40.32854894972581</v>
+        <v>28.55106858744498</v>
       </c>
       <c r="D123">
-        <v>21.09133998298594</v>
+        <v>23.9768329565351</v>
       </c>
       <c r="E123">
-        <v>0.9990972199999999</v>
+        <v>1</v>
       </c>
       <c r="F123">
-        <v>0.9990972199999999</v>
+        <v>1</v>
       </c>
       <c r="G123">
-        <v>0.2156468205051487</v>
+        <v>0.05571185335164408</v>
       </c>
       <c r="H123">
-        <v>0.99752223</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="1">
-        <v>46155</v>
+        <v>46168</v>
       </c>
       <c r="B124" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C124">
-        <v>40.47987921095815</v>
+        <v>28.54681541456266</v>
       </c>
       <c r="D124">
-        <v>21.35995364434454</v>
+        <v>23.97386168967948</v>
       </c>
       <c r="E124">
-        <v>0.9991780100000001</v>
+        <v>1</v>
       </c>
       <c r="F124">
-        <v>0.9991780100000001</v>
+        <v>1</v>
       </c>
       <c r="G124">
-        <v>0.2270956128473374</v>
+        <v>0.04837034303541388</v>
       </c>
       <c r="H124">
-        <v>0.9975825700000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="1">
-        <v>46156</v>
+        <v>46169</v>
       </c>
       <c r="B125" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C125">
-        <v>41.20436574895244</v>
+        <v>28.83672936868491</v>
       </c>
       <c r="D125">
-        <v>21.48149674387778</v>
+        <v>24.203511281145</v>
       </c>
       <c r="E125">
-        <v>0.9991793299999999</v>
+        <v>1</v>
       </c>
       <c r="F125">
-        <v>0.9991793299999999</v>
+        <v>1</v>
       </c>
       <c r="G125">
-        <v>0.2454829228401052</v>
+        <v>0.05962723282507953</v>
       </c>
       <c r="H125">
-        <v>0.99754722</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" s="1">
-        <v>46157</v>
+        <v>46170</v>
       </c>
       <c r="B126" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C126">
-        <v>40.80613062958688</v>
+        <v>28.88109630394224</v>
       </c>
       <c r="D126">
-        <v>21.08912555803936</v>
+        <v>24.34085451035401</v>
       </c>
       <c r="E126">
-        <v>0.9991790600000001</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F126">
-        <v>0.9991790600000001</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G126">
-        <v>0.2230017445022556</v>
+        <v>0.06647938938594877</v>
       </c>
       <c r="H126">
-        <v>0.9975824700000002</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" s="1">
-        <v>46160</v>
+        <v>46171</v>
       </c>
       <c r="B127" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C127">
-        <v>40.11672876026724</v>
+        <v>28.92588622185229</v>
       </c>
       <c r="D127">
-        <v>20.79541439916316</v>
+        <v>24.37463012178961</v>
       </c>
       <c r="E127">
-        <v>0.999152</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F127">
-        <v>0.999152</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G127">
-        <v>0.2098184021536666</v>
+        <v>0.0669687424559624</v>
       </c>
       <c r="H127">
-        <v>0.9975007899999999</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="1">
-        <v>46161</v>
+        <v>46174</v>
       </c>
       <c r="B128" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C128">
-        <v>39.69086941528401</v>
+        <v>28.479823472488</v>
       </c>
       <c r="D128">
-        <v>20.74924328599426</v>
+        <v>23.940843604634</v>
       </c>
       <c r="E128">
-        <v>0.99914989</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F128">
-        <v>0.99914989</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G128">
-        <v>0.2020471776850241</v>
+        <v>0.05385076946675693</v>
       </c>
       <c r="H128">
-        <v>0.9974417</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="1">
-        <v>46162</v>
+        <v>46175</v>
       </c>
       <c r="B129" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C129">
-        <v>40.37836787855562</v>
+        <v>28.11501250979268</v>
       </c>
       <c r="D129">
-        <v>21.11271132314188</v>
+        <v>23.53470929078268</v>
       </c>
       <c r="E129">
-        <v>0.99915058</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F129">
-        <v>0.99915058</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G129">
-        <v>0.2291077670847563</v>
+        <v>0.03476107722835287</v>
       </c>
       <c r="H129">
-        <v>0.9974415600000001</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" s="1">
-        <v>46163</v>
+        <v>46153</v>
       </c>
       <c r="B130" t="s">
         <v>16</v>
       </c>
       <c r="C130">
-        <v>38.9123066967842</v>
+        <v>40.68830633303975</v>
       </c>
       <c r="D130">
-        <v>21.28910644207464</v>
+        <v>21.50431773660198</v>
       </c>
       <c r="E130">
-        <v>0.9989350699999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="F130">
-        <v>0.9989350699999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="G130">
-        <v>0.2392382040170877</v>
+        <v>0.2342423866086769</v>
       </c>
       <c r="H130">
-        <v>0.99726191</v>
+        <v>0.9974930900000001</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" s="1">
-        <v>46164</v>
+        <v>46154</v>
       </c>
       <c r="B131" t="s">
         <v>16</v>
       </c>
       <c r="C131">
-        <v>39.43913909150694</v>
+        <v>40.32854894972581</v>
       </c>
       <c r="D131">
-        <v>21.05297617141148</v>
+        <v>21.09133998298594</v>
       </c>
       <c r="E131">
-        <v>0.999144</v>
+        <v>0.9990972199999999</v>
       </c>
       <c r="F131">
-        <v>0.999144</v>
+        <v>0.9990972199999999</v>
       </c>
       <c r="G131">
-        <v>0.2516582935428642</v>
+        <v>0.2156468205051487</v>
       </c>
       <c r="H131">
-        <v>0.9974678400000001</v>
+        <v>0.99752223</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="1">
-        <v>46167</v>
+        <v>46155</v>
       </c>
       <c r="B132" t="s">
         <v>16</v>
       </c>
       <c r="C132">
-        <v>39.45782844313628</v>
+        <v>40.47987921095815</v>
       </c>
       <c r="D132">
-        <v>21.0518901572272</v>
+        <v>21.35995364434454</v>
       </c>
       <c r="E132">
-        <v>0.999144</v>
+        <v>0.9991780100000001</v>
       </c>
       <c r="F132">
-        <v>0.999144</v>
+        <v>0.9991780100000001</v>
       </c>
       <c r="G132">
-        <v>0.2516582935428642</v>
+        <v>0.2270956128473374</v>
       </c>
       <c r="H132">
-        <v>0.9974678400000001</v>
+        <v>0.9975825700000001</v>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="1">
-        <v>46168</v>
+        <v>46156</v>
       </c>
       <c r="B133" t="s">
         <v>16</v>
       </c>
       <c r="C133">
-        <v>40.20219297984542</v>
+        <v>41.20436574895244</v>
       </c>
       <c r="D133">
-        <v>21.93106024403281</v>
+        <v>21.48149674387778</v>
       </c>
       <c r="E133">
-        <v>0.9991421799999999</v>
+        <v>0.9991793299999999</v>
       </c>
       <c r="F133">
-        <v>0.9991421799999999</v>
+        <v>0.9991793299999999</v>
       </c>
       <c r="G133">
-        <v>0.2846167552893293</v>
+        <v>0.2454829228401052</v>
       </c>
       <c r="H133">
-        <v>0.9974609800000001</v>
+        <v>0.99754722</v>
       </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="1">
-        <v>46169</v>
+        <v>46157</v>
       </c>
       <c r="B134" t="s">
         <v>16</v>
       </c>
       <c r="C134">
-        <v>40.34993865302093</v>
+        <v>40.80613062958688</v>
       </c>
       <c r="D134">
-        <v>21.65366031776487</v>
+        <v>21.08912555803936</v>
       </c>
       <c r="E134">
-        <v>0.9991434600000001</v>
+        <v>0.9991790600000001</v>
       </c>
       <c r="F134">
-        <v>0.9991434600000001</v>
+        <v>0.9991790600000001</v>
       </c>
       <c r="G134">
-        <v>0.2796902860011767</v>
+        <v>0.2230017445022556</v>
       </c>
       <c r="H134">
-        <v>0.9991434600000001</v>
+        <v>0.9975824700000002</v>
       </c>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="1">
-        <v>46170</v>
+        <v>46160</v>
       </c>
       <c r="B135" t="s">
         <v>16</v>
       </c>
       <c r="C135">
-        <v>40.5850485390846</v>
+        <v>40.11672876026724</v>
       </c>
       <c r="D135">
-        <v>21.75450977746074</v>
+        <v>20.79541439916316</v>
       </c>
       <c r="E135">
-        <v>0.99914592</v>
+        <v>0.999152</v>
       </c>
       <c r="F135">
-        <v>0.99914592</v>
+        <v>0.999152</v>
       </c>
       <c r="G135">
-        <v>0.2964818481030536</v>
+        <v>0.2098184021536666</v>
       </c>
       <c r="H135">
-        <v>0.99914592</v>
+        <v>0.9975007899999999</v>
       </c>
     </row>
     <row r="136" spans="1:8">
       <c r="A136" s="1">
-        <v>46171</v>
+        <v>46161</v>
       </c>
       <c r="B136" t="s">
         <v>16</v>
       </c>
       <c r="C136">
-        <v>41.86785805184477</v>
+        <v>39.69086941528401</v>
       </c>
       <c r="D136">
-        <v>22.33589392797469</v>
+        <v>20.74924328599426</v>
       </c>
       <c r="E136">
-        <v>0.9991336999999999</v>
+        <v>0.99914989</v>
       </c>
       <c r="F136">
-        <v>0.9991336999999999</v>
+        <v>0.99914989</v>
       </c>
       <c r="G136">
-        <v>0.3254158954996882</v>
+        <v>0.2020471776850241</v>
       </c>
       <c r="H136">
-        <v>0.9991336999999999</v>
+        <v>0.9974417</v>
       </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="1">
-        <v>46174</v>
+        <v>46162</v>
       </c>
       <c r="B137" t="s">
         <v>16</v>
       </c>
       <c r="C137">
+        <v>40.37836787855562</v>
+      </c>
+      <c r="D137">
+        <v>21.11271132314188</v>
+      </c>
+      <c r="E137">
+        <v>0.99915058</v>
+      </c>
+      <c r="F137">
+        <v>0.99915058</v>
+      </c>
+      <c r="G137">
+        <v>0.2291077670847563</v>
+      </c>
+      <c r="H137">
+        <v>0.9974415600000001</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
+      <c r="A138" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138">
+        <v>38.9123066967842</v>
+      </c>
+      <c r="D138">
+        <v>21.28910644207464</v>
+      </c>
+      <c r="E138">
+        <v>0.9989350699999999</v>
+      </c>
+      <c r="F138">
+        <v>0.9989350699999999</v>
+      </c>
+      <c r="G138">
+        <v>0.2392382040170877</v>
+      </c>
+      <c r="H138">
+        <v>0.99726191</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
+      <c r="A139" s="1">
+        <v>46164</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139">
+        <v>39.43913909150694</v>
+      </c>
+      <c r="D139">
+        <v>21.05297617141148</v>
+      </c>
+      <c r="E139">
+        <v>0.999144</v>
+      </c>
+      <c r="F139">
+        <v>0.999144</v>
+      </c>
+      <c r="G139">
+        <v>0.2516582935428642</v>
+      </c>
+      <c r="H139">
+        <v>0.9974678400000001</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
+      <c r="A140" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140">
+        <v>39.45782844313628</v>
+      </c>
+      <c r="D140">
+        <v>21.0518901572272</v>
+      </c>
+      <c r="E140">
+        <v>0.999144</v>
+      </c>
+      <c r="F140">
+        <v>0.999144</v>
+      </c>
+      <c r="G140">
+        <v>0.2516582935428642</v>
+      </c>
+      <c r="H140">
+        <v>0.9974678400000001</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
+      <c r="A141" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141">
+        <v>40.20219297984542</v>
+      </c>
+      <c r="D141">
+        <v>21.93106024403281</v>
+      </c>
+      <c r="E141">
+        <v>0.9991421799999999</v>
+      </c>
+      <c r="F141">
+        <v>0.9991421799999999</v>
+      </c>
+      <c r="G141">
+        <v>0.2846167552893293</v>
+      </c>
+      <c r="H141">
+        <v>0.9974609800000001</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
+      <c r="A142" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142">
+        <v>40.34993865302093</v>
+      </c>
+      <c r="D142">
+        <v>21.65366031776487</v>
+      </c>
+      <c r="E142">
+        <v>0.9991434600000001</v>
+      </c>
+      <c r="F142">
+        <v>0.9991434600000001</v>
+      </c>
+      <c r="G142">
+        <v>0.2796902860011767</v>
+      </c>
+      <c r="H142">
+        <v>0.9991434600000001</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
+      <c r="A143" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143">
+        <v>40.5850485390846</v>
+      </c>
+      <c r="D143">
+        <v>21.75450977746074</v>
+      </c>
+      <c r="E143">
+        <v>0.99914592</v>
+      </c>
+      <c r="F143">
+        <v>0.99914592</v>
+      </c>
+      <c r="G143">
+        <v>0.2964818481030536</v>
+      </c>
+      <c r="H143">
+        <v>0.99914592</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
+      <c r="A144" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144">
+        <v>41.86785805184477</v>
+      </c>
+      <c r="D144">
+        <v>22.33589392797469</v>
+      </c>
+      <c r="E144">
+        <v>0.9991336999999999</v>
+      </c>
+      <c r="F144">
+        <v>0.9991336999999999</v>
+      </c>
+      <c r="G144">
+        <v>0.3254158954996882</v>
+      </c>
+      <c r="H144">
+        <v>0.9991336999999999</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
+      <c r="A145" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145">
         <v>42.82932322850974</v>
       </c>
-      <c r="D137">
+      <c r="D145">
         <v>22.98998911430362</v>
       </c>
-      <c r="E137">
+      <c r="E145">
         <v>0.99914238</v>
       </c>
-      <c r="F137">
+      <c r="F145">
         <v>0.99914238</v>
       </c>
-      <c r="G137">
+      <c r="G145">
         <v>0.3583049032509023</v>
       </c>
-      <c r="H137">
+      <c r="H145">
         <v>0.99914238</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8">
+      <c r="A146" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146">
+        <v>43.11872937189534</v>
+      </c>
+      <c r="D146">
+        <v>22.90628380907704</v>
+      </c>
+      <c r="E146">
+        <v>0.9990972800000002</v>
+      </c>
+      <c r="F146">
+        <v>0.9990972800000002</v>
+      </c>
+      <c r="G146">
+        <v>0.3753046155885469</v>
+      </c>
+      <c r="H146">
+        <v>0.9990972800000002</v>
       </c>
     </row>
   </sheetData>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="17">
   <si>
     <t>Date</t>
   </si>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H146"/>
+  <dimension ref="A1:H155"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -691,42 +691,42 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1">
-        <v>46153</v>
+        <v>46176</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12">
-        <v>53.14833755912058</v>
+        <v>26.37947335703338</v>
       </c>
       <c r="D12">
-        <v>25.84885448407537</v>
+        <v>17.69604280148869</v>
       </c>
       <c r="E12">
-        <v>0.9262</v>
+        <v>0.8606</v>
       </c>
       <c r="F12">
-        <v>0.9262</v>
+        <v>0.8606</v>
       </c>
       <c r="G12">
-        <v>0.3839084462043663</v>
+        <v>0.7017717781378616</v>
       </c>
       <c r="H12">
-        <v>0.9262</v>
+        <v>0.9132999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B13" t="s">
         <v>9</v>
       </c>
       <c r="C13">
-        <v>51.82921169635205</v>
+        <v>53.14833755912058</v>
       </c>
       <c r="D13">
-        <v>25.32805827181975</v>
+        <v>25.84885448407537</v>
       </c>
       <c r="E13">
         <v>0.9262</v>
@@ -735,7 +735,7 @@
         <v>0.9262</v>
       </c>
       <c r="G13">
-        <v>0.3568580281685669</v>
+        <v>0.3839084462043663</v>
       </c>
       <c r="H13">
         <v>0.9262</v>
@@ -743,120 +743,120 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
       </c>
       <c r="C14">
-        <v>52.28471716753184</v>
+        <v>51.82921169635205</v>
       </c>
       <c r="D14">
-        <v>25.54525144150689</v>
+        <v>25.32805827181975</v>
       </c>
       <c r="E14">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="F14">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="G14">
-        <v>0.378012896547947</v>
+        <v>0.3568580281685669</v>
       </c>
       <c r="H14">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
       </c>
       <c r="C15">
-        <v>53.87287273813902</v>
+        <v>52.28471716753184</v>
       </c>
       <c r="D15">
-        <v>26.32154226438612</v>
+        <v>25.54525144150689</v>
       </c>
       <c r="E15">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="F15">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="G15">
-        <v>0.4166811087612758</v>
+        <v>0.378012896547947</v>
       </c>
       <c r="H15">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
       </c>
       <c r="C16">
-        <v>52.18747148214074</v>
+        <v>53.87287273813902</v>
       </c>
       <c r="D16">
-        <v>25.13616059644496</v>
+        <v>26.32154226438612</v>
       </c>
       <c r="E16">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="F16">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="G16">
-        <v>0.3627535778249862</v>
+        <v>0.4166811087612758</v>
       </c>
       <c r="H16">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
       </c>
       <c r="C17">
-        <v>50.72035274995172</v>
+        <v>52.18747148214074</v>
       </c>
       <c r="D17">
-        <v>24.61756040386634</v>
+        <v>25.13616059644496</v>
       </c>
       <c r="E17">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="F17">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="G17">
         <v>0.3627535778249862</v>
       </c>
       <c r="H17">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="B18" t="s">
         <v>9</v>
       </c>
       <c r="C18">
-        <v>50.11981086673613</v>
+        <v>50.72035274995172</v>
       </c>
       <c r="D18">
-        <v>24.13061679021705</v>
+        <v>24.61756040386634</v>
       </c>
       <c r="E18">
         <v>0.9259000000000001</v>
@@ -865,7 +865,7 @@
         <v>0.9259000000000001</v>
       </c>
       <c r="G18">
-        <v>0.3258193430227221</v>
+        <v>0.3627535778249862</v>
       </c>
       <c r="H18">
         <v>0.9259000000000001</v>
@@ -873,120 +873,120 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="B19" t="s">
         <v>9</v>
       </c>
       <c r="C19">
-        <v>51.74165648409151</v>
+        <v>50.11981086673613</v>
       </c>
       <c r="D19">
-        <v>24.98091384114761</v>
+        <v>24.13061679021705</v>
       </c>
       <c r="E19">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="F19">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="G19">
-        <v>0.3818277262286871</v>
+        <v>0.3258193430227221</v>
       </c>
       <c r="H19">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="B20" t="s">
         <v>9</v>
       </c>
       <c r="C20">
-        <v>49.13455894175823</v>
+        <v>51.74165648409151</v>
       </c>
       <c r="D20">
-        <v>25.30005057653127</v>
+        <v>24.98091384114761</v>
       </c>
       <c r="E20">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="F20">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="G20">
-        <v>0.4028091571787618</v>
+        <v>0.3818277262286871</v>
       </c>
       <c r="H20">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="B21" t="s">
         <v>9</v>
       </c>
       <c r="C21">
-        <v>49.57776597479297</v>
+        <v>49.13455894175823</v>
       </c>
       <c r="D21">
-        <v>25.04906725563518</v>
+        <v>25.30005057653127</v>
       </c>
       <c r="E21">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="F21">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="G21">
-        <v>0.4256980029692063</v>
+        <v>0.4028091571787618</v>
       </c>
       <c r="H21">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="B22" t="s">
         <v>9</v>
       </c>
       <c r="C22">
-        <v>49.71239596645896</v>
+        <v>49.57776597479297</v>
       </c>
       <c r="D22">
-        <v>25.18778610744295</v>
+        <v>25.04906725563518</v>
       </c>
       <c r="E22">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="F22">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="G22">
-        <v>0.4525749835757003</v>
+        <v>0.4256980029692063</v>
       </c>
       <c r="H22">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="B23" t="s">
         <v>9</v>
       </c>
       <c r="C23">
-        <v>50.77166277510776</v>
+        <v>49.71239596645896</v>
       </c>
       <c r="D23">
-        <v>25.7431782858765</v>
+        <v>25.18778610744295</v>
       </c>
       <c r="E23">
         <v>0.9231999999999999</v>
@@ -995,7 +995,7 @@
         <v>0.9231999999999999</v>
       </c>
       <c r="G23">
-        <v>0.4700884597036457</v>
+        <v>0.4525749835757003</v>
       </c>
       <c r="H23">
         <v>0.9231999999999999</v>
@@ -1003,120 +1003,120 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1">
-        <v>46169</v>
+        <v>46168</v>
       </c>
       <c r="B24" t="s">
         <v>9</v>
       </c>
       <c r="C24">
-        <v>50.57689164833899</v>
+        <v>50.77166277510776</v>
       </c>
       <c r="D24">
-        <v>25.70244067238947</v>
+        <v>25.7431782858765</v>
       </c>
       <c r="E24">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="F24">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="G24">
-        <v>0.4518814984464716</v>
+        <v>0.4700884597036457</v>
       </c>
       <c r="H24">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
       </c>
       <c r="C25">
-        <v>50.80027854822009</v>
+        <v>50.57689164833899</v>
       </c>
       <c r="D25">
-        <v>25.90068415792015</v>
+        <v>25.70244067238947</v>
       </c>
       <c r="E25">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
       <c r="F25">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
       <c r="G25">
-        <v>0.4699150222743402</v>
+        <v>0.4518814984464716</v>
       </c>
       <c r="H25">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
       </c>
       <c r="C26">
-        <v>51.44563447241545</v>
+        <v>50.80027854822009</v>
       </c>
       <c r="D26">
-        <v>26.0970978996374</v>
+        <v>25.90068415792015</v>
       </c>
       <c r="E26">
-        <v>0.9246</v>
+        <v>0.9231</v>
       </c>
       <c r="F26">
-        <v>0.9246</v>
+        <v>0.9231</v>
       </c>
       <c r="G26">
-        <v>0.4791053539115764</v>
+        <v>0.4699150222743402</v>
       </c>
       <c r="H26">
-        <v>0.9246</v>
+        <v>0.9231</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1">
-        <v>46174</v>
+        <v>46171</v>
       </c>
       <c r="B27" t="s">
         <v>9</v>
       </c>
       <c r="C27">
-        <v>53.05792083471825</v>
+        <v>51.44563447241545</v>
       </c>
       <c r="D27">
-        <v>26.86242981002239</v>
+        <v>26.0970978996374</v>
       </c>
       <c r="E27">
-        <v>0.9254999999999999</v>
+        <v>0.9246</v>
       </c>
       <c r="F27">
-        <v>0.9254999999999999</v>
+        <v>0.9246</v>
       </c>
       <c r="G27">
-        <v>0.5306051577195796</v>
+        <v>0.4791053539115764</v>
       </c>
       <c r="H27">
-        <v>0.9254999999999999</v>
+        <v>0.9246</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="B28" t="s">
         <v>9</v>
       </c>
       <c r="C28">
-        <v>54.38946369031042</v>
+        <v>53.05792083471825</v>
       </c>
       <c r="D28">
-        <v>27.57160808325711</v>
+        <v>26.86242981002239</v>
       </c>
       <c r="E28">
         <v>0.9254999999999999</v>
@@ -1125,7 +1125,7 @@
         <v>0.9254999999999999</v>
       </c>
       <c r="G28">
-        <v>0.5845326886558693</v>
+        <v>0.5306051577195796</v>
       </c>
       <c r="H28">
         <v>0.9254999999999999</v>
@@ -1133,146 +1133,146 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1">
-        <v>46153</v>
+        <v>46175</v>
       </c>
       <c r="B29" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C29">
-        <v>34.64560932909123</v>
+        <v>54.38946369031042</v>
       </c>
       <c r="D29">
-        <v>26.08311546080494</v>
+        <v>27.57160808325711</v>
       </c>
       <c r="E29">
-        <v>0.9983000000000001</v>
+        <v>0.9254999999999999</v>
       </c>
       <c r="F29">
-        <v>0.9983000000000001</v>
+        <v>0.9254999999999999</v>
       </c>
       <c r="G29">
-        <v>0.06258613715048233</v>
+        <v>0.5845326886558693</v>
       </c>
       <c r="H29">
-        <v>0.9983000000000001</v>
+        <v>0.9254999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1">
-        <v>46154</v>
+        <v>46176</v>
       </c>
       <c r="B30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C30">
-        <v>34.50204921141101</v>
+        <v>54.35279063045283</v>
       </c>
       <c r="D30">
-        <v>25.94535229304585</v>
+        <v>27.50874919819178</v>
       </c>
       <c r="E30">
-        <v>0.9984</v>
+        <v>0.9162000000000001</v>
       </c>
       <c r="F30">
-        <v>0.9984</v>
+        <v>0.9162000000000001</v>
       </c>
       <c r="G30">
-        <v>0.05768943168306073</v>
+        <v>0.5992718273849102</v>
       </c>
       <c r="H30">
-        <v>0.9984</v>
+        <v>0.9162000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="B31" t="s">
         <v>10</v>
       </c>
       <c r="C31">
-        <v>35.10429483281073</v>
+        <v>34.64560932909123</v>
       </c>
       <c r="D31">
-        <v>26.43864879939599</v>
+        <v>26.08311546080494</v>
       </c>
       <c r="E31">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="F31">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="G31">
-        <v>0.07926550001722021</v>
+        <v>0.06258613715048233</v>
       </c>
       <c r="H31">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
       </c>
       <c r="C32">
-        <v>35.36860632820093</v>
+        <v>34.50204921141101</v>
       </c>
       <c r="D32">
-        <v>26.56575571102338</v>
+        <v>25.94535229304585</v>
       </c>
       <c r="E32">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F32">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G32">
-        <v>0.08553946591902095</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H32">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="B33" t="s">
         <v>10</v>
       </c>
       <c r="C33">
-        <v>34.88080083527914</v>
+        <v>35.10429483281073</v>
       </c>
       <c r="D33">
-        <v>26.19322945679072</v>
+        <v>26.43864879939599</v>
       </c>
       <c r="E33">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="F33">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="G33">
-        <v>0.06870693142475881</v>
+        <v>0.07926550001722021</v>
       </c>
       <c r="H33">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1">
-        <v>46160</v>
+        <v>46156</v>
       </c>
       <c r="B34" t="s">
         <v>10</v>
       </c>
       <c r="C34">
-        <v>34.67638692539213</v>
+        <v>35.36860632820093</v>
       </c>
       <c r="D34">
-        <v>26.06707890342319</v>
+        <v>26.56575571102338</v>
       </c>
       <c r="E34">
         <v>0.9985999999999999</v>
@@ -1281,7 +1281,7 @@
         <v>0.9985999999999999</v>
       </c>
       <c r="G34">
-        <v>0.06289213016552919</v>
+        <v>0.08553946591902095</v>
       </c>
       <c r="H34">
         <v>0.9985999999999999</v>
@@ -1289,120 +1289,120 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="B35" t="s">
         <v>10</v>
       </c>
       <c r="C35">
-        <v>34.21212662725402</v>
+        <v>34.88080083527914</v>
       </c>
       <c r="D35">
-        <v>25.60349394367002</v>
+        <v>26.19322945679072</v>
       </c>
       <c r="E35">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="F35">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="G35">
-        <v>0.0486610616591685</v>
+        <v>0.06870693142475881</v>
       </c>
       <c r="H35">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="B36" t="s">
         <v>10</v>
       </c>
       <c r="C36">
-        <v>34.78598436564941</v>
+        <v>34.67638692539213</v>
       </c>
       <c r="D36">
-        <v>25.95505316769806</v>
+        <v>26.06707890342319</v>
       </c>
       <c r="E36">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="F36">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="G36">
-        <v>0.06335117806143331</v>
+        <v>0.06289213016552919</v>
       </c>
       <c r="H36">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1">
-        <v>46163</v>
+        <v>46161</v>
       </c>
       <c r="B37" t="s">
         <v>10</v>
       </c>
       <c r="C37">
-        <v>33.4539909056227</v>
+        <v>34.21212662725402</v>
       </c>
       <c r="D37">
-        <v>25.96014535427112</v>
+        <v>25.60349394367002</v>
       </c>
       <c r="E37">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="F37">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="G37">
-        <v>0.06350423294229035</v>
+        <v>0.0486610616591685</v>
       </c>
       <c r="H37">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1">
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="B38" t="s">
         <v>10</v>
       </c>
       <c r="C38">
-        <v>33.24951933563993</v>
+        <v>34.78598436564941</v>
       </c>
       <c r="D38">
-        <v>25.46629530314992</v>
+        <v>25.95505316769806</v>
       </c>
       <c r="E38">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="F38">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="G38">
-        <v>0.06136193159696024</v>
+        <v>0.06335117806143331</v>
       </c>
       <c r="H38">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1">
-        <v>46167</v>
+        <v>46163</v>
       </c>
       <c r="B39" t="s">
         <v>10</v>
       </c>
       <c r="C39">
-        <v>33.29896419867477</v>
+        <v>33.4539909056227</v>
       </c>
       <c r="D39">
-        <v>25.45090185337973</v>
+        <v>25.96014535427112</v>
       </c>
       <c r="E39">
         <v>0.9984</v>
@@ -1411,7 +1411,7 @@
         <v>0.9984</v>
       </c>
       <c r="G39">
-        <v>0.06136193159696024</v>
+        <v>0.06350423294229035</v>
       </c>
       <c r="H39">
         <v>0.9984</v>
@@ -1419,16 +1419,16 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1">
-        <v>46168</v>
+        <v>46164</v>
       </c>
       <c r="B40" t="s">
         <v>10</v>
       </c>
       <c r="C40">
-        <v>33.41270923608511</v>
+        <v>33.24951933563993</v>
       </c>
       <c r="D40">
-        <v>25.54156152389702</v>
+        <v>25.46629530314992</v>
       </c>
       <c r="E40">
         <v>0.9984</v>
@@ -1437,7 +1437,7 @@
         <v>0.9984</v>
       </c>
       <c r="G40">
-        <v>0.06549347940676342</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H40">
         <v>0.9984</v>
@@ -1445,718 +1445,718 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1">
-        <v>46169</v>
+        <v>46167</v>
       </c>
       <c r="B41" t="s">
         <v>10</v>
       </c>
       <c r="C41">
-        <v>33.73350746548562</v>
+        <v>33.29896419867477</v>
       </c>
       <c r="D41">
-        <v>25.75393367034243</v>
+        <v>25.45090185337973</v>
       </c>
       <c r="E41">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="F41">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="G41">
-        <v>0.07620510288008187</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H41">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1">
-        <v>46170</v>
+        <v>46168</v>
       </c>
       <c r="B42" t="s">
         <v>10</v>
       </c>
       <c r="C42">
-        <v>33.84336414535104</v>
+        <v>33.41270923608511</v>
       </c>
       <c r="D42">
-        <v>25.97168203877208</v>
+        <v>25.54156152389702</v>
       </c>
       <c r="E42">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
       <c r="F42">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
       <c r="G42">
-        <v>0.0844683152463559</v>
+        <v>0.06549347940676342</v>
       </c>
       <c r="H42">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1">
-        <v>46171</v>
+        <v>46169</v>
       </c>
       <c r="B43" t="s">
         <v>10</v>
       </c>
       <c r="C43">
-        <v>33.73370320039719</v>
+        <v>33.73350746548562</v>
       </c>
       <c r="D43">
-        <v>25.880209881309</v>
+        <v>25.75393367034243</v>
       </c>
       <c r="E43">
-        <v>0.9988</v>
+        <v>0.9987000000000001</v>
       </c>
       <c r="F43">
-        <v>0.9988</v>
+        <v>0.9987000000000001</v>
       </c>
       <c r="G43">
-        <v>0.08201990413931148</v>
+        <v>0.07620510288008187</v>
       </c>
       <c r="H43">
-        <v>0.9988</v>
+        <v>0.9987000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1">
-        <v>46174</v>
+        <v>46170</v>
       </c>
       <c r="B44" t="s">
         <v>10</v>
       </c>
       <c r="C44">
-        <v>33.45546240777382</v>
+        <v>33.84336414535104</v>
       </c>
       <c r="D44">
-        <v>25.61350381215703</v>
+        <v>25.97168203877208</v>
       </c>
       <c r="E44">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
       <c r="F44">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
       <c r="G44">
-        <v>0.06901304118647311</v>
+        <v>0.0844683152463559</v>
       </c>
       <c r="H44">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1">
-        <v>46175</v>
+        <v>46171</v>
       </c>
       <c r="B45" t="s">
         <v>10</v>
       </c>
       <c r="C45">
-        <v>33.31245255516097</v>
+        <v>33.73370320039719</v>
       </c>
       <c r="D45">
-        <v>25.36461330330757</v>
+        <v>25.880209881309</v>
       </c>
       <c r="E45">
-        <v>0.9989999999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="F45">
-        <v>0.9989999999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="G45">
-        <v>0.05845447259401171</v>
+        <v>0.08201990413931148</v>
       </c>
       <c r="H45">
-        <v>0.9989999999999999</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1">
-        <v>46153</v>
+        <v>46174</v>
       </c>
       <c r="B46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C46">
-        <v>36.55790859258162</v>
+        <v>33.45546240777382</v>
       </c>
       <c r="D46">
-        <v>22.67181120908155</v>
+        <v>25.61350381215703</v>
       </c>
       <c r="E46">
-        <v>0.9990740999999999</v>
+        <v>0.999</v>
       </c>
       <c r="F46">
-        <v>0.9990740999999999</v>
+        <v>0.999</v>
       </c>
       <c r="G46">
-        <v>0.1648443271746771</v>
+        <v>0.06901304118647311</v>
       </c>
       <c r="H46">
-        <v>0.9990740999999999</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1">
-        <v>46154</v>
+        <v>46175</v>
       </c>
       <c r="B47" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C47">
-        <v>36.44753722959613</v>
+        <v>33.31245255516097</v>
       </c>
       <c r="D47">
-        <v>22.40292401789388</v>
+        <v>25.36461330330757</v>
       </c>
       <c r="E47">
-        <v>0.9990772499999999</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="F47">
-        <v>0.9990772499999999</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="G47">
-        <v>0.154964342628132</v>
+        <v>0.05845447259401171</v>
       </c>
       <c r="H47">
-        <v>0.9990772499999999</v>
+        <v>0.9989999999999999</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1">
-        <v>46155</v>
+        <v>46176</v>
       </c>
       <c r="B48" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C48">
-        <v>36.63128514035871</v>
+        <v>33.02444632653544</v>
       </c>
       <c r="D48">
-        <v>22.65773388934668</v>
+        <v>25.07926152561908</v>
       </c>
       <c r="E48">
-        <v>0.99907745</v>
+        <v>0.9991</v>
       </c>
       <c r="F48">
-        <v>0.99907745</v>
+        <v>0.9991</v>
       </c>
       <c r="G48">
-        <v>0.1671633421405267</v>
+        <v>0.04697780820974229</v>
       </c>
       <c r="H48">
-        <v>0.99907745</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="B49" t="s">
         <v>11</v>
       </c>
       <c r="C49">
-        <v>36.87865927427314</v>
+        <v>36.55790859258162</v>
       </c>
       <c r="D49">
-        <v>22.69755646854794</v>
+        <v>22.67181120908155</v>
       </c>
       <c r="E49">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="F49">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="G49">
-        <v>0.1754592080224002</v>
+        <v>0.1648443271746771</v>
       </c>
       <c r="H49">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="B50" t="s">
         <v>11</v>
       </c>
       <c r="C50">
-        <v>36.52208783231286</v>
+        <v>36.44753722959613</v>
       </c>
       <c r="D50">
-        <v>22.32462309676992</v>
+        <v>22.40292401789388</v>
       </c>
       <c r="E50">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="F50">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="G50">
-        <v>0.1577242156354994</v>
+        <v>0.154964342628132</v>
       </c>
       <c r="H50">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="B51" t="s">
         <v>11</v>
       </c>
       <c r="C51">
-        <v>36.25604200674668</v>
+        <v>36.63128514035871</v>
       </c>
       <c r="D51">
-        <v>22.16555007468561</v>
+        <v>22.65773388934668</v>
       </c>
       <c r="E51">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="F51">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="G51">
-        <v>0.1527434068648266</v>
+        <v>0.1671633421405267</v>
       </c>
       <c r="H51">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1">
-        <v>46161</v>
+        <v>46156</v>
       </c>
       <c r="B52" t="s">
         <v>11</v>
       </c>
       <c r="C52">
-        <v>36.01040085730018</v>
+        <v>36.87865927427314</v>
       </c>
       <c r="D52">
-        <v>22.19475589056387</v>
+        <v>22.69755646854794</v>
       </c>
       <c r="E52">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="F52">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="G52">
-        <v>0.1456396418594061</v>
+        <v>0.1754592080224002</v>
       </c>
       <c r="H52">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1">
-        <v>46162</v>
+        <v>46157</v>
       </c>
       <c r="B53" t="s">
         <v>11</v>
       </c>
       <c r="C53">
-        <v>36.45290912796982</v>
+        <v>36.52208783231286</v>
       </c>
       <c r="D53">
-        <v>22.46357594746874</v>
+        <v>22.32462309676992</v>
       </c>
       <c r="E53">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="F53">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="G53">
-        <v>0.1646157747240327</v>
+        <v>0.1577242156354994</v>
       </c>
       <c r="H53">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1">
-        <v>46163</v>
+        <v>46160</v>
       </c>
       <c r="B54" t="s">
         <v>11</v>
       </c>
       <c r="C54">
-        <v>35.75282090566891</v>
+        <v>36.25604200674668</v>
       </c>
       <c r="D54">
-        <v>22.57615417310648</v>
+        <v>22.16555007468561</v>
       </c>
       <c r="E54">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="F54">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="G54">
-        <v>0.1668367104873381</v>
+        <v>0.1527434068648266</v>
       </c>
       <c r="H54">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1">
-        <v>46164</v>
+        <v>46161</v>
       </c>
       <c r="B55" t="s">
         <v>11</v>
       </c>
       <c r="C55">
-        <v>35.75514940724808</v>
+        <v>36.01040085730018</v>
       </c>
       <c r="D55">
-        <v>22.28880693466429</v>
+        <v>22.19475589056387</v>
       </c>
       <c r="E55">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="F55">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="G55">
-        <v>0.1717848261904962</v>
+        <v>0.1456396418594061</v>
       </c>
       <c r="H55">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1">
-        <v>46167</v>
+        <v>46162</v>
       </c>
       <c r="B56" t="s">
         <v>11</v>
       </c>
       <c r="C56">
-        <v>35.84133099010302</v>
+        <v>36.45290912796982</v>
       </c>
       <c r="D56">
-        <v>22.37458514769363</v>
+        <v>22.46357594746874</v>
       </c>
       <c r="E56">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="F56">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="G56">
-        <v>0.1717848261904962</v>
+        <v>0.1646157747240327</v>
       </c>
       <c r="H56">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1">
-        <v>46168</v>
+        <v>46163</v>
       </c>
       <c r="B57" t="s">
         <v>11</v>
       </c>
       <c r="C57">
-        <v>36.23214279739292</v>
+        <v>35.75282090566891</v>
       </c>
       <c r="D57">
-        <v>22.93484792820123</v>
+        <v>22.57615417310648</v>
       </c>
       <c r="E57">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
       <c r="F57">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
       <c r="G57">
-        <v>0.1925900763781823</v>
+        <v>0.1668367104873381</v>
       </c>
       <c r="H57">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="B58" t="s">
         <v>11</v>
       </c>
       <c r="C58">
-        <v>36.4336692499184</v>
+        <v>35.75514940724808</v>
       </c>
       <c r="D58">
-        <v>22.75940954009856</v>
+        <v>22.28880693466429</v>
       </c>
       <c r="E58">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="F58">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="G58">
-        <v>0.1912346098381414</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H58">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="B59" t="s">
         <v>11</v>
       </c>
       <c r="C59">
-        <v>36.57358557066742</v>
+        <v>35.84133099010302</v>
       </c>
       <c r="D59">
-        <v>22.83069636955243</v>
+        <v>22.37458514769363</v>
       </c>
       <c r="E59">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="F59">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="G59">
-        <v>0.2012778603742877</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H59">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1">
-        <v>46171</v>
+        <v>46168</v>
       </c>
       <c r="B60" t="s">
         <v>11</v>
       </c>
       <c r="C60">
-        <v>36.67481300942</v>
+        <v>36.23214279739292</v>
       </c>
       <c r="D60">
-        <v>22.95852861681004</v>
+        <v>22.93484792820123</v>
       </c>
       <c r="E60">
-        <v>0.9964953299999998</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="F60">
-        <v>0.9964953299999998</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="G60">
-        <v>0.2057034850411275</v>
+        <v>0.1925900763781823</v>
       </c>
       <c r="H60">
-        <v>0.9994474899999999</v>
+        <v>0.9992609200000001</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1">
-        <v>46174</v>
+        <v>46169</v>
       </c>
       <c r="B61" t="s">
         <v>11</v>
       </c>
       <c r="C61">
-        <v>36.84565507982974</v>
+        <v>36.4336692499184</v>
       </c>
       <c r="D61">
-        <v>23.15960292175205</v>
+        <v>22.75940954009856</v>
       </c>
       <c r="E61">
-        <v>0.99646052</v>
+        <v>0.9992099400000001</v>
       </c>
       <c r="F61">
-        <v>0.99646052</v>
+        <v>0.9992099400000001</v>
       </c>
       <c r="G61">
-        <v>0.2129379226426205</v>
+        <v>0.1912346098381414</v>
       </c>
       <c r="H61">
-        <v>0.9993986199999999</v>
+        <v>0.9992099400000001</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1">
-        <v>46175</v>
+        <v>46170</v>
       </c>
       <c r="B62" t="s">
         <v>11</v>
       </c>
       <c r="C62">
-        <v>36.88482057171844</v>
+        <v>36.57358557066742</v>
       </c>
       <c r="D62">
-        <v>23.03898938038424</v>
+        <v>22.83069636955243</v>
       </c>
       <c r="E62">
-        <v>0.99645675</v>
+        <v>0.9994435600000001</v>
       </c>
       <c r="F62">
-        <v>0.99645675</v>
+        <v>0.9994435600000001</v>
       </c>
       <c r="G62">
-        <v>0.2185229551183987</v>
+        <v>0.2012778603742877</v>
       </c>
       <c r="H62">
-        <v>0.9994034199999998</v>
+        <v>0.9994435600000001</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1">
-        <v>46153</v>
+        <v>46171</v>
       </c>
       <c r="B63" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C63">
-        <v>52.70832779833182</v>
+        <v>36.67481300942</v>
       </c>
       <c r="D63">
-        <v>23.99044674439659</v>
+        <v>22.95852861681004</v>
       </c>
       <c r="E63">
-        <v>0.9994000000000002</v>
+        <v>0.9964953299999998</v>
       </c>
       <c r="F63">
-        <v>0.9994000000000002</v>
+        <v>0.9964953299999998</v>
       </c>
       <c r="G63">
-        <v>0.5438253854918791</v>
+        <v>0.2057034850411275</v>
       </c>
       <c r="H63">
-        <v>0.9994000000000002</v>
+        <v>0.9994474899999999</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1">
-        <v>46154</v>
+        <v>46174</v>
       </c>
       <c r="B64" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C64">
-        <v>50.89464485280568</v>
+        <v>36.84565507982974</v>
       </c>
       <c r="D64">
-        <v>23.21558303176282</v>
+        <v>23.15960292175205</v>
       </c>
       <c r="E64">
-        <v>0.9996</v>
+        <v>0.99646052</v>
       </c>
       <c r="F64">
-        <v>0.9996</v>
+        <v>0.99646052</v>
       </c>
       <c r="G64">
-        <v>0.5034825029548833</v>
+        <v>0.2129379226426205</v>
       </c>
       <c r="H64">
-        <v>0.9996</v>
+        <v>0.9993986199999999</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1">
-        <v>46155</v>
+        <v>46175</v>
       </c>
       <c r="B65" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C65">
-        <v>51.8659994471731</v>
+        <v>36.88482057171844</v>
       </c>
       <c r="D65">
-        <v>23.7009037279043</v>
+        <v>23.03898938038424</v>
       </c>
       <c r="E65">
-        <v>1.0002</v>
+        <v>0.99645675</v>
       </c>
       <c r="F65">
-        <v>1.0002</v>
+        <v>0.99645675</v>
       </c>
       <c r="G65">
-        <v>0.533512029714132</v>
+        <v>0.2185229551183987</v>
       </c>
       <c r="H65">
-        <v>1.0002</v>
+        <v>0.9994034199999998</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1">
-        <v>46156</v>
+        <v>46176</v>
       </c>
       <c r="B66" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C66">
-        <v>52.4470179952828</v>
+        <v>36.96809213745556</v>
       </c>
       <c r="D66">
-        <v>23.76861704536814</v>
+        <v>22.99660212231548</v>
       </c>
       <c r="E66">
-        <v>0.9998</v>
+        <v>0.9964706</v>
       </c>
       <c r="F66">
-        <v>0.9998</v>
+        <v>0.9964706</v>
       </c>
       <c r="G66">
-        <v>0.5492634496849078</v>
+        <v>0.2153385706032709</v>
       </c>
       <c r="H66">
-        <v>0.9998</v>
+        <v>0.9993955800000001</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="B67" t="s">
         <v>12</v>
       </c>
       <c r="C67">
-        <v>50.81077380018606</v>
+        <v>52.70832779833182</v>
       </c>
       <c r="D67">
-        <v>22.76900580927995</v>
+        <v>23.99044674439659</v>
       </c>
       <c r="E67">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="F67">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="G67">
-        <v>0.4903296143797722</v>
+        <v>0.5438253854918791</v>
       </c>
       <c r="H67">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1">
-        <v>46160</v>
+        <v>46154</v>
       </c>
       <c r="B68" t="s">
         <v>12</v>
       </c>
       <c r="C68">
-        <v>49.50286387149169</v>
+        <v>50.89464485280568</v>
       </c>
       <c r="D68">
-        <v>22.24532119914133</v>
+        <v>23.21558303176282</v>
       </c>
       <c r="E68">
         <v>0.9996</v>
@@ -2165,7 +2165,7 @@
         <v>0.9996</v>
       </c>
       <c r="G68">
-        <v>0.4630591776162345</v>
+        <v>0.5034825029548833</v>
       </c>
       <c r="H68">
         <v>0.9996</v>
@@ -2173,224 +2173,224 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1">
-        <v>46161</v>
+        <v>46155</v>
       </c>
       <c r="B69" t="s">
         <v>12</v>
       </c>
       <c r="C69">
-        <v>49.29146729279496</v>
+        <v>51.8659994471731</v>
       </c>
       <c r="D69">
-        <v>22.22167836589682</v>
+        <v>23.7009037279043</v>
       </c>
       <c r="E69">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="F69">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="G69">
-        <v>0.4571659248870246</v>
+        <v>0.533512029714132</v>
       </c>
       <c r="H69">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1">
-        <v>46162</v>
+        <v>46156</v>
       </c>
       <c r="B70" t="s">
         <v>12</v>
       </c>
       <c r="C70">
-        <v>50.88652370817657</v>
+        <v>52.4470179952828</v>
       </c>
       <c r="D70">
-        <v>22.93254398967657</v>
+        <v>23.76861704536814</v>
       </c>
       <c r="E70">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F70">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G70">
-        <v>0.5126171754864624</v>
+        <v>0.5492634496849078</v>
       </c>
       <c r="H70">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1">
-        <v>46163</v>
+        <v>46157</v>
       </c>
       <c r="B71" t="s">
         <v>12</v>
       </c>
       <c r="C71">
-        <v>48.26646764818586</v>
+        <v>50.81077380018606</v>
       </c>
       <c r="D71">
-        <v>23.11655387625012</v>
+        <v>22.76900580927995</v>
       </c>
       <c r="E71">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="F71">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="G71">
-        <v>0.521243030947425</v>
+        <v>0.4903296143797722</v>
       </c>
       <c r="H71">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1">
-        <v>46164</v>
+        <v>46160</v>
       </c>
       <c r="B72" t="s">
         <v>12</v>
       </c>
       <c r="C72">
-        <v>48.84737503703267</v>
+        <v>49.50286387149169</v>
       </c>
       <c r="D72">
-        <v>22.83557604744466</v>
+        <v>22.24532119914133</v>
       </c>
       <c r="E72">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="F72">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="G72">
-        <v>0.5438521997590966</v>
+        <v>0.4630591776162345</v>
       </c>
       <c r="H72">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1">
-        <v>46167</v>
+        <v>46161</v>
       </c>
       <c r="B73" t="s">
         <v>12</v>
       </c>
       <c r="C73">
-        <v>48.85151560750146</v>
+        <v>49.29146729279496</v>
       </c>
       <c r="D73">
-        <v>22.83513820206554</v>
+        <v>22.22167836589682</v>
       </c>
       <c r="E73">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F73">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G73">
-        <v>0.5438521997590966</v>
+        <v>0.4571659248870246</v>
       </c>
       <c r="H73">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1">
-        <v>46168</v>
+        <v>46162</v>
       </c>
       <c r="B74" t="s">
         <v>12</v>
       </c>
       <c r="C74">
-        <v>50.90437883274981</v>
+        <v>50.88652370817657</v>
       </c>
       <c r="D74">
-        <v>24.25672473501501</v>
+        <v>22.93254398967657</v>
       </c>
       <c r="E74">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F74">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G74">
-        <v>0.6130191115419561</v>
+        <v>0.5126171754864624</v>
       </c>
       <c r="H74">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1">
-        <v>46169</v>
+        <v>46163</v>
       </c>
       <c r="B75" t="s">
         <v>12</v>
       </c>
       <c r="C75">
-        <v>50.47312432255841</v>
+        <v>48.26646764818586</v>
       </c>
       <c r="D75">
-        <v>23.84499305142194</v>
+        <v>23.11655387625012</v>
       </c>
       <c r="E75">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="F75">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="G75">
-        <v>0.5952317692821967</v>
+        <v>0.521243030947425</v>
       </c>
       <c r="H75">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1">
-        <v>46170</v>
+        <v>46164</v>
       </c>
       <c r="B76" t="s">
         <v>12</v>
       </c>
       <c r="C76">
-        <v>50.84596269629946</v>
+        <v>48.84737503703267</v>
       </c>
       <c r="D76">
-        <v>23.7680603326165</v>
+        <v>22.83557604744466</v>
       </c>
       <c r="E76">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F76">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G76">
-        <v>0.606831065374982</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H76">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1">
-        <v>46171</v>
+        <v>46167</v>
       </c>
       <c r="B77" t="s">
         <v>12</v>
       </c>
       <c r="C77">
-        <v>51.08372269965196</v>
+        <v>48.85151560750146</v>
       </c>
       <c r="D77">
-        <v>23.88880359436525</v>
+        <v>22.83513820206554</v>
       </c>
       <c r="E77">
         <v>0.9998999999999999</v>
@@ -2399,7 +2399,7 @@
         <v>0.9998999999999999</v>
       </c>
       <c r="G77">
-        <v>0.604420070348211</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H77">
         <v>0.9998999999999999</v>
@@ -2407,1186 +2407,1186 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="1">
-        <v>46174</v>
+        <v>46168</v>
       </c>
       <c r="B78" t="s">
         <v>12</v>
       </c>
       <c r="C78">
-        <v>51.84875713649351</v>
+        <v>50.90437883274981</v>
       </c>
       <c r="D78">
-        <v>24.29466650399529</v>
+        <v>24.25672473501501</v>
       </c>
       <c r="E78">
-        <v>0.9998</v>
+        <v>0.9996999999999999</v>
       </c>
       <c r="F78">
-        <v>0.9998</v>
+        <v>0.9996999999999999</v>
       </c>
       <c r="G78">
-        <v>0.6282079224060508</v>
+        <v>0.6130191115419561</v>
       </c>
       <c r="H78">
-        <v>0.9998</v>
+        <v>0.9996999999999999</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1">
-        <v>46175</v>
+        <v>46169</v>
       </c>
       <c r="B79" t="s">
         <v>12</v>
       </c>
       <c r="C79">
-        <v>53.42858844634741</v>
+        <v>50.47312432255841</v>
       </c>
       <c r="D79">
-        <v>24.82449061140869</v>
+        <v>23.84499305142194</v>
       </c>
       <c r="E79">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="F79">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="G79">
-        <v>0.6935709687814895</v>
+        <v>0.5952317692821967</v>
       </c>
       <c r="H79">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1">
-        <v>46153</v>
+        <v>46170</v>
       </c>
       <c r="B80" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C80">
-        <v>57.1732166855686</v>
+        <v>50.84596269629946</v>
       </c>
       <c r="D80">
-        <v>23.50022751267814</v>
+        <v>23.7680603326165</v>
       </c>
       <c r="E80">
-        <v>0.9991</v>
+        <v>0.9998</v>
       </c>
       <c r="F80">
-        <v>0.9991</v>
+        <v>0.9998</v>
       </c>
       <c r="G80">
-        <v>0.6994110097039083</v>
+        <v>0.606831065374982</v>
       </c>
       <c r="H80">
-        <v>0.9991</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="1">
-        <v>46154</v>
+        <v>46171</v>
       </c>
       <c r="B81" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C81">
-        <v>54.77380642078597</v>
+        <v>51.08372269965196</v>
       </c>
       <c r="D81">
-        <v>22.55192940254518</v>
+        <v>23.88880359436525</v>
       </c>
       <c r="E81">
-        <v>0.9990000000000001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F81">
-        <v>0.9990000000000001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G81">
-        <v>0.6459175880844941</v>
+        <v>0.604420070348211</v>
       </c>
       <c r="H81">
-        <v>0.9990000000000001</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="1">
-        <v>46155</v>
+        <v>46174</v>
       </c>
       <c r="B82" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C82">
-        <v>56.32187380830906</v>
+        <v>51.84875713649351</v>
       </c>
       <c r="D82">
-        <v>23.17121437414109</v>
+        <v>24.29466650399529</v>
       </c>
       <c r="E82">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
       <c r="F82">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
       <c r="G82">
-        <v>0.6851523922954754</v>
+        <v>0.6282079224060508</v>
       </c>
       <c r="H82">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="1">
-        <v>46156</v>
+        <v>46175</v>
       </c>
       <c r="B83" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C83">
-        <v>56.15321618553139</v>
+        <v>53.42858844634741</v>
       </c>
       <c r="D83">
-        <v>22.95838347314443</v>
+        <v>24.82449061140869</v>
       </c>
       <c r="E83">
-        <v>0.9992</v>
+        <v>1</v>
       </c>
       <c r="F83">
-        <v>0.9992</v>
+        <v>1</v>
       </c>
       <c r="G83">
-        <v>0.6907028507208208</v>
+        <v>0.6935709687814895</v>
       </c>
       <c r="H83">
-        <v>0.9992</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="1">
-        <v>46157</v>
+        <v>46176</v>
       </c>
       <c r="B84" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C84">
-        <v>54.47755813049488</v>
+        <v>53.95056789686777</v>
       </c>
       <c r="D84">
-        <v>22.0083816089626</v>
+        <v>24.99295077214167</v>
       </c>
       <c r="E84">
-        <v>0.9986</v>
+        <v>0.9996000000000002</v>
       </c>
       <c r="F84">
-        <v>0.9986</v>
+        <v>0.9996000000000002</v>
       </c>
       <c r="G84">
-        <v>0.6220895940829376</v>
+        <v>0.7088134081800193</v>
       </c>
       <c r="H84">
-        <v>0.9986</v>
+        <v>0.9996000000000002</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
       </c>
       <c r="C85">
-        <v>52.6278781150669</v>
+        <v>57.1732166855686</v>
       </c>
       <c r="D85">
-        <v>21.5357353870778</v>
+        <v>23.50022751267814</v>
       </c>
       <c r="E85">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F85">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G85">
-        <v>0.5845134636435627</v>
+        <v>0.6994110097039083</v>
       </c>
       <c r="H85">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
       </c>
       <c r="C86">
-        <v>54.91583234840245</v>
+        <v>54.77380642078597</v>
       </c>
       <c r="D86">
-        <v>22.38321645985006</v>
+        <v>22.55192940254518</v>
       </c>
       <c r="E86">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F86">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G86">
-        <v>0.6596976539194066</v>
+        <v>0.6459175880844941</v>
       </c>
       <c r="H86">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B87" t="s">
         <v>13</v>
       </c>
       <c r="C87">
-        <v>53.91712298548793</v>
+        <v>56.32187380830906</v>
       </c>
       <c r="D87">
-        <v>22.73711181201267</v>
+        <v>23.17121437414109</v>
       </c>
       <c r="E87">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F87">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G87">
-        <v>0.6737329602396263</v>
+        <v>0.6851523922954754</v>
       </c>
       <c r="H87">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="B88" t="s">
         <v>13</v>
       </c>
       <c r="C88">
-        <v>55.19651747515625</v>
+        <v>56.15321618553139</v>
       </c>
       <c r="D88">
-        <v>22.79462037330554</v>
+        <v>22.95838347314443</v>
       </c>
       <c r="E88">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
       <c r="F88">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
       <c r="G88">
-        <v>0.7139885317003913</v>
+        <v>0.6907028507208208</v>
       </c>
       <c r="H88">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="1">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
       </c>
       <c r="C89">
-        <v>55.28054997487197</v>
+        <v>54.47755813049488</v>
       </c>
       <c r="D89">
-        <v>23.00160891539877</v>
+        <v>22.0083816089626</v>
       </c>
       <c r="E89">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="F89">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="G89">
-        <v>0.7139885317003913</v>
+        <v>0.6220895940829376</v>
       </c>
       <c r="H89">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="1">
-        <v>46168</v>
+        <v>46161</v>
       </c>
       <c r="B90" t="s">
         <v>13</v>
       </c>
       <c r="C90">
-        <v>58.75156728873073</v>
+        <v>52.6278781150669</v>
       </c>
       <c r="D90">
-        <v>24.84249654093248</v>
+        <v>21.5357353870778</v>
       </c>
       <c r="E90">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="F90">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="G90">
-        <v>0.8184872182632257</v>
+        <v>0.5845134636435627</v>
       </c>
       <c r="H90">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="1">
-        <v>46169</v>
+        <v>46162</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
       </c>
       <c r="C91">
-        <v>57.86771234337395</v>
+        <v>54.91583234840245</v>
       </c>
       <c r="D91">
-        <v>24.21066615243091</v>
+        <v>22.38321645985006</v>
       </c>
       <c r="E91">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="F91">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="G91">
-        <v>0.798997241708943</v>
+        <v>0.6596976539194066</v>
       </c>
       <c r="H91">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="1">
-        <v>46170</v>
+        <v>46163</v>
       </c>
       <c r="B92" t="s">
         <v>13</v>
       </c>
       <c r="C92">
-        <v>58.18666682631797</v>
+        <v>53.91712298548793</v>
       </c>
       <c r="D92">
-        <v>24.09552344282839</v>
+        <v>22.73711181201267</v>
       </c>
       <c r="E92">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="F92">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="G92">
-        <v>0.8165093478664007</v>
+        <v>0.6737329602396263</v>
       </c>
       <c r="H92">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="1">
-        <v>46171</v>
+        <v>46164</v>
       </c>
       <c r="B93" t="s">
         <v>13</v>
       </c>
       <c r="C93">
-        <v>58.79256019733606</v>
+        <v>55.19651747515625</v>
       </c>
       <c r="D93">
-        <v>24.33854853448823</v>
+        <v>22.79462037330554</v>
       </c>
       <c r="E93">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F93">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G93">
-        <v>0.8152654642198496</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H93">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="1">
-        <v>46174</v>
+        <v>46167</v>
       </c>
       <c r="B94" t="s">
         <v>13</v>
       </c>
       <c r="C94">
-        <v>58.97156722185718</v>
+        <v>55.28054997487197</v>
       </c>
       <c r="D94">
-        <v>24.48296361348067</v>
+        <v>23.00160891539877</v>
       </c>
       <c r="E94">
-        <v>0.9990000000000001</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="F94">
-        <v>0.9990000000000001</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="G94">
-        <v>0.8243563865851753</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H94">
-        <v>0.9990000000000001</v>
+        <v>0.9989000000000001</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="1">
-        <v>46175</v>
+        <v>46168</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
       </c>
       <c r="C95">
-        <v>61.6542902214027</v>
+        <v>58.75156728873073</v>
       </c>
       <c r="D95">
-        <v>25.06517348653028</v>
+        <v>24.84249654093248</v>
       </c>
       <c r="E95">
-        <v>0.9988</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="F95">
-        <v>0.9988</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="G95">
-        <v>0.9299077697948877</v>
+        <v>0.8184872182632257</v>
       </c>
       <c r="H95">
-        <v>0.9988</v>
+        <v>0.9989000000000001</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="1">
-        <v>46153</v>
+        <v>46169</v>
       </c>
       <c r="B96" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C96">
-        <v>35.78646526282436</v>
+        <v>57.86771234337395</v>
       </c>
       <c r="D96">
-        <v>18.96635091925032</v>
+        <v>24.21066615243091</v>
       </c>
       <c r="E96">
-        <v>0.9996491399999999</v>
+        <v>0.9986999999999999</v>
       </c>
       <c r="F96">
-        <v>0.9996491399999999</v>
+        <v>0.9986999999999999</v>
       </c>
       <c r="G96">
-        <v>0.2240600969213613</v>
+        <v>0.798997241708943</v>
       </c>
       <c r="H96">
-        <v>0.9985614899999999</v>
+        <v>0.9986999999999999</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="1">
-        <v>46154</v>
+        <v>46170</v>
       </c>
       <c r="B97" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C97">
-        <v>35.71584102184062</v>
+        <v>58.18666682631797</v>
       </c>
       <c r="D97">
-        <v>18.62432950231353</v>
+        <v>24.09552344282839</v>
       </c>
       <c r="E97">
-        <v>0.99965481</v>
+        <v>0.9991</v>
       </c>
       <c r="F97">
-        <v>0.99965481</v>
+        <v>0.9991</v>
       </c>
       <c r="G97">
-        <v>0.2104844827747143</v>
+        <v>0.8165093478664007</v>
       </c>
       <c r="H97">
-        <v>0.9985622199999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="1">
-        <v>46155</v>
+        <v>46171</v>
       </c>
       <c r="B98" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C98">
-        <v>35.95182028203252</v>
+        <v>58.79256019733606</v>
       </c>
       <c r="D98">
-        <v>18.95670796791552</v>
+        <v>24.33854853448823</v>
       </c>
       <c r="E98">
-        <v>0.9996515200000001</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="F98">
-        <v>0.9996515200000001</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="G98">
-        <v>0.2259035693959275</v>
+        <v>0.8152654642198496</v>
       </c>
       <c r="H98">
-        <v>0.99855193</v>
+        <v>0.9989999999999999</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="1">
-        <v>46156</v>
+        <v>46174</v>
       </c>
       <c r="B99" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C99">
-        <v>36.14451597805883</v>
+        <v>58.97156722185718</v>
       </c>
       <c r="D99">
-        <v>18.86297660538653</v>
+        <v>24.48296361348067</v>
       </c>
       <c r="E99">
-        <v>0.9996563399999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F99">
-        <v>0.9996563399999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G99">
-        <v>0.2362110061840785</v>
+        <v>0.8243563865851753</v>
       </c>
       <c r="H99">
-        <v>0.99857265</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="1">
-        <v>46157</v>
+        <v>46175</v>
       </c>
       <c r="B100" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C100">
-        <v>35.32805803135546</v>
+        <v>61.6542902214027</v>
       </c>
       <c r="D100">
-        <v>18.35643242381478</v>
+        <v>25.06517348653028</v>
       </c>
       <c r="E100">
-        <v>0.9997415800000001</v>
+        <v>0.9988</v>
       </c>
       <c r="F100">
-        <v>0.9997415800000001</v>
+        <v>0.9988</v>
       </c>
       <c r="G100">
-        <v>0.2023559161375383</v>
+        <v>0.9299077697948877</v>
       </c>
       <c r="H100">
-        <v>0.9986639900000002</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="1">
-        <v>46160</v>
+        <v>46176</v>
       </c>
       <c r="B101" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C101">
-        <v>34.83995455757461</v>
+        <v>63.0681947750049</v>
       </c>
       <c r="D101">
-        <v>18.02301281718857</v>
+        <v>25.58770976382014</v>
       </c>
       <c r="E101">
-        <v>0.9996851299999999</v>
+        <v>0.9988000000000002</v>
       </c>
       <c r="F101">
-        <v>0.9996851299999999</v>
+        <v>0.9988000000000002</v>
       </c>
       <c r="G101">
-        <v>0.1850932291737926</v>
+        <v>0.9639112148600193</v>
       </c>
       <c r="H101">
-        <v>0.99857724</v>
+        <v>0.9988000000000002</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B102" t="s">
         <v>14</v>
       </c>
       <c r="C102">
-        <v>34.45479308705605</v>
+        <v>35.78646526282436</v>
       </c>
       <c r="D102">
-        <v>18.09576834566068</v>
+        <v>18.96635091925032</v>
       </c>
       <c r="E102">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="F102">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="G102">
-        <v>0.1784731209386736</v>
+        <v>0.2240600969213613</v>
       </c>
       <c r="H102">
-        <v>0.9985337599999999</v>
+        <v>0.9985614899999999</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B103" t="s">
         <v>14</v>
       </c>
       <c r="C103">
-        <v>34.96336277390787</v>
+        <v>35.71584102184062</v>
       </c>
       <c r="D103">
-        <v>18.34938420029253</v>
+        <v>18.62432950231353</v>
       </c>
       <c r="E103">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="F103">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="G103">
-        <v>0.2009313391215752</v>
+        <v>0.2104844827747143</v>
       </c>
       <c r="H103">
-        <v>0.99848777</v>
+        <v>0.9985622199999999</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B104" t="s">
         <v>14</v>
       </c>
       <c r="C104">
-        <v>34.44616924817128</v>
+        <v>35.95182028203252</v>
       </c>
       <c r="D104">
-        <v>18.60085625074367</v>
+        <v>18.95670796791552</v>
       </c>
       <c r="E104">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="F104">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="G104">
-        <v>0.2124957180214682</v>
+        <v>0.2259035693959275</v>
       </c>
       <c r="H104">
-        <v>0.9985085200000001</v>
+        <v>0.99855193</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="1">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="B105" t="s">
         <v>14</v>
       </c>
       <c r="C105">
-        <v>34.62137220937314</v>
+        <v>36.14451597805883</v>
       </c>
       <c r="D105">
-        <v>18.28780484745949</v>
+        <v>18.86297660538653</v>
       </c>
       <c r="E105">
-        <v>0.9996106299999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="F105">
-        <v>0.9996106299999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="G105">
-        <v>0.2145907067863493</v>
+        <v>0.2362110061840785</v>
       </c>
       <c r="H105">
-        <v>0.9932939299999999</v>
+        <v>0.99857265</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="1">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="B106" t="s">
         <v>14</v>
       </c>
       <c r="C106">
-        <v>34.6540695486741</v>
+        <v>35.32805803135546</v>
       </c>
       <c r="D106">
-        <v>18.36409048915342</v>
+        <v>18.35643242381478</v>
       </c>
       <c r="E106">
-        <v>0.9995448900000001</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="F106">
-        <v>0.9995448900000001</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="G106">
-        <v>0.2145907067863493</v>
+        <v>0.2023559161375383</v>
       </c>
       <c r="H106">
-        <v>0.9984302600000001</v>
+        <v>0.9986639900000002</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="1">
-        <v>46168</v>
+        <v>46160</v>
       </c>
       <c r="B107" t="s">
         <v>14</v>
       </c>
       <c r="C107">
-        <v>35.4820130509417</v>
+        <v>34.83995455757461</v>
       </c>
       <c r="D107">
-        <v>19.20292041814603</v>
+        <v>18.02301281718857</v>
       </c>
       <c r="E107">
-        <v>0.9995448900000001</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="F107">
-        <v>0.9995448900000001</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="G107">
-        <v>0.2553172934903569</v>
+        <v>0.1850932291737926</v>
       </c>
       <c r="H107">
-        <v>0.9984302600000001</v>
+        <v>0.99857724</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="1">
-        <v>46169</v>
+        <v>46161</v>
       </c>
       <c r="B108" t="s">
         <v>14</v>
       </c>
       <c r="C108">
-        <v>35.71913468603401</v>
+        <v>34.45479308705605</v>
       </c>
       <c r="D108">
-        <v>18.96318693998171</v>
+        <v>18.09576834566068</v>
       </c>
       <c r="E108">
-        <v>0.99955466</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="F108">
-        <v>0.99955466</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="G108">
-        <v>0.2536413280520453</v>
+        <v>0.1784731209386736</v>
       </c>
       <c r="H108">
-        <v>0.9984700500000001</v>
+        <v>0.9985337599999999</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="1">
-        <v>46170</v>
+        <v>46162</v>
       </c>
       <c r="B109" t="s">
         <v>14</v>
       </c>
       <c r="C109">
-        <v>35.76226417354731</v>
+        <v>34.96336277390787</v>
       </c>
       <c r="D109">
-        <v>18.89050847207122</v>
+        <v>18.34938420029253</v>
       </c>
       <c r="E109">
-        <v>0.9995525399999999</v>
+        <v>0.99963413</v>
       </c>
       <c r="F109">
-        <v>0.9995525399999999</v>
+        <v>0.99963413</v>
       </c>
       <c r="G109">
-        <v>0.2580826940041561</v>
+        <v>0.2009313391215752</v>
       </c>
       <c r="H109">
-        <v>0.99847732</v>
+        <v>0.99848777</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="1">
-        <v>46171</v>
+        <v>46163</v>
       </c>
       <c r="B110" t="s">
         <v>14</v>
       </c>
       <c r="C110">
-        <v>35.84309020154227</v>
+        <v>34.44616924817128</v>
       </c>
       <c r="D110">
-        <v>19.06511612333149</v>
+        <v>18.60085625074367</v>
       </c>
       <c r="E110">
-        <v>0.9995533299999999</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="F110">
-        <v>0.9995533299999999</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="G110">
-        <v>0.2619374017254759</v>
+        <v>0.2124957180214682</v>
       </c>
       <c r="H110">
-        <v>0.99849382</v>
+        <v>0.9985085200000001</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="1">
-        <v>46174</v>
+        <v>46164</v>
       </c>
       <c r="B111" t="s">
         <v>14</v>
       </c>
       <c r="C111">
-        <v>36.27022125574057</v>
+        <v>34.62137220937314</v>
       </c>
       <c r="D111">
-        <v>19.32711369104533</v>
+        <v>18.28780484745949</v>
       </c>
       <c r="E111">
-        <v>0.9995550400000001</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="F111">
-        <v>0.9995550400000001</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="G111">
-        <v>0.2764348160433892</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H111">
-        <v>0.9985177199999999</v>
+        <v>0.9932939299999999</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="1">
-        <v>46175</v>
+        <v>46167</v>
       </c>
       <c r="B112" t="s">
         <v>14</v>
       </c>
       <c r="C112">
-        <v>36.57133692946976</v>
+        <v>34.6540695486741</v>
       </c>
       <c r="D112">
-        <v>19.33857330565742</v>
+        <v>18.36409048915342</v>
       </c>
       <c r="E112">
-        <v>0.9994989200000002</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="F112">
-        <v>0.9994989200000002</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="G112">
-        <v>0.2931947261624381</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H112">
-        <v>0.9984577800000001</v>
+        <v>0.9984302600000001</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="1">
-        <v>46153</v>
+        <v>46168</v>
       </c>
       <c r="B113" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C113">
-        <v>28.12253390077671</v>
+        <v>35.4820130509417</v>
       </c>
       <c r="D113">
-        <v>23.58699683751922</v>
+        <v>19.20292041814603</v>
       </c>
       <c r="E113">
-        <v>0.9997295369999999</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="F113">
-        <v>0.9997295369999999</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="G113">
-        <v>0.03368732240295347</v>
+        <v>0.2553172934903569</v>
       </c>
       <c r="H113">
-        <v>0.9997295369999999</v>
+        <v>0.9984302600000001</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="1">
-        <v>46154</v>
+        <v>46169</v>
       </c>
       <c r="B114" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C114">
-        <v>28.17715727830483</v>
+        <v>35.71913468603401</v>
       </c>
       <c r="D114">
-        <v>23.63894513078866</v>
+        <v>18.96318693998171</v>
       </c>
       <c r="E114">
-        <v>1.000319473</v>
+        <v>0.99955466</v>
       </c>
       <c r="F114">
-        <v>1.000319473</v>
+        <v>0.99955466</v>
       </c>
       <c r="G114">
-        <v>0.03515547182056333</v>
+        <v>0.2536413280520453</v>
       </c>
       <c r="H114">
-        <v>1.000319473</v>
+        <v>0.9984700500000001</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="1">
-        <v>46155</v>
+        <v>46170</v>
       </c>
       <c r="B115" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C115">
-        <v>28.59002627414054</v>
+        <v>35.76226417354731</v>
       </c>
       <c r="D115">
-        <v>23.96230704059692</v>
+        <v>18.89050847207122</v>
       </c>
       <c r="E115">
-        <v>0.9999999989999999</v>
+        <v>0.9995525399999999</v>
       </c>
       <c r="F115">
-        <v>0.9999999989999999</v>
+        <v>0.9995525399999999</v>
       </c>
       <c r="G115">
-        <v>0.05179637495949674</v>
+        <v>0.2580826940041561</v>
       </c>
       <c r="H115">
-        <v>0.9999999989999999</v>
+        <v>0.99847732</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="1">
-        <v>46156</v>
+        <v>46171</v>
       </c>
       <c r="B116" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C116">
-        <v>28.56217859389523</v>
+        <v>35.84309020154227</v>
       </c>
       <c r="D116">
-        <v>23.9411987302529</v>
+        <v>19.06511612333149</v>
       </c>
       <c r="E116">
-        <v>1</v>
+        <v>0.9995533299999999</v>
       </c>
       <c r="F116">
-        <v>1</v>
+        <v>0.9995533299999999</v>
       </c>
       <c r="G116">
-        <v>0.04837024516756849</v>
+        <v>0.2619374017254759</v>
       </c>
       <c r="H116">
-        <v>1</v>
+        <v>0.99849382</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="1">
-        <v>46157</v>
+        <v>46174</v>
       </c>
       <c r="B117" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C117">
-        <v>28.57618675936338</v>
+        <v>36.27022125574057</v>
       </c>
       <c r="D117">
-        <v>23.9576220541054</v>
+        <v>19.32711369104533</v>
       </c>
       <c r="E117">
-        <v>0.999503249</v>
+        <v>0.9995550400000001</v>
       </c>
       <c r="F117">
-        <v>0.999503249</v>
+        <v>0.9995550400000001</v>
       </c>
       <c r="G117">
-        <v>0.04983868243960732</v>
+        <v>0.2764348160433892</v>
       </c>
       <c r="H117">
-        <v>0.999503249</v>
+        <v>0.9985177199999999</v>
       </c>
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="1">
-        <v>46160</v>
+        <v>46175</v>
       </c>
       <c r="B118" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C118">
-        <v>28.68951918518517</v>
+        <v>36.57133692946976</v>
       </c>
       <c r="D118">
-        <v>24.06134728453882</v>
+        <v>19.33857330565742</v>
       </c>
       <c r="E118">
-        <v>0.999503249</v>
+        <v>0.9994989200000002</v>
       </c>
       <c r="F118">
-        <v>0.999503249</v>
+        <v>0.9994989200000002</v>
       </c>
       <c r="G118">
-        <v>0.04983868243960732</v>
+        <v>0.2931947261624381</v>
       </c>
       <c r="H118">
-        <v>0.999503249</v>
+        <v>0.9984577800000001</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="1">
-        <v>46161</v>
+        <v>46176</v>
       </c>
       <c r="B119" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C119">
-        <v>28.31167386654059</v>
+        <v>36.8289666508657</v>
       </c>
       <c r="D119">
-        <v>23.75157719455474</v>
+        <v>19.43137154505686</v>
       </c>
       <c r="E119">
-        <v>1.000177331</v>
+        <v>0.9994838199999998</v>
       </c>
       <c r="F119">
-        <v>1.000177331</v>
+        <v>0.9994838199999998</v>
       </c>
       <c r="G119">
-        <v>0.04053938625111919</v>
+        <v>0.2996471994933361</v>
       </c>
       <c r="H119">
-        <v>1.000177331</v>
+        <v>0.9984549499999998</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="1">
-        <v>46162</v>
+        <v>46153</v>
       </c>
       <c r="B120" t="s">
         <v>15</v>
       </c>
       <c r="C120">
-        <v>28.57911382310097</v>
+        <v>28.12253390077671</v>
       </c>
       <c r="D120">
-        <v>23.89431741541233</v>
+        <v>23.58699683751922</v>
       </c>
       <c r="E120">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="F120">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="G120">
-        <v>0.04690190590044785</v>
+        <v>0.03368732240295347</v>
       </c>
       <c r="H120">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="1">
-        <v>46163</v>
+        <v>46154</v>
       </c>
       <c r="B121" t="s">
         <v>15</v>
       </c>
       <c r="C121">
-        <v>28.55785065378643</v>
+        <v>28.17715727830483</v>
       </c>
       <c r="D121">
-        <v>24.04274714970193</v>
+        <v>23.63894513078866</v>
       </c>
       <c r="E121">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="F121">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="G121">
-        <v>0.05228572319419666</v>
+        <v>0.03515547182056333</v>
       </c>
       <c r="H121">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="1">
-        <v>46164</v>
+        <v>46155</v>
       </c>
       <c r="B122" t="s">
         <v>15</v>
       </c>
       <c r="C122">
-        <v>28.50194638163107</v>
+        <v>28.59002627414054</v>
       </c>
       <c r="D122">
-        <v>23.99272397156045</v>
+        <v>23.96230704059692</v>
       </c>
       <c r="E122">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F122">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G122">
-        <v>0.04934923597154284</v>
+        <v>0.05179637495949674</v>
       </c>
       <c r="H122">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="1">
-        <v>46167</v>
+        <v>46156</v>
       </c>
       <c r="B123" t="s">
         <v>15</v>
       </c>
       <c r="C123">
-        <v>28.55106858744498</v>
+        <v>28.56217859389523</v>
       </c>
       <c r="D123">
-        <v>23.9768329565351</v>
+        <v>23.9411987302529</v>
       </c>
       <c r="E123">
         <v>1</v>
@@ -3595,7 +3595,7 @@
         <v>1</v>
       </c>
       <c r="G123">
-        <v>0.05571185335164408</v>
+        <v>0.04837024516756849</v>
       </c>
       <c r="H123">
         <v>1</v>
@@ -3603,600 +3603,834 @@
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="1">
-        <v>46168</v>
+        <v>46157</v>
       </c>
       <c r="B124" t="s">
         <v>15</v>
       </c>
       <c r="C124">
-        <v>28.54681541456266</v>
+        <v>28.57618675936338</v>
       </c>
       <c r="D124">
-        <v>23.97386168967948</v>
+        <v>23.9576220541054</v>
       </c>
       <c r="E124">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="F124">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="G124">
-        <v>0.04837034303541388</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H124">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="1">
-        <v>46169</v>
+        <v>46160</v>
       </c>
       <c r="B125" t="s">
         <v>15</v>
       </c>
       <c r="C125">
-        <v>28.83672936868491</v>
+        <v>28.68951918518517</v>
       </c>
       <c r="D125">
-        <v>24.203511281145</v>
+        <v>24.06134728453882</v>
       </c>
       <c r="E125">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="F125">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="G125">
-        <v>0.05962723282507953</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H125">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" s="1">
-        <v>46170</v>
+        <v>46161</v>
       </c>
       <c r="B126" t="s">
         <v>15</v>
       </c>
       <c r="C126">
-        <v>28.88109630394224</v>
+        <v>28.31167386654059</v>
       </c>
       <c r="D126">
-        <v>24.34085451035401</v>
+        <v>23.75157719455474</v>
       </c>
       <c r="E126">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
       <c r="F126">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
       <c r="G126">
-        <v>0.06647938938594877</v>
+        <v>0.04053938625111919</v>
       </c>
       <c r="H126">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" s="1">
-        <v>46171</v>
+        <v>46162</v>
       </c>
       <c r="B127" t="s">
         <v>15</v>
       </c>
       <c r="C127">
-        <v>28.92588622185229</v>
+        <v>28.57911382310097</v>
       </c>
       <c r="D127">
-        <v>24.37463012178961</v>
+        <v>23.89431741541233</v>
       </c>
       <c r="E127">
-        <v>0.9999999989999999</v>
+        <v>0.999503734</v>
       </c>
       <c r="F127">
-        <v>0.9999999989999999</v>
+        <v>0.999503734</v>
       </c>
       <c r="G127">
-        <v>0.0669687424559624</v>
+        <v>0.04690190590044785</v>
       </c>
       <c r="H127">
-        <v>0.9999999989999999</v>
+        <v>0.999503734</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="1">
-        <v>46174</v>
+        <v>46163</v>
       </c>
       <c r="B128" t="s">
         <v>15</v>
       </c>
       <c r="C128">
-        <v>28.479823472488</v>
+        <v>28.55785065378643</v>
       </c>
       <c r="D128">
-        <v>23.940843604634</v>
+        <v>24.04274714970193</v>
       </c>
       <c r="E128">
-        <v>0.9999999999999999</v>
+        <v>1.000229282</v>
       </c>
       <c r="F128">
-        <v>0.9999999999999999</v>
+        <v>1.000229282</v>
       </c>
       <c r="G128">
-        <v>0.05385076946675693</v>
+        <v>0.05228572319419666</v>
       </c>
       <c r="H128">
-        <v>0.9999999999999999</v>
+        <v>1.000229282</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="1">
-        <v>46175</v>
+        <v>46164</v>
       </c>
       <c r="B129" t="s">
         <v>15</v>
       </c>
       <c r="C129">
-        <v>28.11501250979268</v>
+        <v>28.50194638163107</v>
       </c>
       <c r="D129">
-        <v>23.53470929078268</v>
+        <v>23.99272397156045</v>
       </c>
       <c r="E129">
-        <v>0.9999999989999999</v>
+        <v>1</v>
       </c>
       <c r="F129">
-        <v>0.9999999989999999</v>
+        <v>1</v>
       </c>
       <c r="G129">
-        <v>0.03476107722835287</v>
+        <v>0.04934923597154284</v>
       </c>
       <c r="H129">
-        <v>0.9999999989999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" s="1">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="B130" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C130">
-        <v>40.68830633303975</v>
+        <v>28.55106858744498</v>
       </c>
       <c r="D130">
-        <v>21.50431773660198</v>
+        <v>23.9768329565351</v>
       </c>
       <c r="E130">
-        <v>0.99909852</v>
+        <v>1</v>
       </c>
       <c r="F130">
-        <v>0.99909852</v>
+        <v>1</v>
       </c>
       <c r="G130">
-        <v>0.2342423866086769</v>
+        <v>0.05571185335164408</v>
       </c>
       <c r="H130">
-        <v>0.9974930900000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" s="1">
-        <v>46154</v>
+        <v>46168</v>
       </c>
       <c r="B131" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C131">
-        <v>40.32854894972581</v>
+        <v>28.54681541456266</v>
       </c>
       <c r="D131">
-        <v>21.09133998298594</v>
+        <v>23.97386168967948</v>
       </c>
       <c r="E131">
-        <v>0.9990972199999999</v>
+        <v>1</v>
       </c>
       <c r="F131">
-        <v>0.9990972199999999</v>
+        <v>1</v>
       </c>
       <c r="G131">
-        <v>0.2156468205051487</v>
+        <v>0.04837034303541388</v>
       </c>
       <c r="H131">
-        <v>0.99752223</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="1">
-        <v>46155</v>
+        <v>46169</v>
       </c>
       <c r="B132" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C132">
-        <v>40.47987921095815</v>
+        <v>28.83672936868491</v>
       </c>
       <c r="D132">
-        <v>21.35995364434454</v>
+        <v>24.203511281145</v>
       </c>
       <c r="E132">
-        <v>0.9991780100000001</v>
+        <v>1</v>
       </c>
       <c r="F132">
-        <v>0.9991780100000001</v>
+        <v>1</v>
       </c>
       <c r="G132">
-        <v>0.2270956128473374</v>
+        <v>0.05962723282507953</v>
       </c>
       <c r="H132">
-        <v>0.9975825700000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="1">
-        <v>46156</v>
+        <v>46170</v>
       </c>
       <c r="B133" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C133">
-        <v>41.20436574895244</v>
+        <v>28.88109630394224</v>
       </c>
       <c r="D133">
-        <v>21.48149674387778</v>
+        <v>24.34085451035401</v>
       </c>
       <c r="E133">
-        <v>0.9991793299999999</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F133">
-        <v>0.9991793299999999</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G133">
-        <v>0.2454829228401052</v>
+        <v>0.06647938938594877</v>
       </c>
       <c r="H133">
-        <v>0.99754722</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="1">
-        <v>46157</v>
+        <v>46171</v>
       </c>
       <c r="B134" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C134">
-        <v>40.80613062958688</v>
+        <v>28.92588622185229</v>
       </c>
       <c r="D134">
-        <v>21.08912555803936</v>
+        <v>24.37463012178961</v>
       </c>
       <c r="E134">
-        <v>0.9991790600000001</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F134">
-        <v>0.9991790600000001</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G134">
-        <v>0.2230017445022556</v>
+        <v>0.0669687424559624</v>
       </c>
       <c r="H134">
-        <v>0.9975824700000002</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="1">
-        <v>46160</v>
+        <v>46174</v>
       </c>
       <c r="B135" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C135">
-        <v>40.11672876026724</v>
+        <v>28.479823472488</v>
       </c>
       <c r="D135">
-        <v>20.79541439916316</v>
+        <v>23.940843604634</v>
       </c>
       <c r="E135">
-        <v>0.999152</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F135">
-        <v>0.999152</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G135">
-        <v>0.2098184021536666</v>
+        <v>0.05385076946675693</v>
       </c>
       <c r="H135">
-        <v>0.9975007899999999</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="136" spans="1:8">
       <c r="A136" s="1">
-        <v>46161</v>
+        <v>46175</v>
       </c>
       <c r="B136" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C136">
-        <v>39.69086941528401</v>
+        <v>28.11501250979268</v>
       </c>
       <c r="D136">
-        <v>20.74924328599426</v>
+        <v>23.53470929078268</v>
       </c>
       <c r="E136">
-        <v>0.99914989</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F136">
-        <v>0.99914989</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G136">
-        <v>0.2020471776850241</v>
+        <v>0.03476107722835287</v>
       </c>
       <c r="H136">
-        <v>0.9974417</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="1">
-        <v>46162</v>
+        <v>46176</v>
       </c>
       <c r="B137" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C137">
-        <v>40.37836787855562</v>
+        <v>28.0115884668485</v>
       </c>
       <c r="D137">
-        <v>21.11271132314188</v>
+        <v>23.38620815625822</v>
       </c>
       <c r="E137">
-        <v>0.99915058</v>
+        <v>0.9993115890000001</v>
       </c>
       <c r="F137">
-        <v>0.99915058</v>
+        <v>0.9993115890000001</v>
       </c>
       <c r="G137">
-        <v>0.2291077670847563</v>
+        <v>0.02105569185214828</v>
       </c>
       <c r="H137">
-        <v>0.9974415600000001</v>
+        <v>0.9993115890000001</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="1">
-        <v>46163</v>
+        <v>46153</v>
       </c>
       <c r="B138" t="s">
         <v>16</v>
       </c>
       <c r="C138">
-        <v>38.9123066967842</v>
+        <v>40.68830633303975</v>
       </c>
       <c r="D138">
-        <v>21.28910644207464</v>
+        <v>21.50431773660198</v>
       </c>
       <c r="E138">
-        <v>0.9989350699999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="F138">
-        <v>0.9989350699999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="G138">
-        <v>0.2392382040170877</v>
+        <v>0.2342423866086769</v>
       </c>
       <c r="H138">
-        <v>0.99726191</v>
+        <v>0.9974930900000001</v>
       </c>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="1">
-        <v>46164</v>
+        <v>46154</v>
       </c>
       <c r="B139" t="s">
         <v>16</v>
       </c>
       <c r="C139">
-        <v>39.43913909150694</v>
+        <v>40.32854894972581</v>
       </c>
       <c r="D139">
-        <v>21.05297617141148</v>
+        <v>21.09133998298594</v>
       </c>
       <c r="E139">
-        <v>0.999144</v>
+        <v>0.9990972199999999</v>
       </c>
       <c r="F139">
-        <v>0.999144</v>
+        <v>0.9990972199999999</v>
       </c>
       <c r="G139">
-        <v>0.2516582935428642</v>
+        <v>0.2156468205051487</v>
       </c>
       <c r="H139">
-        <v>0.9974678400000001</v>
+        <v>0.99752223</v>
       </c>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="1">
-        <v>46167</v>
+        <v>46155</v>
       </c>
       <c r="B140" t="s">
         <v>16</v>
       </c>
       <c r="C140">
-        <v>39.45782844313628</v>
+        <v>40.47987921095815</v>
       </c>
       <c r="D140">
-        <v>21.0518901572272</v>
+        <v>21.35995364434454</v>
       </c>
       <c r="E140">
-        <v>0.999144</v>
+        <v>0.9991780100000001</v>
       </c>
       <c r="F140">
-        <v>0.999144</v>
+        <v>0.9991780100000001</v>
       </c>
       <c r="G140">
-        <v>0.2516582935428642</v>
+        <v>0.2270956128473374</v>
       </c>
       <c r="H140">
-        <v>0.9974678400000001</v>
+        <v>0.9975825700000001</v>
       </c>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="1">
-        <v>46168</v>
+        <v>46156</v>
       </c>
       <c r="B141" t="s">
         <v>16</v>
       </c>
       <c r="C141">
-        <v>40.20219297984542</v>
+        <v>41.20436574895244</v>
       </c>
       <c r="D141">
-        <v>21.93106024403281</v>
+        <v>21.48149674387778</v>
       </c>
       <c r="E141">
-        <v>0.9991421799999999</v>
+        <v>0.9991793299999999</v>
       </c>
       <c r="F141">
-        <v>0.9991421799999999</v>
+        <v>0.9991793299999999</v>
       </c>
       <c r="G141">
-        <v>0.2846167552893293</v>
+        <v>0.2454829228401052</v>
       </c>
       <c r="H141">
-        <v>0.9974609800000001</v>
+        <v>0.99754722</v>
       </c>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="1">
-        <v>46169</v>
+        <v>46157</v>
       </c>
       <c r="B142" t="s">
         <v>16</v>
       </c>
       <c r="C142">
-        <v>40.34993865302093</v>
+        <v>40.80613062958688</v>
       </c>
       <c r="D142">
-        <v>21.65366031776487</v>
+        <v>21.08912555803936</v>
       </c>
       <c r="E142">
-        <v>0.9991434600000001</v>
+        <v>0.9991790600000001</v>
       </c>
       <c r="F142">
-        <v>0.9991434600000001</v>
+        <v>0.9991790600000001</v>
       </c>
       <c r="G142">
-        <v>0.2796902860011767</v>
+        <v>0.2230017445022556</v>
       </c>
       <c r="H142">
-        <v>0.9991434600000001</v>
+        <v>0.9975824700000002</v>
       </c>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="1">
-        <v>46170</v>
+        <v>46160</v>
       </c>
       <c r="B143" t="s">
         <v>16</v>
       </c>
       <c r="C143">
-        <v>40.5850485390846</v>
+        <v>40.11672876026724</v>
       </c>
       <c r="D143">
-        <v>21.75450977746074</v>
+        <v>20.79541439916316</v>
       </c>
       <c r="E143">
-        <v>0.99914592</v>
+        <v>0.999152</v>
       </c>
       <c r="F143">
-        <v>0.99914592</v>
+        <v>0.999152</v>
       </c>
       <c r="G143">
-        <v>0.2964818481030536</v>
+        <v>0.2098184021536666</v>
       </c>
       <c r="H143">
-        <v>0.99914592</v>
+        <v>0.9975007899999999</v>
       </c>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="1">
-        <v>46171</v>
+        <v>46161</v>
       </c>
       <c r="B144" t="s">
         <v>16</v>
       </c>
       <c r="C144">
-        <v>41.86785805184477</v>
+        <v>39.69086941528401</v>
       </c>
       <c r="D144">
-        <v>22.33589392797469</v>
+        <v>20.74924328599426</v>
       </c>
       <c r="E144">
-        <v>0.9991336999999999</v>
+        <v>0.99914989</v>
       </c>
       <c r="F144">
-        <v>0.9991336999999999</v>
+        <v>0.99914989</v>
       </c>
       <c r="G144">
-        <v>0.3254158954996882</v>
+        <v>0.2020471776850241</v>
       </c>
       <c r="H144">
-        <v>0.9991336999999999</v>
+        <v>0.9974417</v>
       </c>
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="1">
-        <v>46174</v>
+        <v>46162</v>
       </c>
       <c r="B145" t="s">
         <v>16</v>
       </c>
       <c r="C145">
-        <v>42.82932322850974</v>
+        <v>40.37836787855562</v>
       </c>
       <c r="D145">
-        <v>22.98998911430362</v>
+        <v>21.11271132314188</v>
       </c>
       <c r="E145">
-        <v>0.99914238</v>
+        <v>0.99915058</v>
       </c>
       <c r="F145">
-        <v>0.99914238</v>
+        <v>0.99915058</v>
       </c>
       <c r="G145">
-        <v>0.3583049032509023</v>
+        <v>0.2291077670847563</v>
       </c>
       <c r="H145">
-        <v>0.99914238</v>
+        <v>0.9974415600000001</v>
       </c>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="1">
-        <v>46175</v>
+        <v>46163</v>
       </c>
       <c r="B146" t="s">
         <v>16</v>
       </c>
       <c r="C146">
+        <v>38.9123066967842</v>
+      </c>
+      <c r="D146">
+        <v>21.28910644207464</v>
+      </c>
+      <c r="E146">
+        <v>0.9989350699999999</v>
+      </c>
+      <c r="F146">
+        <v>0.9989350699999999</v>
+      </c>
+      <c r="G146">
+        <v>0.2392382040170877</v>
+      </c>
+      <c r="H146">
+        <v>0.99726191</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
+      <c r="A147" s="1">
+        <v>46164</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147">
+        <v>39.43913909150694</v>
+      </c>
+      <c r="D147">
+        <v>21.05297617141148</v>
+      </c>
+      <c r="E147">
+        <v>0.999144</v>
+      </c>
+      <c r="F147">
+        <v>0.999144</v>
+      </c>
+      <c r="G147">
+        <v>0.2516582935428642</v>
+      </c>
+      <c r="H147">
+        <v>0.9974678400000001</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148">
+        <v>39.45782844313628</v>
+      </c>
+      <c r="D148">
+        <v>21.0518901572272</v>
+      </c>
+      <c r="E148">
+        <v>0.999144</v>
+      </c>
+      <c r="F148">
+        <v>0.999144</v>
+      </c>
+      <c r="G148">
+        <v>0.2516582935428642</v>
+      </c>
+      <c r="H148">
+        <v>0.9974678400000001</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
+      <c r="A149" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149">
+        <v>40.20219297984542</v>
+      </c>
+      <c r="D149">
+        <v>21.93106024403281</v>
+      </c>
+      <c r="E149">
+        <v>0.9991421799999999</v>
+      </c>
+      <c r="F149">
+        <v>0.9991421799999999</v>
+      </c>
+      <c r="G149">
+        <v>0.2846167552893293</v>
+      </c>
+      <c r="H149">
+        <v>0.9974609800000001</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
+      <c r="A150" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150">
+        <v>40.34993865302093</v>
+      </c>
+      <c r="D150">
+        <v>21.65366031776487</v>
+      </c>
+      <c r="E150">
+        <v>0.9991434600000001</v>
+      </c>
+      <c r="F150">
+        <v>0.9991434600000001</v>
+      </c>
+      <c r="G150">
+        <v>0.2796902860011767</v>
+      </c>
+      <c r="H150">
+        <v>0.9991434600000001</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
+      <c r="A151" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151">
+        <v>40.5850485390846</v>
+      </c>
+      <c r="D151">
+        <v>21.75450977746074</v>
+      </c>
+      <c r="E151">
+        <v>0.99914592</v>
+      </c>
+      <c r="F151">
+        <v>0.99914592</v>
+      </c>
+      <c r="G151">
+        <v>0.2964818481030536</v>
+      </c>
+      <c r="H151">
+        <v>0.99914592</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8">
+      <c r="A152" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152">
+        <v>41.86785805184477</v>
+      </c>
+      <c r="D152">
+        <v>22.33589392797469</v>
+      </c>
+      <c r="E152">
+        <v>0.9991336999999999</v>
+      </c>
+      <c r="F152">
+        <v>0.9991336999999999</v>
+      </c>
+      <c r="G152">
+        <v>0.3254158954996882</v>
+      </c>
+      <c r="H152">
+        <v>0.9991336999999999</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8">
+      <c r="A153" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153">
+        <v>42.82932322850974</v>
+      </c>
+      <c r="D153">
+        <v>22.98998911430362</v>
+      </c>
+      <c r="E153">
+        <v>0.99914238</v>
+      </c>
+      <c r="F153">
+        <v>0.99914238</v>
+      </c>
+      <c r="G153">
+        <v>0.3583049032509023</v>
+      </c>
+      <c r="H153">
+        <v>0.99914238</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8">
+      <c r="A154" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154">
         <v>43.11872937189534</v>
       </c>
-      <c r="D146">
+      <c r="D154">
         <v>22.90628380907704</v>
       </c>
-      <c r="E146">
+      <c r="E154">
         <v>0.9990972800000002</v>
       </c>
-      <c r="F146">
+      <c r="F154">
         <v>0.9990972800000002</v>
       </c>
-      <c r="G146">
+      <c r="G154">
         <v>0.3753046155885469</v>
       </c>
-      <c r="H146">
+      <c r="H154">
         <v>0.9990972800000002</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8">
+      <c r="A155" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155">
+        <v>42.86143001679577</v>
+      </c>
+      <c r="D155">
+        <v>22.72053012591219</v>
+      </c>
+      <c r="E155">
+        <v>0.9990984299999999</v>
+      </c>
+      <c r="F155">
+        <v>0.9990984299999999</v>
+      </c>
+      <c r="G155">
+        <v>0.3615660647779204</v>
+      </c>
+      <c r="H155">
+        <v>0.9990984299999999</v>
       </c>
     </row>
   </sheetData>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="17">
   <si>
     <t>Date</t>
   </si>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H155"/>
+  <dimension ref="A1:H164"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -717,42 +717,42 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1">
-        <v>46153</v>
+        <v>46177</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13">
-        <v>53.14833755912058</v>
+        <v>26.36483813478422</v>
       </c>
       <c r="D13">
-        <v>25.84885448407537</v>
+        <v>17.57877627082322</v>
       </c>
       <c r="E13">
-        <v>0.9262</v>
+        <v>0.8638999999999999</v>
       </c>
       <c r="F13">
-        <v>0.9262</v>
+        <v>0.8638999999999999</v>
       </c>
       <c r="G13">
-        <v>0.3839084462043663</v>
+        <v>0.6597119451886302</v>
       </c>
       <c r="H13">
-        <v>0.9262</v>
+        <v>0.9166</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
       </c>
       <c r="C14">
-        <v>51.82921169635205</v>
+        <v>53.14833755912058</v>
       </c>
       <c r="D14">
-        <v>25.32805827181975</v>
+        <v>25.84885448407537</v>
       </c>
       <c r="E14">
         <v>0.9262</v>
@@ -761,7 +761,7 @@
         <v>0.9262</v>
       </c>
       <c r="G14">
-        <v>0.3568580281685669</v>
+        <v>0.3839084462043663</v>
       </c>
       <c r="H14">
         <v>0.9262</v>
@@ -769,120 +769,120 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
       </c>
       <c r="C15">
-        <v>52.28471716753184</v>
+        <v>51.82921169635205</v>
       </c>
       <c r="D15">
-        <v>25.54525144150689</v>
+        <v>25.32805827181975</v>
       </c>
       <c r="E15">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="F15">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="G15">
-        <v>0.378012896547947</v>
+        <v>0.3568580281685669</v>
       </c>
       <c r="H15">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
       </c>
       <c r="C16">
-        <v>53.87287273813902</v>
+        <v>52.28471716753184</v>
       </c>
       <c r="D16">
-        <v>26.32154226438612</v>
+        <v>25.54525144150689</v>
       </c>
       <c r="E16">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="F16">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="G16">
-        <v>0.4166811087612758</v>
+        <v>0.378012896547947</v>
       </c>
       <c r="H16">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
       </c>
       <c r="C17">
-        <v>52.18747148214074</v>
+        <v>53.87287273813902</v>
       </c>
       <c r="D17">
-        <v>25.13616059644496</v>
+        <v>26.32154226438612</v>
       </c>
       <c r="E17">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="F17">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="G17">
-        <v>0.3627535778249862</v>
+        <v>0.4166811087612758</v>
       </c>
       <c r="H17">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="B18" t="s">
         <v>9</v>
       </c>
       <c r="C18">
-        <v>50.72035274995172</v>
+        <v>52.18747148214074</v>
       </c>
       <c r="D18">
-        <v>24.61756040386634</v>
+        <v>25.13616059644496</v>
       </c>
       <c r="E18">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="F18">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="G18">
         <v>0.3627535778249862</v>
       </c>
       <c r="H18">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="B19" t="s">
         <v>9</v>
       </c>
       <c r="C19">
-        <v>50.11981086673613</v>
+        <v>50.72035274995172</v>
       </c>
       <c r="D19">
-        <v>24.13061679021705</v>
+        <v>24.61756040386634</v>
       </c>
       <c r="E19">
         <v>0.9259000000000001</v>
@@ -891,7 +891,7 @@
         <v>0.9259000000000001</v>
       </c>
       <c r="G19">
-        <v>0.3258193430227221</v>
+        <v>0.3627535778249862</v>
       </c>
       <c r="H19">
         <v>0.9259000000000001</v>
@@ -899,120 +899,120 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="B20" t="s">
         <v>9</v>
       </c>
       <c r="C20">
-        <v>51.74165648409151</v>
+        <v>50.11981086673613</v>
       </c>
       <c r="D20">
-        <v>24.98091384114761</v>
+        <v>24.13061679021705</v>
       </c>
       <c r="E20">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="F20">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="G20">
-        <v>0.3818277262286871</v>
+        <v>0.3258193430227221</v>
       </c>
       <c r="H20">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="B21" t="s">
         <v>9</v>
       </c>
       <c r="C21">
-        <v>49.13455894175823</v>
+        <v>51.74165648409151</v>
       </c>
       <c r="D21">
-        <v>25.30005057653127</v>
+        <v>24.98091384114761</v>
       </c>
       <c r="E21">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="F21">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="G21">
-        <v>0.4028091571787618</v>
+        <v>0.3818277262286871</v>
       </c>
       <c r="H21">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="B22" t="s">
         <v>9</v>
       </c>
       <c r="C22">
-        <v>49.57776597479297</v>
+        <v>49.13455894175823</v>
       </c>
       <c r="D22">
-        <v>25.04906725563518</v>
+        <v>25.30005057653127</v>
       </c>
       <c r="E22">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="F22">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="G22">
-        <v>0.4256980029692063</v>
+        <v>0.4028091571787618</v>
       </c>
       <c r="H22">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="B23" t="s">
         <v>9</v>
       </c>
       <c r="C23">
-        <v>49.71239596645896</v>
+        <v>49.57776597479297</v>
       </c>
       <c r="D23">
-        <v>25.18778610744295</v>
+        <v>25.04906725563518</v>
       </c>
       <c r="E23">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="F23">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="G23">
-        <v>0.4525749835757003</v>
+        <v>0.4256980029692063</v>
       </c>
       <c r="H23">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="B24" t="s">
         <v>9</v>
       </c>
       <c r="C24">
-        <v>50.77166277510776</v>
+        <v>49.71239596645896</v>
       </c>
       <c r="D24">
-        <v>25.7431782858765</v>
+        <v>25.18778610744295</v>
       </c>
       <c r="E24">
         <v>0.9231999999999999</v>
@@ -1021,7 +1021,7 @@
         <v>0.9231999999999999</v>
       </c>
       <c r="G24">
-        <v>0.4700884597036457</v>
+        <v>0.4525749835757003</v>
       </c>
       <c r="H24">
         <v>0.9231999999999999</v>
@@ -1029,120 +1029,120 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1">
-        <v>46169</v>
+        <v>46168</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
       </c>
       <c r="C25">
-        <v>50.57689164833899</v>
+        <v>50.77166277510776</v>
       </c>
       <c r="D25">
-        <v>25.70244067238947</v>
+        <v>25.7431782858765</v>
       </c>
       <c r="E25">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="F25">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="G25">
-        <v>0.4518814984464716</v>
+        <v>0.4700884597036457</v>
       </c>
       <c r="H25">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
       </c>
       <c r="C26">
-        <v>50.80027854822009</v>
+        <v>50.57689164833899</v>
       </c>
       <c r="D26">
-        <v>25.90068415792015</v>
+        <v>25.70244067238947</v>
       </c>
       <c r="E26">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
       <c r="F26">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
       <c r="G26">
-        <v>0.4699150222743402</v>
+        <v>0.4518814984464716</v>
       </c>
       <c r="H26">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="B27" t="s">
         <v>9</v>
       </c>
       <c r="C27">
-        <v>51.44563447241545</v>
+        <v>50.80027854822009</v>
       </c>
       <c r="D27">
-        <v>26.0970978996374</v>
+        <v>25.90068415792015</v>
       </c>
       <c r="E27">
-        <v>0.9246</v>
+        <v>0.9231</v>
       </c>
       <c r="F27">
-        <v>0.9246</v>
+        <v>0.9231</v>
       </c>
       <c r="G27">
-        <v>0.4791053539115764</v>
+        <v>0.4699150222743402</v>
       </c>
       <c r="H27">
-        <v>0.9246</v>
+        <v>0.9231</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1">
-        <v>46174</v>
+        <v>46171</v>
       </c>
       <c r="B28" t="s">
         <v>9</v>
       </c>
       <c r="C28">
-        <v>53.05792083471825</v>
+        <v>51.44563447241545</v>
       </c>
       <c r="D28">
-        <v>26.86242981002239</v>
+        <v>26.0970978996374</v>
       </c>
       <c r="E28">
-        <v>0.9254999999999999</v>
+        <v>0.9246</v>
       </c>
       <c r="F28">
-        <v>0.9254999999999999</v>
+        <v>0.9246</v>
       </c>
       <c r="G28">
-        <v>0.5306051577195796</v>
+        <v>0.4791053539115764</v>
       </c>
       <c r="H28">
-        <v>0.9254999999999999</v>
+        <v>0.9246</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="B29" t="s">
         <v>9</v>
       </c>
       <c r="C29">
-        <v>54.38946369031042</v>
+        <v>53.05792083471825</v>
       </c>
       <c r="D29">
-        <v>27.57160808325711</v>
+        <v>26.86242981002239</v>
       </c>
       <c r="E29">
         <v>0.9254999999999999</v>
@@ -1151,7 +1151,7 @@
         <v>0.9254999999999999</v>
       </c>
       <c r="G29">
-        <v>0.5845326886558693</v>
+        <v>0.5306051577195796</v>
       </c>
       <c r="H29">
         <v>0.9254999999999999</v>
@@ -1159,172 +1159,172 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="B30" t="s">
         <v>9</v>
       </c>
       <c r="C30">
-        <v>54.35279063045283</v>
+        <v>54.38946369031042</v>
       </c>
       <c r="D30">
-        <v>27.50874919819178</v>
+        <v>27.57160808325711</v>
       </c>
       <c r="E30">
-        <v>0.9162000000000001</v>
+        <v>0.9254999999999999</v>
       </c>
       <c r="F30">
-        <v>0.9162000000000001</v>
+        <v>0.9254999999999999</v>
       </c>
       <c r="G30">
-        <v>0.5992718273849102</v>
+        <v>0.5845326886558693</v>
       </c>
       <c r="H30">
-        <v>0.9162000000000001</v>
+        <v>0.9254999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1">
-        <v>46153</v>
+        <v>46176</v>
       </c>
       <c r="B31" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C31">
-        <v>34.64560932909123</v>
+        <v>54.35279063045283</v>
       </c>
       <c r="D31">
-        <v>26.08311546080494</v>
+        <v>27.50874919819178</v>
       </c>
       <c r="E31">
-        <v>0.9983000000000001</v>
+        <v>0.9162000000000001</v>
       </c>
       <c r="F31">
-        <v>0.9983000000000001</v>
+        <v>0.9162000000000001</v>
       </c>
       <c r="G31">
-        <v>0.06258613715048233</v>
+        <v>0.5992718273849102</v>
       </c>
       <c r="H31">
-        <v>0.9983000000000001</v>
+        <v>0.9162000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1">
-        <v>46154</v>
+        <v>46177</v>
       </c>
       <c r="B32" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C32">
-        <v>34.50204921141101</v>
+        <v>53.45790968334249</v>
       </c>
       <c r="D32">
-        <v>25.94535229304585</v>
+        <v>26.99486187834476</v>
       </c>
       <c r="E32">
-        <v>0.9984</v>
+        <v>0.9154000000000001</v>
       </c>
       <c r="F32">
-        <v>0.9984</v>
+        <v>0.9154000000000001</v>
       </c>
       <c r="G32">
-        <v>0.05768943168306073</v>
+        <v>0.5691000647975994</v>
       </c>
       <c r="H32">
-        <v>0.9984</v>
+        <v>0.9154000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="B33" t="s">
         <v>10</v>
       </c>
       <c r="C33">
-        <v>35.10429483281073</v>
+        <v>34.64560932909123</v>
       </c>
       <c r="D33">
-        <v>26.43864879939599</v>
+        <v>26.08311546080494</v>
       </c>
       <c r="E33">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="F33">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="G33">
-        <v>0.07926550001722021</v>
+        <v>0.06258613715048233</v>
       </c>
       <c r="H33">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="B34" t="s">
         <v>10</v>
       </c>
       <c r="C34">
-        <v>35.36860632820093</v>
+        <v>34.50204921141101</v>
       </c>
       <c r="D34">
-        <v>26.56575571102338</v>
+        <v>25.94535229304585</v>
       </c>
       <c r="E34">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F34">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G34">
-        <v>0.08553946591902095</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H34">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="B35" t="s">
         <v>10</v>
       </c>
       <c r="C35">
-        <v>34.88080083527914</v>
+        <v>35.10429483281073</v>
       </c>
       <c r="D35">
-        <v>26.19322945679072</v>
+        <v>26.43864879939599</v>
       </c>
       <c r="E35">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="F35">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="G35">
-        <v>0.06870693142475881</v>
+        <v>0.07926550001722021</v>
       </c>
       <c r="H35">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1">
-        <v>46160</v>
+        <v>46156</v>
       </c>
       <c r="B36" t="s">
         <v>10</v>
       </c>
       <c r="C36">
-        <v>34.67638692539213</v>
+        <v>35.36860632820093</v>
       </c>
       <c r="D36">
-        <v>26.06707890342319</v>
+        <v>26.56575571102338</v>
       </c>
       <c r="E36">
         <v>0.9985999999999999</v>
@@ -1333,7 +1333,7 @@
         <v>0.9985999999999999</v>
       </c>
       <c r="G36">
-        <v>0.06289213016552919</v>
+        <v>0.08553946591902095</v>
       </c>
       <c r="H36">
         <v>0.9985999999999999</v>
@@ -1341,120 +1341,120 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="B37" t="s">
         <v>10</v>
       </c>
       <c r="C37">
-        <v>34.21212662725402</v>
+        <v>34.88080083527914</v>
       </c>
       <c r="D37">
-        <v>25.60349394367002</v>
+        <v>26.19322945679072</v>
       </c>
       <c r="E37">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="F37">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="G37">
-        <v>0.0486610616591685</v>
+        <v>0.06870693142475881</v>
       </c>
       <c r="H37">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="B38" t="s">
         <v>10</v>
       </c>
       <c r="C38">
-        <v>34.78598436564941</v>
+        <v>34.67638692539213</v>
       </c>
       <c r="D38">
-        <v>25.95505316769806</v>
+        <v>26.06707890342319</v>
       </c>
       <c r="E38">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="F38">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="G38">
-        <v>0.06335117806143331</v>
+        <v>0.06289213016552919</v>
       </c>
       <c r="H38">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1">
-        <v>46163</v>
+        <v>46161</v>
       </c>
       <c r="B39" t="s">
         <v>10</v>
       </c>
       <c r="C39">
-        <v>33.4539909056227</v>
+        <v>34.21212662725402</v>
       </c>
       <c r="D39">
-        <v>25.96014535427112</v>
+        <v>25.60349394367002</v>
       </c>
       <c r="E39">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="F39">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="G39">
-        <v>0.06350423294229035</v>
+        <v>0.0486610616591685</v>
       </c>
       <c r="H39">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1">
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="B40" t="s">
         <v>10</v>
       </c>
       <c r="C40">
-        <v>33.24951933563993</v>
+        <v>34.78598436564941</v>
       </c>
       <c r="D40">
-        <v>25.46629530314992</v>
+        <v>25.95505316769806</v>
       </c>
       <c r="E40">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="F40">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="G40">
-        <v>0.06136193159696024</v>
+        <v>0.06335117806143331</v>
       </c>
       <c r="H40">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1">
-        <v>46167</v>
+        <v>46163</v>
       </c>
       <c r="B41" t="s">
         <v>10</v>
       </c>
       <c r="C41">
-        <v>33.29896419867477</v>
+        <v>33.4539909056227</v>
       </c>
       <c r="D41">
-        <v>25.45090185337973</v>
+        <v>25.96014535427112</v>
       </c>
       <c r="E41">
         <v>0.9984</v>
@@ -1463,7 +1463,7 @@
         <v>0.9984</v>
       </c>
       <c r="G41">
-        <v>0.06136193159696024</v>
+        <v>0.06350423294229035</v>
       </c>
       <c r="H41">
         <v>0.9984</v>
@@ -1471,16 +1471,16 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1">
-        <v>46168</v>
+        <v>46164</v>
       </c>
       <c r="B42" t="s">
         <v>10</v>
       </c>
       <c r="C42">
-        <v>33.41270923608511</v>
+        <v>33.24951933563993</v>
       </c>
       <c r="D42">
-        <v>25.54156152389702</v>
+        <v>25.46629530314992</v>
       </c>
       <c r="E42">
         <v>0.9984</v>
@@ -1489,7 +1489,7 @@
         <v>0.9984</v>
       </c>
       <c r="G42">
-        <v>0.06549347940676342</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H42">
         <v>0.9984</v>
@@ -1497,770 +1497,770 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1">
-        <v>46169</v>
+        <v>46167</v>
       </c>
       <c r="B43" t="s">
         <v>10</v>
       </c>
       <c r="C43">
-        <v>33.73350746548562</v>
+        <v>33.29896419867477</v>
       </c>
       <c r="D43">
-        <v>25.75393367034243</v>
+        <v>25.45090185337973</v>
       </c>
       <c r="E43">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="F43">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="G43">
-        <v>0.07620510288008187</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H43">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1">
-        <v>46170</v>
+        <v>46168</v>
       </c>
       <c r="B44" t="s">
         <v>10</v>
       </c>
       <c r="C44">
-        <v>33.84336414535104</v>
+        <v>33.41270923608511</v>
       </c>
       <c r="D44">
-        <v>25.97168203877208</v>
+        <v>25.54156152389702</v>
       </c>
       <c r="E44">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
       <c r="F44">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
       <c r="G44">
-        <v>0.0844683152463559</v>
+        <v>0.06549347940676342</v>
       </c>
       <c r="H44">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1">
-        <v>46171</v>
+        <v>46169</v>
       </c>
       <c r="B45" t="s">
         <v>10</v>
       </c>
       <c r="C45">
-        <v>33.73370320039719</v>
+        <v>33.73350746548562</v>
       </c>
       <c r="D45">
-        <v>25.880209881309</v>
+        <v>25.75393367034243</v>
       </c>
       <c r="E45">
-        <v>0.9988</v>
+        <v>0.9987000000000001</v>
       </c>
       <c r="F45">
-        <v>0.9988</v>
+        <v>0.9987000000000001</v>
       </c>
       <c r="G45">
-        <v>0.08201990413931148</v>
+        <v>0.07620510288008187</v>
       </c>
       <c r="H45">
-        <v>0.9988</v>
+        <v>0.9987000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1">
-        <v>46174</v>
+        <v>46170</v>
       </c>
       <c r="B46" t="s">
         <v>10</v>
       </c>
       <c r="C46">
-        <v>33.45546240777382</v>
+        <v>33.84336414535104</v>
       </c>
       <c r="D46">
-        <v>25.61350381215703</v>
+        <v>25.97168203877208</v>
       </c>
       <c r="E46">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
       <c r="F46">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
       <c r="G46">
-        <v>0.06901304118647311</v>
+        <v>0.0844683152463559</v>
       </c>
       <c r="H46">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1">
-        <v>46175</v>
+        <v>46171</v>
       </c>
       <c r="B47" t="s">
         <v>10</v>
       </c>
       <c r="C47">
-        <v>33.31245255516097</v>
+        <v>33.73370320039719</v>
       </c>
       <c r="D47">
-        <v>25.36461330330757</v>
+        <v>25.880209881309</v>
       </c>
       <c r="E47">
-        <v>0.9989999999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="F47">
-        <v>0.9989999999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="G47">
-        <v>0.05845447259401171</v>
+        <v>0.08201990413931148</v>
       </c>
       <c r="H47">
-        <v>0.9989999999999999</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="B48" t="s">
         <v>10</v>
       </c>
       <c r="C48">
-        <v>33.02444632653544</v>
+        <v>33.45546240777382</v>
       </c>
       <c r="D48">
-        <v>25.07926152561908</v>
+        <v>25.61350381215703</v>
       </c>
       <c r="E48">
-        <v>0.9991</v>
+        <v>0.999</v>
       </c>
       <c r="F48">
-        <v>0.9991</v>
+        <v>0.999</v>
       </c>
       <c r="G48">
-        <v>0.04697780820974229</v>
+        <v>0.06901304118647311</v>
       </c>
       <c r="H48">
-        <v>0.9991</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1">
-        <v>46153</v>
+        <v>46175</v>
       </c>
       <c r="B49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C49">
-        <v>36.55790859258162</v>
+        <v>33.31245255516097</v>
       </c>
       <c r="D49">
-        <v>22.67181120908155</v>
+        <v>25.36461330330757</v>
       </c>
       <c r="E49">
-        <v>0.9990740999999999</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="F49">
-        <v>0.9990740999999999</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="G49">
-        <v>0.1648443271746771</v>
+        <v>0.05845447259401171</v>
       </c>
       <c r="H49">
-        <v>0.9990740999999999</v>
+        <v>0.9989999999999999</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1">
-        <v>46154</v>
+        <v>46176</v>
       </c>
       <c r="B50" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C50">
-        <v>36.44753722959613</v>
+        <v>33.02444632653544</v>
       </c>
       <c r="D50">
-        <v>22.40292401789388</v>
+        <v>25.07926152561908</v>
       </c>
       <c r="E50">
-        <v>0.9990772499999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F50">
-        <v>0.9990772499999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G50">
-        <v>0.154964342628132</v>
+        <v>0.04697780820974229</v>
       </c>
       <c r="H50">
-        <v>0.9990772499999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1">
-        <v>46155</v>
+        <v>46177</v>
       </c>
       <c r="B51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C51">
-        <v>36.63128514035871</v>
+        <v>33.50291463064395</v>
       </c>
       <c r="D51">
-        <v>22.65773388934668</v>
+        <v>25.33002193941023</v>
       </c>
       <c r="E51">
-        <v>0.99907745</v>
+        <v>0.9991000000000001</v>
       </c>
       <c r="F51">
-        <v>0.99907745</v>
+        <v>0.9991000000000001</v>
       </c>
       <c r="G51">
-        <v>0.1671633421405267</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H51">
-        <v>0.99907745</v>
+        <v>0.9991000000000001</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="B52" t="s">
         <v>11</v>
       </c>
       <c r="C52">
-        <v>36.87865927427314</v>
+        <v>36.55790859258162</v>
       </c>
       <c r="D52">
-        <v>22.69755646854794</v>
+        <v>22.67181120908155</v>
       </c>
       <c r="E52">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="F52">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="G52">
-        <v>0.1754592080224002</v>
+        <v>0.1648443271746771</v>
       </c>
       <c r="H52">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="B53" t="s">
         <v>11</v>
       </c>
       <c r="C53">
-        <v>36.52208783231286</v>
+        <v>36.44753722959613</v>
       </c>
       <c r="D53">
-        <v>22.32462309676992</v>
+        <v>22.40292401789388</v>
       </c>
       <c r="E53">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="F53">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="G53">
-        <v>0.1577242156354994</v>
+        <v>0.154964342628132</v>
       </c>
       <c r="H53">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="B54" t="s">
         <v>11</v>
       </c>
       <c r="C54">
-        <v>36.25604200674668</v>
+        <v>36.63128514035871</v>
       </c>
       <c r="D54">
-        <v>22.16555007468561</v>
+        <v>22.65773388934668</v>
       </c>
       <c r="E54">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="F54">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="G54">
-        <v>0.1527434068648266</v>
+        <v>0.1671633421405267</v>
       </c>
       <c r="H54">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1">
-        <v>46161</v>
+        <v>46156</v>
       </c>
       <c r="B55" t="s">
         <v>11</v>
       </c>
       <c r="C55">
-        <v>36.01040085730018</v>
+        <v>36.87865927427314</v>
       </c>
       <c r="D55">
-        <v>22.19475589056387</v>
+        <v>22.69755646854794</v>
       </c>
       <c r="E55">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="F55">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="G55">
-        <v>0.1456396418594061</v>
+        <v>0.1754592080224002</v>
       </c>
       <c r="H55">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1">
-        <v>46162</v>
+        <v>46157</v>
       </c>
       <c r="B56" t="s">
         <v>11</v>
       </c>
       <c r="C56">
-        <v>36.45290912796982</v>
+        <v>36.52208783231286</v>
       </c>
       <c r="D56">
-        <v>22.46357594746874</v>
+        <v>22.32462309676992</v>
       </c>
       <c r="E56">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="F56">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="G56">
-        <v>0.1646157747240327</v>
+        <v>0.1577242156354994</v>
       </c>
       <c r="H56">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1">
-        <v>46163</v>
+        <v>46160</v>
       </c>
       <c r="B57" t="s">
         <v>11</v>
       </c>
       <c r="C57">
-        <v>35.75282090566891</v>
+        <v>36.25604200674668</v>
       </c>
       <c r="D57">
-        <v>22.57615417310648</v>
+        <v>22.16555007468561</v>
       </c>
       <c r="E57">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="F57">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="G57">
-        <v>0.1668367104873381</v>
+        <v>0.1527434068648266</v>
       </c>
       <c r="H57">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1">
-        <v>46164</v>
+        <v>46161</v>
       </c>
       <c r="B58" t="s">
         <v>11</v>
       </c>
       <c r="C58">
-        <v>35.75514940724808</v>
+        <v>36.01040085730018</v>
       </c>
       <c r="D58">
-        <v>22.28880693466429</v>
+        <v>22.19475589056387</v>
       </c>
       <c r="E58">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="F58">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="G58">
-        <v>0.1717848261904962</v>
+        <v>0.1456396418594061</v>
       </c>
       <c r="H58">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1">
-        <v>46167</v>
+        <v>46162</v>
       </c>
       <c r="B59" t="s">
         <v>11</v>
       </c>
       <c r="C59">
-        <v>35.84133099010302</v>
+        <v>36.45290912796982</v>
       </c>
       <c r="D59">
-        <v>22.37458514769363</v>
+        <v>22.46357594746874</v>
       </c>
       <c r="E59">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="F59">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="G59">
-        <v>0.1717848261904962</v>
+        <v>0.1646157747240327</v>
       </c>
       <c r="H59">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1">
-        <v>46168</v>
+        <v>46163</v>
       </c>
       <c r="B60" t="s">
         <v>11</v>
       </c>
       <c r="C60">
-        <v>36.23214279739292</v>
+        <v>35.75282090566891</v>
       </c>
       <c r="D60">
-        <v>22.93484792820123</v>
+        <v>22.57615417310648</v>
       </c>
       <c r="E60">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
       <c r="F60">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
       <c r="G60">
-        <v>0.1925900763781823</v>
+        <v>0.1668367104873381</v>
       </c>
       <c r="H60">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="B61" t="s">
         <v>11</v>
       </c>
       <c r="C61">
-        <v>36.4336692499184</v>
+        <v>35.75514940724808</v>
       </c>
       <c r="D61">
-        <v>22.75940954009856</v>
+        <v>22.28880693466429</v>
       </c>
       <c r="E61">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="F61">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="G61">
-        <v>0.1912346098381414</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H61">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="B62" t="s">
         <v>11</v>
       </c>
       <c r="C62">
-        <v>36.57358557066742</v>
+        <v>35.84133099010302</v>
       </c>
       <c r="D62">
-        <v>22.83069636955243</v>
+        <v>22.37458514769363</v>
       </c>
       <c r="E62">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="F62">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="G62">
-        <v>0.2012778603742877</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H62">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1">
-        <v>46171</v>
+        <v>46168</v>
       </c>
       <c r="B63" t="s">
         <v>11</v>
       </c>
       <c r="C63">
-        <v>36.67481300942</v>
+        <v>36.23214279739292</v>
       </c>
       <c r="D63">
-        <v>22.95852861681004</v>
+        <v>22.93484792820123</v>
       </c>
       <c r="E63">
-        <v>0.9964953299999998</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="F63">
-        <v>0.9964953299999998</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="G63">
-        <v>0.2057034850411275</v>
+        <v>0.1925900763781823</v>
       </c>
       <c r="H63">
-        <v>0.9994474899999999</v>
+        <v>0.9992609200000001</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1">
-        <v>46174</v>
+        <v>46169</v>
       </c>
       <c r="B64" t="s">
         <v>11</v>
       </c>
       <c r="C64">
-        <v>36.84565507982974</v>
+        <v>36.4336692499184</v>
       </c>
       <c r="D64">
-        <v>23.15960292175205</v>
+        <v>22.75940954009856</v>
       </c>
       <c r="E64">
-        <v>0.99646052</v>
+        <v>0.9992099400000001</v>
       </c>
       <c r="F64">
-        <v>0.99646052</v>
+        <v>0.9992099400000001</v>
       </c>
       <c r="G64">
-        <v>0.2129379226426205</v>
+        <v>0.1912346098381414</v>
       </c>
       <c r="H64">
-        <v>0.9993986199999999</v>
+        <v>0.9992099400000001</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1">
-        <v>46175</v>
+        <v>46170</v>
       </c>
       <c r="B65" t="s">
         <v>11</v>
       </c>
       <c r="C65">
-        <v>36.88482057171844</v>
+        <v>36.57358557066742</v>
       </c>
       <c r="D65">
-        <v>23.03898938038424</v>
+        <v>22.83069636955243</v>
       </c>
       <c r="E65">
-        <v>0.99645675</v>
+        <v>0.9994435600000001</v>
       </c>
       <c r="F65">
-        <v>0.99645675</v>
+        <v>0.9994435600000001</v>
       </c>
       <c r="G65">
-        <v>0.2185229551183987</v>
+        <v>0.2012778603742877</v>
       </c>
       <c r="H65">
-        <v>0.9994034199999998</v>
+        <v>0.9994435600000001</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1">
-        <v>46176</v>
+        <v>46171</v>
       </c>
       <c r="B66" t="s">
         <v>11</v>
       </c>
       <c r="C66">
-        <v>36.96809213745556</v>
+        <v>36.67481300942</v>
       </c>
       <c r="D66">
-        <v>22.99660212231548</v>
+        <v>22.95852861681004</v>
       </c>
       <c r="E66">
-        <v>0.9964706</v>
+        <v>0.9964953299999998</v>
       </c>
       <c r="F66">
-        <v>0.9964706</v>
+        <v>0.9964953299999998</v>
       </c>
       <c r="G66">
-        <v>0.2153385706032709</v>
+        <v>0.2057034850411275</v>
       </c>
       <c r="H66">
-        <v>0.9993955800000001</v>
+        <v>0.9994474899999999</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1">
-        <v>46153</v>
+        <v>46174</v>
       </c>
       <c r="B67" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C67">
-        <v>52.70832779833182</v>
+        <v>36.84565507982974</v>
       </c>
       <c r="D67">
-        <v>23.99044674439659</v>
+        <v>23.15960292175205</v>
       </c>
       <c r="E67">
-        <v>0.9994000000000002</v>
+        <v>0.99646052</v>
       </c>
       <c r="F67">
-        <v>0.9994000000000002</v>
+        <v>0.99646052</v>
       </c>
       <c r="G67">
-        <v>0.5438253854918791</v>
+        <v>0.2129379226426205</v>
       </c>
       <c r="H67">
-        <v>0.9994000000000002</v>
+        <v>0.9993986199999999</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1">
-        <v>46154</v>
+        <v>46175</v>
       </c>
       <c r="B68" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C68">
-        <v>50.89464485280568</v>
+        <v>36.88482057171844</v>
       </c>
       <c r="D68">
-        <v>23.21558303176282</v>
+        <v>23.03898938038424</v>
       </c>
       <c r="E68">
-        <v>0.9996</v>
+        <v>0.99645675</v>
       </c>
       <c r="F68">
-        <v>0.9996</v>
+        <v>0.99645675</v>
       </c>
       <c r="G68">
-        <v>0.5034825029548833</v>
+        <v>0.2185229551183987</v>
       </c>
       <c r="H68">
-        <v>0.9996</v>
+        <v>0.9994034199999998</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1">
-        <v>46155</v>
+        <v>46176</v>
       </c>
       <c r="B69" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C69">
-        <v>51.8659994471731</v>
+        <v>36.96809213745556</v>
       </c>
       <c r="D69">
-        <v>23.7009037279043</v>
+        <v>22.99660212231548</v>
       </c>
       <c r="E69">
-        <v>1.0002</v>
+        <v>0.9964706</v>
       </c>
       <c r="F69">
-        <v>1.0002</v>
+        <v>0.9964706</v>
       </c>
       <c r="G69">
-        <v>0.533512029714132</v>
+        <v>0.2153385706032709</v>
       </c>
       <c r="H69">
-        <v>1.0002</v>
+        <v>0.9993955800000001</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1">
-        <v>46156</v>
+        <v>46177</v>
       </c>
       <c r="B70" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C70">
-        <v>52.4470179952828</v>
+        <v>37.13780815830533</v>
       </c>
       <c r="D70">
-        <v>23.76861704536814</v>
+        <v>22.74889586257873</v>
       </c>
       <c r="E70">
-        <v>0.9998</v>
+        <v>0.9964706899999999</v>
       </c>
       <c r="F70">
-        <v>0.9998</v>
+        <v>0.9964706899999999</v>
       </c>
       <c r="G70">
-        <v>0.5492634496849078</v>
+        <v>0.2094594998678323</v>
       </c>
       <c r="H70">
-        <v>0.9998</v>
+        <v>0.99938478</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="B71" t="s">
         <v>12</v>
       </c>
       <c r="C71">
-        <v>50.81077380018606</v>
+        <v>52.70832779833182</v>
       </c>
       <c r="D71">
-        <v>22.76900580927995</v>
+        <v>23.99044674439659</v>
       </c>
       <c r="E71">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="F71">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="G71">
-        <v>0.4903296143797722</v>
+        <v>0.5438253854918791</v>
       </c>
       <c r="H71">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1">
-        <v>46160</v>
+        <v>46154</v>
       </c>
       <c r="B72" t="s">
         <v>12</v>
       </c>
       <c r="C72">
-        <v>49.50286387149169</v>
+        <v>50.89464485280568</v>
       </c>
       <c r="D72">
-        <v>22.24532119914133</v>
+        <v>23.21558303176282</v>
       </c>
       <c r="E72">
         <v>0.9996</v>
@@ -2269,7 +2269,7 @@
         <v>0.9996</v>
       </c>
       <c r="G72">
-        <v>0.4630591776162345</v>
+        <v>0.5034825029548833</v>
       </c>
       <c r="H72">
         <v>0.9996</v>
@@ -2277,224 +2277,224 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1">
-        <v>46161</v>
+        <v>46155</v>
       </c>
       <c r="B73" t="s">
         <v>12</v>
       </c>
       <c r="C73">
-        <v>49.29146729279496</v>
+        <v>51.8659994471731</v>
       </c>
       <c r="D73">
-        <v>22.22167836589682</v>
+        <v>23.7009037279043</v>
       </c>
       <c r="E73">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="F73">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="G73">
-        <v>0.4571659248870246</v>
+        <v>0.533512029714132</v>
       </c>
       <c r="H73">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1">
-        <v>46162</v>
+        <v>46156</v>
       </c>
       <c r="B74" t="s">
         <v>12</v>
       </c>
       <c r="C74">
-        <v>50.88652370817657</v>
+        <v>52.4470179952828</v>
       </c>
       <c r="D74">
-        <v>22.93254398967657</v>
+        <v>23.76861704536814</v>
       </c>
       <c r="E74">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F74">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G74">
-        <v>0.5126171754864624</v>
+        <v>0.5492634496849078</v>
       </c>
       <c r="H74">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1">
-        <v>46163</v>
+        <v>46157</v>
       </c>
       <c r="B75" t="s">
         <v>12</v>
       </c>
       <c r="C75">
-        <v>48.26646764818586</v>
+        <v>50.81077380018606</v>
       </c>
       <c r="D75">
-        <v>23.11655387625012</v>
+        <v>22.76900580927995</v>
       </c>
       <c r="E75">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="F75">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="G75">
-        <v>0.521243030947425</v>
+        <v>0.4903296143797722</v>
       </c>
       <c r="H75">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1">
-        <v>46164</v>
+        <v>46160</v>
       </c>
       <c r="B76" t="s">
         <v>12</v>
       </c>
       <c r="C76">
-        <v>48.84737503703267</v>
+        <v>49.50286387149169</v>
       </c>
       <c r="D76">
-        <v>22.83557604744466</v>
+        <v>22.24532119914133</v>
       </c>
       <c r="E76">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="F76">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="G76">
-        <v>0.5438521997590966</v>
+        <v>0.4630591776162345</v>
       </c>
       <c r="H76">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1">
-        <v>46167</v>
+        <v>46161</v>
       </c>
       <c r="B77" t="s">
         <v>12</v>
       </c>
       <c r="C77">
-        <v>48.85151560750146</v>
+        <v>49.29146729279496</v>
       </c>
       <c r="D77">
-        <v>22.83513820206554</v>
+        <v>22.22167836589682</v>
       </c>
       <c r="E77">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F77">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G77">
-        <v>0.5438521997590966</v>
+        <v>0.4571659248870246</v>
       </c>
       <c r="H77">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="1">
-        <v>46168</v>
+        <v>46162</v>
       </c>
       <c r="B78" t="s">
         <v>12</v>
       </c>
       <c r="C78">
-        <v>50.90437883274981</v>
+        <v>50.88652370817657</v>
       </c>
       <c r="D78">
-        <v>24.25672473501501</v>
+        <v>22.93254398967657</v>
       </c>
       <c r="E78">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F78">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G78">
-        <v>0.6130191115419561</v>
+        <v>0.5126171754864624</v>
       </c>
       <c r="H78">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1">
-        <v>46169</v>
+        <v>46163</v>
       </c>
       <c r="B79" t="s">
         <v>12</v>
       </c>
       <c r="C79">
-        <v>50.47312432255841</v>
+        <v>48.26646764818586</v>
       </c>
       <c r="D79">
-        <v>23.84499305142194</v>
+        <v>23.11655387625012</v>
       </c>
       <c r="E79">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="F79">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="G79">
-        <v>0.5952317692821967</v>
+        <v>0.521243030947425</v>
       </c>
       <c r="H79">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1">
-        <v>46170</v>
+        <v>46164</v>
       </c>
       <c r="B80" t="s">
         <v>12</v>
       </c>
       <c r="C80">
-        <v>50.84596269629946</v>
+        <v>48.84737503703267</v>
       </c>
       <c r="D80">
-        <v>23.7680603326165</v>
+        <v>22.83557604744466</v>
       </c>
       <c r="E80">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F80">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G80">
-        <v>0.606831065374982</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H80">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="1">
-        <v>46171</v>
+        <v>46167</v>
       </c>
       <c r="B81" t="s">
         <v>12</v>
       </c>
       <c r="C81">
-        <v>51.08372269965196</v>
+        <v>48.85151560750146</v>
       </c>
       <c r="D81">
-        <v>23.88880359436525</v>
+        <v>22.83513820206554</v>
       </c>
       <c r="E81">
         <v>0.9998999999999999</v>
@@ -2503,7 +2503,7 @@
         <v>0.9998999999999999</v>
       </c>
       <c r="G81">
-        <v>0.604420070348211</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H81">
         <v>0.9998999999999999</v>
@@ -2511,1264 +2511,1264 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="1">
-        <v>46174</v>
+        <v>46168</v>
       </c>
       <c r="B82" t="s">
         <v>12</v>
       </c>
       <c r="C82">
-        <v>51.84875713649351</v>
+        <v>50.90437883274981</v>
       </c>
       <c r="D82">
-        <v>24.29466650399529</v>
+        <v>24.25672473501501</v>
       </c>
       <c r="E82">
-        <v>0.9998</v>
+        <v>0.9996999999999999</v>
       </c>
       <c r="F82">
-        <v>0.9998</v>
+        <v>0.9996999999999999</v>
       </c>
       <c r="G82">
-        <v>0.6282079224060508</v>
+        <v>0.6130191115419561</v>
       </c>
       <c r="H82">
-        <v>0.9998</v>
+        <v>0.9996999999999999</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="1">
-        <v>46175</v>
+        <v>46169</v>
       </c>
       <c r="B83" t="s">
         <v>12</v>
       </c>
       <c r="C83">
-        <v>53.42858844634741</v>
+        <v>50.47312432255841</v>
       </c>
       <c r="D83">
-        <v>24.82449061140869</v>
+        <v>23.84499305142194</v>
       </c>
       <c r="E83">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="F83">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="G83">
-        <v>0.6935709687814895</v>
+        <v>0.5952317692821967</v>
       </c>
       <c r="H83">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="1">
-        <v>46176</v>
+        <v>46170</v>
       </c>
       <c r="B84" t="s">
         <v>12</v>
       </c>
       <c r="C84">
-        <v>53.95056789686777</v>
+        <v>50.84596269629946</v>
       </c>
       <c r="D84">
-        <v>24.99295077214167</v>
+        <v>23.7680603326165</v>
       </c>
       <c r="E84">
-        <v>0.9996000000000002</v>
+        <v>0.9998</v>
       </c>
       <c r="F84">
-        <v>0.9996000000000002</v>
+        <v>0.9998</v>
       </c>
       <c r="G84">
-        <v>0.7088134081800193</v>
+        <v>0.606831065374982</v>
       </c>
       <c r="H84">
-        <v>0.9996000000000002</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1">
-        <v>46153</v>
+        <v>46171</v>
       </c>
       <c r="B85" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C85">
-        <v>57.1732166855686</v>
+        <v>51.08372269965196</v>
       </c>
       <c r="D85">
-        <v>23.50022751267814</v>
+        <v>23.88880359436525</v>
       </c>
       <c r="E85">
-        <v>0.9991</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F85">
-        <v>0.9991</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G85">
-        <v>0.6994110097039083</v>
+        <v>0.604420070348211</v>
       </c>
       <c r="H85">
-        <v>0.9991</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="1">
-        <v>46154</v>
+        <v>46174</v>
       </c>
       <c r="B86" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C86">
-        <v>54.77380642078597</v>
+        <v>51.84875713649351</v>
       </c>
       <c r="D86">
-        <v>22.55192940254518</v>
+        <v>24.29466650399529</v>
       </c>
       <c r="E86">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
       <c r="F86">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
       <c r="G86">
-        <v>0.6459175880844941</v>
+        <v>0.6282079224060508</v>
       </c>
       <c r="H86">
-        <v>0.9990000000000001</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="1">
-        <v>46155</v>
+        <v>46175</v>
       </c>
       <c r="B87" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C87">
-        <v>56.32187380830906</v>
+        <v>53.42858844634741</v>
       </c>
       <c r="D87">
-        <v>23.17121437414109</v>
+        <v>24.82449061140869</v>
       </c>
       <c r="E87">
-        <v>0.9990000000000001</v>
+        <v>1</v>
       </c>
       <c r="F87">
-        <v>0.9990000000000001</v>
+        <v>1</v>
       </c>
       <c r="G87">
-        <v>0.6851523922954754</v>
+        <v>0.6935709687814895</v>
       </c>
       <c r="H87">
-        <v>0.9990000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1">
-        <v>46156</v>
+        <v>46176</v>
       </c>
       <c r="B88" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C88">
-        <v>56.15321618553139</v>
+        <v>53.95056789686777</v>
       </c>
       <c r="D88">
-        <v>22.95838347314443</v>
+        <v>24.99295077214167</v>
       </c>
       <c r="E88">
-        <v>0.9992</v>
+        <v>0.9996000000000002</v>
       </c>
       <c r="F88">
-        <v>0.9992</v>
+        <v>0.9996000000000002</v>
       </c>
       <c r="G88">
-        <v>0.6907028507208208</v>
+        <v>0.7088134081800193</v>
       </c>
       <c r="H88">
-        <v>0.9992</v>
+        <v>0.9996000000000002</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="1">
-        <v>46157</v>
+        <v>46177</v>
       </c>
       <c r="B89" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C89">
-        <v>54.47755813049488</v>
+        <v>53.29782764127071</v>
       </c>
       <c r="D89">
-        <v>22.0083816089626</v>
+        <v>24.48126483589962</v>
       </c>
       <c r="E89">
-        <v>0.9986</v>
+        <v>1.0001</v>
       </c>
       <c r="F89">
-        <v>0.9986</v>
+        <v>1.0001</v>
       </c>
       <c r="G89">
-        <v>0.6220895940829376</v>
+        <v>0.6810341543458651</v>
       </c>
       <c r="H89">
-        <v>0.9986</v>
+        <v>1.0001</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B90" t="s">
         <v>13</v>
       </c>
       <c r="C90">
-        <v>52.6278781150669</v>
+        <v>57.1732166855686</v>
       </c>
       <c r="D90">
-        <v>21.5357353870778</v>
+        <v>23.50022751267814</v>
       </c>
       <c r="E90">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F90">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G90">
-        <v>0.5845134636435627</v>
+        <v>0.6994110097039083</v>
       </c>
       <c r="H90">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
       </c>
       <c r="C91">
-        <v>54.91583234840245</v>
+        <v>54.77380642078597</v>
       </c>
       <c r="D91">
-        <v>22.38321645985006</v>
+        <v>22.55192940254518</v>
       </c>
       <c r="E91">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F91">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G91">
-        <v>0.6596976539194066</v>
+        <v>0.6459175880844941</v>
       </c>
       <c r="H91">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B92" t="s">
         <v>13</v>
       </c>
       <c r="C92">
-        <v>53.91712298548793</v>
+        <v>56.32187380830906</v>
       </c>
       <c r="D92">
-        <v>22.73711181201267</v>
+        <v>23.17121437414109</v>
       </c>
       <c r="E92">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F92">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G92">
-        <v>0.6737329602396263</v>
+        <v>0.6851523922954754</v>
       </c>
       <c r="H92">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="1">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="B93" t="s">
         <v>13</v>
       </c>
       <c r="C93">
-        <v>55.19651747515625</v>
+        <v>56.15321618553139</v>
       </c>
       <c r="D93">
-        <v>22.79462037330554</v>
+        <v>22.95838347314443</v>
       </c>
       <c r="E93">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
       <c r="F93">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
       <c r="G93">
-        <v>0.7139885317003913</v>
+        <v>0.6907028507208208</v>
       </c>
       <c r="H93">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="1">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="B94" t="s">
         <v>13</v>
       </c>
       <c r="C94">
-        <v>55.28054997487197</v>
+        <v>54.47755813049488</v>
       </c>
       <c r="D94">
-        <v>23.00160891539877</v>
+        <v>22.0083816089626</v>
       </c>
       <c r="E94">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="F94">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="G94">
-        <v>0.7139885317003913</v>
+        <v>0.6220895940829376</v>
       </c>
       <c r="H94">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="1">
-        <v>46168</v>
+        <v>46161</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
       </c>
       <c r="C95">
-        <v>58.75156728873073</v>
+        <v>52.6278781150669</v>
       </c>
       <c r="D95">
-        <v>24.84249654093248</v>
+        <v>21.5357353870778</v>
       </c>
       <c r="E95">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="F95">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="G95">
-        <v>0.8184872182632257</v>
+        <v>0.5845134636435627</v>
       </c>
       <c r="H95">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="1">
-        <v>46169</v>
+        <v>46162</v>
       </c>
       <c r="B96" t="s">
         <v>13</v>
       </c>
       <c r="C96">
-        <v>57.86771234337395</v>
+        <v>54.91583234840245</v>
       </c>
       <c r="D96">
-        <v>24.21066615243091</v>
+        <v>22.38321645985006</v>
       </c>
       <c r="E96">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="F96">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="G96">
-        <v>0.798997241708943</v>
+        <v>0.6596976539194066</v>
       </c>
       <c r="H96">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="1">
-        <v>46170</v>
+        <v>46163</v>
       </c>
       <c r="B97" t="s">
         <v>13</v>
       </c>
       <c r="C97">
-        <v>58.18666682631797</v>
+        <v>53.91712298548793</v>
       </c>
       <c r="D97">
-        <v>24.09552344282839</v>
+        <v>22.73711181201267</v>
       </c>
       <c r="E97">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="F97">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="G97">
-        <v>0.8165093478664007</v>
+        <v>0.6737329602396263</v>
       </c>
       <c r="H97">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="1">
-        <v>46171</v>
+        <v>46164</v>
       </c>
       <c r="B98" t="s">
         <v>13</v>
       </c>
       <c r="C98">
-        <v>58.79256019733606</v>
+        <v>55.19651747515625</v>
       </c>
       <c r="D98">
-        <v>24.33854853448823</v>
+        <v>22.79462037330554</v>
       </c>
       <c r="E98">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F98">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G98">
-        <v>0.8152654642198496</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H98">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="1">
-        <v>46174</v>
+        <v>46167</v>
       </c>
       <c r="B99" t="s">
         <v>13</v>
       </c>
       <c r="C99">
-        <v>58.97156722185718</v>
+        <v>55.28054997487197</v>
       </c>
       <c r="D99">
-        <v>24.48296361348067</v>
+        <v>23.00160891539877</v>
       </c>
       <c r="E99">
-        <v>0.9990000000000001</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="F99">
-        <v>0.9990000000000001</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="G99">
-        <v>0.8243563865851753</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H99">
-        <v>0.9990000000000001</v>
+        <v>0.9989000000000001</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="1">
-        <v>46175</v>
+        <v>46168</v>
       </c>
       <c r="B100" t="s">
         <v>13</v>
       </c>
       <c r="C100">
-        <v>61.6542902214027</v>
+        <v>58.75156728873073</v>
       </c>
       <c r="D100">
-        <v>25.06517348653028</v>
+        <v>24.84249654093248</v>
       </c>
       <c r="E100">
-        <v>0.9988</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="F100">
-        <v>0.9988</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="G100">
-        <v>0.9299077697948877</v>
+        <v>0.8184872182632257</v>
       </c>
       <c r="H100">
-        <v>0.9988</v>
+        <v>0.9989000000000001</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="1">
-        <v>46176</v>
+        <v>46169</v>
       </c>
       <c r="B101" t="s">
         <v>13</v>
       </c>
       <c r="C101">
-        <v>63.0681947750049</v>
+        <v>57.86771234337395</v>
       </c>
       <c r="D101">
-        <v>25.58770976382014</v>
+        <v>24.21066615243091</v>
       </c>
       <c r="E101">
-        <v>0.9988000000000002</v>
+        <v>0.9986999999999999</v>
       </c>
       <c r="F101">
-        <v>0.9988000000000002</v>
+        <v>0.9986999999999999</v>
       </c>
       <c r="G101">
-        <v>0.9639112148600193</v>
+        <v>0.798997241708943</v>
       </c>
       <c r="H101">
-        <v>0.9988000000000002</v>
+        <v>0.9986999999999999</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="1">
-        <v>46153</v>
+        <v>46170</v>
       </c>
       <c r="B102" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C102">
-        <v>35.78646526282436</v>
+        <v>58.18666682631797</v>
       </c>
       <c r="D102">
-        <v>18.96635091925032</v>
+        <v>24.09552344282839</v>
       </c>
       <c r="E102">
-        <v>0.9996491399999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F102">
-        <v>0.9996491399999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G102">
-        <v>0.2240600969213613</v>
+        <v>0.8165093478664007</v>
       </c>
       <c r="H102">
-        <v>0.9985614899999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="1">
-        <v>46154</v>
+        <v>46171</v>
       </c>
       <c r="B103" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C103">
-        <v>35.71584102184062</v>
+        <v>58.79256019733606</v>
       </c>
       <c r="D103">
-        <v>18.62432950231353</v>
+        <v>24.33854853448823</v>
       </c>
       <c r="E103">
-        <v>0.99965481</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="F103">
-        <v>0.99965481</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="G103">
-        <v>0.2104844827747143</v>
+        <v>0.8152654642198496</v>
       </c>
       <c r="H103">
-        <v>0.9985622199999999</v>
+        <v>0.9989999999999999</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="1">
-        <v>46155</v>
+        <v>46174</v>
       </c>
       <c r="B104" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C104">
-        <v>35.95182028203252</v>
+        <v>58.97156722185718</v>
       </c>
       <c r="D104">
-        <v>18.95670796791552</v>
+        <v>24.48296361348067</v>
       </c>
       <c r="E104">
-        <v>0.9996515200000001</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F104">
-        <v>0.9996515200000001</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G104">
-        <v>0.2259035693959275</v>
+        <v>0.8243563865851753</v>
       </c>
       <c r="H104">
-        <v>0.99855193</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="1">
-        <v>46156</v>
+        <v>46175</v>
       </c>
       <c r="B105" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C105">
-        <v>36.14451597805883</v>
+        <v>61.6542902214027</v>
       </c>
       <c r="D105">
-        <v>18.86297660538653</v>
+        <v>25.06517348653028</v>
       </c>
       <c r="E105">
-        <v>0.9996563399999999</v>
+        <v>0.9988</v>
       </c>
       <c r="F105">
-        <v>0.9996563399999999</v>
+        <v>0.9988</v>
       </c>
       <c r="G105">
-        <v>0.2362110061840785</v>
+        <v>0.9299077697948877</v>
       </c>
       <c r="H105">
-        <v>0.99857265</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="1">
-        <v>46157</v>
+        <v>46176</v>
       </c>
       <c r="B106" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C106">
-        <v>35.32805803135546</v>
+        <v>63.0681947750049</v>
       </c>
       <c r="D106">
-        <v>18.35643242381478</v>
+        <v>25.58770976382014</v>
       </c>
       <c r="E106">
-        <v>0.9997415800000001</v>
+        <v>0.9988000000000002</v>
       </c>
       <c r="F106">
-        <v>0.9997415800000001</v>
+        <v>0.9988000000000002</v>
       </c>
       <c r="G106">
-        <v>0.2023559161375383</v>
+        <v>0.9639112148600193</v>
       </c>
       <c r="H106">
-        <v>0.9986639900000002</v>
+        <v>0.9988000000000002</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="1">
-        <v>46160</v>
+        <v>46177</v>
       </c>
       <c r="B107" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C107">
-        <v>34.83995455757461</v>
+        <v>61.53154955456358</v>
       </c>
       <c r="D107">
-        <v>18.02301281718857</v>
+        <v>24.75810538712983</v>
       </c>
       <c r="E107">
-        <v>0.9996851299999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F107">
-        <v>0.9996851299999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G107">
-        <v>0.1850932291737926</v>
+        <v>0.9225710173552821</v>
       </c>
       <c r="H107">
-        <v>0.99857724</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B108" t="s">
         <v>14</v>
       </c>
       <c r="C108">
-        <v>34.45479308705605</v>
+        <v>35.78646526282436</v>
       </c>
       <c r="D108">
-        <v>18.09576834566068</v>
+        <v>18.96635091925032</v>
       </c>
       <c r="E108">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="F108">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="G108">
-        <v>0.1784731209386736</v>
+        <v>0.2240600969213613</v>
       </c>
       <c r="H108">
-        <v>0.9985337599999999</v>
+        <v>0.9985614899999999</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B109" t="s">
         <v>14</v>
       </c>
       <c r="C109">
-        <v>34.96336277390787</v>
+        <v>35.71584102184062</v>
       </c>
       <c r="D109">
-        <v>18.34938420029253</v>
+        <v>18.62432950231353</v>
       </c>
       <c r="E109">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="F109">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="G109">
-        <v>0.2009313391215752</v>
+        <v>0.2104844827747143</v>
       </c>
       <c r="H109">
-        <v>0.99848777</v>
+        <v>0.9985622199999999</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B110" t="s">
         <v>14</v>
       </c>
       <c r="C110">
-        <v>34.44616924817128</v>
+        <v>35.95182028203252</v>
       </c>
       <c r="D110">
-        <v>18.60085625074367</v>
+        <v>18.95670796791552</v>
       </c>
       <c r="E110">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="F110">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="G110">
-        <v>0.2124957180214682</v>
+        <v>0.2259035693959275</v>
       </c>
       <c r="H110">
-        <v>0.9985085200000001</v>
+        <v>0.99855193</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="1">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="B111" t="s">
         <v>14</v>
       </c>
       <c r="C111">
-        <v>34.62137220937314</v>
+        <v>36.14451597805883</v>
       </c>
       <c r="D111">
-        <v>18.28780484745949</v>
+        <v>18.86297660538653</v>
       </c>
       <c r="E111">
-        <v>0.9996106299999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="F111">
-        <v>0.9996106299999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="G111">
-        <v>0.2145907067863493</v>
+        <v>0.2362110061840785</v>
       </c>
       <c r="H111">
-        <v>0.9932939299999999</v>
+        <v>0.99857265</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="1">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="B112" t="s">
         <v>14</v>
       </c>
       <c r="C112">
-        <v>34.6540695486741</v>
+        <v>35.32805803135546</v>
       </c>
       <c r="D112">
-        <v>18.36409048915342</v>
+        <v>18.35643242381478</v>
       </c>
       <c r="E112">
-        <v>0.9995448900000001</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="F112">
-        <v>0.9995448900000001</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="G112">
-        <v>0.2145907067863493</v>
+        <v>0.2023559161375383</v>
       </c>
       <c r="H112">
-        <v>0.9984302600000001</v>
+        <v>0.9986639900000002</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="1">
-        <v>46168</v>
+        <v>46160</v>
       </c>
       <c r="B113" t="s">
         <v>14</v>
       </c>
       <c r="C113">
-        <v>35.4820130509417</v>
+        <v>34.83995455757461</v>
       </c>
       <c r="D113">
-        <v>19.20292041814603</v>
+        <v>18.02301281718857</v>
       </c>
       <c r="E113">
-        <v>0.9995448900000001</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="F113">
-        <v>0.9995448900000001</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="G113">
-        <v>0.2553172934903569</v>
+        <v>0.1850932291737926</v>
       </c>
       <c r="H113">
-        <v>0.9984302600000001</v>
+        <v>0.99857724</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="1">
-        <v>46169</v>
+        <v>46161</v>
       </c>
       <c r="B114" t="s">
         <v>14</v>
       </c>
       <c r="C114">
-        <v>35.71913468603401</v>
+        <v>34.45479308705605</v>
       </c>
       <c r="D114">
-        <v>18.96318693998171</v>
+        <v>18.09576834566068</v>
       </c>
       <c r="E114">
-        <v>0.99955466</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="F114">
-        <v>0.99955466</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="G114">
-        <v>0.2536413280520453</v>
+        <v>0.1784731209386736</v>
       </c>
       <c r="H114">
-        <v>0.9984700500000001</v>
+        <v>0.9985337599999999</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="1">
-        <v>46170</v>
+        <v>46162</v>
       </c>
       <c r="B115" t="s">
         <v>14</v>
       </c>
       <c r="C115">
-        <v>35.76226417354731</v>
+        <v>34.96336277390787</v>
       </c>
       <c r="D115">
-        <v>18.89050847207122</v>
+        <v>18.34938420029253</v>
       </c>
       <c r="E115">
-        <v>0.9995525399999999</v>
+        <v>0.99963413</v>
       </c>
       <c r="F115">
-        <v>0.9995525399999999</v>
+        <v>0.99963413</v>
       </c>
       <c r="G115">
-        <v>0.2580826940041561</v>
+        <v>0.2009313391215752</v>
       </c>
       <c r="H115">
-        <v>0.99847732</v>
+        <v>0.99848777</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="1">
-        <v>46171</v>
+        <v>46163</v>
       </c>
       <c r="B116" t="s">
         <v>14</v>
       </c>
       <c r="C116">
-        <v>35.84309020154227</v>
+        <v>34.44616924817128</v>
       </c>
       <c r="D116">
-        <v>19.06511612333149</v>
+        <v>18.60085625074367</v>
       </c>
       <c r="E116">
-        <v>0.9995533299999999</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="F116">
-        <v>0.9995533299999999</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="G116">
-        <v>0.2619374017254759</v>
+        <v>0.2124957180214682</v>
       </c>
       <c r="H116">
-        <v>0.99849382</v>
+        <v>0.9985085200000001</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="1">
-        <v>46174</v>
+        <v>46164</v>
       </c>
       <c r="B117" t="s">
         <v>14</v>
       </c>
       <c r="C117">
-        <v>36.27022125574057</v>
+        <v>34.62137220937314</v>
       </c>
       <c r="D117">
-        <v>19.32711369104533</v>
+        <v>18.28780484745949</v>
       </c>
       <c r="E117">
-        <v>0.9995550400000001</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="F117">
-        <v>0.9995550400000001</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="G117">
-        <v>0.2764348160433892</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H117">
-        <v>0.9985177199999999</v>
+        <v>0.9932939299999999</v>
       </c>
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="1">
-        <v>46175</v>
+        <v>46167</v>
       </c>
       <c r="B118" t="s">
         <v>14</v>
       </c>
       <c r="C118">
-        <v>36.57133692946976</v>
+        <v>34.6540695486741</v>
       </c>
       <c r="D118">
-        <v>19.33857330565742</v>
+        <v>18.36409048915342</v>
       </c>
       <c r="E118">
-        <v>0.9994989200000002</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="F118">
-        <v>0.9994989200000002</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="G118">
-        <v>0.2931947261624381</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H118">
-        <v>0.9984577800000001</v>
+        <v>0.9984302600000001</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="1">
-        <v>46176</v>
+        <v>46168</v>
       </c>
       <c r="B119" t="s">
         <v>14</v>
       </c>
       <c r="C119">
-        <v>36.8289666508657</v>
+        <v>35.4820130509417</v>
       </c>
       <c r="D119">
-        <v>19.43137154505686</v>
+        <v>19.20292041814603</v>
       </c>
       <c r="E119">
-        <v>0.9994838199999998</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="F119">
-        <v>0.9994838199999998</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="G119">
-        <v>0.2996471994933361</v>
+        <v>0.2553172934903569</v>
       </c>
       <c r="H119">
-        <v>0.9984549499999998</v>
+        <v>0.9984302600000001</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="1">
-        <v>46153</v>
+        <v>46169</v>
       </c>
       <c r="B120" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C120">
-        <v>28.12253390077671</v>
+        <v>35.71913468603401</v>
       </c>
       <c r="D120">
-        <v>23.58699683751922</v>
+        <v>18.96318693998171</v>
       </c>
       <c r="E120">
-        <v>0.9997295369999999</v>
+        <v>0.99955466</v>
       </c>
       <c r="F120">
-        <v>0.9997295369999999</v>
+        <v>0.99955466</v>
       </c>
       <c r="G120">
-        <v>0.03368732240295347</v>
+        <v>0.2536413280520453</v>
       </c>
       <c r="H120">
-        <v>0.9997295369999999</v>
+        <v>0.9984700500000001</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="1">
-        <v>46154</v>
+        <v>46170</v>
       </c>
       <c r="B121" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C121">
-        <v>28.17715727830483</v>
+        <v>35.76226417354731</v>
       </c>
       <c r="D121">
-        <v>23.63894513078866</v>
+        <v>18.89050847207122</v>
       </c>
       <c r="E121">
-        <v>1.000319473</v>
+        <v>0.9995525399999999</v>
       </c>
       <c r="F121">
-        <v>1.000319473</v>
+        <v>0.9995525399999999</v>
       </c>
       <c r="G121">
-        <v>0.03515547182056333</v>
+        <v>0.2580826940041561</v>
       </c>
       <c r="H121">
-        <v>1.000319473</v>
+        <v>0.99847732</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="1">
-        <v>46155</v>
+        <v>46171</v>
       </c>
       <c r="B122" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C122">
-        <v>28.59002627414054</v>
+        <v>35.84309020154227</v>
       </c>
       <c r="D122">
-        <v>23.96230704059692</v>
+        <v>19.06511612333149</v>
       </c>
       <c r="E122">
-        <v>0.9999999989999999</v>
+        <v>0.9995533299999999</v>
       </c>
       <c r="F122">
-        <v>0.9999999989999999</v>
+        <v>0.9995533299999999</v>
       </c>
       <c r="G122">
-        <v>0.05179637495949674</v>
+        <v>0.2619374017254759</v>
       </c>
       <c r="H122">
-        <v>0.9999999989999999</v>
+        <v>0.99849382</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="1">
-        <v>46156</v>
+        <v>46174</v>
       </c>
       <c r="B123" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C123">
-        <v>28.56217859389523</v>
+        <v>36.27022125574057</v>
       </c>
       <c r="D123">
-        <v>23.9411987302529</v>
+        <v>19.32711369104533</v>
       </c>
       <c r="E123">
-        <v>1</v>
+        <v>0.9995550400000001</v>
       </c>
       <c r="F123">
-        <v>1</v>
+        <v>0.9995550400000001</v>
       </c>
       <c r="G123">
-        <v>0.04837024516756849</v>
+        <v>0.2764348160433892</v>
       </c>
       <c r="H123">
-        <v>1</v>
+        <v>0.9985177199999999</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="1">
-        <v>46157</v>
+        <v>46175</v>
       </c>
       <c r="B124" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C124">
-        <v>28.57618675936338</v>
+        <v>36.57133692946976</v>
       </c>
       <c r="D124">
-        <v>23.9576220541054</v>
+        <v>19.33857330565742</v>
       </c>
       <c r="E124">
-        <v>0.999503249</v>
+        <v>0.9994989200000002</v>
       </c>
       <c r="F124">
-        <v>0.999503249</v>
+        <v>0.9994989200000002</v>
       </c>
       <c r="G124">
-        <v>0.04983868243960732</v>
+        <v>0.2931947261624381</v>
       </c>
       <c r="H124">
-        <v>0.999503249</v>
+        <v>0.9984577800000001</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="1">
-        <v>46160</v>
+        <v>46176</v>
       </c>
       <c r="B125" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C125">
-        <v>28.68951918518517</v>
+        <v>36.8289666508657</v>
       </c>
       <c r="D125">
-        <v>24.06134728453882</v>
+        <v>19.43137154505686</v>
       </c>
       <c r="E125">
-        <v>0.999503249</v>
+        <v>0.9994838199999998</v>
       </c>
       <c r="F125">
-        <v>0.999503249</v>
+        <v>0.9994838199999998</v>
       </c>
       <c r="G125">
-        <v>0.04983868243960732</v>
+        <v>0.2996471994933361</v>
       </c>
       <c r="H125">
-        <v>0.999503249</v>
+        <v>0.9984549499999998</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" s="1">
-        <v>46161</v>
+        <v>46177</v>
       </c>
       <c r="B126" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C126">
-        <v>28.31167386654059</v>
+        <v>36.76760036565858</v>
       </c>
       <c r="D126">
-        <v>23.75157719455474</v>
+        <v>18.98774474764188</v>
       </c>
       <c r="E126">
-        <v>1.000177331</v>
+        <v>0.99948384</v>
       </c>
       <c r="F126">
-        <v>1.000177331</v>
+        <v>0.99948384</v>
       </c>
       <c r="G126">
-        <v>0.04053938625111919</v>
+        <v>0.2807085470912787</v>
       </c>
       <c r="H126">
-        <v>1.000177331</v>
+        <v>0.9984696899999999</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" s="1">
-        <v>46162</v>
+        <v>46153</v>
       </c>
       <c r="B127" t="s">
         <v>15</v>
       </c>
       <c r="C127">
-        <v>28.57911382310097</v>
+        <v>28.12253390077671</v>
       </c>
       <c r="D127">
-        <v>23.89431741541233</v>
+        <v>23.58699683751922</v>
       </c>
       <c r="E127">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="F127">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="G127">
-        <v>0.04690190590044785</v>
+        <v>0.03368732240295347</v>
       </c>
       <c r="H127">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="1">
-        <v>46163</v>
+        <v>46154</v>
       </c>
       <c r="B128" t="s">
         <v>15</v>
       </c>
       <c r="C128">
-        <v>28.55785065378643</v>
+        <v>28.17715727830483</v>
       </c>
       <c r="D128">
-        <v>24.04274714970193</v>
+        <v>23.63894513078866</v>
       </c>
       <c r="E128">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="F128">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="G128">
-        <v>0.05228572319419666</v>
+        <v>0.03515547182056333</v>
       </c>
       <c r="H128">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="1">
-        <v>46164</v>
+        <v>46155</v>
       </c>
       <c r="B129" t="s">
         <v>15</v>
       </c>
       <c r="C129">
-        <v>28.50194638163107</v>
+        <v>28.59002627414054</v>
       </c>
       <c r="D129">
-        <v>23.99272397156045</v>
+        <v>23.96230704059692</v>
       </c>
       <c r="E129">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F129">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G129">
-        <v>0.04934923597154284</v>
+        <v>0.05179637495949674</v>
       </c>
       <c r="H129">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" s="1">
-        <v>46167</v>
+        <v>46156</v>
       </c>
       <c r="B130" t="s">
         <v>15</v>
       </c>
       <c r="C130">
-        <v>28.55106858744498</v>
+        <v>28.56217859389523</v>
       </c>
       <c r="D130">
-        <v>23.9768329565351</v>
+        <v>23.9411987302529</v>
       </c>
       <c r="E130">
         <v>1</v>
@@ -3777,7 +3777,7 @@
         <v>1</v>
       </c>
       <c r="G130">
-        <v>0.05571185335164408</v>
+        <v>0.04837024516756849</v>
       </c>
       <c r="H130">
         <v>1</v>
@@ -3785,652 +3785,886 @@
     </row>
     <row r="131" spans="1:8">
       <c r="A131" s="1">
-        <v>46168</v>
+        <v>46157</v>
       </c>
       <c r="B131" t="s">
         <v>15</v>
       </c>
       <c r="C131">
-        <v>28.54681541456266</v>
+        <v>28.57618675936338</v>
       </c>
       <c r="D131">
-        <v>23.97386168967948</v>
+        <v>23.9576220541054</v>
       </c>
       <c r="E131">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="F131">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="G131">
-        <v>0.04837034303541388</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H131">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="1">
-        <v>46169</v>
+        <v>46160</v>
       </c>
       <c r="B132" t="s">
         <v>15</v>
       </c>
       <c r="C132">
-        <v>28.83672936868491</v>
+        <v>28.68951918518517</v>
       </c>
       <c r="D132">
-        <v>24.203511281145</v>
+        <v>24.06134728453882</v>
       </c>
       <c r="E132">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="F132">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="G132">
-        <v>0.05962723282507953</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H132">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="1">
-        <v>46170</v>
+        <v>46161</v>
       </c>
       <c r="B133" t="s">
         <v>15</v>
       </c>
       <c r="C133">
-        <v>28.88109630394224</v>
+        <v>28.31167386654059</v>
       </c>
       <c r="D133">
-        <v>24.34085451035401</v>
+        <v>23.75157719455474</v>
       </c>
       <c r="E133">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
       <c r="F133">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
       <c r="G133">
-        <v>0.06647938938594877</v>
+        <v>0.04053938625111919</v>
       </c>
       <c r="H133">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="1">
-        <v>46171</v>
+        <v>46162</v>
       </c>
       <c r="B134" t="s">
         <v>15</v>
       </c>
       <c r="C134">
-        <v>28.92588622185229</v>
+        <v>28.57911382310097</v>
       </c>
       <c r="D134">
-        <v>24.37463012178961</v>
+        <v>23.89431741541233</v>
       </c>
       <c r="E134">
-        <v>0.9999999989999999</v>
+        <v>0.999503734</v>
       </c>
       <c r="F134">
-        <v>0.9999999989999999</v>
+        <v>0.999503734</v>
       </c>
       <c r="G134">
-        <v>0.0669687424559624</v>
+        <v>0.04690190590044785</v>
       </c>
       <c r="H134">
-        <v>0.9999999989999999</v>
+        <v>0.999503734</v>
       </c>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="1">
-        <v>46174</v>
+        <v>46163</v>
       </c>
       <c r="B135" t="s">
         <v>15</v>
       </c>
       <c r="C135">
-        <v>28.479823472488</v>
+        <v>28.55785065378643</v>
       </c>
       <c r="D135">
-        <v>23.940843604634</v>
+        <v>24.04274714970193</v>
       </c>
       <c r="E135">
-        <v>0.9999999999999999</v>
+        <v>1.000229282</v>
       </c>
       <c r="F135">
-        <v>0.9999999999999999</v>
+        <v>1.000229282</v>
       </c>
       <c r="G135">
-        <v>0.05385076946675693</v>
+        <v>0.05228572319419666</v>
       </c>
       <c r="H135">
-        <v>0.9999999999999999</v>
+        <v>1.000229282</v>
       </c>
     </row>
     <row r="136" spans="1:8">
       <c r="A136" s="1">
-        <v>46175</v>
+        <v>46164</v>
       </c>
       <c r="B136" t="s">
         <v>15</v>
       </c>
       <c r="C136">
-        <v>28.11501250979268</v>
+        <v>28.50194638163107</v>
       </c>
       <c r="D136">
-        <v>23.53470929078268</v>
+        <v>23.99272397156045</v>
       </c>
       <c r="E136">
-        <v>0.9999999989999999</v>
+        <v>1</v>
       </c>
       <c r="F136">
-        <v>0.9999999989999999</v>
+        <v>1</v>
       </c>
       <c r="G136">
-        <v>0.03476107722835287</v>
+        <v>0.04934923597154284</v>
       </c>
       <c r="H136">
-        <v>0.9999999989999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="1">
-        <v>46176</v>
+        <v>46167</v>
       </c>
       <c r="B137" t="s">
         <v>15</v>
       </c>
       <c r="C137">
-        <v>28.0115884668485</v>
+        <v>28.55106858744498</v>
       </c>
       <c r="D137">
-        <v>23.38620815625822</v>
+        <v>23.9768329565351</v>
       </c>
       <c r="E137">
-        <v>0.9993115890000001</v>
+        <v>1</v>
       </c>
       <c r="F137">
-        <v>0.9993115890000001</v>
+        <v>1</v>
       </c>
       <c r="G137">
-        <v>0.02105569185214828</v>
+        <v>0.05571185335164408</v>
       </c>
       <c r="H137">
-        <v>0.9993115890000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="1">
-        <v>46153</v>
+        <v>46168</v>
       </c>
       <c r="B138" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C138">
-        <v>40.68830633303975</v>
+        <v>28.54681541456266</v>
       </c>
       <c r="D138">
-        <v>21.50431773660198</v>
+        <v>23.97386168967948</v>
       </c>
       <c r="E138">
-        <v>0.99909852</v>
+        <v>1</v>
       </c>
       <c r="F138">
-        <v>0.99909852</v>
+        <v>1</v>
       </c>
       <c r="G138">
-        <v>0.2342423866086769</v>
+        <v>0.04837034303541388</v>
       </c>
       <c r="H138">
-        <v>0.9974930900000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="1">
-        <v>46154</v>
+        <v>46169</v>
       </c>
       <c r="B139" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C139">
-        <v>40.32854894972581</v>
+        <v>28.83672936868491</v>
       </c>
       <c r="D139">
-        <v>21.09133998298594</v>
+        <v>24.203511281145</v>
       </c>
       <c r="E139">
-        <v>0.9990972199999999</v>
+        <v>1</v>
       </c>
       <c r="F139">
-        <v>0.9990972199999999</v>
+        <v>1</v>
       </c>
       <c r="G139">
-        <v>0.2156468205051487</v>
+        <v>0.05962723282507953</v>
       </c>
       <c r="H139">
-        <v>0.99752223</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="1">
-        <v>46155</v>
+        <v>46170</v>
       </c>
       <c r="B140" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C140">
-        <v>40.47987921095815</v>
+        <v>28.88109630394224</v>
       </c>
       <c r="D140">
-        <v>21.35995364434454</v>
+        <v>24.34085451035401</v>
       </c>
       <c r="E140">
-        <v>0.9991780100000001</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F140">
-        <v>0.9991780100000001</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G140">
-        <v>0.2270956128473374</v>
+        <v>0.06647938938594877</v>
       </c>
       <c r="H140">
-        <v>0.9975825700000001</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="1">
-        <v>46156</v>
+        <v>46171</v>
       </c>
       <c r="B141" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C141">
-        <v>41.20436574895244</v>
+        <v>28.92588622185229</v>
       </c>
       <c r="D141">
-        <v>21.48149674387778</v>
+        <v>24.37463012178961</v>
       </c>
       <c r="E141">
-        <v>0.9991793299999999</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F141">
-        <v>0.9991793299999999</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G141">
-        <v>0.2454829228401052</v>
+        <v>0.0669687424559624</v>
       </c>
       <c r="H141">
-        <v>0.99754722</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="1">
-        <v>46157</v>
+        <v>46174</v>
       </c>
       <c r="B142" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C142">
-        <v>40.80613062958688</v>
+        <v>28.479823472488</v>
       </c>
       <c r="D142">
-        <v>21.08912555803936</v>
+        <v>23.940843604634</v>
       </c>
       <c r="E142">
-        <v>0.9991790600000001</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F142">
-        <v>0.9991790600000001</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G142">
-        <v>0.2230017445022556</v>
+        <v>0.05385076946675693</v>
       </c>
       <c r="H142">
-        <v>0.9975824700000002</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="1">
-        <v>46160</v>
+        <v>46175</v>
       </c>
       <c r="B143" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C143">
-        <v>40.11672876026724</v>
+        <v>28.11501250979268</v>
       </c>
       <c r="D143">
-        <v>20.79541439916316</v>
+        <v>23.53470929078268</v>
       </c>
       <c r="E143">
-        <v>0.999152</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F143">
-        <v>0.999152</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G143">
-        <v>0.2098184021536666</v>
+        <v>0.03476107722835287</v>
       </c>
       <c r="H143">
-        <v>0.9975007899999999</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="1">
-        <v>46161</v>
+        <v>46176</v>
       </c>
       <c r="B144" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C144">
-        <v>39.69086941528401</v>
+        <v>28.0115884668485</v>
       </c>
       <c r="D144">
-        <v>20.74924328599426</v>
+        <v>23.38620815625822</v>
       </c>
       <c r="E144">
-        <v>0.99914989</v>
+        <v>0.9993115890000001</v>
       </c>
       <c r="F144">
-        <v>0.99914989</v>
+        <v>0.9993115890000001</v>
       </c>
       <c r="G144">
-        <v>0.2020471776850241</v>
+        <v>0.02105569185214828</v>
       </c>
       <c r="H144">
-        <v>0.9974417</v>
+        <v>0.9993115890000001</v>
       </c>
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="1">
-        <v>46162</v>
+        <v>46177</v>
       </c>
       <c r="B145" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C145">
-        <v>40.37836787855562</v>
+        <v>28.38208530418455</v>
       </c>
       <c r="D145">
-        <v>21.11271132314188</v>
+        <v>23.57230416238753</v>
       </c>
       <c r="E145">
-        <v>0.99915058</v>
+        <v>1.000774061</v>
       </c>
       <c r="F145">
-        <v>0.99915058</v>
+        <v>1.000774061</v>
       </c>
       <c r="G145">
-        <v>0.2291077670847563</v>
+        <v>0.03133473088430172</v>
       </c>
       <c r="H145">
-        <v>0.9974415600000001</v>
+        <v>1.000774061</v>
       </c>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="1">
-        <v>46163</v>
+        <v>46153</v>
       </c>
       <c r="B146" t="s">
         <v>16</v>
       </c>
       <c r="C146">
-        <v>38.9123066967842</v>
+        <v>40.68830633303975</v>
       </c>
       <c r="D146">
-        <v>21.28910644207464</v>
+        <v>21.50431773660198</v>
       </c>
       <c r="E146">
-        <v>0.9989350699999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="F146">
-        <v>0.9989350699999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="G146">
-        <v>0.2392382040170877</v>
+        <v>0.2342423866086769</v>
       </c>
       <c r="H146">
-        <v>0.99726191</v>
+        <v>0.9974930900000001</v>
       </c>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="1">
-        <v>46164</v>
+        <v>46154</v>
       </c>
       <c r="B147" t="s">
         <v>16</v>
       </c>
       <c r="C147">
-        <v>39.43913909150694</v>
+        <v>40.32854894972581</v>
       </c>
       <c r="D147">
-        <v>21.05297617141148</v>
+        <v>21.09133998298594</v>
       </c>
       <c r="E147">
-        <v>0.999144</v>
+        <v>0.9990972199999999</v>
       </c>
       <c r="F147">
-        <v>0.999144</v>
+        <v>0.9990972199999999</v>
       </c>
       <c r="G147">
-        <v>0.2516582935428642</v>
+        <v>0.2156468205051487</v>
       </c>
       <c r="H147">
-        <v>0.9974678400000001</v>
+        <v>0.99752223</v>
       </c>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="1">
-        <v>46167</v>
+        <v>46155</v>
       </c>
       <c r="B148" t="s">
         <v>16</v>
       </c>
       <c r="C148">
-        <v>39.45782844313628</v>
+        <v>40.47987921095815</v>
       </c>
       <c r="D148">
-        <v>21.0518901572272</v>
+        <v>21.35995364434454</v>
       </c>
       <c r="E148">
-        <v>0.999144</v>
+        <v>0.9991780100000001</v>
       </c>
       <c r="F148">
-        <v>0.999144</v>
+        <v>0.9991780100000001</v>
       </c>
       <c r="G148">
-        <v>0.2516582935428642</v>
+        <v>0.2270956128473374</v>
       </c>
       <c r="H148">
-        <v>0.9974678400000001</v>
+        <v>0.9975825700000001</v>
       </c>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="1">
-        <v>46168</v>
+        <v>46156</v>
       </c>
       <c r="B149" t="s">
         <v>16</v>
       </c>
       <c r="C149">
-        <v>40.20219297984542</v>
+        <v>41.20436574895244</v>
       </c>
       <c r="D149">
-        <v>21.93106024403281</v>
+        <v>21.48149674387778</v>
       </c>
       <c r="E149">
-        <v>0.9991421799999999</v>
+        <v>0.9991793299999999</v>
       </c>
       <c r="F149">
-        <v>0.9991421799999999</v>
+        <v>0.9991793299999999</v>
       </c>
       <c r="G149">
-        <v>0.2846167552893293</v>
+        <v>0.2454829228401052</v>
       </c>
       <c r="H149">
-        <v>0.9974609800000001</v>
+        <v>0.99754722</v>
       </c>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" s="1">
-        <v>46169</v>
+        <v>46157</v>
       </c>
       <c r="B150" t="s">
         <v>16</v>
       </c>
       <c r="C150">
-        <v>40.34993865302093</v>
+        <v>40.80613062958688</v>
       </c>
       <c r="D150">
-        <v>21.65366031776487</v>
+        <v>21.08912555803936</v>
       </c>
       <c r="E150">
-        <v>0.9991434600000001</v>
+        <v>0.9991790600000001</v>
       </c>
       <c r="F150">
-        <v>0.9991434600000001</v>
+        <v>0.9991790600000001</v>
       </c>
       <c r="G150">
-        <v>0.2796902860011767</v>
+        <v>0.2230017445022556</v>
       </c>
       <c r="H150">
-        <v>0.9991434600000001</v>
+        <v>0.9975824700000002</v>
       </c>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="1">
-        <v>46170</v>
+        <v>46160</v>
       </c>
       <c r="B151" t="s">
         <v>16</v>
       </c>
       <c r="C151">
-        <v>40.5850485390846</v>
+        <v>40.11672876026724</v>
       </c>
       <c r="D151">
-        <v>21.75450977746074</v>
+        <v>20.79541439916316</v>
       </c>
       <c r="E151">
-        <v>0.99914592</v>
+        <v>0.999152</v>
       </c>
       <c r="F151">
-        <v>0.99914592</v>
+        <v>0.999152</v>
       </c>
       <c r="G151">
-        <v>0.2964818481030536</v>
+        <v>0.2098184021536666</v>
       </c>
       <c r="H151">
-        <v>0.99914592</v>
+        <v>0.9975007899999999</v>
       </c>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="1">
-        <v>46171</v>
+        <v>46161</v>
       </c>
       <c r="B152" t="s">
         <v>16</v>
       </c>
       <c r="C152">
-        <v>41.86785805184477</v>
+        <v>39.69086941528401</v>
       </c>
       <c r="D152">
-        <v>22.33589392797469</v>
+        <v>20.74924328599426</v>
       </c>
       <c r="E152">
-        <v>0.9991336999999999</v>
+        <v>0.99914989</v>
       </c>
       <c r="F152">
-        <v>0.9991336999999999</v>
+        <v>0.99914989</v>
       </c>
       <c r="G152">
-        <v>0.3254158954996882</v>
+        <v>0.2020471776850241</v>
       </c>
       <c r="H152">
-        <v>0.9991336999999999</v>
+        <v>0.9974417</v>
       </c>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" s="1">
-        <v>46174</v>
+        <v>46162</v>
       </c>
       <c r="B153" t="s">
         <v>16</v>
       </c>
       <c r="C153">
-        <v>42.82932322850974</v>
+        <v>40.37836787855562</v>
       </c>
       <c r="D153">
-        <v>22.98998911430362</v>
+        <v>21.11271132314188</v>
       </c>
       <c r="E153">
-        <v>0.99914238</v>
+        <v>0.99915058</v>
       </c>
       <c r="F153">
-        <v>0.99914238</v>
+        <v>0.99915058</v>
       </c>
       <c r="G153">
-        <v>0.3583049032509023</v>
+        <v>0.2291077670847563</v>
       </c>
       <c r="H153">
-        <v>0.99914238</v>
+        <v>0.9974415600000001</v>
       </c>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" s="1">
-        <v>46175</v>
+        <v>46163</v>
       </c>
       <c r="B154" t="s">
         <v>16</v>
       </c>
       <c r="C154">
-        <v>43.11872937189534</v>
+        <v>38.9123066967842</v>
       </c>
       <c r="D154">
-        <v>22.90628380907704</v>
+        <v>21.28910644207464</v>
       </c>
       <c r="E154">
-        <v>0.9990972800000002</v>
+        <v>0.9989350699999999</v>
       </c>
       <c r="F154">
-        <v>0.9990972800000002</v>
+        <v>0.9989350699999999</v>
       </c>
       <c r="G154">
-        <v>0.3753046155885469</v>
+        <v>0.2392382040170877</v>
       </c>
       <c r="H154">
-        <v>0.9990972800000002</v>
+        <v>0.99726191</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" s="1">
-        <v>46176</v>
+        <v>46164</v>
       </c>
       <c r="B155" t="s">
         <v>16</v>
       </c>
       <c r="C155">
+        <v>39.43913909150694</v>
+      </c>
+      <c r="D155">
+        <v>21.05297617141148</v>
+      </c>
+      <c r="E155">
+        <v>0.999144</v>
+      </c>
+      <c r="F155">
+        <v>0.999144</v>
+      </c>
+      <c r="G155">
+        <v>0.2516582935428642</v>
+      </c>
+      <c r="H155">
+        <v>0.9974678400000001</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8">
+      <c r="A156" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156">
+        <v>39.45782844313628</v>
+      </c>
+      <c r="D156">
+        <v>21.0518901572272</v>
+      </c>
+      <c r="E156">
+        <v>0.999144</v>
+      </c>
+      <c r="F156">
+        <v>0.999144</v>
+      </c>
+      <c r="G156">
+        <v>0.2516582935428642</v>
+      </c>
+      <c r="H156">
+        <v>0.9974678400000001</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8">
+      <c r="A157" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157">
+        <v>40.20219297984542</v>
+      </c>
+      <c r="D157">
+        <v>21.93106024403281</v>
+      </c>
+      <c r="E157">
+        <v>0.9991421799999999</v>
+      </c>
+      <c r="F157">
+        <v>0.9991421799999999</v>
+      </c>
+      <c r="G157">
+        <v>0.2846167552893293</v>
+      </c>
+      <c r="H157">
+        <v>0.9974609800000001</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8">
+      <c r="A158" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158">
+        <v>40.34993865302093</v>
+      </c>
+      <c r="D158">
+        <v>21.65366031776487</v>
+      </c>
+      <c r="E158">
+        <v>0.9991434600000001</v>
+      </c>
+      <c r="F158">
+        <v>0.9991434600000001</v>
+      </c>
+      <c r="G158">
+        <v>0.2796902860011767</v>
+      </c>
+      <c r="H158">
+        <v>0.9991434600000001</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8">
+      <c r="A159" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159">
+        <v>40.5850485390846</v>
+      </c>
+      <c r="D159">
+        <v>21.75450977746074</v>
+      </c>
+      <c r="E159">
+        <v>0.99914592</v>
+      </c>
+      <c r="F159">
+        <v>0.99914592</v>
+      </c>
+      <c r="G159">
+        <v>0.2964818481030536</v>
+      </c>
+      <c r="H159">
+        <v>0.99914592</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8">
+      <c r="A160" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160">
+        <v>41.86785805184477</v>
+      </c>
+      <c r="D160">
+        <v>22.33589392797469</v>
+      </c>
+      <c r="E160">
+        <v>0.9991336999999999</v>
+      </c>
+      <c r="F160">
+        <v>0.9991336999999999</v>
+      </c>
+      <c r="G160">
+        <v>0.3254158954996882</v>
+      </c>
+      <c r="H160">
+        <v>0.9991336999999999</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8">
+      <c r="A161" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161">
+        <v>42.82932322850974</v>
+      </c>
+      <c r="D161">
+        <v>22.98998911430362</v>
+      </c>
+      <c r="E161">
+        <v>0.99914238</v>
+      </c>
+      <c r="F161">
+        <v>0.99914238</v>
+      </c>
+      <c r="G161">
+        <v>0.3583049032509023</v>
+      </c>
+      <c r="H161">
+        <v>0.99914238</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8">
+      <c r="A162" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162">
+        <v>43.11872937189534</v>
+      </c>
+      <c r="D162">
+        <v>22.90628380907704</v>
+      </c>
+      <c r="E162">
+        <v>0.9990972800000002</v>
+      </c>
+      <c r="F162">
+        <v>0.9990972800000002</v>
+      </c>
+      <c r="G162">
+        <v>0.3753046155885469</v>
+      </c>
+      <c r="H162">
+        <v>0.9990972800000002</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8">
+      <c r="A163" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163">
         <v>42.86143001679577</v>
       </c>
-      <c r="D155">
+      <c r="D163">
         <v>22.72053012591219</v>
       </c>
-      <c r="E155">
+      <c r="E163">
         <v>0.9990984299999999</v>
       </c>
-      <c r="F155">
+      <c r="F163">
         <v>0.9990984299999999</v>
       </c>
-      <c r="G155">
+      <c r="G163">
         <v>0.3615660647779204</v>
       </c>
-      <c r="H155">
+      <c r="H163">
         <v>0.9990984299999999</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8">
+      <c r="A164" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164">
+        <v>42.57902095847519</v>
+      </c>
+      <c r="D164">
+        <v>22.20304338566557</v>
+      </c>
+      <c r="E164">
+        <v>0.9990006900000001</v>
+      </c>
+      <c r="F164">
+        <v>0.9990006900000001</v>
+      </c>
+      <c r="G164">
+        <v>0.34033389372967</v>
+      </c>
+      <c r="H164">
+        <v>0.9990006900000001</v>
       </c>
     </row>
   </sheetData>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="17">
   <si>
     <t>Date</t>
   </si>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H164"/>
+  <dimension ref="A1:H173"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -743,42 +743,42 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1">
-        <v>46153</v>
+        <v>46178</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14">
-        <v>53.14833755912058</v>
+        <v>24.23525994891068</v>
       </c>
       <c r="D14">
-        <v>25.84885448407537</v>
+        <v>16.19071928045521</v>
       </c>
       <c r="E14">
-        <v>0.9262</v>
+        <v>0.8611</v>
       </c>
       <c r="F14">
-        <v>0.9262</v>
+        <v>0.8611</v>
       </c>
       <c r="G14">
-        <v>0.3839084462043663</v>
+        <v>0.5010763775801161</v>
       </c>
       <c r="H14">
-        <v>0.9262</v>
+        <v>0.9132</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
       </c>
       <c r="C15">
-        <v>51.82921169635205</v>
+        <v>53.14833755912058</v>
       </c>
       <c r="D15">
-        <v>25.32805827181975</v>
+        <v>25.84885448407537</v>
       </c>
       <c r="E15">
         <v>0.9262</v>
@@ -787,7 +787,7 @@
         <v>0.9262</v>
       </c>
       <c r="G15">
-        <v>0.3568580281685669</v>
+        <v>0.3839084462043663</v>
       </c>
       <c r="H15">
         <v>0.9262</v>
@@ -795,120 +795,120 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
       </c>
       <c r="C16">
-        <v>52.28471716753184</v>
+        <v>51.82921169635205</v>
       </c>
       <c r="D16">
-        <v>25.54525144150689</v>
+        <v>25.32805827181975</v>
       </c>
       <c r="E16">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="F16">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="G16">
-        <v>0.378012896547947</v>
+        <v>0.3568580281685669</v>
       </c>
       <c r="H16">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
       </c>
       <c r="C17">
-        <v>53.87287273813902</v>
+        <v>52.28471716753184</v>
       </c>
       <c r="D17">
-        <v>26.32154226438612</v>
+        <v>25.54525144150689</v>
       </c>
       <c r="E17">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="F17">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="G17">
-        <v>0.4166811087612758</v>
+        <v>0.378012896547947</v>
       </c>
       <c r="H17">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="B18" t="s">
         <v>9</v>
       </c>
       <c r="C18">
-        <v>52.18747148214074</v>
+        <v>53.87287273813902</v>
       </c>
       <c r="D18">
-        <v>25.13616059644496</v>
+        <v>26.32154226438612</v>
       </c>
       <c r="E18">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="F18">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="G18">
-        <v>0.3627535778249862</v>
+        <v>0.4166811087612758</v>
       </c>
       <c r="H18">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="B19" t="s">
         <v>9</v>
       </c>
       <c r="C19">
-        <v>50.72035274995172</v>
+        <v>52.18747148214074</v>
       </c>
       <c r="D19">
-        <v>24.61756040386634</v>
+        <v>25.13616059644496</v>
       </c>
       <c r="E19">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="F19">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="G19">
         <v>0.3627535778249862</v>
       </c>
       <c r="H19">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="B20" t="s">
         <v>9</v>
       </c>
       <c r="C20">
-        <v>50.11981086673613</v>
+        <v>50.72035274995172</v>
       </c>
       <c r="D20">
-        <v>24.13061679021705</v>
+        <v>24.61756040386634</v>
       </c>
       <c r="E20">
         <v>0.9259000000000001</v>
@@ -917,7 +917,7 @@
         <v>0.9259000000000001</v>
       </c>
       <c r="G20">
-        <v>0.3258193430227221</v>
+        <v>0.3627535778249862</v>
       </c>
       <c r="H20">
         <v>0.9259000000000001</v>
@@ -925,120 +925,120 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="B21" t="s">
         <v>9</v>
       </c>
       <c r="C21">
-        <v>51.74165648409151</v>
+        <v>50.11981086673613</v>
       </c>
       <c r="D21">
-        <v>24.98091384114761</v>
+        <v>24.13061679021705</v>
       </c>
       <c r="E21">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="F21">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="G21">
-        <v>0.3818277262286871</v>
+        <v>0.3258193430227221</v>
       </c>
       <c r="H21">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="B22" t="s">
         <v>9</v>
       </c>
       <c r="C22">
-        <v>49.13455894175823</v>
+        <v>51.74165648409151</v>
       </c>
       <c r="D22">
-        <v>25.30005057653127</v>
+        <v>24.98091384114761</v>
       </c>
       <c r="E22">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="F22">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="G22">
-        <v>0.4028091571787618</v>
+        <v>0.3818277262286871</v>
       </c>
       <c r="H22">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="B23" t="s">
         <v>9</v>
       </c>
       <c r="C23">
-        <v>49.57776597479297</v>
+        <v>49.13455894175823</v>
       </c>
       <c r="D23">
-        <v>25.04906725563518</v>
+        <v>25.30005057653127</v>
       </c>
       <c r="E23">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="F23">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="G23">
-        <v>0.4256980029692063</v>
+        <v>0.4028091571787618</v>
       </c>
       <c r="H23">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="B24" t="s">
         <v>9</v>
       </c>
       <c r="C24">
-        <v>49.71239596645896</v>
+        <v>49.57776597479297</v>
       </c>
       <c r="D24">
-        <v>25.18778610744295</v>
+        <v>25.04906725563518</v>
       </c>
       <c r="E24">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="F24">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="G24">
-        <v>0.4525749835757003</v>
+        <v>0.4256980029692063</v>
       </c>
       <c r="H24">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
       </c>
       <c r="C25">
-        <v>50.77166277510776</v>
+        <v>49.71239596645896</v>
       </c>
       <c r="D25">
-        <v>25.7431782858765</v>
+        <v>25.18778610744295</v>
       </c>
       <c r="E25">
         <v>0.9231999999999999</v>
@@ -1047,7 +1047,7 @@
         <v>0.9231999999999999</v>
       </c>
       <c r="G25">
-        <v>0.4700884597036457</v>
+        <v>0.4525749835757003</v>
       </c>
       <c r="H25">
         <v>0.9231999999999999</v>
@@ -1055,120 +1055,120 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1">
-        <v>46169</v>
+        <v>46168</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
       </c>
       <c r="C26">
-        <v>50.57689164833899</v>
+        <v>50.77166277510776</v>
       </c>
       <c r="D26">
-        <v>25.70244067238947</v>
+        <v>25.7431782858765</v>
       </c>
       <c r="E26">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="F26">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="G26">
-        <v>0.4518814984464716</v>
+        <v>0.4700884597036457</v>
       </c>
       <c r="H26">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="B27" t="s">
         <v>9</v>
       </c>
       <c r="C27">
-        <v>50.80027854822009</v>
+        <v>50.57689164833899</v>
       </c>
       <c r="D27">
-        <v>25.90068415792015</v>
+        <v>25.70244067238947</v>
       </c>
       <c r="E27">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
       <c r="F27">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
       <c r="G27">
-        <v>0.4699150222743402</v>
+        <v>0.4518814984464716</v>
       </c>
       <c r="H27">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="B28" t="s">
         <v>9</v>
       </c>
       <c r="C28">
-        <v>51.44563447241545</v>
+        <v>50.80027854822009</v>
       </c>
       <c r="D28">
-        <v>26.0970978996374</v>
+        <v>25.90068415792015</v>
       </c>
       <c r="E28">
-        <v>0.9246</v>
+        <v>0.9231</v>
       </c>
       <c r="F28">
-        <v>0.9246</v>
+        <v>0.9231</v>
       </c>
       <c r="G28">
-        <v>0.4791053539115764</v>
+        <v>0.4699150222743402</v>
       </c>
       <c r="H28">
-        <v>0.9246</v>
+        <v>0.9231</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1">
-        <v>46174</v>
+        <v>46171</v>
       </c>
       <c r="B29" t="s">
         <v>9</v>
       </c>
       <c r="C29">
-        <v>53.05792083471825</v>
+        <v>51.44563447241545</v>
       </c>
       <c r="D29">
-        <v>26.86242981002239</v>
+        <v>26.0970978996374</v>
       </c>
       <c r="E29">
-        <v>0.9254999999999999</v>
+        <v>0.9246</v>
       </c>
       <c r="F29">
-        <v>0.9254999999999999</v>
+        <v>0.9246</v>
       </c>
       <c r="G29">
-        <v>0.5306051577195796</v>
+        <v>0.4791053539115764</v>
       </c>
       <c r="H29">
-        <v>0.9254999999999999</v>
+        <v>0.9246</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="B30" t="s">
         <v>9</v>
       </c>
       <c r="C30">
-        <v>54.38946369031042</v>
+        <v>53.05792083471825</v>
       </c>
       <c r="D30">
-        <v>27.57160808325711</v>
+        <v>26.86242981002239</v>
       </c>
       <c r="E30">
         <v>0.9254999999999999</v>
@@ -1177,7 +1177,7 @@
         <v>0.9254999999999999</v>
       </c>
       <c r="G30">
-        <v>0.5845326886558693</v>
+        <v>0.5306051577195796</v>
       </c>
       <c r="H30">
         <v>0.9254999999999999</v>
@@ -1185,198 +1185,198 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="B31" t="s">
         <v>9</v>
       </c>
       <c r="C31">
-        <v>54.35279063045283</v>
+        <v>54.38946369031042</v>
       </c>
       <c r="D31">
-        <v>27.50874919819178</v>
+        <v>27.57160808325711</v>
       </c>
       <c r="E31">
-        <v>0.9162000000000001</v>
+        <v>0.9254999999999999</v>
       </c>
       <c r="F31">
-        <v>0.9162000000000001</v>
+        <v>0.9254999999999999</v>
       </c>
       <c r="G31">
-        <v>0.5992718273849102</v>
+        <v>0.5845326886558693</v>
       </c>
       <c r="H31">
-        <v>0.9162000000000001</v>
+        <v>0.9254999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="B32" t="s">
         <v>9</v>
       </c>
       <c r="C32">
-        <v>53.45790968334249</v>
+        <v>54.35279063045283</v>
       </c>
       <c r="D32">
-        <v>26.99486187834476</v>
+        <v>27.50874919819178</v>
       </c>
       <c r="E32">
-        <v>0.9154000000000001</v>
+        <v>0.9162000000000001</v>
       </c>
       <c r="F32">
-        <v>0.9154000000000001</v>
+        <v>0.9162000000000001</v>
       </c>
       <c r="G32">
-        <v>0.5691000647975994</v>
+        <v>0.5992718273849102</v>
       </c>
       <c r="H32">
-        <v>0.9154000000000001</v>
+        <v>0.9162000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1">
-        <v>46153</v>
+        <v>46177</v>
       </c>
       <c r="B33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C33">
-        <v>34.64560932909123</v>
+        <v>53.45790968334249</v>
       </c>
       <c r="D33">
-        <v>26.08311546080494</v>
+        <v>26.99486187834476</v>
       </c>
       <c r="E33">
-        <v>0.9983000000000001</v>
+        <v>0.9154000000000001</v>
       </c>
       <c r="F33">
-        <v>0.9983000000000001</v>
+        <v>0.9154000000000001</v>
       </c>
       <c r="G33">
-        <v>0.06258613715048233</v>
+        <v>0.5691000647975994</v>
       </c>
       <c r="H33">
-        <v>0.9983000000000001</v>
+        <v>0.9154000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1">
-        <v>46154</v>
+        <v>46178</v>
       </c>
       <c r="B34" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C34">
-        <v>34.50204921141101</v>
+        <v>52.01314444713902</v>
       </c>
       <c r="D34">
-        <v>25.94535229304585</v>
+        <v>25.48849727916627</v>
       </c>
       <c r="E34">
-        <v>0.9984</v>
+        <v>0.9142999999999999</v>
       </c>
       <c r="F34">
-        <v>0.9984</v>
+        <v>0.9142999999999999</v>
       </c>
       <c r="G34">
-        <v>0.05768943168306073</v>
+        <v>0.4380094145699611</v>
       </c>
       <c r="H34">
-        <v>0.9984</v>
+        <v>0.9142999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="B35" t="s">
         <v>10</v>
       </c>
       <c r="C35">
-        <v>35.10429483281073</v>
+        <v>34.64560932909123</v>
       </c>
       <c r="D35">
-        <v>26.43864879939599</v>
+        <v>26.08311546080494</v>
       </c>
       <c r="E35">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="F35">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="G35">
-        <v>0.07926550001722021</v>
+        <v>0.06258613715048233</v>
       </c>
       <c r="H35">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="B36" t="s">
         <v>10</v>
       </c>
       <c r="C36">
-        <v>35.36860632820093</v>
+        <v>34.50204921141101</v>
       </c>
       <c r="D36">
-        <v>26.56575571102338</v>
+        <v>25.94535229304585</v>
       </c>
       <c r="E36">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F36">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G36">
-        <v>0.08553946591902095</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H36">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="B37" t="s">
         <v>10</v>
       </c>
       <c r="C37">
-        <v>34.88080083527914</v>
+        <v>35.10429483281073</v>
       </c>
       <c r="D37">
-        <v>26.19322945679072</v>
+        <v>26.43864879939599</v>
       </c>
       <c r="E37">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="F37">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="G37">
-        <v>0.06870693142475881</v>
+        <v>0.07926550001722021</v>
       </c>
       <c r="H37">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1">
-        <v>46160</v>
+        <v>46156</v>
       </c>
       <c r="B38" t="s">
         <v>10</v>
       </c>
       <c r="C38">
-        <v>34.67638692539213</v>
+        <v>35.36860632820093</v>
       </c>
       <c r="D38">
-        <v>26.06707890342319</v>
+        <v>26.56575571102338</v>
       </c>
       <c r="E38">
         <v>0.9985999999999999</v>
@@ -1385,7 +1385,7 @@
         <v>0.9985999999999999</v>
       </c>
       <c r="G38">
-        <v>0.06289213016552919</v>
+        <v>0.08553946591902095</v>
       </c>
       <c r="H38">
         <v>0.9985999999999999</v>
@@ -1393,120 +1393,120 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="B39" t="s">
         <v>10</v>
       </c>
       <c r="C39">
-        <v>34.21212662725402</v>
+        <v>34.88080083527914</v>
       </c>
       <c r="D39">
-        <v>25.60349394367002</v>
+        <v>26.19322945679072</v>
       </c>
       <c r="E39">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="F39">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="G39">
-        <v>0.0486610616591685</v>
+        <v>0.06870693142475881</v>
       </c>
       <c r="H39">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="B40" t="s">
         <v>10</v>
       </c>
       <c r="C40">
-        <v>34.78598436564941</v>
+        <v>34.67638692539213</v>
       </c>
       <c r="D40">
-        <v>25.95505316769806</v>
+        <v>26.06707890342319</v>
       </c>
       <c r="E40">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="F40">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="G40">
-        <v>0.06335117806143331</v>
+        <v>0.06289213016552919</v>
       </c>
       <c r="H40">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1">
-        <v>46163</v>
+        <v>46161</v>
       </c>
       <c r="B41" t="s">
         <v>10</v>
       </c>
       <c r="C41">
-        <v>33.4539909056227</v>
+        <v>34.21212662725402</v>
       </c>
       <c r="D41">
-        <v>25.96014535427112</v>
+        <v>25.60349394367002</v>
       </c>
       <c r="E41">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="F41">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="G41">
-        <v>0.06350423294229035</v>
+        <v>0.0486610616591685</v>
       </c>
       <c r="H41">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1">
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="B42" t="s">
         <v>10</v>
       </c>
       <c r="C42">
-        <v>33.24951933563993</v>
+        <v>34.78598436564941</v>
       </c>
       <c r="D42">
-        <v>25.46629530314992</v>
+        <v>25.95505316769806</v>
       </c>
       <c r="E42">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="F42">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="G42">
-        <v>0.06136193159696024</v>
+        <v>0.06335117806143331</v>
       </c>
       <c r="H42">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1">
-        <v>46167</v>
+        <v>46163</v>
       </c>
       <c r="B43" t="s">
         <v>10</v>
       </c>
       <c r="C43">
-        <v>33.29896419867477</v>
+        <v>33.4539909056227</v>
       </c>
       <c r="D43">
-        <v>25.45090185337973</v>
+        <v>25.96014535427112</v>
       </c>
       <c r="E43">
         <v>0.9984</v>
@@ -1515,7 +1515,7 @@
         <v>0.9984</v>
       </c>
       <c r="G43">
-        <v>0.06136193159696024</v>
+        <v>0.06350423294229035</v>
       </c>
       <c r="H43">
         <v>0.9984</v>
@@ -1523,16 +1523,16 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1">
-        <v>46168</v>
+        <v>46164</v>
       </c>
       <c r="B44" t="s">
         <v>10</v>
       </c>
       <c r="C44">
-        <v>33.41270923608511</v>
+        <v>33.24951933563993</v>
       </c>
       <c r="D44">
-        <v>25.54156152389702</v>
+        <v>25.46629530314992</v>
       </c>
       <c r="E44">
         <v>0.9984</v>
@@ -1541,7 +1541,7 @@
         <v>0.9984</v>
       </c>
       <c r="G44">
-        <v>0.06549347940676342</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H44">
         <v>0.9984</v>
@@ -1549,822 +1549,822 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1">
-        <v>46169</v>
+        <v>46167</v>
       </c>
       <c r="B45" t="s">
         <v>10</v>
       </c>
       <c r="C45">
-        <v>33.73350746548562</v>
+        <v>33.29896419867477</v>
       </c>
       <c r="D45">
-        <v>25.75393367034243</v>
+        <v>25.45090185337973</v>
       </c>
       <c r="E45">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="F45">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="G45">
-        <v>0.07620510288008187</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H45">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1">
-        <v>46170</v>
+        <v>46168</v>
       </c>
       <c r="B46" t="s">
         <v>10</v>
       </c>
       <c r="C46">
-        <v>33.84336414535104</v>
+        <v>33.41270923608511</v>
       </c>
       <c r="D46">
-        <v>25.97168203877208</v>
+        <v>25.54156152389702</v>
       </c>
       <c r="E46">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
       <c r="F46">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
       <c r="G46">
-        <v>0.0844683152463559</v>
+        <v>0.06549347940676342</v>
       </c>
       <c r="H46">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1">
-        <v>46171</v>
+        <v>46169</v>
       </c>
       <c r="B47" t="s">
         <v>10</v>
       </c>
       <c r="C47">
-        <v>33.73370320039719</v>
+        <v>33.73350746548562</v>
       </c>
       <c r="D47">
-        <v>25.880209881309</v>
+        <v>25.75393367034243</v>
       </c>
       <c r="E47">
-        <v>0.9988</v>
+        <v>0.9987000000000001</v>
       </c>
       <c r="F47">
-        <v>0.9988</v>
+        <v>0.9987000000000001</v>
       </c>
       <c r="G47">
-        <v>0.08201990413931148</v>
+        <v>0.07620510288008187</v>
       </c>
       <c r="H47">
-        <v>0.9988</v>
+        <v>0.9987000000000001</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1">
-        <v>46174</v>
+        <v>46170</v>
       </c>
       <c r="B48" t="s">
         <v>10</v>
       </c>
       <c r="C48">
-        <v>33.45546240777382</v>
+        <v>33.84336414535104</v>
       </c>
       <c r="D48">
-        <v>25.61350381215703</v>
+        <v>25.97168203877208</v>
       </c>
       <c r="E48">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
       <c r="F48">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
       <c r="G48">
-        <v>0.06901304118647311</v>
+        <v>0.0844683152463559</v>
       </c>
       <c r="H48">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1">
-        <v>46175</v>
+        <v>46171</v>
       </c>
       <c r="B49" t="s">
         <v>10</v>
       </c>
       <c r="C49">
-        <v>33.31245255516097</v>
+        <v>33.73370320039719</v>
       </c>
       <c r="D49">
-        <v>25.36461330330757</v>
+        <v>25.880209881309</v>
       </c>
       <c r="E49">
-        <v>0.9989999999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="F49">
-        <v>0.9989999999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="G49">
-        <v>0.05845447259401171</v>
+        <v>0.08201990413931148</v>
       </c>
       <c r="H49">
-        <v>0.9989999999999999</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="B50" t="s">
         <v>10</v>
       </c>
       <c r="C50">
-        <v>33.02444632653544</v>
+        <v>33.45546240777382</v>
       </c>
       <c r="D50">
-        <v>25.07926152561908</v>
+        <v>25.61350381215703</v>
       </c>
       <c r="E50">
-        <v>0.9991</v>
+        <v>0.999</v>
       </c>
       <c r="F50">
-        <v>0.9991</v>
+        <v>0.999</v>
       </c>
       <c r="G50">
-        <v>0.04697780820974229</v>
+        <v>0.06901304118647311</v>
       </c>
       <c r="H50">
-        <v>0.9991</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1">
-        <v>46177</v>
+        <v>46175</v>
       </c>
       <c r="B51" t="s">
         <v>10</v>
       </c>
       <c r="C51">
-        <v>33.50291463064395</v>
+        <v>33.31245255516097</v>
       </c>
       <c r="D51">
-        <v>25.33002193941023</v>
+        <v>25.36461330330757</v>
       </c>
       <c r="E51">
-        <v>0.9991000000000001</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="F51">
-        <v>0.9991000000000001</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="G51">
-        <v>0.05768943168306073</v>
+        <v>0.05845447259401171</v>
       </c>
       <c r="H51">
-        <v>0.9991000000000001</v>
+        <v>0.9989999999999999</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1">
-        <v>46153</v>
+        <v>46176</v>
       </c>
       <c r="B52" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C52">
-        <v>36.55790859258162</v>
+        <v>33.02444632653544</v>
       </c>
       <c r="D52">
-        <v>22.67181120908155</v>
+        <v>25.07926152561908</v>
       </c>
       <c r="E52">
-        <v>0.9990740999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F52">
-        <v>0.9990740999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G52">
-        <v>0.1648443271746771</v>
+        <v>0.04697780820974229</v>
       </c>
       <c r="H52">
-        <v>0.9990740999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1">
-        <v>46154</v>
+        <v>46177</v>
       </c>
       <c r="B53" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C53">
-        <v>36.44753722959613</v>
+        <v>33.50291463064395</v>
       </c>
       <c r="D53">
-        <v>22.40292401789388</v>
+        <v>25.33002193941023</v>
       </c>
       <c r="E53">
-        <v>0.9990772499999999</v>
+        <v>0.9991000000000001</v>
       </c>
       <c r="F53">
-        <v>0.9990772499999999</v>
+        <v>0.9991000000000001</v>
       </c>
       <c r="G53">
-        <v>0.154964342628132</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H53">
-        <v>0.9990772499999999</v>
+        <v>0.9991000000000001</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1">
-        <v>46155</v>
+        <v>46178</v>
       </c>
       <c r="B54" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C54">
-        <v>36.63128514035871</v>
+        <v>32.19021336116872</v>
       </c>
       <c r="D54">
-        <v>22.65773388934668</v>
+        <v>24.38570557505481</v>
       </c>
       <c r="E54">
-        <v>0.99907745</v>
+        <v>0.9991</v>
       </c>
       <c r="F54">
-        <v>0.99907745</v>
+        <v>0.9991</v>
       </c>
       <c r="G54">
-        <v>0.1671633421405267</v>
+        <v>0.01775063028607016</v>
       </c>
       <c r="H54">
-        <v>0.99907745</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="B55" t="s">
         <v>11</v>
       </c>
       <c r="C55">
-        <v>36.87865927427314</v>
+        <v>36.55790859258162</v>
       </c>
       <c r="D55">
-        <v>22.69755646854794</v>
+        <v>22.67181120908155</v>
       </c>
       <c r="E55">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="F55">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="G55">
-        <v>0.1754592080224002</v>
+        <v>0.1648443271746771</v>
       </c>
       <c r="H55">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="B56" t="s">
         <v>11</v>
       </c>
       <c r="C56">
-        <v>36.52208783231286</v>
+        <v>36.44753722959613</v>
       </c>
       <c r="D56">
-        <v>22.32462309676992</v>
+        <v>22.40292401789388</v>
       </c>
       <c r="E56">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="F56">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="G56">
-        <v>0.1577242156354994</v>
+        <v>0.154964342628132</v>
       </c>
       <c r="H56">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="B57" t="s">
         <v>11</v>
       </c>
       <c r="C57">
-        <v>36.25604200674668</v>
+        <v>36.63128514035871</v>
       </c>
       <c r="D57">
-        <v>22.16555007468561</v>
+        <v>22.65773388934668</v>
       </c>
       <c r="E57">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="F57">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="G57">
-        <v>0.1527434068648266</v>
+        <v>0.1671633421405267</v>
       </c>
       <c r="H57">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1">
-        <v>46161</v>
+        <v>46156</v>
       </c>
       <c r="B58" t="s">
         <v>11</v>
       </c>
       <c r="C58">
-        <v>36.01040085730018</v>
+        <v>36.87865927427314</v>
       </c>
       <c r="D58">
-        <v>22.19475589056387</v>
+        <v>22.69755646854794</v>
       </c>
       <c r="E58">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="F58">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="G58">
-        <v>0.1456396418594061</v>
+        <v>0.1754592080224002</v>
       </c>
       <c r="H58">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1">
-        <v>46162</v>
+        <v>46157</v>
       </c>
       <c r="B59" t="s">
         <v>11</v>
       </c>
       <c r="C59">
-        <v>36.45290912796982</v>
+        <v>36.52208783231286</v>
       </c>
       <c r="D59">
-        <v>22.46357594746874</v>
+        <v>22.32462309676992</v>
       </c>
       <c r="E59">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="F59">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="G59">
-        <v>0.1646157747240327</v>
+        <v>0.1577242156354994</v>
       </c>
       <c r="H59">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1">
-        <v>46163</v>
+        <v>46160</v>
       </c>
       <c r="B60" t="s">
         <v>11</v>
       </c>
       <c r="C60">
-        <v>35.75282090566891</v>
+        <v>36.25604200674668</v>
       </c>
       <c r="D60">
-        <v>22.57615417310648</v>
+        <v>22.16555007468561</v>
       </c>
       <c r="E60">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="F60">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="G60">
-        <v>0.1668367104873381</v>
+        <v>0.1527434068648266</v>
       </c>
       <c r="H60">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1">
-        <v>46164</v>
+        <v>46161</v>
       </c>
       <c r="B61" t="s">
         <v>11</v>
       </c>
       <c r="C61">
-        <v>35.75514940724808</v>
+        <v>36.01040085730018</v>
       </c>
       <c r="D61">
-        <v>22.28880693466429</v>
+        <v>22.19475589056387</v>
       </c>
       <c r="E61">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="F61">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="G61">
-        <v>0.1717848261904962</v>
+        <v>0.1456396418594061</v>
       </c>
       <c r="H61">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1">
-        <v>46167</v>
+        <v>46162</v>
       </c>
       <c r="B62" t="s">
         <v>11</v>
       </c>
       <c r="C62">
-        <v>35.84133099010302</v>
+        <v>36.45290912796982</v>
       </c>
       <c r="D62">
-        <v>22.37458514769363</v>
+        <v>22.46357594746874</v>
       </c>
       <c r="E62">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="F62">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="G62">
-        <v>0.1717848261904962</v>
+        <v>0.1646157747240327</v>
       </c>
       <c r="H62">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1">
-        <v>46168</v>
+        <v>46163</v>
       </c>
       <c r="B63" t="s">
         <v>11</v>
       </c>
       <c r="C63">
-        <v>36.23214279739292</v>
+        <v>35.75282090566891</v>
       </c>
       <c r="D63">
-        <v>22.93484792820123</v>
+        <v>22.57615417310648</v>
       </c>
       <c r="E63">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
       <c r="F63">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
       <c r="G63">
-        <v>0.1925900763781823</v>
+        <v>0.1668367104873381</v>
       </c>
       <c r="H63">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="B64" t="s">
         <v>11</v>
       </c>
       <c r="C64">
-        <v>36.4336692499184</v>
+        <v>35.75514940724808</v>
       </c>
       <c r="D64">
-        <v>22.75940954009856</v>
+        <v>22.28880693466429</v>
       </c>
       <c r="E64">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="F64">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="G64">
-        <v>0.1912346098381414</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H64">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="B65" t="s">
         <v>11</v>
       </c>
       <c r="C65">
-        <v>36.57358557066742</v>
+        <v>35.84133099010302</v>
       </c>
       <c r="D65">
-        <v>22.83069636955243</v>
+        <v>22.37458514769363</v>
       </c>
       <c r="E65">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="F65">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="G65">
-        <v>0.2012778603742877</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H65">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1">
-        <v>46171</v>
+        <v>46168</v>
       </c>
       <c r="B66" t="s">
         <v>11</v>
       </c>
       <c r="C66">
-        <v>36.67481300942</v>
+        <v>36.23214279739292</v>
       </c>
       <c r="D66">
-        <v>22.95852861681004</v>
+        <v>22.93484792820123</v>
       </c>
       <c r="E66">
-        <v>0.9964953299999998</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="F66">
-        <v>0.9964953299999998</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="G66">
-        <v>0.2057034850411275</v>
+        <v>0.1925900763781823</v>
       </c>
       <c r="H66">
-        <v>0.9994474899999999</v>
+        <v>0.9992609200000001</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1">
-        <v>46174</v>
+        <v>46169</v>
       </c>
       <c r="B67" t="s">
         <v>11</v>
       </c>
       <c r="C67">
-        <v>36.84565507982974</v>
+        <v>36.4336692499184</v>
       </c>
       <c r="D67">
-        <v>23.15960292175205</v>
+        <v>22.75940954009856</v>
       </c>
       <c r="E67">
-        <v>0.99646052</v>
+        <v>0.9992099400000001</v>
       </c>
       <c r="F67">
-        <v>0.99646052</v>
+        <v>0.9992099400000001</v>
       </c>
       <c r="G67">
-        <v>0.2129379226426205</v>
+        <v>0.1912346098381414</v>
       </c>
       <c r="H67">
-        <v>0.9993986199999999</v>
+        <v>0.9992099400000001</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1">
-        <v>46175</v>
+        <v>46170</v>
       </c>
       <c r="B68" t="s">
         <v>11</v>
       </c>
       <c r="C68">
-        <v>36.88482057171844</v>
+        <v>36.57358557066742</v>
       </c>
       <c r="D68">
-        <v>23.03898938038424</v>
+        <v>22.83069636955243</v>
       </c>
       <c r="E68">
-        <v>0.99645675</v>
+        <v>0.9994435600000001</v>
       </c>
       <c r="F68">
-        <v>0.99645675</v>
+        <v>0.9994435600000001</v>
       </c>
       <c r="G68">
-        <v>0.2185229551183987</v>
+        <v>0.2012778603742877</v>
       </c>
       <c r="H68">
-        <v>0.9994034199999998</v>
+        <v>0.9994435600000001</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1">
-        <v>46176</v>
+        <v>46171</v>
       </c>
       <c r="B69" t="s">
         <v>11</v>
       </c>
       <c r="C69">
-        <v>36.96809213745556</v>
+        <v>36.67481300942</v>
       </c>
       <c r="D69">
-        <v>22.99660212231548</v>
+        <v>22.95852861681004</v>
       </c>
       <c r="E69">
-        <v>0.9964706</v>
+        <v>0.9964953299999998</v>
       </c>
       <c r="F69">
-        <v>0.9964706</v>
+        <v>0.9964953299999998</v>
       </c>
       <c r="G69">
-        <v>0.2153385706032709</v>
+        <v>0.2057034850411275</v>
       </c>
       <c r="H69">
-        <v>0.9993955800000001</v>
+        <v>0.9994474899999999</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1">
-        <v>46177</v>
+        <v>46174</v>
       </c>
       <c r="B70" t="s">
         <v>11</v>
       </c>
       <c r="C70">
-        <v>37.13780815830533</v>
+        <v>36.84565507982974</v>
       </c>
       <c r="D70">
-        <v>22.74889586257873</v>
+        <v>23.15960292175205</v>
       </c>
       <c r="E70">
-        <v>0.9964706899999999</v>
+        <v>0.99646052</v>
       </c>
       <c r="F70">
-        <v>0.9964706899999999</v>
+        <v>0.99646052</v>
       </c>
       <c r="G70">
-        <v>0.2094594998678323</v>
+        <v>0.2129379226426205</v>
       </c>
       <c r="H70">
-        <v>0.99938478</v>
+        <v>0.9993986199999999</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1">
-        <v>46153</v>
+        <v>46175</v>
       </c>
       <c r="B71" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C71">
-        <v>52.70832779833182</v>
+        <v>36.88482057171844</v>
       </c>
       <c r="D71">
-        <v>23.99044674439659</v>
+        <v>23.03898938038424</v>
       </c>
       <c r="E71">
-        <v>0.9994000000000002</v>
+        <v>0.99645675</v>
       </c>
       <c r="F71">
-        <v>0.9994000000000002</v>
+        <v>0.99645675</v>
       </c>
       <c r="G71">
-        <v>0.5438253854918791</v>
+        <v>0.2185229551183987</v>
       </c>
       <c r="H71">
-        <v>0.9994000000000002</v>
+        <v>0.9994034199999998</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1">
-        <v>46154</v>
+        <v>46176</v>
       </c>
       <c r="B72" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C72">
-        <v>50.89464485280568</v>
+        <v>36.96809213745556</v>
       </c>
       <c r="D72">
-        <v>23.21558303176282</v>
+        <v>22.99660212231548</v>
       </c>
       <c r="E72">
-        <v>0.9996</v>
+        <v>0.9964706</v>
       </c>
       <c r="F72">
-        <v>0.9996</v>
+        <v>0.9964706</v>
       </c>
       <c r="G72">
-        <v>0.5034825029548833</v>
+        <v>0.2153385706032709</v>
       </c>
       <c r="H72">
-        <v>0.9996</v>
+        <v>0.9993955800000001</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1">
-        <v>46155</v>
+        <v>46177</v>
       </c>
       <c r="B73" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C73">
-        <v>51.8659994471731</v>
+        <v>37.13780815830533</v>
       </c>
       <c r="D73">
-        <v>23.7009037279043</v>
+        <v>22.74889586257873</v>
       </c>
       <c r="E73">
-        <v>1.0002</v>
+        <v>0.9964706899999999</v>
       </c>
       <c r="F73">
-        <v>1.0002</v>
+        <v>0.9964706899999999</v>
       </c>
       <c r="G73">
-        <v>0.533512029714132</v>
+        <v>0.2094594998678323</v>
       </c>
       <c r="H73">
-        <v>1.0002</v>
+        <v>0.99938478</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1">
-        <v>46156</v>
+        <v>46178</v>
       </c>
       <c r="B74" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C74">
-        <v>52.4470179952828</v>
+        <v>35.57681391373501</v>
       </c>
       <c r="D74">
-        <v>23.76861704536814</v>
+        <v>21.69452833602077</v>
       </c>
       <c r="E74">
-        <v>0.9998</v>
+        <v>0.9964558499999999</v>
       </c>
       <c r="F74">
-        <v>0.9998</v>
+        <v>0.9964558499999999</v>
       </c>
       <c r="G74">
-        <v>0.5492634496849078</v>
+        <v>0.151404286858543</v>
       </c>
       <c r="H74">
-        <v>0.9998</v>
+        <v>0.9993850399999999</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="B75" t="s">
         <v>12</v>
       </c>
       <c r="C75">
-        <v>50.81077380018606</v>
+        <v>52.70832779833182</v>
       </c>
       <c r="D75">
-        <v>22.76900580927995</v>
+        <v>23.99044674439659</v>
       </c>
       <c r="E75">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="F75">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="G75">
-        <v>0.4903296143797722</v>
+        <v>0.5438253854918791</v>
       </c>
       <c r="H75">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1">
-        <v>46160</v>
+        <v>46154</v>
       </c>
       <c r="B76" t="s">
         <v>12</v>
       </c>
       <c r="C76">
-        <v>49.50286387149169</v>
+        <v>50.89464485280568</v>
       </c>
       <c r="D76">
-        <v>22.24532119914133</v>
+        <v>23.21558303176282</v>
       </c>
       <c r="E76">
         <v>0.9996</v>
@@ -2373,7 +2373,7 @@
         <v>0.9996</v>
       </c>
       <c r="G76">
-        <v>0.4630591776162345</v>
+        <v>0.5034825029548833</v>
       </c>
       <c r="H76">
         <v>0.9996</v>
@@ -2381,224 +2381,224 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1">
-        <v>46161</v>
+        <v>46155</v>
       </c>
       <c r="B77" t="s">
         <v>12</v>
       </c>
       <c r="C77">
-        <v>49.29146729279496</v>
+        <v>51.8659994471731</v>
       </c>
       <c r="D77">
-        <v>22.22167836589682</v>
+        <v>23.7009037279043</v>
       </c>
       <c r="E77">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="F77">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="G77">
-        <v>0.4571659248870246</v>
+        <v>0.533512029714132</v>
       </c>
       <c r="H77">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="1">
-        <v>46162</v>
+        <v>46156</v>
       </c>
       <c r="B78" t="s">
         <v>12</v>
       </c>
       <c r="C78">
-        <v>50.88652370817657</v>
+        <v>52.4470179952828</v>
       </c>
       <c r="D78">
-        <v>22.93254398967657</v>
+        <v>23.76861704536814</v>
       </c>
       <c r="E78">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F78">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G78">
-        <v>0.5126171754864624</v>
+        <v>0.5492634496849078</v>
       </c>
       <c r="H78">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1">
-        <v>46163</v>
+        <v>46157</v>
       </c>
       <c r="B79" t="s">
         <v>12</v>
       </c>
       <c r="C79">
-        <v>48.26646764818586</v>
+        <v>50.81077380018606</v>
       </c>
       <c r="D79">
-        <v>23.11655387625012</v>
+        <v>22.76900580927995</v>
       </c>
       <c r="E79">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="F79">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="G79">
-        <v>0.521243030947425</v>
+        <v>0.4903296143797722</v>
       </c>
       <c r="H79">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1">
-        <v>46164</v>
+        <v>46160</v>
       </c>
       <c r="B80" t="s">
         <v>12</v>
       </c>
       <c r="C80">
-        <v>48.84737503703267</v>
+        <v>49.50286387149169</v>
       </c>
       <c r="D80">
-        <v>22.83557604744466</v>
+        <v>22.24532119914133</v>
       </c>
       <c r="E80">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="F80">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="G80">
-        <v>0.5438521997590966</v>
+        <v>0.4630591776162345</v>
       </c>
       <c r="H80">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="1">
-        <v>46167</v>
+        <v>46161</v>
       </c>
       <c r="B81" t="s">
         <v>12</v>
       </c>
       <c r="C81">
-        <v>48.85151560750146</v>
+        <v>49.29146729279496</v>
       </c>
       <c r="D81">
-        <v>22.83513820206554</v>
+        <v>22.22167836589682</v>
       </c>
       <c r="E81">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F81">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G81">
-        <v>0.5438521997590966</v>
+        <v>0.4571659248870246</v>
       </c>
       <c r="H81">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="1">
-        <v>46168</v>
+        <v>46162</v>
       </c>
       <c r="B82" t="s">
         <v>12</v>
       </c>
       <c r="C82">
-        <v>50.90437883274981</v>
+        <v>50.88652370817657</v>
       </c>
       <c r="D82">
-        <v>24.25672473501501</v>
+        <v>22.93254398967657</v>
       </c>
       <c r="E82">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F82">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G82">
-        <v>0.6130191115419561</v>
+        <v>0.5126171754864624</v>
       </c>
       <c r="H82">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="1">
-        <v>46169</v>
+        <v>46163</v>
       </c>
       <c r="B83" t="s">
         <v>12</v>
       </c>
       <c r="C83">
-        <v>50.47312432255841</v>
+        <v>48.26646764818586</v>
       </c>
       <c r="D83">
-        <v>23.84499305142194</v>
+        <v>23.11655387625012</v>
       </c>
       <c r="E83">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="F83">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="G83">
-        <v>0.5952317692821967</v>
+        <v>0.521243030947425</v>
       </c>
       <c r="H83">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="1">
-        <v>46170</v>
+        <v>46164</v>
       </c>
       <c r="B84" t="s">
         <v>12</v>
       </c>
       <c r="C84">
-        <v>50.84596269629946</v>
+        <v>48.84737503703267</v>
       </c>
       <c r="D84">
-        <v>23.7680603326165</v>
+        <v>22.83557604744466</v>
       </c>
       <c r="E84">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F84">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G84">
-        <v>0.606831065374982</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H84">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1">
-        <v>46171</v>
+        <v>46167</v>
       </c>
       <c r="B85" t="s">
         <v>12</v>
       </c>
       <c r="C85">
-        <v>51.08372269965196</v>
+        <v>48.85151560750146</v>
       </c>
       <c r="D85">
-        <v>23.88880359436525</v>
+        <v>22.83513820206554</v>
       </c>
       <c r="E85">
         <v>0.9998999999999999</v>
@@ -2607,7 +2607,7 @@
         <v>0.9998999999999999</v>
       </c>
       <c r="G85">
-        <v>0.604420070348211</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H85">
         <v>0.9998999999999999</v>
@@ -2615,562 +2615,562 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="1">
-        <v>46174</v>
+        <v>46168</v>
       </c>
       <c r="B86" t="s">
         <v>12</v>
       </c>
       <c r="C86">
-        <v>51.84875713649351</v>
+        <v>50.90437883274981</v>
       </c>
       <c r="D86">
-        <v>24.29466650399529</v>
+        <v>24.25672473501501</v>
       </c>
       <c r="E86">
-        <v>0.9998</v>
+        <v>0.9996999999999999</v>
       </c>
       <c r="F86">
-        <v>0.9998</v>
+        <v>0.9996999999999999</v>
       </c>
       <c r="G86">
-        <v>0.6282079224060508</v>
+        <v>0.6130191115419561</v>
       </c>
       <c r="H86">
-        <v>0.9998</v>
+        <v>0.9996999999999999</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="1">
-        <v>46175</v>
+        <v>46169</v>
       </c>
       <c r="B87" t="s">
         <v>12</v>
       </c>
       <c r="C87">
-        <v>53.42858844634741</v>
+        <v>50.47312432255841</v>
       </c>
       <c r="D87">
-        <v>24.82449061140869</v>
+        <v>23.84499305142194</v>
       </c>
       <c r="E87">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="F87">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="G87">
-        <v>0.6935709687814895</v>
+        <v>0.5952317692821967</v>
       </c>
       <c r="H87">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1">
-        <v>46176</v>
+        <v>46170</v>
       </c>
       <c r="B88" t="s">
         <v>12</v>
       </c>
       <c r="C88">
-        <v>53.95056789686777</v>
+        <v>50.84596269629946</v>
       </c>
       <c r="D88">
-        <v>24.99295077214167</v>
+        <v>23.7680603326165</v>
       </c>
       <c r="E88">
-        <v>0.9996000000000002</v>
+        <v>0.9998</v>
       </c>
       <c r="F88">
-        <v>0.9996000000000002</v>
+        <v>0.9998</v>
       </c>
       <c r="G88">
-        <v>0.7088134081800193</v>
+        <v>0.606831065374982</v>
       </c>
       <c r="H88">
-        <v>0.9996000000000002</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="1">
-        <v>46177</v>
+        <v>46171</v>
       </c>
       <c r="B89" t="s">
         <v>12</v>
       </c>
       <c r="C89">
-        <v>53.29782764127071</v>
+        <v>51.08372269965196</v>
       </c>
       <c r="D89">
-        <v>24.48126483589962</v>
+        <v>23.88880359436525</v>
       </c>
       <c r="E89">
-        <v>1.0001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F89">
-        <v>1.0001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G89">
-        <v>0.6810341543458651</v>
+        <v>0.604420070348211</v>
       </c>
       <c r="H89">
-        <v>1.0001</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="1">
-        <v>46153</v>
+        <v>46174</v>
       </c>
       <c r="B90" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C90">
-        <v>57.1732166855686</v>
+        <v>51.84875713649351</v>
       </c>
       <c r="D90">
-        <v>23.50022751267814</v>
+        <v>24.29466650399529</v>
       </c>
       <c r="E90">
-        <v>0.9991</v>
+        <v>0.9998</v>
       </c>
       <c r="F90">
-        <v>0.9991</v>
+        <v>0.9998</v>
       </c>
       <c r="G90">
-        <v>0.6994110097039083</v>
+        <v>0.6282079224060508</v>
       </c>
       <c r="H90">
-        <v>0.9991</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="1">
-        <v>46154</v>
+        <v>46175</v>
       </c>
       <c r="B91" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C91">
-        <v>54.77380642078597</v>
+        <v>53.42858844634741</v>
       </c>
       <c r="D91">
-        <v>22.55192940254518</v>
+        <v>24.82449061140869</v>
       </c>
       <c r="E91">
-        <v>0.9990000000000001</v>
+        <v>1</v>
       </c>
       <c r="F91">
-        <v>0.9990000000000001</v>
+        <v>1</v>
       </c>
       <c r="G91">
-        <v>0.6459175880844941</v>
+        <v>0.6935709687814895</v>
       </c>
       <c r="H91">
-        <v>0.9990000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="1">
-        <v>46155</v>
+        <v>46176</v>
       </c>
       <c r="B92" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C92">
-        <v>56.32187380830906</v>
+        <v>53.95056789686777</v>
       </c>
       <c r="D92">
-        <v>23.17121437414109</v>
+        <v>24.99295077214167</v>
       </c>
       <c r="E92">
-        <v>0.9990000000000001</v>
+        <v>0.9996000000000002</v>
       </c>
       <c r="F92">
-        <v>0.9990000000000001</v>
+        <v>0.9996000000000002</v>
       </c>
       <c r="G92">
-        <v>0.6851523922954754</v>
+        <v>0.7088134081800193</v>
       </c>
       <c r="H92">
-        <v>0.9990000000000001</v>
+        <v>0.9996000000000002</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="1">
-        <v>46156</v>
+        <v>46177</v>
       </c>
       <c r="B93" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C93">
-        <v>56.15321618553139</v>
+        <v>53.29782764127071</v>
       </c>
       <c r="D93">
-        <v>22.95838347314443</v>
+        <v>24.48126483589962</v>
       </c>
       <c r="E93">
-        <v>0.9992</v>
+        <v>1.0001</v>
       </c>
       <c r="F93">
-        <v>0.9992</v>
+        <v>1.0001</v>
       </c>
       <c r="G93">
-        <v>0.6907028507208208</v>
+        <v>0.6810341543458651</v>
       </c>
       <c r="H93">
-        <v>0.9992</v>
+        <v>1.0001</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="1">
-        <v>46157</v>
+        <v>46178</v>
       </c>
       <c r="B94" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C94">
-        <v>54.47755813049488</v>
+        <v>48.44949949587421</v>
       </c>
       <c r="D94">
-        <v>22.0083816089626</v>
+        <v>22.39103669390088</v>
       </c>
       <c r="E94">
-        <v>0.9986</v>
+        <v>0.9995999999999999</v>
       </c>
       <c r="F94">
-        <v>0.9986</v>
+        <v>0.9995999999999999</v>
       </c>
       <c r="G94">
-        <v>0.6220895940829376</v>
+        <v>0.5260916717665549</v>
       </c>
       <c r="H94">
-        <v>0.9986</v>
+        <v>0.9995999999999999</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
       </c>
       <c r="C95">
-        <v>52.6278781150669</v>
+        <v>57.1732166855686</v>
       </c>
       <c r="D95">
-        <v>21.5357353870778</v>
+        <v>23.50022751267814</v>
       </c>
       <c r="E95">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F95">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G95">
-        <v>0.5845134636435627</v>
+        <v>0.6994110097039083</v>
       </c>
       <c r="H95">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B96" t="s">
         <v>13</v>
       </c>
       <c r="C96">
-        <v>54.91583234840245</v>
+        <v>54.77380642078597</v>
       </c>
       <c r="D96">
-        <v>22.38321645985006</v>
+        <v>22.55192940254518</v>
       </c>
       <c r="E96">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F96">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G96">
-        <v>0.6596976539194066</v>
+        <v>0.6459175880844941</v>
       </c>
       <c r="H96">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B97" t="s">
         <v>13</v>
       </c>
       <c r="C97">
-        <v>53.91712298548793</v>
+        <v>56.32187380830906</v>
       </c>
       <c r="D97">
-        <v>22.73711181201267</v>
+        <v>23.17121437414109</v>
       </c>
       <c r="E97">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F97">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G97">
-        <v>0.6737329602396263</v>
+        <v>0.6851523922954754</v>
       </c>
       <c r="H97">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="1">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="B98" t="s">
         <v>13</v>
       </c>
       <c r="C98">
-        <v>55.19651747515625</v>
+        <v>56.15321618553139</v>
       </c>
       <c r="D98">
-        <v>22.79462037330554</v>
+        <v>22.95838347314443</v>
       </c>
       <c r="E98">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
       <c r="F98">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
       <c r="G98">
-        <v>0.7139885317003913</v>
+        <v>0.6907028507208208</v>
       </c>
       <c r="H98">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="1">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="B99" t="s">
         <v>13</v>
       </c>
       <c r="C99">
-        <v>55.28054997487197</v>
+        <v>54.47755813049488</v>
       </c>
       <c r="D99">
-        <v>23.00160891539877</v>
+        <v>22.0083816089626</v>
       </c>
       <c r="E99">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="F99">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="G99">
-        <v>0.7139885317003913</v>
+        <v>0.6220895940829376</v>
       </c>
       <c r="H99">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="1">
-        <v>46168</v>
+        <v>46161</v>
       </c>
       <c r="B100" t="s">
         <v>13</v>
       </c>
       <c r="C100">
-        <v>58.75156728873073</v>
+        <v>52.6278781150669</v>
       </c>
       <c r="D100">
-        <v>24.84249654093248</v>
+        <v>21.5357353870778</v>
       </c>
       <c r="E100">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="F100">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="G100">
-        <v>0.8184872182632257</v>
+        <v>0.5845134636435627</v>
       </c>
       <c r="H100">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="1">
-        <v>46169</v>
+        <v>46162</v>
       </c>
       <c r="B101" t="s">
         <v>13</v>
       </c>
       <c r="C101">
-        <v>57.86771234337395</v>
+        <v>54.91583234840245</v>
       </c>
       <c r="D101">
-        <v>24.21066615243091</v>
+        <v>22.38321645985006</v>
       </c>
       <c r="E101">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="F101">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="G101">
-        <v>0.798997241708943</v>
+        <v>0.6596976539194066</v>
       </c>
       <c r="H101">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="1">
-        <v>46170</v>
+        <v>46163</v>
       </c>
       <c r="B102" t="s">
         <v>13</v>
       </c>
       <c r="C102">
-        <v>58.18666682631797</v>
+        <v>53.91712298548793</v>
       </c>
       <c r="D102">
-        <v>24.09552344282839</v>
+        <v>22.73711181201267</v>
       </c>
       <c r="E102">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="F102">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="G102">
-        <v>0.8165093478664007</v>
+        <v>0.6737329602396263</v>
       </c>
       <c r="H102">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="1">
-        <v>46171</v>
+        <v>46164</v>
       </c>
       <c r="B103" t="s">
         <v>13</v>
       </c>
       <c r="C103">
-        <v>58.79256019733606</v>
+        <v>55.19651747515625</v>
       </c>
       <c r="D103">
-        <v>24.33854853448823</v>
+        <v>22.79462037330554</v>
       </c>
       <c r="E103">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F103">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G103">
-        <v>0.8152654642198496</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H103">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="1">
-        <v>46174</v>
+        <v>46167</v>
       </c>
       <c r="B104" t="s">
         <v>13</v>
       </c>
       <c r="C104">
-        <v>58.97156722185718</v>
+        <v>55.28054997487197</v>
       </c>
       <c r="D104">
-        <v>24.48296361348067</v>
+        <v>23.00160891539877</v>
       </c>
       <c r="E104">
-        <v>0.9990000000000001</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="F104">
-        <v>0.9990000000000001</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="G104">
-        <v>0.8243563865851753</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H104">
-        <v>0.9990000000000001</v>
+        <v>0.9989000000000001</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="1">
-        <v>46175</v>
+        <v>46168</v>
       </c>
       <c r="B105" t="s">
         <v>13</v>
       </c>
       <c r="C105">
-        <v>61.6542902214027</v>
+        <v>58.75156728873073</v>
       </c>
       <c r="D105">
-        <v>25.06517348653028</v>
+        <v>24.84249654093248</v>
       </c>
       <c r="E105">
-        <v>0.9988</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="F105">
-        <v>0.9988</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="G105">
-        <v>0.9299077697948877</v>
+        <v>0.8184872182632257</v>
       </c>
       <c r="H105">
-        <v>0.9988</v>
+        <v>0.9989000000000001</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="1">
-        <v>46176</v>
+        <v>46169</v>
       </c>
       <c r="B106" t="s">
         <v>13</v>
       </c>
       <c r="C106">
-        <v>63.0681947750049</v>
+        <v>57.86771234337395</v>
       </c>
       <c r="D106">
-        <v>25.58770976382014</v>
+        <v>24.21066615243091</v>
       </c>
       <c r="E106">
-        <v>0.9988000000000002</v>
+        <v>0.9986999999999999</v>
       </c>
       <c r="F106">
-        <v>0.9988000000000002</v>
+        <v>0.9986999999999999</v>
       </c>
       <c r="G106">
-        <v>0.9639112148600193</v>
+        <v>0.798997241708943</v>
       </c>
       <c r="H106">
-        <v>0.9988000000000002</v>
+        <v>0.9986999999999999</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="1">
-        <v>46177</v>
+        <v>46170</v>
       </c>
       <c r="B107" t="s">
         <v>13</v>
       </c>
       <c r="C107">
-        <v>61.53154955456358</v>
+        <v>58.18666682631797</v>
       </c>
       <c r="D107">
-        <v>24.75810538712983</v>
+        <v>24.09552344282839</v>
       </c>
       <c r="E107">
         <v>0.9991</v>
@@ -3179,7 +3179,7 @@
         <v>0.9991</v>
       </c>
       <c r="G107">
-        <v>0.9225710173552821</v>
+        <v>0.8165093478664007</v>
       </c>
       <c r="H107">
         <v>0.9991</v>
@@ -3187,770 +3187,770 @@
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="1">
-        <v>46153</v>
+        <v>46171</v>
       </c>
       <c r="B108" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C108">
-        <v>35.78646526282436</v>
+        <v>58.79256019733606</v>
       </c>
       <c r="D108">
-        <v>18.96635091925032</v>
+        <v>24.33854853448823</v>
       </c>
       <c r="E108">
-        <v>0.9996491399999999</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="F108">
-        <v>0.9996491399999999</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="G108">
-        <v>0.2240600969213613</v>
+        <v>0.8152654642198496</v>
       </c>
       <c r="H108">
-        <v>0.9985614899999999</v>
+        <v>0.9989999999999999</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="1">
-        <v>46154</v>
+        <v>46174</v>
       </c>
       <c r="B109" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C109">
-        <v>35.71584102184062</v>
+        <v>58.97156722185718</v>
       </c>
       <c r="D109">
-        <v>18.62432950231353</v>
+        <v>24.48296361348067</v>
       </c>
       <c r="E109">
-        <v>0.99965481</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F109">
-        <v>0.99965481</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G109">
-        <v>0.2104844827747143</v>
+        <v>0.8243563865851753</v>
       </c>
       <c r="H109">
-        <v>0.9985622199999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="1">
-        <v>46155</v>
+        <v>46175</v>
       </c>
       <c r="B110" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C110">
-        <v>35.95182028203252</v>
+        <v>61.6542902214027</v>
       </c>
       <c r="D110">
-        <v>18.95670796791552</v>
+        <v>25.06517348653028</v>
       </c>
       <c r="E110">
-        <v>0.9996515200000001</v>
+        <v>0.9988</v>
       </c>
       <c r="F110">
-        <v>0.9996515200000001</v>
+        <v>0.9988</v>
       </c>
       <c r="G110">
-        <v>0.2259035693959275</v>
+        <v>0.9299077697948877</v>
       </c>
       <c r="H110">
-        <v>0.99855193</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="1">
-        <v>46156</v>
+        <v>46176</v>
       </c>
       <c r="B111" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C111">
-        <v>36.14451597805883</v>
+        <v>63.0681947750049</v>
       </c>
       <c r="D111">
-        <v>18.86297660538653</v>
+        <v>25.58770976382014</v>
       </c>
       <c r="E111">
-        <v>0.9996563399999999</v>
+        <v>0.9988000000000002</v>
       </c>
       <c r="F111">
-        <v>0.9996563399999999</v>
+        <v>0.9988000000000002</v>
       </c>
       <c r="G111">
-        <v>0.2362110061840785</v>
+        <v>0.9639112148600193</v>
       </c>
       <c r="H111">
-        <v>0.99857265</v>
+        <v>0.9988000000000002</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="1">
-        <v>46157</v>
+        <v>46177</v>
       </c>
       <c r="B112" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C112">
-        <v>35.32805803135546</v>
+        <v>61.53154955456358</v>
       </c>
       <c r="D112">
-        <v>18.35643242381478</v>
+        <v>24.75810538712983</v>
       </c>
       <c r="E112">
-        <v>0.9997415800000001</v>
+        <v>0.9991</v>
       </c>
       <c r="F112">
-        <v>0.9997415800000001</v>
+        <v>0.9991</v>
       </c>
       <c r="G112">
-        <v>0.2023559161375383</v>
+        <v>0.9225710173552821</v>
       </c>
       <c r="H112">
-        <v>0.9986639900000002</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="1">
-        <v>46160</v>
+        <v>46178</v>
       </c>
       <c r="B113" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C113">
-        <v>34.83995455757461</v>
+        <v>55.42493637343647</v>
       </c>
       <c r="D113">
-        <v>18.02301281718857</v>
+        <v>22.47054621698377</v>
       </c>
       <c r="E113">
-        <v>0.9996851299999999</v>
+        <v>0.9987</v>
       </c>
       <c r="F113">
-        <v>0.9996851299999999</v>
+        <v>0.9987</v>
       </c>
       <c r="G113">
-        <v>0.1850932291737926</v>
+        <v>0.7217717116249776</v>
       </c>
       <c r="H113">
-        <v>0.99857724</v>
+        <v>0.9987</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B114" t="s">
         <v>14</v>
       </c>
       <c r="C114">
-        <v>34.45479308705605</v>
+        <v>35.78646526282436</v>
       </c>
       <c r="D114">
-        <v>18.09576834566068</v>
+        <v>18.96635091925032</v>
       </c>
       <c r="E114">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="F114">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="G114">
-        <v>0.1784731209386736</v>
+        <v>0.2240600969213613</v>
       </c>
       <c r="H114">
-        <v>0.9985337599999999</v>
+        <v>0.9985614899999999</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B115" t="s">
         <v>14</v>
       </c>
       <c r="C115">
-        <v>34.96336277390787</v>
+        <v>35.71584102184062</v>
       </c>
       <c r="D115">
-        <v>18.34938420029253</v>
+        <v>18.62432950231353</v>
       </c>
       <c r="E115">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="F115">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="G115">
-        <v>0.2009313391215752</v>
+        <v>0.2104844827747143</v>
       </c>
       <c r="H115">
-        <v>0.99848777</v>
+        <v>0.9985622199999999</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B116" t="s">
         <v>14</v>
       </c>
       <c r="C116">
-        <v>34.44616924817128</v>
+        <v>35.95182028203252</v>
       </c>
       <c r="D116">
-        <v>18.60085625074367</v>
+        <v>18.95670796791552</v>
       </c>
       <c r="E116">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="F116">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="G116">
-        <v>0.2124957180214682</v>
+        <v>0.2259035693959275</v>
       </c>
       <c r="H116">
-        <v>0.9985085200000001</v>
+        <v>0.99855193</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="1">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="B117" t="s">
         <v>14</v>
       </c>
       <c r="C117">
-        <v>34.62137220937314</v>
+        <v>36.14451597805883</v>
       </c>
       <c r="D117">
-        <v>18.28780484745949</v>
+        <v>18.86297660538653</v>
       </c>
       <c r="E117">
-        <v>0.9996106299999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="F117">
-        <v>0.9996106299999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="G117">
-        <v>0.2145907067863493</v>
+        <v>0.2362110061840785</v>
       </c>
       <c r="H117">
-        <v>0.9932939299999999</v>
+        <v>0.99857265</v>
       </c>
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="1">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="B118" t="s">
         <v>14</v>
       </c>
       <c r="C118">
-        <v>34.6540695486741</v>
+        <v>35.32805803135546</v>
       </c>
       <c r="D118">
-        <v>18.36409048915342</v>
+        <v>18.35643242381478</v>
       </c>
       <c r="E118">
-        <v>0.9995448900000001</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="F118">
-        <v>0.9995448900000001</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="G118">
-        <v>0.2145907067863493</v>
+        <v>0.2023559161375383</v>
       </c>
       <c r="H118">
-        <v>0.9984302600000001</v>
+        <v>0.9986639900000002</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="1">
-        <v>46168</v>
+        <v>46160</v>
       </c>
       <c r="B119" t="s">
         <v>14</v>
       </c>
       <c r="C119">
-        <v>35.4820130509417</v>
+        <v>34.83995455757461</v>
       </c>
       <c r="D119">
-        <v>19.20292041814603</v>
+        <v>18.02301281718857</v>
       </c>
       <c r="E119">
-        <v>0.9995448900000001</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="F119">
-        <v>0.9995448900000001</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="G119">
-        <v>0.2553172934903569</v>
+        <v>0.1850932291737926</v>
       </c>
       <c r="H119">
-        <v>0.9984302600000001</v>
+        <v>0.99857724</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="1">
-        <v>46169</v>
+        <v>46161</v>
       </c>
       <c r="B120" t="s">
         <v>14</v>
       </c>
       <c r="C120">
-        <v>35.71913468603401</v>
+        <v>34.45479308705605</v>
       </c>
       <c r="D120">
-        <v>18.96318693998171</v>
+        <v>18.09576834566068</v>
       </c>
       <c r="E120">
-        <v>0.99955466</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="F120">
-        <v>0.99955466</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="G120">
-        <v>0.2536413280520453</v>
+        <v>0.1784731209386736</v>
       </c>
       <c r="H120">
-        <v>0.9984700500000001</v>
+        <v>0.9985337599999999</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="1">
-        <v>46170</v>
+        <v>46162</v>
       </c>
       <c r="B121" t="s">
         <v>14</v>
       </c>
       <c r="C121">
-        <v>35.76226417354731</v>
+        <v>34.96336277390787</v>
       </c>
       <c r="D121">
-        <v>18.89050847207122</v>
+        <v>18.34938420029253</v>
       </c>
       <c r="E121">
-        <v>0.9995525399999999</v>
+        <v>0.99963413</v>
       </c>
       <c r="F121">
-        <v>0.9995525399999999</v>
+        <v>0.99963413</v>
       </c>
       <c r="G121">
-        <v>0.2580826940041561</v>
+        <v>0.2009313391215752</v>
       </c>
       <c r="H121">
-        <v>0.99847732</v>
+        <v>0.99848777</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="1">
-        <v>46171</v>
+        <v>46163</v>
       </c>
       <c r="B122" t="s">
         <v>14</v>
       </c>
       <c r="C122">
-        <v>35.84309020154227</v>
+        <v>34.44616924817128</v>
       </c>
       <c r="D122">
-        <v>19.06511612333149</v>
+        <v>18.60085625074367</v>
       </c>
       <c r="E122">
-        <v>0.9995533299999999</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="F122">
-        <v>0.9995533299999999</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="G122">
-        <v>0.2619374017254759</v>
+        <v>0.2124957180214682</v>
       </c>
       <c r="H122">
-        <v>0.99849382</v>
+        <v>0.9985085200000001</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="1">
-        <v>46174</v>
+        <v>46164</v>
       </c>
       <c r="B123" t="s">
         <v>14</v>
       </c>
       <c r="C123">
-        <v>36.27022125574057</v>
+        <v>34.62137220937314</v>
       </c>
       <c r="D123">
-        <v>19.32711369104533</v>
+        <v>18.28780484745949</v>
       </c>
       <c r="E123">
-        <v>0.9995550400000001</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="F123">
-        <v>0.9995550400000001</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="G123">
-        <v>0.2764348160433892</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H123">
-        <v>0.9985177199999999</v>
+        <v>0.9932939299999999</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="1">
-        <v>46175</v>
+        <v>46167</v>
       </c>
       <c r="B124" t="s">
         <v>14</v>
       </c>
       <c r="C124">
-        <v>36.57133692946976</v>
+        <v>34.6540695486741</v>
       </c>
       <c r="D124">
-        <v>19.33857330565742</v>
+        <v>18.36409048915342</v>
       </c>
       <c r="E124">
-        <v>0.9994989200000002</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="F124">
-        <v>0.9994989200000002</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="G124">
-        <v>0.2931947261624381</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H124">
-        <v>0.9984577800000001</v>
+        <v>0.9984302600000001</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="1">
-        <v>46176</v>
+        <v>46168</v>
       </c>
       <c r="B125" t="s">
         <v>14</v>
       </c>
       <c r="C125">
-        <v>36.8289666508657</v>
+        <v>35.4820130509417</v>
       </c>
       <c r="D125">
-        <v>19.43137154505686</v>
+        <v>19.20292041814603</v>
       </c>
       <c r="E125">
-        <v>0.9994838199999998</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="F125">
-        <v>0.9994838199999998</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="G125">
-        <v>0.2996471994933361</v>
+        <v>0.2553172934903569</v>
       </c>
       <c r="H125">
-        <v>0.9984549499999998</v>
+        <v>0.9984302600000001</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" s="1">
-        <v>46177</v>
+        <v>46169</v>
       </c>
       <c r="B126" t="s">
         <v>14</v>
       </c>
       <c r="C126">
-        <v>36.76760036565858</v>
+        <v>35.71913468603401</v>
       </c>
       <c r="D126">
-        <v>18.98774474764188</v>
+        <v>18.96318693998171</v>
       </c>
       <c r="E126">
-        <v>0.99948384</v>
+        <v>0.99955466</v>
       </c>
       <c r="F126">
-        <v>0.99948384</v>
+        <v>0.99955466</v>
       </c>
       <c r="G126">
-        <v>0.2807085470912787</v>
+        <v>0.2536413280520453</v>
       </c>
       <c r="H126">
-        <v>0.9984696899999999</v>
+        <v>0.9984700500000001</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" s="1">
-        <v>46153</v>
+        <v>46170</v>
       </c>
       <c r="B127" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C127">
-        <v>28.12253390077671</v>
+        <v>35.76226417354731</v>
       </c>
       <c r="D127">
-        <v>23.58699683751922</v>
+        <v>18.89050847207122</v>
       </c>
       <c r="E127">
-        <v>0.9997295369999999</v>
+        <v>0.9995525399999999</v>
       </c>
       <c r="F127">
-        <v>0.9997295369999999</v>
+        <v>0.9995525399999999</v>
       </c>
       <c r="G127">
-        <v>0.03368732240295347</v>
+        <v>0.2580826940041561</v>
       </c>
       <c r="H127">
-        <v>0.9997295369999999</v>
+        <v>0.99847732</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="1">
-        <v>46154</v>
+        <v>46171</v>
       </c>
       <c r="B128" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C128">
-        <v>28.17715727830483</v>
+        <v>35.84309020154227</v>
       </c>
       <c r="D128">
-        <v>23.63894513078866</v>
+        <v>19.06511612333149</v>
       </c>
       <c r="E128">
-        <v>1.000319473</v>
+        <v>0.9995533299999999</v>
       </c>
       <c r="F128">
-        <v>1.000319473</v>
+        <v>0.9995533299999999</v>
       </c>
       <c r="G128">
-        <v>0.03515547182056333</v>
+        <v>0.2619374017254759</v>
       </c>
       <c r="H128">
-        <v>1.000319473</v>
+        <v>0.99849382</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="1">
-        <v>46155</v>
+        <v>46174</v>
       </c>
       <c r="B129" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C129">
-        <v>28.59002627414054</v>
+        <v>36.27022125574057</v>
       </c>
       <c r="D129">
-        <v>23.96230704059692</v>
+        <v>19.32711369104533</v>
       </c>
       <c r="E129">
-        <v>0.9999999989999999</v>
+        <v>0.9995550400000001</v>
       </c>
       <c r="F129">
-        <v>0.9999999989999999</v>
+        <v>0.9995550400000001</v>
       </c>
       <c r="G129">
-        <v>0.05179637495949674</v>
+        <v>0.2764348160433892</v>
       </c>
       <c r="H129">
-        <v>0.9999999989999999</v>
+        <v>0.9985177199999999</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" s="1">
-        <v>46156</v>
+        <v>46175</v>
       </c>
       <c r="B130" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C130">
-        <v>28.56217859389523</v>
+        <v>36.57133692946976</v>
       </c>
       <c r="D130">
-        <v>23.9411987302529</v>
+        <v>19.33857330565742</v>
       </c>
       <c r="E130">
-        <v>1</v>
+        <v>0.9994989200000002</v>
       </c>
       <c r="F130">
-        <v>1</v>
+        <v>0.9994989200000002</v>
       </c>
       <c r="G130">
-        <v>0.04837024516756849</v>
+        <v>0.2931947261624381</v>
       </c>
       <c r="H130">
-        <v>1</v>
+        <v>0.9984577800000001</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" s="1">
-        <v>46157</v>
+        <v>46176</v>
       </c>
       <c r="B131" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C131">
-        <v>28.57618675936338</v>
+        <v>36.8289666508657</v>
       </c>
       <c r="D131">
-        <v>23.9576220541054</v>
+        <v>19.43137154505686</v>
       </c>
       <c r="E131">
-        <v>0.999503249</v>
+        <v>0.9994838199999998</v>
       </c>
       <c r="F131">
-        <v>0.999503249</v>
+        <v>0.9994838199999998</v>
       </c>
       <c r="G131">
-        <v>0.04983868243960732</v>
+        <v>0.2996471994933361</v>
       </c>
       <c r="H131">
-        <v>0.999503249</v>
+        <v>0.9984549499999998</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="1">
-        <v>46160</v>
+        <v>46177</v>
       </c>
       <c r="B132" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C132">
-        <v>28.68951918518517</v>
+        <v>36.76760036565858</v>
       </c>
       <c r="D132">
-        <v>24.06134728453882</v>
+        <v>18.98774474764188</v>
       </c>
       <c r="E132">
-        <v>0.999503249</v>
+        <v>0.99948384</v>
       </c>
       <c r="F132">
-        <v>0.999503249</v>
+        <v>0.99948384</v>
       </c>
       <c r="G132">
-        <v>0.04983868243960732</v>
+        <v>0.2807085470912787</v>
       </c>
       <c r="H132">
-        <v>0.999503249</v>
+        <v>0.9984696899999999</v>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="1">
-        <v>46161</v>
+        <v>46178</v>
       </c>
       <c r="B133" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C133">
-        <v>28.31167386654059</v>
+        <v>34.71533981972338</v>
       </c>
       <c r="D133">
-        <v>23.75157719455474</v>
+        <v>17.87291658642534</v>
       </c>
       <c r="E133">
-        <v>1.000177331</v>
+        <v>0.9994584900000001</v>
       </c>
       <c r="F133">
-        <v>1.000177331</v>
+        <v>0.9994584900000001</v>
       </c>
       <c r="G133">
-        <v>0.04053938625111919</v>
+        <v>0.2090599057587512</v>
       </c>
       <c r="H133">
-        <v>1.000177331</v>
+        <v>0.9984184600000001</v>
       </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="1">
-        <v>46162</v>
+        <v>46153</v>
       </c>
       <c r="B134" t="s">
         <v>15</v>
       </c>
       <c r="C134">
-        <v>28.57911382310097</v>
+        <v>28.12253390077671</v>
       </c>
       <c r="D134">
-        <v>23.89431741541233</v>
+        <v>23.58699683751922</v>
       </c>
       <c r="E134">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="F134">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="G134">
-        <v>0.04690190590044785</v>
+        <v>0.03368732240295347</v>
       </c>
       <c r="H134">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="1">
-        <v>46163</v>
+        <v>46154</v>
       </c>
       <c r="B135" t="s">
         <v>15</v>
       </c>
       <c r="C135">
-        <v>28.55785065378643</v>
+        <v>28.17715727830483</v>
       </c>
       <c r="D135">
-        <v>24.04274714970193</v>
+        <v>23.63894513078866</v>
       </c>
       <c r="E135">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="F135">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="G135">
-        <v>0.05228572319419666</v>
+        <v>0.03515547182056333</v>
       </c>
       <c r="H135">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
     </row>
     <row r="136" spans="1:8">
       <c r="A136" s="1">
-        <v>46164</v>
+        <v>46155</v>
       </c>
       <c r="B136" t="s">
         <v>15</v>
       </c>
       <c r="C136">
-        <v>28.50194638163107</v>
+        <v>28.59002627414054</v>
       </c>
       <c r="D136">
-        <v>23.99272397156045</v>
+        <v>23.96230704059692</v>
       </c>
       <c r="E136">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F136">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G136">
-        <v>0.04934923597154284</v>
+        <v>0.05179637495949674</v>
       </c>
       <c r="H136">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="1">
-        <v>46167</v>
+        <v>46156</v>
       </c>
       <c r="B137" t="s">
         <v>15</v>
       </c>
       <c r="C137">
-        <v>28.55106858744498</v>
+        <v>28.56217859389523</v>
       </c>
       <c r="D137">
-        <v>23.9768329565351</v>
+        <v>23.9411987302529</v>
       </c>
       <c r="E137">
         <v>1</v>
@@ -3959,7 +3959,7 @@
         <v>1</v>
       </c>
       <c r="G137">
-        <v>0.05571185335164408</v>
+        <v>0.04837024516756849</v>
       </c>
       <c r="H137">
         <v>1</v>
@@ -3967,704 +3967,938 @@
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="1">
-        <v>46168</v>
+        <v>46157</v>
       </c>
       <c r="B138" t="s">
         <v>15</v>
       </c>
       <c r="C138">
-        <v>28.54681541456266</v>
+        <v>28.57618675936338</v>
       </c>
       <c r="D138">
-        <v>23.97386168967948</v>
+        <v>23.9576220541054</v>
       </c>
       <c r="E138">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="F138">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="G138">
-        <v>0.04837034303541388</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H138">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="1">
-        <v>46169</v>
+        <v>46160</v>
       </c>
       <c r="B139" t="s">
         <v>15</v>
       </c>
       <c r="C139">
-        <v>28.83672936868491</v>
+        <v>28.68951918518517</v>
       </c>
       <c r="D139">
-        <v>24.203511281145</v>
+        <v>24.06134728453882</v>
       </c>
       <c r="E139">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="F139">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="G139">
-        <v>0.05962723282507953</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H139">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="1">
-        <v>46170</v>
+        <v>46161</v>
       </c>
       <c r="B140" t="s">
         <v>15</v>
       </c>
       <c r="C140">
-        <v>28.88109630394224</v>
+        <v>28.31167386654059</v>
       </c>
       <c r="D140">
-        <v>24.34085451035401</v>
+        <v>23.75157719455474</v>
       </c>
       <c r="E140">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
       <c r="F140">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
       <c r="G140">
-        <v>0.06647938938594877</v>
+        <v>0.04053938625111919</v>
       </c>
       <c r="H140">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="1">
-        <v>46171</v>
+        <v>46162</v>
       </c>
       <c r="B141" t="s">
         <v>15</v>
       </c>
       <c r="C141">
-        <v>28.92588622185229</v>
+        <v>28.57911382310097</v>
       </c>
       <c r="D141">
-        <v>24.37463012178961</v>
+        <v>23.89431741541233</v>
       </c>
       <c r="E141">
-        <v>0.9999999989999999</v>
+        <v>0.999503734</v>
       </c>
       <c r="F141">
-        <v>0.9999999989999999</v>
+        <v>0.999503734</v>
       </c>
       <c r="G141">
-        <v>0.0669687424559624</v>
+        <v>0.04690190590044785</v>
       </c>
       <c r="H141">
-        <v>0.9999999989999999</v>
+        <v>0.999503734</v>
       </c>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="1">
-        <v>46174</v>
+        <v>46163</v>
       </c>
       <c r="B142" t="s">
         <v>15</v>
       </c>
       <c r="C142">
-        <v>28.479823472488</v>
+        <v>28.55785065378643</v>
       </c>
       <c r="D142">
-        <v>23.940843604634</v>
+        <v>24.04274714970193</v>
       </c>
       <c r="E142">
-        <v>0.9999999999999999</v>
+        <v>1.000229282</v>
       </c>
       <c r="F142">
-        <v>0.9999999999999999</v>
+        <v>1.000229282</v>
       </c>
       <c r="G142">
-        <v>0.05385076946675693</v>
+        <v>0.05228572319419666</v>
       </c>
       <c r="H142">
-        <v>0.9999999999999999</v>
+        <v>1.000229282</v>
       </c>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="1">
-        <v>46175</v>
+        <v>46164</v>
       </c>
       <c r="B143" t="s">
         <v>15</v>
       </c>
       <c r="C143">
-        <v>28.11501250979268</v>
+        <v>28.50194638163107</v>
       </c>
       <c r="D143">
-        <v>23.53470929078268</v>
+        <v>23.99272397156045</v>
       </c>
       <c r="E143">
-        <v>0.9999999989999999</v>
+        <v>1</v>
       </c>
       <c r="F143">
-        <v>0.9999999989999999</v>
+        <v>1</v>
       </c>
       <c r="G143">
-        <v>0.03476107722835287</v>
+        <v>0.04934923597154284</v>
       </c>
       <c r="H143">
-        <v>0.9999999989999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="1">
-        <v>46176</v>
+        <v>46167</v>
       </c>
       <c r="B144" t="s">
         <v>15</v>
       </c>
       <c r="C144">
-        <v>28.0115884668485</v>
+        <v>28.55106858744498</v>
       </c>
       <c r="D144">
-        <v>23.38620815625822</v>
+        <v>23.9768329565351</v>
       </c>
       <c r="E144">
-        <v>0.9993115890000001</v>
+        <v>1</v>
       </c>
       <c r="F144">
-        <v>0.9993115890000001</v>
+        <v>1</v>
       </c>
       <c r="G144">
-        <v>0.02105569185214828</v>
+        <v>0.05571185335164408</v>
       </c>
       <c r="H144">
-        <v>0.9993115890000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="1">
-        <v>46177</v>
+        <v>46168</v>
       </c>
       <c r="B145" t="s">
         <v>15</v>
       </c>
       <c r="C145">
-        <v>28.38208530418455</v>
+        <v>28.54681541456266</v>
       </c>
       <c r="D145">
-        <v>23.57230416238753</v>
+        <v>23.97386168967948</v>
       </c>
       <c r="E145">
-        <v>1.000774061</v>
+        <v>1</v>
       </c>
       <c r="F145">
-        <v>1.000774061</v>
+        <v>1</v>
       </c>
       <c r="G145">
-        <v>0.03133473088430172</v>
+        <v>0.04837034303541388</v>
       </c>
       <c r="H145">
-        <v>1.000774061</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="1">
-        <v>46153</v>
+        <v>46169</v>
       </c>
       <c r="B146" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C146">
-        <v>40.68830633303975</v>
+        <v>28.83672936868491</v>
       </c>
       <c r="D146">
-        <v>21.50431773660198</v>
+        <v>24.203511281145</v>
       </c>
       <c r="E146">
-        <v>0.99909852</v>
+        <v>1</v>
       </c>
       <c r="F146">
-        <v>0.99909852</v>
+        <v>1</v>
       </c>
       <c r="G146">
-        <v>0.2342423866086769</v>
+        <v>0.05962723282507953</v>
       </c>
       <c r="H146">
-        <v>0.9974930900000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="1">
-        <v>46154</v>
+        <v>46170</v>
       </c>
       <c r="B147" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C147">
-        <v>40.32854894972581</v>
+        <v>28.88109630394224</v>
       </c>
       <c r="D147">
-        <v>21.09133998298594</v>
+        <v>24.34085451035401</v>
       </c>
       <c r="E147">
-        <v>0.9990972199999999</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F147">
-        <v>0.9990972199999999</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G147">
-        <v>0.2156468205051487</v>
+        <v>0.06647938938594877</v>
       </c>
       <c r="H147">
-        <v>0.99752223</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="1">
-        <v>46155</v>
+        <v>46171</v>
       </c>
       <c r="B148" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C148">
-        <v>40.47987921095815</v>
+        <v>28.92588622185229</v>
       </c>
       <c r="D148">
-        <v>21.35995364434454</v>
+        <v>24.37463012178961</v>
       </c>
       <c r="E148">
-        <v>0.9991780100000001</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F148">
-        <v>0.9991780100000001</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G148">
-        <v>0.2270956128473374</v>
+        <v>0.0669687424559624</v>
       </c>
       <c r="H148">
-        <v>0.9975825700000001</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="1">
-        <v>46156</v>
+        <v>46174</v>
       </c>
       <c r="B149" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C149">
-        <v>41.20436574895244</v>
+        <v>28.479823472488</v>
       </c>
       <c r="D149">
-        <v>21.48149674387778</v>
+        <v>23.940843604634</v>
       </c>
       <c r="E149">
-        <v>0.9991793299999999</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F149">
-        <v>0.9991793299999999</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G149">
-        <v>0.2454829228401052</v>
+        <v>0.05385076946675693</v>
       </c>
       <c r="H149">
-        <v>0.99754722</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" s="1">
-        <v>46157</v>
+        <v>46175</v>
       </c>
       <c r="B150" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C150">
-        <v>40.80613062958688</v>
+        <v>28.11501250979268</v>
       </c>
       <c r="D150">
-        <v>21.08912555803936</v>
+        <v>23.53470929078268</v>
       </c>
       <c r="E150">
-        <v>0.9991790600000001</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F150">
-        <v>0.9991790600000001</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G150">
-        <v>0.2230017445022556</v>
+        <v>0.03476107722835287</v>
       </c>
       <c r="H150">
-        <v>0.9975824700000002</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="1">
-        <v>46160</v>
+        <v>46176</v>
       </c>
       <c r="B151" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C151">
-        <v>40.11672876026724</v>
+        <v>28.0115884668485</v>
       </c>
       <c r="D151">
-        <v>20.79541439916316</v>
+        <v>23.38620815625822</v>
       </c>
       <c r="E151">
-        <v>0.999152</v>
+        <v>0.9993115890000001</v>
       </c>
       <c r="F151">
-        <v>0.999152</v>
+        <v>0.9993115890000001</v>
       </c>
       <c r="G151">
-        <v>0.2098184021536666</v>
+        <v>0.02105569185214828</v>
       </c>
       <c r="H151">
-        <v>0.9975007899999999</v>
+        <v>0.9993115890000001</v>
       </c>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="1">
-        <v>46161</v>
+        <v>46177</v>
       </c>
       <c r="B152" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C152">
-        <v>39.69086941528401</v>
+        <v>28.38208530418455</v>
       </c>
       <c r="D152">
-        <v>20.74924328599426</v>
+        <v>23.57230416238753</v>
       </c>
       <c r="E152">
-        <v>0.99914989</v>
+        <v>1.000774061</v>
       </c>
       <c r="F152">
-        <v>0.99914989</v>
+        <v>1.000774061</v>
       </c>
       <c r="G152">
-        <v>0.2020471776850241</v>
+        <v>0.03133473088430172</v>
       </c>
       <c r="H152">
-        <v>0.9974417</v>
+        <v>1.000774061</v>
       </c>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" s="1">
-        <v>46162</v>
+        <v>46178</v>
       </c>
       <c r="B153" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C153">
-        <v>40.37836787855562</v>
+        <v>27.67379569436247</v>
       </c>
       <c r="D153">
-        <v>21.11271132314188</v>
+        <v>23.02577481291606</v>
       </c>
       <c r="E153">
-        <v>0.99915058</v>
+        <v>1.000106056</v>
       </c>
       <c r="F153">
-        <v>0.99915058</v>
+        <v>1.000106056</v>
       </c>
       <c r="G153">
-        <v>0.2291077670847563</v>
+        <v>0.01248973263108488</v>
       </c>
       <c r="H153">
-        <v>0.9974415600000001</v>
+        <v>1.000106056</v>
       </c>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" s="1">
-        <v>46163</v>
+        <v>46153</v>
       </c>
       <c r="B154" t="s">
         <v>16</v>
       </c>
       <c r="C154">
-        <v>38.9123066967842</v>
+        <v>40.68830633303975</v>
       </c>
       <c r="D154">
-        <v>21.28910644207464</v>
+        <v>21.50431773660198</v>
       </c>
       <c r="E154">
-        <v>0.9989350699999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="F154">
-        <v>0.9989350699999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="G154">
-        <v>0.2392382040170877</v>
+        <v>0.2342423866086769</v>
       </c>
       <c r="H154">
-        <v>0.99726191</v>
+        <v>0.9974930900000001</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" s="1">
-        <v>46164</v>
+        <v>46154</v>
       </c>
       <c r="B155" t="s">
         <v>16</v>
       </c>
       <c r="C155">
-        <v>39.43913909150694</v>
+        <v>40.32854894972581</v>
       </c>
       <c r="D155">
-        <v>21.05297617141148</v>
+        <v>21.09133998298594</v>
       </c>
       <c r="E155">
-        <v>0.999144</v>
+        <v>0.9990972199999999</v>
       </c>
       <c r="F155">
-        <v>0.999144</v>
+        <v>0.9990972199999999</v>
       </c>
       <c r="G155">
-        <v>0.2516582935428642</v>
+        <v>0.2156468205051487</v>
       </c>
       <c r="H155">
-        <v>0.9974678400000001</v>
+        <v>0.99752223</v>
       </c>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" s="1">
-        <v>46167</v>
+        <v>46155</v>
       </c>
       <c r="B156" t="s">
         <v>16</v>
       </c>
       <c r="C156">
-        <v>39.45782844313628</v>
+        <v>40.47987921095815</v>
       </c>
       <c r="D156">
-        <v>21.0518901572272</v>
+        <v>21.35995364434454</v>
       </c>
       <c r="E156">
-        <v>0.999144</v>
+        <v>0.9991780100000001</v>
       </c>
       <c r="F156">
-        <v>0.999144</v>
+        <v>0.9991780100000001</v>
       </c>
       <c r="G156">
-        <v>0.2516582935428642</v>
+        <v>0.2270956128473374</v>
       </c>
       <c r="H156">
-        <v>0.9974678400000001</v>
+        <v>0.9975825700000001</v>
       </c>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" s="1">
-        <v>46168</v>
+        <v>46156</v>
       </c>
       <c r="B157" t="s">
         <v>16</v>
       </c>
       <c r="C157">
-        <v>40.20219297984542</v>
+        <v>41.20436574895244</v>
       </c>
       <c r="D157">
-        <v>21.93106024403281</v>
+        <v>21.48149674387778</v>
       </c>
       <c r="E157">
-        <v>0.9991421799999999</v>
+        <v>0.9991793299999999</v>
       </c>
       <c r="F157">
-        <v>0.9991421799999999</v>
+        <v>0.9991793299999999</v>
       </c>
       <c r="G157">
-        <v>0.2846167552893293</v>
+        <v>0.2454829228401052</v>
       </c>
       <c r="H157">
-        <v>0.9974609800000001</v>
+        <v>0.99754722</v>
       </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="1">
-        <v>46169</v>
+        <v>46157</v>
       </c>
       <c r="B158" t="s">
         <v>16</v>
       </c>
       <c r="C158">
-        <v>40.34993865302093</v>
+        <v>40.80613062958688</v>
       </c>
       <c r="D158">
-        <v>21.65366031776487</v>
+        <v>21.08912555803936</v>
       </c>
       <c r="E158">
-        <v>0.9991434600000001</v>
+        <v>0.9991790600000001</v>
       </c>
       <c r="F158">
-        <v>0.9991434600000001</v>
+        <v>0.9991790600000001</v>
       </c>
       <c r="G158">
-        <v>0.2796902860011767</v>
+        <v>0.2230017445022556</v>
       </c>
       <c r="H158">
-        <v>0.9991434600000001</v>
+        <v>0.9975824700000002</v>
       </c>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" s="1">
-        <v>46170</v>
+        <v>46160</v>
       </c>
       <c r="B159" t="s">
         <v>16</v>
       </c>
       <c r="C159">
-        <v>40.5850485390846</v>
+        <v>40.11672876026724</v>
       </c>
       <c r="D159">
-        <v>21.75450977746074</v>
+        <v>20.79541439916316</v>
       </c>
       <c r="E159">
-        <v>0.99914592</v>
+        <v>0.999152</v>
       </c>
       <c r="F159">
-        <v>0.99914592</v>
+        <v>0.999152</v>
       </c>
       <c r="G159">
-        <v>0.2964818481030536</v>
+        <v>0.2098184021536666</v>
       </c>
       <c r="H159">
-        <v>0.99914592</v>
+        <v>0.9975007899999999</v>
       </c>
     </row>
     <row r="160" spans="1:8">
       <c r="A160" s="1">
-        <v>46171</v>
+        <v>46161</v>
       </c>
       <c r="B160" t="s">
         <v>16</v>
       </c>
       <c r="C160">
-        <v>41.86785805184477</v>
+        <v>39.69086941528401</v>
       </c>
       <c r="D160">
-        <v>22.33589392797469</v>
+        <v>20.74924328599426</v>
       </c>
       <c r="E160">
-        <v>0.9991336999999999</v>
+        <v>0.99914989</v>
       </c>
       <c r="F160">
-        <v>0.9991336999999999</v>
+        <v>0.99914989</v>
       </c>
       <c r="G160">
-        <v>0.3254158954996882</v>
+        <v>0.2020471776850241</v>
       </c>
       <c r="H160">
-        <v>0.9991336999999999</v>
+        <v>0.9974417</v>
       </c>
     </row>
     <row r="161" spans="1:8">
       <c r="A161" s="1">
-        <v>46174</v>
+        <v>46162</v>
       </c>
       <c r="B161" t="s">
         <v>16</v>
       </c>
       <c r="C161">
-        <v>42.82932322850974</v>
+        <v>40.37836787855562</v>
       </c>
       <c r="D161">
-        <v>22.98998911430362</v>
+        <v>21.11271132314188</v>
       </c>
       <c r="E161">
-        <v>0.99914238</v>
+        <v>0.99915058</v>
       </c>
       <c r="F161">
-        <v>0.99914238</v>
+        <v>0.99915058</v>
       </c>
       <c r="G161">
-        <v>0.3583049032509023</v>
+        <v>0.2291077670847563</v>
       </c>
       <c r="H161">
-        <v>0.99914238</v>
+        <v>0.9974415600000001</v>
       </c>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" s="1">
-        <v>46175</v>
+        <v>46163</v>
       </c>
       <c r="B162" t="s">
         <v>16</v>
       </c>
       <c r="C162">
-        <v>43.11872937189534</v>
+        <v>38.9123066967842</v>
       </c>
       <c r="D162">
-        <v>22.90628380907704</v>
+        <v>21.28910644207464</v>
       </c>
       <c r="E162">
-        <v>0.9990972800000002</v>
+        <v>0.9989350699999999</v>
       </c>
       <c r="F162">
-        <v>0.9990972800000002</v>
+        <v>0.9989350699999999</v>
       </c>
       <c r="G162">
-        <v>0.3753046155885469</v>
+        <v>0.2392382040170877</v>
       </c>
       <c r="H162">
-        <v>0.9990972800000002</v>
+        <v>0.99726191</v>
       </c>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" s="1">
-        <v>46176</v>
+        <v>46164</v>
       </c>
       <c r="B163" t="s">
         <v>16</v>
       </c>
       <c r="C163">
-        <v>42.86143001679577</v>
+        <v>39.43913909150694</v>
       </c>
       <c r="D163">
-        <v>22.72053012591219</v>
+        <v>21.05297617141148</v>
       </c>
       <c r="E163">
-        <v>0.9990984299999999</v>
+        <v>0.999144</v>
       </c>
       <c r="F163">
-        <v>0.9990984299999999</v>
+        <v>0.999144</v>
       </c>
       <c r="G163">
-        <v>0.3615660647779204</v>
+        <v>0.2516582935428642</v>
       </c>
       <c r="H163">
-        <v>0.9990984299999999</v>
+        <v>0.9974678400000001</v>
       </c>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" s="1">
-        <v>46177</v>
+        <v>46167</v>
       </c>
       <c r="B164" t="s">
         <v>16</v>
       </c>
       <c r="C164">
+        <v>39.45782844313628</v>
+      </c>
+      <c r="D164">
+        <v>21.0518901572272</v>
+      </c>
+      <c r="E164">
+        <v>0.999144</v>
+      </c>
+      <c r="F164">
+        <v>0.999144</v>
+      </c>
+      <c r="G164">
+        <v>0.2516582935428642</v>
+      </c>
+      <c r="H164">
+        <v>0.9974678400000001</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8">
+      <c r="A165" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165">
+        <v>40.20219297984542</v>
+      </c>
+      <c r="D165">
+        <v>21.93106024403281</v>
+      </c>
+      <c r="E165">
+        <v>0.9991421799999999</v>
+      </c>
+      <c r="F165">
+        <v>0.9991421799999999</v>
+      </c>
+      <c r="G165">
+        <v>0.2846167552893293</v>
+      </c>
+      <c r="H165">
+        <v>0.9974609800000001</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8">
+      <c r="A166" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166">
+        <v>40.34993865302093</v>
+      </c>
+      <c r="D166">
+        <v>21.65366031776487</v>
+      </c>
+      <c r="E166">
+        <v>0.9991434600000001</v>
+      </c>
+      <c r="F166">
+        <v>0.9991434600000001</v>
+      </c>
+      <c r="G166">
+        <v>0.2796902860011767</v>
+      </c>
+      <c r="H166">
+        <v>0.9991434600000001</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8">
+      <c r="A167" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167">
+        <v>40.5850485390846</v>
+      </c>
+      <c r="D167">
+        <v>21.75450977746074</v>
+      </c>
+      <c r="E167">
+        <v>0.99914592</v>
+      </c>
+      <c r="F167">
+        <v>0.99914592</v>
+      </c>
+      <c r="G167">
+        <v>0.2964818481030536</v>
+      </c>
+      <c r="H167">
+        <v>0.99914592</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8">
+      <c r="A168" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168">
+        <v>41.86785805184477</v>
+      </c>
+      <c r="D168">
+        <v>22.33589392797469</v>
+      </c>
+      <c r="E168">
+        <v>0.9991336999999999</v>
+      </c>
+      <c r="F168">
+        <v>0.9991336999999999</v>
+      </c>
+      <c r="G168">
+        <v>0.3254158954996882</v>
+      </c>
+      <c r="H168">
+        <v>0.9991336999999999</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8">
+      <c r="A169" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169">
+        <v>42.82932322850974</v>
+      </c>
+      <c r="D169">
+        <v>22.98998911430362</v>
+      </c>
+      <c r="E169">
+        <v>0.99914238</v>
+      </c>
+      <c r="F169">
+        <v>0.99914238</v>
+      </c>
+      <c r="G169">
+        <v>0.3583049032509023</v>
+      </c>
+      <c r="H169">
+        <v>0.99914238</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8">
+      <c r="A170" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170">
+        <v>43.11872937189534</v>
+      </c>
+      <c r="D170">
+        <v>22.90628380907704</v>
+      </c>
+      <c r="E170">
+        <v>0.9990972800000002</v>
+      </c>
+      <c r="F170">
+        <v>0.9990972800000002</v>
+      </c>
+      <c r="G170">
+        <v>0.3753046155885469</v>
+      </c>
+      <c r="H170">
+        <v>0.9990972800000002</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8">
+      <c r="A171" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171">
+        <v>42.86143001679577</v>
+      </c>
+      <c r="D171">
+        <v>22.72053012591219</v>
+      </c>
+      <c r="E171">
+        <v>0.9990984299999999</v>
+      </c>
+      <c r="F171">
+        <v>0.9990984299999999</v>
+      </c>
+      <c r="G171">
+        <v>0.3615660647779204</v>
+      </c>
+      <c r="H171">
+        <v>0.9990984299999999</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8">
+      <c r="A172" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172">
         <v>42.57902095847519</v>
       </c>
-      <c r="D164">
+      <c r="D172">
         <v>22.20304338566557</v>
       </c>
-      <c r="E164">
+      <c r="E172">
         <v>0.9990006900000001</v>
       </c>
-      <c r="F164">
+      <c r="F172">
         <v>0.9990006900000001</v>
       </c>
-      <c r="G164">
+      <c r="G172">
         <v>0.34033389372967</v>
       </c>
-      <c r="H164">
+      <c r="H172">
         <v>0.9990006900000001</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8">
+      <c r="A173" s="1">
+        <v>46178</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173">
+        <v>39.64354477595148</v>
+      </c>
+      <c r="D173">
+        <v>20.69555521363093</v>
+      </c>
+      <c r="E173">
+        <v>0.9992026399999999</v>
+      </c>
+      <c r="F173">
+        <v>0.9992026399999999</v>
+      </c>
+      <c r="G173">
+        <v>0.251033842835561</v>
+      </c>
+      <c r="H173">
+        <v>0.9992026399999999</v>
       </c>
     </row>
   </sheetData>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="17">
   <si>
     <t>Date</t>
   </si>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H173"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -769,42 +769,42 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1">
-        <v>46153</v>
+        <v>46182</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15">
-        <v>53.14833755912058</v>
+        <v>25.09128029557501</v>
       </c>
       <c r="D15">
-        <v>25.84885448407537</v>
+        <v>16.46002919022756</v>
       </c>
       <c r="E15">
-        <v>0.9262</v>
+        <v>0.8745999999999999</v>
       </c>
       <c r="F15">
-        <v>0.9262</v>
+        <v>0.8693</v>
       </c>
       <c r="G15">
-        <v>0.3839084462043663</v>
+        <v>0.477398597525494</v>
       </c>
       <c r="H15">
-        <v>0.9262</v>
+        <v>0.9271999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
       </c>
       <c r="C16">
-        <v>51.82921169635205</v>
+        <v>53.14833755912058</v>
       </c>
       <c r="D16">
-        <v>25.32805827181975</v>
+        <v>25.84885448407537</v>
       </c>
       <c r="E16">
         <v>0.9262</v>
@@ -813,7 +813,7 @@
         <v>0.9262</v>
       </c>
       <c r="G16">
-        <v>0.3568580281685669</v>
+        <v>0.3839084462043663</v>
       </c>
       <c r="H16">
         <v>0.9262</v>
@@ -821,120 +821,120 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
       </c>
       <c r="C17">
-        <v>52.28471716753184</v>
+        <v>51.82921169635205</v>
       </c>
       <c r="D17">
-        <v>25.54525144150689</v>
+        <v>25.32805827181975</v>
       </c>
       <c r="E17">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="F17">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="G17">
-        <v>0.378012896547947</v>
+        <v>0.3568580281685669</v>
       </c>
       <c r="H17">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B18" t="s">
         <v>9</v>
       </c>
       <c r="C18">
-        <v>53.87287273813902</v>
+        <v>52.28471716753184</v>
       </c>
       <c r="D18">
-        <v>26.32154226438612</v>
+        <v>25.54525144150689</v>
       </c>
       <c r="E18">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="F18">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="G18">
-        <v>0.4166811087612758</v>
+        <v>0.378012896547947</v>
       </c>
       <c r="H18">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="B19" t="s">
         <v>9</v>
       </c>
       <c r="C19">
-        <v>52.18747148214074</v>
+        <v>53.87287273813902</v>
       </c>
       <c r="D19">
-        <v>25.13616059644496</v>
+        <v>26.32154226438612</v>
       </c>
       <c r="E19">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="F19">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="G19">
-        <v>0.3627535778249862</v>
+        <v>0.4166811087612758</v>
       </c>
       <c r="H19">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="B20" t="s">
         <v>9</v>
       </c>
       <c r="C20">
-        <v>50.72035274995172</v>
+        <v>52.18747148214074</v>
       </c>
       <c r="D20">
-        <v>24.61756040386634</v>
+        <v>25.13616059644496</v>
       </c>
       <c r="E20">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="F20">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="G20">
         <v>0.3627535778249862</v>
       </c>
       <c r="H20">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="B21" t="s">
         <v>9</v>
       </c>
       <c r="C21">
-        <v>50.11981086673613</v>
+        <v>50.72035274995172</v>
       </c>
       <c r="D21">
-        <v>24.13061679021705</v>
+        <v>24.61756040386634</v>
       </c>
       <c r="E21">
         <v>0.9259000000000001</v>
@@ -943,7 +943,7 @@
         <v>0.9259000000000001</v>
       </c>
       <c r="G21">
-        <v>0.3258193430227221</v>
+        <v>0.3627535778249862</v>
       </c>
       <c r="H21">
         <v>0.9259000000000001</v>
@@ -951,120 +951,120 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="B22" t="s">
         <v>9</v>
       </c>
       <c r="C22">
-        <v>51.74165648409151</v>
+        <v>50.11981086673613</v>
       </c>
       <c r="D22">
-        <v>24.98091384114761</v>
+        <v>24.13061679021705</v>
       </c>
       <c r="E22">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="F22">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="G22">
-        <v>0.3818277262286871</v>
+        <v>0.3258193430227221</v>
       </c>
       <c r="H22">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="B23" t="s">
         <v>9</v>
       </c>
       <c r="C23">
-        <v>49.13455894175823</v>
+        <v>51.74165648409151</v>
       </c>
       <c r="D23">
-        <v>25.30005057653127</v>
+        <v>24.98091384114761</v>
       </c>
       <c r="E23">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="F23">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="G23">
-        <v>0.4028091571787618</v>
+        <v>0.3818277262286871</v>
       </c>
       <c r="H23">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="B24" t="s">
         <v>9</v>
       </c>
       <c r="C24">
-        <v>49.57776597479297</v>
+        <v>49.13455894175823</v>
       </c>
       <c r="D24">
-        <v>25.04906725563518</v>
+        <v>25.30005057653127</v>
       </c>
       <c r="E24">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="F24">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="G24">
-        <v>0.4256980029692063</v>
+        <v>0.4028091571787618</v>
       </c>
       <c r="H24">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
       </c>
       <c r="C25">
-        <v>49.71239596645896</v>
+        <v>49.57776597479297</v>
       </c>
       <c r="D25">
-        <v>25.18778610744295</v>
+        <v>25.04906725563518</v>
       </c>
       <c r="E25">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="F25">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="G25">
-        <v>0.4525749835757003</v>
+        <v>0.4256980029692063</v>
       </c>
       <c r="H25">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
       </c>
       <c r="C26">
-        <v>50.77166277510776</v>
+        <v>49.71239596645896</v>
       </c>
       <c r="D26">
-        <v>25.7431782858765</v>
+        <v>25.18778610744295</v>
       </c>
       <c r="E26">
         <v>0.9231999999999999</v>
@@ -1073,7 +1073,7 @@
         <v>0.9231999999999999</v>
       </c>
       <c r="G26">
-        <v>0.4700884597036457</v>
+        <v>0.4525749835757003</v>
       </c>
       <c r="H26">
         <v>0.9231999999999999</v>
@@ -1081,120 +1081,120 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1">
-        <v>46169</v>
+        <v>46168</v>
       </c>
       <c r="B27" t="s">
         <v>9</v>
       </c>
       <c r="C27">
-        <v>50.57689164833899</v>
+        <v>50.77166277510776</v>
       </c>
       <c r="D27">
-        <v>25.70244067238947</v>
+        <v>25.7431782858765</v>
       </c>
       <c r="E27">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="F27">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="G27">
-        <v>0.4518814984464716</v>
+        <v>0.4700884597036457</v>
       </c>
       <c r="H27">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="B28" t="s">
         <v>9</v>
       </c>
       <c r="C28">
-        <v>50.80027854822009</v>
+        <v>50.57689164833899</v>
       </c>
       <c r="D28">
-        <v>25.90068415792015</v>
+        <v>25.70244067238947</v>
       </c>
       <c r="E28">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
       <c r="F28">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
       <c r="G28">
-        <v>0.4699150222743402</v>
+        <v>0.4518814984464716</v>
       </c>
       <c r="H28">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="B29" t="s">
         <v>9</v>
       </c>
       <c r="C29">
-        <v>51.44563447241545</v>
+        <v>50.80027854822009</v>
       </c>
       <c r="D29">
-        <v>26.0970978996374</v>
+        <v>25.90068415792015</v>
       </c>
       <c r="E29">
-        <v>0.9246</v>
+        <v>0.9231</v>
       </c>
       <c r="F29">
-        <v>0.9246</v>
+        <v>0.9231</v>
       </c>
       <c r="G29">
-        <v>0.4791053539115764</v>
+        <v>0.4699150222743402</v>
       </c>
       <c r="H29">
-        <v>0.9246</v>
+        <v>0.9231</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1">
-        <v>46174</v>
+        <v>46171</v>
       </c>
       <c r="B30" t="s">
         <v>9</v>
       </c>
       <c r="C30">
-        <v>53.05792083471825</v>
+        <v>51.44563447241545</v>
       </c>
       <c r="D30">
-        <v>26.86242981002239</v>
+        <v>26.0970978996374</v>
       </c>
       <c r="E30">
-        <v>0.9254999999999999</v>
+        <v>0.9246</v>
       </c>
       <c r="F30">
-        <v>0.9254999999999999</v>
+        <v>0.9246</v>
       </c>
       <c r="G30">
-        <v>0.5306051577195796</v>
+        <v>0.4791053539115764</v>
       </c>
       <c r="H30">
-        <v>0.9254999999999999</v>
+        <v>0.9246</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="B31" t="s">
         <v>9</v>
       </c>
       <c r="C31">
-        <v>54.38946369031042</v>
+        <v>53.05792083471825</v>
       </c>
       <c r="D31">
-        <v>27.57160808325711</v>
+        <v>26.86242981002239</v>
       </c>
       <c r="E31">
         <v>0.9254999999999999</v>
@@ -1203,7 +1203,7 @@
         <v>0.9254999999999999</v>
       </c>
       <c r="G31">
-        <v>0.5845326886558693</v>
+        <v>0.5306051577195796</v>
       </c>
       <c r="H31">
         <v>0.9254999999999999</v>
@@ -1211,224 +1211,224 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="B32" t="s">
         <v>9</v>
       </c>
       <c r="C32">
-        <v>54.35279063045283</v>
+        <v>54.38946369031042</v>
       </c>
       <c r="D32">
-        <v>27.50874919819178</v>
+        <v>27.57160808325711</v>
       </c>
       <c r="E32">
-        <v>0.9162000000000001</v>
+        <v>0.9254999999999999</v>
       </c>
       <c r="F32">
-        <v>0.9162000000000001</v>
+        <v>0.9254999999999999</v>
       </c>
       <c r="G32">
-        <v>0.5992718273849102</v>
+        <v>0.5845326886558693</v>
       </c>
       <c r="H32">
-        <v>0.9162000000000001</v>
+        <v>0.9254999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="B33" t="s">
         <v>9</v>
       </c>
       <c r="C33">
-        <v>53.45790968334249</v>
+        <v>54.35279063045283</v>
       </c>
       <c r="D33">
-        <v>26.99486187834476</v>
+        <v>27.50874919819178</v>
       </c>
       <c r="E33">
-        <v>0.9154000000000001</v>
+        <v>0.9162000000000001</v>
       </c>
       <c r="F33">
-        <v>0.9154000000000001</v>
+        <v>0.9162000000000001</v>
       </c>
       <c r="G33">
-        <v>0.5691000647975994</v>
+        <v>0.5992718273849102</v>
       </c>
       <c r="H33">
-        <v>0.9154000000000001</v>
+        <v>0.9162000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="B34" t="s">
         <v>9</v>
       </c>
       <c r="C34">
-        <v>52.01314444713902</v>
+        <v>53.45790968334249</v>
       </c>
       <c r="D34">
-        <v>25.48849727916627</v>
+        <v>26.99486187834476</v>
       </c>
       <c r="E34">
-        <v>0.9142999999999999</v>
+        <v>0.9154000000000001</v>
       </c>
       <c r="F34">
-        <v>0.9142999999999999</v>
+        <v>0.9154000000000001</v>
       </c>
       <c r="G34">
-        <v>0.4380094145699611</v>
+        <v>0.5691000647975994</v>
       </c>
       <c r="H34">
-        <v>0.9142999999999999</v>
+        <v>0.9154000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1">
-        <v>46153</v>
+        <v>46178</v>
       </c>
       <c r="B35" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C35">
-        <v>34.64560932909123</v>
+        <v>52.01314444713902</v>
       </c>
       <c r="D35">
-        <v>26.08311546080494</v>
+        <v>25.48849727916627</v>
       </c>
       <c r="E35">
-        <v>0.9983000000000001</v>
+        <v>0.9142999999999999</v>
       </c>
       <c r="F35">
-        <v>0.9983000000000001</v>
+        <v>0.9142999999999999</v>
       </c>
       <c r="G35">
-        <v>0.06258613715048233</v>
+        <v>0.4380094145699611</v>
       </c>
       <c r="H35">
-        <v>0.9983000000000001</v>
+        <v>0.9142999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1">
-        <v>46154</v>
+        <v>46182</v>
       </c>
       <c r="B36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C36">
-        <v>34.50204921141101</v>
+        <v>48.52114115454133</v>
       </c>
       <c r="D36">
-        <v>25.94535229304585</v>
+        <v>24.5918103168291</v>
       </c>
       <c r="E36">
-        <v>0.9984</v>
+        <v>0.916</v>
       </c>
       <c r="F36">
-        <v>0.9984</v>
+        <v>0.916</v>
       </c>
       <c r="G36">
-        <v>0.05768943168306073</v>
+        <v>0.4418242442507014</v>
       </c>
       <c r="H36">
-        <v>0.9984</v>
+        <v>0.916</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="B37" t="s">
         <v>10</v>
       </c>
       <c r="C37">
-        <v>35.10429483281073</v>
+        <v>34.64560932909123</v>
       </c>
       <c r="D37">
-        <v>26.43864879939599</v>
+        <v>26.08311546080494</v>
       </c>
       <c r="E37">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="F37">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="G37">
-        <v>0.07926550001722021</v>
+        <v>0.06258613715048233</v>
       </c>
       <c r="H37">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="B38" t="s">
         <v>10</v>
       </c>
       <c r="C38">
-        <v>35.36860632820093</v>
+        <v>34.50204921141101</v>
       </c>
       <c r="D38">
-        <v>26.56575571102338</v>
+        <v>25.94535229304585</v>
       </c>
       <c r="E38">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F38">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G38">
-        <v>0.08553946591902095</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H38">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="B39" t="s">
         <v>10</v>
       </c>
       <c r="C39">
-        <v>34.88080083527914</v>
+        <v>35.10429483281073</v>
       </c>
       <c r="D39">
-        <v>26.19322945679072</v>
+        <v>26.43864879939599</v>
       </c>
       <c r="E39">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="F39">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="G39">
-        <v>0.06870693142475881</v>
+        <v>0.07926550001722021</v>
       </c>
       <c r="H39">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1">
-        <v>46160</v>
+        <v>46156</v>
       </c>
       <c r="B40" t="s">
         <v>10</v>
       </c>
       <c r="C40">
-        <v>34.67638692539213</v>
+        <v>35.36860632820093</v>
       </c>
       <c r="D40">
-        <v>26.06707890342319</v>
+        <v>26.56575571102338</v>
       </c>
       <c r="E40">
         <v>0.9985999999999999</v>
@@ -1437,7 +1437,7 @@
         <v>0.9985999999999999</v>
       </c>
       <c r="G40">
-        <v>0.06289213016552919</v>
+        <v>0.08553946591902095</v>
       </c>
       <c r="H40">
         <v>0.9985999999999999</v>
@@ -1445,120 +1445,120 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="B41" t="s">
         <v>10</v>
       </c>
       <c r="C41">
-        <v>34.21212662725402</v>
+        <v>34.88080083527914</v>
       </c>
       <c r="D41">
-        <v>25.60349394367002</v>
+        <v>26.19322945679072</v>
       </c>
       <c r="E41">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="F41">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="G41">
-        <v>0.0486610616591685</v>
+        <v>0.06870693142475881</v>
       </c>
       <c r="H41">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="B42" t="s">
         <v>10</v>
       </c>
       <c r="C42">
-        <v>34.78598436564941</v>
+        <v>34.67638692539213</v>
       </c>
       <c r="D42">
-        <v>25.95505316769806</v>
+        <v>26.06707890342319</v>
       </c>
       <c r="E42">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="F42">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="G42">
-        <v>0.06335117806143331</v>
+        <v>0.06289213016552919</v>
       </c>
       <c r="H42">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1">
-        <v>46163</v>
+        <v>46161</v>
       </c>
       <c r="B43" t="s">
         <v>10</v>
       </c>
       <c r="C43">
-        <v>33.4539909056227</v>
+        <v>34.21212662725402</v>
       </c>
       <c r="D43">
-        <v>25.96014535427112</v>
+        <v>25.60349394367002</v>
       </c>
       <c r="E43">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="F43">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="G43">
-        <v>0.06350423294229035</v>
+        <v>0.0486610616591685</v>
       </c>
       <c r="H43">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1">
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="B44" t="s">
         <v>10</v>
       </c>
       <c r="C44">
-        <v>33.24951933563993</v>
+        <v>34.78598436564941</v>
       </c>
       <c r="D44">
-        <v>25.46629530314992</v>
+        <v>25.95505316769806</v>
       </c>
       <c r="E44">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="F44">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="G44">
-        <v>0.06136193159696024</v>
+        <v>0.06335117806143331</v>
       </c>
       <c r="H44">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1">
-        <v>46167</v>
+        <v>46163</v>
       </c>
       <c r="B45" t="s">
         <v>10</v>
       </c>
       <c r="C45">
-        <v>33.29896419867477</v>
+        <v>33.4539909056227</v>
       </c>
       <c r="D45">
-        <v>25.45090185337973</v>
+        <v>25.96014535427112</v>
       </c>
       <c r="E45">
         <v>0.9984</v>
@@ -1567,7 +1567,7 @@
         <v>0.9984</v>
       </c>
       <c r="G45">
-        <v>0.06136193159696024</v>
+        <v>0.06350423294229035</v>
       </c>
       <c r="H45">
         <v>0.9984</v>
@@ -1575,16 +1575,16 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1">
-        <v>46168</v>
+        <v>46164</v>
       </c>
       <c r="B46" t="s">
         <v>10</v>
       </c>
       <c r="C46">
-        <v>33.41270923608511</v>
+        <v>33.24951933563993</v>
       </c>
       <c r="D46">
-        <v>25.54156152389702</v>
+        <v>25.46629530314992</v>
       </c>
       <c r="E46">
         <v>0.9984</v>
@@ -1593,7 +1593,7 @@
         <v>0.9984</v>
       </c>
       <c r="G46">
-        <v>0.06549347940676342</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H46">
         <v>0.9984</v>
@@ -1601,198 +1601,198 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1">
-        <v>46169</v>
+        <v>46167</v>
       </c>
       <c r="B47" t="s">
         <v>10</v>
       </c>
       <c r="C47">
-        <v>33.73350746548562</v>
+        <v>33.29896419867477</v>
       </c>
       <c r="D47">
-        <v>25.75393367034243</v>
+        <v>25.45090185337973</v>
       </c>
       <c r="E47">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="F47">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="G47">
-        <v>0.07620510288008187</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H47">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1">
-        <v>46170</v>
+        <v>46168</v>
       </c>
       <c r="B48" t="s">
         <v>10</v>
       </c>
       <c r="C48">
-        <v>33.84336414535104</v>
+        <v>33.41270923608511</v>
       </c>
       <c r="D48">
-        <v>25.97168203877208</v>
+        <v>25.54156152389702</v>
       </c>
       <c r="E48">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
       <c r="F48">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
       <c r="G48">
-        <v>0.0844683152463559</v>
+        <v>0.06549347940676342</v>
       </c>
       <c r="H48">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1">
-        <v>46171</v>
+        <v>46169</v>
       </c>
       <c r="B49" t="s">
         <v>10</v>
       </c>
       <c r="C49">
-        <v>33.73370320039719</v>
+        <v>33.73350746548562</v>
       </c>
       <c r="D49">
-        <v>25.880209881309</v>
+        <v>25.75393367034243</v>
       </c>
       <c r="E49">
-        <v>0.9988</v>
+        <v>0.9987000000000001</v>
       </c>
       <c r="F49">
-        <v>0.9988</v>
+        <v>0.9987000000000001</v>
       </c>
       <c r="G49">
-        <v>0.08201990413931148</v>
+        <v>0.07620510288008187</v>
       </c>
       <c r="H49">
-        <v>0.9988</v>
+        <v>0.9987000000000001</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1">
-        <v>46174</v>
+        <v>46170</v>
       </c>
       <c r="B50" t="s">
         <v>10</v>
       </c>
       <c r="C50">
-        <v>33.45546240777382</v>
+        <v>33.84336414535104</v>
       </c>
       <c r="D50">
-        <v>25.61350381215703</v>
+        <v>25.97168203877208</v>
       </c>
       <c r="E50">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
       <c r="F50">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
       <c r="G50">
-        <v>0.06901304118647311</v>
+        <v>0.0844683152463559</v>
       </c>
       <c r="H50">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1">
-        <v>46175</v>
+        <v>46171</v>
       </c>
       <c r="B51" t="s">
         <v>10</v>
       </c>
       <c r="C51">
-        <v>33.31245255516097</v>
+        <v>33.73370320039719</v>
       </c>
       <c r="D51">
-        <v>25.36461330330757</v>
+        <v>25.880209881309</v>
       </c>
       <c r="E51">
-        <v>0.9989999999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="F51">
-        <v>0.9989999999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="G51">
-        <v>0.05845447259401171</v>
+        <v>0.08201990413931148</v>
       </c>
       <c r="H51">
-        <v>0.9989999999999999</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="B52" t="s">
         <v>10</v>
       </c>
       <c r="C52">
-        <v>33.02444632653544</v>
+        <v>33.45546240777382</v>
       </c>
       <c r="D52">
-        <v>25.07926152561908</v>
+        <v>25.61350381215703</v>
       </c>
       <c r="E52">
-        <v>0.9991</v>
+        <v>0.999</v>
       </c>
       <c r="F52">
-        <v>0.9991</v>
+        <v>0.999</v>
       </c>
       <c r="G52">
-        <v>0.04697780820974229</v>
+        <v>0.06901304118647311</v>
       </c>
       <c r="H52">
-        <v>0.9991</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1">
-        <v>46177</v>
+        <v>46175</v>
       </c>
       <c r="B53" t="s">
         <v>10</v>
       </c>
       <c r="C53">
-        <v>33.50291463064395</v>
+        <v>33.31245255516097</v>
       </c>
       <c r="D53">
-        <v>25.33002193941023</v>
+        <v>25.36461330330757</v>
       </c>
       <c r="E53">
-        <v>0.9991000000000001</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="F53">
-        <v>0.9991000000000001</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="G53">
-        <v>0.05768943168306073</v>
+        <v>0.05845447259401171</v>
       </c>
       <c r="H53">
-        <v>0.9991000000000001</v>
+        <v>0.9989999999999999</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1">
-        <v>46178</v>
+        <v>46176</v>
       </c>
       <c r="B54" t="s">
         <v>10</v>
       </c>
       <c r="C54">
-        <v>32.19021336116872</v>
+        <v>33.02444632653544</v>
       </c>
       <c r="D54">
-        <v>24.38570557505481</v>
+        <v>25.07926152561908</v>
       </c>
       <c r="E54">
         <v>0.9991</v>
@@ -1801,7 +1801,7 @@
         <v>0.9991</v>
       </c>
       <c r="G54">
-        <v>0.01775063028607016</v>
+        <v>0.04697780820974229</v>
       </c>
       <c r="H54">
         <v>0.9991</v>
@@ -1809,666 +1809,666 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1">
-        <v>46153</v>
+        <v>46177</v>
       </c>
       <c r="B55" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C55">
-        <v>36.55790859258162</v>
+        <v>33.50291463064395</v>
       </c>
       <c r="D55">
-        <v>22.67181120908155</v>
+        <v>25.33002193941023</v>
       </c>
       <c r="E55">
-        <v>0.9990740999999999</v>
+        <v>0.9991000000000001</v>
       </c>
       <c r="F55">
-        <v>0.9990740999999999</v>
+        <v>0.9991000000000001</v>
       </c>
       <c r="G55">
-        <v>0.1648443271746771</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H55">
-        <v>0.9990740999999999</v>
+        <v>0.9991000000000001</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1">
-        <v>46154</v>
+        <v>46178</v>
       </c>
       <c r="B56" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C56">
-        <v>36.44753722959613</v>
+        <v>32.19021336116872</v>
       </c>
       <c r="D56">
-        <v>22.40292401789388</v>
+        <v>24.38570557505481</v>
       </c>
       <c r="E56">
-        <v>0.9990772499999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F56">
-        <v>0.9990772499999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G56">
-        <v>0.154964342628132</v>
+        <v>0.01775063028607016</v>
       </c>
       <c r="H56">
-        <v>0.9990772499999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1">
-        <v>46155</v>
+        <v>46182</v>
       </c>
       <c r="B57" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C57">
-        <v>36.63128514035871</v>
+        <v>31.82278781619365</v>
       </c>
       <c r="D57">
-        <v>22.65773388934668</v>
+        <v>23.98410280709619</v>
       </c>
       <c r="E57">
-        <v>0.99907745</v>
+        <v>0.9992000000000001</v>
       </c>
       <c r="F57">
-        <v>0.99907745</v>
+        <v>0.9992000000000001</v>
       </c>
       <c r="G57">
-        <v>0.1671633421405267</v>
+        <v>-0.001224205553522206</v>
       </c>
       <c r="H57">
-        <v>0.99907745</v>
+        <v>0.9992000000000001</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="B58" t="s">
         <v>11</v>
       </c>
       <c r="C58">
-        <v>36.87865927427314</v>
+        <v>36.55790859258162</v>
       </c>
       <c r="D58">
-        <v>22.69755646854794</v>
+        <v>22.67181120908155</v>
       </c>
       <c r="E58">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="F58">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="G58">
-        <v>0.1754592080224002</v>
+        <v>0.1648443271746771</v>
       </c>
       <c r="H58">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="B59" t="s">
         <v>11</v>
       </c>
       <c r="C59">
-        <v>36.52208783231286</v>
+        <v>36.44753722959613</v>
       </c>
       <c r="D59">
-        <v>22.32462309676992</v>
+        <v>22.40292401789388</v>
       </c>
       <c r="E59">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="F59">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="G59">
-        <v>0.1577242156354994</v>
+        <v>0.154964342628132</v>
       </c>
       <c r="H59">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="B60" t="s">
         <v>11</v>
       </c>
       <c r="C60">
-        <v>36.25604200674668</v>
+        <v>36.63128514035871</v>
       </c>
       <c r="D60">
-        <v>22.16555007468561</v>
+        <v>22.65773388934668</v>
       </c>
       <c r="E60">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="F60">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="G60">
-        <v>0.1527434068648266</v>
+        <v>0.1671633421405267</v>
       </c>
       <c r="H60">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1">
-        <v>46161</v>
+        <v>46156</v>
       </c>
       <c r="B61" t="s">
         <v>11</v>
       </c>
       <c r="C61">
-        <v>36.01040085730018</v>
+        <v>36.87865927427314</v>
       </c>
       <c r="D61">
-        <v>22.19475589056387</v>
+        <v>22.69755646854794</v>
       </c>
       <c r="E61">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="F61">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="G61">
-        <v>0.1456396418594061</v>
+        <v>0.1754592080224002</v>
       </c>
       <c r="H61">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1">
-        <v>46162</v>
+        <v>46157</v>
       </c>
       <c r="B62" t="s">
         <v>11</v>
       </c>
       <c r="C62">
-        <v>36.45290912796982</v>
+        <v>36.52208783231286</v>
       </c>
       <c r="D62">
-        <v>22.46357594746874</v>
+        <v>22.32462309676992</v>
       </c>
       <c r="E62">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="F62">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="G62">
-        <v>0.1646157747240327</v>
+        <v>0.1577242156354994</v>
       </c>
       <c r="H62">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1">
-        <v>46163</v>
+        <v>46160</v>
       </c>
       <c r="B63" t="s">
         <v>11</v>
       </c>
       <c r="C63">
-        <v>35.75282090566891</v>
+        <v>36.25604200674668</v>
       </c>
       <c r="D63">
-        <v>22.57615417310648</v>
+        <v>22.16555007468561</v>
       </c>
       <c r="E63">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="F63">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="G63">
-        <v>0.1668367104873381</v>
+        <v>0.1527434068648266</v>
       </c>
       <c r="H63">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1">
-        <v>46164</v>
+        <v>46161</v>
       </c>
       <c r="B64" t="s">
         <v>11</v>
       </c>
       <c r="C64">
-        <v>35.75514940724808</v>
+        <v>36.01040085730018</v>
       </c>
       <c r="D64">
-        <v>22.28880693466429</v>
+        <v>22.19475589056387</v>
       </c>
       <c r="E64">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="F64">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="G64">
-        <v>0.1717848261904962</v>
+        <v>0.1456396418594061</v>
       </c>
       <c r="H64">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1">
-        <v>46167</v>
+        <v>46162</v>
       </c>
       <c r="B65" t="s">
         <v>11</v>
       </c>
       <c r="C65">
-        <v>35.84133099010302</v>
+        <v>36.45290912796982</v>
       </c>
       <c r="D65">
-        <v>22.37458514769363</v>
+        <v>22.46357594746874</v>
       </c>
       <c r="E65">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="F65">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="G65">
-        <v>0.1717848261904962</v>
+        <v>0.1646157747240327</v>
       </c>
       <c r="H65">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1">
-        <v>46168</v>
+        <v>46163</v>
       </c>
       <c r="B66" t="s">
         <v>11</v>
       </c>
       <c r="C66">
-        <v>36.23214279739292</v>
+        <v>35.75282090566891</v>
       </c>
       <c r="D66">
-        <v>22.93484792820123</v>
+        <v>22.57615417310648</v>
       </c>
       <c r="E66">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
       <c r="F66">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
       <c r="G66">
-        <v>0.1925900763781823</v>
+        <v>0.1668367104873381</v>
       </c>
       <c r="H66">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="B67" t="s">
         <v>11</v>
       </c>
       <c r="C67">
-        <v>36.4336692499184</v>
+        <v>35.75514940724808</v>
       </c>
       <c r="D67">
-        <v>22.75940954009856</v>
+        <v>22.28880693466429</v>
       </c>
       <c r="E67">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="F67">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="G67">
-        <v>0.1912346098381414</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H67">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="B68" t="s">
         <v>11</v>
       </c>
       <c r="C68">
-        <v>36.57358557066742</v>
+        <v>35.84133099010302</v>
       </c>
       <c r="D68">
-        <v>22.83069636955243</v>
+        <v>22.37458514769363</v>
       </c>
       <c r="E68">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="F68">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="G68">
-        <v>0.2012778603742877</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H68">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1">
-        <v>46171</v>
+        <v>46168</v>
       </c>
       <c r="B69" t="s">
         <v>11</v>
       </c>
       <c r="C69">
-        <v>36.67481300942</v>
+        <v>36.23214279739292</v>
       </c>
       <c r="D69">
-        <v>22.95852861681004</v>
+        <v>22.93484792820123</v>
       </c>
       <c r="E69">
-        <v>0.9964953299999998</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="F69">
-        <v>0.9964953299999998</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="G69">
-        <v>0.2057034850411275</v>
+        <v>0.1925900763781823</v>
       </c>
       <c r="H69">
-        <v>0.9994474899999999</v>
+        <v>0.9992609200000001</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1">
-        <v>46174</v>
+        <v>46169</v>
       </c>
       <c r="B70" t="s">
         <v>11</v>
       </c>
       <c r="C70">
-        <v>36.84565507982974</v>
+        <v>36.4336692499184</v>
       </c>
       <c r="D70">
-        <v>23.15960292175205</v>
+        <v>22.75940954009856</v>
       </c>
       <c r="E70">
-        <v>0.99646052</v>
+        <v>0.9992099400000001</v>
       </c>
       <c r="F70">
-        <v>0.99646052</v>
+        <v>0.9992099400000001</v>
       </c>
       <c r="G70">
-        <v>0.2129379226426205</v>
+        <v>0.1912346098381414</v>
       </c>
       <c r="H70">
-        <v>0.9993986199999999</v>
+        <v>0.9992099400000001</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1">
-        <v>46175</v>
+        <v>46170</v>
       </c>
       <c r="B71" t="s">
         <v>11</v>
       </c>
       <c r="C71">
-        <v>36.88482057171844</v>
+        <v>36.57358557066742</v>
       </c>
       <c r="D71">
-        <v>23.03898938038424</v>
+        <v>22.83069636955243</v>
       </c>
       <c r="E71">
-        <v>0.99645675</v>
+        <v>0.9994435600000001</v>
       </c>
       <c r="F71">
-        <v>0.99645675</v>
+        <v>0.9994435600000001</v>
       </c>
       <c r="G71">
-        <v>0.2185229551183987</v>
+        <v>0.2012778603742877</v>
       </c>
       <c r="H71">
-        <v>0.9994034199999998</v>
+        <v>0.9994435600000001</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1">
-        <v>46176</v>
+        <v>46171</v>
       </c>
       <c r="B72" t="s">
         <v>11</v>
       </c>
       <c r="C72">
-        <v>36.96809213745556</v>
+        <v>36.67481300942</v>
       </c>
       <c r="D72">
-        <v>22.99660212231548</v>
+        <v>22.95852861681004</v>
       </c>
       <c r="E72">
-        <v>0.9964706</v>
+        <v>0.9964953299999998</v>
       </c>
       <c r="F72">
-        <v>0.9964706</v>
+        <v>0.9964953299999998</v>
       </c>
       <c r="G72">
-        <v>0.2153385706032709</v>
+        <v>0.2057034850411275</v>
       </c>
       <c r="H72">
-        <v>0.9993955800000001</v>
+        <v>0.9994474899999999</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1">
-        <v>46177</v>
+        <v>46174</v>
       </c>
       <c r="B73" t="s">
         <v>11</v>
       </c>
       <c r="C73">
-        <v>37.13780815830533</v>
+        <v>36.84565507982974</v>
       </c>
       <c r="D73">
-        <v>22.74889586257873</v>
+        <v>23.15960292175205</v>
       </c>
       <c r="E73">
-        <v>0.9964706899999999</v>
+        <v>0.99646052</v>
       </c>
       <c r="F73">
-        <v>0.9964706899999999</v>
+        <v>0.99646052</v>
       </c>
       <c r="G73">
-        <v>0.2094594998678323</v>
+        <v>0.2129379226426205</v>
       </c>
       <c r="H73">
-        <v>0.99938478</v>
+        <v>0.9993986199999999</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1">
-        <v>46178</v>
+        <v>46175</v>
       </c>
       <c r="B74" t="s">
         <v>11</v>
       </c>
       <c r="C74">
-        <v>35.57681391373501</v>
+        <v>36.88482057171844</v>
       </c>
       <c r="D74">
-        <v>21.69452833602077</v>
+        <v>23.03898938038424</v>
       </c>
       <c r="E74">
-        <v>0.9964558499999999</v>
+        <v>0.99645675</v>
       </c>
       <c r="F74">
-        <v>0.9964558499999999</v>
+        <v>0.99645675</v>
       </c>
       <c r="G74">
-        <v>0.151404286858543</v>
+        <v>0.2185229551183987</v>
       </c>
       <c r="H74">
-        <v>0.9993850399999999</v>
+        <v>0.9994034199999998</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1">
-        <v>46153</v>
+        <v>46176</v>
       </c>
       <c r="B75" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C75">
-        <v>52.70832779833182</v>
+        <v>36.96809213745556</v>
       </c>
       <c r="D75">
-        <v>23.99044674439659</v>
+        <v>22.99660212231548</v>
       </c>
       <c r="E75">
-        <v>0.9994000000000002</v>
+        <v>0.9964706</v>
       </c>
       <c r="F75">
-        <v>0.9994000000000002</v>
+        <v>0.9964706</v>
       </c>
       <c r="G75">
-        <v>0.5438253854918791</v>
+        <v>0.2153385706032709</v>
       </c>
       <c r="H75">
-        <v>0.9994000000000002</v>
+        <v>0.9993955800000001</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1">
-        <v>46154</v>
+        <v>46177</v>
       </c>
       <c r="B76" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C76">
-        <v>50.89464485280568</v>
+        <v>37.13780815830533</v>
       </c>
       <c r="D76">
-        <v>23.21558303176282</v>
+        <v>22.74889586257873</v>
       </c>
       <c r="E76">
-        <v>0.9996</v>
+        <v>0.9964706899999999</v>
       </c>
       <c r="F76">
-        <v>0.9996</v>
+        <v>0.9964706899999999</v>
       </c>
       <c r="G76">
-        <v>0.5034825029548833</v>
+        <v>0.2094594998678323</v>
       </c>
       <c r="H76">
-        <v>0.9996</v>
+        <v>0.99938478</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1">
-        <v>46155</v>
+        <v>46178</v>
       </c>
       <c r="B77" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C77">
-        <v>51.8659994471731</v>
+        <v>35.57681391373501</v>
       </c>
       <c r="D77">
-        <v>23.7009037279043</v>
+        <v>21.69452833602077</v>
       </c>
       <c r="E77">
-        <v>1.0002</v>
+        <v>0.9964558499999999</v>
       </c>
       <c r="F77">
-        <v>1.0002</v>
+        <v>0.9964558499999999</v>
       </c>
       <c r="G77">
-        <v>0.533512029714132</v>
+        <v>0.151404286858543</v>
       </c>
       <c r="H77">
-        <v>1.0002</v>
+        <v>0.9993850399999999</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="1">
-        <v>46156</v>
+        <v>46182</v>
       </c>
       <c r="B78" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C78">
-        <v>52.4470179952828</v>
+        <v>35.07954985374597</v>
       </c>
       <c r="D78">
-        <v>23.76861704536814</v>
+        <v>21.50135646273161</v>
       </c>
       <c r="E78">
-        <v>0.9998</v>
+        <v>0.9962853900000002</v>
       </c>
       <c r="F78">
-        <v>0.9998</v>
+        <v>0.9962853900000002</v>
       </c>
       <c r="G78">
-        <v>0.5492634496849078</v>
+        <v>0.1358738837011901</v>
       </c>
       <c r="H78">
-        <v>0.9998</v>
+        <v>0.9992534400000002</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="B79" t="s">
         <v>12</v>
       </c>
       <c r="C79">
-        <v>50.81077380018606</v>
+        <v>52.70832779833182</v>
       </c>
       <c r="D79">
-        <v>22.76900580927995</v>
+        <v>23.99044674439659</v>
       </c>
       <c r="E79">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="F79">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="G79">
-        <v>0.4903296143797722</v>
+        <v>0.5438253854918791</v>
       </c>
       <c r="H79">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1">
-        <v>46160</v>
+        <v>46154</v>
       </c>
       <c r="B80" t="s">
         <v>12</v>
       </c>
       <c r="C80">
-        <v>49.50286387149169</v>
+        <v>50.89464485280568</v>
       </c>
       <c r="D80">
-        <v>22.24532119914133</v>
+        <v>23.21558303176282</v>
       </c>
       <c r="E80">
         <v>0.9996</v>
@@ -2477,7 +2477,7 @@
         <v>0.9996</v>
       </c>
       <c r="G80">
-        <v>0.4630591776162345</v>
+        <v>0.5034825029548833</v>
       </c>
       <c r="H80">
         <v>0.9996</v>
@@ -2485,224 +2485,224 @@
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="1">
-        <v>46161</v>
+        <v>46155</v>
       </c>
       <c r="B81" t="s">
         <v>12</v>
       </c>
       <c r="C81">
-        <v>49.29146729279496</v>
+        <v>51.8659994471731</v>
       </c>
       <c r="D81">
-        <v>22.22167836589682</v>
+        <v>23.7009037279043</v>
       </c>
       <c r="E81">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="F81">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="G81">
-        <v>0.4571659248870246</v>
+        <v>0.533512029714132</v>
       </c>
       <c r="H81">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="1">
-        <v>46162</v>
+        <v>46156</v>
       </c>
       <c r="B82" t="s">
         <v>12</v>
       </c>
       <c r="C82">
-        <v>50.88652370817657</v>
+        <v>52.4470179952828</v>
       </c>
       <c r="D82">
-        <v>22.93254398967657</v>
+        <v>23.76861704536814</v>
       </c>
       <c r="E82">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F82">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G82">
-        <v>0.5126171754864624</v>
+        <v>0.5492634496849078</v>
       </c>
       <c r="H82">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="1">
-        <v>46163</v>
+        <v>46157</v>
       </c>
       <c r="B83" t="s">
         <v>12</v>
       </c>
       <c r="C83">
-        <v>48.26646764818586</v>
+        <v>50.81077380018606</v>
       </c>
       <c r="D83">
-        <v>23.11655387625012</v>
+        <v>22.76900580927995</v>
       </c>
       <c r="E83">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="F83">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="G83">
-        <v>0.521243030947425</v>
+        <v>0.4903296143797722</v>
       </c>
       <c r="H83">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="1">
-        <v>46164</v>
+        <v>46160</v>
       </c>
       <c r="B84" t="s">
         <v>12</v>
       </c>
       <c r="C84">
-        <v>48.84737503703267</v>
+        <v>49.50286387149169</v>
       </c>
       <c r="D84">
-        <v>22.83557604744466</v>
+        <v>22.24532119914133</v>
       </c>
       <c r="E84">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="F84">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="G84">
-        <v>0.5438521997590966</v>
+        <v>0.4630591776162345</v>
       </c>
       <c r="H84">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1">
-        <v>46167</v>
+        <v>46161</v>
       </c>
       <c r="B85" t="s">
         <v>12</v>
       </c>
       <c r="C85">
-        <v>48.85151560750146</v>
+        <v>49.29146729279496</v>
       </c>
       <c r="D85">
-        <v>22.83513820206554</v>
+        <v>22.22167836589682</v>
       </c>
       <c r="E85">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F85">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G85">
-        <v>0.5438521997590966</v>
+        <v>0.4571659248870246</v>
       </c>
       <c r="H85">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="1">
-        <v>46168</v>
+        <v>46162</v>
       </c>
       <c r="B86" t="s">
         <v>12</v>
       </c>
       <c r="C86">
-        <v>50.90437883274981</v>
+        <v>50.88652370817657</v>
       </c>
       <c r="D86">
-        <v>24.25672473501501</v>
+        <v>22.93254398967657</v>
       </c>
       <c r="E86">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F86">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G86">
-        <v>0.6130191115419561</v>
+        <v>0.5126171754864624</v>
       </c>
       <c r="H86">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="1">
-        <v>46169</v>
+        <v>46163</v>
       </c>
       <c r="B87" t="s">
         <v>12</v>
       </c>
       <c r="C87">
-        <v>50.47312432255841</v>
+        <v>48.26646764818586</v>
       </c>
       <c r="D87">
-        <v>23.84499305142194</v>
+        <v>23.11655387625012</v>
       </c>
       <c r="E87">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="F87">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="G87">
-        <v>0.5952317692821967</v>
+        <v>0.521243030947425</v>
       </c>
       <c r="H87">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1">
-        <v>46170</v>
+        <v>46164</v>
       </c>
       <c r="B88" t="s">
         <v>12</v>
       </c>
       <c r="C88">
-        <v>50.84596269629946</v>
+        <v>48.84737503703267</v>
       </c>
       <c r="D88">
-        <v>23.7680603326165</v>
+        <v>22.83557604744466</v>
       </c>
       <c r="E88">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F88">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G88">
-        <v>0.606831065374982</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H88">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="1">
-        <v>46171</v>
+        <v>46167</v>
       </c>
       <c r="B89" t="s">
         <v>12</v>
       </c>
       <c r="C89">
-        <v>51.08372269965196</v>
+        <v>48.85151560750146</v>
       </c>
       <c r="D89">
-        <v>23.88880359436525</v>
+        <v>22.83513820206554</v>
       </c>
       <c r="E89">
         <v>0.9998999999999999</v>
@@ -2711,7 +2711,7 @@
         <v>0.9998999999999999</v>
       </c>
       <c r="G89">
-        <v>0.604420070348211</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H89">
         <v>0.9998999999999999</v>
@@ -2719,588 +2719,588 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="1">
-        <v>46174</v>
+        <v>46168</v>
       </c>
       <c r="B90" t="s">
         <v>12</v>
       </c>
       <c r="C90">
-        <v>51.84875713649351</v>
+        <v>50.90437883274981</v>
       </c>
       <c r="D90">
-        <v>24.29466650399529</v>
+        <v>24.25672473501501</v>
       </c>
       <c r="E90">
-        <v>0.9998</v>
+        <v>0.9996999999999999</v>
       </c>
       <c r="F90">
-        <v>0.9998</v>
+        <v>0.9996999999999999</v>
       </c>
       <c r="G90">
-        <v>0.6282079224060508</v>
+        <v>0.6130191115419561</v>
       </c>
       <c r="H90">
-        <v>0.9998</v>
+        <v>0.9996999999999999</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="1">
-        <v>46175</v>
+        <v>46169</v>
       </c>
       <c r="B91" t="s">
         <v>12</v>
       </c>
       <c r="C91">
-        <v>53.42858844634741</v>
+        <v>50.47312432255841</v>
       </c>
       <c r="D91">
-        <v>24.82449061140869</v>
+        <v>23.84499305142194</v>
       </c>
       <c r="E91">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="F91">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="G91">
-        <v>0.6935709687814895</v>
+        <v>0.5952317692821967</v>
       </c>
       <c r="H91">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="1">
-        <v>46176</v>
+        <v>46170</v>
       </c>
       <c r="B92" t="s">
         <v>12</v>
       </c>
       <c r="C92">
-        <v>53.95056789686777</v>
+        <v>50.84596269629946</v>
       </c>
       <c r="D92">
-        <v>24.99295077214167</v>
+        <v>23.7680603326165</v>
       </c>
       <c r="E92">
-        <v>0.9996000000000002</v>
+        <v>0.9998</v>
       </c>
       <c r="F92">
-        <v>0.9996000000000002</v>
+        <v>0.9998</v>
       </c>
       <c r="G92">
-        <v>0.7088134081800193</v>
+        <v>0.606831065374982</v>
       </c>
       <c r="H92">
-        <v>0.9996000000000002</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="1">
-        <v>46177</v>
+        <v>46171</v>
       </c>
       <c r="B93" t="s">
         <v>12</v>
       </c>
       <c r="C93">
-        <v>53.29782764127071</v>
+        <v>51.08372269965196</v>
       </c>
       <c r="D93">
-        <v>24.48126483589962</v>
+        <v>23.88880359436525</v>
       </c>
       <c r="E93">
-        <v>1.0001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F93">
-        <v>1.0001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G93">
-        <v>0.6810341543458651</v>
+        <v>0.604420070348211</v>
       </c>
       <c r="H93">
-        <v>1.0001</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="1">
-        <v>46178</v>
+        <v>46174</v>
       </c>
       <c r="B94" t="s">
         <v>12</v>
       </c>
       <c r="C94">
-        <v>48.44949949587421</v>
+        <v>51.84875713649351</v>
       </c>
       <c r="D94">
-        <v>22.39103669390088</v>
+        <v>24.29466650399529</v>
       </c>
       <c r="E94">
-        <v>0.9995999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F94">
-        <v>0.9995999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G94">
-        <v>0.5260916717665549</v>
+        <v>0.6282079224060508</v>
       </c>
       <c r="H94">
-        <v>0.9995999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="1">
-        <v>46153</v>
+        <v>46175</v>
       </c>
       <c r="B95" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C95">
-        <v>57.1732166855686</v>
+        <v>53.42858844634741</v>
       </c>
       <c r="D95">
-        <v>23.50022751267814</v>
+        <v>24.82449061140869</v>
       </c>
       <c r="E95">
-        <v>0.9991</v>
+        <v>1</v>
       </c>
       <c r="F95">
-        <v>0.9991</v>
+        <v>1</v>
       </c>
       <c r="G95">
-        <v>0.6994110097039083</v>
+        <v>0.6935709687814895</v>
       </c>
       <c r="H95">
-        <v>0.9991</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="1">
-        <v>46154</v>
+        <v>46176</v>
       </c>
       <c r="B96" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C96">
-        <v>54.77380642078597</v>
+        <v>53.95056789686777</v>
       </c>
       <c r="D96">
-        <v>22.55192940254518</v>
+        <v>24.99295077214167</v>
       </c>
       <c r="E96">
-        <v>0.9990000000000001</v>
+        <v>0.9996000000000002</v>
       </c>
       <c r="F96">
-        <v>0.9990000000000001</v>
+        <v>0.9996000000000002</v>
       </c>
       <c r="G96">
-        <v>0.6459175880844941</v>
+        <v>0.7088134081800193</v>
       </c>
       <c r="H96">
-        <v>0.9990000000000001</v>
+        <v>0.9996000000000002</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="1">
-        <v>46155</v>
+        <v>46177</v>
       </c>
       <c r="B97" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C97">
-        <v>56.32187380830906</v>
+        <v>53.29782764127071</v>
       </c>
       <c r="D97">
-        <v>23.17121437414109</v>
+        <v>24.48126483589962</v>
       </c>
       <c r="E97">
-        <v>0.9990000000000001</v>
+        <v>1.0001</v>
       </c>
       <c r="F97">
-        <v>0.9990000000000001</v>
+        <v>1.0001</v>
       </c>
       <c r="G97">
-        <v>0.6851523922954754</v>
+        <v>0.6810341543458651</v>
       </c>
       <c r="H97">
-        <v>0.9990000000000001</v>
+        <v>1.0001</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="1">
-        <v>46156</v>
+        <v>46178</v>
       </c>
       <c r="B98" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C98">
-        <v>56.15321618553139</v>
+        <v>48.44949949587421</v>
       </c>
       <c r="D98">
-        <v>22.95838347314443</v>
+        <v>22.39103669390088</v>
       </c>
       <c r="E98">
-        <v>0.9992</v>
+        <v>0.9995999999999999</v>
       </c>
       <c r="F98">
-        <v>0.9992</v>
+        <v>0.9995999999999999</v>
       </c>
       <c r="G98">
-        <v>0.6907028507208208</v>
+        <v>0.5260916717665549</v>
       </c>
       <c r="H98">
-        <v>0.9992</v>
+        <v>0.9995999999999999</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="1">
-        <v>46157</v>
+        <v>46182</v>
       </c>
       <c r="B99" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C99">
-        <v>54.47755813049488</v>
+        <v>48.59345545448965</v>
       </c>
       <c r="D99">
-        <v>22.0083816089626</v>
+        <v>22.38620275513295</v>
       </c>
       <c r="E99">
-        <v>0.9986</v>
+        <v>0.9997</v>
       </c>
       <c r="F99">
-        <v>0.9986</v>
+        <v>0.9997</v>
       </c>
       <c r="G99">
-        <v>0.6220895940829376</v>
+        <v>0.53573532487038</v>
       </c>
       <c r="H99">
-        <v>0.9986</v>
+        <v>0.9997</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B100" t="s">
         <v>13</v>
       </c>
       <c r="C100">
-        <v>52.6278781150669</v>
+        <v>57.1732166855686</v>
       </c>
       <c r="D100">
-        <v>21.5357353870778</v>
+        <v>23.50022751267814</v>
       </c>
       <c r="E100">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F100">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G100">
-        <v>0.5845134636435627</v>
+        <v>0.6994110097039083</v>
       </c>
       <c r="H100">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B101" t="s">
         <v>13</v>
       </c>
       <c r="C101">
-        <v>54.91583234840245</v>
+        <v>54.77380642078597</v>
       </c>
       <c r="D101">
-        <v>22.38321645985006</v>
+        <v>22.55192940254518</v>
       </c>
       <c r="E101">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F101">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G101">
-        <v>0.6596976539194066</v>
+        <v>0.6459175880844941</v>
       </c>
       <c r="H101">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B102" t="s">
         <v>13</v>
       </c>
       <c r="C102">
-        <v>53.91712298548793</v>
+        <v>56.32187380830906</v>
       </c>
       <c r="D102">
-        <v>22.73711181201267</v>
+        <v>23.17121437414109</v>
       </c>
       <c r="E102">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F102">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G102">
-        <v>0.6737329602396263</v>
+        <v>0.6851523922954754</v>
       </c>
       <c r="H102">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="1">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="B103" t="s">
         <v>13</v>
       </c>
       <c r="C103">
-        <v>55.19651747515625</v>
+        <v>56.15321618553139</v>
       </c>
       <c r="D103">
-        <v>22.79462037330554</v>
+        <v>22.95838347314443</v>
       </c>
       <c r="E103">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
       <c r="F103">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
       <c r="G103">
-        <v>0.7139885317003913</v>
+        <v>0.6907028507208208</v>
       </c>
       <c r="H103">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="1">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="B104" t="s">
         <v>13</v>
       </c>
       <c r="C104">
-        <v>55.28054997487197</v>
+        <v>54.47755813049488</v>
       </c>
       <c r="D104">
-        <v>23.00160891539877</v>
+        <v>22.0083816089626</v>
       </c>
       <c r="E104">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="F104">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="G104">
-        <v>0.7139885317003913</v>
+        <v>0.6220895940829376</v>
       </c>
       <c r="H104">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="1">
-        <v>46168</v>
+        <v>46161</v>
       </c>
       <c r="B105" t="s">
         <v>13</v>
       </c>
       <c r="C105">
-        <v>58.75156728873073</v>
+        <v>52.6278781150669</v>
       </c>
       <c r="D105">
-        <v>24.84249654093248</v>
+        <v>21.5357353870778</v>
       </c>
       <c r="E105">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="F105">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="G105">
-        <v>0.8184872182632257</v>
+        <v>0.5845134636435627</v>
       </c>
       <c r="H105">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="1">
-        <v>46169</v>
+        <v>46162</v>
       </c>
       <c r="B106" t="s">
         <v>13</v>
       </c>
       <c r="C106">
-        <v>57.86771234337395</v>
+        <v>54.91583234840245</v>
       </c>
       <c r="D106">
-        <v>24.21066615243091</v>
+        <v>22.38321645985006</v>
       </c>
       <c r="E106">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="F106">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="G106">
-        <v>0.798997241708943</v>
+        <v>0.6596976539194066</v>
       </c>
       <c r="H106">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="1">
-        <v>46170</v>
+        <v>46163</v>
       </c>
       <c r="B107" t="s">
         <v>13</v>
       </c>
       <c r="C107">
-        <v>58.18666682631797</v>
+        <v>53.91712298548793</v>
       </c>
       <c r="D107">
-        <v>24.09552344282839</v>
+        <v>22.73711181201267</v>
       </c>
       <c r="E107">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="F107">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="G107">
-        <v>0.8165093478664007</v>
+        <v>0.6737329602396263</v>
       </c>
       <c r="H107">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="1">
-        <v>46171</v>
+        <v>46164</v>
       </c>
       <c r="B108" t="s">
         <v>13</v>
       </c>
       <c r="C108">
-        <v>58.79256019733606</v>
+        <v>55.19651747515625</v>
       </c>
       <c r="D108">
-        <v>24.33854853448823</v>
+        <v>22.79462037330554</v>
       </c>
       <c r="E108">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F108">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G108">
-        <v>0.8152654642198496</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H108">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="1">
-        <v>46174</v>
+        <v>46167</v>
       </c>
       <c r="B109" t="s">
         <v>13</v>
       </c>
       <c r="C109">
-        <v>58.97156722185718</v>
+        <v>55.28054997487197</v>
       </c>
       <c r="D109">
-        <v>24.48296361348067</v>
+        <v>23.00160891539877</v>
       </c>
       <c r="E109">
-        <v>0.9990000000000001</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="F109">
-        <v>0.9990000000000001</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="G109">
-        <v>0.8243563865851753</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H109">
-        <v>0.9990000000000001</v>
+        <v>0.9989000000000001</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="1">
-        <v>46175</v>
+        <v>46168</v>
       </c>
       <c r="B110" t="s">
         <v>13</v>
       </c>
       <c r="C110">
-        <v>61.6542902214027</v>
+        <v>58.75156728873073</v>
       </c>
       <c r="D110">
-        <v>25.06517348653028</v>
+        <v>24.84249654093248</v>
       </c>
       <c r="E110">
-        <v>0.9988</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="F110">
-        <v>0.9988</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="G110">
-        <v>0.9299077697948877</v>
+        <v>0.8184872182632257</v>
       </c>
       <c r="H110">
-        <v>0.9988</v>
+        <v>0.9989000000000001</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="1">
-        <v>46176</v>
+        <v>46169</v>
       </c>
       <c r="B111" t="s">
         <v>13</v>
       </c>
       <c r="C111">
-        <v>63.0681947750049</v>
+        <v>57.86771234337395</v>
       </c>
       <c r="D111">
-        <v>25.58770976382014</v>
+        <v>24.21066615243091</v>
       </c>
       <c r="E111">
-        <v>0.9988000000000002</v>
+        <v>0.9986999999999999</v>
       </c>
       <c r="F111">
-        <v>0.9988000000000002</v>
+        <v>0.9986999999999999</v>
       </c>
       <c r="G111">
-        <v>0.9639112148600193</v>
+        <v>0.798997241708943</v>
       </c>
       <c r="H111">
-        <v>0.9988000000000002</v>
+        <v>0.9986999999999999</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="1">
-        <v>46177</v>
+        <v>46170</v>
       </c>
       <c r="B112" t="s">
         <v>13</v>
       </c>
       <c r="C112">
-        <v>61.53154955456358</v>
+        <v>58.18666682631797</v>
       </c>
       <c r="D112">
-        <v>24.75810538712983</v>
+        <v>24.09552344282839</v>
       </c>
       <c r="E112">
         <v>0.9991</v>
@@ -3309,7 +3309,7 @@
         <v>0.9991</v>
       </c>
       <c r="G112">
-        <v>0.9225710173552821</v>
+        <v>0.8165093478664007</v>
       </c>
       <c r="H112">
         <v>0.9991</v>
@@ -3317,822 +3317,822 @@
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="1">
-        <v>46178</v>
+        <v>46171</v>
       </c>
       <c r="B113" t="s">
         <v>13</v>
       </c>
       <c r="C113">
-        <v>55.42493637343647</v>
+        <v>58.79256019733606</v>
       </c>
       <c r="D113">
-        <v>22.47054621698377</v>
+        <v>24.33854853448823</v>
       </c>
       <c r="E113">
-        <v>0.9987</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="F113">
-        <v>0.9987</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="G113">
-        <v>0.7217717116249776</v>
+        <v>0.8152654642198496</v>
       </c>
       <c r="H113">
-        <v>0.9987</v>
+        <v>0.9989999999999999</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="1">
-        <v>46153</v>
+        <v>46174</v>
       </c>
       <c r="B114" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C114">
-        <v>35.78646526282436</v>
+        <v>58.97156722185718</v>
       </c>
       <c r="D114">
-        <v>18.96635091925032</v>
+        <v>24.48296361348067</v>
       </c>
       <c r="E114">
-        <v>0.9996491399999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F114">
-        <v>0.9996491399999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G114">
-        <v>0.2240600969213613</v>
+        <v>0.8243563865851753</v>
       </c>
       <c r="H114">
-        <v>0.9985614899999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="1">
-        <v>46154</v>
+        <v>46175</v>
       </c>
       <c r="B115" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C115">
-        <v>35.71584102184062</v>
+        <v>61.6542902214027</v>
       </c>
       <c r="D115">
-        <v>18.62432950231353</v>
+        <v>25.06517348653028</v>
       </c>
       <c r="E115">
-        <v>0.99965481</v>
+        <v>0.9988</v>
       </c>
       <c r="F115">
-        <v>0.99965481</v>
+        <v>0.9988</v>
       </c>
       <c r="G115">
-        <v>0.2104844827747143</v>
+        <v>0.9299077697948877</v>
       </c>
       <c r="H115">
-        <v>0.9985622199999999</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="1">
-        <v>46155</v>
+        <v>46176</v>
       </c>
       <c r="B116" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C116">
-        <v>35.95182028203252</v>
+        <v>63.0681947750049</v>
       </c>
       <c r="D116">
-        <v>18.95670796791552</v>
+        <v>25.58770976382014</v>
       </c>
       <c r="E116">
-        <v>0.9996515200000001</v>
+        <v>0.9988000000000002</v>
       </c>
       <c r="F116">
-        <v>0.9996515200000001</v>
+        <v>0.9988000000000002</v>
       </c>
       <c r="G116">
-        <v>0.2259035693959275</v>
+        <v>0.9639112148600193</v>
       </c>
       <c r="H116">
-        <v>0.99855193</v>
+        <v>0.9988000000000002</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="1">
-        <v>46156</v>
+        <v>46177</v>
       </c>
       <c r="B117" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C117">
-        <v>36.14451597805883</v>
+        <v>61.53154955456358</v>
       </c>
       <c r="D117">
-        <v>18.86297660538653</v>
+        <v>24.75810538712983</v>
       </c>
       <c r="E117">
-        <v>0.9996563399999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F117">
-        <v>0.9996563399999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G117">
-        <v>0.2362110061840785</v>
+        <v>0.9225710173552821</v>
       </c>
       <c r="H117">
-        <v>0.99857265</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="1">
-        <v>46157</v>
+        <v>46178</v>
       </c>
       <c r="B118" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C118">
-        <v>35.32805803135546</v>
+        <v>55.42493637343647</v>
       </c>
       <c r="D118">
-        <v>18.35643242381478</v>
+        <v>22.47054621698377</v>
       </c>
       <c r="E118">
-        <v>0.9997415800000001</v>
+        <v>0.9987</v>
       </c>
       <c r="F118">
-        <v>0.9997415800000001</v>
+        <v>0.9987</v>
       </c>
       <c r="G118">
-        <v>0.2023559161375383</v>
+        <v>0.7217717116249776</v>
       </c>
       <c r="H118">
-        <v>0.9986639900000002</v>
+        <v>0.9987</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="1">
-        <v>46160</v>
+        <v>46182</v>
       </c>
       <c r="B119" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C119">
-        <v>34.83995455757461</v>
+        <v>55.60031148827208</v>
       </c>
       <c r="D119">
-        <v>18.02301281718857</v>
+        <v>22.45772203407765</v>
       </c>
       <c r="E119">
-        <v>0.9996851299999999</v>
+        <v>0.999</v>
       </c>
       <c r="F119">
-        <v>0.9996851299999999</v>
+        <v>0.999</v>
       </c>
       <c r="G119">
-        <v>0.1850932291737926</v>
+        <v>0.7325533345047268</v>
       </c>
       <c r="H119">
-        <v>0.99857724</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B120" t="s">
         <v>14</v>
       </c>
       <c r="C120">
-        <v>34.45479308705605</v>
+        <v>35.78646526282436</v>
       </c>
       <c r="D120">
-        <v>18.09576834566068</v>
+        <v>18.96635091925032</v>
       </c>
       <c r="E120">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="F120">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="G120">
-        <v>0.1784731209386736</v>
+        <v>0.2240600969213613</v>
       </c>
       <c r="H120">
-        <v>0.9985337599999999</v>
+        <v>0.9985614899999999</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B121" t="s">
         <v>14</v>
       </c>
       <c r="C121">
-        <v>34.96336277390787</v>
+        <v>35.71584102184062</v>
       </c>
       <c r="D121">
-        <v>18.34938420029253</v>
+        <v>18.62432950231353</v>
       </c>
       <c r="E121">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="F121">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="G121">
-        <v>0.2009313391215752</v>
+        <v>0.2104844827747143</v>
       </c>
       <c r="H121">
-        <v>0.99848777</v>
+        <v>0.9985622199999999</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B122" t="s">
         <v>14</v>
       </c>
       <c r="C122">
-        <v>34.44616924817128</v>
+        <v>35.95182028203252</v>
       </c>
       <c r="D122">
-        <v>18.60085625074367</v>
+        <v>18.95670796791552</v>
       </c>
       <c r="E122">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="F122">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="G122">
-        <v>0.2124957180214682</v>
+        <v>0.2259035693959275</v>
       </c>
       <c r="H122">
-        <v>0.9985085200000001</v>
+        <v>0.99855193</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="1">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="B123" t="s">
         <v>14</v>
       </c>
       <c r="C123">
-        <v>34.62137220937314</v>
+        <v>36.14451597805883</v>
       </c>
       <c r="D123">
-        <v>18.28780484745949</v>
+        <v>18.86297660538653</v>
       </c>
       <c r="E123">
-        <v>0.9996106299999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="F123">
-        <v>0.9996106299999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="G123">
-        <v>0.2145907067863493</v>
+        <v>0.2362110061840785</v>
       </c>
       <c r="H123">
-        <v>0.9932939299999999</v>
+        <v>0.99857265</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="1">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="B124" t="s">
         <v>14</v>
       </c>
       <c r="C124">
-        <v>34.6540695486741</v>
+        <v>35.32805803135546</v>
       </c>
       <c r="D124">
-        <v>18.36409048915342</v>
+        <v>18.35643242381478</v>
       </c>
       <c r="E124">
-        <v>0.9995448900000001</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="F124">
-        <v>0.9995448900000001</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="G124">
-        <v>0.2145907067863493</v>
+        <v>0.2023559161375383</v>
       </c>
       <c r="H124">
-        <v>0.9984302600000001</v>
+        <v>0.9986639900000002</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="1">
-        <v>46168</v>
+        <v>46160</v>
       </c>
       <c r="B125" t="s">
         <v>14</v>
       </c>
       <c r="C125">
-        <v>35.4820130509417</v>
+        <v>34.83995455757461</v>
       </c>
       <c r="D125">
-        <v>19.20292041814603</v>
+        <v>18.02301281718857</v>
       </c>
       <c r="E125">
-        <v>0.9995448900000001</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="F125">
-        <v>0.9995448900000001</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="G125">
-        <v>0.2553172934903569</v>
+        <v>0.1850932291737926</v>
       </c>
       <c r="H125">
-        <v>0.9984302600000001</v>
+        <v>0.99857724</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" s="1">
-        <v>46169</v>
+        <v>46161</v>
       </c>
       <c r="B126" t="s">
         <v>14</v>
       </c>
       <c r="C126">
-        <v>35.71913468603401</v>
+        <v>34.45479308705605</v>
       </c>
       <c r="D126">
-        <v>18.96318693998171</v>
+        <v>18.09576834566068</v>
       </c>
       <c r="E126">
-        <v>0.99955466</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="F126">
-        <v>0.99955466</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="G126">
-        <v>0.2536413280520453</v>
+        <v>0.1784731209386736</v>
       </c>
       <c r="H126">
-        <v>0.9984700500000001</v>
+        <v>0.9985337599999999</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" s="1">
-        <v>46170</v>
+        <v>46162</v>
       </c>
       <c r="B127" t="s">
         <v>14</v>
       </c>
       <c r="C127">
-        <v>35.76226417354731</v>
+        <v>34.96336277390787</v>
       </c>
       <c r="D127">
-        <v>18.89050847207122</v>
+        <v>18.34938420029253</v>
       </c>
       <c r="E127">
-        <v>0.9995525399999999</v>
+        <v>0.99963413</v>
       </c>
       <c r="F127">
-        <v>0.9995525399999999</v>
+        <v>0.99963413</v>
       </c>
       <c r="G127">
-        <v>0.2580826940041561</v>
+        <v>0.2009313391215752</v>
       </c>
       <c r="H127">
-        <v>0.99847732</v>
+        <v>0.99848777</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="1">
-        <v>46171</v>
+        <v>46163</v>
       </c>
       <c r="B128" t="s">
         <v>14</v>
       </c>
       <c r="C128">
-        <v>35.84309020154227</v>
+        <v>34.44616924817128</v>
       </c>
       <c r="D128">
-        <v>19.06511612333149</v>
+        <v>18.60085625074367</v>
       </c>
       <c r="E128">
-        <v>0.9995533299999999</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="F128">
-        <v>0.9995533299999999</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="G128">
-        <v>0.2619374017254759</v>
+        <v>0.2124957180214682</v>
       </c>
       <c r="H128">
-        <v>0.99849382</v>
+        <v>0.9985085200000001</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="1">
-        <v>46174</v>
+        <v>46164</v>
       </c>
       <c r="B129" t="s">
         <v>14</v>
       </c>
       <c r="C129">
-        <v>36.27022125574057</v>
+        <v>34.62137220937314</v>
       </c>
       <c r="D129">
-        <v>19.32711369104533</v>
+        <v>18.28780484745949</v>
       </c>
       <c r="E129">
-        <v>0.9995550400000001</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="F129">
-        <v>0.9995550400000001</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="G129">
-        <v>0.2764348160433892</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H129">
-        <v>0.9985177199999999</v>
+        <v>0.9932939299999999</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" s="1">
-        <v>46175</v>
+        <v>46167</v>
       </c>
       <c r="B130" t="s">
         <v>14</v>
       </c>
       <c r="C130">
-        <v>36.57133692946976</v>
+        <v>34.6540695486741</v>
       </c>
       <c r="D130">
-        <v>19.33857330565742</v>
+        <v>18.36409048915342</v>
       </c>
       <c r="E130">
-        <v>0.9994989200000002</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="F130">
-        <v>0.9994989200000002</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="G130">
-        <v>0.2931947261624381</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H130">
-        <v>0.9984577800000001</v>
+        <v>0.9984302600000001</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" s="1">
-        <v>46176</v>
+        <v>46168</v>
       </c>
       <c r="B131" t="s">
         <v>14</v>
       </c>
       <c r="C131">
-        <v>36.8289666508657</v>
+        <v>35.4820130509417</v>
       </c>
       <c r="D131">
-        <v>19.43137154505686</v>
+        <v>19.20292041814603</v>
       </c>
       <c r="E131">
-        <v>0.9994838199999998</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="F131">
-        <v>0.9994838199999998</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="G131">
-        <v>0.2996471994933361</v>
+        <v>0.2553172934903569</v>
       </c>
       <c r="H131">
-        <v>0.9984549499999998</v>
+        <v>0.9984302600000001</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="1">
-        <v>46177</v>
+        <v>46169</v>
       </c>
       <c r="B132" t="s">
         <v>14</v>
       </c>
       <c r="C132">
-        <v>36.76760036565858</v>
+        <v>35.71913468603401</v>
       </c>
       <c r="D132">
-        <v>18.98774474764188</v>
+        <v>18.96318693998171</v>
       </c>
       <c r="E132">
-        <v>0.99948384</v>
+        <v>0.99955466</v>
       </c>
       <c r="F132">
-        <v>0.99948384</v>
+        <v>0.99955466</v>
       </c>
       <c r="G132">
-        <v>0.2807085470912787</v>
+        <v>0.2536413280520453</v>
       </c>
       <c r="H132">
-        <v>0.9984696899999999</v>
+        <v>0.9984700500000001</v>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="1">
-        <v>46178</v>
+        <v>46170</v>
       </c>
       <c r="B133" t="s">
         <v>14</v>
       </c>
       <c r="C133">
-        <v>34.71533981972338</v>
+        <v>35.76226417354731</v>
       </c>
       <c r="D133">
-        <v>17.87291658642534</v>
+        <v>18.89050847207122</v>
       </c>
       <c r="E133">
-        <v>0.9994584900000001</v>
+        <v>0.9995525399999999</v>
       </c>
       <c r="F133">
-        <v>0.9994584900000001</v>
+        <v>0.9995525399999999</v>
       </c>
       <c r="G133">
-        <v>0.2090599057587512</v>
+        <v>0.2580826940041561</v>
       </c>
       <c r="H133">
-        <v>0.9984184600000001</v>
+        <v>0.99847732</v>
       </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="1">
-        <v>46153</v>
+        <v>46171</v>
       </c>
       <c r="B134" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C134">
-        <v>28.12253390077671</v>
+        <v>35.84309020154227</v>
       </c>
       <c r="D134">
-        <v>23.58699683751922</v>
+        <v>19.06511612333149</v>
       </c>
       <c r="E134">
-        <v>0.9997295369999999</v>
+        <v>0.9995533299999999</v>
       </c>
       <c r="F134">
-        <v>0.9997295369999999</v>
+        <v>0.9995533299999999</v>
       </c>
       <c r="G134">
-        <v>0.03368732240295347</v>
+        <v>0.2619374017254759</v>
       </c>
       <c r="H134">
-        <v>0.9997295369999999</v>
+        <v>0.99849382</v>
       </c>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="1">
-        <v>46154</v>
+        <v>46174</v>
       </c>
       <c r="B135" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C135">
-        <v>28.17715727830483</v>
+        <v>36.27022125574057</v>
       </c>
       <c r="D135">
-        <v>23.63894513078866</v>
+        <v>19.32711369104533</v>
       </c>
       <c r="E135">
-        <v>1.000319473</v>
+        <v>0.9995550400000001</v>
       </c>
       <c r="F135">
-        <v>1.000319473</v>
+        <v>0.9995550400000001</v>
       </c>
       <c r="G135">
-        <v>0.03515547182056333</v>
+        <v>0.2764348160433892</v>
       </c>
       <c r="H135">
-        <v>1.000319473</v>
+        <v>0.9985177199999999</v>
       </c>
     </row>
     <row r="136" spans="1:8">
       <c r="A136" s="1">
-        <v>46155</v>
+        <v>46175</v>
       </c>
       <c r="B136" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C136">
-        <v>28.59002627414054</v>
+        <v>36.57133692946976</v>
       </c>
       <c r="D136">
-        <v>23.96230704059692</v>
+        <v>19.33857330565742</v>
       </c>
       <c r="E136">
-        <v>0.9999999989999999</v>
+        <v>0.9994989200000002</v>
       </c>
       <c r="F136">
-        <v>0.9999999989999999</v>
+        <v>0.9994989200000002</v>
       </c>
       <c r="G136">
-        <v>0.05179637495949674</v>
+        <v>0.2931947261624381</v>
       </c>
       <c r="H136">
-        <v>0.9999999989999999</v>
+        <v>0.9984577800000001</v>
       </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="1">
-        <v>46156</v>
+        <v>46176</v>
       </c>
       <c r="B137" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C137">
-        <v>28.56217859389523</v>
+        <v>36.8289666508657</v>
       </c>
       <c r="D137">
-        <v>23.9411987302529</v>
+        <v>19.43137154505686</v>
       </c>
       <c r="E137">
-        <v>1</v>
+        <v>0.9994838199999998</v>
       </c>
       <c r="F137">
-        <v>1</v>
+        <v>0.9994838199999998</v>
       </c>
       <c r="G137">
-        <v>0.04837024516756849</v>
+        <v>0.2996471994933361</v>
       </c>
       <c r="H137">
-        <v>1</v>
+        <v>0.9984549499999998</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="1">
-        <v>46157</v>
+        <v>46177</v>
       </c>
       <c r="B138" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C138">
-        <v>28.57618675936338</v>
+        <v>36.76760036565858</v>
       </c>
       <c r="D138">
-        <v>23.9576220541054</v>
+        <v>18.98774474764188</v>
       </c>
       <c r="E138">
-        <v>0.999503249</v>
+        <v>0.99948384</v>
       </c>
       <c r="F138">
-        <v>0.999503249</v>
+        <v>0.99948384</v>
       </c>
       <c r="G138">
-        <v>0.04983868243960732</v>
+        <v>0.2807085470912787</v>
       </c>
       <c r="H138">
-        <v>0.999503249</v>
+        <v>0.9984696899999999</v>
       </c>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="1">
-        <v>46160</v>
+        <v>46178</v>
       </c>
       <c r="B139" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C139">
-        <v>28.68951918518517</v>
+        <v>34.71533981972338</v>
       </c>
       <c r="D139">
-        <v>24.06134728453882</v>
+        <v>17.87291658642534</v>
       </c>
       <c r="E139">
-        <v>0.999503249</v>
+        <v>0.9994584900000001</v>
       </c>
       <c r="F139">
-        <v>0.999503249</v>
+        <v>0.9994584900000001</v>
       </c>
       <c r="G139">
-        <v>0.04983868243960732</v>
+        <v>0.2090599057587512</v>
       </c>
       <c r="H139">
-        <v>0.999503249</v>
+        <v>0.9984184600000001</v>
       </c>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="1">
-        <v>46161</v>
+        <v>46182</v>
       </c>
       <c r="B140" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C140">
-        <v>28.31167386654059</v>
+        <v>34.47584515007753</v>
       </c>
       <c r="D140">
-        <v>23.75157719455474</v>
+        <v>17.86980250897732</v>
       </c>
       <c r="E140">
-        <v>1.000177331</v>
+        <v>0.9994212399999999</v>
       </c>
       <c r="F140">
-        <v>1.000177331</v>
+        <v>0.9994212399999999</v>
       </c>
       <c r="G140">
-        <v>0.04053938625111919</v>
+        <v>0.2106528848867353</v>
       </c>
       <c r="H140">
-        <v>1.000177331</v>
+        <v>0.99833116</v>
       </c>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="1">
-        <v>46162</v>
+        <v>46153</v>
       </c>
       <c r="B141" t="s">
         <v>15</v>
       </c>
       <c r="C141">
-        <v>28.57911382310097</v>
+        <v>28.12253390077671</v>
       </c>
       <c r="D141">
-        <v>23.89431741541233</v>
+        <v>23.58699683751922</v>
       </c>
       <c r="E141">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="F141">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="G141">
-        <v>0.04690190590044785</v>
+        <v>0.03368732240295347</v>
       </c>
       <c r="H141">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="1">
-        <v>46163</v>
+        <v>46154</v>
       </c>
       <c r="B142" t="s">
         <v>15</v>
       </c>
       <c r="C142">
-        <v>28.55785065378643</v>
+        <v>28.17715727830483</v>
       </c>
       <c r="D142">
-        <v>24.04274714970193</v>
+        <v>23.63894513078866</v>
       </c>
       <c r="E142">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="F142">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="G142">
-        <v>0.05228572319419666</v>
+        <v>0.03515547182056333</v>
       </c>
       <c r="H142">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="1">
-        <v>46164</v>
+        <v>46155</v>
       </c>
       <c r="B143" t="s">
         <v>15</v>
       </c>
       <c r="C143">
-        <v>28.50194638163107</v>
+        <v>28.59002627414054</v>
       </c>
       <c r="D143">
-        <v>23.99272397156045</v>
+        <v>23.96230704059692</v>
       </c>
       <c r="E143">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F143">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G143">
-        <v>0.04934923597154284</v>
+        <v>0.05179637495949674</v>
       </c>
       <c r="H143">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="1">
-        <v>46167</v>
+        <v>46156</v>
       </c>
       <c r="B144" t="s">
         <v>15</v>
       </c>
       <c r="C144">
-        <v>28.55106858744498</v>
+        <v>28.56217859389523</v>
       </c>
       <c r="D144">
-        <v>23.9768329565351</v>
+        <v>23.9411987302529</v>
       </c>
       <c r="E144">
         <v>1</v>
@@ -4141,7 +4141,7 @@
         <v>1</v>
       </c>
       <c r="G144">
-        <v>0.05571185335164408</v>
+        <v>0.04837024516756849</v>
       </c>
       <c r="H144">
         <v>1</v>
@@ -4149,756 +4149,990 @@
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="1">
-        <v>46168</v>
+        <v>46157</v>
       </c>
       <c r="B145" t="s">
         <v>15</v>
       </c>
       <c r="C145">
-        <v>28.54681541456266</v>
+        <v>28.57618675936338</v>
       </c>
       <c r="D145">
-        <v>23.97386168967948</v>
+        <v>23.9576220541054</v>
       </c>
       <c r="E145">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="F145">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="G145">
-        <v>0.04837034303541388</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H145">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="1">
-        <v>46169</v>
+        <v>46160</v>
       </c>
       <c r="B146" t="s">
         <v>15</v>
       </c>
       <c r="C146">
-        <v>28.83672936868491</v>
+        <v>28.68951918518517</v>
       </c>
       <c r="D146">
-        <v>24.203511281145</v>
+        <v>24.06134728453882</v>
       </c>
       <c r="E146">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="F146">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="G146">
-        <v>0.05962723282507953</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H146">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="1">
-        <v>46170</v>
+        <v>46161</v>
       </c>
       <c r="B147" t="s">
         <v>15</v>
       </c>
       <c r="C147">
-        <v>28.88109630394224</v>
+        <v>28.31167386654059</v>
       </c>
       <c r="D147">
-        <v>24.34085451035401</v>
+        <v>23.75157719455474</v>
       </c>
       <c r="E147">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
       <c r="F147">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
       <c r="G147">
-        <v>0.06647938938594877</v>
+        <v>0.04053938625111919</v>
       </c>
       <c r="H147">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="1">
-        <v>46171</v>
+        <v>46162</v>
       </c>
       <c r="B148" t="s">
         <v>15</v>
       </c>
       <c r="C148">
-        <v>28.92588622185229</v>
+        <v>28.57911382310097</v>
       </c>
       <c r="D148">
-        <v>24.37463012178961</v>
+        <v>23.89431741541233</v>
       </c>
       <c r="E148">
-        <v>0.9999999989999999</v>
+        <v>0.999503734</v>
       </c>
       <c r="F148">
-        <v>0.9999999989999999</v>
+        <v>0.999503734</v>
       </c>
       <c r="G148">
-        <v>0.0669687424559624</v>
+        <v>0.04690190590044785</v>
       </c>
       <c r="H148">
-        <v>0.9999999989999999</v>
+        <v>0.999503734</v>
       </c>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="1">
-        <v>46174</v>
+        <v>46163</v>
       </c>
       <c r="B149" t="s">
         <v>15</v>
       </c>
       <c r="C149">
-        <v>28.479823472488</v>
+        <v>28.55785065378643</v>
       </c>
       <c r="D149">
-        <v>23.940843604634</v>
+        <v>24.04274714970193</v>
       </c>
       <c r="E149">
-        <v>0.9999999999999999</v>
+        <v>1.000229282</v>
       </c>
       <c r="F149">
-        <v>0.9999999999999999</v>
+        <v>1.000229282</v>
       </c>
       <c r="G149">
-        <v>0.05385076946675693</v>
+        <v>0.05228572319419666</v>
       </c>
       <c r="H149">
-        <v>0.9999999999999999</v>
+        <v>1.000229282</v>
       </c>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" s="1">
-        <v>46175</v>
+        <v>46164</v>
       </c>
       <c r="B150" t="s">
         <v>15</v>
       </c>
       <c r="C150">
-        <v>28.11501250979268</v>
+        <v>28.50194638163107</v>
       </c>
       <c r="D150">
-        <v>23.53470929078268</v>
+        <v>23.99272397156045</v>
       </c>
       <c r="E150">
-        <v>0.9999999989999999</v>
+        <v>1</v>
       </c>
       <c r="F150">
-        <v>0.9999999989999999</v>
+        <v>1</v>
       </c>
       <c r="G150">
-        <v>0.03476107722835287</v>
+        <v>0.04934923597154284</v>
       </c>
       <c r="H150">
-        <v>0.9999999989999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="1">
-        <v>46176</v>
+        <v>46167</v>
       </c>
       <c r="B151" t="s">
         <v>15</v>
       </c>
       <c r="C151">
-        <v>28.0115884668485</v>
+        <v>28.55106858744498</v>
       </c>
       <c r="D151">
-        <v>23.38620815625822</v>
+        <v>23.9768329565351</v>
       </c>
       <c r="E151">
-        <v>0.9993115890000001</v>
+        <v>1</v>
       </c>
       <c r="F151">
-        <v>0.9993115890000001</v>
+        <v>1</v>
       </c>
       <c r="G151">
-        <v>0.02105569185214828</v>
+        <v>0.05571185335164408</v>
       </c>
       <c r="H151">
-        <v>0.9993115890000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="1">
-        <v>46177</v>
+        <v>46168</v>
       </c>
       <c r="B152" t="s">
         <v>15</v>
       </c>
       <c r="C152">
-        <v>28.38208530418455</v>
+        <v>28.54681541456266</v>
       </c>
       <c r="D152">
-        <v>23.57230416238753</v>
+        <v>23.97386168967948</v>
       </c>
       <c r="E152">
-        <v>1.000774061</v>
+        <v>1</v>
       </c>
       <c r="F152">
-        <v>1.000774061</v>
+        <v>1</v>
       </c>
       <c r="G152">
-        <v>0.03133473088430172</v>
+        <v>0.04837034303541388</v>
       </c>
       <c r="H152">
-        <v>1.000774061</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" s="1">
-        <v>46178</v>
+        <v>46169</v>
       </c>
       <c r="B153" t="s">
         <v>15</v>
       </c>
       <c r="C153">
-        <v>27.67379569436247</v>
+        <v>28.83672936868491</v>
       </c>
       <c r="D153">
-        <v>23.02577481291606</v>
+        <v>24.203511281145</v>
       </c>
       <c r="E153">
-        <v>1.000106056</v>
+        <v>1</v>
       </c>
       <c r="F153">
-        <v>1.000106056</v>
+        <v>1</v>
       </c>
       <c r="G153">
-        <v>0.01248973263108488</v>
+        <v>0.05962723282507953</v>
       </c>
       <c r="H153">
-        <v>1.000106056</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" s="1">
-        <v>46153</v>
+        <v>46170</v>
       </c>
       <c r="B154" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C154">
-        <v>40.68830633303975</v>
+        <v>28.88109630394224</v>
       </c>
       <c r="D154">
-        <v>21.50431773660198</v>
+        <v>24.34085451035401</v>
       </c>
       <c r="E154">
-        <v>0.99909852</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F154">
-        <v>0.99909852</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G154">
-        <v>0.2342423866086769</v>
+        <v>0.06647938938594877</v>
       </c>
       <c r="H154">
-        <v>0.9974930900000001</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" s="1">
-        <v>46154</v>
+        <v>46171</v>
       </c>
       <c r="B155" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C155">
-        <v>40.32854894972581</v>
+        <v>28.92588622185229</v>
       </c>
       <c r="D155">
-        <v>21.09133998298594</v>
+        <v>24.37463012178961</v>
       </c>
       <c r="E155">
-        <v>0.9990972199999999</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F155">
-        <v>0.9990972199999999</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G155">
-        <v>0.2156468205051487</v>
+        <v>0.0669687424559624</v>
       </c>
       <c r="H155">
-        <v>0.99752223</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" s="1">
-        <v>46155</v>
+        <v>46174</v>
       </c>
       <c r="B156" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C156">
-        <v>40.47987921095815</v>
+        <v>28.479823472488</v>
       </c>
       <c r="D156">
-        <v>21.35995364434454</v>
+        <v>23.940843604634</v>
       </c>
       <c r="E156">
-        <v>0.9991780100000001</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F156">
-        <v>0.9991780100000001</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G156">
-        <v>0.2270956128473374</v>
+        <v>0.05385076946675693</v>
       </c>
       <c r="H156">
-        <v>0.9975825700000001</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" s="1">
-        <v>46156</v>
+        <v>46175</v>
       </c>
       <c r="B157" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C157">
-        <v>41.20436574895244</v>
+        <v>28.11501250979268</v>
       </c>
       <c r="D157">
-        <v>21.48149674387778</v>
+        <v>23.53470929078268</v>
       </c>
       <c r="E157">
-        <v>0.9991793299999999</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F157">
-        <v>0.9991793299999999</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G157">
-        <v>0.2454829228401052</v>
+        <v>0.03476107722835287</v>
       </c>
       <c r="H157">
-        <v>0.99754722</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="1">
-        <v>46157</v>
+        <v>46176</v>
       </c>
       <c r="B158" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C158">
-        <v>40.80613062958688</v>
+        <v>28.0115884668485</v>
       </c>
       <c r="D158">
-        <v>21.08912555803936</v>
+        <v>23.38620815625822</v>
       </c>
       <c r="E158">
-        <v>0.9991790600000001</v>
+        <v>0.9993115890000001</v>
       </c>
       <c r="F158">
-        <v>0.9991790600000001</v>
+        <v>0.9993115890000001</v>
       </c>
       <c r="G158">
-        <v>0.2230017445022556</v>
+        <v>0.02105569185214828</v>
       </c>
       <c r="H158">
-        <v>0.9975824700000002</v>
+        <v>0.9993115890000001</v>
       </c>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" s="1">
-        <v>46160</v>
+        <v>46177</v>
       </c>
       <c r="B159" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C159">
-        <v>40.11672876026724</v>
+        <v>28.38208530418455</v>
       </c>
       <c r="D159">
-        <v>20.79541439916316</v>
+        <v>23.57230416238753</v>
       </c>
       <c r="E159">
-        <v>0.999152</v>
+        <v>1.000774061</v>
       </c>
       <c r="F159">
-        <v>0.999152</v>
+        <v>1.000774061</v>
       </c>
       <c r="G159">
-        <v>0.2098184021536666</v>
+        <v>0.03133473088430172</v>
       </c>
       <c r="H159">
-        <v>0.9975007899999999</v>
+        <v>1.000774061</v>
       </c>
     </row>
     <row r="160" spans="1:8">
       <c r="A160" s="1">
-        <v>46161</v>
+        <v>46178</v>
       </c>
       <c r="B160" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C160">
-        <v>39.69086941528401</v>
+        <v>27.67379569436247</v>
       </c>
       <c r="D160">
-        <v>20.74924328599426</v>
+        <v>23.02577481291606</v>
       </c>
       <c r="E160">
-        <v>0.99914989</v>
+        <v>1.000106056</v>
       </c>
       <c r="F160">
-        <v>0.99914989</v>
+        <v>1.000106056</v>
       </c>
       <c r="G160">
-        <v>0.2020471776850241</v>
+        <v>0.01248973263108488</v>
       </c>
       <c r="H160">
-        <v>0.9974417</v>
+        <v>1.000106056</v>
       </c>
     </row>
     <row r="161" spans="1:8">
       <c r="A161" s="1">
-        <v>46162</v>
+        <v>46182</v>
       </c>
       <c r="B161" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C161">
-        <v>40.37836787855562</v>
+        <v>27.20669560544778</v>
       </c>
       <c r="D161">
-        <v>21.11271132314188</v>
+        <v>22.56956256091779</v>
       </c>
       <c r="E161">
-        <v>0.99915058</v>
+        <v>0.9999738310000001</v>
       </c>
       <c r="F161">
-        <v>0.99915058</v>
+        <v>0.9999738310000001</v>
       </c>
       <c r="G161">
-        <v>0.2291077670847563</v>
+        <v>-0.01222906775659949</v>
       </c>
       <c r="H161">
-        <v>0.9974415600000001</v>
+        <v>0.9999738310000001</v>
       </c>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" s="1">
-        <v>46163</v>
+        <v>46153</v>
       </c>
       <c r="B162" t="s">
         <v>16</v>
       </c>
       <c r="C162">
-        <v>38.9123066967842</v>
+        <v>40.68830633303975</v>
       </c>
       <c r="D162">
-        <v>21.28910644207464</v>
+        <v>21.50431773660198</v>
       </c>
       <c r="E162">
-        <v>0.9989350699999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="F162">
-        <v>0.9989350699999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="G162">
-        <v>0.2392382040170877</v>
+        <v>0.2342423866086769</v>
       </c>
       <c r="H162">
-        <v>0.99726191</v>
+        <v>0.9974930900000001</v>
       </c>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" s="1">
-        <v>46164</v>
+        <v>46154</v>
       </c>
       <c r="B163" t="s">
         <v>16</v>
       </c>
       <c r="C163">
-        <v>39.43913909150694</v>
+        <v>40.32854894972581</v>
       </c>
       <c r="D163">
-        <v>21.05297617141148</v>
+        <v>21.09133998298594</v>
       </c>
       <c r="E163">
-        <v>0.999144</v>
+        <v>0.9990972199999999</v>
       </c>
       <c r="F163">
-        <v>0.999144</v>
+        <v>0.9990972199999999</v>
       </c>
       <c r="G163">
-        <v>0.2516582935428642</v>
+        <v>0.2156468205051487</v>
       </c>
       <c r="H163">
-        <v>0.9974678400000001</v>
+        <v>0.99752223</v>
       </c>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" s="1">
-        <v>46167</v>
+        <v>46155</v>
       </c>
       <c r="B164" t="s">
         <v>16</v>
       </c>
       <c r="C164">
-        <v>39.45782844313628</v>
+        <v>40.47987921095815</v>
       </c>
       <c r="D164">
-        <v>21.0518901572272</v>
+        <v>21.35995364434454</v>
       </c>
       <c r="E164">
-        <v>0.999144</v>
+        <v>0.9991780100000001</v>
       </c>
       <c r="F164">
-        <v>0.999144</v>
+        <v>0.9991780100000001</v>
       </c>
       <c r="G164">
-        <v>0.2516582935428642</v>
+        <v>0.2270956128473374</v>
       </c>
       <c r="H164">
-        <v>0.9974678400000001</v>
+        <v>0.9975825700000001</v>
       </c>
     </row>
     <row r="165" spans="1:8">
       <c r="A165" s="1">
-        <v>46168</v>
+        <v>46156</v>
       </c>
       <c r="B165" t="s">
         <v>16</v>
       </c>
       <c r="C165">
-        <v>40.20219297984542</v>
+        <v>41.20436574895244</v>
       </c>
       <c r="D165">
-        <v>21.93106024403281</v>
+        <v>21.48149674387778</v>
       </c>
       <c r="E165">
-        <v>0.9991421799999999</v>
+        <v>0.9991793299999999</v>
       </c>
       <c r="F165">
-        <v>0.9991421799999999</v>
+        <v>0.9991793299999999</v>
       </c>
       <c r="G165">
-        <v>0.2846167552893293</v>
+        <v>0.2454829228401052</v>
       </c>
       <c r="H165">
-        <v>0.9974609800000001</v>
+        <v>0.99754722</v>
       </c>
     </row>
     <row r="166" spans="1:8">
       <c r="A166" s="1">
-        <v>46169</v>
+        <v>46157</v>
       </c>
       <c r="B166" t="s">
         <v>16</v>
       </c>
       <c r="C166">
-        <v>40.34993865302093</v>
+        <v>40.80613062958688</v>
       </c>
       <c r="D166">
-        <v>21.65366031776487</v>
+        <v>21.08912555803936</v>
       </c>
       <c r="E166">
-        <v>0.9991434600000001</v>
+        <v>0.9991790600000001</v>
       </c>
       <c r="F166">
-        <v>0.9991434600000001</v>
+        <v>0.9991790600000001</v>
       </c>
       <c r="G166">
-        <v>0.2796902860011767</v>
+        <v>0.2230017445022556</v>
       </c>
       <c r="H166">
-        <v>0.9991434600000001</v>
+        <v>0.9975824700000002</v>
       </c>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" s="1">
-        <v>46170</v>
+        <v>46160</v>
       </c>
       <c r="B167" t="s">
         <v>16</v>
       </c>
       <c r="C167">
-        <v>40.5850485390846</v>
+        <v>40.11672876026724</v>
       </c>
       <c r="D167">
-        <v>21.75450977746074</v>
+        <v>20.79541439916316</v>
       </c>
       <c r="E167">
-        <v>0.99914592</v>
+        <v>0.999152</v>
       </c>
       <c r="F167">
-        <v>0.99914592</v>
+        <v>0.999152</v>
       </c>
       <c r="G167">
-        <v>0.2964818481030536</v>
+        <v>0.2098184021536666</v>
       </c>
       <c r="H167">
-        <v>0.99914592</v>
+        <v>0.9975007899999999</v>
       </c>
     </row>
     <row r="168" spans="1:8">
       <c r="A168" s="1">
-        <v>46171</v>
+        <v>46161</v>
       </c>
       <c r="B168" t="s">
         <v>16</v>
       </c>
       <c r="C168">
-        <v>41.86785805184477</v>
+        <v>39.69086941528401</v>
       </c>
       <c r="D168">
-        <v>22.33589392797469</v>
+        <v>20.74924328599426</v>
       </c>
       <c r="E168">
-        <v>0.9991336999999999</v>
+        <v>0.99914989</v>
       </c>
       <c r="F168">
-        <v>0.9991336999999999</v>
+        <v>0.99914989</v>
       </c>
       <c r="G168">
-        <v>0.3254158954996882</v>
+        <v>0.2020471776850241</v>
       </c>
       <c r="H168">
-        <v>0.9991336999999999</v>
+        <v>0.9974417</v>
       </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" s="1">
-        <v>46174</v>
+        <v>46162</v>
       </c>
       <c r="B169" t="s">
         <v>16</v>
       </c>
       <c r="C169">
-        <v>42.82932322850974</v>
+        <v>40.37836787855562</v>
       </c>
       <c r="D169">
-        <v>22.98998911430362</v>
+        <v>21.11271132314188</v>
       </c>
       <c r="E169">
-        <v>0.99914238</v>
+        <v>0.99915058</v>
       </c>
       <c r="F169">
-        <v>0.99914238</v>
+        <v>0.99915058</v>
       </c>
       <c r="G169">
-        <v>0.3583049032509023</v>
+        <v>0.2291077670847563</v>
       </c>
       <c r="H169">
-        <v>0.99914238</v>
+        <v>0.9974415600000001</v>
       </c>
     </row>
     <row r="170" spans="1:8">
       <c r="A170" s="1">
-        <v>46175</v>
+        <v>46163</v>
       </c>
       <c r="B170" t="s">
         <v>16</v>
       </c>
       <c r="C170">
-        <v>43.11872937189534</v>
+        <v>38.9123066967842</v>
       </c>
       <c r="D170">
-        <v>22.90628380907704</v>
+        <v>21.28910644207464</v>
       </c>
       <c r="E170">
-        <v>0.9990972800000002</v>
+        <v>0.9989350699999999</v>
       </c>
       <c r="F170">
-        <v>0.9990972800000002</v>
+        <v>0.9989350699999999</v>
       </c>
       <c r="G170">
-        <v>0.3753046155885469</v>
+        <v>0.2392382040170877</v>
       </c>
       <c r="H170">
-        <v>0.9990972800000002</v>
+        <v>0.99726191</v>
       </c>
     </row>
     <row r="171" spans="1:8">
       <c r="A171" s="1">
-        <v>46176</v>
+        <v>46164</v>
       </c>
       <c r="B171" t="s">
         <v>16</v>
       </c>
       <c r="C171">
-        <v>42.86143001679577</v>
+        <v>39.43913909150694</v>
       </c>
       <c r="D171">
-        <v>22.72053012591219</v>
+        <v>21.05297617141148</v>
       </c>
       <c r="E171">
-        <v>0.9990984299999999</v>
+        <v>0.999144</v>
       </c>
       <c r="F171">
-        <v>0.9990984299999999</v>
+        <v>0.999144</v>
       </c>
       <c r="G171">
-        <v>0.3615660647779204</v>
+        <v>0.2516582935428642</v>
       </c>
       <c r="H171">
-        <v>0.9990984299999999</v>
+        <v>0.9974678400000001</v>
       </c>
     </row>
     <row r="172" spans="1:8">
       <c r="A172" s="1">
-        <v>46177</v>
+        <v>46167</v>
       </c>
       <c r="B172" t="s">
         <v>16</v>
       </c>
       <c r="C172">
-        <v>42.57902095847519</v>
+        <v>39.45782844313628</v>
       </c>
       <c r="D172">
-        <v>22.20304338566557</v>
+        <v>21.0518901572272</v>
       </c>
       <c r="E172">
-        <v>0.9990006900000001</v>
+        <v>0.999144</v>
       </c>
       <c r="F172">
-        <v>0.9990006900000001</v>
+        <v>0.999144</v>
       </c>
       <c r="G172">
-        <v>0.34033389372967</v>
+        <v>0.2516582935428642</v>
       </c>
       <c r="H172">
-        <v>0.9990006900000001</v>
+        <v>0.9974678400000001</v>
       </c>
     </row>
     <row r="173" spans="1:8">
       <c r="A173" s="1">
-        <v>46178</v>
+        <v>46168</v>
       </c>
       <c r="B173" t="s">
         <v>16</v>
       </c>
       <c r="C173">
+        <v>40.20219297984542</v>
+      </c>
+      <c r="D173">
+        <v>21.93106024403281</v>
+      </c>
+      <c r="E173">
+        <v>0.9991421799999999</v>
+      </c>
+      <c r="F173">
+        <v>0.9991421799999999</v>
+      </c>
+      <c r="G173">
+        <v>0.2846167552893293</v>
+      </c>
+      <c r="H173">
+        <v>0.9974609800000001</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8">
+      <c r="A174" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174">
+        <v>40.34993865302093</v>
+      </c>
+      <c r="D174">
+        <v>21.65366031776487</v>
+      </c>
+      <c r="E174">
+        <v>0.9991434600000001</v>
+      </c>
+      <c r="F174">
+        <v>0.9991434600000001</v>
+      </c>
+      <c r="G174">
+        <v>0.2796902860011767</v>
+      </c>
+      <c r="H174">
+        <v>0.9991434600000001</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8">
+      <c r="A175" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175">
+        <v>40.5850485390846</v>
+      </c>
+      <c r="D175">
+        <v>21.75450977746074</v>
+      </c>
+      <c r="E175">
+        <v>0.99914592</v>
+      </c>
+      <c r="F175">
+        <v>0.99914592</v>
+      </c>
+      <c r="G175">
+        <v>0.2964818481030536</v>
+      </c>
+      <c r="H175">
+        <v>0.99914592</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8">
+      <c r="A176" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176">
+        <v>41.86785805184477</v>
+      </c>
+      <c r="D176">
+        <v>22.33589392797469</v>
+      </c>
+      <c r="E176">
+        <v>0.9991336999999999</v>
+      </c>
+      <c r="F176">
+        <v>0.9991336999999999</v>
+      </c>
+      <c r="G176">
+        <v>0.3254158954996882</v>
+      </c>
+      <c r="H176">
+        <v>0.9991336999999999</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8">
+      <c r="A177" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177">
+        <v>42.82932322850974</v>
+      </c>
+      <c r="D177">
+        <v>22.98998911430362</v>
+      </c>
+      <c r="E177">
+        <v>0.99914238</v>
+      </c>
+      <c r="F177">
+        <v>0.99914238</v>
+      </c>
+      <c r="G177">
+        <v>0.3583049032509023</v>
+      </c>
+      <c r="H177">
+        <v>0.99914238</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8">
+      <c r="A178" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178">
+        <v>43.11872937189534</v>
+      </c>
+      <c r="D178">
+        <v>22.90628380907704</v>
+      </c>
+      <c r="E178">
+        <v>0.9990972800000002</v>
+      </c>
+      <c r="F178">
+        <v>0.9990972800000002</v>
+      </c>
+      <c r="G178">
+        <v>0.3753046155885469</v>
+      </c>
+      <c r="H178">
+        <v>0.9990972800000002</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8">
+      <c r="A179" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179">
+        <v>42.86143001679577</v>
+      </c>
+      <c r="D179">
+        <v>22.72053012591219</v>
+      </c>
+      <c r="E179">
+        <v>0.9990984299999999</v>
+      </c>
+      <c r="F179">
+        <v>0.9990984299999999</v>
+      </c>
+      <c r="G179">
+        <v>0.3615660647779204</v>
+      </c>
+      <c r="H179">
+        <v>0.9990984299999999</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8">
+      <c r="A180" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180">
+        <v>42.57902095847519</v>
+      </c>
+      <c r="D180">
+        <v>22.20304338566557</v>
+      </c>
+      <c r="E180">
+        <v>0.9990006900000001</v>
+      </c>
+      <c r="F180">
+        <v>0.9990006900000001</v>
+      </c>
+      <c r="G180">
+        <v>0.34033389372967</v>
+      </c>
+      <c r="H180">
+        <v>0.9990006900000001</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8">
+      <c r="A181" s="1">
+        <v>46178</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181">
         <v>39.64354477595148</v>
       </c>
-      <c r="D173">
+      <c r="D181">
         <v>20.69555521363093</v>
       </c>
-      <c r="E173">
+      <c r="E181">
         <v>0.9992026399999999</v>
       </c>
-      <c r="F173">
+      <c r="F181">
         <v>0.9992026399999999</v>
       </c>
-      <c r="G173">
+      <c r="G181">
         <v>0.251033842835561</v>
       </c>
-      <c r="H173">
+      <c r="H181">
         <v>0.9992026399999999</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8">
+      <c r="A182" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182">
+        <v>38.75915162143414</v>
+      </c>
+      <c r="D182">
+        <v>20.35001897047279</v>
+      </c>
+      <c r="E182">
+        <v>0.9992145899999999</v>
+      </c>
+      <c r="F182">
+        <v>0.9992145899999999</v>
+      </c>
+      <c r="G182">
+        <v>0.2282057121464345</v>
+      </c>
+      <c r="H182">
+        <v>0.9992145899999999</v>
       </c>
     </row>
   </sheetData>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -775,22 +775,22 @@
         <v>8</v>
       </c>
       <c r="C15">
-        <v>25.09128029557501</v>
+        <v>27.27566394701579</v>
       </c>
       <c r="D15">
-        <v>16.46002919022756</v>
+        <v>17.54510978141869</v>
       </c>
       <c r="E15">
-        <v>0.8745999999999999</v>
+        <v>0.8795999999999999</v>
       </c>
       <c r="F15">
-        <v>0.8693</v>
+        <v>0.8795999999999999</v>
       </c>
       <c r="G15">
-        <v>0.477398597525494</v>
+        <v>0.5078655154648422</v>
       </c>
       <c r="H15">
-        <v>0.9271999999999999</v>
+        <v>0.9318</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1321,10 +1321,10 @@
         <v>9</v>
       </c>
       <c r="C36">
-        <v>48.52114115454133</v>
+        <v>50.12461745484359</v>
       </c>
       <c r="D36">
-        <v>24.5918103168291</v>
+        <v>25.31796473106079</v>
       </c>
       <c r="E36">
         <v>0.916</v>
@@ -1333,7 +1333,7 @@
         <v>0.916</v>
       </c>
       <c r="G36">
-        <v>0.4418242442507014</v>
+        <v>0.4801457138994158</v>
       </c>
       <c r="H36">
         <v>0.916</v>
@@ -1867,22 +1867,22 @@
         <v>10</v>
       </c>
       <c r="C57">
-        <v>31.82278781619365</v>
+        <v>32.06505731417286</v>
       </c>
       <c r="D57">
-        <v>23.98410280709619</v>
+        <v>24.06041109516704</v>
       </c>
       <c r="E57">
-        <v>0.9992000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="F57">
-        <v>0.9992000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="G57">
-        <v>-0.001224205553522206</v>
+        <v>0.004743767333231785</v>
       </c>
       <c r="H57">
-        <v>0.9992000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -2413,10 +2413,10 @@
         <v>11</v>
       </c>
       <c r="C78">
-        <v>35.07954985374597</v>
+        <v>35.58815840295288</v>
       </c>
       <c r="D78">
-        <v>21.50135646273161</v>
+        <v>21.80812849732373</v>
       </c>
       <c r="E78">
         <v>0.9962853900000002</v>
@@ -2425,7 +2425,7 @@
         <v>0.9962853900000002</v>
       </c>
       <c r="G78">
-        <v>0.1358738837011901</v>
+        <v>0.1559278910539408</v>
       </c>
       <c r="H78">
         <v>0.9992534400000002</v>
@@ -2959,10 +2959,10 @@
         <v>12</v>
       </c>
       <c r="C99">
-        <v>48.59345545448965</v>
+        <v>50.39371086612305</v>
       </c>
       <c r="D99">
-        <v>22.38620275513295</v>
+        <v>23.09650971949351</v>
       </c>
       <c r="E99">
         <v>0.9997</v>
@@ -2971,7 +2971,7 @@
         <v>0.9997</v>
       </c>
       <c r="G99">
-        <v>0.53573532487038</v>
+        <v>0.5832039354188183</v>
       </c>
       <c r="H99">
         <v>0.9997</v>
@@ -3479,10 +3479,10 @@
         <v>13</v>
       </c>
       <c r="C119">
-        <v>55.60031148827208</v>
+        <v>57.84835101034041</v>
       </c>
       <c r="D119">
-        <v>22.45772203407765</v>
+        <v>23.24662656171655</v>
       </c>
       <c r="E119">
         <v>0.999</v>
@@ -3491,7 +3491,7 @@
         <v>0.999</v>
       </c>
       <c r="G119">
-        <v>0.7325533345047268</v>
+        <v>0.7931280733869936</v>
       </c>
       <c r="H119">
         <v>0.999</v>
@@ -4025,10 +4025,10 @@
         <v>14</v>
       </c>
       <c r="C140">
-        <v>34.47584515007753</v>
+        <v>35.03764279648938</v>
       </c>
       <c r="D140">
-        <v>17.86980250897732</v>
+        <v>18.26945792236365</v>
       </c>
       <c r="E140">
         <v>0.9994212399999999</v>
@@ -4037,7 +4037,7 @@
         <v>0.9994212399999999</v>
       </c>
       <c r="G140">
-        <v>0.2106528848867353</v>
+        <v>0.2361271247979846</v>
       </c>
       <c r="H140">
         <v>0.99833116</v>
@@ -4571,10 +4571,10 @@
         <v>15</v>
       </c>
       <c r="C161">
-        <v>27.20669560544778</v>
+        <v>27.45237632057606</v>
       </c>
       <c r="D161">
-        <v>22.56956256091779</v>
+        <v>22.58943922039682</v>
       </c>
       <c r="E161">
         <v>0.9999738310000001</v>
@@ -4583,7 +4583,7 @@
         <v>0.9999738310000001</v>
       </c>
       <c r="G161">
-        <v>-0.01222906775659949</v>
+        <v>-0.01076068709534461</v>
       </c>
       <c r="H161">
         <v>0.9999738310000001</v>
@@ -5117,10 +5117,10 @@
         <v>16</v>
       </c>
       <c r="C182">
-        <v>38.75915162143414</v>
+        <v>39.7656886466531</v>
       </c>
       <c r="D182">
-        <v>20.35001897047279</v>
+        <v>20.79148740795913</v>
       </c>
       <c r="E182">
         <v>0.9992145899999999</v>
@@ -5129,7 +5129,7 @@
         <v>0.9992145899999999</v>
       </c>
       <c r="G182">
-        <v>0.2282057121464345</v>
+        <v>0.2542950043625791</v>
       </c>
       <c r="H182">
         <v>0.9992145899999999</v>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="17">
   <si>
     <t>Date</t>
   </si>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -795,42 +795,42 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1">
-        <v>46153</v>
+        <v>46183</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16">
-        <v>53.14833755912058</v>
+        <v>25.34080161625639</v>
       </c>
       <c r="D16">
-        <v>25.84885448407537</v>
+        <v>16.48213593414579</v>
       </c>
       <c r="E16">
-        <v>0.9262</v>
+        <v>0.8813999999999999</v>
       </c>
       <c r="F16">
-        <v>0.9262</v>
+        <v>0.8813999999999999</v>
       </c>
       <c r="G16">
-        <v>0.3839084462043663</v>
+        <v>0.4509025274406799</v>
       </c>
       <c r="H16">
-        <v>0.9262</v>
+        <v>0.9329999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
       </c>
       <c r="C17">
-        <v>51.82921169635205</v>
+        <v>53.14833755912058</v>
       </c>
       <c r="D17">
-        <v>25.32805827181975</v>
+        <v>25.84885448407537</v>
       </c>
       <c r="E17">
         <v>0.9262</v>
@@ -839,7 +839,7 @@
         <v>0.9262</v>
       </c>
       <c r="G17">
-        <v>0.3568580281685669</v>
+        <v>0.3839084462043663</v>
       </c>
       <c r="H17">
         <v>0.9262</v>
@@ -847,120 +847,120 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B18" t="s">
         <v>9</v>
       </c>
       <c r="C18">
-        <v>52.28471716753184</v>
+        <v>51.82921169635205</v>
       </c>
       <c r="D18">
-        <v>25.54525144150689</v>
+        <v>25.32805827181975</v>
       </c>
       <c r="E18">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="F18">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="G18">
-        <v>0.378012896547947</v>
+        <v>0.3568580281685669</v>
       </c>
       <c r="H18">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B19" t="s">
         <v>9</v>
       </c>
       <c r="C19">
-        <v>53.87287273813902</v>
+        <v>52.28471716753184</v>
       </c>
       <c r="D19">
-        <v>26.32154226438612</v>
+        <v>25.54525144150689</v>
       </c>
       <c r="E19">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="F19">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="G19">
-        <v>0.4166811087612758</v>
+        <v>0.378012896547947</v>
       </c>
       <c r="H19">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="B20" t="s">
         <v>9</v>
       </c>
       <c r="C20">
-        <v>52.18747148214074</v>
+        <v>53.87287273813902</v>
       </c>
       <c r="D20">
-        <v>25.13616059644496</v>
+        <v>26.32154226438612</v>
       </c>
       <c r="E20">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="F20">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="G20">
-        <v>0.3627535778249862</v>
+        <v>0.4166811087612758</v>
       </c>
       <c r="H20">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="B21" t="s">
         <v>9</v>
       </c>
       <c r="C21">
-        <v>50.72035274995172</v>
+        <v>52.18747148214074</v>
       </c>
       <c r="D21">
-        <v>24.61756040386634</v>
+        <v>25.13616059644496</v>
       </c>
       <c r="E21">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="F21">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="G21">
         <v>0.3627535778249862</v>
       </c>
       <c r="H21">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="B22" t="s">
         <v>9</v>
       </c>
       <c r="C22">
-        <v>50.11981086673613</v>
+        <v>50.72035274995172</v>
       </c>
       <c r="D22">
-        <v>24.13061679021705</v>
+        <v>24.61756040386634</v>
       </c>
       <c r="E22">
         <v>0.9259000000000001</v>
@@ -969,7 +969,7 @@
         <v>0.9259000000000001</v>
       </c>
       <c r="G22">
-        <v>0.3258193430227221</v>
+        <v>0.3627535778249862</v>
       </c>
       <c r="H22">
         <v>0.9259000000000001</v>
@@ -977,120 +977,120 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="B23" t="s">
         <v>9</v>
       </c>
       <c r="C23">
-        <v>51.74165648409151</v>
+        <v>50.11981086673613</v>
       </c>
       <c r="D23">
-        <v>24.98091384114761</v>
+        <v>24.13061679021705</v>
       </c>
       <c r="E23">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="F23">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="G23">
-        <v>0.3818277262286871</v>
+        <v>0.3258193430227221</v>
       </c>
       <c r="H23">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="B24" t="s">
         <v>9</v>
       </c>
       <c r="C24">
-        <v>49.13455894175823</v>
+        <v>51.74165648409151</v>
       </c>
       <c r="D24">
-        <v>25.30005057653127</v>
+        <v>24.98091384114761</v>
       </c>
       <c r="E24">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="F24">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="G24">
-        <v>0.4028091571787618</v>
+        <v>0.3818277262286871</v>
       </c>
       <c r="H24">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
       </c>
       <c r="C25">
-        <v>49.57776597479297</v>
+        <v>49.13455894175823</v>
       </c>
       <c r="D25">
-        <v>25.04906725563518</v>
+        <v>25.30005057653127</v>
       </c>
       <c r="E25">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="F25">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="G25">
-        <v>0.4256980029692063</v>
+        <v>0.4028091571787618</v>
       </c>
       <c r="H25">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
       </c>
       <c r="C26">
-        <v>49.71239596645896</v>
+        <v>49.57776597479297</v>
       </c>
       <c r="D26">
-        <v>25.18778610744295</v>
+        <v>25.04906725563518</v>
       </c>
       <c r="E26">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="F26">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="G26">
-        <v>0.4525749835757003</v>
+        <v>0.4256980029692063</v>
       </c>
       <c r="H26">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="B27" t="s">
         <v>9</v>
       </c>
       <c r="C27">
-        <v>50.77166277510776</v>
+        <v>49.71239596645896</v>
       </c>
       <c r="D27">
-        <v>25.7431782858765</v>
+        <v>25.18778610744295</v>
       </c>
       <c r="E27">
         <v>0.9231999999999999</v>
@@ -1099,7 +1099,7 @@
         <v>0.9231999999999999</v>
       </c>
       <c r="G27">
-        <v>0.4700884597036457</v>
+        <v>0.4525749835757003</v>
       </c>
       <c r="H27">
         <v>0.9231999999999999</v>
@@ -1107,120 +1107,120 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1">
-        <v>46169</v>
+        <v>46168</v>
       </c>
       <c r="B28" t="s">
         <v>9</v>
       </c>
       <c r="C28">
-        <v>50.57689164833899</v>
+        <v>50.77166277510776</v>
       </c>
       <c r="D28">
-        <v>25.70244067238947</v>
+        <v>25.7431782858765</v>
       </c>
       <c r="E28">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="F28">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="G28">
-        <v>0.4518814984464716</v>
+        <v>0.4700884597036457</v>
       </c>
       <c r="H28">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="B29" t="s">
         <v>9</v>
       </c>
       <c r="C29">
-        <v>50.80027854822009</v>
+        <v>50.57689164833899</v>
       </c>
       <c r="D29">
-        <v>25.90068415792015</v>
+        <v>25.70244067238947</v>
       </c>
       <c r="E29">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
       <c r="F29">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
       <c r="G29">
-        <v>0.4699150222743402</v>
+        <v>0.4518814984464716</v>
       </c>
       <c r="H29">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="B30" t="s">
         <v>9</v>
       </c>
       <c r="C30">
-        <v>51.44563447241545</v>
+        <v>50.80027854822009</v>
       </c>
       <c r="D30">
-        <v>26.0970978996374</v>
+        <v>25.90068415792015</v>
       </c>
       <c r="E30">
-        <v>0.9246</v>
+        <v>0.9231</v>
       </c>
       <c r="F30">
-        <v>0.9246</v>
+        <v>0.9231</v>
       </c>
       <c r="G30">
-        <v>0.4791053539115764</v>
+        <v>0.4699150222743402</v>
       </c>
       <c r="H30">
-        <v>0.9246</v>
+        <v>0.9231</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1">
-        <v>46174</v>
+        <v>46171</v>
       </c>
       <c r="B31" t="s">
         <v>9</v>
       </c>
       <c r="C31">
-        <v>53.05792083471825</v>
+        <v>51.44563447241545</v>
       </c>
       <c r="D31">
-        <v>26.86242981002239</v>
+        <v>26.0970978996374</v>
       </c>
       <c r="E31">
-        <v>0.9254999999999999</v>
+        <v>0.9246</v>
       </c>
       <c r="F31">
-        <v>0.9254999999999999</v>
+        <v>0.9246</v>
       </c>
       <c r="G31">
-        <v>0.5306051577195796</v>
+        <v>0.4791053539115764</v>
       </c>
       <c r="H31">
-        <v>0.9254999999999999</v>
+        <v>0.9246</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="B32" t="s">
         <v>9</v>
       </c>
       <c r="C32">
-        <v>54.38946369031042</v>
+        <v>53.05792083471825</v>
       </c>
       <c r="D32">
-        <v>27.57160808325711</v>
+        <v>26.86242981002239</v>
       </c>
       <c r="E32">
         <v>0.9254999999999999</v>
@@ -1229,7 +1229,7 @@
         <v>0.9254999999999999</v>
       </c>
       <c r="G32">
-        <v>0.5845326886558693</v>
+        <v>0.5306051577195796</v>
       </c>
       <c r="H32">
         <v>0.9254999999999999</v>
@@ -1237,250 +1237,250 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="B33" t="s">
         <v>9</v>
       </c>
       <c r="C33">
-        <v>54.35279063045283</v>
+        <v>54.38946369031042</v>
       </c>
       <c r="D33">
-        <v>27.50874919819178</v>
+        <v>27.57160808325711</v>
       </c>
       <c r="E33">
-        <v>0.9162000000000001</v>
+        <v>0.9254999999999999</v>
       </c>
       <c r="F33">
-        <v>0.9162000000000001</v>
+        <v>0.9254999999999999</v>
       </c>
       <c r="G33">
-        <v>0.5992718273849102</v>
+        <v>0.5845326886558693</v>
       </c>
       <c r="H33">
-        <v>0.9162000000000001</v>
+        <v>0.9254999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="B34" t="s">
         <v>9</v>
       </c>
       <c r="C34">
-        <v>53.45790968334249</v>
+        <v>54.35279063045283</v>
       </c>
       <c r="D34">
-        <v>26.99486187834476</v>
+        <v>27.50874919819178</v>
       </c>
       <c r="E34">
-        <v>0.9154000000000001</v>
+        <v>0.9162000000000001</v>
       </c>
       <c r="F34">
-        <v>0.9154000000000001</v>
+        <v>0.9162000000000001</v>
       </c>
       <c r="G34">
-        <v>0.5691000647975994</v>
+        <v>0.5992718273849102</v>
       </c>
       <c r="H34">
-        <v>0.9154000000000001</v>
+        <v>0.9162000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="B35" t="s">
         <v>9</v>
       </c>
       <c r="C35">
-        <v>52.01314444713902</v>
+        <v>53.45790968334249</v>
       </c>
       <c r="D35">
-        <v>25.48849727916627</v>
+        <v>26.99486187834476</v>
       </c>
       <c r="E35">
-        <v>0.9142999999999999</v>
+        <v>0.9154000000000001</v>
       </c>
       <c r="F35">
-        <v>0.9142999999999999</v>
+        <v>0.9154000000000001</v>
       </c>
       <c r="G35">
-        <v>0.4380094145699611</v>
+        <v>0.5691000647975994</v>
       </c>
       <c r="H35">
-        <v>0.9142999999999999</v>
+        <v>0.9154000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1">
-        <v>46182</v>
+        <v>46178</v>
       </c>
       <c r="B36" t="s">
         <v>9</v>
       </c>
       <c r="C36">
-        <v>50.12461745484359</v>
+        <v>52.01314444713902</v>
       </c>
       <c r="D36">
-        <v>25.31796473106079</v>
+        <v>25.48849727916627</v>
       </c>
       <c r="E36">
-        <v>0.916</v>
+        <v>0.9142999999999999</v>
       </c>
       <c r="F36">
-        <v>0.916</v>
+        <v>0.9142999999999999</v>
       </c>
       <c r="G36">
-        <v>0.4801457138994158</v>
+        <v>0.4380094145699611</v>
       </c>
       <c r="H36">
-        <v>0.916</v>
+        <v>0.9142999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1">
-        <v>46153</v>
+        <v>46182</v>
       </c>
       <c r="B37" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C37">
-        <v>34.64560932909123</v>
+        <v>50.12461745484359</v>
       </c>
       <c r="D37">
-        <v>26.08311546080494</v>
+        <v>25.31796473106079</v>
       </c>
       <c r="E37">
-        <v>0.9983000000000001</v>
+        <v>0.916</v>
       </c>
       <c r="F37">
-        <v>0.9983000000000001</v>
+        <v>0.916</v>
       </c>
       <c r="G37">
-        <v>0.06258613715048233</v>
+        <v>0.4801457138994158</v>
       </c>
       <c r="H37">
-        <v>0.9983000000000001</v>
+        <v>0.916</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1">
-        <v>46154</v>
+        <v>46183</v>
       </c>
       <c r="B38" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C38">
-        <v>34.50204921141101</v>
+        <v>51.46065536727718</v>
       </c>
       <c r="D38">
-        <v>25.94535229304585</v>
+        <v>25.08120911400394</v>
       </c>
       <c r="E38">
-        <v>0.9984</v>
+        <v>0.9188000000000002</v>
       </c>
       <c r="F38">
-        <v>0.9984</v>
+        <v>0.9188000000000002</v>
       </c>
       <c r="G38">
-        <v>0.05768943168306073</v>
+        <v>0.426738362957046</v>
       </c>
       <c r="H38">
-        <v>0.9984</v>
+        <v>0.9188000000000002</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="B39" t="s">
         <v>10</v>
       </c>
       <c r="C39">
-        <v>35.10429483281073</v>
+        <v>34.64560932909123</v>
       </c>
       <c r="D39">
-        <v>26.43864879939599</v>
+        <v>26.08311546080494</v>
       </c>
       <c r="E39">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="F39">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="G39">
-        <v>0.07926550001722021</v>
+        <v>0.06258613715048233</v>
       </c>
       <c r="H39">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="B40" t="s">
         <v>10</v>
       </c>
       <c r="C40">
-        <v>35.36860632820093</v>
+        <v>34.50204921141101</v>
       </c>
       <c r="D40">
-        <v>26.56575571102338</v>
+        <v>25.94535229304585</v>
       </c>
       <c r="E40">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F40">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G40">
-        <v>0.08553946591902095</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H40">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="B41" t="s">
         <v>10</v>
       </c>
       <c r="C41">
-        <v>34.88080083527914</v>
+        <v>35.10429483281073</v>
       </c>
       <c r="D41">
-        <v>26.19322945679072</v>
+        <v>26.43864879939599</v>
       </c>
       <c r="E41">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="F41">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="G41">
-        <v>0.06870693142475881</v>
+        <v>0.07926550001722021</v>
       </c>
       <c r="H41">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1">
-        <v>46160</v>
+        <v>46156</v>
       </c>
       <c r="B42" t="s">
         <v>10</v>
       </c>
       <c r="C42">
-        <v>34.67638692539213</v>
+        <v>35.36860632820093</v>
       </c>
       <c r="D42">
-        <v>26.06707890342319</v>
+        <v>26.56575571102338</v>
       </c>
       <c r="E42">
         <v>0.9985999999999999</v>
@@ -1489,7 +1489,7 @@
         <v>0.9985999999999999</v>
       </c>
       <c r="G42">
-        <v>0.06289213016552919</v>
+        <v>0.08553946591902095</v>
       </c>
       <c r="H42">
         <v>0.9985999999999999</v>
@@ -1497,120 +1497,120 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="B43" t="s">
         <v>10</v>
       </c>
       <c r="C43">
-        <v>34.21212662725402</v>
+        <v>34.88080083527914</v>
       </c>
       <c r="D43">
-        <v>25.60349394367002</v>
+        <v>26.19322945679072</v>
       </c>
       <c r="E43">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="F43">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="G43">
-        <v>0.0486610616591685</v>
+        <v>0.06870693142475881</v>
       </c>
       <c r="H43">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="B44" t="s">
         <v>10</v>
       </c>
       <c r="C44">
-        <v>34.78598436564941</v>
+        <v>34.67638692539213</v>
       </c>
       <c r="D44">
-        <v>25.95505316769806</v>
+        <v>26.06707890342319</v>
       </c>
       <c r="E44">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="F44">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="G44">
-        <v>0.06335117806143331</v>
+        <v>0.06289213016552919</v>
       </c>
       <c r="H44">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1">
-        <v>46163</v>
+        <v>46161</v>
       </c>
       <c r="B45" t="s">
         <v>10</v>
       </c>
       <c r="C45">
-        <v>33.4539909056227</v>
+        <v>34.21212662725402</v>
       </c>
       <c r="D45">
-        <v>25.96014535427112</v>
+        <v>25.60349394367002</v>
       </c>
       <c r="E45">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="F45">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="G45">
-        <v>0.06350423294229035</v>
+        <v>0.0486610616591685</v>
       </c>
       <c r="H45">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1">
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="B46" t="s">
         <v>10</v>
       </c>
       <c r="C46">
-        <v>33.24951933563993</v>
+        <v>34.78598436564941</v>
       </c>
       <c r="D46">
-        <v>25.46629530314992</v>
+        <v>25.95505316769806</v>
       </c>
       <c r="E46">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="F46">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="G46">
-        <v>0.06136193159696024</v>
+        <v>0.06335117806143331</v>
       </c>
       <c r="H46">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1">
-        <v>46167</v>
+        <v>46163</v>
       </c>
       <c r="B47" t="s">
         <v>10</v>
       </c>
       <c r="C47">
-        <v>33.29896419867477</v>
+        <v>33.4539909056227</v>
       </c>
       <c r="D47">
-        <v>25.45090185337973</v>
+        <v>25.96014535427112</v>
       </c>
       <c r="E47">
         <v>0.9984</v>
@@ -1619,7 +1619,7 @@
         <v>0.9984</v>
       </c>
       <c r="G47">
-        <v>0.06136193159696024</v>
+        <v>0.06350423294229035</v>
       </c>
       <c r="H47">
         <v>0.9984</v>
@@ -1627,16 +1627,16 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1">
-        <v>46168</v>
+        <v>46164</v>
       </c>
       <c r="B48" t="s">
         <v>10</v>
       </c>
       <c r="C48">
-        <v>33.41270923608511</v>
+        <v>33.24951933563993</v>
       </c>
       <c r="D48">
-        <v>25.54156152389702</v>
+        <v>25.46629530314992</v>
       </c>
       <c r="E48">
         <v>0.9984</v>
@@ -1645,7 +1645,7 @@
         <v>0.9984</v>
       </c>
       <c r="G48">
-        <v>0.06549347940676342</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H48">
         <v>0.9984</v>
@@ -1653,198 +1653,198 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1">
-        <v>46169</v>
+        <v>46167</v>
       </c>
       <c r="B49" t="s">
         <v>10</v>
       </c>
       <c r="C49">
-        <v>33.73350746548562</v>
+        <v>33.29896419867477</v>
       </c>
       <c r="D49">
-        <v>25.75393367034243</v>
+        <v>25.45090185337973</v>
       </c>
       <c r="E49">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="F49">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="G49">
-        <v>0.07620510288008187</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H49">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1">
-        <v>46170</v>
+        <v>46168</v>
       </c>
       <c r="B50" t="s">
         <v>10</v>
       </c>
       <c r="C50">
-        <v>33.84336414535104</v>
+        <v>33.41270923608511</v>
       </c>
       <c r="D50">
-        <v>25.97168203877208</v>
+        <v>25.54156152389702</v>
       </c>
       <c r="E50">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
       <c r="F50">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
       <c r="G50">
-        <v>0.0844683152463559</v>
+        <v>0.06549347940676342</v>
       </c>
       <c r="H50">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1">
-        <v>46171</v>
+        <v>46169</v>
       </c>
       <c r="B51" t="s">
         <v>10</v>
       </c>
       <c r="C51">
-        <v>33.73370320039719</v>
+        <v>33.73350746548562</v>
       </c>
       <c r="D51">
-        <v>25.880209881309</v>
+        <v>25.75393367034243</v>
       </c>
       <c r="E51">
-        <v>0.9988</v>
+        <v>0.9987000000000001</v>
       </c>
       <c r="F51">
-        <v>0.9988</v>
+        <v>0.9987000000000001</v>
       </c>
       <c r="G51">
-        <v>0.08201990413931148</v>
+        <v>0.07620510288008187</v>
       </c>
       <c r="H51">
-        <v>0.9988</v>
+        <v>0.9987000000000001</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1">
-        <v>46174</v>
+        <v>46170</v>
       </c>
       <c r="B52" t="s">
         <v>10</v>
       </c>
       <c r="C52">
-        <v>33.45546240777382</v>
+        <v>33.84336414535104</v>
       </c>
       <c r="D52">
-        <v>25.61350381215703</v>
+        <v>25.97168203877208</v>
       </c>
       <c r="E52">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
       <c r="F52">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
       <c r="G52">
-        <v>0.06901304118647311</v>
+        <v>0.0844683152463559</v>
       </c>
       <c r="H52">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1">
-        <v>46175</v>
+        <v>46171</v>
       </c>
       <c r="B53" t="s">
         <v>10</v>
       </c>
       <c r="C53">
-        <v>33.31245255516097</v>
+        <v>33.73370320039719</v>
       </c>
       <c r="D53">
-        <v>25.36461330330757</v>
+        <v>25.880209881309</v>
       </c>
       <c r="E53">
-        <v>0.9989999999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="F53">
-        <v>0.9989999999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="G53">
-        <v>0.05845447259401171</v>
+        <v>0.08201990413931148</v>
       </c>
       <c r="H53">
-        <v>0.9989999999999999</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="B54" t="s">
         <v>10</v>
       </c>
       <c r="C54">
-        <v>33.02444632653544</v>
+        <v>33.45546240777382</v>
       </c>
       <c r="D54">
-        <v>25.07926152561908</v>
+        <v>25.61350381215703</v>
       </c>
       <c r="E54">
-        <v>0.9991</v>
+        <v>0.999</v>
       </c>
       <c r="F54">
-        <v>0.9991</v>
+        <v>0.999</v>
       </c>
       <c r="G54">
-        <v>0.04697780820974229</v>
+        <v>0.06901304118647311</v>
       </c>
       <c r="H54">
-        <v>0.9991</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1">
-        <v>46177</v>
+        <v>46175</v>
       </c>
       <c r="B55" t="s">
         <v>10</v>
       </c>
       <c r="C55">
-        <v>33.50291463064395</v>
+        <v>33.31245255516097</v>
       </c>
       <c r="D55">
-        <v>25.33002193941023</v>
+        <v>25.36461330330757</v>
       </c>
       <c r="E55">
-        <v>0.9991000000000001</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="F55">
-        <v>0.9991000000000001</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="G55">
-        <v>0.05768943168306073</v>
+        <v>0.05845447259401171</v>
       </c>
       <c r="H55">
-        <v>0.9991000000000001</v>
+        <v>0.9989999999999999</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1">
-        <v>46178</v>
+        <v>46176</v>
       </c>
       <c r="B56" t="s">
         <v>10</v>
       </c>
       <c r="C56">
-        <v>32.19021336116872</v>
+        <v>33.02444632653544</v>
       </c>
       <c r="D56">
-        <v>24.38570557505481</v>
+        <v>25.07926152561908</v>
       </c>
       <c r="E56">
         <v>0.9991</v>
@@ -1853,7 +1853,7 @@
         <v>0.9991</v>
       </c>
       <c r="G56">
-        <v>0.01775063028607016</v>
+        <v>0.04697780820974229</v>
       </c>
       <c r="H56">
         <v>0.9991</v>
@@ -1861,718 +1861,718 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1">
-        <v>46182</v>
+        <v>46177</v>
       </c>
       <c r="B57" t="s">
         <v>10</v>
       </c>
       <c r="C57">
-        <v>32.06505731417286</v>
+        <v>33.50291463064395</v>
       </c>
       <c r="D57">
-        <v>24.06041109516704</v>
+        <v>25.33002193941023</v>
       </c>
       <c r="E57">
-        <v>0.9988999999999999</v>
+        <v>0.9991000000000001</v>
       </c>
       <c r="F57">
-        <v>0.9988999999999999</v>
+        <v>0.9991000000000001</v>
       </c>
       <c r="G57">
-        <v>0.004743767333231785</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H57">
-        <v>0.9988999999999999</v>
+        <v>0.9991000000000001</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1">
-        <v>46153</v>
+        <v>46178</v>
       </c>
       <c r="B58" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C58">
-        <v>36.55790859258162</v>
+        <v>32.19021336116872</v>
       </c>
       <c r="D58">
-        <v>22.67181120908155</v>
+        <v>24.38570557505481</v>
       </c>
       <c r="E58">
-        <v>0.9990740999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F58">
-        <v>0.9990740999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G58">
-        <v>0.1648443271746771</v>
+        <v>0.01775063028607016</v>
       </c>
       <c r="H58">
-        <v>0.9990740999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1">
-        <v>46154</v>
+        <v>46182</v>
       </c>
       <c r="B59" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C59">
-        <v>36.44753722959613</v>
+        <v>32.06505731417286</v>
       </c>
       <c r="D59">
-        <v>22.40292401789388</v>
+        <v>24.06041109516704</v>
       </c>
       <c r="E59">
-        <v>0.9990772499999999</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="F59">
-        <v>0.9990772499999999</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="G59">
-        <v>0.154964342628132</v>
+        <v>0.004743767333231785</v>
       </c>
       <c r="H59">
-        <v>0.9990772499999999</v>
+        <v>0.9988999999999999</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1">
-        <v>46155</v>
+        <v>46183</v>
       </c>
       <c r="B60" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C60">
-        <v>36.63128514035871</v>
+        <v>31.23512211947358</v>
       </c>
       <c r="D60">
-        <v>22.65773388934668</v>
+        <v>23.50146802051874</v>
       </c>
       <c r="E60">
-        <v>0.99907745</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="F60">
-        <v>0.99907745</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="G60">
-        <v>0.1671633421405267</v>
+        <v>-0.01729146564349893</v>
       </c>
       <c r="H60">
-        <v>0.99907745</v>
+        <v>0.9989999999999999</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="B61" t="s">
         <v>11</v>
       </c>
       <c r="C61">
-        <v>36.87865927427314</v>
+        <v>36.55790859258162</v>
       </c>
       <c r="D61">
-        <v>22.69755646854794</v>
+        <v>22.67181120908155</v>
       </c>
       <c r="E61">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="F61">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="G61">
-        <v>0.1754592080224002</v>
+        <v>0.1648443271746771</v>
       </c>
       <c r="H61">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="B62" t="s">
         <v>11</v>
       </c>
       <c r="C62">
-        <v>36.52208783231286</v>
+        <v>36.44753722959613</v>
       </c>
       <c r="D62">
-        <v>22.32462309676992</v>
+        <v>22.40292401789388</v>
       </c>
       <c r="E62">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="F62">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="G62">
-        <v>0.1577242156354994</v>
+        <v>0.154964342628132</v>
       </c>
       <c r="H62">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="B63" t="s">
         <v>11</v>
       </c>
       <c r="C63">
-        <v>36.25604200674668</v>
+        <v>36.63128514035871</v>
       </c>
       <c r="D63">
-        <v>22.16555007468561</v>
+        <v>22.65773388934668</v>
       </c>
       <c r="E63">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="F63">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="G63">
-        <v>0.1527434068648266</v>
+        <v>0.1671633421405267</v>
       </c>
       <c r="H63">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1">
-        <v>46161</v>
+        <v>46156</v>
       </c>
       <c r="B64" t="s">
         <v>11</v>
       </c>
       <c r="C64">
-        <v>36.01040085730018</v>
+        <v>36.87865927427314</v>
       </c>
       <c r="D64">
-        <v>22.19475589056387</v>
+        <v>22.69755646854794</v>
       </c>
       <c r="E64">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="F64">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="G64">
-        <v>0.1456396418594061</v>
+        <v>0.1754592080224002</v>
       </c>
       <c r="H64">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1">
-        <v>46162</v>
+        <v>46157</v>
       </c>
       <c r="B65" t="s">
         <v>11</v>
       </c>
       <c r="C65">
-        <v>36.45290912796982</v>
+        <v>36.52208783231286</v>
       </c>
       <c r="D65">
-        <v>22.46357594746874</v>
+        <v>22.32462309676992</v>
       </c>
       <c r="E65">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="F65">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="G65">
-        <v>0.1646157747240327</v>
+        <v>0.1577242156354994</v>
       </c>
       <c r="H65">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1">
-        <v>46163</v>
+        <v>46160</v>
       </c>
       <c r="B66" t="s">
         <v>11</v>
       </c>
       <c r="C66">
-        <v>35.75282090566891</v>
+        <v>36.25604200674668</v>
       </c>
       <c r="D66">
-        <v>22.57615417310648</v>
+        <v>22.16555007468561</v>
       </c>
       <c r="E66">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="F66">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="G66">
-        <v>0.1668367104873381</v>
+        <v>0.1527434068648266</v>
       </c>
       <c r="H66">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1">
-        <v>46164</v>
+        <v>46161</v>
       </c>
       <c r="B67" t="s">
         <v>11</v>
       </c>
       <c r="C67">
-        <v>35.75514940724808</v>
+        <v>36.01040085730018</v>
       </c>
       <c r="D67">
-        <v>22.28880693466429</v>
+        <v>22.19475589056387</v>
       </c>
       <c r="E67">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="F67">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="G67">
-        <v>0.1717848261904962</v>
+        <v>0.1456396418594061</v>
       </c>
       <c r="H67">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1">
-        <v>46167</v>
+        <v>46162</v>
       </c>
       <c r="B68" t="s">
         <v>11</v>
       </c>
       <c r="C68">
-        <v>35.84133099010302</v>
+        <v>36.45290912796982</v>
       </c>
       <c r="D68">
-        <v>22.37458514769363</v>
+        <v>22.46357594746874</v>
       </c>
       <c r="E68">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="F68">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="G68">
-        <v>0.1717848261904962</v>
+        <v>0.1646157747240327</v>
       </c>
       <c r="H68">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1">
-        <v>46168</v>
+        <v>46163</v>
       </c>
       <c r="B69" t="s">
         <v>11</v>
       </c>
       <c r="C69">
-        <v>36.23214279739292</v>
+        <v>35.75282090566891</v>
       </c>
       <c r="D69">
-        <v>22.93484792820123</v>
+        <v>22.57615417310648</v>
       </c>
       <c r="E69">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
       <c r="F69">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
       <c r="G69">
-        <v>0.1925900763781823</v>
+        <v>0.1668367104873381</v>
       </c>
       <c r="H69">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="B70" t="s">
         <v>11</v>
       </c>
       <c r="C70">
-        <v>36.4336692499184</v>
+        <v>35.75514940724808</v>
       </c>
       <c r="D70">
-        <v>22.75940954009856</v>
+        <v>22.28880693466429</v>
       </c>
       <c r="E70">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="F70">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="G70">
-        <v>0.1912346098381414</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H70">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="B71" t="s">
         <v>11</v>
       </c>
       <c r="C71">
-        <v>36.57358557066742</v>
+        <v>35.84133099010302</v>
       </c>
       <c r="D71">
-        <v>22.83069636955243</v>
+        <v>22.37458514769363</v>
       </c>
       <c r="E71">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="F71">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="G71">
-        <v>0.2012778603742877</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H71">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1">
-        <v>46171</v>
+        <v>46168</v>
       </c>
       <c r="B72" t="s">
         <v>11</v>
       </c>
       <c r="C72">
-        <v>36.67481300942</v>
+        <v>36.23214279739292</v>
       </c>
       <c r="D72">
-        <v>22.95852861681004</v>
+        <v>22.93484792820123</v>
       </c>
       <c r="E72">
-        <v>0.9964953299999998</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="F72">
-        <v>0.9964953299999998</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="G72">
-        <v>0.2057034850411275</v>
+        <v>0.1925900763781823</v>
       </c>
       <c r="H72">
-        <v>0.9994474899999999</v>
+        <v>0.9992609200000001</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1">
-        <v>46174</v>
+        <v>46169</v>
       </c>
       <c r="B73" t="s">
         <v>11</v>
       </c>
       <c r="C73">
-        <v>36.84565507982974</v>
+        <v>36.4336692499184</v>
       </c>
       <c r="D73">
-        <v>23.15960292175205</v>
+        <v>22.75940954009856</v>
       </c>
       <c r="E73">
-        <v>0.99646052</v>
+        <v>0.9992099400000001</v>
       </c>
       <c r="F73">
-        <v>0.99646052</v>
+        <v>0.9992099400000001</v>
       </c>
       <c r="G73">
-        <v>0.2129379226426205</v>
+        <v>0.1912346098381414</v>
       </c>
       <c r="H73">
-        <v>0.9993986199999999</v>
+        <v>0.9992099400000001</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1">
-        <v>46175</v>
+        <v>46170</v>
       </c>
       <c r="B74" t="s">
         <v>11</v>
       </c>
       <c r="C74">
-        <v>36.88482057171844</v>
+        <v>36.57358557066742</v>
       </c>
       <c r="D74">
-        <v>23.03898938038424</v>
+        <v>22.83069636955243</v>
       </c>
       <c r="E74">
-        <v>0.99645675</v>
+        <v>0.9994435600000001</v>
       </c>
       <c r="F74">
-        <v>0.99645675</v>
+        <v>0.9994435600000001</v>
       </c>
       <c r="G74">
-        <v>0.2185229551183987</v>
+        <v>0.2012778603742877</v>
       </c>
       <c r="H74">
-        <v>0.9994034199999998</v>
+        <v>0.9994435600000001</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1">
-        <v>46176</v>
+        <v>46171</v>
       </c>
       <c r="B75" t="s">
         <v>11</v>
       </c>
       <c r="C75">
-        <v>36.96809213745556</v>
+        <v>36.67481300942</v>
       </c>
       <c r="D75">
-        <v>22.99660212231548</v>
+        <v>22.95852861681004</v>
       </c>
       <c r="E75">
-        <v>0.9964706</v>
+        <v>0.9964953299999998</v>
       </c>
       <c r="F75">
-        <v>0.9964706</v>
+        <v>0.9964953299999998</v>
       </c>
       <c r="G75">
-        <v>0.2153385706032709</v>
+        <v>0.2057034850411275</v>
       </c>
       <c r="H75">
-        <v>0.9993955800000001</v>
+        <v>0.9994474899999999</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1">
-        <v>46177</v>
+        <v>46174</v>
       </c>
       <c r="B76" t="s">
         <v>11</v>
       </c>
       <c r="C76">
-        <v>37.13780815830533</v>
+        <v>36.84565507982974</v>
       </c>
       <c r="D76">
-        <v>22.74889586257873</v>
+        <v>23.15960292175205</v>
       </c>
       <c r="E76">
-        <v>0.9964706899999999</v>
+        <v>0.99646052</v>
       </c>
       <c r="F76">
-        <v>0.9964706899999999</v>
+        <v>0.99646052</v>
       </c>
       <c r="G76">
-        <v>0.2094594998678323</v>
+        <v>0.2129379226426205</v>
       </c>
       <c r="H76">
-        <v>0.99938478</v>
+        <v>0.9993986199999999</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1">
-        <v>46178</v>
+        <v>46175</v>
       </c>
       <c r="B77" t="s">
         <v>11</v>
       </c>
       <c r="C77">
-        <v>35.57681391373501</v>
+        <v>36.88482057171844</v>
       </c>
       <c r="D77">
-        <v>21.69452833602077</v>
+        <v>23.03898938038424</v>
       </c>
       <c r="E77">
-        <v>0.9964558499999999</v>
+        <v>0.99645675</v>
       </c>
       <c r="F77">
-        <v>0.9964558499999999</v>
+        <v>0.99645675</v>
       </c>
       <c r="G77">
-        <v>0.151404286858543</v>
+        <v>0.2185229551183987</v>
       </c>
       <c r="H77">
-        <v>0.9993850399999999</v>
+        <v>0.9994034199999998</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="1">
-        <v>46182</v>
+        <v>46176</v>
       </c>
       <c r="B78" t="s">
         <v>11</v>
       </c>
       <c r="C78">
-        <v>35.58815840295288</v>
+        <v>36.96809213745556</v>
       </c>
       <c r="D78">
-        <v>21.80812849732373</v>
+        <v>22.99660212231548</v>
       </c>
       <c r="E78">
-        <v>0.9962853900000002</v>
+        <v>0.9964706</v>
       </c>
       <c r="F78">
-        <v>0.9962853900000002</v>
+        <v>0.9964706</v>
       </c>
       <c r="G78">
-        <v>0.1559278910539408</v>
+        <v>0.2153385706032709</v>
       </c>
       <c r="H78">
-        <v>0.9992534400000002</v>
+        <v>0.9993955800000001</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1">
-        <v>46153</v>
+        <v>46177</v>
       </c>
       <c r="B79" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C79">
-        <v>52.70832779833182</v>
+        <v>37.13780815830533</v>
       </c>
       <c r="D79">
-        <v>23.99044674439659</v>
+        <v>22.74889586257873</v>
       </c>
       <c r="E79">
-        <v>0.9994000000000002</v>
+        <v>0.9964706899999999</v>
       </c>
       <c r="F79">
-        <v>0.9994000000000002</v>
+        <v>0.9964706899999999</v>
       </c>
       <c r="G79">
-        <v>0.5438253854918791</v>
+        <v>0.2094594998678323</v>
       </c>
       <c r="H79">
-        <v>0.9994000000000002</v>
+        <v>0.99938478</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1">
-        <v>46154</v>
+        <v>46178</v>
       </c>
       <c r="B80" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C80">
-        <v>50.89464485280568</v>
+        <v>35.57681391373501</v>
       </c>
       <c r="D80">
-        <v>23.21558303176282</v>
+        <v>21.69452833602077</v>
       </c>
       <c r="E80">
-        <v>0.9996</v>
+        <v>0.9964558499999999</v>
       </c>
       <c r="F80">
-        <v>0.9996</v>
+        <v>0.9964558499999999</v>
       </c>
       <c r="G80">
-        <v>0.5034825029548833</v>
+        <v>0.151404286858543</v>
       </c>
       <c r="H80">
-        <v>0.9996</v>
+        <v>0.9993850399999999</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="1">
-        <v>46155</v>
+        <v>46182</v>
       </c>
       <c r="B81" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C81">
-        <v>51.8659994471731</v>
+        <v>35.58815840295288</v>
       </c>
       <c r="D81">
-        <v>23.7009037279043</v>
+        <v>21.80812849732373</v>
       </c>
       <c r="E81">
-        <v>1.0002</v>
+        <v>0.9962853900000002</v>
       </c>
       <c r="F81">
-        <v>1.0002</v>
+        <v>0.9962853900000002</v>
       </c>
       <c r="G81">
-        <v>0.533512029714132</v>
+        <v>0.1559278910539408</v>
       </c>
       <c r="H81">
-        <v>1.0002</v>
+        <v>0.9992534400000002</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="1">
-        <v>46156</v>
+        <v>46183</v>
       </c>
       <c r="B82" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C82">
-        <v>52.4470179952828</v>
+        <v>34.74027179067053</v>
       </c>
       <c r="D82">
-        <v>23.76861704536814</v>
+        <v>21.20683390251297</v>
       </c>
       <c r="E82">
-        <v>0.9998</v>
+        <v>0.9962360400000001</v>
       </c>
       <c r="F82">
-        <v>0.9998</v>
+        <v>0.9962360400000001</v>
       </c>
       <c r="G82">
-        <v>0.5492634496849078</v>
+        <v>0.132836418641906</v>
       </c>
       <c r="H82">
-        <v>0.9998</v>
+        <v>0.9992478800000001</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="1">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="B83" t="s">
         <v>12</v>
       </c>
       <c r="C83">
-        <v>50.81077380018606</v>
+        <v>52.70832779833182</v>
       </c>
       <c r="D83">
-        <v>22.76900580927995</v>
+        <v>23.99044674439659</v>
       </c>
       <c r="E83">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="F83">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="G83">
-        <v>0.4903296143797722</v>
+        <v>0.5438253854918791</v>
       </c>
       <c r="H83">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="1">
-        <v>46160</v>
+        <v>46154</v>
       </c>
       <c r="B84" t="s">
         <v>12</v>
       </c>
       <c r="C84">
-        <v>49.50286387149169</v>
+        <v>50.89464485280568</v>
       </c>
       <c r="D84">
-        <v>22.24532119914133</v>
+        <v>23.21558303176282</v>
       </c>
       <c r="E84">
         <v>0.9996</v>
@@ -2581,7 +2581,7 @@
         <v>0.9996</v>
       </c>
       <c r="G84">
-        <v>0.4630591776162345</v>
+        <v>0.5034825029548833</v>
       </c>
       <c r="H84">
         <v>0.9996</v>
@@ -2589,224 +2589,224 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1">
-        <v>46161</v>
+        <v>46155</v>
       </c>
       <c r="B85" t="s">
         <v>12</v>
       </c>
       <c r="C85">
-        <v>49.29146729279496</v>
+        <v>51.8659994471731</v>
       </c>
       <c r="D85">
-        <v>22.22167836589682</v>
+        <v>23.7009037279043</v>
       </c>
       <c r="E85">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="F85">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="G85">
-        <v>0.4571659248870246</v>
+        <v>0.533512029714132</v>
       </c>
       <c r="H85">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="1">
-        <v>46162</v>
+        <v>46156</v>
       </c>
       <c r="B86" t="s">
         <v>12</v>
       </c>
       <c r="C86">
-        <v>50.88652370817657</v>
+        <v>52.4470179952828</v>
       </c>
       <c r="D86">
-        <v>22.93254398967657</v>
+        <v>23.76861704536814</v>
       </c>
       <c r="E86">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F86">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G86">
-        <v>0.5126171754864624</v>
+        <v>0.5492634496849078</v>
       </c>
       <c r="H86">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="1">
-        <v>46163</v>
+        <v>46157</v>
       </c>
       <c r="B87" t="s">
         <v>12</v>
       </c>
       <c r="C87">
-        <v>48.26646764818586</v>
+        <v>50.81077380018606</v>
       </c>
       <c r="D87">
-        <v>23.11655387625012</v>
+        <v>22.76900580927995</v>
       </c>
       <c r="E87">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="F87">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="G87">
-        <v>0.521243030947425</v>
+        <v>0.4903296143797722</v>
       </c>
       <c r="H87">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1">
-        <v>46164</v>
+        <v>46160</v>
       </c>
       <c r="B88" t="s">
         <v>12</v>
       </c>
       <c r="C88">
-        <v>48.84737503703267</v>
+        <v>49.50286387149169</v>
       </c>
       <c r="D88">
-        <v>22.83557604744466</v>
+        <v>22.24532119914133</v>
       </c>
       <c r="E88">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="F88">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="G88">
-        <v>0.5438521997590966</v>
+        <v>0.4630591776162345</v>
       </c>
       <c r="H88">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="1">
-        <v>46167</v>
+        <v>46161</v>
       </c>
       <c r="B89" t="s">
         <v>12</v>
       </c>
       <c r="C89">
-        <v>48.85151560750146</v>
+        <v>49.29146729279496</v>
       </c>
       <c r="D89">
-        <v>22.83513820206554</v>
+        <v>22.22167836589682</v>
       </c>
       <c r="E89">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F89">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G89">
-        <v>0.5438521997590966</v>
+        <v>0.4571659248870246</v>
       </c>
       <c r="H89">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="1">
-        <v>46168</v>
+        <v>46162</v>
       </c>
       <c r="B90" t="s">
         <v>12</v>
       </c>
       <c r="C90">
-        <v>50.90437883274981</v>
+        <v>50.88652370817657</v>
       </c>
       <c r="D90">
-        <v>24.25672473501501</v>
+        <v>22.93254398967657</v>
       </c>
       <c r="E90">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F90">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G90">
-        <v>0.6130191115419561</v>
+        <v>0.5126171754864624</v>
       </c>
       <c r="H90">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="1">
-        <v>46169</v>
+        <v>46163</v>
       </c>
       <c r="B91" t="s">
         <v>12</v>
       </c>
       <c r="C91">
-        <v>50.47312432255841</v>
+        <v>48.26646764818586</v>
       </c>
       <c r="D91">
-        <v>23.84499305142194</v>
+        <v>23.11655387625012</v>
       </c>
       <c r="E91">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="F91">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="G91">
-        <v>0.5952317692821967</v>
+        <v>0.521243030947425</v>
       </c>
       <c r="H91">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="1">
-        <v>46170</v>
+        <v>46164</v>
       </c>
       <c r="B92" t="s">
         <v>12</v>
       </c>
       <c r="C92">
-        <v>50.84596269629946</v>
+        <v>48.84737503703267</v>
       </c>
       <c r="D92">
-        <v>23.7680603326165</v>
+        <v>22.83557604744466</v>
       </c>
       <c r="E92">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F92">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G92">
-        <v>0.606831065374982</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H92">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="1">
-        <v>46171</v>
+        <v>46167</v>
       </c>
       <c r="B93" t="s">
         <v>12</v>
       </c>
       <c r="C93">
-        <v>51.08372269965196</v>
+        <v>48.85151560750146</v>
       </c>
       <c r="D93">
-        <v>23.88880359436525</v>
+        <v>22.83513820206554</v>
       </c>
       <c r="E93">
         <v>0.9998999999999999</v>
@@ -2815,7 +2815,7 @@
         <v>0.9998999999999999</v>
       </c>
       <c r="G93">
-        <v>0.604420070348211</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H93">
         <v>0.9998999999999999</v>
@@ -2823,614 +2823,614 @@
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="1">
-        <v>46174</v>
+        <v>46168</v>
       </c>
       <c r="B94" t="s">
         <v>12</v>
       </c>
       <c r="C94">
-        <v>51.84875713649351</v>
+        <v>50.90437883274981</v>
       </c>
       <c r="D94">
-        <v>24.29466650399529</v>
+        <v>24.25672473501501</v>
       </c>
       <c r="E94">
-        <v>0.9998</v>
+        <v>0.9996999999999999</v>
       </c>
       <c r="F94">
-        <v>0.9998</v>
+        <v>0.9996999999999999</v>
       </c>
       <c r="G94">
-        <v>0.6282079224060508</v>
+        <v>0.6130191115419561</v>
       </c>
       <c r="H94">
-        <v>0.9998</v>
+        <v>0.9996999999999999</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="1">
-        <v>46175</v>
+        <v>46169</v>
       </c>
       <c r="B95" t="s">
         <v>12</v>
       </c>
       <c r="C95">
-        <v>53.42858844634741</v>
+        <v>50.47312432255841</v>
       </c>
       <c r="D95">
-        <v>24.82449061140869</v>
+        <v>23.84499305142194</v>
       </c>
       <c r="E95">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="F95">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="G95">
-        <v>0.6935709687814895</v>
+        <v>0.5952317692821967</v>
       </c>
       <c r="H95">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="1">
-        <v>46176</v>
+        <v>46170</v>
       </c>
       <c r="B96" t="s">
         <v>12</v>
       </c>
       <c r="C96">
-        <v>53.95056789686777</v>
+        <v>50.84596269629946</v>
       </c>
       <c r="D96">
-        <v>24.99295077214167</v>
+        <v>23.7680603326165</v>
       </c>
       <c r="E96">
-        <v>0.9996000000000002</v>
+        <v>0.9998</v>
       </c>
       <c r="F96">
-        <v>0.9996000000000002</v>
+        <v>0.9998</v>
       </c>
       <c r="G96">
-        <v>0.7088134081800193</v>
+        <v>0.606831065374982</v>
       </c>
       <c r="H96">
-        <v>0.9996000000000002</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="1">
-        <v>46177</v>
+        <v>46171</v>
       </c>
       <c r="B97" t="s">
         <v>12</v>
       </c>
       <c r="C97">
-        <v>53.29782764127071</v>
+        <v>51.08372269965196</v>
       </c>
       <c r="D97">
-        <v>24.48126483589962</v>
+        <v>23.88880359436525</v>
       </c>
       <c r="E97">
-        <v>1.0001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F97">
-        <v>1.0001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G97">
-        <v>0.6810341543458651</v>
+        <v>0.604420070348211</v>
       </c>
       <c r="H97">
-        <v>1.0001</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="1">
-        <v>46178</v>
+        <v>46174</v>
       </c>
       <c r="B98" t="s">
         <v>12</v>
       </c>
       <c r="C98">
-        <v>48.44949949587421</v>
+        <v>51.84875713649351</v>
       </c>
       <c r="D98">
-        <v>22.39103669390088</v>
+        <v>24.29466650399529</v>
       </c>
       <c r="E98">
-        <v>0.9995999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F98">
-        <v>0.9995999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G98">
-        <v>0.5260916717665549</v>
+        <v>0.6282079224060508</v>
       </c>
       <c r="H98">
-        <v>0.9995999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="1">
-        <v>46182</v>
+        <v>46175</v>
       </c>
       <c r="B99" t="s">
         <v>12</v>
       </c>
       <c r="C99">
-        <v>50.39371086612305</v>
+        <v>53.42858844634741</v>
       </c>
       <c r="D99">
-        <v>23.09650971949351</v>
+        <v>24.82449061140869</v>
       </c>
       <c r="E99">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="F99">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="G99">
-        <v>0.5832039354188183</v>
+        <v>0.6935709687814895</v>
       </c>
       <c r="H99">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="1">
-        <v>46153</v>
+        <v>46176</v>
       </c>
       <c r="B100" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C100">
-        <v>57.1732166855686</v>
+        <v>53.95056789686777</v>
       </c>
       <c r="D100">
-        <v>23.50022751267814</v>
+        <v>24.99295077214167</v>
       </c>
       <c r="E100">
-        <v>0.9991</v>
+        <v>0.9996000000000002</v>
       </c>
       <c r="F100">
-        <v>0.9991</v>
+        <v>0.9996000000000002</v>
       </c>
       <c r="G100">
-        <v>0.6994110097039083</v>
+        <v>0.7088134081800193</v>
       </c>
       <c r="H100">
-        <v>0.9991</v>
+        <v>0.9996000000000002</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="1">
-        <v>46154</v>
+        <v>46177</v>
       </c>
       <c r="B101" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C101">
-        <v>54.77380642078597</v>
+        <v>53.29782764127071</v>
       </c>
       <c r="D101">
-        <v>22.55192940254518</v>
+        <v>24.48126483589962</v>
       </c>
       <c r="E101">
-        <v>0.9990000000000001</v>
+        <v>1.0001</v>
       </c>
       <c r="F101">
-        <v>0.9990000000000001</v>
+        <v>1.0001</v>
       </c>
       <c r="G101">
-        <v>0.6459175880844941</v>
+        <v>0.6810341543458651</v>
       </c>
       <c r="H101">
-        <v>0.9990000000000001</v>
+        <v>1.0001</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="1">
-        <v>46155</v>
+        <v>46178</v>
       </c>
       <c r="B102" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C102">
-        <v>56.32187380830906</v>
+        <v>48.44949949587421</v>
       </c>
       <c r="D102">
-        <v>23.17121437414109</v>
+        <v>22.39103669390088</v>
       </c>
       <c r="E102">
-        <v>0.9990000000000001</v>
+        <v>0.9995999999999999</v>
       </c>
       <c r="F102">
-        <v>0.9990000000000001</v>
+        <v>0.9995999999999999</v>
       </c>
       <c r="G102">
-        <v>0.6851523922954754</v>
+        <v>0.5260916717665549</v>
       </c>
       <c r="H102">
-        <v>0.9990000000000001</v>
+        <v>0.9995999999999999</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="1">
-        <v>46156</v>
+        <v>46182</v>
       </c>
       <c r="B103" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C103">
-        <v>56.15321618553139</v>
+        <v>50.39371086612305</v>
       </c>
       <c r="D103">
-        <v>22.95838347314443</v>
+        <v>23.09650971949351</v>
       </c>
       <c r="E103">
-        <v>0.9992</v>
+        <v>0.9997</v>
       </c>
       <c r="F103">
-        <v>0.9992</v>
+        <v>0.9997</v>
       </c>
       <c r="G103">
-        <v>0.6907028507208208</v>
+        <v>0.5832039354188183</v>
       </c>
       <c r="H103">
-        <v>0.9992</v>
+        <v>0.9997</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="1">
-        <v>46157</v>
+        <v>46183</v>
       </c>
       <c r="B104" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C104">
-        <v>54.47755813049488</v>
+        <v>48.17343634448468</v>
       </c>
       <c r="D104">
-        <v>22.0083816089626</v>
+        <v>22.05005999539094</v>
       </c>
       <c r="E104">
-        <v>0.9986</v>
+        <v>0.9994999999999999</v>
       </c>
       <c r="F104">
-        <v>0.9986</v>
+        <v>0.9994999999999999</v>
       </c>
       <c r="G104">
-        <v>0.6220895940829376</v>
+        <v>0.5293597423345122</v>
       </c>
       <c r="H104">
-        <v>0.9986</v>
+        <v>0.9994999999999999</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B105" t="s">
         <v>13</v>
       </c>
       <c r="C105">
-        <v>52.6278781150669</v>
+        <v>57.1732166855686</v>
       </c>
       <c r="D105">
-        <v>21.5357353870778</v>
+        <v>23.50022751267814</v>
       </c>
       <c r="E105">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F105">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G105">
-        <v>0.5845134636435627</v>
+        <v>0.6994110097039083</v>
       </c>
       <c r="H105">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B106" t="s">
         <v>13</v>
       </c>
       <c r="C106">
-        <v>54.91583234840245</v>
+        <v>54.77380642078597</v>
       </c>
       <c r="D106">
-        <v>22.38321645985006</v>
+        <v>22.55192940254518</v>
       </c>
       <c r="E106">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F106">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G106">
-        <v>0.6596976539194066</v>
+        <v>0.6459175880844941</v>
       </c>
       <c r="H106">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B107" t="s">
         <v>13</v>
       </c>
       <c r="C107">
-        <v>53.91712298548793</v>
+        <v>56.32187380830906</v>
       </c>
       <c r="D107">
-        <v>22.73711181201267</v>
+        <v>23.17121437414109</v>
       </c>
       <c r="E107">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F107">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G107">
-        <v>0.6737329602396263</v>
+        <v>0.6851523922954754</v>
       </c>
       <c r="H107">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="1">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="B108" t="s">
         <v>13</v>
       </c>
       <c r="C108">
-        <v>55.19651747515625</v>
+        <v>56.15321618553139</v>
       </c>
       <c r="D108">
-        <v>22.79462037330554</v>
+        <v>22.95838347314443</v>
       </c>
       <c r="E108">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
       <c r="F108">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
       <c r="G108">
-        <v>0.7139885317003913</v>
+        <v>0.6907028507208208</v>
       </c>
       <c r="H108">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="1">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="B109" t="s">
         <v>13</v>
       </c>
       <c r="C109">
-        <v>55.28054997487197</v>
+        <v>54.47755813049488</v>
       </c>
       <c r="D109">
-        <v>23.00160891539877</v>
+        <v>22.0083816089626</v>
       </c>
       <c r="E109">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="F109">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="G109">
-        <v>0.7139885317003913</v>
+        <v>0.6220895940829376</v>
       </c>
       <c r="H109">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="1">
-        <v>46168</v>
+        <v>46161</v>
       </c>
       <c r="B110" t="s">
         <v>13</v>
       </c>
       <c r="C110">
-        <v>58.75156728873073</v>
+        <v>52.6278781150669</v>
       </c>
       <c r="D110">
-        <v>24.84249654093248</v>
+        <v>21.5357353870778</v>
       </c>
       <c r="E110">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="F110">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="G110">
-        <v>0.8184872182632257</v>
+        <v>0.5845134636435627</v>
       </c>
       <c r="H110">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="1">
-        <v>46169</v>
+        <v>46162</v>
       </c>
       <c r="B111" t="s">
         <v>13</v>
       </c>
       <c r="C111">
-        <v>57.86771234337395</v>
+        <v>54.91583234840245</v>
       </c>
       <c r="D111">
-        <v>24.21066615243091</v>
+        <v>22.38321645985006</v>
       </c>
       <c r="E111">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="F111">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="G111">
-        <v>0.798997241708943</v>
+        <v>0.6596976539194066</v>
       </c>
       <c r="H111">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="1">
-        <v>46170</v>
+        <v>46163</v>
       </c>
       <c r="B112" t="s">
         <v>13</v>
       </c>
       <c r="C112">
-        <v>58.18666682631797</v>
+        <v>53.91712298548793</v>
       </c>
       <c r="D112">
-        <v>24.09552344282839</v>
+        <v>22.73711181201267</v>
       </c>
       <c r="E112">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="F112">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="G112">
-        <v>0.8165093478664007</v>
+        <v>0.6737329602396263</v>
       </c>
       <c r="H112">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="1">
-        <v>46171</v>
+        <v>46164</v>
       </c>
       <c r="B113" t="s">
         <v>13</v>
       </c>
       <c r="C113">
-        <v>58.79256019733606</v>
+        <v>55.19651747515625</v>
       </c>
       <c r="D113">
-        <v>24.33854853448823</v>
+        <v>22.79462037330554</v>
       </c>
       <c r="E113">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F113">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G113">
-        <v>0.8152654642198496</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H113">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="1">
-        <v>46174</v>
+        <v>46167</v>
       </c>
       <c r="B114" t="s">
         <v>13</v>
       </c>
       <c r="C114">
-        <v>58.97156722185718</v>
+        <v>55.28054997487197</v>
       </c>
       <c r="D114">
-        <v>24.48296361348067</v>
+        <v>23.00160891539877</v>
       </c>
       <c r="E114">
-        <v>0.9990000000000001</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="F114">
-        <v>0.9990000000000001</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="G114">
-        <v>0.8243563865851753</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H114">
-        <v>0.9990000000000001</v>
+        <v>0.9989000000000001</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="1">
-        <v>46175</v>
+        <v>46168</v>
       </c>
       <c r="B115" t="s">
         <v>13</v>
       </c>
       <c r="C115">
-        <v>61.6542902214027</v>
+        <v>58.75156728873073</v>
       </c>
       <c r="D115">
-        <v>25.06517348653028</v>
+        <v>24.84249654093248</v>
       </c>
       <c r="E115">
-        <v>0.9988</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="F115">
-        <v>0.9988</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="G115">
-        <v>0.9299077697948877</v>
+        <v>0.8184872182632257</v>
       </c>
       <c r="H115">
-        <v>0.9988</v>
+        <v>0.9989000000000001</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="1">
-        <v>46176</v>
+        <v>46169</v>
       </c>
       <c r="B116" t="s">
         <v>13</v>
       </c>
       <c r="C116">
-        <v>63.0681947750049</v>
+        <v>57.86771234337395</v>
       </c>
       <c r="D116">
-        <v>25.58770976382014</v>
+        <v>24.21066615243091</v>
       </c>
       <c r="E116">
-        <v>0.9988000000000002</v>
+        <v>0.9986999999999999</v>
       </c>
       <c r="F116">
-        <v>0.9988000000000002</v>
+        <v>0.9986999999999999</v>
       </c>
       <c r="G116">
-        <v>0.9639112148600193</v>
+        <v>0.798997241708943</v>
       </c>
       <c r="H116">
-        <v>0.9988000000000002</v>
+        <v>0.9986999999999999</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="1">
-        <v>46177</v>
+        <v>46170</v>
       </c>
       <c r="B117" t="s">
         <v>13</v>
       </c>
       <c r="C117">
-        <v>61.53154955456358</v>
+        <v>58.18666682631797</v>
       </c>
       <c r="D117">
-        <v>24.75810538712983</v>
+        <v>24.09552344282839</v>
       </c>
       <c r="E117">
         <v>0.9991</v>
@@ -3439,7 +3439,7 @@
         <v>0.9991</v>
       </c>
       <c r="G117">
-        <v>0.9225710173552821</v>
+        <v>0.8165093478664007</v>
       </c>
       <c r="H117">
         <v>0.9991</v>
@@ -3447,874 +3447,874 @@
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="1">
-        <v>46178</v>
+        <v>46171</v>
       </c>
       <c r="B118" t="s">
         <v>13</v>
       </c>
       <c r="C118">
-        <v>55.42493637343647</v>
+        <v>58.79256019733606</v>
       </c>
       <c r="D118">
-        <v>22.47054621698377</v>
+        <v>24.33854853448823</v>
       </c>
       <c r="E118">
-        <v>0.9987</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="F118">
-        <v>0.9987</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="G118">
-        <v>0.7217717116249776</v>
+        <v>0.8152654642198496</v>
       </c>
       <c r="H118">
-        <v>0.9987</v>
+        <v>0.9989999999999999</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="1">
-        <v>46182</v>
+        <v>46174</v>
       </c>
       <c r="B119" t="s">
         <v>13</v>
       </c>
       <c r="C119">
-        <v>57.84835101034041</v>
+        <v>58.97156722185718</v>
       </c>
       <c r="D119">
-        <v>23.24662656171655</v>
+        <v>24.48296361348067</v>
       </c>
       <c r="E119">
-        <v>0.999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F119">
-        <v>0.999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G119">
-        <v>0.7931280733869936</v>
+        <v>0.8243563865851753</v>
       </c>
       <c r="H119">
-        <v>0.999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="1">
-        <v>46153</v>
+        <v>46175</v>
       </c>
       <c r="B120" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C120">
-        <v>35.78646526282436</v>
+        <v>61.6542902214027</v>
       </c>
       <c r="D120">
-        <v>18.96635091925032</v>
+        <v>25.06517348653028</v>
       </c>
       <c r="E120">
-        <v>0.9996491399999999</v>
+        <v>0.9988</v>
       </c>
       <c r="F120">
-        <v>0.9996491399999999</v>
+        <v>0.9988</v>
       </c>
       <c r="G120">
-        <v>0.2240600969213613</v>
+        <v>0.9299077697948877</v>
       </c>
       <c r="H120">
-        <v>0.9985614899999999</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="1">
-        <v>46154</v>
+        <v>46176</v>
       </c>
       <c r="B121" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C121">
-        <v>35.71584102184062</v>
+        <v>63.0681947750049</v>
       </c>
       <c r="D121">
-        <v>18.62432950231353</v>
+        <v>25.58770976382014</v>
       </c>
       <c r="E121">
-        <v>0.99965481</v>
+        <v>0.9988000000000002</v>
       </c>
       <c r="F121">
-        <v>0.99965481</v>
+        <v>0.9988000000000002</v>
       </c>
       <c r="G121">
-        <v>0.2104844827747143</v>
+        <v>0.9639112148600193</v>
       </c>
       <c r="H121">
-        <v>0.9985622199999999</v>
+        <v>0.9988000000000002</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="1">
-        <v>46155</v>
+        <v>46177</v>
       </c>
       <c r="B122" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C122">
-        <v>35.95182028203252</v>
+        <v>61.53154955456358</v>
       </c>
       <c r="D122">
-        <v>18.95670796791552</v>
+        <v>24.75810538712983</v>
       </c>
       <c r="E122">
-        <v>0.9996515200000001</v>
+        <v>0.9991</v>
       </c>
       <c r="F122">
-        <v>0.9996515200000001</v>
+        <v>0.9991</v>
       </c>
       <c r="G122">
-        <v>0.2259035693959275</v>
+        <v>0.9225710173552821</v>
       </c>
       <c r="H122">
-        <v>0.99855193</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="1">
-        <v>46156</v>
+        <v>46178</v>
       </c>
       <c r="B123" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C123">
-        <v>36.14451597805883</v>
+        <v>55.42493637343647</v>
       </c>
       <c r="D123">
-        <v>18.86297660538653</v>
+        <v>22.47054621698377</v>
       </c>
       <c r="E123">
-        <v>0.9996563399999999</v>
+        <v>0.9987</v>
       </c>
       <c r="F123">
-        <v>0.9996563399999999</v>
+        <v>0.9987</v>
       </c>
       <c r="G123">
-        <v>0.2362110061840785</v>
+        <v>0.7217717116249776</v>
       </c>
       <c r="H123">
-        <v>0.99857265</v>
+        <v>0.9987</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="1">
-        <v>46157</v>
+        <v>46182</v>
       </c>
       <c r="B124" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C124">
-        <v>35.32805803135546</v>
+        <v>57.84835101034041</v>
       </c>
       <c r="D124">
-        <v>18.35643242381478</v>
+        <v>23.24662656171655</v>
       </c>
       <c r="E124">
-        <v>0.9997415800000001</v>
+        <v>0.999</v>
       </c>
       <c r="F124">
-        <v>0.9997415800000001</v>
+        <v>0.999</v>
       </c>
       <c r="G124">
-        <v>0.2023559161375383</v>
+        <v>0.7931280733869936</v>
       </c>
       <c r="H124">
-        <v>0.9986639900000002</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="1">
-        <v>46160</v>
+        <v>46183</v>
       </c>
       <c r="B125" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C125">
-        <v>34.83995455757461</v>
+        <v>55.28729760663236</v>
       </c>
       <c r="D125">
-        <v>18.02301281718857</v>
+        <v>22.10409273362112</v>
       </c>
       <c r="E125">
-        <v>0.9996851299999999</v>
+        <v>0.9987999999999999</v>
       </c>
       <c r="F125">
-        <v>0.9996851299999999</v>
+        <v>0.9987999999999999</v>
       </c>
       <c r="G125">
-        <v>0.1850932291737926</v>
+        <v>0.7273219753588771</v>
       </c>
       <c r="H125">
-        <v>0.99857724</v>
+        <v>0.9987999999999999</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B126" t="s">
         <v>14</v>
       </c>
       <c r="C126">
-        <v>34.45479308705605</v>
+        <v>35.78646526282436</v>
       </c>
       <c r="D126">
-        <v>18.09576834566068</v>
+        <v>18.96635091925032</v>
       </c>
       <c r="E126">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="F126">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="G126">
-        <v>0.1784731209386736</v>
+        <v>0.2240600969213613</v>
       </c>
       <c r="H126">
-        <v>0.9985337599999999</v>
+        <v>0.9985614899999999</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B127" t="s">
         <v>14</v>
       </c>
       <c r="C127">
-        <v>34.96336277390787</v>
+        <v>35.71584102184062</v>
       </c>
       <c r="D127">
-        <v>18.34938420029253</v>
+        <v>18.62432950231353</v>
       </c>
       <c r="E127">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="F127">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="G127">
-        <v>0.2009313391215752</v>
+        <v>0.2104844827747143</v>
       </c>
       <c r="H127">
-        <v>0.99848777</v>
+        <v>0.9985622199999999</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B128" t="s">
         <v>14</v>
       </c>
       <c r="C128">
-        <v>34.44616924817128</v>
+        <v>35.95182028203252</v>
       </c>
       <c r="D128">
-        <v>18.60085625074367</v>
+        <v>18.95670796791552</v>
       </c>
       <c r="E128">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="F128">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="G128">
-        <v>0.2124957180214682</v>
+        <v>0.2259035693959275</v>
       </c>
       <c r="H128">
-        <v>0.9985085200000001</v>
+        <v>0.99855193</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="1">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="B129" t="s">
         <v>14</v>
       </c>
       <c r="C129">
-        <v>34.62137220937314</v>
+        <v>36.14451597805883</v>
       </c>
       <c r="D129">
-        <v>18.28780484745949</v>
+        <v>18.86297660538653</v>
       </c>
       <c r="E129">
-        <v>0.9996106299999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="F129">
-        <v>0.9996106299999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="G129">
-        <v>0.2145907067863493</v>
+        <v>0.2362110061840785</v>
       </c>
       <c r="H129">
-        <v>0.9932939299999999</v>
+        <v>0.99857265</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" s="1">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="B130" t="s">
         <v>14</v>
       </c>
       <c r="C130">
-        <v>34.6540695486741</v>
+        <v>35.32805803135546</v>
       </c>
       <c r="D130">
-        <v>18.36409048915342</v>
+        <v>18.35643242381478</v>
       </c>
       <c r="E130">
-        <v>0.9995448900000001</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="F130">
-        <v>0.9995448900000001</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="G130">
-        <v>0.2145907067863493</v>
+        <v>0.2023559161375383</v>
       </c>
       <c r="H130">
-        <v>0.9984302600000001</v>
+        <v>0.9986639900000002</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" s="1">
-        <v>46168</v>
+        <v>46160</v>
       </c>
       <c r="B131" t="s">
         <v>14</v>
       </c>
       <c r="C131">
-        <v>35.4820130509417</v>
+        <v>34.83995455757461</v>
       </c>
       <c r="D131">
-        <v>19.20292041814603</v>
+        <v>18.02301281718857</v>
       </c>
       <c r="E131">
-        <v>0.9995448900000001</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="F131">
-        <v>0.9995448900000001</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="G131">
-        <v>0.2553172934903569</v>
+        <v>0.1850932291737926</v>
       </c>
       <c r="H131">
-        <v>0.9984302600000001</v>
+        <v>0.99857724</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="1">
-        <v>46169</v>
+        <v>46161</v>
       </c>
       <c r="B132" t="s">
         <v>14</v>
       </c>
       <c r="C132">
-        <v>35.71913468603401</v>
+        <v>34.45479308705605</v>
       </c>
       <c r="D132">
-        <v>18.96318693998171</v>
+        <v>18.09576834566068</v>
       </c>
       <c r="E132">
-        <v>0.99955466</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="F132">
-        <v>0.99955466</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="G132">
-        <v>0.2536413280520453</v>
+        <v>0.1784731209386736</v>
       </c>
       <c r="H132">
-        <v>0.9984700500000001</v>
+        <v>0.9985337599999999</v>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="1">
-        <v>46170</v>
+        <v>46162</v>
       </c>
       <c r="B133" t="s">
         <v>14</v>
       </c>
       <c r="C133">
-        <v>35.76226417354731</v>
+        <v>34.96336277390787</v>
       </c>
       <c r="D133">
-        <v>18.89050847207122</v>
+        <v>18.34938420029253</v>
       </c>
       <c r="E133">
-        <v>0.9995525399999999</v>
+        <v>0.99963413</v>
       </c>
       <c r="F133">
-        <v>0.9995525399999999</v>
+        <v>0.99963413</v>
       </c>
       <c r="G133">
-        <v>0.2580826940041561</v>
+        <v>0.2009313391215752</v>
       </c>
       <c r="H133">
-        <v>0.99847732</v>
+        <v>0.99848777</v>
       </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="1">
-        <v>46171</v>
+        <v>46163</v>
       </c>
       <c r="B134" t="s">
         <v>14</v>
       </c>
       <c r="C134">
-        <v>35.84309020154227</v>
+        <v>34.44616924817128</v>
       </c>
       <c r="D134">
-        <v>19.06511612333149</v>
+        <v>18.60085625074367</v>
       </c>
       <c r="E134">
-        <v>0.9995533299999999</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="F134">
-        <v>0.9995533299999999</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="G134">
-        <v>0.2619374017254759</v>
+        <v>0.2124957180214682</v>
       </c>
       <c r="H134">
-        <v>0.99849382</v>
+        <v>0.9985085200000001</v>
       </c>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="1">
-        <v>46174</v>
+        <v>46164</v>
       </c>
       <c r="B135" t="s">
         <v>14</v>
       </c>
       <c r="C135">
-        <v>36.27022125574057</v>
+        <v>34.62137220937314</v>
       </c>
       <c r="D135">
-        <v>19.32711369104533</v>
+        <v>18.28780484745949</v>
       </c>
       <c r="E135">
-        <v>0.9995550400000001</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="F135">
-        <v>0.9995550400000001</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="G135">
-        <v>0.2764348160433892</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H135">
-        <v>0.9985177199999999</v>
+        <v>0.9932939299999999</v>
       </c>
     </row>
     <row r="136" spans="1:8">
       <c r="A136" s="1">
-        <v>46175</v>
+        <v>46167</v>
       </c>
       <c r="B136" t="s">
         <v>14</v>
       </c>
       <c r="C136">
-        <v>36.57133692946976</v>
+        <v>34.6540695486741</v>
       </c>
       <c r="D136">
-        <v>19.33857330565742</v>
+        <v>18.36409048915342</v>
       </c>
       <c r="E136">
-        <v>0.9994989200000002</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="F136">
-        <v>0.9994989200000002</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="G136">
-        <v>0.2931947261624381</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H136">
-        <v>0.9984577800000001</v>
+        <v>0.9984302600000001</v>
       </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="1">
-        <v>46176</v>
+        <v>46168</v>
       </c>
       <c r="B137" t="s">
         <v>14</v>
       </c>
       <c r="C137">
-        <v>36.8289666508657</v>
+        <v>35.4820130509417</v>
       </c>
       <c r="D137">
-        <v>19.43137154505686</v>
+        <v>19.20292041814603</v>
       </c>
       <c r="E137">
-        <v>0.9994838199999998</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="F137">
-        <v>0.9994838199999998</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="G137">
-        <v>0.2996471994933361</v>
+        <v>0.2553172934903569</v>
       </c>
       <c r="H137">
-        <v>0.9984549499999998</v>
+        <v>0.9984302600000001</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="1">
-        <v>46177</v>
+        <v>46169</v>
       </c>
       <c r="B138" t="s">
         <v>14</v>
       </c>
       <c r="C138">
-        <v>36.76760036565858</v>
+        <v>35.71913468603401</v>
       </c>
       <c r="D138">
-        <v>18.98774474764188</v>
+        <v>18.96318693998171</v>
       </c>
       <c r="E138">
-        <v>0.99948384</v>
+        <v>0.99955466</v>
       </c>
       <c r="F138">
-        <v>0.99948384</v>
+        <v>0.99955466</v>
       </c>
       <c r="G138">
-        <v>0.2807085470912787</v>
+        <v>0.2536413280520453</v>
       </c>
       <c r="H138">
-        <v>0.9984696899999999</v>
+        <v>0.9984700500000001</v>
       </c>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="1">
-        <v>46178</v>
+        <v>46170</v>
       </c>
       <c r="B139" t="s">
         <v>14</v>
       </c>
       <c r="C139">
-        <v>34.71533981972338</v>
+        <v>35.76226417354731</v>
       </c>
       <c r="D139">
-        <v>17.87291658642534</v>
+        <v>18.89050847207122</v>
       </c>
       <c r="E139">
-        <v>0.9994584900000001</v>
+        <v>0.9995525399999999</v>
       </c>
       <c r="F139">
-        <v>0.9994584900000001</v>
+        <v>0.9995525399999999</v>
       </c>
       <c r="G139">
-        <v>0.2090599057587512</v>
+        <v>0.2580826940041561</v>
       </c>
       <c r="H139">
-        <v>0.9984184600000001</v>
+        <v>0.99847732</v>
       </c>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="1">
-        <v>46182</v>
+        <v>46171</v>
       </c>
       <c r="B140" t="s">
         <v>14</v>
       </c>
       <c r="C140">
-        <v>35.03764279648938</v>
+        <v>35.84309020154227</v>
       </c>
       <c r="D140">
-        <v>18.26945792236365</v>
+        <v>19.06511612333149</v>
       </c>
       <c r="E140">
-        <v>0.9994212399999999</v>
+        <v>0.9995533299999999</v>
       </c>
       <c r="F140">
-        <v>0.9994212399999999</v>
+        <v>0.9995533299999999</v>
       </c>
       <c r="G140">
-        <v>0.2361271247979846</v>
+        <v>0.2619374017254759</v>
       </c>
       <c r="H140">
-        <v>0.99833116</v>
+        <v>0.99849382</v>
       </c>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="1">
-        <v>46153</v>
+        <v>46174</v>
       </c>
       <c r="B141" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C141">
-        <v>28.12253390077671</v>
+        <v>36.27022125574057</v>
       </c>
       <c r="D141">
-        <v>23.58699683751922</v>
+        <v>19.32711369104533</v>
       </c>
       <c r="E141">
-        <v>0.9997295369999999</v>
+        <v>0.9995550400000001</v>
       </c>
       <c r="F141">
-        <v>0.9997295369999999</v>
+        <v>0.9995550400000001</v>
       </c>
       <c r="G141">
-        <v>0.03368732240295347</v>
+        <v>0.2764348160433892</v>
       </c>
       <c r="H141">
-        <v>0.9997295369999999</v>
+        <v>0.9985177199999999</v>
       </c>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="1">
-        <v>46154</v>
+        <v>46175</v>
       </c>
       <c r="B142" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C142">
-        <v>28.17715727830483</v>
+        <v>36.57133692946976</v>
       </c>
       <c r="D142">
-        <v>23.63894513078866</v>
+        <v>19.33857330565742</v>
       </c>
       <c r="E142">
-        <v>1.000319473</v>
+        <v>0.9994989200000002</v>
       </c>
       <c r="F142">
-        <v>1.000319473</v>
+        <v>0.9994989200000002</v>
       </c>
       <c r="G142">
-        <v>0.03515547182056333</v>
+        <v>0.2931947261624381</v>
       </c>
       <c r="H142">
-        <v>1.000319473</v>
+        <v>0.9984577800000001</v>
       </c>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="1">
-        <v>46155</v>
+        <v>46176</v>
       </c>
       <c r="B143" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C143">
-        <v>28.59002627414054</v>
+        <v>36.8289666508657</v>
       </c>
       <c r="D143">
-        <v>23.96230704059692</v>
+        <v>19.43137154505686</v>
       </c>
       <c r="E143">
-        <v>0.9999999989999999</v>
+        <v>0.9994838199999998</v>
       </c>
       <c r="F143">
-        <v>0.9999999989999999</v>
+        <v>0.9994838199999998</v>
       </c>
       <c r="G143">
-        <v>0.05179637495949674</v>
+        <v>0.2996471994933361</v>
       </c>
       <c r="H143">
-        <v>0.9999999989999999</v>
+        <v>0.9984549499999998</v>
       </c>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="1">
-        <v>46156</v>
+        <v>46177</v>
       </c>
       <c r="B144" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C144">
-        <v>28.56217859389523</v>
+        <v>36.76760036565858</v>
       </c>
       <c r="D144">
-        <v>23.9411987302529</v>
+        <v>18.98774474764188</v>
       </c>
       <c r="E144">
-        <v>1</v>
+        <v>0.99948384</v>
       </c>
       <c r="F144">
-        <v>1</v>
+        <v>0.99948384</v>
       </c>
       <c r="G144">
-        <v>0.04837024516756849</v>
+        <v>0.2807085470912787</v>
       </c>
       <c r="H144">
-        <v>1</v>
+        <v>0.9984696899999999</v>
       </c>
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="1">
-        <v>46157</v>
+        <v>46178</v>
       </c>
       <c r="B145" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C145">
-        <v>28.57618675936338</v>
+        <v>34.71533981972338</v>
       </c>
       <c r="D145">
-        <v>23.9576220541054</v>
+        <v>17.87291658642534</v>
       </c>
       <c r="E145">
-        <v>0.999503249</v>
+        <v>0.9994584900000001</v>
       </c>
       <c r="F145">
-        <v>0.999503249</v>
+        <v>0.9994584900000001</v>
       </c>
       <c r="G145">
-        <v>0.04983868243960732</v>
+        <v>0.2090599057587512</v>
       </c>
       <c r="H145">
-        <v>0.999503249</v>
+        <v>0.9984184600000001</v>
       </c>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="1">
-        <v>46160</v>
+        <v>46182</v>
       </c>
       <c r="B146" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C146">
-        <v>28.68951918518517</v>
+        <v>35.03764279648938</v>
       </c>
       <c r="D146">
-        <v>24.06134728453882</v>
+        <v>18.26945792236365</v>
       </c>
       <c r="E146">
-        <v>0.999503249</v>
+        <v>0.9994212399999999</v>
       </c>
       <c r="F146">
-        <v>0.999503249</v>
+        <v>0.9994212399999999</v>
       </c>
       <c r="G146">
-        <v>0.04983868243960732</v>
+        <v>0.2361271247979846</v>
       </c>
       <c r="H146">
-        <v>0.999503249</v>
+        <v>0.99833116</v>
       </c>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="1">
-        <v>46161</v>
+        <v>46183</v>
       </c>
       <c r="B147" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C147">
-        <v>28.31167386654059</v>
+        <v>34.21862503455022</v>
       </c>
       <c r="D147">
-        <v>23.75157719455474</v>
+        <v>17.67576313213109</v>
       </c>
       <c r="E147">
-        <v>1.000177331</v>
+        <v>0.9991916599999998</v>
       </c>
       <c r="F147">
-        <v>1.000177331</v>
+        <v>0.9991916599999998</v>
       </c>
       <c r="G147">
-        <v>0.04053938625111919</v>
+        <v>0.2040318815758499</v>
       </c>
       <c r="H147">
-        <v>1.000177331</v>
+        <v>0.99808951</v>
       </c>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="1">
-        <v>46162</v>
+        <v>46153</v>
       </c>
       <c r="B148" t="s">
         <v>15</v>
       </c>
       <c r="C148">
-        <v>28.57911382310097</v>
+        <v>28.12253390077671</v>
       </c>
       <c r="D148">
-        <v>23.89431741541233</v>
+        <v>23.58699683751922</v>
       </c>
       <c r="E148">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="F148">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="G148">
-        <v>0.04690190590044785</v>
+        <v>0.03368732240295347</v>
       </c>
       <c r="H148">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="1">
-        <v>46163</v>
+        <v>46154</v>
       </c>
       <c r="B149" t="s">
         <v>15</v>
       </c>
       <c r="C149">
-        <v>28.55785065378643</v>
+        <v>28.17715727830483</v>
       </c>
       <c r="D149">
-        <v>24.04274714970193</v>
+        <v>23.63894513078866</v>
       </c>
       <c r="E149">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="F149">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="G149">
-        <v>0.05228572319419666</v>
+        <v>0.03515547182056333</v>
       </c>
       <c r="H149">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" s="1">
-        <v>46164</v>
+        <v>46155</v>
       </c>
       <c r="B150" t="s">
         <v>15</v>
       </c>
       <c r="C150">
-        <v>28.50194638163107</v>
+        <v>28.59002627414054</v>
       </c>
       <c r="D150">
-        <v>23.99272397156045</v>
+        <v>23.96230704059692</v>
       </c>
       <c r="E150">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F150">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G150">
-        <v>0.04934923597154284</v>
+        <v>0.05179637495949674</v>
       </c>
       <c r="H150">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="1">
-        <v>46167</v>
+        <v>46156</v>
       </c>
       <c r="B151" t="s">
         <v>15</v>
       </c>
       <c r="C151">
-        <v>28.55106858744498</v>
+        <v>28.56217859389523</v>
       </c>
       <c r="D151">
-        <v>23.9768329565351</v>
+        <v>23.9411987302529</v>
       </c>
       <c r="E151">
         <v>1</v>
@@ -4323,7 +4323,7 @@
         <v>1</v>
       </c>
       <c r="G151">
-        <v>0.05571185335164408</v>
+        <v>0.04837024516756849</v>
       </c>
       <c r="H151">
         <v>1</v>
@@ -4331,808 +4331,1042 @@
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="1">
-        <v>46168</v>
+        <v>46157</v>
       </c>
       <c r="B152" t="s">
         <v>15</v>
       </c>
       <c r="C152">
-        <v>28.54681541456266</v>
+        <v>28.57618675936338</v>
       </c>
       <c r="D152">
-        <v>23.97386168967948</v>
+        <v>23.9576220541054</v>
       </c>
       <c r="E152">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="F152">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="G152">
-        <v>0.04837034303541388</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H152">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" s="1">
-        <v>46169</v>
+        <v>46160</v>
       </c>
       <c r="B153" t="s">
         <v>15</v>
       </c>
       <c r="C153">
-        <v>28.83672936868491</v>
+        <v>28.68951918518517</v>
       </c>
       <c r="D153">
-        <v>24.203511281145</v>
+        <v>24.06134728453882</v>
       </c>
       <c r="E153">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="F153">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="G153">
-        <v>0.05962723282507953</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H153">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" s="1">
-        <v>46170</v>
+        <v>46161</v>
       </c>
       <c r="B154" t="s">
         <v>15</v>
       </c>
       <c r="C154">
-        <v>28.88109630394224</v>
+        <v>28.31167386654059</v>
       </c>
       <c r="D154">
-        <v>24.34085451035401</v>
+        <v>23.75157719455474</v>
       </c>
       <c r="E154">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
       <c r="F154">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
       <c r="G154">
-        <v>0.06647938938594877</v>
+        <v>0.04053938625111919</v>
       </c>
       <c r="H154">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" s="1">
-        <v>46171</v>
+        <v>46162</v>
       </c>
       <c r="B155" t="s">
         <v>15</v>
       </c>
       <c r="C155">
-        <v>28.92588622185229</v>
+        <v>28.57911382310097</v>
       </c>
       <c r="D155">
-        <v>24.37463012178961</v>
+        <v>23.89431741541233</v>
       </c>
       <c r="E155">
-        <v>0.9999999989999999</v>
+        <v>0.999503734</v>
       </c>
       <c r="F155">
-        <v>0.9999999989999999</v>
+        <v>0.999503734</v>
       </c>
       <c r="G155">
-        <v>0.0669687424559624</v>
+        <v>0.04690190590044785</v>
       </c>
       <c r="H155">
-        <v>0.9999999989999999</v>
+        <v>0.999503734</v>
       </c>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" s="1">
-        <v>46174</v>
+        <v>46163</v>
       </c>
       <c r="B156" t="s">
         <v>15</v>
       </c>
       <c r="C156">
-        <v>28.479823472488</v>
+        <v>28.55785065378643</v>
       </c>
       <c r="D156">
-        <v>23.940843604634</v>
+        <v>24.04274714970193</v>
       </c>
       <c r="E156">
-        <v>0.9999999999999999</v>
+        <v>1.000229282</v>
       </c>
       <c r="F156">
-        <v>0.9999999999999999</v>
+        <v>1.000229282</v>
       </c>
       <c r="G156">
-        <v>0.05385076946675693</v>
+        <v>0.05228572319419666</v>
       </c>
       <c r="H156">
-        <v>0.9999999999999999</v>
+        <v>1.000229282</v>
       </c>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" s="1">
-        <v>46175</v>
+        <v>46164</v>
       </c>
       <c r="B157" t="s">
         <v>15</v>
       </c>
       <c r="C157">
-        <v>28.11501250979268</v>
+        <v>28.50194638163107</v>
       </c>
       <c r="D157">
-        <v>23.53470929078268</v>
+        <v>23.99272397156045</v>
       </c>
       <c r="E157">
-        <v>0.9999999989999999</v>
+        <v>1</v>
       </c>
       <c r="F157">
-        <v>0.9999999989999999</v>
+        <v>1</v>
       </c>
       <c r="G157">
-        <v>0.03476107722835287</v>
+        <v>0.04934923597154284</v>
       </c>
       <c r="H157">
-        <v>0.9999999989999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="1">
-        <v>46176</v>
+        <v>46167</v>
       </c>
       <c r="B158" t="s">
         <v>15</v>
       </c>
       <c r="C158">
-        <v>28.0115884668485</v>
+        <v>28.55106858744498</v>
       </c>
       <c r="D158">
-        <v>23.38620815625822</v>
+        <v>23.9768329565351</v>
       </c>
       <c r="E158">
-        <v>0.9993115890000001</v>
+        <v>1</v>
       </c>
       <c r="F158">
-        <v>0.9993115890000001</v>
+        <v>1</v>
       </c>
       <c r="G158">
-        <v>0.02105569185214828</v>
+        <v>0.05571185335164408</v>
       </c>
       <c r="H158">
-        <v>0.9993115890000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" s="1">
-        <v>46177</v>
+        <v>46168</v>
       </c>
       <c r="B159" t="s">
         <v>15</v>
       </c>
       <c r="C159">
-        <v>28.38208530418455</v>
+        <v>28.54681541456266</v>
       </c>
       <c r="D159">
-        <v>23.57230416238753</v>
+        <v>23.97386168967948</v>
       </c>
       <c r="E159">
-        <v>1.000774061</v>
+        <v>1</v>
       </c>
       <c r="F159">
-        <v>1.000774061</v>
+        <v>1</v>
       </c>
       <c r="G159">
-        <v>0.03133473088430172</v>
+        <v>0.04837034303541388</v>
       </c>
       <c r="H159">
-        <v>1.000774061</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:8">
       <c r="A160" s="1">
-        <v>46178</v>
+        <v>46169</v>
       </c>
       <c r="B160" t="s">
         <v>15</v>
       </c>
       <c r="C160">
-        <v>27.67379569436247</v>
+        <v>28.83672936868491</v>
       </c>
       <c r="D160">
-        <v>23.02577481291606</v>
+        <v>24.203511281145</v>
       </c>
       <c r="E160">
-        <v>1.000106056</v>
+        <v>1</v>
       </c>
       <c r="F160">
-        <v>1.000106056</v>
+        <v>1</v>
       </c>
       <c r="G160">
-        <v>0.01248973263108488</v>
+        <v>0.05962723282507953</v>
       </c>
       <c r="H160">
-        <v>1.000106056</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:8">
       <c r="A161" s="1">
-        <v>46182</v>
+        <v>46170</v>
       </c>
       <c r="B161" t="s">
         <v>15</v>
       </c>
       <c r="C161">
-        <v>27.45237632057606</v>
+        <v>28.88109630394224</v>
       </c>
       <c r="D161">
-        <v>22.58943922039682</v>
+        <v>24.34085451035401</v>
       </c>
       <c r="E161">
-        <v>0.9999738310000001</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F161">
-        <v>0.9999738310000001</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G161">
-        <v>-0.01076068709534461</v>
+        <v>0.06647938938594877</v>
       </c>
       <c r="H161">
-        <v>0.9999738310000001</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" s="1">
-        <v>46153</v>
+        <v>46171</v>
       </c>
       <c r="B162" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C162">
-        <v>40.68830633303975</v>
+        <v>28.92588622185229</v>
       </c>
       <c r="D162">
-        <v>21.50431773660198</v>
+        <v>24.37463012178961</v>
       </c>
       <c r="E162">
-        <v>0.99909852</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F162">
-        <v>0.99909852</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G162">
-        <v>0.2342423866086769</v>
+        <v>0.0669687424559624</v>
       </c>
       <c r="H162">
-        <v>0.9974930900000001</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" s="1">
-        <v>46154</v>
+        <v>46174</v>
       </c>
       <c r="B163" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C163">
-        <v>40.32854894972581</v>
+        <v>28.479823472488</v>
       </c>
       <c r="D163">
-        <v>21.09133998298594</v>
+        <v>23.940843604634</v>
       </c>
       <c r="E163">
-        <v>0.9990972199999999</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F163">
-        <v>0.9990972199999999</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G163">
-        <v>0.2156468205051487</v>
+        <v>0.05385076946675693</v>
       </c>
       <c r="H163">
-        <v>0.99752223</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" s="1">
-        <v>46155</v>
+        <v>46175</v>
       </c>
       <c r="B164" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C164">
-        <v>40.47987921095815</v>
+        <v>28.11501250979268</v>
       </c>
       <c r="D164">
-        <v>21.35995364434454</v>
+        <v>23.53470929078268</v>
       </c>
       <c r="E164">
-        <v>0.9991780100000001</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F164">
-        <v>0.9991780100000001</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G164">
-        <v>0.2270956128473374</v>
+        <v>0.03476107722835287</v>
       </c>
       <c r="H164">
-        <v>0.9975825700000001</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="165" spans="1:8">
       <c r="A165" s="1">
-        <v>46156</v>
+        <v>46176</v>
       </c>
       <c r="B165" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C165">
-        <v>41.20436574895244</v>
+        <v>28.0115884668485</v>
       </c>
       <c r="D165">
-        <v>21.48149674387778</v>
+        <v>23.38620815625822</v>
       </c>
       <c r="E165">
-        <v>0.9991793299999999</v>
+        <v>0.9993115890000001</v>
       </c>
       <c r="F165">
-        <v>0.9991793299999999</v>
+        <v>0.9993115890000001</v>
       </c>
       <c r="G165">
-        <v>0.2454829228401052</v>
+        <v>0.02105569185214828</v>
       </c>
       <c r="H165">
-        <v>0.99754722</v>
+        <v>0.9993115890000001</v>
       </c>
     </row>
     <row r="166" spans="1:8">
       <c r="A166" s="1">
-        <v>46157</v>
+        <v>46177</v>
       </c>
       <c r="B166" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C166">
-        <v>40.80613062958688</v>
+        <v>28.38208530418455</v>
       </c>
       <c r="D166">
-        <v>21.08912555803936</v>
+        <v>23.57230416238753</v>
       </c>
       <c r="E166">
-        <v>0.9991790600000001</v>
+        <v>1.000774061</v>
       </c>
       <c r="F166">
-        <v>0.9991790600000001</v>
+        <v>1.000774061</v>
       </c>
       <c r="G166">
-        <v>0.2230017445022556</v>
+        <v>0.03133473088430172</v>
       </c>
       <c r="H166">
-        <v>0.9975824700000002</v>
+        <v>1.000774061</v>
       </c>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" s="1">
-        <v>46160</v>
+        <v>46178</v>
       </c>
       <c r="B167" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C167">
-        <v>40.11672876026724</v>
+        <v>27.67379569436247</v>
       </c>
       <c r="D167">
-        <v>20.79541439916316</v>
+        <v>23.02577481291606</v>
       </c>
       <c r="E167">
-        <v>0.999152</v>
+        <v>1.000106056</v>
       </c>
       <c r="F167">
-        <v>0.999152</v>
+        <v>1.000106056</v>
       </c>
       <c r="G167">
-        <v>0.2098184021536666</v>
+        <v>0.01248973263108488</v>
       </c>
       <c r="H167">
-        <v>0.9975007899999999</v>
+        <v>1.000106056</v>
       </c>
     </row>
     <row r="168" spans="1:8">
       <c r="A168" s="1">
-        <v>46161</v>
+        <v>46182</v>
       </c>
       <c r="B168" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C168">
-        <v>39.69086941528401</v>
+        <v>27.45237632057606</v>
       </c>
       <c r="D168">
-        <v>20.74924328599426</v>
+        <v>22.58943922039682</v>
       </c>
       <c r="E168">
-        <v>0.99914989</v>
+        <v>0.9999738310000001</v>
       </c>
       <c r="F168">
-        <v>0.99914989</v>
+        <v>0.9999738310000001</v>
       </c>
       <c r="G168">
-        <v>0.2020471776850241</v>
+        <v>-0.01076068709534461</v>
       </c>
       <c r="H168">
-        <v>0.9974417</v>
+        <v>0.9999738310000001</v>
       </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" s="1">
-        <v>46162</v>
+        <v>46183</v>
       </c>
       <c r="B169" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C169">
-        <v>40.37836787855562</v>
+        <v>26.87898580194432</v>
       </c>
       <c r="D169">
-        <v>21.11271132314188</v>
+        <v>22.24994492425726</v>
       </c>
       <c r="E169">
-        <v>0.99915058</v>
+        <v>1.000000001</v>
       </c>
       <c r="F169">
-        <v>0.99915058</v>
+        <v>1.000000001</v>
       </c>
       <c r="G169">
-        <v>0.2291077670847563</v>
+        <v>-0.02299778174457945</v>
       </c>
       <c r="H169">
-        <v>0.9974415600000001</v>
+        <v>1.000000001</v>
       </c>
     </row>
     <row r="170" spans="1:8">
       <c r="A170" s="1">
-        <v>46163</v>
+        <v>46153</v>
       </c>
       <c r="B170" t="s">
         <v>16</v>
       </c>
       <c r="C170">
-        <v>38.9123066967842</v>
+        <v>40.68830633303975</v>
       </c>
       <c r="D170">
-        <v>21.28910644207464</v>
+        <v>21.50431773660198</v>
       </c>
       <c r="E170">
-        <v>0.9989350699999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="F170">
-        <v>0.9989350699999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="G170">
-        <v>0.2392382040170877</v>
+        <v>0.2342423866086769</v>
       </c>
       <c r="H170">
-        <v>0.99726191</v>
+        <v>0.9974930900000001</v>
       </c>
     </row>
     <row r="171" spans="1:8">
       <c r="A171" s="1">
-        <v>46164</v>
+        <v>46154</v>
       </c>
       <c r="B171" t="s">
         <v>16</v>
       </c>
       <c r="C171">
-        <v>39.43913909150694</v>
+        <v>40.32854894972581</v>
       </c>
       <c r="D171">
-        <v>21.05297617141148</v>
+        <v>21.09133998298594</v>
       </c>
       <c r="E171">
-        <v>0.999144</v>
+        <v>0.9990972199999999</v>
       </c>
       <c r="F171">
-        <v>0.999144</v>
+        <v>0.9990972199999999</v>
       </c>
       <c r="G171">
-        <v>0.2516582935428642</v>
+        <v>0.2156468205051487</v>
       </c>
       <c r="H171">
-        <v>0.9974678400000001</v>
+        <v>0.99752223</v>
       </c>
     </row>
     <row r="172" spans="1:8">
       <c r="A172" s="1">
-        <v>46167</v>
+        <v>46155</v>
       </c>
       <c r="B172" t="s">
         <v>16</v>
       </c>
       <c r="C172">
-        <v>39.45782844313628</v>
+        <v>40.47987921095815</v>
       </c>
       <c r="D172">
-        <v>21.0518901572272</v>
+        <v>21.35995364434454</v>
       </c>
       <c r="E172">
-        <v>0.999144</v>
+        <v>0.9991780100000001</v>
       </c>
       <c r="F172">
-        <v>0.999144</v>
+        <v>0.9991780100000001</v>
       </c>
       <c r="G172">
-        <v>0.2516582935428642</v>
+        <v>0.2270956128473374</v>
       </c>
       <c r="H172">
-        <v>0.9974678400000001</v>
+        <v>0.9975825700000001</v>
       </c>
     </row>
     <row r="173" spans="1:8">
       <c r="A173" s="1">
-        <v>46168</v>
+        <v>46156</v>
       </c>
       <c r="B173" t="s">
         <v>16</v>
       </c>
       <c r="C173">
-        <v>40.20219297984542</v>
+        <v>41.20436574895244</v>
       </c>
       <c r="D173">
-        <v>21.93106024403281</v>
+        <v>21.48149674387778</v>
       </c>
       <c r="E173">
-        <v>0.9991421799999999</v>
+        <v>0.9991793299999999</v>
       </c>
       <c r="F173">
-        <v>0.9991421799999999</v>
+        <v>0.9991793299999999</v>
       </c>
       <c r="G173">
-        <v>0.2846167552893293</v>
+        <v>0.2454829228401052</v>
       </c>
       <c r="H173">
-        <v>0.9974609800000001</v>
+        <v>0.99754722</v>
       </c>
     </row>
     <row r="174" spans="1:8">
       <c r="A174" s="1">
-        <v>46169</v>
+        <v>46157</v>
       </c>
       <c r="B174" t="s">
         <v>16</v>
       </c>
       <c r="C174">
-        <v>40.34993865302093</v>
+        <v>40.80613062958688</v>
       </c>
       <c r="D174">
-        <v>21.65366031776487</v>
+        <v>21.08912555803936</v>
       </c>
       <c r="E174">
-        <v>0.9991434600000001</v>
+        <v>0.9991790600000001</v>
       </c>
       <c r="F174">
-        <v>0.9991434600000001</v>
+        <v>0.9991790600000001</v>
       </c>
       <c r="G174">
-        <v>0.2796902860011767</v>
+        <v>0.2230017445022556</v>
       </c>
       <c r="H174">
-        <v>0.9991434600000001</v>
+        <v>0.9975824700000002</v>
       </c>
     </row>
     <row r="175" spans="1:8">
       <c r="A175" s="1">
-        <v>46170</v>
+        <v>46160</v>
       </c>
       <c r="B175" t="s">
         <v>16</v>
       </c>
       <c r="C175">
-        <v>40.5850485390846</v>
+        <v>40.11672876026724</v>
       </c>
       <c r="D175">
-        <v>21.75450977746074</v>
+        <v>20.79541439916316</v>
       </c>
       <c r="E175">
-        <v>0.99914592</v>
+        <v>0.999152</v>
       </c>
       <c r="F175">
-        <v>0.99914592</v>
+        <v>0.999152</v>
       </c>
       <c r="G175">
-        <v>0.2964818481030536</v>
+        <v>0.2098184021536666</v>
       </c>
       <c r="H175">
-        <v>0.99914592</v>
+        <v>0.9975007899999999</v>
       </c>
     </row>
     <row r="176" spans="1:8">
       <c r="A176" s="1">
-        <v>46171</v>
+        <v>46161</v>
       </c>
       <c r="B176" t="s">
         <v>16</v>
       </c>
       <c r="C176">
-        <v>41.86785805184477</v>
+        <v>39.69086941528401</v>
       </c>
       <c r="D176">
-        <v>22.33589392797469</v>
+        <v>20.74924328599426</v>
       </c>
       <c r="E176">
-        <v>0.9991336999999999</v>
+        <v>0.99914989</v>
       </c>
       <c r="F176">
-        <v>0.9991336999999999</v>
+        <v>0.99914989</v>
       </c>
       <c r="G176">
-        <v>0.3254158954996882</v>
+        <v>0.2020471776850241</v>
       </c>
       <c r="H176">
-        <v>0.9991336999999999</v>
+        <v>0.9974417</v>
       </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177" s="1">
-        <v>46174</v>
+        <v>46162</v>
       </c>
       <c r="B177" t="s">
         <v>16</v>
       </c>
       <c r="C177">
-        <v>42.82932322850974</v>
+        <v>40.37836787855562</v>
       </c>
       <c r="D177">
-        <v>22.98998911430362</v>
+        <v>21.11271132314188</v>
       </c>
       <c r="E177">
-        <v>0.99914238</v>
+        <v>0.99915058</v>
       </c>
       <c r="F177">
-        <v>0.99914238</v>
+        <v>0.99915058</v>
       </c>
       <c r="G177">
-        <v>0.3583049032509023</v>
+        <v>0.2291077670847563</v>
       </c>
       <c r="H177">
-        <v>0.99914238</v>
+        <v>0.9974415600000001</v>
       </c>
     </row>
     <row r="178" spans="1:8">
       <c r="A178" s="1">
-        <v>46175</v>
+        <v>46163</v>
       </c>
       <c r="B178" t="s">
         <v>16</v>
       </c>
       <c r="C178">
-        <v>43.11872937189534</v>
+        <v>38.9123066967842</v>
       </c>
       <c r="D178">
-        <v>22.90628380907704</v>
+        <v>21.28910644207464</v>
       </c>
       <c r="E178">
-        <v>0.9990972800000002</v>
+        <v>0.9989350699999999</v>
       </c>
       <c r="F178">
-        <v>0.9990972800000002</v>
+        <v>0.9989350699999999</v>
       </c>
       <c r="G178">
-        <v>0.3753046155885469</v>
+        <v>0.2392382040170877</v>
       </c>
       <c r="H178">
-        <v>0.9990972800000002</v>
+        <v>0.99726191</v>
       </c>
     </row>
     <row r="179" spans="1:8">
       <c r="A179" s="1">
-        <v>46176</v>
+        <v>46164</v>
       </c>
       <c r="B179" t="s">
         <v>16</v>
       </c>
       <c r="C179">
-        <v>42.86143001679577</v>
+        <v>39.43913909150694</v>
       </c>
       <c r="D179">
-        <v>22.72053012591219</v>
+        <v>21.05297617141148</v>
       </c>
       <c r="E179">
-        <v>0.9990984299999999</v>
+        <v>0.999144</v>
       </c>
       <c r="F179">
-        <v>0.9990984299999999</v>
+        <v>0.999144</v>
       </c>
       <c r="G179">
-        <v>0.3615660647779204</v>
+        <v>0.2516582935428642</v>
       </c>
       <c r="H179">
-        <v>0.9990984299999999</v>
+        <v>0.9974678400000001</v>
       </c>
     </row>
     <row r="180" spans="1:8">
       <c r="A180" s="1">
-        <v>46177</v>
+        <v>46167</v>
       </c>
       <c r="B180" t="s">
         <v>16</v>
       </c>
       <c r="C180">
-        <v>42.57902095847519</v>
+        <v>39.45782844313628</v>
       </c>
       <c r="D180">
-        <v>22.20304338566557</v>
+        <v>21.0518901572272</v>
       </c>
       <c r="E180">
-        <v>0.9990006900000001</v>
+        <v>0.999144</v>
       </c>
       <c r="F180">
-        <v>0.9990006900000001</v>
+        <v>0.999144</v>
       </c>
       <c r="G180">
-        <v>0.34033389372967</v>
+        <v>0.2516582935428642</v>
       </c>
       <c r="H180">
-        <v>0.9990006900000001</v>
+        <v>0.9974678400000001</v>
       </c>
     </row>
     <row r="181" spans="1:8">
       <c r="A181" s="1">
-        <v>46178</v>
+        <v>46168</v>
       </c>
       <c r="B181" t="s">
         <v>16</v>
       </c>
       <c r="C181">
-        <v>39.64354477595148</v>
+        <v>40.20219297984542</v>
       </c>
       <c r="D181">
-        <v>20.69555521363093</v>
+        <v>21.93106024403281</v>
       </c>
       <c r="E181">
-        <v>0.9992026399999999</v>
+        <v>0.9991421799999999</v>
       </c>
       <c r="F181">
-        <v>0.9992026399999999</v>
+        <v>0.9991421799999999</v>
       </c>
       <c r="G181">
-        <v>0.251033842835561</v>
+        <v>0.2846167552893293</v>
       </c>
       <c r="H181">
-        <v>0.9992026399999999</v>
+        <v>0.9974609800000001</v>
       </c>
     </row>
     <row r="182" spans="1:8">
       <c r="A182" s="1">
-        <v>46182</v>
+        <v>46169</v>
       </c>
       <c r="B182" t="s">
         <v>16</v>
       </c>
       <c r="C182">
+        <v>40.34993865302093</v>
+      </c>
+      <c r="D182">
+        <v>21.65366031776487</v>
+      </c>
+      <c r="E182">
+        <v>0.9991434600000001</v>
+      </c>
+      <c r="F182">
+        <v>0.9991434600000001</v>
+      </c>
+      <c r="G182">
+        <v>0.2796902860011767</v>
+      </c>
+      <c r="H182">
+        <v>0.9991434600000001</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8">
+      <c r="A183" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183">
+        <v>40.5850485390846</v>
+      </c>
+      <c r="D183">
+        <v>21.75450977746074</v>
+      </c>
+      <c r="E183">
+        <v>0.99914592</v>
+      </c>
+      <c r="F183">
+        <v>0.99914592</v>
+      </c>
+      <c r="G183">
+        <v>0.2964818481030536</v>
+      </c>
+      <c r="H183">
+        <v>0.99914592</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8">
+      <c r="A184" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184">
+        <v>41.86785805184477</v>
+      </c>
+      <c r="D184">
+        <v>22.33589392797469</v>
+      </c>
+      <c r="E184">
+        <v>0.9991336999999999</v>
+      </c>
+      <c r="F184">
+        <v>0.9991336999999999</v>
+      </c>
+      <c r="G184">
+        <v>0.3254158954996882</v>
+      </c>
+      <c r="H184">
+        <v>0.9991336999999999</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8">
+      <c r="A185" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185">
+        <v>42.82932322850974</v>
+      </c>
+      <c r="D185">
+        <v>22.98998911430362</v>
+      </c>
+      <c r="E185">
+        <v>0.99914238</v>
+      </c>
+      <c r="F185">
+        <v>0.99914238</v>
+      </c>
+      <c r="G185">
+        <v>0.3583049032509023</v>
+      </c>
+      <c r="H185">
+        <v>0.99914238</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8">
+      <c r="A186" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186">
+        <v>43.11872937189534</v>
+      </c>
+      <c r="D186">
+        <v>22.90628380907704</v>
+      </c>
+      <c r="E186">
+        <v>0.9990972800000002</v>
+      </c>
+      <c r="F186">
+        <v>0.9990972800000002</v>
+      </c>
+      <c r="G186">
+        <v>0.3753046155885469</v>
+      </c>
+      <c r="H186">
+        <v>0.9990972800000002</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8">
+      <c r="A187" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187">
+        <v>42.86143001679577</v>
+      </c>
+      <c r="D187">
+        <v>22.72053012591219</v>
+      </c>
+      <c r="E187">
+        <v>0.9990984299999999</v>
+      </c>
+      <c r="F187">
+        <v>0.9990984299999999</v>
+      </c>
+      <c r="G187">
+        <v>0.3615660647779204</v>
+      </c>
+      <c r="H187">
+        <v>0.9990984299999999</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8">
+      <c r="A188" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188">
+        <v>42.57902095847519</v>
+      </c>
+      <c r="D188">
+        <v>22.20304338566557</v>
+      </c>
+      <c r="E188">
+        <v>0.9990006900000001</v>
+      </c>
+      <c r="F188">
+        <v>0.9990006900000001</v>
+      </c>
+      <c r="G188">
+        <v>0.34033389372967</v>
+      </c>
+      <c r="H188">
+        <v>0.9990006900000001</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8">
+      <c r="A189" s="1">
+        <v>46178</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189">
+        <v>39.64354477595148</v>
+      </c>
+      <c r="D189">
+        <v>20.69555521363093</v>
+      </c>
+      <c r="E189">
+        <v>0.9992026399999999</v>
+      </c>
+      <c r="F189">
+        <v>0.9992026399999999</v>
+      </c>
+      <c r="G189">
+        <v>0.251033842835561</v>
+      </c>
+      <c r="H189">
+        <v>0.9992026399999999</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8">
+      <c r="A190" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190">
         <v>39.7656886466531</v>
       </c>
-      <c r="D182">
+      <c r="D190">
         <v>20.79148740795913</v>
       </c>
-      <c r="E182">
+      <c r="E190">
         <v>0.9992145899999999</v>
       </c>
-      <c r="F182">
+      <c r="F190">
         <v>0.9992145899999999</v>
       </c>
-      <c r="G182">
+      <c r="G190">
         <v>0.2542950043625791</v>
       </c>
-      <c r="H182">
+      <c r="H190">
         <v>0.9992145899999999</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8">
+      <c r="A191" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191">
+        <v>38.48800295288941</v>
+      </c>
+      <c r="D191">
+        <v>20.05492629580107</v>
+      </c>
+      <c r="E191">
+        <v>0.9992031100000001</v>
+      </c>
+      <c r="F191">
+        <v>0.9992031100000001</v>
+      </c>
+      <c r="G191">
+        <v>0.2255691072017123</v>
+      </c>
+      <c r="H191">
+        <v>0.9992031100000001</v>
       </c>
     </row>
   </sheetData>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="17">
   <si>
     <t>Date</t>
   </si>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H191"/>
+  <dimension ref="A1:H200"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -821,42 +821,42 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1">
-        <v>46153</v>
+        <v>46184</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17">
-        <v>53.14833755912058</v>
+        <v>27.85109007326567</v>
       </c>
       <c r="D17">
-        <v>25.84885448407537</v>
+        <v>17.7287336596346</v>
       </c>
       <c r="E17">
-        <v>0.9262</v>
+        <v>0.8855000000000001</v>
       </c>
       <c r="F17">
-        <v>0.9262</v>
+        <v>0.8855000000000001</v>
       </c>
       <c r="G17">
-        <v>0.3839084462043663</v>
+        <v>0.530551436319759</v>
       </c>
       <c r="H17">
-        <v>0.9262</v>
+        <v>0.9359</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B18" t="s">
         <v>9</v>
       </c>
       <c r="C18">
-        <v>51.82921169635205</v>
+        <v>53.14833755912058</v>
       </c>
       <c r="D18">
-        <v>25.32805827181975</v>
+        <v>25.84885448407537</v>
       </c>
       <c r="E18">
         <v>0.9262</v>
@@ -865,7 +865,7 @@
         <v>0.9262</v>
       </c>
       <c r="G18">
-        <v>0.3568580281685669</v>
+        <v>0.3839084462043663</v>
       </c>
       <c r="H18">
         <v>0.9262</v>
@@ -873,120 +873,120 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B19" t="s">
         <v>9</v>
       </c>
       <c r="C19">
-        <v>52.28471716753184</v>
+        <v>51.82921169635205</v>
       </c>
       <c r="D19">
-        <v>25.54525144150689</v>
+        <v>25.32805827181975</v>
       </c>
       <c r="E19">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="F19">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="G19">
-        <v>0.378012896547947</v>
+        <v>0.3568580281685669</v>
       </c>
       <c r="H19">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B20" t="s">
         <v>9</v>
       </c>
       <c r="C20">
-        <v>53.87287273813902</v>
+        <v>52.28471716753184</v>
       </c>
       <c r="D20">
-        <v>26.32154226438612</v>
+        <v>25.54525144150689</v>
       </c>
       <c r="E20">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="F20">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="G20">
-        <v>0.4166811087612758</v>
+        <v>0.378012896547947</v>
       </c>
       <c r="H20">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="B21" t="s">
         <v>9</v>
       </c>
       <c r="C21">
-        <v>52.18747148214074</v>
+        <v>53.87287273813902</v>
       </c>
       <c r="D21">
-        <v>25.13616059644496</v>
+        <v>26.32154226438612</v>
       </c>
       <c r="E21">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="F21">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="G21">
-        <v>0.3627535778249862</v>
+        <v>0.4166811087612758</v>
       </c>
       <c r="H21">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="B22" t="s">
         <v>9</v>
       </c>
       <c r="C22">
-        <v>50.72035274995172</v>
+        <v>52.18747148214074</v>
       </c>
       <c r="D22">
-        <v>24.61756040386634</v>
+        <v>25.13616059644496</v>
       </c>
       <c r="E22">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="F22">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="G22">
         <v>0.3627535778249862</v>
       </c>
       <c r="H22">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="B23" t="s">
         <v>9</v>
       </c>
       <c r="C23">
-        <v>50.11981086673613</v>
+        <v>50.72035274995172</v>
       </c>
       <c r="D23">
-        <v>24.13061679021705</v>
+        <v>24.61756040386634</v>
       </c>
       <c r="E23">
         <v>0.9259000000000001</v>
@@ -995,7 +995,7 @@
         <v>0.9259000000000001</v>
       </c>
       <c r="G23">
-        <v>0.3258193430227221</v>
+        <v>0.3627535778249862</v>
       </c>
       <c r="H23">
         <v>0.9259000000000001</v>
@@ -1003,120 +1003,120 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="B24" t="s">
         <v>9</v>
       </c>
       <c r="C24">
-        <v>51.74165648409151</v>
+        <v>50.11981086673613</v>
       </c>
       <c r="D24">
-        <v>24.98091384114761</v>
+        <v>24.13061679021705</v>
       </c>
       <c r="E24">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="F24">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="G24">
-        <v>0.3818277262286871</v>
+        <v>0.3258193430227221</v>
       </c>
       <c r="H24">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
       </c>
       <c r="C25">
-        <v>49.13455894175823</v>
+        <v>51.74165648409151</v>
       </c>
       <c r="D25">
-        <v>25.30005057653127</v>
+        <v>24.98091384114761</v>
       </c>
       <c r="E25">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="F25">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="G25">
-        <v>0.4028091571787618</v>
+        <v>0.3818277262286871</v>
       </c>
       <c r="H25">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
       </c>
       <c r="C26">
-        <v>49.57776597479297</v>
+        <v>49.13455894175823</v>
       </c>
       <c r="D26">
-        <v>25.04906725563518</v>
+        <v>25.30005057653127</v>
       </c>
       <c r="E26">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="F26">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="G26">
-        <v>0.4256980029692063</v>
+        <v>0.4028091571787618</v>
       </c>
       <c r="H26">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="B27" t="s">
         <v>9</v>
       </c>
       <c r="C27">
-        <v>49.71239596645896</v>
+        <v>49.57776597479297</v>
       </c>
       <c r="D27">
-        <v>25.18778610744295</v>
+        <v>25.04906725563518</v>
       </c>
       <c r="E27">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="F27">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="G27">
-        <v>0.4525749835757003</v>
+        <v>0.4256980029692063</v>
       </c>
       <c r="H27">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="B28" t="s">
         <v>9</v>
       </c>
       <c r="C28">
-        <v>50.77166277510776</v>
+        <v>49.71239596645896</v>
       </c>
       <c r="D28">
-        <v>25.7431782858765</v>
+        <v>25.18778610744295</v>
       </c>
       <c r="E28">
         <v>0.9231999999999999</v>
@@ -1125,7 +1125,7 @@
         <v>0.9231999999999999</v>
       </c>
       <c r="G28">
-        <v>0.4700884597036457</v>
+        <v>0.4525749835757003</v>
       </c>
       <c r="H28">
         <v>0.9231999999999999</v>
@@ -1133,120 +1133,120 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1">
-        <v>46169</v>
+        <v>46168</v>
       </c>
       <c r="B29" t="s">
         <v>9</v>
       </c>
       <c r="C29">
-        <v>50.57689164833899</v>
+        <v>50.77166277510776</v>
       </c>
       <c r="D29">
-        <v>25.70244067238947</v>
+        <v>25.7431782858765</v>
       </c>
       <c r="E29">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="F29">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="G29">
-        <v>0.4518814984464716</v>
+        <v>0.4700884597036457</v>
       </c>
       <c r="H29">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="B30" t="s">
         <v>9</v>
       </c>
       <c r="C30">
-        <v>50.80027854822009</v>
+        <v>50.57689164833899</v>
       </c>
       <c r="D30">
-        <v>25.90068415792015</v>
+        <v>25.70244067238947</v>
       </c>
       <c r="E30">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
       <c r="F30">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
       <c r="G30">
-        <v>0.4699150222743402</v>
+        <v>0.4518814984464716</v>
       </c>
       <c r="H30">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="B31" t="s">
         <v>9</v>
       </c>
       <c r="C31">
-        <v>51.44563447241545</v>
+        <v>50.80027854822009</v>
       </c>
       <c r="D31">
-        <v>26.0970978996374</v>
+        <v>25.90068415792015</v>
       </c>
       <c r="E31">
-        <v>0.9246</v>
+        <v>0.9231</v>
       </c>
       <c r="F31">
-        <v>0.9246</v>
+        <v>0.9231</v>
       </c>
       <c r="G31">
-        <v>0.4791053539115764</v>
+        <v>0.4699150222743402</v>
       </c>
       <c r="H31">
-        <v>0.9246</v>
+        <v>0.9231</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1">
-        <v>46174</v>
+        <v>46171</v>
       </c>
       <c r="B32" t="s">
         <v>9</v>
       </c>
       <c r="C32">
-        <v>53.05792083471825</v>
+        <v>51.44563447241545</v>
       </c>
       <c r="D32">
-        <v>26.86242981002239</v>
+        <v>26.0970978996374</v>
       </c>
       <c r="E32">
-        <v>0.9254999999999999</v>
+        <v>0.9246</v>
       </c>
       <c r="F32">
-        <v>0.9254999999999999</v>
+        <v>0.9246</v>
       </c>
       <c r="G32">
-        <v>0.5306051577195796</v>
+        <v>0.4791053539115764</v>
       </c>
       <c r="H32">
-        <v>0.9254999999999999</v>
+        <v>0.9246</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="B33" t="s">
         <v>9</v>
       </c>
       <c r="C33">
-        <v>54.38946369031042</v>
+        <v>53.05792083471825</v>
       </c>
       <c r="D33">
-        <v>27.57160808325711</v>
+        <v>26.86242981002239</v>
       </c>
       <c r="E33">
         <v>0.9254999999999999</v>
@@ -1255,7 +1255,7 @@
         <v>0.9254999999999999</v>
       </c>
       <c r="G33">
-        <v>0.5845326886558693</v>
+        <v>0.5306051577195796</v>
       </c>
       <c r="H33">
         <v>0.9254999999999999</v>
@@ -1263,276 +1263,276 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="B34" t="s">
         <v>9</v>
       </c>
       <c r="C34">
-        <v>54.35279063045283</v>
+        <v>54.38946369031042</v>
       </c>
       <c r="D34">
-        <v>27.50874919819178</v>
+        <v>27.57160808325711</v>
       </c>
       <c r="E34">
-        <v>0.9162000000000001</v>
+        <v>0.9254999999999999</v>
       </c>
       <c r="F34">
-        <v>0.9162000000000001</v>
+        <v>0.9254999999999999</v>
       </c>
       <c r="G34">
-        <v>0.5992718273849102</v>
+        <v>0.5845326886558693</v>
       </c>
       <c r="H34">
-        <v>0.9162000000000001</v>
+        <v>0.9254999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="B35" t="s">
         <v>9</v>
       </c>
       <c r="C35">
-        <v>53.45790968334249</v>
+        <v>54.35279063045283</v>
       </c>
       <c r="D35">
-        <v>26.99486187834476</v>
+        <v>27.50874919819178</v>
       </c>
       <c r="E35">
-        <v>0.9154000000000001</v>
+        <v>0.9162000000000001</v>
       </c>
       <c r="F35">
-        <v>0.9154000000000001</v>
+        <v>0.9162000000000001</v>
       </c>
       <c r="G35">
-        <v>0.5691000647975994</v>
+        <v>0.5992718273849102</v>
       </c>
       <c r="H35">
-        <v>0.9154000000000001</v>
+        <v>0.9162000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="B36" t="s">
         <v>9</v>
       </c>
       <c r="C36">
-        <v>52.01314444713902</v>
+        <v>53.45790968334249</v>
       </c>
       <c r="D36">
-        <v>25.48849727916627</v>
+        <v>26.99486187834476</v>
       </c>
       <c r="E36">
-        <v>0.9142999999999999</v>
+        <v>0.9154000000000001</v>
       </c>
       <c r="F36">
-        <v>0.9142999999999999</v>
+        <v>0.9154000000000001</v>
       </c>
       <c r="G36">
-        <v>0.4380094145699611</v>
+        <v>0.5691000647975994</v>
       </c>
       <c r="H36">
-        <v>0.9142999999999999</v>
+        <v>0.9154000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1">
-        <v>46182</v>
+        <v>46178</v>
       </c>
       <c r="B37" t="s">
         <v>9</v>
       </c>
       <c r="C37">
-        <v>50.12461745484359</v>
+        <v>52.01314444713902</v>
       </c>
       <c r="D37">
-        <v>25.31796473106079</v>
+        <v>25.48849727916627</v>
       </c>
       <c r="E37">
-        <v>0.916</v>
+        <v>0.9142999999999999</v>
       </c>
       <c r="F37">
-        <v>0.916</v>
+        <v>0.9142999999999999</v>
       </c>
       <c r="G37">
-        <v>0.4801457138994158</v>
+        <v>0.4380094145699611</v>
       </c>
       <c r="H37">
-        <v>0.916</v>
+        <v>0.9142999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="B38" t="s">
         <v>9</v>
       </c>
       <c r="C38">
-        <v>51.46065536727718</v>
+        <v>50.12461745484359</v>
       </c>
       <c r="D38">
-        <v>25.08120911400394</v>
+        <v>25.31796473106079</v>
       </c>
       <c r="E38">
-        <v>0.9188000000000002</v>
+        <v>0.916</v>
       </c>
       <c r="F38">
-        <v>0.9188000000000002</v>
+        <v>0.916</v>
       </c>
       <c r="G38">
-        <v>0.426738362957046</v>
+        <v>0.4801457138994158</v>
       </c>
       <c r="H38">
-        <v>0.9188000000000002</v>
+        <v>0.916</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1">
-        <v>46153</v>
+        <v>46183</v>
       </c>
       <c r="B39" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C39">
-        <v>34.64560932909123</v>
+        <v>51.46065536727718</v>
       </c>
       <c r="D39">
-        <v>26.08311546080494</v>
+        <v>25.08120911400394</v>
       </c>
       <c r="E39">
-        <v>0.9983000000000001</v>
+        <v>0.9188000000000002</v>
       </c>
       <c r="F39">
-        <v>0.9983000000000001</v>
+        <v>0.9188000000000002</v>
       </c>
       <c r="G39">
-        <v>0.06258613715048233</v>
+        <v>0.426738362957046</v>
       </c>
       <c r="H39">
-        <v>0.9983000000000001</v>
+        <v>0.9188000000000002</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1">
-        <v>46154</v>
+        <v>46184</v>
       </c>
       <c r="B40" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C40">
-        <v>34.50204921141101</v>
+        <v>56.06808173087</v>
       </c>
       <c r="D40">
-        <v>25.94535229304585</v>
+        <v>26.41955208935029</v>
       </c>
       <c r="E40">
-        <v>0.9984</v>
+        <v>0.9193</v>
       </c>
       <c r="F40">
-        <v>0.9984</v>
+        <v>0.9193</v>
       </c>
       <c r="G40">
-        <v>0.05768943168306073</v>
+        <v>0.5195075435359697</v>
       </c>
       <c r="H40">
-        <v>0.9984</v>
+        <v>0.9193</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="B41" t="s">
         <v>10</v>
       </c>
       <c r="C41">
-        <v>35.10429483281073</v>
+        <v>34.64560932909123</v>
       </c>
       <c r="D41">
-        <v>26.43864879939599</v>
+        <v>26.08311546080494</v>
       </c>
       <c r="E41">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="F41">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="G41">
-        <v>0.07926550001722021</v>
+        <v>0.06258613715048233</v>
       </c>
       <c r="H41">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="B42" t="s">
         <v>10</v>
       </c>
       <c r="C42">
-        <v>35.36860632820093</v>
+        <v>34.50204921141101</v>
       </c>
       <c r="D42">
-        <v>26.56575571102338</v>
+        <v>25.94535229304585</v>
       </c>
       <c r="E42">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F42">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G42">
-        <v>0.08553946591902095</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H42">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="B43" t="s">
         <v>10</v>
       </c>
       <c r="C43">
-        <v>34.88080083527914</v>
+        <v>35.10429483281073</v>
       </c>
       <c r="D43">
-        <v>26.19322945679072</v>
+        <v>26.43864879939599</v>
       </c>
       <c r="E43">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="F43">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="G43">
-        <v>0.06870693142475881</v>
+        <v>0.07926550001722021</v>
       </c>
       <c r="H43">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1">
-        <v>46160</v>
+        <v>46156</v>
       </c>
       <c r="B44" t="s">
         <v>10</v>
       </c>
       <c r="C44">
-        <v>34.67638692539213</v>
+        <v>35.36860632820093</v>
       </c>
       <c r="D44">
-        <v>26.06707890342319</v>
+        <v>26.56575571102338</v>
       </c>
       <c r="E44">
         <v>0.9985999999999999</v>
@@ -1541,7 +1541,7 @@
         <v>0.9985999999999999</v>
       </c>
       <c r="G44">
-        <v>0.06289213016552919</v>
+        <v>0.08553946591902095</v>
       </c>
       <c r="H44">
         <v>0.9985999999999999</v>
@@ -1549,120 +1549,120 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="B45" t="s">
         <v>10</v>
       </c>
       <c r="C45">
-        <v>34.21212662725402</v>
+        <v>34.88080083527914</v>
       </c>
       <c r="D45">
-        <v>25.60349394367002</v>
+        <v>26.19322945679072</v>
       </c>
       <c r="E45">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="F45">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="G45">
-        <v>0.0486610616591685</v>
+        <v>0.06870693142475881</v>
       </c>
       <c r="H45">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="B46" t="s">
         <v>10</v>
       </c>
       <c r="C46">
-        <v>34.78598436564941</v>
+        <v>34.67638692539213</v>
       </c>
       <c r="D46">
-        <v>25.95505316769806</v>
+        <v>26.06707890342319</v>
       </c>
       <c r="E46">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="F46">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="G46">
-        <v>0.06335117806143331</v>
+        <v>0.06289213016552919</v>
       </c>
       <c r="H46">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1">
-        <v>46163</v>
+        <v>46161</v>
       </c>
       <c r="B47" t="s">
         <v>10</v>
       </c>
       <c r="C47">
-        <v>33.4539909056227</v>
+        <v>34.21212662725402</v>
       </c>
       <c r="D47">
-        <v>25.96014535427112</v>
+        <v>25.60349394367002</v>
       </c>
       <c r="E47">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="F47">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="G47">
-        <v>0.06350423294229035</v>
+        <v>0.0486610616591685</v>
       </c>
       <c r="H47">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1">
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="B48" t="s">
         <v>10</v>
       </c>
       <c r="C48">
-        <v>33.24951933563993</v>
+        <v>34.78598436564941</v>
       </c>
       <c r="D48">
-        <v>25.46629530314992</v>
+        <v>25.95505316769806</v>
       </c>
       <c r="E48">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="F48">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="G48">
-        <v>0.06136193159696024</v>
+        <v>0.06335117806143331</v>
       </c>
       <c r="H48">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1">
-        <v>46167</v>
+        <v>46163</v>
       </c>
       <c r="B49" t="s">
         <v>10</v>
       </c>
       <c r="C49">
-        <v>33.29896419867477</v>
+        <v>33.4539909056227</v>
       </c>
       <c r="D49">
-        <v>25.45090185337973</v>
+        <v>25.96014535427112</v>
       </c>
       <c r="E49">
         <v>0.9984</v>
@@ -1671,7 +1671,7 @@
         <v>0.9984</v>
       </c>
       <c r="G49">
-        <v>0.06136193159696024</v>
+        <v>0.06350423294229035</v>
       </c>
       <c r="H49">
         <v>0.9984</v>
@@ -1679,16 +1679,16 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1">
-        <v>46168</v>
+        <v>46164</v>
       </c>
       <c r="B50" t="s">
         <v>10</v>
       </c>
       <c r="C50">
-        <v>33.41270923608511</v>
+        <v>33.24951933563993</v>
       </c>
       <c r="D50">
-        <v>25.54156152389702</v>
+        <v>25.46629530314992</v>
       </c>
       <c r="E50">
         <v>0.9984</v>
@@ -1697,7 +1697,7 @@
         <v>0.9984</v>
       </c>
       <c r="G50">
-        <v>0.06549347940676342</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H50">
         <v>0.9984</v>
@@ -1705,198 +1705,198 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1">
-        <v>46169</v>
+        <v>46167</v>
       </c>
       <c r="B51" t="s">
         <v>10</v>
       </c>
       <c r="C51">
-        <v>33.73350746548562</v>
+        <v>33.29896419867477</v>
       </c>
       <c r="D51">
-        <v>25.75393367034243</v>
+        <v>25.45090185337973</v>
       </c>
       <c r="E51">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="F51">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="G51">
-        <v>0.07620510288008187</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H51">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1">
-        <v>46170</v>
+        <v>46168</v>
       </c>
       <c r="B52" t="s">
         <v>10</v>
       </c>
       <c r="C52">
-        <v>33.84336414535104</v>
+        <v>33.41270923608511</v>
       </c>
       <c r="D52">
-        <v>25.97168203877208</v>
+        <v>25.54156152389702</v>
       </c>
       <c r="E52">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
       <c r="F52">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
       <c r="G52">
-        <v>0.0844683152463559</v>
+        <v>0.06549347940676342</v>
       </c>
       <c r="H52">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1">
-        <v>46171</v>
+        <v>46169</v>
       </c>
       <c r="B53" t="s">
         <v>10</v>
       </c>
       <c r="C53">
-        <v>33.73370320039719</v>
+        <v>33.73350746548562</v>
       </c>
       <c r="D53">
-        <v>25.880209881309</v>
+        <v>25.75393367034243</v>
       </c>
       <c r="E53">
-        <v>0.9988</v>
+        <v>0.9987000000000001</v>
       </c>
       <c r="F53">
-        <v>0.9988</v>
+        <v>0.9987000000000001</v>
       </c>
       <c r="G53">
-        <v>0.08201990413931148</v>
+        <v>0.07620510288008187</v>
       </c>
       <c r="H53">
-        <v>0.9988</v>
+        <v>0.9987000000000001</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1">
-        <v>46174</v>
+        <v>46170</v>
       </c>
       <c r="B54" t="s">
         <v>10</v>
       </c>
       <c r="C54">
-        <v>33.45546240777382</v>
+        <v>33.84336414535104</v>
       </c>
       <c r="D54">
-        <v>25.61350381215703</v>
+        <v>25.97168203877208</v>
       </c>
       <c r="E54">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
       <c r="F54">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
       <c r="G54">
-        <v>0.06901304118647311</v>
+        <v>0.0844683152463559</v>
       </c>
       <c r="H54">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1">
-        <v>46175</v>
+        <v>46171</v>
       </c>
       <c r="B55" t="s">
         <v>10</v>
       </c>
       <c r="C55">
-        <v>33.31245255516097</v>
+        <v>33.73370320039719</v>
       </c>
       <c r="D55">
-        <v>25.36461330330757</v>
+        <v>25.880209881309</v>
       </c>
       <c r="E55">
-        <v>0.9989999999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="F55">
-        <v>0.9989999999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="G55">
-        <v>0.05845447259401171</v>
+        <v>0.08201990413931148</v>
       </c>
       <c r="H55">
-        <v>0.9989999999999999</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="B56" t="s">
         <v>10</v>
       </c>
       <c r="C56">
-        <v>33.02444632653544</v>
+        <v>33.45546240777382</v>
       </c>
       <c r="D56">
-        <v>25.07926152561908</v>
+        <v>25.61350381215703</v>
       </c>
       <c r="E56">
-        <v>0.9991</v>
+        <v>0.999</v>
       </c>
       <c r="F56">
-        <v>0.9991</v>
+        <v>0.999</v>
       </c>
       <c r="G56">
-        <v>0.04697780820974229</v>
+        <v>0.06901304118647311</v>
       </c>
       <c r="H56">
-        <v>0.9991</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1">
-        <v>46177</v>
+        <v>46175</v>
       </c>
       <c r="B57" t="s">
         <v>10</v>
       </c>
       <c r="C57">
-        <v>33.50291463064395</v>
+        <v>33.31245255516097</v>
       </c>
       <c r="D57">
-        <v>25.33002193941023</v>
+        <v>25.36461330330757</v>
       </c>
       <c r="E57">
-        <v>0.9991000000000001</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="F57">
-        <v>0.9991000000000001</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="G57">
-        <v>0.05768943168306073</v>
+        <v>0.05845447259401171</v>
       </c>
       <c r="H57">
-        <v>0.9991000000000001</v>
+        <v>0.9989999999999999</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1">
-        <v>46178</v>
+        <v>46176</v>
       </c>
       <c r="B58" t="s">
         <v>10</v>
       </c>
       <c r="C58">
-        <v>32.19021336116872</v>
+        <v>33.02444632653544</v>
       </c>
       <c r="D58">
-        <v>24.38570557505481</v>
+        <v>25.07926152561908</v>
       </c>
       <c r="E58">
         <v>0.9991</v>
@@ -1905,7 +1905,7 @@
         <v>0.9991</v>
       </c>
       <c r="G58">
-        <v>0.01775063028607016</v>
+        <v>0.04697780820974229</v>
       </c>
       <c r="H58">
         <v>0.9991</v>
@@ -1913,770 +1913,770 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1">
-        <v>46182</v>
+        <v>46177</v>
       </c>
       <c r="B59" t="s">
         <v>10</v>
       </c>
       <c r="C59">
-        <v>32.06505731417286</v>
+        <v>33.50291463064395</v>
       </c>
       <c r="D59">
-        <v>24.06041109516704</v>
+        <v>25.33002193941023</v>
       </c>
       <c r="E59">
-        <v>0.9988999999999999</v>
+        <v>0.9991000000000001</v>
       </c>
       <c r="F59">
-        <v>0.9988999999999999</v>
+        <v>0.9991000000000001</v>
       </c>
       <c r="G59">
-        <v>0.004743767333231785</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H59">
-        <v>0.9988999999999999</v>
+        <v>0.9991000000000001</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1">
-        <v>46183</v>
+        <v>46178</v>
       </c>
       <c r="B60" t="s">
         <v>10</v>
       </c>
       <c r="C60">
-        <v>31.23512211947358</v>
+        <v>32.19021336116872</v>
       </c>
       <c r="D60">
-        <v>23.50146802051874</v>
+        <v>24.38570557505481</v>
       </c>
       <c r="E60">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F60">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G60">
-        <v>-0.01729146564349893</v>
+        <v>0.01775063028607016</v>
       </c>
       <c r="H60">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1">
-        <v>46153</v>
+        <v>46182</v>
       </c>
       <c r="B61" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C61">
-        <v>36.55790859258162</v>
+        <v>32.06505731417286</v>
       </c>
       <c r="D61">
-        <v>22.67181120908155</v>
+        <v>24.06041109516704</v>
       </c>
       <c r="E61">
-        <v>0.9990740999999999</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="F61">
-        <v>0.9990740999999999</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="G61">
-        <v>0.1648443271746771</v>
+        <v>0.004743767333231785</v>
       </c>
       <c r="H61">
-        <v>0.9990740999999999</v>
+        <v>0.9988999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1">
-        <v>46154</v>
+        <v>46183</v>
       </c>
       <c r="B62" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C62">
-        <v>36.44753722959613</v>
+        <v>31.23512211947358</v>
       </c>
       <c r="D62">
-        <v>22.40292401789388</v>
+        <v>23.50146802051874</v>
       </c>
       <c r="E62">
-        <v>0.9990772499999999</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="F62">
-        <v>0.9990772499999999</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="G62">
-        <v>0.154964342628132</v>
+        <v>-0.01729146564349893</v>
       </c>
       <c r="H62">
-        <v>0.9990772499999999</v>
+        <v>0.9989999999999999</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1">
-        <v>46155</v>
+        <v>46184</v>
       </c>
       <c r="B63" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C63">
-        <v>36.63128514035871</v>
+        <v>31.67819012660615</v>
       </c>
       <c r="D63">
-        <v>22.65773388934668</v>
+        <v>23.76719139935413</v>
       </c>
       <c r="E63">
-        <v>0.99907745</v>
+        <v>0.9992000000000001</v>
       </c>
       <c r="F63">
-        <v>0.99907745</v>
+        <v>0.9992000000000001</v>
       </c>
       <c r="G63">
-        <v>0.1671633421405267</v>
+        <v>-0.006732897051037523</v>
       </c>
       <c r="H63">
-        <v>0.99907745</v>
+        <v>0.9992000000000001</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="B64" t="s">
         <v>11</v>
       </c>
       <c r="C64">
-        <v>36.87865927427314</v>
+        <v>36.55790859258162</v>
       </c>
       <c r="D64">
-        <v>22.69755646854794</v>
+        <v>22.67181120908155</v>
       </c>
       <c r="E64">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="F64">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="G64">
-        <v>0.1754592080224002</v>
+        <v>0.1648443271746771</v>
       </c>
       <c r="H64">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="B65" t="s">
         <v>11</v>
       </c>
       <c r="C65">
-        <v>36.52208783231286</v>
+        <v>36.44753722959613</v>
       </c>
       <c r="D65">
-        <v>22.32462309676992</v>
+        <v>22.40292401789388</v>
       </c>
       <c r="E65">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="F65">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="G65">
-        <v>0.1577242156354994</v>
+        <v>0.154964342628132</v>
       </c>
       <c r="H65">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="B66" t="s">
         <v>11</v>
       </c>
       <c r="C66">
-        <v>36.25604200674668</v>
+        <v>36.63128514035871</v>
       </c>
       <c r="D66">
-        <v>22.16555007468561</v>
+        <v>22.65773388934668</v>
       </c>
       <c r="E66">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="F66">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="G66">
-        <v>0.1527434068648266</v>
+        <v>0.1671633421405267</v>
       </c>
       <c r="H66">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1">
-        <v>46161</v>
+        <v>46156</v>
       </c>
       <c r="B67" t="s">
         <v>11</v>
       </c>
       <c r="C67">
-        <v>36.01040085730018</v>
+        <v>36.87865927427314</v>
       </c>
       <c r="D67">
-        <v>22.19475589056387</v>
+        <v>22.69755646854794</v>
       </c>
       <c r="E67">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="F67">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="G67">
-        <v>0.1456396418594061</v>
+        <v>0.1754592080224002</v>
       </c>
       <c r="H67">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1">
-        <v>46162</v>
+        <v>46157</v>
       </c>
       <c r="B68" t="s">
         <v>11</v>
       </c>
       <c r="C68">
-        <v>36.45290912796982</v>
+        <v>36.52208783231286</v>
       </c>
       <c r="D68">
-        <v>22.46357594746874</v>
+        <v>22.32462309676992</v>
       </c>
       <c r="E68">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="F68">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="G68">
-        <v>0.1646157747240327</v>
+        <v>0.1577242156354994</v>
       </c>
       <c r="H68">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1">
-        <v>46163</v>
+        <v>46160</v>
       </c>
       <c r="B69" t="s">
         <v>11</v>
       </c>
       <c r="C69">
-        <v>35.75282090566891</v>
+        <v>36.25604200674668</v>
       </c>
       <c r="D69">
-        <v>22.57615417310648</v>
+        <v>22.16555007468561</v>
       </c>
       <c r="E69">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="F69">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="G69">
-        <v>0.1668367104873381</v>
+        <v>0.1527434068648266</v>
       </c>
       <c r="H69">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1">
-        <v>46164</v>
+        <v>46161</v>
       </c>
       <c r="B70" t="s">
         <v>11</v>
       </c>
       <c r="C70">
-        <v>35.75514940724808</v>
+        <v>36.01040085730018</v>
       </c>
       <c r="D70">
-        <v>22.28880693466429</v>
+        <v>22.19475589056387</v>
       </c>
       <c r="E70">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="F70">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="G70">
-        <v>0.1717848261904962</v>
+        <v>0.1456396418594061</v>
       </c>
       <c r="H70">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1">
-        <v>46167</v>
+        <v>46162</v>
       </c>
       <c r="B71" t="s">
         <v>11</v>
       </c>
       <c r="C71">
-        <v>35.84133099010302</v>
+        <v>36.45290912796982</v>
       </c>
       <c r="D71">
-        <v>22.37458514769363</v>
+        <v>22.46357594746874</v>
       </c>
       <c r="E71">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="F71">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="G71">
-        <v>0.1717848261904962</v>
+        <v>0.1646157747240327</v>
       </c>
       <c r="H71">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1">
-        <v>46168</v>
+        <v>46163</v>
       </c>
       <c r="B72" t="s">
         <v>11</v>
       </c>
       <c r="C72">
-        <v>36.23214279739292</v>
+        <v>35.75282090566891</v>
       </c>
       <c r="D72">
-        <v>22.93484792820123</v>
+        <v>22.57615417310648</v>
       </c>
       <c r="E72">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
       <c r="F72">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
       <c r="G72">
-        <v>0.1925900763781823</v>
+        <v>0.1668367104873381</v>
       </c>
       <c r="H72">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="B73" t="s">
         <v>11</v>
       </c>
       <c r="C73">
-        <v>36.4336692499184</v>
+        <v>35.75514940724808</v>
       </c>
       <c r="D73">
-        <v>22.75940954009856</v>
+        <v>22.28880693466429</v>
       </c>
       <c r="E73">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="F73">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="G73">
-        <v>0.1912346098381414</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H73">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="B74" t="s">
         <v>11</v>
       </c>
       <c r="C74">
-        <v>36.57358557066742</v>
+        <v>35.84133099010302</v>
       </c>
       <c r="D74">
-        <v>22.83069636955243</v>
+        <v>22.37458514769363</v>
       </c>
       <c r="E74">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="F74">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="G74">
-        <v>0.2012778603742877</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H74">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1">
-        <v>46171</v>
+        <v>46168</v>
       </c>
       <c r="B75" t="s">
         <v>11</v>
       </c>
       <c r="C75">
-        <v>36.67481300942</v>
+        <v>36.23214279739292</v>
       </c>
       <c r="D75">
-        <v>22.95852861681004</v>
+        <v>22.93484792820123</v>
       </c>
       <c r="E75">
-        <v>0.9964953299999998</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="F75">
-        <v>0.9964953299999998</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="G75">
-        <v>0.2057034850411275</v>
+        <v>0.1925900763781823</v>
       </c>
       <c r="H75">
-        <v>0.9994474899999999</v>
+        <v>0.9992609200000001</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1">
-        <v>46174</v>
+        <v>46169</v>
       </c>
       <c r="B76" t="s">
         <v>11</v>
       </c>
       <c r="C76">
-        <v>36.84565507982974</v>
+        <v>36.4336692499184</v>
       </c>
       <c r="D76">
-        <v>23.15960292175205</v>
+        <v>22.75940954009856</v>
       </c>
       <c r="E76">
-        <v>0.99646052</v>
+        <v>0.9992099400000001</v>
       </c>
       <c r="F76">
-        <v>0.99646052</v>
+        <v>0.9992099400000001</v>
       </c>
       <c r="G76">
-        <v>0.2129379226426205</v>
+        <v>0.1912346098381414</v>
       </c>
       <c r="H76">
-        <v>0.9993986199999999</v>
+        <v>0.9992099400000001</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1">
-        <v>46175</v>
+        <v>46170</v>
       </c>
       <c r="B77" t="s">
         <v>11</v>
       </c>
       <c r="C77">
-        <v>36.88482057171844</v>
+        <v>36.57358557066742</v>
       </c>
       <c r="D77">
-        <v>23.03898938038424</v>
+        <v>22.83069636955243</v>
       </c>
       <c r="E77">
-        <v>0.99645675</v>
+        <v>0.9994435600000001</v>
       </c>
       <c r="F77">
-        <v>0.99645675</v>
+        <v>0.9994435600000001</v>
       </c>
       <c r="G77">
-        <v>0.2185229551183987</v>
+        <v>0.2012778603742877</v>
       </c>
       <c r="H77">
-        <v>0.9994034199999998</v>
+        <v>0.9994435600000001</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="1">
-        <v>46176</v>
+        <v>46171</v>
       </c>
       <c r="B78" t="s">
         <v>11</v>
       </c>
       <c r="C78">
-        <v>36.96809213745556</v>
+        <v>36.67481300942</v>
       </c>
       <c r="D78">
-        <v>22.99660212231548</v>
+        <v>22.95852861681004</v>
       </c>
       <c r="E78">
-        <v>0.9964706</v>
+        <v>0.9964953299999998</v>
       </c>
       <c r="F78">
-        <v>0.9964706</v>
+        <v>0.9964953299999998</v>
       </c>
       <c r="G78">
-        <v>0.2153385706032709</v>
+        <v>0.2057034850411275</v>
       </c>
       <c r="H78">
-        <v>0.9993955800000001</v>
+        <v>0.9994474899999999</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1">
-        <v>46177</v>
+        <v>46174</v>
       </c>
       <c r="B79" t="s">
         <v>11</v>
       </c>
       <c r="C79">
-        <v>37.13780815830533</v>
+        <v>36.84565507982974</v>
       </c>
       <c r="D79">
-        <v>22.74889586257873</v>
+        <v>23.15960292175205</v>
       </c>
       <c r="E79">
-        <v>0.9964706899999999</v>
+        <v>0.99646052</v>
       </c>
       <c r="F79">
-        <v>0.9964706899999999</v>
+        <v>0.99646052</v>
       </c>
       <c r="G79">
-        <v>0.2094594998678323</v>
+        <v>0.2129379226426205</v>
       </c>
       <c r="H79">
-        <v>0.99938478</v>
+        <v>0.9993986199999999</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1">
-        <v>46178</v>
+        <v>46175</v>
       </c>
       <c r="B80" t="s">
         <v>11</v>
       </c>
       <c r="C80">
-        <v>35.57681391373501</v>
+        <v>36.88482057171844</v>
       </c>
       <c r="D80">
-        <v>21.69452833602077</v>
+        <v>23.03898938038424</v>
       </c>
       <c r="E80">
-        <v>0.9964558499999999</v>
+        <v>0.99645675</v>
       </c>
       <c r="F80">
-        <v>0.9964558499999999</v>
+        <v>0.99645675</v>
       </c>
       <c r="G80">
-        <v>0.151404286858543</v>
+        <v>0.2185229551183987</v>
       </c>
       <c r="H80">
-        <v>0.9993850399999999</v>
+        <v>0.9994034199999998</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="1">
-        <v>46182</v>
+        <v>46176</v>
       </c>
       <c r="B81" t="s">
         <v>11</v>
       </c>
       <c r="C81">
-        <v>35.58815840295288</v>
+        <v>36.96809213745556</v>
       </c>
       <c r="D81">
-        <v>21.80812849732373</v>
+        <v>22.99660212231548</v>
       </c>
       <c r="E81">
-        <v>0.9962853900000002</v>
+        <v>0.9964706</v>
       </c>
       <c r="F81">
-        <v>0.9962853900000002</v>
+        <v>0.9964706</v>
       </c>
       <c r="G81">
-        <v>0.1559278910539408</v>
+        <v>0.2153385706032709</v>
       </c>
       <c r="H81">
-        <v>0.9992534400000002</v>
+        <v>0.9993955800000001</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="1">
-        <v>46183</v>
+        <v>46177</v>
       </c>
       <c r="B82" t="s">
         <v>11</v>
       </c>
       <c r="C82">
-        <v>34.74027179067053</v>
+        <v>37.13780815830533</v>
       </c>
       <c r="D82">
-        <v>21.20683390251297</v>
+        <v>22.74889586257873</v>
       </c>
       <c r="E82">
-        <v>0.9962360400000001</v>
+        <v>0.9964706899999999</v>
       </c>
       <c r="F82">
-        <v>0.9962360400000001</v>
+        <v>0.9964706899999999</v>
       </c>
       <c r="G82">
-        <v>0.132836418641906</v>
+        <v>0.2094594998678323</v>
       </c>
       <c r="H82">
-        <v>0.9992478800000001</v>
+        <v>0.99938478</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="1">
-        <v>46153</v>
+        <v>46178</v>
       </c>
       <c r="B83" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C83">
-        <v>52.70832779833182</v>
+        <v>35.57681391373501</v>
       </c>
       <c r="D83">
-        <v>23.99044674439659</v>
+        <v>21.69452833602077</v>
       </c>
       <c r="E83">
-        <v>0.9994000000000002</v>
+        <v>0.9964558499999999</v>
       </c>
       <c r="F83">
-        <v>0.9994000000000002</v>
+        <v>0.9964558499999999</v>
       </c>
       <c r="G83">
-        <v>0.5438253854918791</v>
+        <v>0.151404286858543</v>
       </c>
       <c r="H83">
-        <v>0.9994000000000002</v>
+        <v>0.9993850399999999</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="1">
-        <v>46154</v>
+        <v>46182</v>
       </c>
       <c r="B84" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C84">
-        <v>50.89464485280568</v>
+        <v>35.58815840295288</v>
       </c>
       <c r="D84">
-        <v>23.21558303176282</v>
+        <v>21.80812849732373</v>
       </c>
       <c r="E84">
-        <v>0.9996</v>
+        <v>0.9962853900000002</v>
       </c>
       <c r="F84">
-        <v>0.9996</v>
+        <v>0.9962853900000002</v>
       </c>
       <c r="G84">
-        <v>0.5034825029548833</v>
+        <v>0.1559278910539408</v>
       </c>
       <c r="H84">
-        <v>0.9996</v>
+        <v>0.9992534400000002</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1">
-        <v>46155</v>
+        <v>46183</v>
       </c>
       <c r="B85" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C85">
-        <v>51.8659994471731</v>
+        <v>34.74027179067053</v>
       </c>
       <c r="D85">
-        <v>23.7009037279043</v>
+        <v>21.20683390251297</v>
       </c>
       <c r="E85">
-        <v>1.0002</v>
+        <v>0.9962360400000001</v>
       </c>
       <c r="F85">
-        <v>1.0002</v>
+        <v>0.9962360400000001</v>
       </c>
       <c r="G85">
-        <v>0.533512029714132</v>
+        <v>0.132836418641906</v>
       </c>
       <c r="H85">
-        <v>1.0002</v>
+        <v>0.9992478800000001</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="1">
-        <v>46156</v>
+        <v>46184</v>
       </c>
       <c r="B86" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C86">
-        <v>52.4470179952828</v>
+        <v>35.56883979970284</v>
       </c>
       <c r="D86">
-        <v>23.76861704536814</v>
+        <v>21.93852986554604</v>
       </c>
       <c r="E86">
-        <v>0.9998</v>
+        <v>0.9961625199999998</v>
       </c>
       <c r="F86">
-        <v>0.9998</v>
+        <v>0.9961625199999998</v>
       </c>
       <c r="G86">
-        <v>0.5492634496849078</v>
+        <v>0.1710989694905902</v>
       </c>
       <c r="H86">
-        <v>0.9998</v>
+        <v>0.999197</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="1">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="B87" t="s">
         <v>12</v>
       </c>
       <c r="C87">
-        <v>50.81077380018606</v>
+        <v>52.70832779833182</v>
       </c>
       <c r="D87">
-        <v>22.76900580927995</v>
+        <v>23.99044674439659</v>
       </c>
       <c r="E87">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="F87">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="G87">
-        <v>0.4903296143797722</v>
+        <v>0.5438253854918791</v>
       </c>
       <c r="H87">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1">
-        <v>46160</v>
+        <v>46154</v>
       </c>
       <c r="B88" t="s">
         <v>12</v>
       </c>
       <c r="C88">
-        <v>49.50286387149169</v>
+        <v>50.89464485280568</v>
       </c>
       <c r="D88">
-        <v>22.24532119914133</v>
+        <v>23.21558303176282</v>
       </c>
       <c r="E88">
         <v>0.9996</v>
@@ -2685,7 +2685,7 @@
         <v>0.9996</v>
       </c>
       <c r="G88">
-        <v>0.4630591776162345</v>
+        <v>0.5034825029548833</v>
       </c>
       <c r="H88">
         <v>0.9996</v>
@@ -2693,224 +2693,224 @@
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="1">
-        <v>46161</v>
+        <v>46155</v>
       </c>
       <c r="B89" t="s">
         <v>12</v>
       </c>
       <c r="C89">
-        <v>49.29146729279496</v>
+        <v>51.8659994471731</v>
       </c>
       <c r="D89">
-        <v>22.22167836589682</v>
+        <v>23.7009037279043</v>
       </c>
       <c r="E89">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="F89">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="G89">
-        <v>0.4571659248870246</v>
+        <v>0.533512029714132</v>
       </c>
       <c r="H89">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="1">
-        <v>46162</v>
+        <v>46156</v>
       </c>
       <c r="B90" t="s">
         <v>12</v>
       </c>
       <c r="C90">
-        <v>50.88652370817657</v>
+        <v>52.4470179952828</v>
       </c>
       <c r="D90">
-        <v>22.93254398967657</v>
+        <v>23.76861704536814</v>
       </c>
       <c r="E90">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F90">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G90">
-        <v>0.5126171754864624</v>
+        <v>0.5492634496849078</v>
       </c>
       <c r="H90">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="1">
-        <v>46163</v>
+        <v>46157</v>
       </c>
       <c r="B91" t="s">
         <v>12</v>
       </c>
       <c r="C91">
-        <v>48.26646764818586</v>
+        <v>50.81077380018606</v>
       </c>
       <c r="D91">
-        <v>23.11655387625012</v>
+        <v>22.76900580927995</v>
       </c>
       <c r="E91">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="F91">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="G91">
-        <v>0.521243030947425</v>
+        <v>0.4903296143797722</v>
       </c>
       <c r="H91">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="1">
-        <v>46164</v>
+        <v>46160</v>
       </c>
       <c r="B92" t="s">
         <v>12</v>
       </c>
       <c r="C92">
-        <v>48.84737503703267</v>
+        <v>49.50286387149169</v>
       </c>
       <c r="D92">
-        <v>22.83557604744466</v>
+        <v>22.24532119914133</v>
       </c>
       <c r="E92">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="F92">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="G92">
-        <v>0.5438521997590966</v>
+        <v>0.4630591776162345</v>
       </c>
       <c r="H92">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="1">
-        <v>46167</v>
+        <v>46161</v>
       </c>
       <c r="B93" t="s">
         <v>12</v>
       </c>
       <c r="C93">
-        <v>48.85151560750146</v>
+        <v>49.29146729279496</v>
       </c>
       <c r="D93">
-        <v>22.83513820206554</v>
+        <v>22.22167836589682</v>
       </c>
       <c r="E93">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F93">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G93">
-        <v>0.5438521997590966</v>
+        <v>0.4571659248870246</v>
       </c>
       <c r="H93">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="1">
-        <v>46168</v>
+        <v>46162</v>
       </c>
       <c r="B94" t="s">
         <v>12</v>
       </c>
       <c r="C94">
-        <v>50.90437883274981</v>
+        <v>50.88652370817657</v>
       </c>
       <c r="D94">
-        <v>24.25672473501501</v>
+        <v>22.93254398967657</v>
       </c>
       <c r="E94">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F94">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G94">
-        <v>0.6130191115419561</v>
+        <v>0.5126171754864624</v>
       </c>
       <c r="H94">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="1">
-        <v>46169</v>
+        <v>46163</v>
       </c>
       <c r="B95" t="s">
         <v>12</v>
       </c>
       <c r="C95">
-        <v>50.47312432255841</v>
+        <v>48.26646764818586</v>
       </c>
       <c r="D95">
-        <v>23.84499305142194</v>
+        <v>23.11655387625012</v>
       </c>
       <c r="E95">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="F95">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="G95">
-        <v>0.5952317692821967</v>
+        <v>0.521243030947425</v>
       </c>
       <c r="H95">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="1">
-        <v>46170</v>
+        <v>46164</v>
       </c>
       <c r="B96" t="s">
         <v>12</v>
       </c>
       <c r="C96">
-        <v>50.84596269629946</v>
+        <v>48.84737503703267</v>
       </c>
       <c r="D96">
-        <v>23.7680603326165</v>
+        <v>22.83557604744466</v>
       </c>
       <c r="E96">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F96">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G96">
-        <v>0.606831065374982</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H96">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="1">
-        <v>46171</v>
+        <v>46167</v>
       </c>
       <c r="B97" t="s">
         <v>12</v>
       </c>
       <c r="C97">
-        <v>51.08372269965196</v>
+        <v>48.85151560750146</v>
       </c>
       <c r="D97">
-        <v>23.88880359436525</v>
+        <v>22.83513820206554</v>
       </c>
       <c r="E97">
         <v>0.9998999999999999</v>
@@ -2919,7 +2919,7 @@
         <v>0.9998999999999999</v>
       </c>
       <c r="G97">
-        <v>0.604420070348211</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H97">
         <v>0.9998999999999999</v>
@@ -2927,640 +2927,640 @@
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="1">
-        <v>46174</v>
+        <v>46168</v>
       </c>
       <c r="B98" t="s">
         <v>12</v>
       </c>
       <c r="C98">
-        <v>51.84875713649351</v>
+        <v>50.90437883274981</v>
       </c>
       <c r="D98">
-        <v>24.29466650399529</v>
+        <v>24.25672473501501</v>
       </c>
       <c r="E98">
-        <v>0.9998</v>
+        <v>0.9996999999999999</v>
       </c>
       <c r="F98">
-        <v>0.9998</v>
+        <v>0.9996999999999999</v>
       </c>
       <c r="G98">
-        <v>0.6282079224060508</v>
+        <v>0.6130191115419561</v>
       </c>
       <c r="H98">
-        <v>0.9998</v>
+        <v>0.9996999999999999</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="1">
-        <v>46175</v>
+        <v>46169</v>
       </c>
       <c r="B99" t="s">
         <v>12</v>
       </c>
       <c r="C99">
-        <v>53.42858844634741</v>
+        <v>50.47312432255841</v>
       </c>
       <c r="D99">
-        <v>24.82449061140869</v>
+        <v>23.84499305142194</v>
       </c>
       <c r="E99">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="F99">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="G99">
-        <v>0.6935709687814895</v>
+        <v>0.5952317692821967</v>
       </c>
       <c r="H99">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="1">
-        <v>46176</v>
+        <v>46170</v>
       </c>
       <c r="B100" t="s">
         <v>12</v>
       </c>
       <c r="C100">
-        <v>53.95056789686777</v>
+        <v>50.84596269629946</v>
       </c>
       <c r="D100">
-        <v>24.99295077214167</v>
+        <v>23.7680603326165</v>
       </c>
       <c r="E100">
-        <v>0.9996000000000002</v>
+        <v>0.9998</v>
       </c>
       <c r="F100">
-        <v>0.9996000000000002</v>
+        <v>0.9998</v>
       </c>
       <c r="G100">
-        <v>0.7088134081800193</v>
+        <v>0.606831065374982</v>
       </c>
       <c r="H100">
-        <v>0.9996000000000002</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="1">
-        <v>46177</v>
+        <v>46171</v>
       </c>
       <c r="B101" t="s">
         <v>12</v>
       </c>
       <c r="C101">
-        <v>53.29782764127071</v>
+        <v>51.08372269965196</v>
       </c>
       <c r="D101">
-        <v>24.48126483589962</v>
+        <v>23.88880359436525</v>
       </c>
       <c r="E101">
-        <v>1.0001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F101">
-        <v>1.0001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G101">
-        <v>0.6810341543458651</v>
+        <v>0.604420070348211</v>
       </c>
       <c r="H101">
-        <v>1.0001</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="1">
-        <v>46178</v>
+        <v>46174</v>
       </c>
       <c r="B102" t="s">
         <v>12</v>
       </c>
       <c r="C102">
-        <v>48.44949949587421</v>
+        <v>51.84875713649351</v>
       </c>
       <c r="D102">
-        <v>22.39103669390088</v>
+        <v>24.29466650399529</v>
       </c>
       <c r="E102">
-        <v>0.9995999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F102">
-        <v>0.9995999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G102">
-        <v>0.5260916717665549</v>
+        <v>0.6282079224060508</v>
       </c>
       <c r="H102">
-        <v>0.9995999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="1">
-        <v>46182</v>
+        <v>46175</v>
       </c>
       <c r="B103" t="s">
         <v>12</v>
       </c>
       <c r="C103">
-        <v>50.39371086612305</v>
+        <v>53.42858844634741</v>
       </c>
       <c r="D103">
-        <v>23.09650971949351</v>
+        <v>24.82449061140869</v>
       </c>
       <c r="E103">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="F103">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="G103">
-        <v>0.5832039354188183</v>
+        <v>0.6935709687814895</v>
       </c>
       <c r="H103">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="1">
-        <v>46183</v>
+        <v>46176</v>
       </c>
       <c r="B104" t="s">
         <v>12</v>
       </c>
       <c r="C104">
-        <v>48.17343634448468</v>
+        <v>53.95056789686777</v>
       </c>
       <c r="D104">
-        <v>22.05005999539094</v>
+        <v>24.99295077214167</v>
       </c>
       <c r="E104">
-        <v>0.9994999999999999</v>
+        <v>0.9996000000000002</v>
       </c>
       <c r="F104">
-        <v>0.9994999999999999</v>
+        <v>0.9996000000000002</v>
       </c>
       <c r="G104">
-        <v>0.5293597423345122</v>
+        <v>0.7088134081800193</v>
       </c>
       <c r="H104">
-        <v>0.9994999999999999</v>
+        <v>0.9996000000000002</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="1">
-        <v>46153</v>
+        <v>46177</v>
       </c>
       <c r="B105" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C105">
-        <v>57.1732166855686</v>
+        <v>53.29782764127071</v>
       </c>
       <c r="D105">
-        <v>23.50022751267814</v>
+        <v>24.48126483589962</v>
       </c>
       <c r="E105">
-        <v>0.9991</v>
+        <v>1.0001</v>
       </c>
       <c r="F105">
-        <v>0.9991</v>
+        <v>1.0001</v>
       </c>
       <c r="G105">
-        <v>0.6994110097039083</v>
+        <v>0.6810341543458651</v>
       </c>
       <c r="H105">
-        <v>0.9991</v>
+        <v>1.0001</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="1">
-        <v>46154</v>
+        <v>46178</v>
       </c>
       <c r="B106" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C106">
-        <v>54.77380642078597</v>
+        <v>48.44949949587421</v>
       </c>
       <c r="D106">
-        <v>22.55192940254518</v>
+        <v>22.39103669390088</v>
       </c>
       <c r="E106">
-        <v>0.9990000000000001</v>
+        <v>0.9995999999999999</v>
       </c>
       <c r="F106">
-        <v>0.9990000000000001</v>
+        <v>0.9995999999999999</v>
       </c>
       <c r="G106">
-        <v>0.6459175880844941</v>
+        <v>0.5260916717665549</v>
       </c>
       <c r="H106">
-        <v>0.9990000000000001</v>
+        <v>0.9995999999999999</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="1">
-        <v>46155</v>
+        <v>46182</v>
       </c>
       <c r="B107" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C107">
-        <v>56.32187380830906</v>
+        <v>50.39371086612305</v>
       </c>
       <c r="D107">
-        <v>23.17121437414109</v>
+        <v>23.09650971949351</v>
       </c>
       <c r="E107">
-        <v>0.9990000000000001</v>
+        <v>0.9997</v>
       </c>
       <c r="F107">
-        <v>0.9990000000000001</v>
+        <v>0.9997</v>
       </c>
       <c r="G107">
-        <v>0.6851523922954754</v>
+        <v>0.5832039354188183</v>
       </c>
       <c r="H107">
-        <v>0.9990000000000001</v>
+        <v>0.9997</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="1">
-        <v>46156</v>
+        <v>46183</v>
       </c>
       <c r="B108" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C108">
-        <v>56.15321618553139</v>
+        <v>48.17343634448468</v>
       </c>
       <c r="D108">
-        <v>22.95838347314443</v>
+        <v>22.05005999539094</v>
       </c>
       <c r="E108">
-        <v>0.9992</v>
+        <v>0.9994999999999999</v>
       </c>
       <c r="F108">
-        <v>0.9992</v>
+        <v>0.9994999999999999</v>
       </c>
       <c r="G108">
-        <v>0.6907028507208208</v>
+        <v>0.5293597423345122</v>
       </c>
       <c r="H108">
-        <v>0.9992</v>
+        <v>0.9994999999999999</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="1">
-        <v>46157</v>
+        <v>46184</v>
       </c>
       <c r="B109" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C109">
-        <v>54.47755813049488</v>
+        <v>52.85189183366637</v>
       </c>
       <c r="D109">
-        <v>22.0083816089626</v>
+        <v>23.55442526604671</v>
       </c>
       <c r="E109">
-        <v>0.9986</v>
+        <v>0.9996</v>
       </c>
       <c r="F109">
-        <v>0.9986</v>
+        <v>0.9996</v>
       </c>
       <c r="G109">
-        <v>0.6220895940829376</v>
+        <v>0.63260121118737</v>
       </c>
       <c r="H109">
-        <v>0.9986</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B110" t="s">
         <v>13</v>
       </c>
       <c r="C110">
-        <v>52.6278781150669</v>
+        <v>57.1732166855686</v>
       </c>
       <c r="D110">
-        <v>21.5357353870778</v>
+        <v>23.50022751267814</v>
       </c>
       <c r="E110">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F110">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G110">
-        <v>0.5845134636435627</v>
+        <v>0.6994110097039083</v>
       </c>
       <c r="H110">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B111" t="s">
         <v>13</v>
       </c>
       <c r="C111">
-        <v>54.91583234840245</v>
+        <v>54.77380642078597</v>
       </c>
       <c r="D111">
-        <v>22.38321645985006</v>
+        <v>22.55192940254518</v>
       </c>
       <c r="E111">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F111">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G111">
-        <v>0.6596976539194066</v>
+        <v>0.6459175880844941</v>
       </c>
       <c r="H111">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B112" t="s">
         <v>13</v>
       </c>
       <c r="C112">
-        <v>53.91712298548793</v>
+        <v>56.32187380830906</v>
       </c>
       <c r="D112">
-        <v>22.73711181201267</v>
+        <v>23.17121437414109</v>
       </c>
       <c r="E112">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F112">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G112">
-        <v>0.6737329602396263</v>
+        <v>0.6851523922954754</v>
       </c>
       <c r="H112">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="1">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="B113" t="s">
         <v>13</v>
       </c>
       <c r="C113">
-        <v>55.19651747515625</v>
+        <v>56.15321618553139</v>
       </c>
       <c r="D113">
-        <v>22.79462037330554</v>
+        <v>22.95838347314443</v>
       </c>
       <c r="E113">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
       <c r="F113">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
       <c r="G113">
-        <v>0.7139885317003913</v>
+        <v>0.6907028507208208</v>
       </c>
       <c r="H113">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="1">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="B114" t="s">
         <v>13</v>
       </c>
       <c r="C114">
-        <v>55.28054997487197</v>
+        <v>54.47755813049488</v>
       </c>
       <c r="D114">
-        <v>23.00160891539877</v>
+        <v>22.0083816089626</v>
       </c>
       <c r="E114">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="F114">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="G114">
-        <v>0.7139885317003913</v>
+        <v>0.6220895940829376</v>
       </c>
       <c r="H114">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="1">
-        <v>46168</v>
+        <v>46161</v>
       </c>
       <c r="B115" t="s">
         <v>13</v>
       </c>
       <c r="C115">
-        <v>58.75156728873073</v>
+        <v>52.6278781150669</v>
       </c>
       <c r="D115">
-        <v>24.84249654093248</v>
+        <v>21.5357353870778</v>
       </c>
       <c r="E115">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="F115">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="G115">
-        <v>0.8184872182632257</v>
+        <v>0.5845134636435627</v>
       </c>
       <c r="H115">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="1">
-        <v>46169</v>
+        <v>46162</v>
       </c>
       <c r="B116" t="s">
         <v>13</v>
       </c>
       <c r="C116">
-        <v>57.86771234337395</v>
+        <v>54.91583234840245</v>
       </c>
       <c r="D116">
-        <v>24.21066615243091</v>
+        <v>22.38321645985006</v>
       </c>
       <c r="E116">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="F116">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="G116">
-        <v>0.798997241708943</v>
+        <v>0.6596976539194066</v>
       </c>
       <c r="H116">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="1">
-        <v>46170</v>
+        <v>46163</v>
       </c>
       <c r="B117" t="s">
         <v>13</v>
       </c>
       <c r="C117">
-        <v>58.18666682631797</v>
+        <v>53.91712298548793</v>
       </c>
       <c r="D117">
-        <v>24.09552344282839</v>
+        <v>22.73711181201267</v>
       </c>
       <c r="E117">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="F117">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="G117">
-        <v>0.8165093478664007</v>
+        <v>0.6737329602396263</v>
       </c>
       <c r="H117">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="1">
-        <v>46171</v>
+        <v>46164</v>
       </c>
       <c r="B118" t="s">
         <v>13</v>
       </c>
       <c r="C118">
-        <v>58.79256019733606</v>
+        <v>55.19651747515625</v>
       </c>
       <c r="D118">
-        <v>24.33854853448823</v>
+        <v>22.79462037330554</v>
       </c>
       <c r="E118">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F118">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G118">
-        <v>0.8152654642198496</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H118">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="1">
-        <v>46174</v>
+        <v>46167</v>
       </c>
       <c r="B119" t="s">
         <v>13</v>
       </c>
       <c r="C119">
-        <v>58.97156722185718</v>
+        <v>55.28054997487197</v>
       </c>
       <c r="D119">
-        <v>24.48296361348067</v>
+        <v>23.00160891539877</v>
       </c>
       <c r="E119">
-        <v>0.9990000000000001</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="F119">
-        <v>0.9990000000000001</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="G119">
-        <v>0.8243563865851753</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H119">
-        <v>0.9990000000000001</v>
+        <v>0.9989000000000001</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="1">
-        <v>46175</v>
+        <v>46168</v>
       </c>
       <c r="B120" t="s">
         <v>13</v>
       </c>
       <c r="C120">
-        <v>61.6542902214027</v>
+        <v>58.75156728873073</v>
       </c>
       <c r="D120">
-        <v>25.06517348653028</v>
+        <v>24.84249654093248</v>
       </c>
       <c r="E120">
-        <v>0.9988</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="F120">
-        <v>0.9988</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="G120">
-        <v>0.9299077697948877</v>
+        <v>0.8184872182632257</v>
       </c>
       <c r="H120">
-        <v>0.9988</v>
+        <v>0.9989000000000001</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="1">
-        <v>46176</v>
+        <v>46169</v>
       </c>
       <c r="B121" t="s">
         <v>13</v>
       </c>
       <c r="C121">
-        <v>63.0681947750049</v>
+        <v>57.86771234337395</v>
       </c>
       <c r="D121">
-        <v>25.58770976382014</v>
+        <v>24.21066615243091</v>
       </c>
       <c r="E121">
-        <v>0.9988000000000002</v>
+        <v>0.9986999999999999</v>
       </c>
       <c r="F121">
-        <v>0.9988000000000002</v>
+        <v>0.9986999999999999</v>
       </c>
       <c r="G121">
-        <v>0.9639112148600193</v>
+        <v>0.798997241708943</v>
       </c>
       <c r="H121">
-        <v>0.9988000000000002</v>
+        <v>0.9986999999999999</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="1">
-        <v>46177</v>
+        <v>46170</v>
       </c>
       <c r="B122" t="s">
         <v>13</v>
       </c>
       <c r="C122">
-        <v>61.53154955456358</v>
+        <v>58.18666682631797</v>
       </c>
       <c r="D122">
-        <v>24.75810538712983</v>
+        <v>24.09552344282839</v>
       </c>
       <c r="E122">
         <v>0.9991</v>
@@ -3569,7 +3569,7 @@
         <v>0.9991</v>
       </c>
       <c r="G122">
-        <v>0.9225710173552821</v>
+        <v>0.8165093478664007</v>
       </c>
       <c r="H122">
         <v>0.9991</v>
@@ -3577,926 +3577,926 @@
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="1">
-        <v>46178</v>
+        <v>46171</v>
       </c>
       <c r="B123" t="s">
         <v>13</v>
       </c>
       <c r="C123">
-        <v>55.42493637343647</v>
+        <v>58.79256019733606</v>
       </c>
       <c r="D123">
-        <v>22.47054621698377</v>
+        <v>24.33854853448823</v>
       </c>
       <c r="E123">
-        <v>0.9987</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="F123">
-        <v>0.9987</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="G123">
-        <v>0.7217717116249776</v>
+        <v>0.8152654642198496</v>
       </c>
       <c r="H123">
-        <v>0.9987</v>
+        <v>0.9989999999999999</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="1">
-        <v>46182</v>
+        <v>46174</v>
       </c>
       <c r="B124" t="s">
         <v>13</v>
       </c>
       <c r="C124">
-        <v>57.84835101034041</v>
+        <v>58.97156722185718</v>
       </c>
       <c r="D124">
-        <v>23.24662656171655</v>
+        <v>24.48296361348067</v>
       </c>
       <c r="E124">
-        <v>0.999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F124">
-        <v>0.999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G124">
-        <v>0.7931280733869936</v>
+        <v>0.8243563865851753</v>
       </c>
       <c r="H124">
-        <v>0.999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="1">
-        <v>46183</v>
+        <v>46175</v>
       </c>
       <c r="B125" t="s">
         <v>13</v>
       </c>
       <c r="C125">
-        <v>55.28729760663236</v>
+        <v>61.6542902214027</v>
       </c>
       <c r="D125">
-        <v>22.10409273362112</v>
+        <v>25.06517348653028</v>
       </c>
       <c r="E125">
-        <v>0.9987999999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="F125">
-        <v>0.9987999999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="G125">
-        <v>0.7273219753588771</v>
+        <v>0.9299077697948877</v>
       </c>
       <c r="H125">
-        <v>0.9987999999999999</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" s="1">
-        <v>46153</v>
+        <v>46176</v>
       </c>
       <c r="B126" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C126">
-        <v>35.78646526282436</v>
+        <v>63.0681947750049</v>
       </c>
       <c r="D126">
-        <v>18.96635091925032</v>
+        <v>25.58770976382014</v>
       </c>
       <c r="E126">
-        <v>0.9996491399999999</v>
+        <v>0.9988000000000002</v>
       </c>
       <c r="F126">
-        <v>0.9996491399999999</v>
+        <v>0.9988000000000002</v>
       </c>
       <c r="G126">
-        <v>0.2240600969213613</v>
+        <v>0.9639112148600193</v>
       </c>
       <c r="H126">
-        <v>0.9985614899999999</v>
+        <v>0.9988000000000002</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" s="1">
-        <v>46154</v>
+        <v>46177</v>
       </c>
       <c r="B127" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C127">
-        <v>35.71584102184062</v>
+        <v>61.53154955456358</v>
       </c>
       <c r="D127">
-        <v>18.62432950231353</v>
+        <v>24.75810538712983</v>
       </c>
       <c r="E127">
-        <v>0.99965481</v>
+        <v>0.9991</v>
       </c>
       <c r="F127">
-        <v>0.99965481</v>
+        <v>0.9991</v>
       </c>
       <c r="G127">
-        <v>0.2104844827747143</v>
+        <v>0.9225710173552821</v>
       </c>
       <c r="H127">
-        <v>0.9985622199999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="1">
-        <v>46155</v>
+        <v>46178</v>
       </c>
       <c r="B128" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C128">
-        <v>35.95182028203252</v>
+        <v>55.42493637343647</v>
       </c>
       <c r="D128">
-        <v>18.95670796791552</v>
+        <v>22.47054621698377</v>
       </c>
       <c r="E128">
-        <v>0.9996515200000001</v>
+        <v>0.9987</v>
       </c>
       <c r="F128">
-        <v>0.9996515200000001</v>
+        <v>0.9987</v>
       </c>
       <c r="G128">
-        <v>0.2259035693959275</v>
+        <v>0.7217717116249776</v>
       </c>
       <c r="H128">
-        <v>0.99855193</v>
+        <v>0.9987</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="1">
-        <v>46156</v>
+        <v>46182</v>
       </c>
       <c r="B129" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C129">
-        <v>36.14451597805883</v>
+        <v>57.84835101034041</v>
       </c>
       <c r="D129">
-        <v>18.86297660538653</v>
+        <v>23.24662656171655</v>
       </c>
       <c r="E129">
-        <v>0.9996563399999999</v>
+        <v>0.999</v>
       </c>
       <c r="F129">
-        <v>0.9996563399999999</v>
+        <v>0.999</v>
       </c>
       <c r="G129">
-        <v>0.2362110061840785</v>
+        <v>0.7931280733869936</v>
       </c>
       <c r="H129">
-        <v>0.99857265</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" s="1">
-        <v>46157</v>
+        <v>46183</v>
       </c>
       <c r="B130" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C130">
-        <v>35.32805803135546</v>
+        <v>55.28729760663236</v>
       </c>
       <c r="D130">
-        <v>18.35643242381478</v>
+        <v>22.10409273362112</v>
       </c>
       <c r="E130">
-        <v>0.9997415800000001</v>
+        <v>0.9987999999999999</v>
       </c>
       <c r="F130">
-        <v>0.9997415800000001</v>
+        <v>0.9987999999999999</v>
       </c>
       <c r="G130">
-        <v>0.2023559161375383</v>
+        <v>0.7273219753588771</v>
       </c>
       <c r="H130">
-        <v>0.9986639900000002</v>
+        <v>0.9987999999999999</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" s="1">
-        <v>46160</v>
+        <v>46184</v>
       </c>
       <c r="B131" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C131">
-        <v>34.83995455757461</v>
+        <v>61.41553176023326</v>
       </c>
       <c r="D131">
-        <v>18.02301281718857</v>
+        <v>23.99650204363438</v>
       </c>
       <c r="E131">
-        <v>0.9996851299999999</v>
+        <v>0.9986000000000002</v>
       </c>
       <c r="F131">
-        <v>0.9996851299999999</v>
+        <v>0.9986000000000002</v>
       </c>
       <c r="G131">
-        <v>0.1850932291737926</v>
+        <v>0.8722037562794076</v>
       </c>
       <c r="H131">
-        <v>0.99857724</v>
+        <v>0.9986000000000002</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B132" t="s">
         <v>14</v>
       </c>
       <c r="C132">
-        <v>34.45479308705605</v>
+        <v>35.78646526282436</v>
       </c>
       <c r="D132">
-        <v>18.09576834566068</v>
+        <v>18.96635091925032</v>
       </c>
       <c r="E132">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="F132">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="G132">
-        <v>0.1784731209386736</v>
+        <v>0.2240600969213613</v>
       </c>
       <c r="H132">
-        <v>0.9985337599999999</v>
+        <v>0.9985614899999999</v>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B133" t="s">
         <v>14</v>
       </c>
       <c r="C133">
-        <v>34.96336277390787</v>
+        <v>35.71584102184062</v>
       </c>
       <c r="D133">
-        <v>18.34938420029253</v>
+        <v>18.62432950231353</v>
       </c>
       <c r="E133">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="F133">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="G133">
-        <v>0.2009313391215752</v>
+        <v>0.2104844827747143</v>
       </c>
       <c r="H133">
-        <v>0.99848777</v>
+        <v>0.9985622199999999</v>
       </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B134" t="s">
         <v>14</v>
       </c>
       <c r="C134">
-        <v>34.44616924817128</v>
+        <v>35.95182028203252</v>
       </c>
       <c r="D134">
-        <v>18.60085625074367</v>
+        <v>18.95670796791552</v>
       </c>
       <c r="E134">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="F134">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="G134">
-        <v>0.2124957180214682</v>
+        <v>0.2259035693959275</v>
       </c>
       <c r="H134">
-        <v>0.9985085200000001</v>
+        <v>0.99855193</v>
       </c>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="1">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="B135" t="s">
         <v>14</v>
       </c>
       <c r="C135">
-        <v>34.62137220937314</v>
+        <v>36.14451597805883</v>
       </c>
       <c r="D135">
-        <v>18.28780484745949</v>
+        <v>18.86297660538653</v>
       </c>
       <c r="E135">
-        <v>0.9996106299999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="F135">
-        <v>0.9996106299999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="G135">
-        <v>0.2145907067863493</v>
+        <v>0.2362110061840785</v>
       </c>
       <c r="H135">
-        <v>0.9932939299999999</v>
+        <v>0.99857265</v>
       </c>
     </row>
     <row r="136" spans="1:8">
       <c r="A136" s="1">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="B136" t="s">
         <v>14</v>
       </c>
       <c r="C136">
-        <v>34.6540695486741</v>
+        <v>35.32805803135546</v>
       </c>
       <c r="D136">
-        <v>18.36409048915342</v>
+        <v>18.35643242381478</v>
       </c>
       <c r="E136">
-        <v>0.9995448900000001</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="F136">
-        <v>0.9995448900000001</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="G136">
-        <v>0.2145907067863493</v>
+        <v>0.2023559161375383</v>
       </c>
       <c r="H136">
-        <v>0.9984302600000001</v>
+        <v>0.9986639900000002</v>
       </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="1">
-        <v>46168</v>
+        <v>46160</v>
       </c>
       <c r="B137" t="s">
         <v>14</v>
       </c>
       <c r="C137">
-        <v>35.4820130509417</v>
+        <v>34.83995455757461</v>
       </c>
       <c r="D137">
-        <v>19.20292041814603</v>
+        <v>18.02301281718857</v>
       </c>
       <c r="E137">
-        <v>0.9995448900000001</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="F137">
-        <v>0.9995448900000001</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="G137">
-        <v>0.2553172934903569</v>
+        <v>0.1850932291737926</v>
       </c>
       <c r="H137">
-        <v>0.9984302600000001</v>
+        <v>0.99857724</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="1">
-        <v>46169</v>
+        <v>46161</v>
       </c>
       <c r="B138" t="s">
         <v>14</v>
       </c>
       <c r="C138">
-        <v>35.71913468603401</v>
+        <v>34.45479308705605</v>
       </c>
       <c r="D138">
-        <v>18.96318693998171</v>
+        <v>18.09576834566068</v>
       </c>
       <c r="E138">
-        <v>0.99955466</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="F138">
-        <v>0.99955466</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="G138">
-        <v>0.2536413280520453</v>
+        <v>0.1784731209386736</v>
       </c>
       <c r="H138">
-        <v>0.9984700500000001</v>
+        <v>0.9985337599999999</v>
       </c>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="1">
-        <v>46170</v>
+        <v>46162</v>
       </c>
       <c r="B139" t="s">
         <v>14</v>
       </c>
       <c r="C139">
-        <v>35.76226417354731</v>
+        <v>34.96336277390787</v>
       </c>
       <c r="D139">
-        <v>18.89050847207122</v>
+        <v>18.34938420029253</v>
       </c>
       <c r="E139">
-        <v>0.9995525399999999</v>
+        <v>0.99963413</v>
       </c>
       <c r="F139">
-        <v>0.9995525399999999</v>
+        <v>0.99963413</v>
       </c>
       <c r="G139">
-        <v>0.2580826940041561</v>
+        <v>0.2009313391215752</v>
       </c>
       <c r="H139">
-        <v>0.99847732</v>
+        <v>0.99848777</v>
       </c>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="1">
-        <v>46171</v>
+        <v>46163</v>
       </c>
       <c r="B140" t="s">
         <v>14</v>
       </c>
       <c r="C140">
-        <v>35.84309020154227</v>
+        <v>34.44616924817128</v>
       </c>
       <c r="D140">
-        <v>19.06511612333149</v>
+        <v>18.60085625074367</v>
       </c>
       <c r="E140">
-        <v>0.9995533299999999</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="F140">
-        <v>0.9995533299999999</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="G140">
-        <v>0.2619374017254759</v>
+        <v>0.2124957180214682</v>
       </c>
       <c r="H140">
-        <v>0.99849382</v>
+        <v>0.9985085200000001</v>
       </c>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="1">
-        <v>46174</v>
+        <v>46164</v>
       </c>
       <c r="B141" t="s">
         <v>14</v>
       </c>
       <c r="C141">
-        <v>36.27022125574057</v>
+        <v>34.62137220937314</v>
       </c>
       <c r="D141">
-        <v>19.32711369104533</v>
+        <v>18.28780484745949</v>
       </c>
       <c r="E141">
-        <v>0.9995550400000001</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="F141">
-        <v>0.9995550400000001</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="G141">
-        <v>0.2764348160433892</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H141">
-        <v>0.9985177199999999</v>
+        <v>0.9932939299999999</v>
       </c>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="1">
-        <v>46175</v>
+        <v>46167</v>
       </c>
       <c r="B142" t="s">
         <v>14</v>
       </c>
       <c r="C142">
-        <v>36.57133692946976</v>
+        <v>34.6540695486741</v>
       </c>
       <c r="D142">
-        <v>19.33857330565742</v>
+        <v>18.36409048915342</v>
       </c>
       <c r="E142">
-        <v>0.9994989200000002</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="F142">
-        <v>0.9994989200000002</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="G142">
-        <v>0.2931947261624381</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H142">
-        <v>0.9984577800000001</v>
+        <v>0.9984302600000001</v>
       </c>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="1">
-        <v>46176</v>
+        <v>46168</v>
       </c>
       <c r="B143" t="s">
         <v>14</v>
       </c>
       <c r="C143">
-        <v>36.8289666508657</v>
+        <v>35.4820130509417</v>
       </c>
       <c r="D143">
-        <v>19.43137154505686</v>
+        <v>19.20292041814603</v>
       </c>
       <c r="E143">
-        <v>0.9994838199999998</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="F143">
-        <v>0.9994838199999998</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="G143">
-        <v>0.2996471994933361</v>
+        <v>0.2553172934903569</v>
       </c>
       <c r="H143">
-        <v>0.9984549499999998</v>
+        <v>0.9984302600000001</v>
       </c>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="1">
-        <v>46177</v>
+        <v>46169</v>
       </c>
       <c r="B144" t="s">
         <v>14</v>
       </c>
       <c r="C144">
-        <v>36.76760036565858</v>
+        <v>35.71913468603401</v>
       </c>
       <c r="D144">
-        <v>18.98774474764188</v>
+        <v>18.96318693998171</v>
       </c>
       <c r="E144">
-        <v>0.99948384</v>
+        <v>0.99955466</v>
       </c>
       <c r="F144">
-        <v>0.99948384</v>
+        <v>0.99955466</v>
       </c>
       <c r="G144">
-        <v>0.2807085470912787</v>
+        <v>0.2536413280520453</v>
       </c>
       <c r="H144">
-        <v>0.9984696899999999</v>
+        <v>0.9984700500000001</v>
       </c>
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="1">
-        <v>46178</v>
+        <v>46170</v>
       </c>
       <c r="B145" t="s">
         <v>14</v>
       </c>
       <c r="C145">
-        <v>34.71533981972338</v>
+        <v>35.76226417354731</v>
       </c>
       <c r="D145">
-        <v>17.87291658642534</v>
+        <v>18.89050847207122</v>
       </c>
       <c r="E145">
-        <v>0.9994584900000001</v>
+        <v>0.9995525399999999</v>
       </c>
       <c r="F145">
-        <v>0.9994584900000001</v>
+        <v>0.9995525399999999</v>
       </c>
       <c r="G145">
-        <v>0.2090599057587512</v>
+        <v>0.2580826940041561</v>
       </c>
       <c r="H145">
-        <v>0.9984184600000001</v>
+        <v>0.99847732</v>
       </c>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="1">
-        <v>46182</v>
+        <v>46171</v>
       </c>
       <c r="B146" t="s">
         <v>14</v>
       </c>
       <c r="C146">
-        <v>35.03764279648938</v>
+        <v>35.84309020154227</v>
       </c>
       <c r="D146">
-        <v>18.26945792236365</v>
+        <v>19.06511612333149</v>
       </c>
       <c r="E146">
-        <v>0.9994212399999999</v>
+        <v>0.9995533299999999</v>
       </c>
       <c r="F146">
-        <v>0.9994212399999999</v>
+        <v>0.9995533299999999</v>
       </c>
       <c r="G146">
-        <v>0.2361271247979846</v>
+        <v>0.2619374017254759</v>
       </c>
       <c r="H146">
-        <v>0.99833116</v>
+        <v>0.99849382</v>
       </c>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="1">
-        <v>46183</v>
+        <v>46174</v>
       </c>
       <c r="B147" t="s">
         <v>14</v>
       </c>
       <c r="C147">
-        <v>34.21862503455022</v>
+        <v>36.27022125574057</v>
       </c>
       <c r="D147">
-        <v>17.67576313213109</v>
+        <v>19.32711369104533</v>
       </c>
       <c r="E147">
-        <v>0.9991916599999998</v>
+        <v>0.9995550400000001</v>
       </c>
       <c r="F147">
-        <v>0.9991916599999998</v>
+        <v>0.9995550400000001</v>
       </c>
       <c r="G147">
-        <v>0.2040318815758499</v>
+        <v>0.2764348160433892</v>
       </c>
       <c r="H147">
-        <v>0.99808951</v>
+        <v>0.9985177199999999</v>
       </c>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="1">
-        <v>46153</v>
+        <v>46175</v>
       </c>
       <c r="B148" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C148">
-        <v>28.12253390077671</v>
+        <v>36.57133692946976</v>
       </c>
       <c r="D148">
-        <v>23.58699683751922</v>
+        <v>19.33857330565742</v>
       </c>
       <c r="E148">
-        <v>0.9997295369999999</v>
+        <v>0.9994989200000002</v>
       </c>
       <c r="F148">
-        <v>0.9997295369999999</v>
+        <v>0.9994989200000002</v>
       </c>
       <c r="G148">
-        <v>0.03368732240295347</v>
+        <v>0.2931947261624381</v>
       </c>
       <c r="H148">
-        <v>0.9997295369999999</v>
+        <v>0.9984577800000001</v>
       </c>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="1">
-        <v>46154</v>
+        <v>46176</v>
       </c>
       <c r="B149" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C149">
-        <v>28.17715727830483</v>
+        <v>36.8289666508657</v>
       </c>
       <c r="D149">
-        <v>23.63894513078866</v>
+        <v>19.43137154505686</v>
       </c>
       <c r="E149">
-        <v>1.000319473</v>
+        <v>0.9994838199999998</v>
       </c>
       <c r="F149">
-        <v>1.000319473</v>
+        <v>0.9994838199999998</v>
       </c>
       <c r="G149">
-        <v>0.03515547182056333</v>
+        <v>0.2996471994933361</v>
       </c>
       <c r="H149">
-        <v>1.000319473</v>
+        <v>0.9984549499999998</v>
       </c>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" s="1">
-        <v>46155</v>
+        <v>46177</v>
       </c>
       <c r="B150" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C150">
-        <v>28.59002627414054</v>
+        <v>36.76760036565858</v>
       </c>
       <c r="D150">
-        <v>23.96230704059692</v>
+        <v>18.98774474764188</v>
       </c>
       <c r="E150">
-        <v>0.9999999989999999</v>
+        <v>0.99948384</v>
       </c>
       <c r="F150">
-        <v>0.9999999989999999</v>
+        <v>0.99948384</v>
       </c>
       <c r="G150">
-        <v>0.05179637495949674</v>
+        <v>0.2807085470912787</v>
       </c>
       <c r="H150">
-        <v>0.9999999989999999</v>
+        <v>0.9984696899999999</v>
       </c>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="1">
-        <v>46156</v>
+        <v>46178</v>
       </c>
       <c r="B151" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C151">
-        <v>28.56217859389523</v>
+        <v>34.71533981972338</v>
       </c>
       <c r="D151">
-        <v>23.9411987302529</v>
+        <v>17.87291658642534</v>
       </c>
       <c r="E151">
-        <v>1</v>
+        <v>0.9994584900000001</v>
       </c>
       <c r="F151">
-        <v>1</v>
+        <v>0.9994584900000001</v>
       </c>
       <c r="G151">
-        <v>0.04837024516756849</v>
+        <v>0.2090599057587512</v>
       </c>
       <c r="H151">
-        <v>1</v>
+        <v>0.9984184600000001</v>
       </c>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="1">
-        <v>46157</v>
+        <v>46182</v>
       </c>
       <c r="B152" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C152">
-        <v>28.57618675936338</v>
+        <v>35.03764279648938</v>
       </c>
       <c r="D152">
-        <v>23.9576220541054</v>
+        <v>18.26945792236365</v>
       </c>
       <c r="E152">
-        <v>0.999503249</v>
+        <v>0.9994212399999999</v>
       </c>
       <c r="F152">
-        <v>0.999503249</v>
+        <v>0.9994212399999999</v>
       </c>
       <c r="G152">
-        <v>0.04983868243960732</v>
+        <v>0.2361271247979846</v>
       </c>
       <c r="H152">
-        <v>0.999503249</v>
+        <v>0.99833116</v>
       </c>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" s="1">
-        <v>46160</v>
+        <v>46183</v>
       </c>
       <c r="B153" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C153">
-        <v>28.68951918518517</v>
+        <v>34.21862503455022</v>
       </c>
       <c r="D153">
-        <v>24.06134728453882</v>
+        <v>17.67576313213109</v>
       </c>
       <c r="E153">
-        <v>0.999503249</v>
+        <v>0.9991916599999998</v>
       </c>
       <c r="F153">
-        <v>0.999503249</v>
+        <v>0.9991916599999998</v>
       </c>
       <c r="G153">
-        <v>0.04983868243960732</v>
+        <v>0.2040318815758499</v>
       </c>
       <c r="H153">
-        <v>0.999503249</v>
+        <v>0.99808951</v>
       </c>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" s="1">
-        <v>46161</v>
+        <v>46184</v>
       </c>
       <c r="B154" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C154">
-        <v>28.31167386654059</v>
+        <v>35.57723814348832</v>
       </c>
       <c r="D154">
-        <v>23.75157719455474</v>
+        <v>18.6194204925492</v>
       </c>
       <c r="E154">
-        <v>1.000177331</v>
+        <v>0.9989294799999999</v>
       </c>
       <c r="F154">
-        <v>1.000177331</v>
+        <v>0.9989294799999999</v>
       </c>
       <c r="G154">
-        <v>0.04053938625111919</v>
+        <v>0.2618536482073486</v>
       </c>
       <c r="H154">
-        <v>1.000177331</v>
+        <v>0.9977895699999999</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" s="1">
-        <v>46162</v>
+        <v>46153</v>
       </c>
       <c r="B155" t="s">
         <v>15</v>
       </c>
       <c r="C155">
-        <v>28.57911382310097</v>
+        <v>28.12253390077671</v>
       </c>
       <c r="D155">
-        <v>23.89431741541233</v>
+        <v>23.58699683751922</v>
       </c>
       <c r="E155">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="F155">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="G155">
-        <v>0.04690190590044785</v>
+        <v>0.03368732240295347</v>
       </c>
       <c r="H155">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" s="1">
-        <v>46163</v>
+        <v>46154</v>
       </c>
       <c r="B156" t="s">
         <v>15</v>
       </c>
       <c r="C156">
-        <v>28.55785065378643</v>
+        <v>28.17715727830483</v>
       </c>
       <c r="D156">
-        <v>24.04274714970193</v>
+        <v>23.63894513078866</v>
       </c>
       <c r="E156">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="F156">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="G156">
-        <v>0.05228572319419666</v>
+        <v>0.03515547182056333</v>
       </c>
       <c r="H156">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" s="1">
-        <v>46164</v>
+        <v>46155</v>
       </c>
       <c r="B157" t="s">
         <v>15</v>
       </c>
       <c r="C157">
-        <v>28.50194638163107</v>
+        <v>28.59002627414054</v>
       </c>
       <c r="D157">
-        <v>23.99272397156045</v>
+        <v>23.96230704059692</v>
       </c>
       <c r="E157">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F157">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G157">
-        <v>0.04934923597154284</v>
+        <v>0.05179637495949674</v>
       </c>
       <c r="H157">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="1">
-        <v>46167</v>
+        <v>46156</v>
       </c>
       <c r="B158" t="s">
         <v>15</v>
       </c>
       <c r="C158">
-        <v>28.55106858744498</v>
+        <v>28.56217859389523</v>
       </c>
       <c r="D158">
-        <v>23.9768329565351</v>
+        <v>23.9411987302529</v>
       </c>
       <c r="E158">
         <v>1</v>
@@ -4505,7 +4505,7 @@
         <v>1</v>
       </c>
       <c r="G158">
-        <v>0.05571185335164408</v>
+        <v>0.04837024516756849</v>
       </c>
       <c r="H158">
         <v>1</v>
@@ -4513,860 +4513,1094 @@
     </row>
     <row r="159" spans="1:8">
       <c r="A159" s="1">
-        <v>46168</v>
+        <v>46157</v>
       </c>
       <c r="B159" t="s">
         <v>15</v>
       </c>
       <c r="C159">
-        <v>28.54681541456266</v>
+        <v>28.57618675936338</v>
       </c>
       <c r="D159">
-        <v>23.97386168967948</v>
+        <v>23.9576220541054</v>
       </c>
       <c r="E159">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="F159">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="G159">
-        <v>0.04837034303541388</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H159">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="160" spans="1:8">
       <c r="A160" s="1">
-        <v>46169</v>
+        <v>46160</v>
       </c>
       <c r="B160" t="s">
         <v>15</v>
       </c>
       <c r="C160">
-        <v>28.83672936868491</v>
+        <v>28.68951918518517</v>
       </c>
       <c r="D160">
-        <v>24.203511281145</v>
+        <v>24.06134728453882</v>
       </c>
       <c r="E160">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="F160">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="G160">
-        <v>0.05962723282507953</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H160">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="161" spans="1:8">
       <c r="A161" s="1">
-        <v>46170</v>
+        <v>46161</v>
       </c>
       <c r="B161" t="s">
         <v>15</v>
       </c>
       <c r="C161">
-        <v>28.88109630394224</v>
+        <v>28.31167386654059</v>
       </c>
       <c r="D161">
-        <v>24.34085451035401</v>
+        <v>23.75157719455474</v>
       </c>
       <c r="E161">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
       <c r="F161">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
       <c r="G161">
-        <v>0.06647938938594877</v>
+        <v>0.04053938625111919</v>
       </c>
       <c r="H161">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" s="1">
-        <v>46171</v>
+        <v>46162</v>
       </c>
       <c r="B162" t="s">
         <v>15</v>
       </c>
       <c r="C162">
-        <v>28.92588622185229</v>
+        <v>28.57911382310097</v>
       </c>
       <c r="D162">
-        <v>24.37463012178961</v>
+        <v>23.89431741541233</v>
       </c>
       <c r="E162">
-        <v>0.9999999989999999</v>
+        <v>0.999503734</v>
       </c>
       <c r="F162">
-        <v>0.9999999989999999</v>
+        <v>0.999503734</v>
       </c>
       <c r="G162">
-        <v>0.0669687424559624</v>
+        <v>0.04690190590044785</v>
       </c>
       <c r="H162">
-        <v>0.9999999989999999</v>
+        <v>0.999503734</v>
       </c>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" s="1">
-        <v>46174</v>
+        <v>46163</v>
       </c>
       <c r="B163" t="s">
         <v>15</v>
       </c>
       <c r="C163">
-        <v>28.479823472488</v>
+        <v>28.55785065378643</v>
       </c>
       <c r="D163">
-        <v>23.940843604634</v>
+        <v>24.04274714970193</v>
       </c>
       <c r="E163">
-        <v>0.9999999999999999</v>
+        <v>1.000229282</v>
       </c>
       <c r="F163">
-        <v>0.9999999999999999</v>
+        <v>1.000229282</v>
       </c>
       <c r="G163">
-        <v>0.05385076946675693</v>
+        <v>0.05228572319419666</v>
       </c>
       <c r="H163">
-        <v>0.9999999999999999</v>
+        <v>1.000229282</v>
       </c>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" s="1">
-        <v>46175</v>
+        <v>46164</v>
       </c>
       <c r="B164" t="s">
         <v>15</v>
       </c>
       <c r="C164">
-        <v>28.11501250979268</v>
+        <v>28.50194638163107</v>
       </c>
       <c r="D164">
-        <v>23.53470929078268</v>
+        <v>23.99272397156045</v>
       </c>
       <c r="E164">
-        <v>0.9999999989999999</v>
+        <v>1</v>
       </c>
       <c r="F164">
-        <v>0.9999999989999999</v>
+        <v>1</v>
       </c>
       <c r="G164">
-        <v>0.03476107722835287</v>
+        <v>0.04934923597154284</v>
       </c>
       <c r="H164">
-        <v>0.9999999989999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165" spans="1:8">
       <c r="A165" s="1">
-        <v>46176</v>
+        <v>46167</v>
       </c>
       <c r="B165" t="s">
         <v>15</v>
       </c>
       <c r="C165">
-        <v>28.0115884668485</v>
+        <v>28.55106858744498</v>
       </c>
       <c r="D165">
-        <v>23.38620815625822</v>
+        <v>23.9768329565351</v>
       </c>
       <c r="E165">
-        <v>0.9993115890000001</v>
+        <v>1</v>
       </c>
       <c r="F165">
-        <v>0.9993115890000001</v>
+        <v>1</v>
       </c>
       <c r="G165">
-        <v>0.02105569185214828</v>
+        <v>0.05571185335164408</v>
       </c>
       <c r="H165">
-        <v>0.9993115890000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166" spans="1:8">
       <c r="A166" s="1">
-        <v>46177</v>
+        <v>46168</v>
       </c>
       <c r="B166" t="s">
         <v>15</v>
       </c>
       <c r="C166">
-        <v>28.38208530418455</v>
+        <v>28.54681541456266</v>
       </c>
       <c r="D166">
-        <v>23.57230416238753</v>
+        <v>23.97386168967948</v>
       </c>
       <c r="E166">
-        <v>1.000774061</v>
+        <v>1</v>
       </c>
       <c r="F166">
-        <v>1.000774061</v>
+        <v>1</v>
       </c>
       <c r="G166">
-        <v>0.03133473088430172</v>
+        <v>0.04837034303541388</v>
       </c>
       <c r="H166">
-        <v>1.000774061</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" s="1">
-        <v>46178</v>
+        <v>46169</v>
       </c>
       <c r="B167" t="s">
         <v>15</v>
       </c>
       <c r="C167">
-        <v>27.67379569436247</v>
+        <v>28.83672936868491</v>
       </c>
       <c r="D167">
-        <v>23.02577481291606</v>
+        <v>24.203511281145</v>
       </c>
       <c r="E167">
-        <v>1.000106056</v>
+        <v>1</v>
       </c>
       <c r="F167">
-        <v>1.000106056</v>
+        <v>1</v>
       </c>
       <c r="G167">
-        <v>0.01248973263108488</v>
+        <v>0.05962723282507953</v>
       </c>
       <c r="H167">
-        <v>1.000106056</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168" spans="1:8">
       <c r="A168" s="1">
-        <v>46182</v>
+        <v>46170</v>
       </c>
       <c r="B168" t="s">
         <v>15</v>
       </c>
       <c r="C168">
-        <v>27.45237632057606</v>
+        <v>28.88109630394224</v>
       </c>
       <c r="D168">
-        <v>22.58943922039682</v>
+        <v>24.34085451035401</v>
       </c>
       <c r="E168">
-        <v>0.9999738310000001</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F168">
-        <v>0.9999738310000001</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G168">
-        <v>-0.01076068709534461</v>
+        <v>0.06647938938594877</v>
       </c>
       <c r="H168">
-        <v>0.9999738310000001</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" s="1">
-        <v>46183</v>
+        <v>46171</v>
       </c>
       <c r="B169" t="s">
         <v>15</v>
       </c>
       <c r="C169">
-        <v>26.87898580194432</v>
+        <v>28.92588622185229</v>
       </c>
       <c r="D169">
-        <v>22.24994492425726</v>
+        <v>24.37463012178961</v>
       </c>
       <c r="E169">
-        <v>1.000000001</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F169">
-        <v>1.000000001</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G169">
-        <v>-0.02299778174457945</v>
+        <v>0.0669687424559624</v>
       </c>
       <c r="H169">
-        <v>1.000000001</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="170" spans="1:8">
       <c r="A170" s="1">
-        <v>46153</v>
+        <v>46174</v>
       </c>
       <c r="B170" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C170">
-        <v>40.68830633303975</v>
+        <v>28.479823472488</v>
       </c>
       <c r="D170">
-        <v>21.50431773660198</v>
+        <v>23.940843604634</v>
       </c>
       <c r="E170">
-        <v>0.99909852</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F170">
-        <v>0.99909852</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G170">
-        <v>0.2342423866086769</v>
+        <v>0.05385076946675693</v>
       </c>
       <c r="H170">
-        <v>0.9974930900000001</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="171" spans="1:8">
       <c r="A171" s="1">
-        <v>46154</v>
+        <v>46175</v>
       </c>
       <c r="B171" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C171">
-        <v>40.32854894972581</v>
+        <v>28.11501250979268</v>
       </c>
       <c r="D171">
-        <v>21.09133998298594</v>
+        <v>23.53470929078268</v>
       </c>
       <c r="E171">
-        <v>0.9990972199999999</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F171">
-        <v>0.9990972199999999</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G171">
-        <v>0.2156468205051487</v>
+        <v>0.03476107722835287</v>
       </c>
       <c r="H171">
-        <v>0.99752223</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="172" spans="1:8">
       <c r="A172" s="1">
-        <v>46155</v>
+        <v>46176</v>
       </c>
       <c r="B172" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C172">
-        <v>40.47987921095815</v>
+        <v>28.0115884668485</v>
       </c>
       <c r="D172">
-        <v>21.35995364434454</v>
+        <v>23.38620815625822</v>
       </c>
       <c r="E172">
-        <v>0.9991780100000001</v>
+        <v>0.9993115890000001</v>
       </c>
       <c r="F172">
-        <v>0.9991780100000001</v>
+        <v>0.9993115890000001</v>
       </c>
       <c r="G172">
-        <v>0.2270956128473374</v>
+        <v>0.02105569185214828</v>
       </c>
       <c r="H172">
-        <v>0.9975825700000001</v>
+        <v>0.9993115890000001</v>
       </c>
     </row>
     <row r="173" spans="1:8">
       <c r="A173" s="1">
-        <v>46156</v>
+        <v>46177</v>
       </c>
       <c r="B173" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C173">
-        <v>41.20436574895244</v>
+        <v>28.38208530418455</v>
       </c>
       <c r="D173">
-        <v>21.48149674387778</v>
+        <v>23.57230416238753</v>
       </c>
       <c r="E173">
-        <v>0.9991793299999999</v>
+        <v>1.000774061</v>
       </c>
       <c r="F173">
-        <v>0.9991793299999999</v>
+        <v>1.000774061</v>
       </c>
       <c r="G173">
-        <v>0.2454829228401052</v>
+        <v>0.03133473088430172</v>
       </c>
       <c r="H173">
-        <v>0.99754722</v>
+        <v>1.000774061</v>
       </c>
     </row>
     <row r="174" spans="1:8">
       <c r="A174" s="1">
-        <v>46157</v>
+        <v>46178</v>
       </c>
       <c r="B174" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C174">
-        <v>40.80613062958688</v>
+        <v>27.67379569436247</v>
       </c>
       <c r="D174">
-        <v>21.08912555803936</v>
+        <v>23.02577481291606</v>
       </c>
       <c r="E174">
-        <v>0.9991790600000001</v>
+        <v>1.000106056</v>
       </c>
       <c r="F174">
-        <v>0.9991790600000001</v>
+        <v>1.000106056</v>
       </c>
       <c r="G174">
-        <v>0.2230017445022556</v>
+        <v>0.01248973263108488</v>
       </c>
       <c r="H174">
-        <v>0.9975824700000002</v>
+        <v>1.000106056</v>
       </c>
     </row>
     <row r="175" spans="1:8">
       <c r="A175" s="1">
-        <v>46160</v>
+        <v>46182</v>
       </c>
       <c r="B175" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C175">
-        <v>40.11672876026724</v>
+        <v>27.45237632057606</v>
       </c>
       <c r="D175">
-        <v>20.79541439916316</v>
+        <v>22.58943922039682</v>
       </c>
       <c r="E175">
-        <v>0.999152</v>
+        <v>0.9999738310000001</v>
       </c>
       <c r="F175">
-        <v>0.999152</v>
+        <v>0.9999738310000001</v>
       </c>
       <c r="G175">
-        <v>0.2098184021536666</v>
+        <v>-0.01076068709534461</v>
       </c>
       <c r="H175">
-        <v>0.9975007899999999</v>
+        <v>0.9999738310000001</v>
       </c>
     </row>
     <row r="176" spans="1:8">
       <c r="A176" s="1">
-        <v>46161</v>
+        <v>46183</v>
       </c>
       <c r="B176" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C176">
-        <v>39.69086941528401</v>
+        <v>26.87898580194432</v>
       </c>
       <c r="D176">
-        <v>20.74924328599426</v>
+        <v>22.24994492425726</v>
       </c>
       <c r="E176">
-        <v>0.99914989</v>
+        <v>1.000000001</v>
       </c>
       <c r="F176">
-        <v>0.99914989</v>
+        <v>1.000000001</v>
       </c>
       <c r="G176">
-        <v>0.2020471776850241</v>
+        <v>-0.02299778174457945</v>
       </c>
       <c r="H176">
-        <v>0.9974417</v>
+        <v>1.000000001</v>
       </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177" s="1">
-        <v>46162</v>
+        <v>46184</v>
       </c>
       <c r="B177" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C177">
-        <v>40.37836787855562</v>
+        <v>26.963842509069</v>
       </c>
       <c r="D177">
-        <v>21.11271132314188</v>
+        <v>22.26031265264148</v>
       </c>
       <c r="E177">
-        <v>0.99915058</v>
+        <v>0.9996853900000001</v>
       </c>
       <c r="F177">
-        <v>0.99915058</v>
+        <v>0.9996853900000001</v>
       </c>
       <c r="G177">
-        <v>0.2291077670847563</v>
+        <v>-0.02299759931689671</v>
       </c>
       <c r="H177">
-        <v>0.9974415600000001</v>
+        <v>0.9996853900000001</v>
       </c>
     </row>
     <row r="178" spans="1:8">
       <c r="A178" s="1">
-        <v>46163</v>
+        <v>46153</v>
       </c>
       <c r="B178" t="s">
         <v>16</v>
       </c>
       <c r="C178">
-        <v>38.9123066967842</v>
+        <v>40.68830633303975</v>
       </c>
       <c r="D178">
-        <v>21.28910644207464</v>
+        <v>21.50431773660198</v>
       </c>
       <c r="E178">
-        <v>0.9989350699999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="F178">
-        <v>0.9989350699999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="G178">
-        <v>0.2392382040170877</v>
+        <v>0.2342423866086769</v>
       </c>
       <c r="H178">
-        <v>0.99726191</v>
+        <v>0.9974930900000001</v>
       </c>
     </row>
     <row r="179" spans="1:8">
       <c r="A179" s="1">
-        <v>46164</v>
+        <v>46154</v>
       </c>
       <c r="B179" t="s">
         <v>16</v>
       </c>
       <c r="C179">
-        <v>39.43913909150694</v>
+        <v>40.32854894972581</v>
       </c>
       <c r="D179">
-        <v>21.05297617141148</v>
+        <v>21.09133998298594</v>
       </c>
       <c r="E179">
-        <v>0.999144</v>
+        <v>0.9990972199999999</v>
       </c>
       <c r="F179">
-        <v>0.999144</v>
+        <v>0.9990972199999999</v>
       </c>
       <c r="G179">
-        <v>0.2516582935428642</v>
+        <v>0.2156468205051487</v>
       </c>
       <c r="H179">
-        <v>0.9974678400000001</v>
+        <v>0.99752223</v>
       </c>
     </row>
     <row r="180" spans="1:8">
       <c r="A180" s="1">
-        <v>46167</v>
+        <v>46155</v>
       </c>
       <c r="B180" t="s">
         <v>16</v>
       </c>
       <c r="C180">
-        <v>39.45782844313628</v>
+        <v>40.47987921095815</v>
       </c>
       <c r="D180">
-        <v>21.0518901572272</v>
+        <v>21.35995364434454</v>
       </c>
       <c r="E180">
-        <v>0.999144</v>
+        <v>0.9991780100000001</v>
       </c>
       <c r="F180">
-        <v>0.999144</v>
+        <v>0.9991780100000001</v>
       </c>
       <c r="G180">
-        <v>0.2516582935428642</v>
+        <v>0.2270956128473374</v>
       </c>
       <c r="H180">
-        <v>0.9974678400000001</v>
+        <v>0.9975825700000001</v>
       </c>
     </row>
     <row r="181" spans="1:8">
       <c r="A181" s="1">
-        <v>46168</v>
+        <v>46156</v>
       </c>
       <c r="B181" t="s">
         <v>16</v>
       </c>
       <c r="C181">
-        <v>40.20219297984542</v>
+        <v>41.20436574895244</v>
       </c>
       <c r="D181">
-        <v>21.93106024403281</v>
+        <v>21.48149674387778</v>
       </c>
       <c r="E181">
-        <v>0.9991421799999999</v>
+        <v>0.9991793299999999</v>
       </c>
       <c r="F181">
-        <v>0.9991421799999999</v>
+        <v>0.9991793299999999</v>
       </c>
       <c r="G181">
-        <v>0.2846167552893293</v>
+        <v>0.2454829228401052</v>
       </c>
       <c r="H181">
-        <v>0.9974609800000001</v>
+        <v>0.99754722</v>
       </c>
     </row>
     <row r="182" spans="1:8">
       <c r="A182" s="1">
-        <v>46169</v>
+        <v>46157</v>
       </c>
       <c r="B182" t="s">
         <v>16</v>
       </c>
       <c r="C182">
-        <v>40.34993865302093</v>
+        <v>40.80613062958688</v>
       </c>
       <c r="D182">
-        <v>21.65366031776487</v>
+        <v>21.08912555803936</v>
       </c>
       <c r="E182">
-        <v>0.9991434600000001</v>
+        <v>0.9991790600000001</v>
       </c>
       <c r="F182">
-        <v>0.9991434600000001</v>
+        <v>0.9991790600000001</v>
       </c>
       <c r="G182">
-        <v>0.2796902860011767</v>
+        <v>0.2230017445022556</v>
       </c>
       <c r="H182">
-        <v>0.9991434600000001</v>
+        <v>0.9975824700000002</v>
       </c>
     </row>
     <row r="183" spans="1:8">
       <c r="A183" s="1">
-        <v>46170</v>
+        <v>46160</v>
       </c>
       <c r="B183" t="s">
         <v>16</v>
       </c>
       <c r="C183">
-        <v>40.5850485390846</v>
+        <v>40.11672876026724</v>
       </c>
       <c r="D183">
-        <v>21.75450977746074</v>
+        <v>20.79541439916316</v>
       </c>
       <c r="E183">
-        <v>0.99914592</v>
+        <v>0.999152</v>
       </c>
       <c r="F183">
-        <v>0.99914592</v>
+        <v>0.999152</v>
       </c>
       <c r="G183">
-        <v>0.2964818481030536</v>
+        <v>0.2098184021536666</v>
       </c>
       <c r="H183">
-        <v>0.99914592</v>
+        <v>0.9975007899999999</v>
       </c>
     </row>
     <row r="184" spans="1:8">
       <c r="A184" s="1">
-        <v>46171</v>
+        <v>46161</v>
       </c>
       <c r="B184" t="s">
         <v>16</v>
       </c>
       <c r="C184">
-        <v>41.86785805184477</v>
+        <v>39.69086941528401</v>
       </c>
       <c r="D184">
-        <v>22.33589392797469</v>
+        <v>20.74924328599426</v>
       </c>
       <c r="E184">
-        <v>0.9991336999999999</v>
+        <v>0.99914989</v>
       </c>
       <c r="F184">
-        <v>0.9991336999999999</v>
+        <v>0.99914989</v>
       </c>
       <c r="G184">
-        <v>0.3254158954996882</v>
+        <v>0.2020471776850241</v>
       </c>
       <c r="H184">
-        <v>0.9991336999999999</v>
+        <v>0.9974417</v>
       </c>
     </row>
     <row r="185" spans="1:8">
       <c r="A185" s="1">
-        <v>46174</v>
+        <v>46162</v>
       </c>
       <c r="B185" t="s">
         <v>16</v>
       </c>
       <c r="C185">
-        <v>42.82932322850974</v>
+        <v>40.37836787855562</v>
       </c>
       <c r="D185">
-        <v>22.98998911430362</v>
+        <v>21.11271132314188</v>
       </c>
       <c r="E185">
-        <v>0.99914238</v>
+        <v>0.99915058</v>
       </c>
       <c r="F185">
-        <v>0.99914238</v>
+        <v>0.99915058</v>
       </c>
       <c r="G185">
-        <v>0.3583049032509023</v>
+        <v>0.2291077670847563</v>
       </c>
       <c r="H185">
-        <v>0.99914238</v>
+        <v>0.9974415600000001</v>
       </c>
     </row>
     <row r="186" spans="1:8">
       <c r="A186" s="1">
-        <v>46175</v>
+        <v>46163</v>
       </c>
       <c r="B186" t="s">
         <v>16</v>
       </c>
       <c r="C186">
-        <v>43.11872937189534</v>
+        <v>38.9123066967842</v>
       </c>
       <c r="D186">
-        <v>22.90628380907704</v>
+        <v>21.28910644207464</v>
       </c>
       <c r="E186">
-        <v>0.9990972800000002</v>
+        <v>0.9989350699999999</v>
       </c>
       <c r="F186">
-        <v>0.9990972800000002</v>
+        <v>0.9989350699999999</v>
       </c>
       <c r="G186">
-        <v>0.3753046155885469</v>
+        <v>0.2392382040170877</v>
       </c>
       <c r="H186">
-        <v>0.9990972800000002</v>
+        <v>0.99726191</v>
       </c>
     </row>
     <row r="187" spans="1:8">
       <c r="A187" s="1">
-        <v>46176</v>
+        <v>46164</v>
       </c>
       <c r="B187" t="s">
         <v>16</v>
       </c>
       <c r="C187">
-        <v>42.86143001679577</v>
+        <v>39.43913909150694</v>
       </c>
       <c r="D187">
-        <v>22.72053012591219</v>
+        <v>21.05297617141148</v>
       </c>
       <c r="E187">
-        <v>0.9990984299999999</v>
+        <v>0.999144</v>
       </c>
       <c r="F187">
-        <v>0.9990984299999999</v>
+        <v>0.999144</v>
       </c>
       <c r="G187">
-        <v>0.3615660647779204</v>
+        <v>0.2516582935428642</v>
       </c>
       <c r="H187">
-        <v>0.9990984299999999</v>
+        <v>0.9974678400000001</v>
       </c>
     </row>
     <row r="188" spans="1:8">
       <c r="A188" s="1">
-        <v>46177</v>
+        <v>46167</v>
       </c>
       <c r="B188" t="s">
         <v>16</v>
       </c>
       <c r="C188">
-        <v>42.57902095847519</v>
+        <v>39.45782844313628</v>
       </c>
       <c r="D188">
-        <v>22.20304338566557</v>
+        <v>21.0518901572272</v>
       </c>
       <c r="E188">
-        <v>0.9990006900000001</v>
+        <v>0.999144</v>
       </c>
       <c r="F188">
-        <v>0.9990006900000001</v>
+        <v>0.999144</v>
       </c>
       <c r="G188">
-        <v>0.34033389372967</v>
+        <v>0.2516582935428642</v>
       </c>
       <c r="H188">
-        <v>0.9990006900000001</v>
+        <v>0.9974678400000001</v>
       </c>
     </row>
     <row r="189" spans="1:8">
       <c r="A189" s="1">
-        <v>46178</v>
+        <v>46168</v>
       </c>
       <c r="B189" t="s">
         <v>16</v>
       </c>
       <c r="C189">
-        <v>39.64354477595148</v>
+        <v>40.20219297984542</v>
       </c>
       <c r="D189">
-        <v>20.69555521363093</v>
+        <v>21.93106024403281</v>
       </c>
       <c r="E189">
-        <v>0.9992026399999999</v>
+        <v>0.9991421799999999</v>
       </c>
       <c r="F189">
-        <v>0.9992026399999999</v>
+        <v>0.9991421799999999</v>
       </c>
       <c r="G189">
-        <v>0.251033842835561</v>
+        <v>0.2846167552893293</v>
       </c>
       <c r="H189">
-        <v>0.9992026399999999</v>
+        <v>0.9974609800000001</v>
       </c>
     </row>
     <row r="190" spans="1:8">
       <c r="A190" s="1">
-        <v>46182</v>
+        <v>46169</v>
       </c>
       <c r="B190" t="s">
         <v>16</v>
       </c>
       <c r="C190">
-        <v>39.7656886466531</v>
+        <v>40.34993865302093</v>
       </c>
       <c r="D190">
-        <v>20.79148740795913</v>
+        <v>21.65366031776487</v>
       </c>
       <c r="E190">
-        <v>0.9992145899999999</v>
+        <v>0.9991434600000001</v>
       </c>
       <c r="F190">
-        <v>0.9992145899999999</v>
+        <v>0.9991434600000001</v>
       </c>
       <c r="G190">
-        <v>0.2542950043625791</v>
+        <v>0.2796902860011767</v>
       </c>
       <c r="H190">
-        <v>0.9992145899999999</v>
+        <v>0.9991434600000001</v>
       </c>
     </row>
     <row r="191" spans="1:8">
       <c r="A191" s="1">
-        <v>46183</v>
+        <v>46170</v>
       </c>
       <c r="B191" t="s">
         <v>16</v>
       </c>
       <c r="C191">
+        <v>40.5850485390846</v>
+      </c>
+      <c r="D191">
+        <v>21.75450977746074</v>
+      </c>
+      <c r="E191">
+        <v>0.99914592</v>
+      </c>
+      <c r="F191">
+        <v>0.99914592</v>
+      </c>
+      <c r="G191">
+        <v>0.2964818481030536</v>
+      </c>
+      <c r="H191">
+        <v>0.99914592</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8">
+      <c r="A192" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192">
+        <v>41.86785805184477</v>
+      </c>
+      <c r="D192">
+        <v>22.33589392797469</v>
+      </c>
+      <c r="E192">
+        <v>0.9991336999999999</v>
+      </c>
+      <c r="F192">
+        <v>0.9991336999999999</v>
+      </c>
+      <c r="G192">
+        <v>0.3254158954996882</v>
+      </c>
+      <c r="H192">
+        <v>0.9991336999999999</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8">
+      <c r="A193" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193">
+        <v>42.82932322850974</v>
+      </c>
+      <c r="D193">
+        <v>22.98998911430362</v>
+      </c>
+      <c r="E193">
+        <v>0.99914238</v>
+      </c>
+      <c r="F193">
+        <v>0.99914238</v>
+      </c>
+      <c r="G193">
+        <v>0.3583049032509023</v>
+      </c>
+      <c r="H193">
+        <v>0.99914238</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8">
+      <c r="A194" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194">
+        <v>43.11872937189534</v>
+      </c>
+      <c r="D194">
+        <v>22.90628380907704</v>
+      </c>
+      <c r="E194">
+        <v>0.9990972800000002</v>
+      </c>
+      <c r="F194">
+        <v>0.9990972800000002</v>
+      </c>
+      <c r="G194">
+        <v>0.3753046155885469</v>
+      </c>
+      <c r="H194">
+        <v>0.9990972800000002</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8">
+      <c r="A195" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195">
+        <v>42.86143001679577</v>
+      </c>
+      <c r="D195">
+        <v>22.72053012591219</v>
+      </c>
+      <c r="E195">
+        <v>0.9990984299999999</v>
+      </c>
+      <c r="F195">
+        <v>0.9990984299999999</v>
+      </c>
+      <c r="G195">
+        <v>0.3615660647779204</v>
+      </c>
+      <c r="H195">
+        <v>0.9990984299999999</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8">
+      <c r="A196" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196">
+        <v>42.57902095847519</v>
+      </c>
+      <c r="D196">
+        <v>22.20304338566557</v>
+      </c>
+      <c r="E196">
+        <v>0.9990006900000001</v>
+      </c>
+      <c r="F196">
+        <v>0.9990006900000001</v>
+      </c>
+      <c r="G196">
+        <v>0.34033389372967</v>
+      </c>
+      <c r="H196">
+        <v>0.9990006900000001</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8">
+      <c r="A197" s="1">
+        <v>46178</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197">
+        <v>39.64354477595148</v>
+      </c>
+      <c r="D197">
+        <v>20.69555521363093</v>
+      </c>
+      <c r="E197">
+        <v>0.9992026399999999</v>
+      </c>
+      <c r="F197">
+        <v>0.9992026399999999</v>
+      </c>
+      <c r="G197">
+        <v>0.251033842835561</v>
+      </c>
+      <c r="H197">
+        <v>0.9992026399999999</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8">
+      <c r="A198" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198">
+        <v>39.7656886466531</v>
+      </c>
+      <c r="D198">
+        <v>20.79148740795913</v>
+      </c>
+      <c r="E198">
+        <v>0.9992145899999999</v>
+      </c>
+      <c r="F198">
+        <v>0.9992145899999999</v>
+      </c>
+      <c r="G198">
+        <v>0.2542950043625791</v>
+      </c>
+      <c r="H198">
+        <v>0.9992145899999999</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8">
+      <c r="A199" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199">
         <v>38.48800295288941</v>
       </c>
-      <c r="D191">
+      <c r="D199">
         <v>20.05492629580107</v>
       </c>
-      <c r="E191">
+      <c r="E199">
         <v>0.9992031100000001</v>
       </c>
-      <c r="F191">
+      <c r="F199">
         <v>0.9992031100000001</v>
       </c>
-      <c r="G191">
+      <c r="G199">
         <v>0.2255691072017123</v>
       </c>
-      <c r="H191">
+      <c r="H199">
         <v>0.9992031100000001</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8">
+      <c r="A200" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200">
+        <v>39.71404813715499</v>
+      </c>
+      <c r="D200">
+        <v>20.78057418129766</v>
+      </c>
+      <c r="E200">
+        <v>0.9991764899999999</v>
+      </c>
+      <c r="F200">
+        <v>0.9991764899999999</v>
+      </c>
+      <c r="G200">
+        <v>0.2712252627049727</v>
+      </c>
+      <c r="H200">
+        <v>0.9991764899999999</v>
       </c>
     </row>
   </sheetData>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="17">
   <si>
     <t>Date</t>
   </si>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H200"/>
+  <dimension ref="A1:H209"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -847,42 +847,42 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1">
-        <v>46153</v>
+        <v>46185</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18">
-        <v>53.14833755912058</v>
+        <v>27.27598802137837</v>
       </c>
       <c r="D18">
-        <v>25.84885448407537</v>
+        <v>17.58981549382293</v>
       </c>
       <c r="E18">
-        <v>0.9262</v>
+        <v>0.8870000000000001</v>
       </c>
       <c r="F18">
-        <v>0.9262</v>
+        <v>0.8870000000000001</v>
       </c>
       <c r="G18">
-        <v>0.3839084462043663</v>
+        <v>0.5423083346745941</v>
       </c>
       <c r="H18">
-        <v>0.9262</v>
+        <v>0.9385000000000002</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B19" t="s">
         <v>9</v>
       </c>
       <c r="C19">
-        <v>51.82921169635205</v>
+        <v>53.14833755912058</v>
       </c>
       <c r="D19">
-        <v>25.32805827181975</v>
+        <v>25.84885448407537</v>
       </c>
       <c r="E19">
         <v>0.9262</v>
@@ -891,7 +891,7 @@
         <v>0.9262</v>
       </c>
       <c r="G19">
-        <v>0.3568580281685669</v>
+        <v>0.3839084462043663</v>
       </c>
       <c r="H19">
         <v>0.9262</v>
@@ -899,120 +899,120 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B20" t="s">
         <v>9</v>
       </c>
       <c r="C20">
-        <v>52.28471716753184</v>
+        <v>51.82921169635205</v>
       </c>
       <c r="D20">
-        <v>25.54525144150689</v>
+        <v>25.32805827181975</v>
       </c>
       <c r="E20">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="F20">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="G20">
-        <v>0.378012896547947</v>
+        <v>0.3568580281685669</v>
       </c>
       <c r="H20">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B21" t="s">
         <v>9</v>
       </c>
       <c r="C21">
-        <v>53.87287273813902</v>
+        <v>52.28471716753184</v>
       </c>
       <c r="D21">
-        <v>26.32154226438612</v>
+        <v>25.54525144150689</v>
       </c>
       <c r="E21">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="F21">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="G21">
-        <v>0.4166811087612758</v>
+        <v>0.378012896547947</v>
       </c>
       <c r="H21">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="B22" t="s">
         <v>9</v>
       </c>
       <c r="C22">
-        <v>52.18747148214074</v>
+        <v>53.87287273813902</v>
       </c>
       <c r="D22">
-        <v>25.13616059644496</v>
+        <v>26.32154226438612</v>
       </c>
       <c r="E22">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="F22">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="G22">
-        <v>0.3627535778249862</v>
+        <v>0.4166811087612758</v>
       </c>
       <c r="H22">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="B23" t="s">
         <v>9</v>
       </c>
       <c r="C23">
-        <v>50.72035274995172</v>
+        <v>52.18747148214074</v>
       </c>
       <c r="D23">
-        <v>24.61756040386634</v>
+        <v>25.13616059644496</v>
       </c>
       <c r="E23">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="F23">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="G23">
         <v>0.3627535778249862</v>
       </c>
       <c r="H23">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="B24" t="s">
         <v>9</v>
       </c>
       <c r="C24">
-        <v>50.11981086673613</v>
+        <v>50.72035274995172</v>
       </c>
       <c r="D24">
-        <v>24.13061679021705</v>
+        <v>24.61756040386634</v>
       </c>
       <c r="E24">
         <v>0.9259000000000001</v>
@@ -1021,7 +1021,7 @@
         <v>0.9259000000000001</v>
       </c>
       <c r="G24">
-        <v>0.3258193430227221</v>
+        <v>0.3627535778249862</v>
       </c>
       <c r="H24">
         <v>0.9259000000000001</v>
@@ -1029,120 +1029,120 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
       </c>
       <c r="C25">
-        <v>51.74165648409151</v>
+        <v>50.11981086673613</v>
       </c>
       <c r="D25">
-        <v>24.98091384114761</v>
+        <v>24.13061679021705</v>
       </c>
       <c r="E25">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="F25">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="G25">
-        <v>0.3818277262286871</v>
+        <v>0.3258193430227221</v>
       </c>
       <c r="H25">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
       </c>
       <c r="C26">
-        <v>49.13455894175823</v>
+        <v>51.74165648409151</v>
       </c>
       <c r="D26">
-        <v>25.30005057653127</v>
+        <v>24.98091384114761</v>
       </c>
       <c r="E26">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="F26">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="G26">
-        <v>0.4028091571787618</v>
+        <v>0.3818277262286871</v>
       </c>
       <c r="H26">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="B27" t="s">
         <v>9</v>
       </c>
       <c r="C27">
-        <v>49.57776597479297</v>
+        <v>49.13455894175823</v>
       </c>
       <c r="D27">
-        <v>25.04906725563518</v>
+        <v>25.30005057653127</v>
       </c>
       <c r="E27">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="F27">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="G27">
-        <v>0.4256980029692063</v>
+        <v>0.4028091571787618</v>
       </c>
       <c r="H27">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="B28" t="s">
         <v>9</v>
       </c>
       <c r="C28">
-        <v>49.71239596645896</v>
+        <v>49.57776597479297</v>
       </c>
       <c r="D28">
-        <v>25.18778610744295</v>
+        <v>25.04906725563518</v>
       </c>
       <c r="E28">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="F28">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="G28">
-        <v>0.4525749835757003</v>
+        <v>0.4256980029692063</v>
       </c>
       <c r="H28">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="B29" t="s">
         <v>9</v>
       </c>
       <c r="C29">
-        <v>50.77166277510776</v>
+        <v>49.71239596645896</v>
       </c>
       <c r="D29">
-        <v>25.7431782858765</v>
+        <v>25.18778610744295</v>
       </c>
       <c r="E29">
         <v>0.9231999999999999</v>
@@ -1151,7 +1151,7 @@
         <v>0.9231999999999999</v>
       </c>
       <c r="G29">
-        <v>0.4700884597036457</v>
+        <v>0.4525749835757003</v>
       </c>
       <c r="H29">
         <v>0.9231999999999999</v>
@@ -1159,120 +1159,120 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1">
-        <v>46169</v>
+        <v>46168</v>
       </c>
       <c r="B30" t="s">
         <v>9</v>
       </c>
       <c r="C30">
-        <v>50.57689164833899</v>
+        <v>50.77166277510776</v>
       </c>
       <c r="D30">
-        <v>25.70244067238947</v>
+        <v>25.7431782858765</v>
       </c>
       <c r="E30">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="F30">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="G30">
-        <v>0.4518814984464716</v>
+        <v>0.4700884597036457</v>
       </c>
       <c r="H30">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="B31" t="s">
         <v>9</v>
       </c>
       <c r="C31">
-        <v>50.80027854822009</v>
+        <v>50.57689164833899</v>
       </c>
       <c r="D31">
-        <v>25.90068415792015</v>
+        <v>25.70244067238947</v>
       </c>
       <c r="E31">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
       <c r="F31">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
       <c r="G31">
-        <v>0.4699150222743402</v>
+        <v>0.4518814984464716</v>
       </c>
       <c r="H31">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="B32" t="s">
         <v>9</v>
       </c>
       <c r="C32">
-        <v>51.44563447241545</v>
+        <v>50.80027854822009</v>
       </c>
       <c r="D32">
-        <v>26.0970978996374</v>
+        <v>25.90068415792015</v>
       </c>
       <c r="E32">
-        <v>0.9246</v>
+        <v>0.9231</v>
       </c>
       <c r="F32">
-        <v>0.9246</v>
+        <v>0.9231</v>
       </c>
       <c r="G32">
-        <v>0.4791053539115764</v>
+        <v>0.4699150222743402</v>
       </c>
       <c r="H32">
-        <v>0.9246</v>
+        <v>0.9231</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1">
-        <v>46174</v>
+        <v>46171</v>
       </c>
       <c r="B33" t="s">
         <v>9</v>
       </c>
       <c r="C33">
-        <v>53.05792083471825</v>
+        <v>51.44563447241545</v>
       </c>
       <c r="D33">
-        <v>26.86242981002239</v>
+        <v>26.0970978996374</v>
       </c>
       <c r="E33">
-        <v>0.9254999999999999</v>
+        <v>0.9246</v>
       </c>
       <c r="F33">
-        <v>0.9254999999999999</v>
+        <v>0.9246</v>
       </c>
       <c r="G33">
-        <v>0.5306051577195796</v>
+        <v>0.4791053539115764</v>
       </c>
       <c r="H33">
-        <v>0.9254999999999999</v>
+        <v>0.9246</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="B34" t="s">
         <v>9</v>
       </c>
       <c r="C34">
-        <v>54.38946369031042</v>
+        <v>53.05792083471825</v>
       </c>
       <c r="D34">
-        <v>27.57160808325711</v>
+        <v>26.86242981002239</v>
       </c>
       <c r="E34">
         <v>0.9254999999999999</v>
@@ -1281,7 +1281,7 @@
         <v>0.9254999999999999</v>
       </c>
       <c r="G34">
-        <v>0.5845326886558693</v>
+        <v>0.5306051577195796</v>
       </c>
       <c r="H34">
         <v>0.9254999999999999</v>
@@ -1289,302 +1289,302 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="B35" t="s">
         <v>9</v>
       </c>
       <c r="C35">
-        <v>54.35279063045283</v>
+        <v>54.38946369031042</v>
       </c>
       <c r="D35">
-        <v>27.50874919819178</v>
+        <v>27.57160808325711</v>
       </c>
       <c r="E35">
-        <v>0.9162000000000001</v>
+        <v>0.9254999999999999</v>
       </c>
       <c r="F35">
-        <v>0.9162000000000001</v>
+        <v>0.9254999999999999</v>
       </c>
       <c r="G35">
-        <v>0.5992718273849102</v>
+        <v>0.5845326886558693</v>
       </c>
       <c r="H35">
-        <v>0.9162000000000001</v>
+        <v>0.9254999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="B36" t="s">
         <v>9</v>
       </c>
       <c r="C36">
-        <v>53.45790968334249</v>
+        <v>54.35279063045283</v>
       </c>
       <c r="D36">
-        <v>26.99486187834476</v>
+        <v>27.50874919819178</v>
       </c>
       <c r="E36">
-        <v>0.9154000000000001</v>
+        <v>0.9162000000000001</v>
       </c>
       <c r="F36">
-        <v>0.9154000000000001</v>
+        <v>0.9162000000000001</v>
       </c>
       <c r="G36">
-        <v>0.5691000647975994</v>
+        <v>0.5992718273849102</v>
       </c>
       <c r="H36">
-        <v>0.9154000000000001</v>
+        <v>0.9162000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="B37" t="s">
         <v>9</v>
       </c>
       <c r="C37">
-        <v>52.01314444713902</v>
+        <v>53.45790968334249</v>
       </c>
       <c r="D37">
-        <v>25.48849727916627</v>
+        <v>26.99486187834476</v>
       </c>
       <c r="E37">
-        <v>0.9142999999999999</v>
+        <v>0.9154000000000001</v>
       </c>
       <c r="F37">
-        <v>0.9142999999999999</v>
+        <v>0.9154000000000001</v>
       </c>
       <c r="G37">
-        <v>0.4380094145699611</v>
+        <v>0.5691000647975994</v>
       </c>
       <c r="H37">
-        <v>0.9142999999999999</v>
+        <v>0.9154000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1">
-        <v>46182</v>
+        <v>46178</v>
       </c>
       <c r="B38" t="s">
         <v>9</v>
       </c>
       <c r="C38">
-        <v>50.12461745484359</v>
+        <v>52.01314444713902</v>
       </c>
       <c r="D38">
-        <v>25.31796473106079</v>
+        <v>25.48849727916627</v>
       </c>
       <c r="E38">
-        <v>0.916</v>
+        <v>0.9142999999999999</v>
       </c>
       <c r="F38">
-        <v>0.916</v>
+        <v>0.9142999999999999</v>
       </c>
       <c r="G38">
-        <v>0.4801457138994158</v>
+        <v>0.4380094145699611</v>
       </c>
       <c r="H38">
-        <v>0.916</v>
+        <v>0.9142999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="B39" t="s">
         <v>9</v>
       </c>
       <c r="C39">
-        <v>51.46065536727718</v>
+        <v>50.12461745484359</v>
       </c>
       <c r="D39">
-        <v>25.08120911400394</v>
+        <v>25.31796473106079</v>
       </c>
       <c r="E39">
-        <v>0.9188000000000002</v>
+        <v>0.916</v>
       </c>
       <c r="F39">
-        <v>0.9188000000000002</v>
+        <v>0.916</v>
       </c>
       <c r="G39">
-        <v>0.426738362957046</v>
+        <v>0.4801457138994158</v>
       </c>
       <c r="H39">
-        <v>0.9188000000000002</v>
+        <v>0.916</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="B40" t="s">
         <v>9</v>
       </c>
       <c r="C40">
-        <v>56.06808173087</v>
+        <v>51.46065536727718</v>
       </c>
       <c r="D40">
-        <v>26.41955208935029</v>
+        <v>25.08120911400394</v>
       </c>
       <c r="E40">
-        <v>0.9193</v>
+        <v>0.9188000000000002</v>
       </c>
       <c r="F40">
-        <v>0.9193</v>
+        <v>0.9188000000000002</v>
       </c>
       <c r="G40">
-        <v>0.5195075435359697</v>
+        <v>0.426738362957046</v>
       </c>
       <c r="H40">
-        <v>0.9193</v>
+        <v>0.9188000000000002</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1">
-        <v>46153</v>
+        <v>46184</v>
       </c>
       <c r="B41" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C41">
-        <v>34.64560932909123</v>
+        <v>56.06808173087</v>
       </c>
       <c r="D41">
-        <v>26.08311546080494</v>
+        <v>26.41955208935029</v>
       </c>
       <c r="E41">
-        <v>0.9983000000000001</v>
+        <v>0.9193</v>
       </c>
       <c r="F41">
-        <v>0.9983000000000001</v>
+        <v>0.9193</v>
       </c>
       <c r="G41">
-        <v>0.06258613715048233</v>
+        <v>0.5195075435359697</v>
       </c>
       <c r="H41">
-        <v>0.9983000000000001</v>
+        <v>0.9193</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1">
-        <v>46154</v>
+        <v>46185</v>
       </c>
       <c r="B42" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C42">
-        <v>34.50204921141101</v>
+        <v>55.25570685331304</v>
       </c>
       <c r="D42">
-        <v>25.94535229304585</v>
+        <v>27.01537159822627</v>
       </c>
       <c r="E42">
-        <v>0.9984</v>
+        <v>0.921</v>
       </c>
       <c r="F42">
-        <v>0.9984</v>
+        <v>0.921</v>
       </c>
       <c r="G42">
-        <v>0.05768943168306073</v>
+        <v>0.5477718912829104</v>
       </c>
       <c r="H42">
-        <v>0.9984</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="B43" t="s">
         <v>10</v>
       </c>
       <c r="C43">
-        <v>35.10429483281073</v>
+        <v>34.64560932909123</v>
       </c>
       <c r="D43">
-        <v>26.43864879939599</v>
+        <v>26.08311546080494</v>
       </c>
       <c r="E43">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="F43">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="G43">
-        <v>0.07926550001722021</v>
+        <v>0.06258613715048233</v>
       </c>
       <c r="H43">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="B44" t="s">
         <v>10</v>
       </c>
       <c r="C44">
-        <v>35.36860632820093</v>
+        <v>34.50204921141101</v>
       </c>
       <c r="D44">
-        <v>26.56575571102338</v>
+        <v>25.94535229304585</v>
       </c>
       <c r="E44">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F44">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G44">
-        <v>0.08553946591902095</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H44">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="B45" t="s">
         <v>10</v>
       </c>
       <c r="C45">
-        <v>34.88080083527914</v>
+        <v>35.10429483281073</v>
       </c>
       <c r="D45">
-        <v>26.19322945679072</v>
+        <v>26.43864879939599</v>
       </c>
       <c r="E45">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="F45">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="G45">
-        <v>0.06870693142475881</v>
+        <v>0.07926550001722021</v>
       </c>
       <c r="H45">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1">
-        <v>46160</v>
+        <v>46156</v>
       </c>
       <c r="B46" t="s">
         <v>10</v>
       </c>
       <c r="C46">
-        <v>34.67638692539213</v>
+        <v>35.36860632820093</v>
       </c>
       <c r="D46">
-        <v>26.06707890342319</v>
+        <v>26.56575571102338</v>
       </c>
       <c r="E46">
         <v>0.9985999999999999</v>
@@ -1593,7 +1593,7 @@
         <v>0.9985999999999999</v>
       </c>
       <c r="G46">
-        <v>0.06289213016552919</v>
+        <v>0.08553946591902095</v>
       </c>
       <c r="H46">
         <v>0.9985999999999999</v>
@@ -1601,120 +1601,120 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="B47" t="s">
         <v>10</v>
       </c>
       <c r="C47">
-        <v>34.21212662725402</v>
+        <v>34.88080083527914</v>
       </c>
       <c r="D47">
-        <v>25.60349394367002</v>
+        <v>26.19322945679072</v>
       </c>
       <c r="E47">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="F47">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="G47">
-        <v>0.0486610616591685</v>
+        <v>0.06870693142475881</v>
       </c>
       <c r="H47">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="B48" t="s">
         <v>10</v>
       </c>
       <c r="C48">
-        <v>34.78598436564941</v>
+        <v>34.67638692539213</v>
       </c>
       <c r="D48">
-        <v>25.95505316769806</v>
+        <v>26.06707890342319</v>
       </c>
       <c r="E48">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="F48">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="G48">
-        <v>0.06335117806143331</v>
+        <v>0.06289213016552919</v>
       </c>
       <c r="H48">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1">
-        <v>46163</v>
+        <v>46161</v>
       </c>
       <c r="B49" t="s">
         <v>10</v>
       </c>
       <c r="C49">
-        <v>33.4539909056227</v>
+        <v>34.21212662725402</v>
       </c>
       <c r="D49">
-        <v>25.96014535427112</v>
+        <v>25.60349394367002</v>
       </c>
       <c r="E49">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="F49">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="G49">
-        <v>0.06350423294229035</v>
+        <v>0.0486610616591685</v>
       </c>
       <c r="H49">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1">
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="B50" t="s">
         <v>10</v>
       </c>
       <c r="C50">
-        <v>33.24951933563993</v>
+        <v>34.78598436564941</v>
       </c>
       <c r="D50">
-        <v>25.46629530314992</v>
+        <v>25.95505316769806</v>
       </c>
       <c r="E50">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="F50">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="G50">
-        <v>0.06136193159696024</v>
+        <v>0.06335117806143331</v>
       </c>
       <c r="H50">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1">
-        <v>46167</v>
+        <v>46163</v>
       </c>
       <c r="B51" t="s">
         <v>10</v>
       </c>
       <c r="C51">
-        <v>33.29896419867477</v>
+        <v>33.4539909056227</v>
       </c>
       <c r="D51">
-        <v>25.45090185337973</v>
+        <v>25.96014535427112</v>
       </c>
       <c r="E51">
         <v>0.9984</v>
@@ -1723,7 +1723,7 @@
         <v>0.9984</v>
       </c>
       <c r="G51">
-        <v>0.06136193159696024</v>
+        <v>0.06350423294229035</v>
       </c>
       <c r="H51">
         <v>0.9984</v>
@@ -1731,16 +1731,16 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1">
-        <v>46168</v>
+        <v>46164</v>
       </c>
       <c r="B52" t="s">
         <v>10</v>
       </c>
       <c r="C52">
-        <v>33.41270923608511</v>
+        <v>33.24951933563993</v>
       </c>
       <c r="D52">
-        <v>25.54156152389702</v>
+        <v>25.46629530314992</v>
       </c>
       <c r="E52">
         <v>0.9984</v>
@@ -1749,7 +1749,7 @@
         <v>0.9984</v>
       </c>
       <c r="G52">
-        <v>0.06549347940676342</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H52">
         <v>0.9984</v>
@@ -1757,198 +1757,198 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1">
-        <v>46169</v>
+        <v>46167</v>
       </c>
       <c r="B53" t="s">
         <v>10</v>
       </c>
       <c r="C53">
-        <v>33.73350746548562</v>
+        <v>33.29896419867477</v>
       </c>
       <c r="D53">
-        <v>25.75393367034243</v>
+        <v>25.45090185337973</v>
       </c>
       <c r="E53">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="F53">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="G53">
-        <v>0.07620510288008187</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H53">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1">
-        <v>46170</v>
+        <v>46168</v>
       </c>
       <c r="B54" t="s">
         <v>10</v>
       </c>
       <c r="C54">
-        <v>33.84336414535104</v>
+        <v>33.41270923608511</v>
       </c>
       <c r="D54">
-        <v>25.97168203877208</v>
+        <v>25.54156152389702</v>
       </c>
       <c r="E54">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
       <c r="F54">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
       <c r="G54">
-        <v>0.0844683152463559</v>
+        <v>0.06549347940676342</v>
       </c>
       <c r="H54">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1">
-        <v>46171</v>
+        <v>46169</v>
       </c>
       <c r="B55" t="s">
         <v>10</v>
       </c>
       <c r="C55">
-        <v>33.73370320039719</v>
+        <v>33.73350746548562</v>
       </c>
       <c r="D55">
-        <v>25.880209881309</v>
+        <v>25.75393367034243</v>
       </c>
       <c r="E55">
-        <v>0.9988</v>
+        <v>0.9987000000000001</v>
       </c>
       <c r="F55">
-        <v>0.9988</v>
+        <v>0.9987000000000001</v>
       </c>
       <c r="G55">
-        <v>0.08201990413931148</v>
+        <v>0.07620510288008187</v>
       </c>
       <c r="H55">
-        <v>0.9988</v>
+        <v>0.9987000000000001</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1">
-        <v>46174</v>
+        <v>46170</v>
       </c>
       <c r="B56" t="s">
         <v>10</v>
       </c>
       <c r="C56">
-        <v>33.45546240777382</v>
+        <v>33.84336414535104</v>
       </c>
       <c r="D56">
-        <v>25.61350381215703</v>
+        <v>25.97168203877208</v>
       </c>
       <c r="E56">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
       <c r="F56">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
       <c r="G56">
-        <v>0.06901304118647311</v>
+        <v>0.0844683152463559</v>
       </c>
       <c r="H56">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1">
-        <v>46175</v>
+        <v>46171</v>
       </c>
       <c r="B57" t="s">
         <v>10</v>
       </c>
       <c r="C57">
-        <v>33.31245255516097</v>
+        <v>33.73370320039719</v>
       </c>
       <c r="D57">
-        <v>25.36461330330757</v>
+        <v>25.880209881309</v>
       </c>
       <c r="E57">
-        <v>0.9989999999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="F57">
-        <v>0.9989999999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="G57">
-        <v>0.05845447259401171</v>
+        <v>0.08201990413931148</v>
       </c>
       <c r="H57">
-        <v>0.9989999999999999</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="B58" t="s">
         <v>10</v>
       </c>
       <c r="C58">
-        <v>33.02444632653544</v>
+        <v>33.45546240777382</v>
       </c>
       <c r="D58">
-        <v>25.07926152561908</v>
+        <v>25.61350381215703</v>
       </c>
       <c r="E58">
-        <v>0.9991</v>
+        <v>0.999</v>
       </c>
       <c r="F58">
-        <v>0.9991</v>
+        <v>0.999</v>
       </c>
       <c r="G58">
-        <v>0.04697780820974229</v>
+        <v>0.06901304118647311</v>
       </c>
       <c r="H58">
-        <v>0.9991</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1">
-        <v>46177</v>
+        <v>46175</v>
       </c>
       <c r="B59" t="s">
         <v>10</v>
       </c>
       <c r="C59">
-        <v>33.50291463064395</v>
+        <v>33.31245255516097</v>
       </c>
       <c r="D59">
-        <v>25.33002193941023</v>
+        <v>25.36461330330757</v>
       </c>
       <c r="E59">
-        <v>0.9991000000000001</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="F59">
-        <v>0.9991000000000001</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="G59">
-        <v>0.05768943168306073</v>
+        <v>0.05845447259401171</v>
       </c>
       <c r="H59">
-        <v>0.9991000000000001</v>
+        <v>0.9989999999999999</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1">
-        <v>46178</v>
+        <v>46176</v>
       </c>
       <c r="B60" t="s">
         <v>10</v>
       </c>
       <c r="C60">
-        <v>32.19021336116872</v>
+        <v>33.02444632653544</v>
       </c>
       <c r="D60">
-        <v>24.38570557505481</v>
+        <v>25.07926152561908</v>
       </c>
       <c r="E60">
         <v>0.9991</v>
@@ -1957,7 +1957,7 @@
         <v>0.9991</v>
       </c>
       <c r="G60">
-        <v>0.01775063028607016</v>
+        <v>0.04697780820974229</v>
       </c>
       <c r="H60">
         <v>0.9991</v>
@@ -1965,822 +1965,822 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1">
-        <v>46182</v>
+        <v>46177</v>
       </c>
       <c r="B61" t="s">
         <v>10</v>
       </c>
       <c r="C61">
-        <v>32.06505731417286</v>
+        <v>33.50291463064395</v>
       </c>
       <c r="D61">
-        <v>24.06041109516704</v>
+        <v>25.33002193941023</v>
       </c>
       <c r="E61">
-        <v>0.9988999999999999</v>
+        <v>0.9991000000000001</v>
       </c>
       <c r="F61">
-        <v>0.9988999999999999</v>
+        <v>0.9991000000000001</v>
       </c>
       <c r="G61">
-        <v>0.004743767333231785</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H61">
-        <v>0.9988999999999999</v>
+        <v>0.9991000000000001</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1">
-        <v>46183</v>
+        <v>46178</v>
       </c>
       <c r="B62" t="s">
         <v>10</v>
       </c>
       <c r="C62">
-        <v>31.23512211947358</v>
+        <v>32.19021336116872</v>
       </c>
       <c r="D62">
-        <v>23.50146802051874</v>
+        <v>24.38570557505481</v>
       </c>
       <c r="E62">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F62">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G62">
-        <v>-0.01729146564349893</v>
+        <v>0.01775063028607016</v>
       </c>
       <c r="H62">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="B63" t="s">
         <v>10</v>
       </c>
       <c r="C63">
-        <v>31.67819012660615</v>
+        <v>32.06505731417286</v>
       </c>
       <c r="D63">
-        <v>23.76719139935413</v>
+        <v>24.06041109516704</v>
       </c>
       <c r="E63">
-        <v>0.9992000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="F63">
-        <v>0.9992000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="G63">
-        <v>-0.006732897051037523</v>
+        <v>0.004743767333231785</v>
       </c>
       <c r="H63">
-        <v>0.9992000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1">
-        <v>46153</v>
+        <v>46183</v>
       </c>
       <c r="B64" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C64">
-        <v>36.55790859258162</v>
+        <v>31.23512211947358</v>
       </c>
       <c r="D64">
-        <v>22.67181120908155</v>
+        <v>23.50146802051874</v>
       </c>
       <c r="E64">
-        <v>0.9990740999999999</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="F64">
-        <v>0.9990740999999999</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="G64">
-        <v>0.1648443271746771</v>
+        <v>-0.01729146564349893</v>
       </c>
       <c r="H64">
-        <v>0.9990740999999999</v>
+        <v>0.9989999999999999</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1">
-        <v>46154</v>
+        <v>46184</v>
       </c>
       <c r="B65" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C65">
-        <v>36.44753722959613</v>
+        <v>31.67819012660615</v>
       </c>
       <c r="D65">
-        <v>22.40292401789388</v>
+        <v>23.76719139935413</v>
       </c>
       <c r="E65">
-        <v>0.9990772499999999</v>
+        <v>0.9992000000000001</v>
       </c>
       <c r="F65">
-        <v>0.9990772499999999</v>
+        <v>0.9992000000000001</v>
       </c>
       <c r="G65">
-        <v>0.154964342628132</v>
+        <v>-0.006732897051037523</v>
       </c>
       <c r="H65">
-        <v>0.9990772499999999</v>
+        <v>0.9992000000000001</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1">
-        <v>46155</v>
+        <v>46185</v>
       </c>
       <c r="B66" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C66">
-        <v>36.63128514035871</v>
+        <v>31.61398696858495</v>
       </c>
       <c r="D66">
-        <v>22.65773388934668</v>
+        <v>23.75142539276475</v>
       </c>
       <c r="E66">
-        <v>0.99907745</v>
+        <v>0.9992000000000002</v>
       </c>
       <c r="F66">
-        <v>0.99907745</v>
+        <v>0.9992000000000002</v>
       </c>
       <c r="G66">
-        <v>0.1671633421405267</v>
+        <v>-0.006732897051037523</v>
       </c>
       <c r="H66">
-        <v>0.99907745</v>
+        <v>0.9992000000000002</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="B67" t="s">
         <v>11</v>
       </c>
       <c r="C67">
-        <v>36.87865927427314</v>
+        <v>36.55790859258162</v>
       </c>
       <c r="D67">
-        <v>22.69755646854794</v>
+        <v>22.67181120908155</v>
       </c>
       <c r="E67">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="F67">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="G67">
-        <v>0.1754592080224002</v>
+        <v>0.1648443271746771</v>
       </c>
       <c r="H67">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="B68" t="s">
         <v>11</v>
       </c>
       <c r="C68">
-        <v>36.52208783231286</v>
+        <v>36.44753722959613</v>
       </c>
       <c r="D68">
-        <v>22.32462309676992</v>
+        <v>22.40292401789388</v>
       </c>
       <c r="E68">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="F68">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="G68">
-        <v>0.1577242156354994</v>
+        <v>0.154964342628132</v>
       </c>
       <c r="H68">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="B69" t="s">
         <v>11</v>
       </c>
       <c r="C69">
-        <v>36.25604200674668</v>
+        <v>36.63128514035871</v>
       </c>
       <c r="D69">
-        <v>22.16555007468561</v>
+        <v>22.65773388934668</v>
       </c>
       <c r="E69">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="F69">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="G69">
-        <v>0.1527434068648266</v>
+        <v>0.1671633421405267</v>
       </c>
       <c r="H69">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1">
-        <v>46161</v>
+        <v>46156</v>
       </c>
       <c r="B70" t="s">
         <v>11</v>
       </c>
       <c r="C70">
-        <v>36.01040085730018</v>
+        <v>36.87865927427314</v>
       </c>
       <c r="D70">
-        <v>22.19475589056387</v>
+        <v>22.69755646854794</v>
       </c>
       <c r="E70">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="F70">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="G70">
-        <v>0.1456396418594061</v>
+        <v>0.1754592080224002</v>
       </c>
       <c r="H70">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1">
-        <v>46162</v>
+        <v>46157</v>
       </c>
       <c r="B71" t="s">
         <v>11</v>
       </c>
       <c r="C71">
-        <v>36.45290912796982</v>
+        <v>36.52208783231286</v>
       </c>
       <c r="D71">
-        <v>22.46357594746874</v>
+        <v>22.32462309676992</v>
       </c>
       <c r="E71">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="F71">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="G71">
-        <v>0.1646157747240327</v>
+        <v>0.1577242156354994</v>
       </c>
       <c r="H71">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1">
-        <v>46163</v>
+        <v>46160</v>
       </c>
       <c r="B72" t="s">
         <v>11</v>
       </c>
       <c r="C72">
-        <v>35.75282090566891</v>
+        <v>36.25604200674668</v>
       </c>
       <c r="D72">
-        <v>22.57615417310648</v>
+        <v>22.16555007468561</v>
       </c>
       <c r="E72">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="F72">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="G72">
-        <v>0.1668367104873381</v>
+        <v>0.1527434068648266</v>
       </c>
       <c r="H72">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1">
-        <v>46164</v>
+        <v>46161</v>
       </c>
       <c r="B73" t="s">
         <v>11</v>
       </c>
       <c r="C73">
-        <v>35.75514940724808</v>
+        <v>36.01040085730018</v>
       </c>
       <c r="D73">
-        <v>22.28880693466429</v>
+        <v>22.19475589056387</v>
       </c>
       <c r="E73">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="F73">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="G73">
-        <v>0.1717848261904962</v>
+        <v>0.1456396418594061</v>
       </c>
       <c r="H73">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1">
-        <v>46167</v>
+        <v>46162</v>
       </c>
       <c r="B74" t="s">
         <v>11</v>
       </c>
       <c r="C74">
-        <v>35.84133099010302</v>
+        <v>36.45290912796982</v>
       </c>
       <c r="D74">
-        <v>22.37458514769363</v>
+        <v>22.46357594746874</v>
       </c>
       <c r="E74">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="F74">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="G74">
-        <v>0.1717848261904962</v>
+        <v>0.1646157747240327</v>
       </c>
       <c r="H74">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1">
-        <v>46168</v>
+        <v>46163</v>
       </c>
       <c r="B75" t="s">
         <v>11</v>
       </c>
       <c r="C75">
-        <v>36.23214279739292</v>
+        <v>35.75282090566891</v>
       </c>
       <c r="D75">
-        <v>22.93484792820123</v>
+        <v>22.57615417310648</v>
       </c>
       <c r="E75">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
       <c r="F75">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
       <c r="G75">
-        <v>0.1925900763781823</v>
+        <v>0.1668367104873381</v>
       </c>
       <c r="H75">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="B76" t="s">
         <v>11</v>
       </c>
       <c r="C76">
-        <v>36.4336692499184</v>
+        <v>35.75514940724808</v>
       </c>
       <c r="D76">
-        <v>22.75940954009856</v>
+        <v>22.28880693466429</v>
       </c>
       <c r="E76">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="F76">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="G76">
-        <v>0.1912346098381414</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H76">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="B77" t="s">
         <v>11</v>
       </c>
       <c r="C77">
-        <v>36.57358557066742</v>
+        <v>35.84133099010302</v>
       </c>
       <c r="D77">
-        <v>22.83069636955243</v>
+        <v>22.37458514769363</v>
       </c>
       <c r="E77">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="F77">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="G77">
-        <v>0.2012778603742877</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H77">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="1">
-        <v>46171</v>
+        <v>46168</v>
       </c>
       <c r="B78" t="s">
         <v>11</v>
       </c>
       <c r="C78">
-        <v>36.67481300942</v>
+        <v>36.23214279739292</v>
       </c>
       <c r="D78">
-        <v>22.95852861681004</v>
+        <v>22.93484792820123</v>
       </c>
       <c r="E78">
-        <v>0.9964953299999998</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="F78">
-        <v>0.9964953299999998</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="G78">
-        <v>0.2057034850411275</v>
+        <v>0.1925900763781823</v>
       </c>
       <c r="H78">
-        <v>0.9994474899999999</v>
+        <v>0.9992609200000001</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1">
-        <v>46174</v>
+        <v>46169</v>
       </c>
       <c r="B79" t="s">
         <v>11</v>
       </c>
       <c r="C79">
-        <v>36.84565507982974</v>
+        <v>36.4336692499184</v>
       </c>
       <c r="D79">
-        <v>23.15960292175205</v>
+        <v>22.75940954009856</v>
       </c>
       <c r="E79">
-        <v>0.99646052</v>
+        <v>0.9992099400000001</v>
       </c>
       <c r="F79">
-        <v>0.99646052</v>
+        <v>0.9992099400000001</v>
       </c>
       <c r="G79">
-        <v>0.2129379226426205</v>
+        <v>0.1912346098381414</v>
       </c>
       <c r="H79">
-        <v>0.9993986199999999</v>
+        <v>0.9992099400000001</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1">
-        <v>46175</v>
+        <v>46170</v>
       </c>
       <c r="B80" t="s">
         <v>11</v>
       </c>
       <c r="C80">
-        <v>36.88482057171844</v>
+        <v>36.57358557066742</v>
       </c>
       <c r="D80">
-        <v>23.03898938038424</v>
+        <v>22.83069636955243</v>
       </c>
       <c r="E80">
-        <v>0.99645675</v>
+        <v>0.9994435600000001</v>
       </c>
       <c r="F80">
-        <v>0.99645675</v>
+        <v>0.9994435600000001</v>
       </c>
       <c r="G80">
-        <v>0.2185229551183987</v>
+        <v>0.2012778603742877</v>
       </c>
       <c r="H80">
-        <v>0.9994034199999998</v>
+        <v>0.9994435600000001</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="1">
-        <v>46176</v>
+        <v>46171</v>
       </c>
       <c r="B81" t="s">
         <v>11</v>
       </c>
       <c r="C81">
-        <v>36.96809213745556</v>
+        <v>36.67481300942</v>
       </c>
       <c r="D81">
-        <v>22.99660212231548</v>
+        <v>22.95852861681004</v>
       </c>
       <c r="E81">
-        <v>0.9964706</v>
+        <v>0.9964953299999998</v>
       </c>
       <c r="F81">
-        <v>0.9964706</v>
+        <v>0.9964953299999998</v>
       </c>
       <c r="G81">
-        <v>0.2153385706032709</v>
+        <v>0.2057034850411275</v>
       </c>
       <c r="H81">
-        <v>0.9993955800000001</v>
+        <v>0.9994474899999999</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="1">
-        <v>46177</v>
+        <v>46174</v>
       </c>
       <c r="B82" t="s">
         <v>11</v>
       </c>
       <c r="C82">
-        <v>37.13780815830533</v>
+        <v>36.84565507982974</v>
       </c>
       <c r="D82">
-        <v>22.74889586257873</v>
+        <v>23.15960292175205</v>
       </c>
       <c r="E82">
-        <v>0.9964706899999999</v>
+        <v>0.99646052</v>
       </c>
       <c r="F82">
-        <v>0.9964706899999999</v>
+        <v>0.99646052</v>
       </c>
       <c r="G82">
-        <v>0.2094594998678323</v>
+        <v>0.2129379226426205</v>
       </c>
       <c r="H82">
-        <v>0.99938478</v>
+        <v>0.9993986199999999</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="1">
-        <v>46178</v>
+        <v>46175</v>
       </c>
       <c r="B83" t="s">
         <v>11</v>
       </c>
       <c r="C83">
-        <v>35.57681391373501</v>
+        <v>36.88482057171844</v>
       </c>
       <c r="D83">
-        <v>21.69452833602077</v>
+        <v>23.03898938038424</v>
       </c>
       <c r="E83">
-        <v>0.9964558499999999</v>
+        <v>0.99645675</v>
       </c>
       <c r="F83">
-        <v>0.9964558499999999</v>
+        <v>0.99645675</v>
       </c>
       <c r="G83">
-        <v>0.151404286858543</v>
+        <v>0.2185229551183987</v>
       </c>
       <c r="H83">
-        <v>0.9993850399999999</v>
+        <v>0.9994034199999998</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="1">
-        <v>46182</v>
+        <v>46176</v>
       </c>
       <c r="B84" t="s">
         <v>11</v>
       </c>
       <c r="C84">
-        <v>35.58815840295288</v>
+        <v>36.96809213745556</v>
       </c>
       <c r="D84">
-        <v>21.80812849732373</v>
+        <v>22.99660212231548</v>
       </c>
       <c r="E84">
-        <v>0.9962853900000002</v>
+        <v>0.9964706</v>
       </c>
       <c r="F84">
-        <v>0.9962853900000002</v>
+        <v>0.9964706</v>
       </c>
       <c r="G84">
-        <v>0.1559278910539408</v>
+        <v>0.2153385706032709</v>
       </c>
       <c r="H84">
-        <v>0.9992534400000002</v>
+        <v>0.9993955800000001</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1">
-        <v>46183</v>
+        <v>46177</v>
       </c>
       <c r="B85" t="s">
         <v>11</v>
       </c>
       <c r="C85">
-        <v>34.74027179067053</v>
+        <v>37.13780815830533</v>
       </c>
       <c r="D85">
-        <v>21.20683390251297</v>
+        <v>22.74889586257873</v>
       </c>
       <c r="E85">
-        <v>0.9962360400000001</v>
+        <v>0.9964706899999999</v>
       </c>
       <c r="F85">
-        <v>0.9962360400000001</v>
+        <v>0.9964706899999999</v>
       </c>
       <c r="G85">
-        <v>0.132836418641906</v>
+        <v>0.2094594998678323</v>
       </c>
       <c r="H85">
-        <v>0.9992478800000001</v>
+        <v>0.99938478</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="1">
-        <v>46184</v>
+        <v>46178</v>
       </c>
       <c r="B86" t="s">
         <v>11</v>
       </c>
       <c r="C86">
-        <v>35.56883979970284</v>
+        <v>35.57681391373501</v>
       </c>
       <c r="D86">
-        <v>21.93852986554604</v>
+        <v>21.69452833602077</v>
       </c>
       <c r="E86">
-        <v>0.9961625199999998</v>
+        <v>0.9964558499999999</v>
       </c>
       <c r="F86">
-        <v>0.9961625199999998</v>
+        <v>0.9964558499999999</v>
       </c>
       <c r="G86">
-        <v>0.1710989694905902</v>
+        <v>0.151404286858543</v>
       </c>
       <c r="H86">
-        <v>0.999197</v>
+        <v>0.9993850399999999</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="1">
-        <v>46153</v>
+        <v>46182</v>
       </c>
       <c r="B87" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C87">
-        <v>52.70832779833182</v>
+        <v>35.58815840295288</v>
       </c>
       <c r="D87">
-        <v>23.99044674439659</v>
+        <v>21.80812849732373</v>
       </c>
       <c r="E87">
-        <v>0.9994000000000002</v>
+        <v>0.9962853900000002</v>
       </c>
       <c r="F87">
-        <v>0.9994000000000002</v>
+        <v>0.9962853900000002</v>
       </c>
       <c r="G87">
-        <v>0.5438253854918791</v>
+        <v>0.1559278910539408</v>
       </c>
       <c r="H87">
-        <v>0.9994000000000002</v>
+        <v>0.9992534400000002</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1">
-        <v>46154</v>
+        <v>46183</v>
       </c>
       <c r="B88" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C88">
-        <v>50.89464485280568</v>
+        <v>34.74027179067053</v>
       </c>
       <c r="D88">
-        <v>23.21558303176282</v>
+        <v>21.20683390251297</v>
       </c>
       <c r="E88">
-        <v>0.9996</v>
+        <v>0.9962360400000001</v>
       </c>
       <c r="F88">
-        <v>0.9996</v>
+        <v>0.9962360400000001</v>
       </c>
       <c r="G88">
-        <v>0.5034825029548833</v>
+        <v>0.132836418641906</v>
       </c>
       <c r="H88">
-        <v>0.9996</v>
+        <v>0.9992478800000001</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="1">
-        <v>46155</v>
+        <v>46184</v>
       </c>
       <c r="B89" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C89">
-        <v>51.8659994471731</v>
+        <v>35.56883979970284</v>
       </c>
       <c r="D89">
-        <v>23.7009037279043</v>
+        <v>21.93852986554604</v>
       </c>
       <c r="E89">
-        <v>1.0002</v>
+        <v>0.9961625199999998</v>
       </c>
       <c r="F89">
-        <v>1.0002</v>
+        <v>0.9961625199999998</v>
       </c>
       <c r="G89">
-        <v>0.533512029714132</v>
+        <v>0.1710989694905902</v>
       </c>
       <c r="H89">
-        <v>1.0002</v>
+        <v>0.999197</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="1">
-        <v>46156</v>
+        <v>46185</v>
       </c>
       <c r="B90" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C90">
-        <v>52.4470179952828</v>
+        <v>35.92309284525166</v>
       </c>
       <c r="D90">
-        <v>23.76861704536814</v>
+        <v>22.00037840050582</v>
       </c>
       <c r="E90">
-        <v>0.9998</v>
+        <v>0.99603186</v>
       </c>
       <c r="F90">
-        <v>0.9998</v>
+        <v>0.99603186</v>
       </c>
       <c r="G90">
-        <v>0.5492634496849078</v>
+        <v>0.1779905285791235</v>
       </c>
       <c r="H90">
-        <v>0.9998</v>
+        <v>0.99904038</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="1">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="B91" t="s">
         <v>12</v>
       </c>
       <c r="C91">
-        <v>50.81077380018606</v>
+        <v>52.70832779833182</v>
       </c>
       <c r="D91">
-        <v>22.76900580927995</v>
+        <v>23.99044674439659</v>
       </c>
       <c r="E91">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="F91">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="G91">
-        <v>0.4903296143797722</v>
+        <v>0.5438253854918791</v>
       </c>
       <c r="H91">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="1">
-        <v>46160</v>
+        <v>46154</v>
       </c>
       <c r="B92" t="s">
         <v>12</v>
       </c>
       <c r="C92">
-        <v>49.50286387149169</v>
+        <v>50.89464485280568</v>
       </c>
       <c r="D92">
-        <v>22.24532119914133</v>
+        <v>23.21558303176282</v>
       </c>
       <c r="E92">
         <v>0.9996</v>
@@ -2789,7 +2789,7 @@
         <v>0.9996</v>
       </c>
       <c r="G92">
-        <v>0.4630591776162345</v>
+        <v>0.5034825029548833</v>
       </c>
       <c r="H92">
         <v>0.9996</v>
@@ -2797,224 +2797,224 @@
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="1">
-        <v>46161</v>
+        <v>46155</v>
       </c>
       <c r="B93" t="s">
         <v>12</v>
       </c>
       <c r="C93">
-        <v>49.29146729279496</v>
+        <v>51.8659994471731</v>
       </c>
       <c r="D93">
-        <v>22.22167836589682</v>
+        <v>23.7009037279043</v>
       </c>
       <c r="E93">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="F93">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="G93">
-        <v>0.4571659248870246</v>
+        <v>0.533512029714132</v>
       </c>
       <c r="H93">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="1">
-        <v>46162</v>
+        <v>46156</v>
       </c>
       <c r="B94" t="s">
         <v>12</v>
       </c>
       <c r="C94">
-        <v>50.88652370817657</v>
+        <v>52.4470179952828</v>
       </c>
       <c r="D94">
-        <v>22.93254398967657</v>
+        <v>23.76861704536814</v>
       </c>
       <c r="E94">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F94">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G94">
-        <v>0.5126171754864624</v>
+        <v>0.5492634496849078</v>
       </c>
       <c r="H94">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="1">
-        <v>46163</v>
+        <v>46157</v>
       </c>
       <c r="B95" t="s">
         <v>12</v>
       </c>
       <c r="C95">
-        <v>48.26646764818586</v>
+        <v>50.81077380018606</v>
       </c>
       <c r="D95">
-        <v>23.11655387625012</v>
+        <v>22.76900580927995</v>
       </c>
       <c r="E95">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="F95">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="G95">
-        <v>0.521243030947425</v>
+        <v>0.4903296143797722</v>
       </c>
       <c r="H95">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="1">
-        <v>46164</v>
+        <v>46160</v>
       </c>
       <c r="B96" t="s">
         <v>12</v>
       </c>
       <c r="C96">
-        <v>48.84737503703267</v>
+        <v>49.50286387149169</v>
       </c>
       <c r="D96">
-        <v>22.83557604744466</v>
+        <v>22.24532119914133</v>
       </c>
       <c r="E96">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="F96">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="G96">
-        <v>0.5438521997590966</v>
+        <v>0.4630591776162345</v>
       </c>
       <c r="H96">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="1">
-        <v>46167</v>
+        <v>46161</v>
       </c>
       <c r="B97" t="s">
         <v>12</v>
       </c>
       <c r="C97">
-        <v>48.85151560750146</v>
+        <v>49.29146729279496</v>
       </c>
       <c r="D97">
-        <v>22.83513820206554</v>
+        <v>22.22167836589682</v>
       </c>
       <c r="E97">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F97">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G97">
-        <v>0.5438521997590966</v>
+        <v>0.4571659248870246</v>
       </c>
       <c r="H97">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="1">
-        <v>46168</v>
+        <v>46162</v>
       </c>
       <c r="B98" t="s">
         <v>12</v>
       </c>
       <c r="C98">
-        <v>50.90437883274981</v>
+        <v>50.88652370817657</v>
       </c>
       <c r="D98">
-        <v>24.25672473501501</v>
+        <v>22.93254398967657</v>
       </c>
       <c r="E98">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F98">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G98">
-        <v>0.6130191115419561</v>
+        <v>0.5126171754864624</v>
       </c>
       <c r="H98">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="1">
-        <v>46169</v>
+        <v>46163</v>
       </c>
       <c r="B99" t="s">
         <v>12</v>
       </c>
       <c r="C99">
-        <v>50.47312432255841</v>
+        <v>48.26646764818586</v>
       </c>
       <c r="D99">
-        <v>23.84499305142194</v>
+        <v>23.11655387625012</v>
       </c>
       <c r="E99">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="F99">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="G99">
-        <v>0.5952317692821967</v>
+        <v>0.521243030947425</v>
       </c>
       <c r="H99">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="1">
-        <v>46170</v>
+        <v>46164</v>
       </c>
       <c r="B100" t="s">
         <v>12</v>
       </c>
       <c r="C100">
-        <v>50.84596269629946</v>
+        <v>48.84737503703267</v>
       </c>
       <c r="D100">
-        <v>23.7680603326165</v>
+        <v>22.83557604744466</v>
       </c>
       <c r="E100">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F100">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G100">
-        <v>0.606831065374982</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H100">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="1">
-        <v>46171</v>
+        <v>46167</v>
       </c>
       <c r="B101" t="s">
         <v>12</v>
       </c>
       <c r="C101">
-        <v>51.08372269965196</v>
+        <v>48.85151560750146</v>
       </c>
       <c r="D101">
-        <v>23.88880359436525</v>
+        <v>22.83513820206554</v>
       </c>
       <c r="E101">
         <v>0.9998999999999999</v>
@@ -3023,7 +3023,7 @@
         <v>0.9998999999999999</v>
       </c>
       <c r="G101">
-        <v>0.604420070348211</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H101">
         <v>0.9998999999999999</v>
@@ -3031,666 +3031,666 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="1">
-        <v>46174</v>
+        <v>46168</v>
       </c>
       <c r="B102" t="s">
         <v>12</v>
       </c>
       <c r="C102">
-        <v>51.84875713649351</v>
+        <v>50.90437883274981</v>
       </c>
       <c r="D102">
-        <v>24.29466650399529</v>
+        <v>24.25672473501501</v>
       </c>
       <c r="E102">
-        <v>0.9998</v>
+        <v>0.9996999999999999</v>
       </c>
       <c r="F102">
-        <v>0.9998</v>
+        <v>0.9996999999999999</v>
       </c>
       <c r="G102">
-        <v>0.6282079224060508</v>
+        <v>0.6130191115419561</v>
       </c>
       <c r="H102">
-        <v>0.9998</v>
+        <v>0.9996999999999999</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="1">
-        <v>46175</v>
+        <v>46169</v>
       </c>
       <c r="B103" t="s">
         <v>12</v>
       </c>
       <c r="C103">
-        <v>53.42858844634741</v>
+        <v>50.47312432255841</v>
       </c>
       <c r="D103">
-        <v>24.82449061140869</v>
+        <v>23.84499305142194</v>
       </c>
       <c r="E103">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="F103">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="G103">
-        <v>0.6935709687814895</v>
+        <v>0.5952317692821967</v>
       </c>
       <c r="H103">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="1">
-        <v>46176</v>
+        <v>46170</v>
       </c>
       <c r="B104" t="s">
         <v>12</v>
       </c>
       <c r="C104">
-        <v>53.95056789686777</v>
+        <v>50.84596269629946</v>
       </c>
       <c r="D104">
-        <v>24.99295077214167</v>
+        <v>23.7680603326165</v>
       </c>
       <c r="E104">
-        <v>0.9996000000000002</v>
+        <v>0.9998</v>
       </c>
       <c r="F104">
-        <v>0.9996000000000002</v>
+        <v>0.9998</v>
       </c>
       <c r="G104">
-        <v>0.7088134081800193</v>
+        <v>0.606831065374982</v>
       </c>
       <c r="H104">
-        <v>0.9996000000000002</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="1">
-        <v>46177</v>
+        <v>46171</v>
       </c>
       <c r="B105" t="s">
         <v>12</v>
       </c>
       <c r="C105">
-        <v>53.29782764127071</v>
+        <v>51.08372269965196</v>
       </c>
       <c r="D105">
-        <v>24.48126483589962</v>
+        <v>23.88880359436525</v>
       </c>
       <c r="E105">
-        <v>1.0001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F105">
-        <v>1.0001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G105">
-        <v>0.6810341543458651</v>
+        <v>0.604420070348211</v>
       </c>
       <c r="H105">
-        <v>1.0001</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="1">
-        <v>46178</v>
+        <v>46174</v>
       </c>
       <c r="B106" t="s">
         <v>12</v>
       </c>
       <c r="C106">
-        <v>48.44949949587421</v>
+        <v>51.84875713649351</v>
       </c>
       <c r="D106">
-        <v>22.39103669390088</v>
+        <v>24.29466650399529</v>
       </c>
       <c r="E106">
-        <v>0.9995999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F106">
-        <v>0.9995999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G106">
-        <v>0.5260916717665549</v>
+        <v>0.6282079224060508</v>
       </c>
       <c r="H106">
-        <v>0.9995999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="1">
-        <v>46182</v>
+        <v>46175</v>
       </c>
       <c r="B107" t="s">
         <v>12</v>
       </c>
       <c r="C107">
-        <v>50.39371086612305</v>
+        <v>53.42858844634741</v>
       </c>
       <c r="D107">
-        <v>23.09650971949351</v>
+        <v>24.82449061140869</v>
       </c>
       <c r="E107">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="F107">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="G107">
-        <v>0.5832039354188183</v>
+        <v>0.6935709687814895</v>
       </c>
       <c r="H107">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="1">
-        <v>46183</v>
+        <v>46176</v>
       </c>
       <c r="B108" t="s">
         <v>12</v>
       </c>
       <c r="C108">
-        <v>48.17343634448468</v>
+        <v>53.95056789686777</v>
       </c>
       <c r="D108">
-        <v>22.05005999539094</v>
+        <v>24.99295077214167</v>
       </c>
       <c r="E108">
-        <v>0.9994999999999999</v>
+        <v>0.9996000000000002</v>
       </c>
       <c r="F108">
-        <v>0.9994999999999999</v>
+        <v>0.9996000000000002</v>
       </c>
       <c r="G108">
-        <v>0.5293597423345122</v>
+        <v>0.7088134081800193</v>
       </c>
       <c r="H108">
-        <v>0.9994999999999999</v>
+        <v>0.9996000000000002</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="1">
-        <v>46184</v>
+        <v>46177</v>
       </c>
       <c r="B109" t="s">
         <v>12</v>
       </c>
       <c r="C109">
-        <v>52.85189183366637</v>
+        <v>53.29782764127071</v>
       </c>
       <c r="D109">
-        <v>23.55442526604671</v>
+        <v>24.48126483589962</v>
       </c>
       <c r="E109">
-        <v>0.9996</v>
+        <v>1.0001</v>
       </c>
       <c r="F109">
-        <v>0.9996</v>
+        <v>1.0001</v>
       </c>
       <c r="G109">
-        <v>0.63260121118737</v>
+        <v>0.6810341543458651</v>
       </c>
       <c r="H109">
-        <v>0.9996</v>
+        <v>1.0001</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="1">
-        <v>46153</v>
+        <v>46178</v>
       </c>
       <c r="B110" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C110">
-        <v>57.1732166855686</v>
+        <v>48.44949949587421</v>
       </c>
       <c r="D110">
-        <v>23.50022751267814</v>
+        <v>22.39103669390088</v>
       </c>
       <c r="E110">
-        <v>0.9991</v>
+        <v>0.9995999999999999</v>
       </c>
       <c r="F110">
-        <v>0.9991</v>
+        <v>0.9995999999999999</v>
       </c>
       <c r="G110">
-        <v>0.6994110097039083</v>
+        <v>0.5260916717665549</v>
       </c>
       <c r="H110">
-        <v>0.9991</v>
+        <v>0.9995999999999999</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="1">
-        <v>46154</v>
+        <v>46182</v>
       </c>
       <c r="B111" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C111">
-        <v>54.77380642078597</v>
+        <v>50.39371086612305</v>
       </c>
       <c r="D111">
-        <v>22.55192940254518</v>
+        <v>23.09650971949351</v>
       </c>
       <c r="E111">
-        <v>0.9990000000000001</v>
+        <v>0.9997</v>
       </c>
       <c r="F111">
-        <v>0.9990000000000001</v>
+        <v>0.9997</v>
       </c>
       <c r="G111">
-        <v>0.6459175880844941</v>
+        <v>0.5832039354188183</v>
       </c>
       <c r="H111">
-        <v>0.9990000000000001</v>
+        <v>0.9997</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="1">
-        <v>46155</v>
+        <v>46183</v>
       </c>
       <c r="B112" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C112">
-        <v>56.32187380830906</v>
+        <v>48.17343634448468</v>
       </c>
       <c r="D112">
-        <v>23.17121437414109</v>
+        <v>22.05005999539094</v>
       </c>
       <c r="E112">
-        <v>0.9990000000000001</v>
+        <v>0.9994999999999999</v>
       </c>
       <c r="F112">
-        <v>0.9990000000000001</v>
+        <v>0.9994999999999999</v>
       </c>
       <c r="G112">
-        <v>0.6851523922954754</v>
+        <v>0.5293597423345122</v>
       </c>
       <c r="H112">
-        <v>0.9990000000000001</v>
+        <v>0.9994999999999999</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="1">
-        <v>46156</v>
+        <v>46184</v>
       </c>
       <c r="B113" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C113">
-        <v>56.15321618553139</v>
+        <v>52.85189183366637</v>
       </c>
       <c r="D113">
-        <v>22.95838347314443</v>
+        <v>23.55442526604671</v>
       </c>
       <c r="E113">
-        <v>0.9992</v>
+        <v>0.9996</v>
       </c>
       <c r="F113">
-        <v>0.9992</v>
+        <v>0.9996</v>
       </c>
       <c r="G113">
-        <v>0.6907028507208208</v>
+        <v>0.63260121118737</v>
       </c>
       <c r="H113">
-        <v>0.9992</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="1">
-        <v>46157</v>
+        <v>46185</v>
       </c>
       <c r="B114" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C114">
-        <v>54.47755813049488</v>
+        <v>52.27613812453644</v>
       </c>
       <c r="D114">
-        <v>22.0083816089626</v>
+        <v>23.80021779840316</v>
       </c>
       <c r="E114">
-        <v>0.9986</v>
+        <v>0.9993999999999998</v>
       </c>
       <c r="F114">
-        <v>0.9986</v>
+        <v>0.9993999999999998</v>
       </c>
       <c r="G114">
-        <v>0.6220895940829376</v>
+        <v>0.6607555377593115</v>
       </c>
       <c r="H114">
-        <v>0.9986</v>
+        <v>0.9993999999999998</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B115" t="s">
         <v>13</v>
       </c>
       <c r="C115">
-        <v>52.6278781150669</v>
+        <v>57.1732166855686</v>
       </c>
       <c r="D115">
-        <v>21.5357353870778</v>
+        <v>23.50022751267814</v>
       </c>
       <c r="E115">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F115">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G115">
-        <v>0.5845134636435627</v>
+        <v>0.6994110097039083</v>
       </c>
       <c r="H115">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B116" t="s">
         <v>13</v>
       </c>
       <c r="C116">
-        <v>54.91583234840245</v>
+        <v>54.77380642078597</v>
       </c>
       <c r="D116">
-        <v>22.38321645985006</v>
+        <v>22.55192940254518</v>
       </c>
       <c r="E116">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F116">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G116">
-        <v>0.6596976539194066</v>
+        <v>0.6459175880844941</v>
       </c>
       <c r="H116">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B117" t="s">
         <v>13</v>
       </c>
       <c r="C117">
-        <v>53.91712298548793</v>
+        <v>56.32187380830906</v>
       </c>
       <c r="D117">
-        <v>22.73711181201267</v>
+        <v>23.17121437414109</v>
       </c>
       <c r="E117">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F117">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G117">
-        <v>0.6737329602396263</v>
+        <v>0.6851523922954754</v>
       </c>
       <c r="H117">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="1">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="B118" t="s">
         <v>13</v>
       </c>
       <c r="C118">
-        <v>55.19651747515625</v>
+        <v>56.15321618553139</v>
       </c>
       <c r="D118">
-        <v>22.79462037330554</v>
+        <v>22.95838347314443</v>
       </c>
       <c r="E118">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
       <c r="F118">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
       <c r="G118">
-        <v>0.7139885317003913</v>
+        <v>0.6907028507208208</v>
       </c>
       <c r="H118">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="1">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="B119" t="s">
         <v>13</v>
       </c>
       <c r="C119">
-        <v>55.28054997487197</v>
+        <v>54.47755813049488</v>
       </c>
       <c r="D119">
-        <v>23.00160891539877</v>
+        <v>22.0083816089626</v>
       </c>
       <c r="E119">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="F119">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="G119">
-        <v>0.7139885317003913</v>
+        <v>0.6220895940829376</v>
       </c>
       <c r="H119">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="1">
-        <v>46168</v>
+        <v>46161</v>
       </c>
       <c r="B120" t="s">
         <v>13</v>
       </c>
       <c r="C120">
-        <v>58.75156728873073</v>
+        <v>52.6278781150669</v>
       </c>
       <c r="D120">
-        <v>24.84249654093248</v>
+        <v>21.5357353870778</v>
       </c>
       <c r="E120">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="F120">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="G120">
-        <v>0.8184872182632257</v>
+        <v>0.5845134636435627</v>
       </c>
       <c r="H120">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="1">
-        <v>46169</v>
+        <v>46162</v>
       </c>
       <c r="B121" t="s">
         <v>13</v>
       </c>
       <c r="C121">
-        <v>57.86771234337395</v>
+        <v>54.91583234840245</v>
       </c>
       <c r="D121">
-        <v>24.21066615243091</v>
+        <v>22.38321645985006</v>
       </c>
       <c r="E121">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="F121">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="G121">
-        <v>0.798997241708943</v>
+        <v>0.6596976539194066</v>
       </c>
       <c r="H121">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="1">
-        <v>46170</v>
+        <v>46163</v>
       </c>
       <c r="B122" t="s">
         <v>13</v>
       </c>
       <c r="C122">
-        <v>58.18666682631797</v>
+        <v>53.91712298548793</v>
       </c>
       <c r="D122">
-        <v>24.09552344282839</v>
+        <v>22.73711181201267</v>
       </c>
       <c r="E122">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="F122">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="G122">
-        <v>0.8165093478664007</v>
+        <v>0.6737329602396263</v>
       </c>
       <c r="H122">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="1">
-        <v>46171</v>
+        <v>46164</v>
       </c>
       <c r="B123" t="s">
         <v>13</v>
       </c>
       <c r="C123">
-        <v>58.79256019733606</v>
+        <v>55.19651747515625</v>
       </c>
       <c r="D123">
-        <v>24.33854853448823</v>
+        <v>22.79462037330554</v>
       </c>
       <c r="E123">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F123">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G123">
-        <v>0.8152654642198496</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H123">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="1">
-        <v>46174</v>
+        <v>46167</v>
       </c>
       <c r="B124" t="s">
         <v>13</v>
       </c>
       <c r="C124">
-        <v>58.97156722185718</v>
+        <v>55.28054997487197</v>
       </c>
       <c r="D124">
-        <v>24.48296361348067</v>
+        <v>23.00160891539877</v>
       </c>
       <c r="E124">
-        <v>0.9990000000000001</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="F124">
-        <v>0.9990000000000001</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="G124">
-        <v>0.8243563865851753</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H124">
-        <v>0.9990000000000001</v>
+        <v>0.9989000000000001</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="1">
-        <v>46175</v>
+        <v>46168</v>
       </c>
       <c r="B125" t="s">
         <v>13</v>
       </c>
       <c r="C125">
-        <v>61.6542902214027</v>
+        <v>58.75156728873073</v>
       </c>
       <c r="D125">
-        <v>25.06517348653028</v>
+        <v>24.84249654093248</v>
       </c>
       <c r="E125">
-        <v>0.9988</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="F125">
-        <v>0.9988</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="G125">
-        <v>0.9299077697948877</v>
+        <v>0.8184872182632257</v>
       </c>
       <c r="H125">
-        <v>0.9988</v>
+        <v>0.9989000000000001</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" s="1">
-        <v>46176</v>
+        <v>46169</v>
       </c>
       <c r="B126" t="s">
         <v>13</v>
       </c>
       <c r="C126">
-        <v>63.0681947750049</v>
+        <v>57.86771234337395</v>
       </c>
       <c r="D126">
-        <v>25.58770976382014</v>
+        <v>24.21066615243091</v>
       </c>
       <c r="E126">
-        <v>0.9988000000000002</v>
+        <v>0.9986999999999999</v>
       </c>
       <c r="F126">
-        <v>0.9988000000000002</v>
+        <v>0.9986999999999999</v>
       </c>
       <c r="G126">
-        <v>0.9639112148600193</v>
+        <v>0.798997241708943</v>
       </c>
       <c r="H126">
-        <v>0.9988000000000002</v>
+        <v>0.9986999999999999</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" s="1">
-        <v>46177</v>
+        <v>46170</v>
       </c>
       <c r="B127" t="s">
         <v>13</v>
       </c>
       <c r="C127">
-        <v>61.53154955456358</v>
+        <v>58.18666682631797</v>
       </c>
       <c r="D127">
-        <v>24.75810538712983</v>
+        <v>24.09552344282839</v>
       </c>
       <c r="E127">
         <v>0.9991</v>
@@ -3699,7 +3699,7 @@
         <v>0.9991</v>
       </c>
       <c r="G127">
-        <v>0.9225710173552821</v>
+        <v>0.8165093478664007</v>
       </c>
       <c r="H127">
         <v>0.9991</v>
@@ -3707,978 +3707,978 @@
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="1">
-        <v>46178</v>
+        <v>46171</v>
       </c>
       <c r="B128" t="s">
         <v>13</v>
       </c>
       <c r="C128">
-        <v>55.42493637343647</v>
+        <v>58.79256019733606</v>
       </c>
       <c r="D128">
-        <v>22.47054621698377</v>
+        <v>24.33854853448823</v>
       </c>
       <c r="E128">
-        <v>0.9987</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="F128">
-        <v>0.9987</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="G128">
-        <v>0.7217717116249776</v>
+        <v>0.8152654642198496</v>
       </c>
       <c r="H128">
-        <v>0.9987</v>
+        <v>0.9989999999999999</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="1">
-        <v>46182</v>
+        <v>46174</v>
       </c>
       <c r="B129" t="s">
         <v>13</v>
       </c>
       <c r="C129">
-        <v>57.84835101034041</v>
+        <v>58.97156722185718</v>
       </c>
       <c r="D129">
-        <v>23.24662656171655</v>
+        <v>24.48296361348067</v>
       </c>
       <c r="E129">
-        <v>0.999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F129">
-        <v>0.999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G129">
-        <v>0.7931280733869936</v>
+        <v>0.8243563865851753</v>
       </c>
       <c r="H129">
-        <v>0.999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" s="1">
-        <v>46183</v>
+        <v>46175</v>
       </c>
       <c r="B130" t="s">
         <v>13</v>
       </c>
       <c r="C130">
-        <v>55.28729760663236</v>
+        <v>61.6542902214027</v>
       </c>
       <c r="D130">
-        <v>22.10409273362112</v>
+        <v>25.06517348653028</v>
       </c>
       <c r="E130">
-        <v>0.9987999999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="F130">
-        <v>0.9987999999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="G130">
-        <v>0.7273219753588771</v>
+        <v>0.9299077697948877</v>
       </c>
       <c r="H130">
-        <v>0.9987999999999999</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" s="1">
-        <v>46184</v>
+        <v>46176</v>
       </c>
       <c r="B131" t="s">
         <v>13</v>
       </c>
       <c r="C131">
-        <v>61.41553176023326</v>
+        <v>63.0681947750049</v>
       </c>
       <c r="D131">
-        <v>23.99650204363438</v>
+        <v>25.58770976382014</v>
       </c>
       <c r="E131">
-        <v>0.9986000000000002</v>
+        <v>0.9988000000000002</v>
       </c>
       <c r="F131">
-        <v>0.9986000000000002</v>
+        <v>0.9988000000000002</v>
       </c>
       <c r="G131">
-        <v>0.8722037562794076</v>
+        <v>0.9639112148600193</v>
       </c>
       <c r="H131">
-        <v>0.9986000000000002</v>
+        <v>0.9988000000000002</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="1">
-        <v>46153</v>
+        <v>46177</v>
       </c>
       <c r="B132" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C132">
-        <v>35.78646526282436</v>
+        <v>61.53154955456358</v>
       </c>
       <c r="D132">
-        <v>18.96635091925032</v>
+        <v>24.75810538712983</v>
       </c>
       <c r="E132">
-        <v>0.9996491399999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F132">
-        <v>0.9996491399999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G132">
-        <v>0.2240600969213613</v>
+        <v>0.9225710173552821</v>
       </c>
       <c r="H132">
-        <v>0.9985614899999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="1">
-        <v>46154</v>
+        <v>46178</v>
       </c>
       <c r="B133" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C133">
-        <v>35.71584102184062</v>
+        <v>55.42493637343647</v>
       </c>
       <c r="D133">
-        <v>18.62432950231353</v>
+        <v>22.47054621698377</v>
       </c>
       <c r="E133">
-        <v>0.99965481</v>
+        <v>0.9987</v>
       </c>
       <c r="F133">
-        <v>0.99965481</v>
+        <v>0.9987</v>
       </c>
       <c r="G133">
-        <v>0.2104844827747143</v>
+        <v>0.7217717116249776</v>
       </c>
       <c r="H133">
-        <v>0.9985622199999999</v>
+        <v>0.9987</v>
       </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="1">
-        <v>46155</v>
+        <v>46182</v>
       </c>
       <c r="B134" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C134">
-        <v>35.95182028203252</v>
+        <v>57.84835101034041</v>
       </c>
       <c r="D134">
-        <v>18.95670796791552</v>
+        <v>23.24662656171655</v>
       </c>
       <c r="E134">
-        <v>0.9996515200000001</v>
+        <v>0.999</v>
       </c>
       <c r="F134">
-        <v>0.9996515200000001</v>
+        <v>0.999</v>
       </c>
       <c r="G134">
-        <v>0.2259035693959275</v>
+        <v>0.7931280733869936</v>
       </c>
       <c r="H134">
-        <v>0.99855193</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="1">
-        <v>46156</v>
+        <v>46183</v>
       </c>
       <c r="B135" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C135">
-        <v>36.14451597805883</v>
+        <v>55.28729760663236</v>
       </c>
       <c r="D135">
-        <v>18.86297660538653</v>
+        <v>22.10409273362112</v>
       </c>
       <c r="E135">
-        <v>0.9996563399999999</v>
+        <v>0.9987999999999999</v>
       </c>
       <c r="F135">
-        <v>0.9996563399999999</v>
+        <v>0.9987999999999999</v>
       </c>
       <c r="G135">
-        <v>0.2362110061840785</v>
+        <v>0.7273219753588771</v>
       </c>
       <c r="H135">
-        <v>0.99857265</v>
+        <v>0.9987999999999999</v>
       </c>
     </row>
     <row r="136" spans="1:8">
       <c r="A136" s="1">
-        <v>46157</v>
+        <v>46184</v>
       </c>
       <c r="B136" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C136">
-        <v>35.32805803135546</v>
+        <v>61.41553176023326</v>
       </c>
       <c r="D136">
-        <v>18.35643242381478</v>
+        <v>23.99650204363438</v>
       </c>
       <c r="E136">
-        <v>0.9997415800000001</v>
+        <v>0.9986000000000002</v>
       </c>
       <c r="F136">
-        <v>0.9997415800000001</v>
+        <v>0.9986000000000002</v>
       </c>
       <c r="G136">
-        <v>0.2023559161375383</v>
+        <v>0.8722037562794076</v>
       </c>
       <c r="H136">
-        <v>0.9986639900000002</v>
+        <v>0.9986000000000002</v>
       </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="1">
-        <v>46160</v>
+        <v>46185</v>
       </c>
       <c r="B137" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C137">
-        <v>34.83995455757461</v>
+        <v>60.84374742307179</v>
       </c>
       <c r="D137">
-        <v>18.02301281718857</v>
+        <v>24.14439702225977</v>
       </c>
       <c r="E137">
-        <v>0.9996851299999999</v>
+        <v>0.9988000000000001</v>
       </c>
       <c r="F137">
-        <v>0.9996851299999999</v>
+        <v>0.9988000000000001</v>
       </c>
       <c r="G137">
-        <v>0.1850932291737926</v>
+        <v>0.9019329453457305</v>
       </c>
       <c r="H137">
-        <v>0.99857724</v>
+        <v>0.9988000000000001</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B138" t="s">
         <v>14</v>
       </c>
       <c r="C138">
-        <v>34.45479308705605</v>
+        <v>35.78646526282436</v>
       </c>
       <c r="D138">
-        <v>18.09576834566068</v>
+        <v>18.96635091925032</v>
       </c>
       <c r="E138">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="F138">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="G138">
-        <v>0.1784731209386736</v>
+        <v>0.2240600969213613</v>
       </c>
       <c r="H138">
-        <v>0.9985337599999999</v>
+        <v>0.9985614899999999</v>
       </c>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B139" t="s">
         <v>14</v>
       </c>
       <c r="C139">
-        <v>34.96336277390787</v>
+        <v>35.71584102184062</v>
       </c>
       <c r="D139">
-        <v>18.34938420029253</v>
+        <v>18.62432950231353</v>
       </c>
       <c r="E139">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="F139">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="G139">
-        <v>0.2009313391215752</v>
+        <v>0.2104844827747143</v>
       </c>
       <c r="H139">
-        <v>0.99848777</v>
+        <v>0.9985622199999999</v>
       </c>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B140" t="s">
         <v>14</v>
       </c>
       <c r="C140">
-        <v>34.44616924817128</v>
+        <v>35.95182028203252</v>
       </c>
       <c r="D140">
-        <v>18.60085625074367</v>
+        <v>18.95670796791552</v>
       </c>
       <c r="E140">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="F140">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="G140">
-        <v>0.2124957180214682</v>
+        <v>0.2259035693959275</v>
       </c>
       <c r="H140">
-        <v>0.9985085200000001</v>
+        <v>0.99855193</v>
       </c>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="1">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="B141" t="s">
         <v>14</v>
       </c>
       <c r="C141">
-        <v>34.62137220937314</v>
+        <v>36.14451597805883</v>
       </c>
       <c r="D141">
-        <v>18.28780484745949</v>
+        <v>18.86297660538653</v>
       </c>
       <c r="E141">
-        <v>0.9996106299999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="F141">
-        <v>0.9996106299999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="G141">
-        <v>0.2145907067863493</v>
+        <v>0.2362110061840785</v>
       </c>
       <c r="H141">
-        <v>0.9932939299999999</v>
+        <v>0.99857265</v>
       </c>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="1">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="B142" t="s">
         <v>14</v>
       </c>
       <c r="C142">
-        <v>34.6540695486741</v>
+        <v>35.32805803135546</v>
       </c>
       <c r="D142">
-        <v>18.36409048915342</v>
+        <v>18.35643242381478</v>
       </c>
       <c r="E142">
-        <v>0.9995448900000001</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="F142">
-        <v>0.9995448900000001</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="G142">
-        <v>0.2145907067863493</v>
+        <v>0.2023559161375383</v>
       </c>
       <c r="H142">
-        <v>0.9984302600000001</v>
+        <v>0.9986639900000002</v>
       </c>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="1">
-        <v>46168</v>
+        <v>46160</v>
       </c>
       <c r="B143" t="s">
         <v>14</v>
       </c>
       <c r="C143">
-        <v>35.4820130509417</v>
+        <v>34.83995455757461</v>
       </c>
       <c r="D143">
-        <v>19.20292041814603</v>
+        <v>18.02301281718857</v>
       </c>
       <c r="E143">
-        <v>0.9995448900000001</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="F143">
-        <v>0.9995448900000001</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="G143">
-        <v>0.2553172934903569</v>
+        <v>0.1850932291737926</v>
       </c>
       <c r="H143">
-        <v>0.9984302600000001</v>
+        <v>0.99857724</v>
       </c>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="1">
-        <v>46169</v>
+        <v>46161</v>
       </c>
       <c r="B144" t="s">
         <v>14</v>
       </c>
       <c r="C144">
-        <v>35.71913468603401</v>
+        <v>34.45479308705605</v>
       </c>
       <c r="D144">
-        <v>18.96318693998171</v>
+        <v>18.09576834566068</v>
       </c>
       <c r="E144">
-        <v>0.99955466</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="F144">
-        <v>0.99955466</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="G144">
-        <v>0.2536413280520453</v>
+        <v>0.1784731209386736</v>
       </c>
       <c r="H144">
-        <v>0.9984700500000001</v>
+        <v>0.9985337599999999</v>
       </c>
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="1">
-        <v>46170</v>
+        <v>46162</v>
       </c>
       <c r="B145" t="s">
         <v>14</v>
       </c>
       <c r="C145">
-        <v>35.76226417354731</v>
+        <v>34.96336277390787</v>
       </c>
       <c r="D145">
-        <v>18.89050847207122</v>
+        <v>18.34938420029253</v>
       </c>
       <c r="E145">
-        <v>0.9995525399999999</v>
+        <v>0.99963413</v>
       </c>
       <c r="F145">
-        <v>0.9995525399999999</v>
+        <v>0.99963413</v>
       </c>
       <c r="G145">
-        <v>0.2580826940041561</v>
+        <v>0.2009313391215752</v>
       </c>
       <c r="H145">
-        <v>0.99847732</v>
+        <v>0.99848777</v>
       </c>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="1">
-        <v>46171</v>
+        <v>46163</v>
       </c>
       <c r="B146" t="s">
         <v>14</v>
       </c>
       <c r="C146">
-        <v>35.84309020154227</v>
+        <v>34.44616924817128</v>
       </c>
       <c r="D146">
-        <v>19.06511612333149</v>
+        <v>18.60085625074367</v>
       </c>
       <c r="E146">
-        <v>0.9995533299999999</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="F146">
-        <v>0.9995533299999999</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="G146">
-        <v>0.2619374017254759</v>
+        <v>0.2124957180214682</v>
       </c>
       <c r="H146">
-        <v>0.99849382</v>
+        <v>0.9985085200000001</v>
       </c>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="1">
-        <v>46174</v>
+        <v>46164</v>
       </c>
       <c r="B147" t="s">
         <v>14</v>
       </c>
       <c r="C147">
-        <v>36.27022125574057</v>
+        <v>34.62137220937314</v>
       </c>
       <c r="D147">
-        <v>19.32711369104533</v>
+        <v>18.28780484745949</v>
       </c>
       <c r="E147">
-        <v>0.9995550400000001</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="F147">
-        <v>0.9995550400000001</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="G147">
-        <v>0.2764348160433892</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H147">
-        <v>0.9985177199999999</v>
+        <v>0.9932939299999999</v>
       </c>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="1">
-        <v>46175</v>
+        <v>46167</v>
       </c>
       <c r="B148" t="s">
         <v>14</v>
       </c>
       <c r="C148">
-        <v>36.57133692946976</v>
+        <v>34.6540695486741</v>
       </c>
       <c r="D148">
-        <v>19.33857330565742</v>
+        <v>18.36409048915342</v>
       </c>
       <c r="E148">
-        <v>0.9994989200000002</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="F148">
-        <v>0.9994989200000002</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="G148">
-        <v>0.2931947261624381</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H148">
-        <v>0.9984577800000001</v>
+        <v>0.9984302600000001</v>
       </c>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="1">
-        <v>46176</v>
+        <v>46168</v>
       </c>
       <c r="B149" t="s">
         <v>14</v>
       </c>
       <c r="C149">
-        <v>36.8289666508657</v>
+        <v>35.4820130509417</v>
       </c>
       <c r="D149">
-        <v>19.43137154505686</v>
+        <v>19.20292041814603</v>
       </c>
       <c r="E149">
-        <v>0.9994838199999998</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="F149">
-        <v>0.9994838199999998</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="G149">
-        <v>0.2996471994933361</v>
+        <v>0.2553172934903569</v>
       </c>
       <c r="H149">
-        <v>0.9984549499999998</v>
+        <v>0.9984302600000001</v>
       </c>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" s="1">
-        <v>46177</v>
+        <v>46169</v>
       </c>
       <c r="B150" t="s">
         <v>14</v>
       </c>
       <c r="C150">
-        <v>36.76760036565858</v>
+        <v>35.71913468603401</v>
       </c>
       <c r="D150">
-        <v>18.98774474764188</v>
+        <v>18.96318693998171</v>
       </c>
       <c r="E150">
-        <v>0.99948384</v>
+        <v>0.99955466</v>
       </c>
       <c r="F150">
-        <v>0.99948384</v>
+        <v>0.99955466</v>
       </c>
       <c r="G150">
-        <v>0.2807085470912787</v>
+        <v>0.2536413280520453</v>
       </c>
       <c r="H150">
-        <v>0.9984696899999999</v>
+        <v>0.9984700500000001</v>
       </c>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="1">
-        <v>46178</v>
+        <v>46170</v>
       </c>
       <c r="B151" t="s">
         <v>14</v>
       </c>
       <c r="C151">
-        <v>34.71533981972338</v>
+        <v>35.76226417354731</v>
       </c>
       <c r="D151">
-        <v>17.87291658642534</v>
+        <v>18.89050847207122</v>
       </c>
       <c r="E151">
-        <v>0.9994584900000001</v>
+        <v>0.9995525399999999</v>
       </c>
       <c r="F151">
-        <v>0.9994584900000001</v>
+        <v>0.9995525399999999</v>
       </c>
       <c r="G151">
-        <v>0.2090599057587512</v>
+        <v>0.2580826940041561</v>
       </c>
       <c r="H151">
-        <v>0.9984184600000001</v>
+        <v>0.99847732</v>
       </c>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="1">
-        <v>46182</v>
+        <v>46171</v>
       </c>
       <c r="B152" t="s">
         <v>14</v>
       </c>
       <c r="C152">
-        <v>35.03764279648938</v>
+        <v>35.84309020154227</v>
       </c>
       <c r="D152">
-        <v>18.26945792236365</v>
+        <v>19.06511612333149</v>
       </c>
       <c r="E152">
-        <v>0.9994212399999999</v>
+        <v>0.9995533299999999</v>
       </c>
       <c r="F152">
-        <v>0.9994212399999999</v>
+        <v>0.9995533299999999</v>
       </c>
       <c r="G152">
-        <v>0.2361271247979846</v>
+        <v>0.2619374017254759</v>
       </c>
       <c r="H152">
-        <v>0.99833116</v>
+        <v>0.99849382</v>
       </c>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" s="1">
-        <v>46183</v>
+        <v>46174</v>
       </c>
       <c r="B153" t="s">
         <v>14</v>
       </c>
       <c r="C153">
-        <v>34.21862503455022</v>
+        <v>36.27022125574057</v>
       </c>
       <c r="D153">
-        <v>17.67576313213109</v>
+        <v>19.32711369104533</v>
       </c>
       <c r="E153">
-        <v>0.9991916599999998</v>
+        <v>0.9995550400000001</v>
       </c>
       <c r="F153">
-        <v>0.9991916599999998</v>
+        <v>0.9995550400000001</v>
       </c>
       <c r="G153">
-        <v>0.2040318815758499</v>
+        <v>0.2764348160433892</v>
       </c>
       <c r="H153">
-        <v>0.99808951</v>
+        <v>0.9985177199999999</v>
       </c>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" s="1">
-        <v>46184</v>
+        <v>46175</v>
       </c>
       <c r="B154" t="s">
         <v>14</v>
       </c>
       <c r="C154">
-        <v>35.57723814348832</v>
+        <v>36.57133692946976</v>
       </c>
       <c r="D154">
-        <v>18.6194204925492</v>
+        <v>19.33857330565742</v>
       </c>
       <c r="E154">
-        <v>0.9989294799999999</v>
+        <v>0.9994989200000002</v>
       </c>
       <c r="F154">
-        <v>0.9989294799999999</v>
+        <v>0.9994989200000002</v>
       </c>
       <c r="G154">
-        <v>0.2618536482073486</v>
+        <v>0.2931947261624381</v>
       </c>
       <c r="H154">
-        <v>0.9977895699999999</v>
+        <v>0.9984577800000001</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" s="1">
-        <v>46153</v>
+        <v>46176</v>
       </c>
       <c r="B155" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C155">
-        <v>28.12253390077671</v>
+        <v>36.8289666508657</v>
       </c>
       <c r="D155">
-        <v>23.58699683751922</v>
+        <v>19.43137154505686</v>
       </c>
       <c r="E155">
-        <v>0.9997295369999999</v>
+        <v>0.9994838199999998</v>
       </c>
       <c r="F155">
-        <v>0.9997295369999999</v>
+        <v>0.9994838199999998</v>
       </c>
       <c r="G155">
-        <v>0.03368732240295347</v>
+        <v>0.2996471994933361</v>
       </c>
       <c r="H155">
-        <v>0.9997295369999999</v>
+        <v>0.9984549499999998</v>
       </c>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" s="1">
-        <v>46154</v>
+        <v>46177</v>
       </c>
       <c r="B156" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C156">
-        <v>28.17715727830483</v>
+        <v>36.76760036565858</v>
       </c>
       <c r="D156">
-        <v>23.63894513078866</v>
+        <v>18.98774474764188</v>
       </c>
       <c r="E156">
-        <v>1.000319473</v>
+        <v>0.99948384</v>
       </c>
       <c r="F156">
-        <v>1.000319473</v>
+        <v>0.99948384</v>
       </c>
       <c r="G156">
-        <v>0.03515547182056333</v>
+        <v>0.2807085470912787</v>
       </c>
       <c r="H156">
-        <v>1.000319473</v>
+        <v>0.9984696899999999</v>
       </c>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" s="1">
-        <v>46155</v>
+        <v>46178</v>
       </c>
       <c r="B157" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C157">
-        <v>28.59002627414054</v>
+        <v>34.71533981972338</v>
       </c>
       <c r="D157">
-        <v>23.96230704059692</v>
+        <v>17.87291658642534</v>
       </c>
       <c r="E157">
-        <v>0.9999999989999999</v>
+        <v>0.9994584900000001</v>
       </c>
       <c r="F157">
-        <v>0.9999999989999999</v>
+        <v>0.9994584900000001</v>
       </c>
       <c r="G157">
-        <v>0.05179637495949674</v>
+        <v>0.2090599057587512</v>
       </c>
       <c r="H157">
-        <v>0.9999999989999999</v>
+        <v>0.9984184600000001</v>
       </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="1">
-        <v>46156</v>
+        <v>46182</v>
       </c>
       <c r="B158" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C158">
-        <v>28.56217859389523</v>
+        <v>35.03764279648938</v>
       </c>
       <c r="D158">
-        <v>23.9411987302529</v>
+        <v>18.26945792236365</v>
       </c>
       <c r="E158">
-        <v>1</v>
+        <v>0.9994212399999999</v>
       </c>
       <c r="F158">
-        <v>1</v>
+        <v>0.9994212399999999</v>
       </c>
       <c r="G158">
-        <v>0.04837024516756849</v>
+        <v>0.2361271247979846</v>
       </c>
       <c r="H158">
-        <v>1</v>
+        <v>0.99833116</v>
       </c>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" s="1">
-        <v>46157</v>
+        <v>46183</v>
       </c>
       <c r="B159" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C159">
-        <v>28.57618675936338</v>
+        <v>34.21862503455022</v>
       </c>
       <c r="D159">
-        <v>23.9576220541054</v>
+        <v>17.67576313213109</v>
       </c>
       <c r="E159">
-        <v>0.999503249</v>
+        <v>0.9991916599999998</v>
       </c>
       <c r="F159">
-        <v>0.999503249</v>
+        <v>0.9991916599999998</v>
       </c>
       <c r="G159">
-        <v>0.04983868243960732</v>
+        <v>0.2040318815758499</v>
       </c>
       <c r="H159">
-        <v>0.999503249</v>
+        <v>0.99808951</v>
       </c>
     </row>
     <row r="160" spans="1:8">
       <c r="A160" s="1">
-        <v>46160</v>
+        <v>46184</v>
       </c>
       <c r="B160" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C160">
-        <v>28.68951918518517</v>
+        <v>35.57723814348832</v>
       </c>
       <c r="D160">
-        <v>24.06134728453882</v>
+        <v>18.6194204925492</v>
       </c>
       <c r="E160">
-        <v>0.999503249</v>
+        <v>0.9989294799999999</v>
       </c>
       <c r="F160">
-        <v>0.999503249</v>
+        <v>0.9989294799999999</v>
       </c>
       <c r="G160">
-        <v>0.04983868243960732</v>
+        <v>0.2618536482073486</v>
       </c>
       <c r="H160">
-        <v>0.999503249</v>
+        <v>0.9977895699999999</v>
       </c>
     </row>
     <row r="161" spans="1:8">
       <c r="A161" s="1">
-        <v>46161</v>
+        <v>46185</v>
       </c>
       <c r="B161" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C161">
-        <v>28.31167386654059</v>
+        <v>36.1035128450924</v>
       </c>
       <c r="D161">
-        <v>23.75157719455474</v>
+        <v>18.65667517843299</v>
       </c>
       <c r="E161">
-        <v>1.000177331</v>
+        <v>0.9988909800000001</v>
       </c>
       <c r="F161">
-        <v>1.000177331</v>
+        <v>0.9988909800000001</v>
       </c>
       <c r="G161">
-        <v>0.04053938625111919</v>
+        <v>0.2777755116732585</v>
       </c>
       <c r="H161">
-        <v>1.000177331</v>
+        <v>0.9978056500000002</v>
       </c>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" s="1">
-        <v>46162</v>
+        <v>46153</v>
       </c>
       <c r="B162" t="s">
         <v>15</v>
       </c>
       <c r="C162">
-        <v>28.57911382310097</v>
+        <v>28.12253390077671</v>
       </c>
       <c r="D162">
-        <v>23.89431741541233</v>
+        <v>23.58699683751922</v>
       </c>
       <c r="E162">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="F162">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="G162">
-        <v>0.04690190590044785</v>
+        <v>0.03368732240295347</v>
       </c>
       <c r="H162">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" s="1">
-        <v>46163</v>
+        <v>46154</v>
       </c>
       <c r="B163" t="s">
         <v>15</v>
       </c>
       <c r="C163">
-        <v>28.55785065378643</v>
+        <v>28.17715727830483</v>
       </c>
       <c r="D163">
-        <v>24.04274714970193</v>
+        <v>23.63894513078866</v>
       </c>
       <c r="E163">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="F163">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="G163">
-        <v>0.05228572319419666</v>
+        <v>0.03515547182056333</v>
       </c>
       <c r="H163">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" s="1">
-        <v>46164</v>
+        <v>46155</v>
       </c>
       <c r="B164" t="s">
         <v>15</v>
       </c>
       <c r="C164">
-        <v>28.50194638163107</v>
+        <v>28.59002627414054</v>
       </c>
       <c r="D164">
-        <v>23.99272397156045</v>
+        <v>23.96230704059692</v>
       </c>
       <c r="E164">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F164">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G164">
-        <v>0.04934923597154284</v>
+        <v>0.05179637495949674</v>
       </c>
       <c r="H164">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="165" spans="1:8">
       <c r="A165" s="1">
-        <v>46167</v>
+        <v>46156</v>
       </c>
       <c r="B165" t="s">
         <v>15</v>
       </c>
       <c r="C165">
-        <v>28.55106858744498</v>
+        <v>28.56217859389523</v>
       </c>
       <c r="D165">
-        <v>23.9768329565351</v>
+        <v>23.9411987302529</v>
       </c>
       <c r="E165">
         <v>1</v>
@@ -4687,7 +4687,7 @@
         <v>1</v>
       </c>
       <c r="G165">
-        <v>0.05571185335164408</v>
+        <v>0.04837024516756849</v>
       </c>
       <c r="H165">
         <v>1</v>
@@ -4695,912 +4695,1146 @@
     </row>
     <row r="166" spans="1:8">
       <c r="A166" s="1">
-        <v>46168</v>
+        <v>46157</v>
       </c>
       <c r="B166" t="s">
         <v>15</v>
       </c>
       <c r="C166">
-        <v>28.54681541456266</v>
+        <v>28.57618675936338</v>
       </c>
       <c r="D166">
-        <v>23.97386168967948</v>
+        <v>23.9576220541054</v>
       </c>
       <c r="E166">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="F166">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="G166">
-        <v>0.04837034303541388</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H166">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" s="1">
-        <v>46169</v>
+        <v>46160</v>
       </c>
       <c r="B167" t="s">
         <v>15</v>
       </c>
       <c r="C167">
-        <v>28.83672936868491</v>
+        <v>28.68951918518517</v>
       </c>
       <c r="D167">
-        <v>24.203511281145</v>
+        <v>24.06134728453882</v>
       </c>
       <c r="E167">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="F167">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="G167">
-        <v>0.05962723282507953</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H167">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="168" spans="1:8">
       <c r="A168" s="1">
-        <v>46170</v>
+        <v>46161</v>
       </c>
       <c r="B168" t="s">
         <v>15</v>
       </c>
       <c r="C168">
-        <v>28.88109630394224</v>
+        <v>28.31167386654059</v>
       </c>
       <c r="D168">
-        <v>24.34085451035401</v>
+        <v>23.75157719455474</v>
       </c>
       <c r="E168">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
       <c r="F168">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
       <c r="G168">
-        <v>0.06647938938594877</v>
+        <v>0.04053938625111919</v>
       </c>
       <c r="H168">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" s="1">
-        <v>46171</v>
+        <v>46162</v>
       </c>
       <c r="B169" t="s">
         <v>15</v>
       </c>
       <c r="C169">
-        <v>28.92588622185229</v>
+        <v>28.57911382310097</v>
       </c>
       <c r="D169">
-        <v>24.37463012178961</v>
+        <v>23.89431741541233</v>
       </c>
       <c r="E169">
-        <v>0.9999999989999999</v>
+        <v>0.999503734</v>
       </c>
       <c r="F169">
-        <v>0.9999999989999999</v>
+        <v>0.999503734</v>
       </c>
       <c r="G169">
-        <v>0.0669687424559624</v>
+        <v>0.04690190590044785</v>
       </c>
       <c r="H169">
-        <v>0.9999999989999999</v>
+        <v>0.999503734</v>
       </c>
     </row>
     <row r="170" spans="1:8">
       <c r="A170" s="1">
-        <v>46174</v>
+        <v>46163</v>
       </c>
       <c r="B170" t="s">
         <v>15</v>
       </c>
       <c r="C170">
-        <v>28.479823472488</v>
+        <v>28.55785065378643</v>
       </c>
       <c r="D170">
-        <v>23.940843604634</v>
+        <v>24.04274714970193</v>
       </c>
       <c r="E170">
-        <v>0.9999999999999999</v>
+        <v>1.000229282</v>
       </c>
       <c r="F170">
-        <v>0.9999999999999999</v>
+        <v>1.000229282</v>
       </c>
       <c r="G170">
-        <v>0.05385076946675693</v>
+        <v>0.05228572319419666</v>
       </c>
       <c r="H170">
-        <v>0.9999999999999999</v>
+        <v>1.000229282</v>
       </c>
     </row>
     <row r="171" spans="1:8">
       <c r="A171" s="1">
-        <v>46175</v>
+        <v>46164</v>
       </c>
       <c r="B171" t="s">
         <v>15</v>
       </c>
       <c r="C171">
-        <v>28.11501250979268</v>
+        <v>28.50194638163107</v>
       </c>
       <c r="D171">
-        <v>23.53470929078268</v>
+        <v>23.99272397156045</v>
       </c>
       <c r="E171">
-        <v>0.9999999989999999</v>
+        <v>1</v>
       </c>
       <c r="F171">
-        <v>0.9999999989999999</v>
+        <v>1</v>
       </c>
       <c r="G171">
-        <v>0.03476107722835287</v>
+        <v>0.04934923597154284</v>
       </c>
       <c r="H171">
-        <v>0.9999999989999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172" spans="1:8">
       <c r="A172" s="1">
-        <v>46176</v>
+        <v>46167</v>
       </c>
       <c r="B172" t="s">
         <v>15</v>
       </c>
       <c r="C172">
-        <v>28.0115884668485</v>
+        <v>28.55106858744498</v>
       </c>
       <c r="D172">
-        <v>23.38620815625822</v>
+        <v>23.9768329565351</v>
       </c>
       <c r="E172">
-        <v>0.9993115890000001</v>
+        <v>1</v>
       </c>
       <c r="F172">
-        <v>0.9993115890000001</v>
+        <v>1</v>
       </c>
       <c r="G172">
-        <v>0.02105569185214828</v>
+        <v>0.05571185335164408</v>
       </c>
       <c r="H172">
-        <v>0.9993115890000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173" spans="1:8">
       <c r="A173" s="1">
-        <v>46177</v>
+        <v>46168</v>
       </c>
       <c r="B173" t="s">
         <v>15</v>
       </c>
       <c r="C173">
-        <v>28.38208530418455</v>
+        <v>28.54681541456266</v>
       </c>
       <c r="D173">
-        <v>23.57230416238753</v>
+        <v>23.97386168967948</v>
       </c>
       <c r="E173">
-        <v>1.000774061</v>
+        <v>1</v>
       </c>
       <c r="F173">
-        <v>1.000774061</v>
+        <v>1</v>
       </c>
       <c r="G173">
-        <v>0.03133473088430172</v>
+        <v>0.04837034303541388</v>
       </c>
       <c r="H173">
-        <v>1.000774061</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174" spans="1:8">
       <c r="A174" s="1">
-        <v>46178</v>
+        <v>46169</v>
       </c>
       <c r="B174" t="s">
         <v>15</v>
       </c>
       <c r="C174">
-        <v>27.67379569436247</v>
+        <v>28.83672936868491</v>
       </c>
       <c r="D174">
-        <v>23.02577481291606</v>
+        <v>24.203511281145</v>
       </c>
       <c r="E174">
-        <v>1.000106056</v>
+        <v>1</v>
       </c>
       <c r="F174">
-        <v>1.000106056</v>
+        <v>1</v>
       </c>
       <c r="G174">
-        <v>0.01248973263108488</v>
+        <v>0.05962723282507953</v>
       </c>
       <c r="H174">
-        <v>1.000106056</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175" spans="1:8">
       <c r="A175" s="1">
-        <v>46182</v>
+        <v>46170</v>
       </c>
       <c r="B175" t="s">
         <v>15</v>
       </c>
       <c r="C175">
-        <v>27.45237632057606</v>
+        <v>28.88109630394224</v>
       </c>
       <c r="D175">
-        <v>22.58943922039682</v>
+        <v>24.34085451035401</v>
       </c>
       <c r="E175">
-        <v>0.9999738310000001</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F175">
-        <v>0.9999738310000001</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G175">
-        <v>-0.01076068709534461</v>
+        <v>0.06647938938594877</v>
       </c>
       <c r="H175">
-        <v>0.9999738310000001</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="176" spans="1:8">
       <c r="A176" s="1">
-        <v>46183</v>
+        <v>46171</v>
       </c>
       <c r="B176" t="s">
         <v>15</v>
       </c>
       <c r="C176">
-        <v>26.87898580194432</v>
+        <v>28.92588622185229</v>
       </c>
       <c r="D176">
-        <v>22.24994492425726</v>
+        <v>24.37463012178961</v>
       </c>
       <c r="E176">
-        <v>1.000000001</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F176">
-        <v>1.000000001</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G176">
-        <v>-0.02299778174457945</v>
+        <v>0.0669687424559624</v>
       </c>
       <c r="H176">
-        <v>1.000000001</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177" s="1">
-        <v>46184</v>
+        <v>46174</v>
       </c>
       <c r="B177" t="s">
         <v>15</v>
       </c>
       <c r="C177">
-        <v>26.963842509069</v>
+        <v>28.479823472488</v>
       </c>
       <c r="D177">
-        <v>22.26031265264148</v>
+        <v>23.940843604634</v>
       </c>
       <c r="E177">
-        <v>0.9996853900000001</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F177">
-        <v>0.9996853900000001</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G177">
-        <v>-0.02299759931689671</v>
+        <v>0.05385076946675693</v>
       </c>
       <c r="H177">
-        <v>0.9996853900000001</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="178" spans="1:8">
       <c r="A178" s="1">
-        <v>46153</v>
+        <v>46175</v>
       </c>
       <c r="B178" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C178">
-        <v>40.68830633303975</v>
+        <v>28.11501250979268</v>
       </c>
       <c r="D178">
-        <v>21.50431773660198</v>
+        <v>23.53470929078268</v>
       </c>
       <c r="E178">
-        <v>0.99909852</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F178">
-        <v>0.99909852</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G178">
-        <v>0.2342423866086769</v>
+        <v>0.03476107722835287</v>
       </c>
       <c r="H178">
-        <v>0.9974930900000001</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="179" spans="1:8">
       <c r="A179" s="1">
-        <v>46154</v>
+        <v>46176</v>
       </c>
       <c r="B179" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C179">
-        <v>40.32854894972581</v>
+        <v>28.0115884668485</v>
       </c>
       <c r="D179">
-        <v>21.09133998298594</v>
+        <v>23.38620815625822</v>
       </c>
       <c r="E179">
-        <v>0.9990972199999999</v>
+        <v>0.9993115890000001</v>
       </c>
       <c r="F179">
-        <v>0.9990972199999999</v>
+        <v>0.9993115890000001</v>
       </c>
       <c r="G179">
-        <v>0.2156468205051487</v>
+        <v>0.02105569185214828</v>
       </c>
       <c r="H179">
-        <v>0.99752223</v>
+        <v>0.9993115890000001</v>
       </c>
     </row>
     <row r="180" spans="1:8">
       <c r="A180" s="1">
-        <v>46155</v>
+        <v>46177</v>
       </c>
       <c r="B180" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C180">
-        <v>40.47987921095815</v>
+        <v>28.38208530418455</v>
       </c>
       <c r="D180">
-        <v>21.35995364434454</v>
+        <v>23.57230416238753</v>
       </c>
       <c r="E180">
-        <v>0.9991780100000001</v>
+        <v>1.000774061</v>
       </c>
       <c r="F180">
-        <v>0.9991780100000001</v>
+        <v>1.000774061</v>
       </c>
       <c r="G180">
-        <v>0.2270956128473374</v>
+        <v>0.03133473088430172</v>
       </c>
       <c r="H180">
-        <v>0.9975825700000001</v>
+        <v>1.000774061</v>
       </c>
     </row>
     <row r="181" spans="1:8">
       <c r="A181" s="1">
-        <v>46156</v>
+        <v>46178</v>
       </c>
       <c r="B181" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C181">
-        <v>41.20436574895244</v>
+        <v>27.67379569436247</v>
       </c>
       <c r="D181">
-        <v>21.48149674387778</v>
+        <v>23.02577481291606</v>
       </c>
       <c r="E181">
-        <v>0.9991793299999999</v>
+        <v>1.000106056</v>
       </c>
       <c r="F181">
-        <v>0.9991793299999999</v>
+        <v>1.000106056</v>
       </c>
       <c r="G181">
-        <v>0.2454829228401052</v>
+        <v>0.01248973263108488</v>
       </c>
       <c r="H181">
-        <v>0.99754722</v>
+        <v>1.000106056</v>
       </c>
     </row>
     <row r="182" spans="1:8">
       <c r="A182" s="1">
-        <v>46157</v>
+        <v>46182</v>
       </c>
       <c r="B182" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C182">
-        <v>40.80613062958688</v>
+        <v>27.45237632057606</v>
       </c>
       <c r="D182">
-        <v>21.08912555803936</v>
+        <v>22.58943922039682</v>
       </c>
       <c r="E182">
-        <v>0.9991790600000001</v>
+        <v>0.9999738310000001</v>
       </c>
       <c r="F182">
-        <v>0.9991790600000001</v>
+        <v>0.9999738310000001</v>
       </c>
       <c r="G182">
-        <v>0.2230017445022556</v>
+        <v>-0.01076068709534461</v>
       </c>
       <c r="H182">
-        <v>0.9975824700000002</v>
+        <v>0.9999738310000001</v>
       </c>
     </row>
     <row r="183" spans="1:8">
       <c r="A183" s="1">
-        <v>46160</v>
+        <v>46183</v>
       </c>
       <c r="B183" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C183">
-        <v>40.11672876026724</v>
+        <v>26.87898580194432</v>
       </c>
       <c r="D183">
-        <v>20.79541439916316</v>
+        <v>22.24994492425726</v>
       </c>
       <c r="E183">
-        <v>0.999152</v>
+        <v>1.000000001</v>
       </c>
       <c r="F183">
-        <v>0.999152</v>
+        <v>1.000000001</v>
       </c>
       <c r="G183">
-        <v>0.2098184021536666</v>
+        <v>-0.02299778174457945</v>
       </c>
       <c r="H183">
-        <v>0.9975007899999999</v>
+        <v>1.000000001</v>
       </c>
     </row>
     <row r="184" spans="1:8">
       <c r="A184" s="1">
-        <v>46161</v>
+        <v>46184</v>
       </c>
       <c r="B184" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C184">
-        <v>39.69086941528401</v>
+        <v>26.963842509069</v>
       </c>
       <c r="D184">
-        <v>20.74924328599426</v>
+        <v>22.26031265264148</v>
       </c>
       <c r="E184">
-        <v>0.99914989</v>
+        <v>0.9996853900000001</v>
       </c>
       <c r="F184">
-        <v>0.99914989</v>
+        <v>0.9996853900000001</v>
       </c>
       <c r="G184">
-        <v>0.2020471776850241</v>
+        <v>-0.02299759931689671</v>
       </c>
       <c r="H184">
-        <v>0.9974417</v>
+        <v>0.9996853900000001</v>
       </c>
     </row>
     <row r="185" spans="1:8">
       <c r="A185" s="1">
-        <v>46162</v>
+        <v>46185</v>
       </c>
       <c r="B185" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C185">
-        <v>40.37836787855562</v>
+        <v>26.83840329983722</v>
       </c>
       <c r="D185">
-        <v>21.11271132314188</v>
+        <v>22.18026196156466</v>
       </c>
       <c r="E185">
-        <v>0.99915058</v>
+        <v>1.000030945</v>
       </c>
       <c r="F185">
-        <v>0.99915058</v>
+        <v>1.000030945</v>
       </c>
       <c r="G185">
-        <v>0.2291077670847563</v>
+        <v>-0.02985038257907502</v>
       </c>
       <c r="H185">
-        <v>0.9974415600000001</v>
+        <v>1.000030945</v>
       </c>
     </row>
     <row r="186" spans="1:8">
       <c r="A186" s="1">
-        <v>46163</v>
+        <v>46153</v>
       </c>
       <c r="B186" t="s">
         <v>16</v>
       </c>
       <c r="C186">
-        <v>38.9123066967842</v>
+        <v>40.68830633303975</v>
       </c>
       <c r="D186">
-        <v>21.28910644207464</v>
+        <v>21.50431773660198</v>
       </c>
       <c r="E186">
-        <v>0.9989350699999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="F186">
-        <v>0.9989350699999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="G186">
-        <v>0.2392382040170877</v>
+        <v>0.2342423866086769</v>
       </c>
       <c r="H186">
-        <v>0.99726191</v>
+        <v>0.9974930900000001</v>
       </c>
     </row>
     <row r="187" spans="1:8">
       <c r="A187" s="1">
-        <v>46164</v>
+        <v>46154</v>
       </c>
       <c r="B187" t="s">
         <v>16</v>
       </c>
       <c r="C187">
-        <v>39.43913909150694</v>
+        <v>40.32854894972581</v>
       </c>
       <c r="D187">
-        <v>21.05297617141148</v>
+        <v>21.09133998298594</v>
       </c>
       <c r="E187">
-        <v>0.999144</v>
+        <v>0.9990972199999999</v>
       </c>
       <c r="F187">
-        <v>0.999144</v>
+        <v>0.9990972199999999</v>
       </c>
       <c r="G187">
-        <v>0.2516582935428642</v>
+        <v>0.2156468205051487</v>
       </c>
       <c r="H187">
-        <v>0.9974678400000001</v>
+        <v>0.99752223</v>
       </c>
     </row>
     <row r="188" spans="1:8">
       <c r="A188" s="1">
-        <v>46167</v>
+        <v>46155</v>
       </c>
       <c r="B188" t="s">
         <v>16</v>
       </c>
       <c r="C188">
-        <v>39.45782844313628</v>
+        <v>40.47987921095815</v>
       </c>
       <c r="D188">
-        <v>21.0518901572272</v>
+        <v>21.35995364434454</v>
       </c>
       <c r="E188">
-        <v>0.999144</v>
+        <v>0.9991780100000001</v>
       </c>
       <c r="F188">
-        <v>0.999144</v>
+        <v>0.9991780100000001</v>
       </c>
       <c r="G188">
-        <v>0.2516582935428642</v>
+        <v>0.2270956128473374</v>
       </c>
       <c r="H188">
-        <v>0.9974678400000001</v>
+        <v>0.9975825700000001</v>
       </c>
     </row>
     <row r="189" spans="1:8">
       <c r="A189" s="1">
-        <v>46168</v>
+        <v>46156</v>
       </c>
       <c r="B189" t="s">
         <v>16</v>
       </c>
       <c r="C189">
-        <v>40.20219297984542</v>
+        <v>41.20436574895244</v>
       </c>
       <c r="D189">
-        <v>21.93106024403281</v>
+        <v>21.48149674387778</v>
       </c>
       <c r="E189">
-        <v>0.9991421799999999</v>
+        <v>0.9991793299999999</v>
       </c>
       <c r="F189">
-        <v>0.9991421799999999</v>
+        <v>0.9991793299999999</v>
       </c>
       <c r="G189">
-        <v>0.2846167552893293</v>
+        <v>0.2454829228401052</v>
       </c>
       <c r="H189">
-        <v>0.9974609800000001</v>
+        <v>0.99754722</v>
       </c>
     </row>
     <row r="190" spans="1:8">
       <c r="A190" s="1">
-        <v>46169</v>
+        <v>46157</v>
       </c>
       <c r="B190" t="s">
         <v>16</v>
       </c>
       <c r="C190">
-        <v>40.34993865302093</v>
+        <v>40.80613062958688</v>
       </c>
       <c r="D190">
-        <v>21.65366031776487</v>
+        <v>21.08912555803936</v>
       </c>
       <c r="E190">
-        <v>0.9991434600000001</v>
+        <v>0.9991790600000001</v>
       </c>
       <c r="F190">
-        <v>0.9991434600000001</v>
+        <v>0.9991790600000001</v>
       </c>
       <c r="G190">
-        <v>0.2796902860011767</v>
+        <v>0.2230017445022556</v>
       </c>
       <c r="H190">
-        <v>0.9991434600000001</v>
+        <v>0.9975824700000002</v>
       </c>
     </row>
     <row r="191" spans="1:8">
       <c r="A191" s="1">
-        <v>46170</v>
+        <v>46160</v>
       </c>
       <c r="B191" t="s">
         <v>16</v>
       </c>
       <c r="C191">
-        <v>40.5850485390846</v>
+        <v>40.11672876026724</v>
       </c>
       <c r="D191">
-        <v>21.75450977746074</v>
+        <v>20.79541439916316</v>
       </c>
       <c r="E191">
-        <v>0.99914592</v>
+        <v>0.999152</v>
       </c>
       <c r="F191">
-        <v>0.99914592</v>
+        <v>0.999152</v>
       </c>
       <c r="G191">
-        <v>0.2964818481030536</v>
+        <v>0.2098184021536666</v>
       </c>
       <c r="H191">
-        <v>0.99914592</v>
+        <v>0.9975007899999999</v>
       </c>
     </row>
     <row r="192" spans="1:8">
       <c r="A192" s="1">
-        <v>46171</v>
+        <v>46161</v>
       </c>
       <c r="B192" t="s">
         <v>16</v>
       </c>
       <c r="C192">
-        <v>41.86785805184477</v>
+        <v>39.69086941528401</v>
       </c>
       <c r="D192">
-        <v>22.33589392797469</v>
+        <v>20.74924328599426</v>
       </c>
       <c r="E192">
-        <v>0.9991336999999999</v>
+        <v>0.99914989</v>
       </c>
       <c r="F192">
-        <v>0.9991336999999999</v>
+        <v>0.99914989</v>
       </c>
       <c r="G192">
-        <v>0.3254158954996882</v>
+        <v>0.2020471776850241</v>
       </c>
       <c r="H192">
-        <v>0.9991336999999999</v>
+        <v>0.9974417</v>
       </c>
     </row>
     <row r="193" spans="1:8">
       <c r="A193" s="1">
-        <v>46174</v>
+        <v>46162</v>
       </c>
       <c r="B193" t="s">
         <v>16</v>
       </c>
       <c r="C193">
-        <v>42.82932322850974</v>
+        <v>40.37836787855562</v>
       </c>
       <c r="D193">
-        <v>22.98998911430362</v>
+        <v>21.11271132314188</v>
       </c>
       <c r="E193">
-        <v>0.99914238</v>
+        <v>0.99915058</v>
       </c>
       <c r="F193">
-        <v>0.99914238</v>
+        <v>0.99915058</v>
       </c>
       <c r="G193">
-        <v>0.3583049032509023</v>
+        <v>0.2291077670847563</v>
       </c>
       <c r="H193">
-        <v>0.99914238</v>
+        <v>0.9974415600000001</v>
       </c>
     </row>
     <row r="194" spans="1:8">
       <c r="A194" s="1">
-        <v>46175</v>
+        <v>46163</v>
       </c>
       <c r="B194" t="s">
         <v>16</v>
       </c>
       <c r="C194">
-        <v>43.11872937189534</v>
+        <v>38.9123066967842</v>
       </c>
       <c r="D194">
-        <v>22.90628380907704</v>
+        <v>21.28910644207464</v>
       </c>
       <c r="E194">
-        <v>0.9990972800000002</v>
+        <v>0.9989350699999999</v>
       </c>
       <c r="F194">
-        <v>0.9990972800000002</v>
+        <v>0.9989350699999999</v>
       </c>
       <c r="G194">
-        <v>0.3753046155885469</v>
+        <v>0.2392382040170877</v>
       </c>
       <c r="H194">
-        <v>0.9990972800000002</v>
+        <v>0.99726191</v>
       </c>
     </row>
     <row r="195" spans="1:8">
       <c r="A195" s="1">
-        <v>46176</v>
+        <v>46164</v>
       </c>
       <c r="B195" t="s">
         <v>16</v>
       </c>
       <c r="C195">
-        <v>42.86143001679577</v>
+        <v>39.43913909150694</v>
       </c>
       <c r="D195">
-        <v>22.72053012591219</v>
+        <v>21.05297617141148</v>
       </c>
       <c r="E195">
-        <v>0.9990984299999999</v>
+        <v>0.999144</v>
       </c>
       <c r="F195">
-        <v>0.9990984299999999</v>
+        <v>0.999144</v>
       </c>
       <c r="G195">
-        <v>0.3615660647779204</v>
+        <v>0.2516582935428642</v>
       </c>
       <c r="H195">
-        <v>0.9990984299999999</v>
+        <v>0.9974678400000001</v>
       </c>
     </row>
     <row r="196" spans="1:8">
       <c r="A196" s="1">
-        <v>46177</v>
+        <v>46167</v>
       </c>
       <c r="B196" t="s">
         <v>16</v>
       </c>
       <c r="C196">
-        <v>42.57902095847519</v>
+        <v>39.45782844313628</v>
       </c>
       <c r="D196">
-        <v>22.20304338566557</v>
+        <v>21.0518901572272</v>
       </c>
       <c r="E196">
-        <v>0.9990006900000001</v>
+        <v>0.999144</v>
       </c>
       <c r="F196">
-        <v>0.9990006900000001</v>
+        <v>0.999144</v>
       </c>
       <c r="G196">
-        <v>0.34033389372967</v>
+        <v>0.2516582935428642</v>
       </c>
       <c r="H196">
-        <v>0.9990006900000001</v>
+        <v>0.9974678400000001</v>
       </c>
     </row>
     <row r="197" spans="1:8">
       <c r="A197" s="1">
-        <v>46178</v>
+        <v>46168</v>
       </c>
       <c r="B197" t="s">
         <v>16</v>
       </c>
       <c r="C197">
-        <v>39.64354477595148</v>
+        <v>40.20219297984542</v>
       </c>
       <c r="D197">
-        <v>20.69555521363093</v>
+        <v>21.93106024403281</v>
       </c>
       <c r="E197">
-        <v>0.9992026399999999</v>
+        <v>0.9991421799999999</v>
       </c>
       <c r="F197">
-        <v>0.9992026399999999</v>
+        <v>0.9991421799999999</v>
       </c>
       <c r="G197">
-        <v>0.251033842835561</v>
+        <v>0.2846167552893293</v>
       </c>
       <c r="H197">
-        <v>0.9992026399999999</v>
+        <v>0.9974609800000001</v>
       </c>
     </row>
     <row r="198" spans="1:8">
       <c r="A198" s="1">
-        <v>46182</v>
+        <v>46169</v>
       </c>
       <c r="B198" t="s">
         <v>16</v>
       </c>
       <c r="C198">
-        <v>39.7656886466531</v>
+        <v>40.34993865302093</v>
       </c>
       <c r="D198">
-        <v>20.79148740795913</v>
+        <v>21.65366031776487</v>
       </c>
       <c r="E198">
-        <v>0.9992145899999999</v>
+        <v>0.9991434600000001</v>
       </c>
       <c r="F198">
-        <v>0.9992145899999999</v>
+        <v>0.9991434600000001</v>
       </c>
       <c r="G198">
-        <v>0.2542950043625791</v>
+        <v>0.2796902860011767</v>
       </c>
       <c r="H198">
-        <v>0.9992145899999999</v>
+        <v>0.9991434600000001</v>
       </c>
     </row>
     <row r="199" spans="1:8">
       <c r="A199" s="1">
-        <v>46183</v>
+        <v>46170</v>
       </c>
       <c r="B199" t="s">
         <v>16</v>
       </c>
       <c r="C199">
-        <v>38.48800295288941</v>
+        <v>40.5850485390846</v>
       </c>
       <c r="D199">
-        <v>20.05492629580107</v>
+        <v>21.75450977746074</v>
       </c>
       <c r="E199">
-        <v>0.9992031100000001</v>
+        <v>0.99914592</v>
       </c>
       <c r="F199">
-        <v>0.9992031100000001</v>
+        <v>0.99914592</v>
       </c>
       <c r="G199">
-        <v>0.2255691072017123</v>
+        <v>0.2964818481030536</v>
       </c>
       <c r="H199">
-        <v>0.9992031100000001</v>
+        <v>0.99914592</v>
       </c>
     </row>
     <row r="200" spans="1:8">
       <c r="A200" s="1">
-        <v>46184</v>
+        <v>46171</v>
       </c>
       <c r="B200" t="s">
         <v>16</v>
       </c>
       <c r="C200">
+        <v>41.86785805184477</v>
+      </c>
+      <c r="D200">
+        <v>22.33589392797469</v>
+      </c>
+      <c r="E200">
+        <v>0.9991336999999999</v>
+      </c>
+      <c r="F200">
+        <v>0.9991336999999999</v>
+      </c>
+      <c r="G200">
+        <v>0.3254158954996882</v>
+      </c>
+      <c r="H200">
+        <v>0.9991336999999999</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8">
+      <c r="A201" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201">
+        <v>42.82932322850974</v>
+      </c>
+      <c r="D201">
+        <v>22.98998911430362</v>
+      </c>
+      <c r="E201">
+        <v>0.99914238</v>
+      </c>
+      <c r="F201">
+        <v>0.99914238</v>
+      </c>
+      <c r="G201">
+        <v>0.3583049032509023</v>
+      </c>
+      <c r="H201">
+        <v>0.99914238</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8">
+      <c r="A202" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B202" t="s">
+        <v>16</v>
+      </c>
+      <c r="C202">
+        <v>43.11872937189534</v>
+      </c>
+      <c r="D202">
+        <v>22.90628380907704</v>
+      </c>
+      <c r="E202">
+        <v>0.9990972800000002</v>
+      </c>
+      <c r="F202">
+        <v>0.9990972800000002</v>
+      </c>
+      <c r="G202">
+        <v>0.3753046155885469</v>
+      </c>
+      <c r="H202">
+        <v>0.9990972800000002</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8">
+      <c r="A203" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B203" t="s">
+        <v>16</v>
+      </c>
+      <c r="C203">
+        <v>42.86143001679577</v>
+      </c>
+      <c r="D203">
+        <v>22.72053012591219</v>
+      </c>
+      <c r="E203">
+        <v>0.9990984299999999</v>
+      </c>
+      <c r="F203">
+        <v>0.9990984299999999</v>
+      </c>
+      <c r="G203">
+        <v>0.3615660647779204</v>
+      </c>
+      <c r="H203">
+        <v>0.9990984299999999</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8">
+      <c r="A204" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B204" t="s">
+        <v>16</v>
+      </c>
+      <c r="C204">
+        <v>42.57902095847519</v>
+      </c>
+      <c r="D204">
+        <v>22.20304338566557</v>
+      </c>
+      <c r="E204">
+        <v>0.9990006900000001</v>
+      </c>
+      <c r="F204">
+        <v>0.9990006900000001</v>
+      </c>
+      <c r="G204">
+        <v>0.34033389372967</v>
+      </c>
+      <c r="H204">
+        <v>0.9990006900000001</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8">
+      <c r="A205" s="1">
+        <v>46178</v>
+      </c>
+      <c r="B205" t="s">
+        <v>16</v>
+      </c>
+      <c r="C205">
+        <v>39.64354477595148</v>
+      </c>
+      <c r="D205">
+        <v>20.69555521363093</v>
+      </c>
+      <c r="E205">
+        <v>0.9992026399999999</v>
+      </c>
+      <c r="F205">
+        <v>0.9992026399999999</v>
+      </c>
+      <c r="G205">
+        <v>0.251033842835561</v>
+      </c>
+      <c r="H205">
+        <v>0.9992026399999999</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8">
+      <c r="A206" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B206" t="s">
+        <v>16</v>
+      </c>
+      <c r="C206">
+        <v>39.7656886466531</v>
+      </c>
+      <c r="D206">
+        <v>20.79148740795913</v>
+      </c>
+      <c r="E206">
+        <v>0.9992145899999999</v>
+      </c>
+      <c r="F206">
+        <v>0.9992145899999999</v>
+      </c>
+      <c r="G206">
+        <v>0.2542950043625791</v>
+      </c>
+      <c r="H206">
+        <v>0.9992145899999999</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8">
+      <c r="A207" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B207" t="s">
+        <v>16</v>
+      </c>
+      <c r="C207">
+        <v>38.48800295288941</v>
+      </c>
+      <c r="D207">
+        <v>20.05492629580107</v>
+      </c>
+      <c r="E207">
+        <v>0.9992031100000001</v>
+      </c>
+      <c r="F207">
+        <v>0.9992031100000001</v>
+      </c>
+      <c r="G207">
+        <v>0.2255691072017123</v>
+      </c>
+      <c r="H207">
+        <v>0.9992031100000001</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8">
+      <c r="A208" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B208" t="s">
+        <v>16</v>
+      </c>
+      <c r="C208">
         <v>39.71404813715499</v>
       </c>
-      <c r="D200">
+      <c r="D208">
         <v>20.78057418129766</v>
       </c>
-      <c r="E200">
+      <c r="E208">
         <v>0.9991764899999999</v>
       </c>
-      <c r="F200">
+      <c r="F208">
         <v>0.9991764899999999</v>
       </c>
-      <c r="G200">
+      <c r="G208">
         <v>0.2712252627049727</v>
       </c>
-      <c r="H200">
+      <c r="H208">
         <v>0.9991764899999999</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8">
+      <c r="A209" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B209" t="s">
+        <v>16</v>
+      </c>
+      <c r="C209">
+        <v>40.05042651208108</v>
+      </c>
+      <c r="D209">
+        <v>20.84207512811844</v>
+      </c>
+      <c r="E209">
+        <v>0.9991762200000001</v>
+      </c>
+      <c r="F209">
+        <v>0.9991762200000001</v>
+      </c>
+      <c r="G209">
+        <v>0.2822576487006332</v>
+      </c>
+      <c r="H209">
+        <v>0.9991762200000001</v>
       </c>
     </row>
   </sheetData>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="17">
   <si>
     <t>Date</t>
   </si>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H209"/>
+  <dimension ref="A1:H218"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -873,42 +873,42 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1">
-        <v>46153</v>
+        <v>46188</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C19">
-        <v>53.14833755912058</v>
+        <v>28.56449485724275</v>
       </c>
       <c r="D19">
-        <v>25.84885448407537</v>
+        <v>18.526579337459</v>
       </c>
       <c r="E19">
-        <v>0.9262</v>
+        <v>0.8778999999999999</v>
       </c>
       <c r="F19">
-        <v>0.9262</v>
+        <v>0.8778999999999999</v>
       </c>
       <c r="G19">
-        <v>0.3839084462043663</v>
+        <v>0.6318927644938916</v>
       </c>
       <c r="H19">
-        <v>0.9262</v>
+        <v>0.9358</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B20" t="s">
         <v>9</v>
       </c>
       <c r="C20">
-        <v>51.82921169635205</v>
+        <v>53.14833755912058</v>
       </c>
       <c r="D20">
-        <v>25.32805827181975</v>
+        <v>25.84885448407537</v>
       </c>
       <c r="E20">
         <v>0.9262</v>
@@ -917,7 +917,7 @@
         <v>0.9262</v>
       </c>
       <c r="G20">
-        <v>0.3568580281685669</v>
+        <v>0.3839084462043663</v>
       </c>
       <c r="H20">
         <v>0.9262</v>
@@ -925,120 +925,120 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="B21" t="s">
         <v>9</v>
       </c>
       <c r="C21">
-        <v>52.28471716753184</v>
+        <v>51.82921169635205</v>
       </c>
       <c r="D21">
-        <v>25.54525144150689</v>
+        <v>25.32805827181975</v>
       </c>
       <c r="E21">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="F21">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
       <c r="G21">
-        <v>0.378012896547947</v>
+        <v>0.3568580281685669</v>
       </c>
       <c r="H21">
-        <v>0.9262000000000001</v>
+        <v>0.9262</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B22" t="s">
         <v>9</v>
       </c>
       <c r="C22">
-        <v>53.87287273813902</v>
+        <v>52.28471716753184</v>
       </c>
       <c r="D22">
-        <v>26.32154226438612</v>
+        <v>25.54525144150689</v>
       </c>
       <c r="E22">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="F22">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
       <c r="G22">
-        <v>0.4166811087612758</v>
+        <v>0.378012896547947</v>
       </c>
       <c r="H22">
-        <v>0.9251999999999999</v>
+        <v>0.9262000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="B23" t="s">
         <v>9</v>
       </c>
       <c r="C23">
-        <v>52.18747148214074</v>
+        <v>53.87287273813902</v>
       </c>
       <c r="D23">
-        <v>25.13616059644496</v>
+        <v>26.32154226438612</v>
       </c>
       <c r="E23">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="F23">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
       <c r="G23">
-        <v>0.3627535778249862</v>
+        <v>0.4166811087612758</v>
       </c>
       <c r="H23">
-        <v>0.9268</v>
+        <v>0.9251999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="B24" t="s">
         <v>9</v>
       </c>
       <c r="C24">
-        <v>50.72035274995172</v>
+        <v>52.18747148214074</v>
       </c>
       <c r="D24">
-        <v>24.61756040386634</v>
+        <v>25.13616059644496</v>
       </c>
       <c r="E24">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="F24">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
       <c r="G24">
         <v>0.3627535778249862</v>
       </c>
       <c r="H24">
-        <v>0.9259000000000001</v>
+        <v>0.9268</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
       </c>
       <c r="C25">
-        <v>50.11981086673613</v>
+        <v>50.72035274995172</v>
       </c>
       <c r="D25">
-        <v>24.13061679021705</v>
+        <v>24.61756040386634</v>
       </c>
       <c r="E25">
         <v>0.9259000000000001</v>
@@ -1047,7 +1047,7 @@
         <v>0.9259000000000001</v>
       </c>
       <c r="G25">
-        <v>0.3258193430227221</v>
+        <v>0.3627535778249862</v>
       </c>
       <c r="H25">
         <v>0.9259000000000001</v>
@@ -1055,120 +1055,120 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
       </c>
       <c r="C26">
-        <v>51.74165648409151</v>
+        <v>50.11981086673613</v>
       </c>
       <c r="D26">
-        <v>24.98091384114761</v>
+        <v>24.13061679021705</v>
       </c>
       <c r="E26">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="F26">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
       <c r="G26">
-        <v>0.3818277262286871</v>
+        <v>0.3258193430227221</v>
       </c>
       <c r="H26">
-        <v>0.9252</v>
+        <v>0.9259000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="B27" t="s">
         <v>9</v>
       </c>
       <c r="C27">
-        <v>49.13455894175823</v>
+        <v>51.74165648409151</v>
       </c>
       <c r="D27">
-        <v>25.30005057653127</v>
+        <v>24.98091384114761</v>
       </c>
       <c r="E27">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="F27">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
       <c r="G27">
-        <v>0.4028091571787618</v>
+        <v>0.3818277262286871</v>
       </c>
       <c r="H27">
-        <v>0.9247</v>
+        <v>0.9252</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="B28" t="s">
         <v>9</v>
       </c>
       <c r="C28">
-        <v>49.57776597479297</v>
+        <v>49.13455894175823</v>
       </c>
       <c r="D28">
-        <v>25.04906725563518</v>
+        <v>25.30005057653127</v>
       </c>
       <c r="E28">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="F28">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
       <c r="G28">
-        <v>0.4256980029692063</v>
+        <v>0.4028091571787618</v>
       </c>
       <c r="H28">
-        <v>0.9245000000000001</v>
+        <v>0.9247</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="B29" t="s">
         <v>9</v>
       </c>
       <c r="C29">
-        <v>49.71239596645896</v>
+        <v>49.57776597479297</v>
       </c>
       <c r="D29">
-        <v>25.18778610744295</v>
+        <v>25.04906725563518</v>
       </c>
       <c r="E29">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="F29">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
       <c r="G29">
-        <v>0.4525749835757003</v>
+        <v>0.4256980029692063</v>
       </c>
       <c r="H29">
-        <v>0.9231999999999999</v>
+        <v>0.9245000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="B30" t="s">
         <v>9</v>
       </c>
       <c r="C30">
-        <v>50.77166277510776</v>
+        <v>49.71239596645896</v>
       </c>
       <c r="D30">
-        <v>25.7431782858765</v>
+        <v>25.18778610744295</v>
       </c>
       <c r="E30">
         <v>0.9231999999999999</v>
@@ -1177,7 +1177,7 @@
         <v>0.9231999999999999</v>
       </c>
       <c r="G30">
-        <v>0.4700884597036457</v>
+        <v>0.4525749835757003</v>
       </c>
       <c r="H30">
         <v>0.9231999999999999</v>
@@ -1185,120 +1185,120 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1">
-        <v>46169</v>
+        <v>46168</v>
       </c>
       <c r="B31" t="s">
         <v>9</v>
       </c>
       <c r="C31">
-        <v>50.57689164833899</v>
+        <v>50.77166277510776</v>
       </c>
       <c r="D31">
-        <v>25.70244067238947</v>
+        <v>25.7431782858765</v>
       </c>
       <c r="E31">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="F31">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
       <c r="G31">
-        <v>0.4518814984464716</v>
+        <v>0.4700884597036457</v>
       </c>
       <c r="H31">
-        <v>0.9217</v>
+        <v>0.9231999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="B32" t="s">
         <v>9</v>
       </c>
       <c r="C32">
-        <v>50.80027854822009</v>
+        <v>50.57689164833899</v>
       </c>
       <c r="D32">
-        <v>25.90068415792015</v>
+        <v>25.70244067238947</v>
       </c>
       <c r="E32">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
       <c r="F32">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
       <c r="G32">
-        <v>0.4699150222743402</v>
+        <v>0.4518814984464716</v>
       </c>
       <c r="H32">
-        <v>0.9231</v>
+        <v>0.9217</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="B33" t="s">
         <v>9</v>
       </c>
       <c r="C33">
-        <v>51.44563447241545</v>
+        <v>50.80027854822009</v>
       </c>
       <c r="D33">
-        <v>26.0970978996374</v>
+        <v>25.90068415792015</v>
       </c>
       <c r="E33">
-        <v>0.9246</v>
+        <v>0.9231</v>
       </c>
       <c r="F33">
-        <v>0.9246</v>
+        <v>0.9231</v>
       </c>
       <c r="G33">
-        <v>0.4791053539115764</v>
+        <v>0.4699150222743402</v>
       </c>
       <c r="H33">
-        <v>0.9246</v>
+        <v>0.9231</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1">
-        <v>46174</v>
+        <v>46171</v>
       </c>
       <c r="B34" t="s">
         <v>9</v>
       </c>
       <c r="C34">
-        <v>53.05792083471825</v>
+        <v>51.44563447241545</v>
       </c>
       <c r="D34">
-        <v>26.86242981002239</v>
+        <v>26.0970978996374</v>
       </c>
       <c r="E34">
-        <v>0.9254999999999999</v>
+        <v>0.9246</v>
       </c>
       <c r="F34">
-        <v>0.9254999999999999</v>
+        <v>0.9246</v>
       </c>
       <c r="G34">
-        <v>0.5306051577195796</v>
+        <v>0.4791053539115764</v>
       </c>
       <c r="H34">
-        <v>0.9254999999999999</v>
+        <v>0.9246</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="B35" t="s">
         <v>9</v>
       </c>
       <c r="C35">
-        <v>54.38946369031042</v>
+        <v>53.05792083471825</v>
       </c>
       <c r="D35">
-        <v>27.57160808325711</v>
+        <v>26.86242981002239</v>
       </c>
       <c r="E35">
         <v>0.9254999999999999</v>
@@ -1307,7 +1307,7 @@
         <v>0.9254999999999999</v>
       </c>
       <c r="G35">
-        <v>0.5845326886558693</v>
+        <v>0.5306051577195796</v>
       </c>
       <c r="H35">
         <v>0.9254999999999999</v>
@@ -1315,328 +1315,328 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="B36" t="s">
         <v>9</v>
       </c>
       <c r="C36">
-        <v>54.35279063045283</v>
+        <v>54.38946369031042</v>
       </c>
       <c r="D36">
-        <v>27.50874919819178</v>
+        <v>27.57160808325711</v>
       </c>
       <c r="E36">
-        <v>0.9162000000000001</v>
+        <v>0.9254999999999999</v>
       </c>
       <c r="F36">
-        <v>0.9162000000000001</v>
+        <v>0.9254999999999999</v>
       </c>
       <c r="G36">
-        <v>0.5992718273849102</v>
+        <v>0.5845326886558693</v>
       </c>
       <c r="H36">
-        <v>0.9162000000000001</v>
+        <v>0.9254999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="B37" t="s">
         <v>9</v>
       </c>
       <c r="C37">
-        <v>53.45790968334249</v>
+        <v>54.35279063045283</v>
       </c>
       <c r="D37">
-        <v>26.99486187834476</v>
+        <v>27.50874919819178</v>
       </c>
       <c r="E37">
-        <v>0.9154000000000001</v>
+        <v>0.9162000000000001</v>
       </c>
       <c r="F37">
-        <v>0.9154000000000001</v>
+        <v>0.9162000000000001</v>
       </c>
       <c r="G37">
-        <v>0.5691000647975994</v>
+        <v>0.5992718273849102</v>
       </c>
       <c r="H37">
-        <v>0.9154000000000001</v>
+        <v>0.9162000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1">
-        <v>46178</v>
+        <v>46177</v>
       </c>
       <c r="B38" t="s">
         <v>9</v>
       </c>
       <c r="C38">
-        <v>52.01314444713902</v>
+        <v>53.45790968334249</v>
       </c>
       <c r="D38">
-        <v>25.48849727916627</v>
+        <v>26.99486187834476</v>
       </c>
       <c r="E38">
-        <v>0.9142999999999999</v>
+        <v>0.9154000000000001</v>
       </c>
       <c r="F38">
-        <v>0.9142999999999999</v>
+        <v>0.9154000000000001</v>
       </c>
       <c r="G38">
-        <v>0.4380094145699611</v>
+        <v>0.5691000647975994</v>
       </c>
       <c r="H38">
-        <v>0.9142999999999999</v>
+        <v>0.9154000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1">
-        <v>46182</v>
+        <v>46178</v>
       </c>
       <c r="B39" t="s">
         <v>9</v>
       </c>
       <c r="C39">
-        <v>50.12461745484359</v>
+        <v>52.01314444713902</v>
       </c>
       <c r="D39">
-        <v>25.31796473106079</v>
+        <v>25.48849727916627</v>
       </c>
       <c r="E39">
-        <v>0.916</v>
+        <v>0.9142999999999999</v>
       </c>
       <c r="F39">
-        <v>0.916</v>
+        <v>0.9142999999999999</v>
       </c>
       <c r="G39">
-        <v>0.4801457138994158</v>
+        <v>0.4380094145699611</v>
       </c>
       <c r="H39">
-        <v>0.916</v>
+        <v>0.9142999999999999</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1">
-        <v>46183</v>
+        <v>46182</v>
       </c>
       <c r="B40" t="s">
         <v>9</v>
       </c>
       <c r="C40">
-        <v>51.46065536727718</v>
+        <v>50.12461745484359</v>
       </c>
       <c r="D40">
-        <v>25.08120911400394</v>
+        <v>25.31796473106079</v>
       </c>
       <c r="E40">
-        <v>0.9188000000000002</v>
+        <v>0.916</v>
       </c>
       <c r="F40">
-        <v>0.9188000000000002</v>
+        <v>0.916</v>
       </c>
       <c r="G40">
-        <v>0.426738362957046</v>
+        <v>0.4801457138994158</v>
       </c>
       <c r="H40">
-        <v>0.9188000000000002</v>
+        <v>0.916</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="B41" t="s">
         <v>9</v>
       </c>
       <c r="C41">
-        <v>56.06808173087</v>
+        <v>51.46065536727718</v>
       </c>
       <c r="D41">
-        <v>26.41955208935029</v>
+        <v>25.08120911400394</v>
       </c>
       <c r="E41">
-        <v>0.9193</v>
+        <v>0.9188000000000002</v>
       </c>
       <c r="F41">
-        <v>0.9193</v>
+        <v>0.9188000000000002</v>
       </c>
       <c r="G41">
-        <v>0.5195075435359697</v>
+        <v>0.426738362957046</v>
       </c>
       <c r="H41">
-        <v>0.9193</v>
+        <v>0.9188000000000002</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="B42" t="s">
         <v>9</v>
       </c>
       <c r="C42">
-        <v>55.25570685331304</v>
+        <v>56.06808173087</v>
       </c>
       <c r="D42">
-        <v>27.01537159822627</v>
+        <v>26.41955208935029</v>
       </c>
       <c r="E42">
-        <v>0.921</v>
+        <v>0.9193</v>
       </c>
       <c r="F42">
-        <v>0.921</v>
+        <v>0.9193</v>
       </c>
       <c r="G42">
-        <v>0.5477718912829104</v>
+        <v>0.5195075435359697</v>
       </c>
       <c r="H42">
-        <v>0.921</v>
+        <v>0.9193</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1">
-        <v>46153</v>
+        <v>46185</v>
       </c>
       <c r="B43" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C43">
-        <v>34.64560932909123</v>
+        <v>55.25570685331304</v>
       </c>
       <c r="D43">
-        <v>26.08311546080494</v>
+        <v>27.01537159822627</v>
       </c>
       <c r="E43">
-        <v>0.9983000000000001</v>
+        <v>0.921</v>
       </c>
       <c r="F43">
-        <v>0.9983000000000001</v>
+        <v>0.921</v>
       </c>
       <c r="G43">
-        <v>0.06258613715048233</v>
+        <v>0.5477718912829104</v>
       </c>
       <c r="H43">
-        <v>0.9983000000000001</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1">
-        <v>46154</v>
+        <v>46188</v>
       </c>
       <c r="B44" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C44">
-        <v>34.50204921141101</v>
+        <v>56.5999353845982</v>
       </c>
       <c r="D44">
-        <v>25.94535229304585</v>
+        <v>28.25944759202702</v>
       </c>
       <c r="E44">
-        <v>0.9984</v>
+        <v>0.9201</v>
       </c>
       <c r="F44">
-        <v>0.9984</v>
+        <v>0.9201</v>
       </c>
       <c r="G44">
-        <v>0.05768943168306073</v>
+        <v>0.6169586086481644</v>
       </c>
       <c r="H44">
-        <v>0.9984</v>
+        <v>0.9201</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="B45" t="s">
         <v>10</v>
       </c>
       <c r="C45">
-        <v>35.10429483281073</v>
+        <v>34.64560932909123</v>
       </c>
       <c r="D45">
-        <v>26.43864879939599</v>
+        <v>26.08311546080494</v>
       </c>
       <c r="E45">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="F45">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
       <c r="G45">
-        <v>0.07926550001722021</v>
+        <v>0.06258613715048233</v>
       </c>
       <c r="H45">
-        <v>0.9984</v>
+        <v>0.9983000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="B46" t="s">
         <v>10</v>
       </c>
       <c r="C46">
-        <v>35.36860632820093</v>
+        <v>34.50204921141101</v>
       </c>
       <c r="D46">
-        <v>26.56575571102338</v>
+        <v>25.94535229304585</v>
       </c>
       <c r="E46">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="F46">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
       <c r="G46">
-        <v>0.08553946591902095</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H46">
-        <v>0.9985999999999999</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="B47" t="s">
         <v>10</v>
       </c>
       <c r="C47">
-        <v>34.88080083527914</v>
+        <v>35.10429483281073</v>
       </c>
       <c r="D47">
-        <v>26.19322945679072</v>
+        <v>26.43864879939599</v>
       </c>
       <c r="E47">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="F47">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
       <c r="G47">
-        <v>0.06870693142475881</v>
+        <v>0.07926550001722021</v>
       </c>
       <c r="H47">
-        <v>0.9983</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1">
-        <v>46160</v>
+        <v>46156</v>
       </c>
       <c r="B48" t="s">
         <v>10</v>
       </c>
       <c r="C48">
-        <v>34.67638692539213</v>
+        <v>35.36860632820093</v>
       </c>
       <c r="D48">
-        <v>26.06707890342319</v>
+        <v>26.56575571102338</v>
       </c>
       <c r="E48">
         <v>0.9985999999999999</v>
@@ -1645,7 +1645,7 @@
         <v>0.9985999999999999</v>
       </c>
       <c r="G48">
-        <v>0.06289213016552919</v>
+        <v>0.08553946591902095</v>
       </c>
       <c r="H48">
         <v>0.9985999999999999</v>
@@ -1653,120 +1653,120 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="B49" t="s">
         <v>10</v>
       </c>
       <c r="C49">
-        <v>34.21212662725402</v>
+        <v>34.88080083527914</v>
       </c>
       <c r="D49">
-        <v>25.60349394367002</v>
+        <v>26.19322945679072</v>
       </c>
       <c r="E49">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="F49">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
       <c r="G49">
-        <v>0.0486610616591685</v>
+        <v>0.06870693142475881</v>
       </c>
       <c r="H49">
-        <v>0.9984999999999998</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="B50" t="s">
         <v>10</v>
       </c>
       <c r="C50">
-        <v>34.78598436564941</v>
+        <v>34.67638692539213</v>
       </c>
       <c r="D50">
-        <v>25.95505316769806</v>
+        <v>26.06707890342319</v>
       </c>
       <c r="E50">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="F50">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
       <c r="G50">
-        <v>0.06335117806143331</v>
+        <v>0.06289213016552919</v>
       </c>
       <c r="H50">
-        <v>0.9983</v>
+        <v>0.9985999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1">
-        <v>46163</v>
+        <v>46161</v>
       </c>
       <c r="B51" t="s">
         <v>10</v>
       </c>
       <c r="C51">
-        <v>33.4539909056227</v>
+        <v>34.21212662725402</v>
       </c>
       <c r="D51">
-        <v>25.96014535427112</v>
+        <v>25.60349394367002</v>
       </c>
       <c r="E51">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="F51">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
       <c r="G51">
-        <v>0.06350423294229035</v>
+        <v>0.0486610616591685</v>
       </c>
       <c r="H51">
-        <v>0.9984</v>
+        <v>0.9984999999999998</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1">
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="B52" t="s">
         <v>10</v>
       </c>
       <c r="C52">
-        <v>33.24951933563993</v>
+        <v>34.78598436564941</v>
       </c>
       <c r="D52">
-        <v>25.46629530314992</v>
+        <v>25.95505316769806</v>
       </c>
       <c r="E52">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="F52">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="G52">
-        <v>0.06136193159696024</v>
+        <v>0.06335117806143331</v>
       </c>
       <c r="H52">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1">
-        <v>46167</v>
+        <v>46163</v>
       </c>
       <c r="B53" t="s">
         <v>10</v>
       </c>
       <c r="C53">
-        <v>33.29896419867477</v>
+        <v>33.4539909056227</v>
       </c>
       <c r="D53">
-        <v>25.45090185337973</v>
+        <v>25.96014535427112</v>
       </c>
       <c r="E53">
         <v>0.9984</v>
@@ -1775,7 +1775,7 @@
         <v>0.9984</v>
       </c>
       <c r="G53">
-        <v>0.06136193159696024</v>
+        <v>0.06350423294229035</v>
       </c>
       <c r="H53">
         <v>0.9984</v>
@@ -1783,16 +1783,16 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1">
-        <v>46168</v>
+        <v>46164</v>
       </c>
       <c r="B54" t="s">
         <v>10</v>
       </c>
       <c r="C54">
-        <v>33.41270923608511</v>
+        <v>33.24951933563993</v>
       </c>
       <c r="D54">
-        <v>25.54156152389702</v>
+        <v>25.46629530314992</v>
       </c>
       <c r="E54">
         <v>0.9984</v>
@@ -1801,7 +1801,7 @@
         <v>0.9984</v>
       </c>
       <c r="G54">
-        <v>0.06549347940676342</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H54">
         <v>0.9984</v>
@@ -1809,198 +1809,198 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1">
-        <v>46169</v>
+        <v>46167</v>
       </c>
       <c r="B55" t="s">
         <v>10</v>
       </c>
       <c r="C55">
-        <v>33.73350746548562</v>
+        <v>33.29896419867477</v>
       </c>
       <c r="D55">
-        <v>25.75393367034243</v>
+        <v>25.45090185337973</v>
       </c>
       <c r="E55">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="F55">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
       <c r="G55">
-        <v>0.07620510288008187</v>
+        <v>0.06136193159696024</v>
       </c>
       <c r="H55">
-        <v>0.9987000000000001</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1">
-        <v>46170</v>
+        <v>46168</v>
       </c>
       <c r="B56" t="s">
         <v>10</v>
       </c>
       <c r="C56">
-        <v>33.84336414535104</v>
+        <v>33.41270923608511</v>
       </c>
       <c r="D56">
-        <v>25.97168203877208</v>
+        <v>25.54156152389702</v>
       </c>
       <c r="E56">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
       <c r="F56">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
       <c r="G56">
-        <v>0.0844683152463559</v>
+        <v>0.06549347940676342</v>
       </c>
       <c r="H56">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1">
-        <v>46171</v>
+        <v>46169</v>
       </c>
       <c r="B57" t="s">
         <v>10</v>
       </c>
       <c r="C57">
-        <v>33.73370320039719</v>
+        <v>33.73350746548562</v>
       </c>
       <c r="D57">
-        <v>25.880209881309</v>
+        <v>25.75393367034243</v>
       </c>
       <c r="E57">
-        <v>0.9988</v>
+        <v>0.9987000000000001</v>
       </c>
       <c r="F57">
-        <v>0.9988</v>
+        <v>0.9987000000000001</v>
       </c>
       <c r="G57">
-        <v>0.08201990413931148</v>
+        <v>0.07620510288008187</v>
       </c>
       <c r="H57">
-        <v>0.9988</v>
+        <v>0.9987000000000001</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1">
-        <v>46174</v>
+        <v>46170</v>
       </c>
       <c r="B58" t="s">
         <v>10</v>
       </c>
       <c r="C58">
-        <v>33.45546240777382</v>
+        <v>33.84336414535104</v>
       </c>
       <c r="D58">
-        <v>25.61350381215703</v>
+        <v>25.97168203877208</v>
       </c>
       <c r="E58">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
       <c r="F58">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
       <c r="G58">
-        <v>0.06901304118647311</v>
+        <v>0.0844683152463559</v>
       </c>
       <c r="H58">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1">
-        <v>46175</v>
+        <v>46171</v>
       </c>
       <c r="B59" t="s">
         <v>10</v>
       </c>
       <c r="C59">
-        <v>33.31245255516097</v>
+        <v>33.73370320039719</v>
       </c>
       <c r="D59">
-        <v>25.36461330330757</v>
+        <v>25.880209881309</v>
       </c>
       <c r="E59">
-        <v>0.9989999999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="F59">
-        <v>0.9989999999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="G59">
-        <v>0.05845447259401171</v>
+        <v>0.08201990413931148</v>
       </c>
       <c r="H59">
-        <v>0.9989999999999999</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1">
-        <v>46176</v>
+        <v>46174</v>
       </c>
       <c r="B60" t="s">
         <v>10</v>
       </c>
       <c r="C60">
-        <v>33.02444632653544</v>
+        <v>33.45546240777382</v>
       </c>
       <c r="D60">
-        <v>25.07926152561908</v>
+        <v>25.61350381215703</v>
       </c>
       <c r="E60">
-        <v>0.9991</v>
+        <v>0.999</v>
       </c>
       <c r="F60">
-        <v>0.9991</v>
+        <v>0.999</v>
       </c>
       <c r="G60">
-        <v>0.04697780820974229</v>
+        <v>0.06901304118647311</v>
       </c>
       <c r="H60">
-        <v>0.9991</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1">
-        <v>46177</v>
+        <v>46175</v>
       </c>
       <c r="B61" t="s">
         <v>10</v>
       </c>
       <c r="C61">
-        <v>33.50291463064395</v>
+        <v>33.31245255516097</v>
       </c>
       <c r="D61">
-        <v>25.33002193941023</v>
+        <v>25.36461330330757</v>
       </c>
       <c r="E61">
-        <v>0.9991000000000001</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="F61">
-        <v>0.9991000000000001</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="G61">
-        <v>0.05768943168306073</v>
+        <v>0.05845447259401171</v>
       </c>
       <c r="H61">
-        <v>0.9991000000000001</v>
+        <v>0.9989999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1">
-        <v>46178</v>
+        <v>46176</v>
       </c>
       <c r="B62" t="s">
         <v>10</v>
       </c>
       <c r="C62">
-        <v>32.19021336116872</v>
+        <v>33.02444632653544</v>
       </c>
       <c r="D62">
-        <v>24.38570557505481</v>
+        <v>25.07926152561908</v>
       </c>
       <c r="E62">
         <v>0.9991</v>
@@ -2009,7 +2009,7 @@
         <v>0.9991</v>
       </c>
       <c r="G62">
-        <v>0.01775063028607016</v>
+        <v>0.04697780820974229</v>
       </c>
       <c r="H62">
         <v>0.9991</v>
@@ -2017,874 +2017,874 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1">
-        <v>46182</v>
+        <v>46177</v>
       </c>
       <c r="B63" t="s">
         <v>10</v>
       </c>
       <c r="C63">
-        <v>32.06505731417286</v>
+        <v>33.50291463064395</v>
       </c>
       <c r="D63">
-        <v>24.06041109516704</v>
+        <v>25.33002193941023</v>
       </c>
       <c r="E63">
-        <v>0.9988999999999999</v>
+        <v>0.9991000000000001</v>
       </c>
       <c r="F63">
-        <v>0.9988999999999999</v>
+        <v>0.9991000000000001</v>
       </c>
       <c r="G63">
-        <v>0.004743767333231785</v>
+        <v>0.05768943168306073</v>
       </c>
       <c r="H63">
-        <v>0.9988999999999999</v>
+        <v>0.9991000000000001</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1">
-        <v>46183</v>
+        <v>46178</v>
       </c>
       <c r="B64" t="s">
         <v>10</v>
       </c>
       <c r="C64">
-        <v>31.23512211947358</v>
+        <v>32.19021336116872</v>
       </c>
       <c r="D64">
-        <v>23.50146802051874</v>
+        <v>24.38570557505481</v>
       </c>
       <c r="E64">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F64">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G64">
-        <v>-0.01729146564349893</v>
+        <v>0.01775063028607016</v>
       </c>
       <c r="H64">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="B65" t="s">
         <v>10</v>
       </c>
       <c r="C65">
-        <v>31.67819012660615</v>
+        <v>32.06505731417286</v>
       </c>
       <c r="D65">
-        <v>23.76719139935413</v>
+        <v>24.06041109516704</v>
       </c>
       <c r="E65">
-        <v>0.9992000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="F65">
-        <v>0.9992000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="G65">
-        <v>-0.006732897051037523</v>
+        <v>0.004743767333231785</v>
       </c>
       <c r="H65">
-        <v>0.9992000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1">
-        <v>46185</v>
+        <v>46183</v>
       </c>
       <c r="B66" t="s">
         <v>10</v>
       </c>
       <c r="C66">
-        <v>31.61398696858495</v>
+        <v>31.23512211947358</v>
       </c>
       <c r="D66">
-        <v>23.75142539276475</v>
+        <v>23.50146802051874</v>
       </c>
       <c r="E66">
-        <v>0.9992000000000002</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="F66">
-        <v>0.9992000000000002</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="G66">
-        <v>-0.006732897051037523</v>
+        <v>-0.01729146564349893</v>
       </c>
       <c r="H66">
-        <v>0.9992000000000002</v>
+        <v>0.9989999999999999</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1">
-        <v>46153</v>
+        <v>46184</v>
       </c>
       <c r="B67" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C67">
-        <v>36.55790859258162</v>
+        <v>31.67819012660615</v>
       </c>
       <c r="D67">
-        <v>22.67181120908155</v>
+        <v>23.76719139935413</v>
       </c>
       <c r="E67">
-        <v>0.9990740999999999</v>
+        <v>0.9992000000000001</v>
       </c>
       <c r="F67">
-        <v>0.9990740999999999</v>
+        <v>0.9992000000000001</v>
       </c>
       <c r="G67">
-        <v>0.1648443271746771</v>
+        <v>-0.006732897051037523</v>
       </c>
       <c r="H67">
-        <v>0.9990740999999999</v>
+        <v>0.9992000000000001</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1">
-        <v>46154</v>
+        <v>46185</v>
       </c>
       <c r="B68" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C68">
-        <v>36.44753722959613</v>
+        <v>31.61398696858495</v>
       </c>
       <c r="D68">
-        <v>22.40292401789388</v>
+        <v>23.75142539276475</v>
       </c>
       <c r="E68">
-        <v>0.9990772499999999</v>
+        <v>0.9992000000000002</v>
       </c>
       <c r="F68">
-        <v>0.9990772499999999</v>
+        <v>0.9992000000000002</v>
       </c>
       <c r="G68">
-        <v>0.154964342628132</v>
+        <v>-0.006732897051037523</v>
       </c>
       <c r="H68">
-        <v>0.9990772499999999</v>
+        <v>0.9992000000000002</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1">
-        <v>46155</v>
+        <v>46188</v>
       </c>
       <c r="B69" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C69">
-        <v>36.63128514035871</v>
+        <v>32.19490444707423</v>
       </c>
       <c r="D69">
-        <v>22.65773388934668</v>
+        <v>24.39321423208603</v>
       </c>
       <c r="E69">
-        <v>0.99907745</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="F69">
-        <v>0.99907745</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="G69">
-        <v>0.1671633421405267</v>
+        <v>0.01943388373549637</v>
       </c>
       <c r="H69">
-        <v>0.99907745</v>
+        <v>0.9991999999999999</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="B70" t="s">
         <v>11</v>
       </c>
       <c r="C70">
-        <v>36.87865927427314</v>
+        <v>36.55790859258162</v>
       </c>
       <c r="D70">
-        <v>22.69755646854794</v>
+        <v>22.67181120908155</v>
       </c>
       <c r="E70">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="F70">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
       <c r="G70">
-        <v>0.1754592080224002</v>
+        <v>0.1648443271746771</v>
       </c>
       <c r="H70">
-        <v>0.99908601</v>
+        <v>0.9990740999999999</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="B71" t="s">
         <v>11</v>
       </c>
       <c r="C71">
-        <v>36.52208783231286</v>
+        <v>36.44753722959613</v>
       </c>
       <c r="D71">
-        <v>22.32462309676992</v>
+        <v>22.40292401789388</v>
       </c>
       <c r="E71">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="F71">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
       <c r="G71">
-        <v>0.1577242156354994</v>
+        <v>0.154964342628132</v>
       </c>
       <c r="H71">
-        <v>0.99915499</v>
+        <v>0.9990772499999999</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1">
-        <v>46160</v>
+        <v>46155</v>
       </c>
       <c r="B72" t="s">
         <v>11</v>
       </c>
       <c r="C72">
-        <v>36.25604200674668</v>
+        <v>36.63128514035871</v>
       </c>
       <c r="D72">
-        <v>22.16555007468561</v>
+        <v>22.65773388934668</v>
       </c>
       <c r="E72">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="F72">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
       <c r="G72">
-        <v>0.1527434068648266</v>
+        <v>0.1671633421405267</v>
       </c>
       <c r="H72">
-        <v>0.9991011900000002</v>
+        <v>0.99907745</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1">
-        <v>46161</v>
+        <v>46156</v>
       </c>
       <c r="B73" t="s">
         <v>11</v>
       </c>
       <c r="C73">
-        <v>36.01040085730018</v>
+        <v>36.87865927427314</v>
       </c>
       <c r="D73">
-        <v>22.19475589056387</v>
+        <v>22.69755646854794</v>
       </c>
       <c r="E73">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="F73">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
       <c r="G73">
-        <v>0.1456396418594061</v>
+        <v>0.1754592080224002</v>
       </c>
       <c r="H73">
-        <v>0.9993222199999999</v>
+        <v>0.99908601</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1">
-        <v>46162</v>
+        <v>46157</v>
       </c>
       <c r="B74" t="s">
         <v>11</v>
       </c>
       <c r="C74">
-        <v>36.45290912796982</v>
+        <v>36.52208783231286</v>
       </c>
       <c r="D74">
-        <v>22.46357594746874</v>
+        <v>22.32462309676992</v>
       </c>
       <c r="E74">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="F74">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
       <c r="G74">
-        <v>0.1646157747240327</v>
+        <v>0.1577242156354994</v>
       </c>
       <c r="H74">
-        <v>0.9992557700000001</v>
+        <v>0.99915499</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1">
-        <v>46163</v>
+        <v>46160</v>
       </c>
       <c r="B75" t="s">
         <v>11</v>
       </c>
       <c r="C75">
-        <v>35.75282090566891</v>
+        <v>36.25604200674668</v>
       </c>
       <c r="D75">
-        <v>22.57615417310648</v>
+        <v>22.16555007468561</v>
       </c>
       <c r="E75">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="F75">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
       <c r="G75">
-        <v>0.1668367104873381</v>
+        <v>0.1527434068648266</v>
       </c>
       <c r="H75">
-        <v>0.99926856</v>
+        <v>0.9991011900000002</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1">
-        <v>46164</v>
+        <v>46161</v>
       </c>
       <c r="B76" t="s">
         <v>11</v>
       </c>
       <c r="C76">
-        <v>35.75514940724808</v>
+        <v>36.01040085730018</v>
       </c>
       <c r="D76">
-        <v>22.28880693466429</v>
+        <v>22.19475589056387</v>
       </c>
       <c r="E76">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="F76">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
       <c r="G76">
-        <v>0.1717848261904962</v>
+        <v>0.1456396418594061</v>
       </c>
       <c r="H76">
-        <v>0.9992573500000002</v>
+        <v>0.9993222199999999</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1">
-        <v>46167</v>
+        <v>46162</v>
       </c>
       <c r="B77" t="s">
         <v>11</v>
       </c>
       <c r="C77">
-        <v>35.84133099010302</v>
+        <v>36.45290912796982</v>
       </c>
       <c r="D77">
-        <v>22.37458514769363</v>
+        <v>22.46357594746874</v>
       </c>
       <c r="E77">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="F77">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
       <c r="G77">
-        <v>0.1717848261904962</v>
+        <v>0.1646157747240327</v>
       </c>
       <c r="H77">
-        <v>0.9992609200000001</v>
+        <v>0.9992557700000001</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="1">
-        <v>46168</v>
+        <v>46163</v>
       </c>
       <c r="B78" t="s">
         <v>11</v>
       </c>
       <c r="C78">
-        <v>36.23214279739292</v>
+        <v>35.75282090566891</v>
       </c>
       <c r="D78">
-        <v>22.93484792820123</v>
+        <v>22.57615417310648</v>
       </c>
       <c r="E78">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
       <c r="F78">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
       <c r="G78">
-        <v>0.1925900763781823</v>
+        <v>0.1668367104873381</v>
       </c>
       <c r="H78">
-        <v>0.9992609200000001</v>
+        <v>0.99926856</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="B79" t="s">
         <v>11</v>
       </c>
       <c r="C79">
-        <v>36.4336692499184</v>
+        <v>35.75514940724808</v>
       </c>
       <c r="D79">
-        <v>22.75940954009856</v>
+        <v>22.28880693466429</v>
       </c>
       <c r="E79">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="F79">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
       <c r="G79">
-        <v>0.1912346098381414</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H79">
-        <v>0.9992099400000001</v>
+        <v>0.9992573500000002</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="B80" t="s">
         <v>11</v>
       </c>
       <c r="C80">
-        <v>36.57358557066742</v>
+        <v>35.84133099010302</v>
       </c>
       <c r="D80">
-        <v>22.83069636955243</v>
+        <v>22.37458514769363</v>
       </c>
       <c r="E80">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="F80">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="G80">
-        <v>0.2012778603742877</v>
+        <v>0.1717848261904962</v>
       </c>
       <c r="H80">
-        <v>0.9994435600000001</v>
+        <v>0.9992609200000001</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="1">
-        <v>46171</v>
+        <v>46168</v>
       </c>
       <c r="B81" t="s">
         <v>11</v>
       </c>
       <c r="C81">
-        <v>36.67481300942</v>
+        <v>36.23214279739292</v>
       </c>
       <c r="D81">
-        <v>22.95852861681004</v>
+        <v>22.93484792820123</v>
       </c>
       <c r="E81">
-        <v>0.9964953299999998</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="F81">
-        <v>0.9964953299999998</v>
+        <v>0.9992609200000001</v>
       </c>
       <c r="G81">
-        <v>0.2057034850411275</v>
+        <v>0.1925900763781823</v>
       </c>
       <c r="H81">
-        <v>0.9994474899999999</v>
+        <v>0.9992609200000001</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="1">
-        <v>46174</v>
+        <v>46169</v>
       </c>
       <c r="B82" t="s">
         <v>11</v>
       </c>
       <c r="C82">
-        <v>36.84565507982974</v>
+        <v>36.4336692499184</v>
       </c>
       <c r="D82">
-        <v>23.15960292175205</v>
+        <v>22.75940954009856</v>
       </c>
       <c r="E82">
-        <v>0.99646052</v>
+        <v>0.9992099400000001</v>
       </c>
       <c r="F82">
-        <v>0.99646052</v>
+        <v>0.9992099400000001</v>
       </c>
       <c r="G82">
-        <v>0.2129379226426205</v>
+        <v>0.1912346098381414</v>
       </c>
       <c r="H82">
-        <v>0.9993986199999999</v>
+        <v>0.9992099400000001</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="1">
-        <v>46175</v>
+        <v>46170</v>
       </c>
       <c r="B83" t="s">
         <v>11</v>
       </c>
       <c r="C83">
-        <v>36.88482057171844</v>
+        <v>36.57358557066742</v>
       </c>
       <c r="D83">
-        <v>23.03898938038424</v>
+        <v>22.83069636955243</v>
       </c>
       <c r="E83">
-        <v>0.99645675</v>
+        <v>0.9994435600000001</v>
       </c>
       <c r="F83">
-        <v>0.99645675</v>
+        <v>0.9994435600000001</v>
       </c>
       <c r="G83">
-        <v>0.2185229551183987</v>
+        <v>0.2012778603742877</v>
       </c>
       <c r="H83">
-        <v>0.9994034199999998</v>
+        <v>0.9994435600000001</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="1">
-        <v>46176</v>
+        <v>46171</v>
       </c>
       <c r="B84" t="s">
         <v>11</v>
       </c>
       <c r="C84">
-        <v>36.96809213745556</v>
+        <v>36.67481300942</v>
       </c>
       <c r="D84">
-        <v>22.99660212231548</v>
+        <v>22.95852861681004</v>
       </c>
       <c r="E84">
-        <v>0.9964706</v>
+        <v>0.9964953299999998</v>
       </c>
       <c r="F84">
-        <v>0.9964706</v>
+        <v>0.9964953299999998</v>
       </c>
       <c r="G84">
-        <v>0.2153385706032709</v>
+        <v>0.2057034850411275</v>
       </c>
       <c r="H84">
-        <v>0.9993955800000001</v>
+        <v>0.9994474899999999</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1">
-        <v>46177</v>
+        <v>46174</v>
       </c>
       <c r="B85" t="s">
         <v>11</v>
       </c>
       <c r="C85">
-        <v>37.13780815830533</v>
+        <v>36.84565507982974</v>
       </c>
       <c r="D85">
-        <v>22.74889586257873</v>
+        <v>23.15960292175205</v>
       </c>
       <c r="E85">
-        <v>0.9964706899999999</v>
+        <v>0.99646052</v>
       </c>
       <c r="F85">
-        <v>0.9964706899999999</v>
+        <v>0.99646052</v>
       </c>
       <c r="G85">
-        <v>0.2094594998678323</v>
+        <v>0.2129379226426205</v>
       </c>
       <c r="H85">
-        <v>0.99938478</v>
+        <v>0.9993986199999999</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="1">
-        <v>46178</v>
+        <v>46175</v>
       </c>
       <c r="B86" t="s">
         <v>11</v>
       </c>
       <c r="C86">
-        <v>35.57681391373501</v>
+        <v>36.88482057171844</v>
       </c>
       <c r="D86">
-        <v>21.69452833602077</v>
+        <v>23.03898938038424</v>
       </c>
       <c r="E86">
-        <v>0.9964558499999999</v>
+        <v>0.99645675</v>
       </c>
       <c r="F86">
-        <v>0.9964558499999999</v>
+        <v>0.99645675</v>
       </c>
       <c r="G86">
-        <v>0.151404286858543</v>
+        <v>0.2185229551183987</v>
       </c>
       <c r="H86">
-        <v>0.9993850399999999</v>
+        <v>0.9994034199999998</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="1">
-        <v>46182</v>
+        <v>46176</v>
       </c>
       <c r="B87" t="s">
         <v>11</v>
       </c>
       <c r="C87">
-        <v>35.58815840295288</v>
+        <v>36.96809213745556</v>
       </c>
       <c r="D87">
-        <v>21.80812849732373</v>
+        <v>22.99660212231548</v>
       </c>
       <c r="E87">
-        <v>0.9962853900000002</v>
+        <v>0.9964706</v>
       </c>
       <c r="F87">
-        <v>0.9962853900000002</v>
+        <v>0.9964706</v>
       </c>
       <c r="G87">
-        <v>0.1559278910539408</v>
+        <v>0.2153385706032709</v>
       </c>
       <c r="H87">
-        <v>0.9992534400000002</v>
+        <v>0.9993955800000001</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1">
-        <v>46183</v>
+        <v>46177</v>
       </c>
       <c r="B88" t="s">
         <v>11</v>
       </c>
       <c r="C88">
-        <v>34.74027179067053</v>
+        <v>37.13780815830533</v>
       </c>
       <c r="D88">
-        <v>21.20683390251297</v>
+        <v>22.74889586257873</v>
       </c>
       <c r="E88">
-        <v>0.9962360400000001</v>
+        <v>0.9964706899999999</v>
       </c>
       <c r="F88">
-        <v>0.9962360400000001</v>
+        <v>0.9964706899999999</v>
       </c>
       <c r="G88">
-        <v>0.132836418641906</v>
+        <v>0.2094594998678323</v>
       </c>
       <c r="H88">
-        <v>0.9992478800000001</v>
+        <v>0.99938478</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="1">
-        <v>46184</v>
+        <v>46178</v>
       </c>
       <c r="B89" t="s">
         <v>11</v>
       </c>
       <c r="C89">
-        <v>35.56883979970284</v>
+        <v>35.57681391373501</v>
       </c>
       <c r="D89">
-        <v>21.93852986554604</v>
+        <v>21.69452833602077</v>
       </c>
       <c r="E89">
-        <v>0.9961625199999998</v>
+        <v>0.9964558499999999</v>
       </c>
       <c r="F89">
-        <v>0.9961625199999998</v>
+        <v>0.9964558499999999</v>
       </c>
       <c r="G89">
-        <v>0.1710989694905902</v>
+        <v>0.151404286858543</v>
       </c>
       <c r="H89">
-        <v>0.999197</v>
+        <v>0.9993850399999999</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="1">
-        <v>46185</v>
+        <v>46182</v>
       </c>
       <c r="B90" t="s">
         <v>11</v>
       </c>
       <c r="C90">
-        <v>35.92309284525166</v>
+        <v>35.58815840295288</v>
       </c>
       <c r="D90">
-        <v>22.00037840050582</v>
+        <v>21.80812849732373</v>
       </c>
       <c r="E90">
-        <v>0.99603186</v>
+        <v>0.9962853900000002</v>
       </c>
       <c r="F90">
-        <v>0.99603186</v>
+        <v>0.9962853900000002</v>
       </c>
       <c r="G90">
-        <v>0.1779905285791235</v>
+        <v>0.1559278910539408</v>
       </c>
       <c r="H90">
-        <v>0.99904038</v>
+        <v>0.9992534400000002</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="1">
-        <v>46153</v>
+        <v>46183</v>
       </c>
       <c r="B91" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C91">
-        <v>52.70832779833182</v>
+        <v>34.74027179067053</v>
       </c>
       <c r="D91">
-        <v>23.99044674439659</v>
+        <v>21.20683390251297</v>
       </c>
       <c r="E91">
-        <v>0.9994000000000002</v>
+        <v>0.9962360400000001</v>
       </c>
       <c r="F91">
-        <v>0.9994000000000002</v>
+        <v>0.9962360400000001</v>
       </c>
       <c r="G91">
-        <v>0.5438253854918791</v>
+        <v>0.132836418641906</v>
       </c>
       <c r="H91">
-        <v>0.9994000000000002</v>
+        <v>0.9992478800000001</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="1">
-        <v>46154</v>
+        <v>46184</v>
       </c>
       <c r="B92" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C92">
-        <v>50.89464485280568</v>
+        <v>35.56883979970284</v>
       </c>
       <c r="D92">
-        <v>23.21558303176282</v>
+        <v>21.93852986554604</v>
       </c>
       <c r="E92">
-        <v>0.9996</v>
+        <v>0.9961625199999998</v>
       </c>
       <c r="F92">
-        <v>0.9996</v>
+        <v>0.9961625199999998</v>
       </c>
       <c r="G92">
-        <v>0.5034825029548833</v>
+        <v>0.1710989694905902</v>
       </c>
       <c r="H92">
-        <v>0.9996</v>
+        <v>0.999197</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="1">
-        <v>46155</v>
+        <v>46185</v>
       </c>
       <c r="B93" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C93">
-        <v>51.8659994471731</v>
+        <v>35.92309284525166</v>
       </c>
       <c r="D93">
-        <v>23.7009037279043</v>
+        <v>22.00037840050582</v>
       </c>
       <c r="E93">
-        <v>1.0002</v>
+        <v>0.99603186</v>
       </c>
       <c r="F93">
-        <v>1.0002</v>
+        <v>0.99603186</v>
       </c>
       <c r="G93">
-        <v>0.533512029714132</v>
+        <v>0.1779905285791235</v>
       </c>
       <c r="H93">
-        <v>1.0002</v>
+        <v>0.99904038</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="1">
-        <v>46156</v>
+        <v>46188</v>
       </c>
       <c r="B94" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C94">
-        <v>52.4470179952828</v>
+        <v>36.41418580189467</v>
       </c>
       <c r="D94">
-        <v>23.76861704536814</v>
+        <v>22.82775744295367</v>
       </c>
       <c r="E94">
-        <v>0.9998</v>
+        <v>0.9961883699999998</v>
       </c>
       <c r="F94">
-        <v>0.9998</v>
+        <v>0.9961883699999998</v>
       </c>
       <c r="G94">
-        <v>0.5492634496849078</v>
+        <v>0.2149955924163247</v>
       </c>
       <c r="H94">
-        <v>0.9998</v>
+        <v>0.9991913599999999</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="1">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="B95" t="s">
         <v>12</v>
       </c>
       <c r="C95">
-        <v>50.81077380018606</v>
+        <v>52.70832779833182</v>
       </c>
       <c r="D95">
-        <v>22.76900580927995</v>
+        <v>23.99044674439659</v>
       </c>
       <c r="E95">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="F95">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
       <c r="G95">
-        <v>0.4903296143797722</v>
+        <v>0.5438253854918791</v>
       </c>
       <c r="H95">
-        <v>0.9998</v>
+        <v>0.9994000000000002</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="1">
-        <v>46160</v>
+        <v>46154</v>
       </c>
       <c r="B96" t="s">
         <v>12</v>
       </c>
       <c r="C96">
-        <v>49.50286387149169</v>
+        <v>50.89464485280568</v>
       </c>
       <c r="D96">
-        <v>22.24532119914133</v>
+        <v>23.21558303176282</v>
       </c>
       <c r="E96">
         <v>0.9996</v>
@@ -2893,7 +2893,7 @@
         <v>0.9996</v>
       </c>
       <c r="G96">
-        <v>0.4630591776162345</v>
+        <v>0.5034825029548833</v>
       </c>
       <c r="H96">
         <v>0.9996</v>
@@ -2901,224 +2901,224 @@
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="1">
-        <v>46161</v>
+        <v>46155</v>
       </c>
       <c r="B97" t="s">
         <v>12</v>
       </c>
       <c r="C97">
-        <v>49.29146729279496</v>
+        <v>51.8659994471731</v>
       </c>
       <c r="D97">
-        <v>22.22167836589682</v>
+        <v>23.7009037279043</v>
       </c>
       <c r="E97">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="F97">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
       <c r="G97">
-        <v>0.4571659248870246</v>
+        <v>0.533512029714132</v>
       </c>
       <c r="H97">
-        <v>0.9998</v>
+        <v>1.0002</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="1">
-        <v>46162</v>
+        <v>46156</v>
       </c>
       <c r="B98" t="s">
         <v>12</v>
       </c>
       <c r="C98">
-        <v>50.88652370817657</v>
+        <v>52.4470179952828</v>
       </c>
       <c r="D98">
-        <v>22.93254398967657</v>
+        <v>23.76861704536814</v>
       </c>
       <c r="E98">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F98">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G98">
-        <v>0.5126171754864624</v>
+        <v>0.5492634496849078</v>
       </c>
       <c r="H98">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="1">
-        <v>46163</v>
+        <v>46157</v>
       </c>
       <c r="B99" t="s">
         <v>12</v>
       </c>
       <c r="C99">
-        <v>48.26646764818586</v>
+        <v>50.81077380018606</v>
       </c>
       <c r="D99">
-        <v>23.11655387625012</v>
+        <v>22.76900580927995</v>
       </c>
       <c r="E99">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="F99">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
       <c r="G99">
-        <v>0.521243030947425</v>
+        <v>0.4903296143797722</v>
       </c>
       <c r="H99">
-        <v>0.9999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="1">
-        <v>46164</v>
+        <v>46160</v>
       </c>
       <c r="B100" t="s">
         <v>12</v>
       </c>
       <c r="C100">
-        <v>48.84737503703267</v>
+        <v>49.50286387149169</v>
       </c>
       <c r="D100">
-        <v>22.83557604744466</v>
+        <v>22.24532119914133</v>
       </c>
       <c r="E100">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="F100">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
       <c r="G100">
-        <v>0.5438521997590966</v>
+        <v>0.4630591776162345</v>
       </c>
       <c r="H100">
-        <v>0.9998999999999999</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="1">
-        <v>46167</v>
+        <v>46161</v>
       </c>
       <c r="B101" t="s">
         <v>12</v>
       </c>
       <c r="C101">
-        <v>48.85151560750146</v>
+        <v>49.29146729279496</v>
       </c>
       <c r="D101">
-        <v>22.83513820206554</v>
+        <v>22.22167836589682</v>
       </c>
       <c r="E101">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F101">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G101">
-        <v>0.5438521997590966</v>
+        <v>0.4571659248870246</v>
       </c>
       <c r="H101">
-        <v>0.9998999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="1">
-        <v>46168</v>
+        <v>46162</v>
       </c>
       <c r="B102" t="s">
         <v>12</v>
       </c>
       <c r="C102">
-        <v>50.90437883274981</v>
+        <v>50.88652370817657</v>
       </c>
       <c r="D102">
-        <v>24.25672473501501</v>
+        <v>22.93254398967657</v>
       </c>
       <c r="E102">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F102">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G102">
-        <v>0.6130191115419561</v>
+        <v>0.5126171754864624</v>
       </c>
       <c r="H102">
-        <v>0.9996999999999999</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="1">
-        <v>46169</v>
+        <v>46163</v>
       </c>
       <c r="B103" t="s">
         <v>12</v>
       </c>
       <c r="C103">
-        <v>50.47312432255841</v>
+        <v>48.26646764818586</v>
       </c>
       <c r="D103">
-        <v>23.84499305142194</v>
+        <v>23.11655387625012</v>
       </c>
       <c r="E103">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="F103">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
       <c r="G103">
-        <v>0.5952317692821967</v>
+        <v>0.521243030947425</v>
       </c>
       <c r="H103">
-        <v>0.9998</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="1">
-        <v>46170</v>
+        <v>46164</v>
       </c>
       <c r="B104" t="s">
         <v>12</v>
       </c>
       <c r="C104">
-        <v>50.84596269629946</v>
+        <v>48.84737503703267</v>
       </c>
       <c r="D104">
-        <v>23.7680603326165</v>
+        <v>22.83557604744466</v>
       </c>
       <c r="E104">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F104">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G104">
-        <v>0.606831065374982</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H104">
-        <v>0.9998</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="1">
-        <v>46171</v>
+        <v>46167</v>
       </c>
       <c r="B105" t="s">
         <v>12</v>
       </c>
       <c r="C105">
-        <v>51.08372269965196</v>
+        <v>48.85151560750146</v>
       </c>
       <c r="D105">
-        <v>23.88880359436525</v>
+        <v>22.83513820206554</v>
       </c>
       <c r="E105">
         <v>0.9998999999999999</v>
@@ -3127,7 +3127,7 @@
         <v>0.9998999999999999</v>
       </c>
       <c r="G105">
-        <v>0.604420070348211</v>
+        <v>0.5438521997590966</v>
       </c>
       <c r="H105">
         <v>0.9998999999999999</v>
@@ -3135,692 +3135,692 @@
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="1">
-        <v>46174</v>
+        <v>46168</v>
       </c>
       <c r="B106" t="s">
         <v>12</v>
       </c>
       <c r="C106">
-        <v>51.84875713649351</v>
+        <v>50.90437883274981</v>
       </c>
       <c r="D106">
-        <v>24.29466650399529</v>
+        <v>24.25672473501501</v>
       </c>
       <c r="E106">
-        <v>0.9998</v>
+        <v>0.9996999999999999</v>
       </c>
       <c r="F106">
-        <v>0.9998</v>
+        <v>0.9996999999999999</v>
       </c>
       <c r="G106">
-        <v>0.6282079224060508</v>
+        <v>0.6130191115419561</v>
       </c>
       <c r="H106">
-        <v>0.9998</v>
+        <v>0.9996999999999999</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="1">
-        <v>46175</v>
+        <v>46169</v>
       </c>
       <c r="B107" t="s">
         <v>12</v>
       </c>
       <c r="C107">
-        <v>53.42858844634741</v>
+        <v>50.47312432255841</v>
       </c>
       <c r="D107">
-        <v>24.82449061140869</v>
+        <v>23.84499305142194</v>
       </c>
       <c r="E107">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="F107">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="G107">
-        <v>0.6935709687814895</v>
+        <v>0.5952317692821967</v>
       </c>
       <c r="H107">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="1">
-        <v>46176</v>
+        <v>46170</v>
       </c>
       <c r="B108" t="s">
         <v>12</v>
       </c>
       <c r="C108">
-        <v>53.95056789686777</v>
+        <v>50.84596269629946</v>
       </c>
       <c r="D108">
-        <v>24.99295077214167</v>
+        <v>23.7680603326165</v>
       </c>
       <c r="E108">
-        <v>0.9996000000000002</v>
+        <v>0.9998</v>
       </c>
       <c r="F108">
-        <v>0.9996000000000002</v>
+        <v>0.9998</v>
       </c>
       <c r="G108">
-        <v>0.7088134081800193</v>
+        <v>0.606831065374982</v>
       </c>
       <c r="H108">
-        <v>0.9996000000000002</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="1">
-        <v>46177</v>
+        <v>46171</v>
       </c>
       <c r="B109" t="s">
         <v>12</v>
       </c>
       <c r="C109">
-        <v>53.29782764127071</v>
+        <v>51.08372269965196</v>
       </c>
       <c r="D109">
-        <v>24.48126483589962</v>
+        <v>23.88880359436525</v>
       </c>
       <c r="E109">
-        <v>1.0001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="F109">
-        <v>1.0001</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="G109">
-        <v>0.6810341543458651</v>
+        <v>0.604420070348211</v>
       </c>
       <c r="H109">
-        <v>1.0001</v>
+        <v>0.9998999999999999</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="1">
-        <v>46178</v>
+        <v>46174</v>
       </c>
       <c r="B110" t="s">
         <v>12</v>
       </c>
       <c r="C110">
-        <v>48.44949949587421</v>
+        <v>51.84875713649351</v>
       </c>
       <c r="D110">
-        <v>22.39103669390088</v>
+        <v>24.29466650399529</v>
       </c>
       <c r="E110">
-        <v>0.9995999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="F110">
-        <v>0.9995999999999999</v>
+        <v>0.9998</v>
       </c>
       <c r="G110">
-        <v>0.5260916717665549</v>
+        <v>0.6282079224060508</v>
       </c>
       <c r="H110">
-        <v>0.9995999999999999</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="1">
-        <v>46182</v>
+        <v>46175</v>
       </c>
       <c r="B111" t="s">
         <v>12</v>
       </c>
       <c r="C111">
-        <v>50.39371086612305</v>
+        <v>53.42858844634741</v>
       </c>
       <c r="D111">
-        <v>23.09650971949351</v>
+        <v>24.82449061140869</v>
       </c>
       <c r="E111">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="F111">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="G111">
-        <v>0.5832039354188183</v>
+        <v>0.6935709687814895</v>
       </c>
       <c r="H111">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="1">
-        <v>46183</v>
+        <v>46176</v>
       </c>
       <c r="B112" t="s">
         <v>12</v>
       </c>
       <c r="C112">
-        <v>48.17343634448468</v>
+        <v>53.95056789686777</v>
       </c>
       <c r="D112">
-        <v>22.05005999539094</v>
+        <v>24.99295077214167</v>
       </c>
       <c r="E112">
-        <v>0.9994999999999999</v>
+        <v>0.9996000000000002</v>
       </c>
       <c r="F112">
-        <v>0.9994999999999999</v>
+        <v>0.9996000000000002</v>
       </c>
       <c r="G112">
-        <v>0.5293597423345122</v>
+        <v>0.7088134081800193</v>
       </c>
       <c r="H112">
-        <v>0.9994999999999999</v>
+        <v>0.9996000000000002</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="1">
-        <v>46184</v>
+        <v>46177</v>
       </c>
       <c r="B113" t="s">
         <v>12</v>
       </c>
       <c r="C113">
-        <v>52.85189183366637</v>
+        <v>53.29782764127071</v>
       </c>
       <c r="D113">
-        <v>23.55442526604671</v>
+        <v>24.48126483589962</v>
       </c>
       <c r="E113">
-        <v>0.9996</v>
+        <v>1.0001</v>
       </c>
       <c r="F113">
-        <v>0.9996</v>
+        <v>1.0001</v>
       </c>
       <c r="G113">
-        <v>0.63260121118737</v>
+        <v>0.6810341543458651</v>
       </c>
       <c r="H113">
-        <v>0.9996</v>
+        <v>1.0001</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="1">
-        <v>46185</v>
+        <v>46178</v>
       </c>
       <c r="B114" t="s">
         <v>12</v>
       </c>
       <c r="C114">
-        <v>52.27613812453644</v>
+        <v>48.44949949587421</v>
       </c>
       <c r="D114">
-        <v>23.80021779840316</v>
+        <v>22.39103669390088</v>
       </c>
       <c r="E114">
-        <v>0.9993999999999998</v>
+        <v>0.9995999999999999</v>
       </c>
       <c r="F114">
-        <v>0.9993999999999998</v>
+        <v>0.9995999999999999</v>
       </c>
       <c r="G114">
-        <v>0.6607555377593115</v>
+        <v>0.5260916717665549</v>
       </c>
       <c r="H114">
-        <v>0.9993999999999998</v>
+        <v>0.9995999999999999</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="1">
-        <v>46153</v>
+        <v>46182</v>
       </c>
       <c r="B115" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C115">
-        <v>57.1732166855686</v>
+        <v>50.39371086612305</v>
       </c>
       <c r="D115">
-        <v>23.50022751267814</v>
+        <v>23.09650971949351</v>
       </c>
       <c r="E115">
-        <v>0.9991</v>
+        <v>0.9997</v>
       </c>
       <c r="F115">
-        <v>0.9991</v>
+        <v>0.9997</v>
       </c>
       <c r="G115">
-        <v>0.6994110097039083</v>
+        <v>0.5832039354188183</v>
       </c>
       <c r="H115">
-        <v>0.9991</v>
+        <v>0.9997</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="1">
-        <v>46154</v>
+        <v>46183</v>
       </c>
       <c r="B116" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C116">
-        <v>54.77380642078597</v>
+        <v>48.17343634448468</v>
       </c>
       <c r="D116">
-        <v>22.55192940254518</v>
+        <v>22.05005999539094</v>
       </c>
       <c r="E116">
-        <v>0.9990000000000001</v>
+        <v>0.9994999999999999</v>
       </c>
       <c r="F116">
-        <v>0.9990000000000001</v>
+        <v>0.9994999999999999</v>
       </c>
       <c r="G116">
-        <v>0.6459175880844941</v>
+        <v>0.5293597423345122</v>
       </c>
       <c r="H116">
-        <v>0.9990000000000001</v>
+        <v>0.9994999999999999</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="1">
-        <v>46155</v>
+        <v>46184</v>
       </c>
       <c r="B117" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C117">
-        <v>56.32187380830906</v>
+        <v>52.85189183366637</v>
       </c>
       <c r="D117">
-        <v>23.17121437414109</v>
+        <v>23.55442526604671</v>
       </c>
       <c r="E117">
-        <v>0.9990000000000001</v>
+        <v>0.9996</v>
       </c>
       <c r="F117">
-        <v>0.9990000000000001</v>
+        <v>0.9996</v>
       </c>
       <c r="G117">
-        <v>0.6851523922954754</v>
+        <v>0.63260121118737</v>
       </c>
       <c r="H117">
-        <v>0.9990000000000001</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="1">
-        <v>46156</v>
+        <v>46185</v>
       </c>
       <c r="B118" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C118">
-        <v>56.15321618553139</v>
+        <v>52.27613812453644</v>
       </c>
       <c r="D118">
-        <v>22.95838347314443</v>
+        <v>23.80021779840316</v>
       </c>
       <c r="E118">
-        <v>0.9992</v>
+        <v>0.9993999999999998</v>
       </c>
       <c r="F118">
-        <v>0.9992</v>
+        <v>0.9993999999999998</v>
       </c>
       <c r="G118">
-        <v>0.6907028507208208</v>
+        <v>0.6607555377593115</v>
       </c>
       <c r="H118">
-        <v>0.9992</v>
+        <v>0.9993999999999998</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="1">
-        <v>46157</v>
+        <v>46188</v>
       </c>
       <c r="B119" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C119">
-        <v>54.47755813049488</v>
+        <v>53.09374842452159</v>
       </c>
       <c r="D119">
-        <v>22.0083816089626</v>
+        <v>25.25230312105937</v>
       </c>
       <c r="E119">
-        <v>0.9986</v>
+        <v>0.9996</v>
       </c>
       <c r="F119">
-        <v>0.9986</v>
+        <v>0.9996</v>
       </c>
       <c r="G119">
-        <v>0.6220895940829376</v>
+        <v>0.7334583357790452</v>
       </c>
       <c r="H119">
-        <v>0.9986</v>
+        <v>0.9996</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B120" t="s">
         <v>13</v>
       </c>
       <c r="C120">
-        <v>52.6278781150669</v>
+        <v>57.1732166855686</v>
       </c>
       <c r="D120">
-        <v>21.5357353870778</v>
+        <v>23.50022751267814</v>
       </c>
       <c r="E120">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F120">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G120">
-        <v>0.5845134636435627</v>
+        <v>0.6994110097039083</v>
       </c>
       <c r="H120">
-        <v>0.9988999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B121" t="s">
         <v>13</v>
       </c>
       <c r="C121">
-        <v>54.91583234840245</v>
+        <v>54.77380642078597</v>
       </c>
       <c r="D121">
-        <v>22.38321645985006</v>
+        <v>22.55192940254518</v>
       </c>
       <c r="E121">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F121">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G121">
-        <v>0.6596976539194066</v>
+        <v>0.6459175880844941</v>
       </c>
       <c r="H121">
-        <v>0.9990999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B122" t="s">
         <v>13</v>
       </c>
       <c r="C122">
-        <v>53.91712298548793</v>
+        <v>56.32187380830906</v>
       </c>
       <c r="D122">
-        <v>22.73711181201267</v>
+        <v>23.17121437414109</v>
       </c>
       <c r="E122">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F122">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G122">
-        <v>0.6737329602396263</v>
+        <v>0.6851523922954754</v>
       </c>
       <c r="H122">
-        <v>0.9991999999999999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="1">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="B123" t="s">
         <v>13</v>
       </c>
       <c r="C123">
-        <v>55.19651747515625</v>
+        <v>56.15321618553139</v>
       </c>
       <c r="D123">
-        <v>22.79462037330554</v>
+        <v>22.95838347314443</v>
       </c>
       <c r="E123">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
       <c r="F123">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
       <c r="G123">
-        <v>0.7139885317003913</v>
+        <v>0.6907028507208208</v>
       </c>
       <c r="H123">
-        <v>0.9991</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="1">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="B124" t="s">
         <v>13</v>
       </c>
       <c r="C124">
-        <v>55.28054997487197</v>
+        <v>54.47755813049488</v>
       </c>
       <c r="D124">
-        <v>23.00160891539877</v>
+        <v>22.0083816089626</v>
       </c>
       <c r="E124">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="F124">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="G124">
-        <v>0.7139885317003913</v>
+        <v>0.6220895940829376</v>
       </c>
       <c r="H124">
-        <v>0.9989000000000001</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="1">
-        <v>46168</v>
+        <v>46161</v>
       </c>
       <c r="B125" t="s">
         <v>13</v>
       </c>
       <c r="C125">
-        <v>58.75156728873073</v>
+        <v>52.6278781150669</v>
       </c>
       <c r="D125">
-        <v>24.84249654093248</v>
+        <v>21.5357353870778</v>
       </c>
       <c r="E125">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="F125">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
       <c r="G125">
-        <v>0.8184872182632257</v>
+        <v>0.5845134636435627</v>
       </c>
       <c r="H125">
-        <v>0.9989000000000001</v>
+        <v>0.9988999999999999</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" s="1">
-        <v>46169</v>
+        <v>46162</v>
       </c>
       <c r="B126" t="s">
         <v>13</v>
       </c>
       <c r="C126">
-        <v>57.86771234337395</v>
+        <v>54.91583234840245</v>
       </c>
       <c r="D126">
-        <v>24.21066615243091</v>
+        <v>22.38321645985006</v>
       </c>
       <c r="E126">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="F126">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
       <c r="G126">
-        <v>0.798997241708943</v>
+        <v>0.6596976539194066</v>
       </c>
       <c r="H126">
-        <v>0.9986999999999999</v>
+        <v>0.9990999999999999</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" s="1">
-        <v>46170</v>
+        <v>46163</v>
       </c>
       <c r="B127" t="s">
         <v>13</v>
       </c>
       <c r="C127">
-        <v>58.18666682631797</v>
+        <v>53.91712298548793</v>
       </c>
       <c r="D127">
-        <v>24.09552344282839</v>
+        <v>22.73711181201267</v>
       </c>
       <c r="E127">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="F127">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
       <c r="G127">
-        <v>0.8165093478664007</v>
+        <v>0.6737329602396263</v>
       </c>
       <c r="H127">
-        <v>0.9991</v>
+        <v>0.9991999999999999</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="1">
-        <v>46171</v>
+        <v>46164</v>
       </c>
       <c r="B128" t="s">
         <v>13</v>
       </c>
       <c r="C128">
-        <v>58.79256019733606</v>
+        <v>55.19651747515625</v>
       </c>
       <c r="D128">
-        <v>24.33854853448823</v>
+        <v>22.79462037330554</v>
       </c>
       <c r="E128">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="F128">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
       <c r="G128">
-        <v>0.8152654642198496</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H128">
-        <v>0.9989999999999999</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="1">
-        <v>46174</v>
+        <v>46167</v>
       </c>
       <c r="B129" t="s">
         <v>13</v>
       </c>
       <c r="C129">
-        <v>58.97156722185718</v>
+        <v>55.28054997487197</v>
       </c>
       <c r="D129">
-        <v>24.48296361348067</v>
+        <v>23.00160891539877</v>
       </c>
       <c r="E129">
-        <v>0.9990000000000001</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="F129">
-        <v>0.9990000000000001</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="G129">
-        <v>0.8243563865851753</v>
+        <v>0.7139885317003913</v>
       </c>
       <c r="H129">
-        <v>0.9990000000000001</v>
+        <v>0.9989000000000001</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" s="1">
-        <v>46175</v>
+        <v>46168</v>
       </c>
       <c r="B130" t="s">
         <v>13</v>
       </c>
       <c r="C130">
-        <v>61.6542902214027</v>
+        <v>58.75156728873073</v>
       </c>
       <c r="D130">
-        <v>25.06517348653028</v>
+        <v>24.84249654093248</v>
       </c>
       <c r="E130">
-        <v>0.9988</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="F130">
-        <v>0.9988</v>
+        <v>0.9989000000000001</v>
       </c>
       <c r="G130">
-        <v>0.9299077697948877</v>
+        <v>0.8184872182632257</v>
       </c>
       <c r="H130">
-        <v>0.9988</v>
+        <v>0.9989000000000001</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" s="1">
-        <v>46176</v>
+        <v>46169</v>
       </c>
       <c r="B131" t="s">
         <v>13</v>
       </c>
       <c r="C131">
-        <v>63.0681947750049</v>
+        <v>57.86771234337395</v>
       </c>
       <c r="D131">
-        <v>25.58770976382014</v>
+        <v>24.21066615243091</v>
       </c>
       <c r="E131">
-        <v>0.9988000000000002</v>
+        <v>0.9986999999999999</v>
       </c>
       <c r="F131">
-        <v>0.9988000000000002</v>
+        <v>0.9986999999999999</v>
       </c>
       <c r="G131">
-        <v>0.9639112148600193</v>
+        <v>0.798997241708943</v>
       </c>
       <c r="H131">
-        <v>0.9988000000000002</v>
+        <v>0.9986999999999999</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="1">
-        <v>46177</v>
+        <v>46170</v>
       </c>
       <c r="B132" t="s">
         <v>13</v>
       </c>
       <c r="C132">
-        <v>61.53154955456358</v>
+        <v>58.18666682631797</v>
       </c>
       <c r="D132">
-        <v>24.75810538712983</v>
+        <v>24.09552344282839</v>
       </c>
       <c r="E132">
         <v>0.9991</v>
@@ -3829,7 +3829,7 @@
         <v>0.9991</v>
       </c>
       <c r="G132">
-        <v>0.9225710173552821</v>
+        <v>0.8165093478664007</v>
       </c>
       <c r="H132">
         <v>0.9991</v>
@@ -3837,1030 +3837,1030 @@
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="1">
-        <v>46178</v>
+        <v>46171</v>
       </c>
       <c r="B133" t="s">
         <v>13</v>
       </c>
       <c r="C133">
-        <v>55.42493637343647</v>
+        <v>58.79256019733606</v>
       </c>
       <c r="D133">
-        <v>22.47054621698377</v>
+        <v>24.33854853448823</v>
       </c>
       <c r="E133">
-        <v>0.9987</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="F133">
-        <v>0.9987</v>
+        <v>0.9989999999999999</v>
       </c>
       <c r="G133">
-        <v>0.7217717116249776</v>
+        <v>0.8152654642198496</v>
       </c>
       <c r="H133">
-        <v>0.9987</v>
+        <v>0.9989999999999999</v>
       </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="1">
-        <v>46182</v>
+        <v>46174</v>
       </c>
       <c r="B134" t="s">
         <v>13</v>
       </c>
       <c r="C134">
-        <v>57.84835101034041</v>
+        <v>58.97156722185718</v>
       </c>
       <c r="D134">
-        <v>23.24662656171655</v>
+        <v>24.48296361348067</v>
       </c>
       <c r="E134">
-        <v>0.999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="F134">
-        <v>0.999</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="G134">
-        <v>0.7931280733869936</v>
+        <v>0.8243563865851753</v>
       </c>
       <c r="H134">
-        <v>0.999</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="1">
-        <v>46183</v>
+        <v>46175</v>
       </c>
       <c r="B135" t="s">
         <v>13</v>
       </c>
       <c r="C135">
-        <v>55.28729760663236</v>
+        <v>61.6542902214027</v>
       </c>
       <c r="D135">
-        <v>22.10409273362112</v>
+        <v>25.06517348653028</v>
       </c>
       <c r="E135">
-        <v>0.9987999999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="F135">
-        <v>0.9987999999999999</v>
+        <v>0.9988</v>
       </c>
       <c r="G135">
-        <v>0.7273219753588771</v>
+        <v>0.9299077697948877</v>
       </c>
       <c r="H135">
-        <v>0.9987999999999999</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="136" spans="1:8">
       <c r="A136" s="1">
-        <v>46184</v>
+        <v>46176</v>
       </c>
       <c r="B136" t="s">
         <v>13</v>
       </c>
       <c r="C136">
-        <v>61.41553176023326</v>
+        <v>63.0681947750049</v>
       </c>
       <c r="D136">
-        <v>23.99650204363438</v>
+        <v>25.58770976382014</v>
       </c>
       <c r="E136">
-        <v>0.9986000000000002</v>
+        <v>0.9988000000000002</v>
       </c>
       <c r="F136">
-        <v>0.9986000000000002</v>
+        <v>0.9988000000000002</v>
       </c>
       <c r="G136">
-        <v>0.8722037562794076</v>
+        <v>0.9639112148600193</v>
       </c>
       <c r="H136">
-        <v>0.9986000000000002</v>
+        <v>0.9988000000000002</v>
       </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="1">
-        <v>46185</v>
+        <v>46177</v>
       </c>
       <c r="B137" t="s">
         <v>13</v>
       </c>
       <c r="C137">
-        <v>60.84374742307179</v>
+        <v>61.53154955456358</v>
       </c>
       <c r="D137">
-        <v>24.14439702225977</v>
+        <v>24.75810538712983</v>
       </c>
       <c r="E137">
-        <v>0.9988000000000001</v>
+        <v>0.9991</v>
       </c>
       <c r="F137">
-        <v>0.9988000000000001</v>
+        <v>0.9991</v>
       </c>
       <c r="G137">
-        <v>0.9019329453457305</v>
+        <v>0.9225710173552821</v>
       </c>
       <c r="H137">
-        <v>0.9988000000000001</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="1">
-        <v>46153</v>
+        <v>46178</v>
       </c>
       <c r="B138" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C138">
-        <v>35.78646526282436</v>
+        <v>55.42493637343647</v>
       </c>
       <c r="D138">
-        <v>18.96635091925032</v>
+        <v>22.47054621698377</v>
       </c>
       <c r="E138">
-        <v>0.9996491399999999</v>
+        <v>0.9987</v>
       </c>
       <c r="F138">
-        <v>0.9996491399999999</v>
+        <v>0.9987</v>
       </c>
       <c r="G138">
-        <v>0.2240600969213613</v>
+        <v>0.7217717116249776</v>
       </c>
       <c r="H138">
-        <v>0.9985614899999999</v>
+        <v>0.9987</v>
       </c>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="1">
-        <v>46154</v>
+        <v>46182</v>
       </c>
       <c r="B139" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C139">
-        <v>35.71584102184062</v>
+        <v>57.84835101034041</v>
       </c>
       <c r="D139">
-        <v>18.62432950231353</v>
+        <v>23.24662656171655</v>
       </c>
       <c r="E139">
-        <v>0.99965481</v>
+        <v>0.999</v>
       </c>
       <c r="F139">
-        <v>0.99965481</v>
+        <v>0.999</v>
       </c>
       <c r="G139">
-        <v>0.2104844827747143</v>
+        <v>0.7931280733869936</v>
       </c>
       <c r="H139">
-        <v>0.9985622199999999</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="1">
-        <v>46155</v>
+        <v>46183</v>
       </c>
       <c r="B140" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C140">
-        <v>35.95182028203252</v>
+        <v>55.28729760663236</v>
       </c>
       <c r="D140">
-        <v>18.95670796791552</v>
+        <v>22.10409273362112</v>
       </c>
       <c r="E140">
-        <v>0.9996515200000001</v>
+        <v>0.9987999999999999</v>
       </c>
       <c r="F140">
-        <v>0.9996515200000001</v>
+        <v>0.9987999999999999</v>
       </c>
       <c r="G140">
-        <v>0.2259035693959275</v>
+        <v>0.7273219753588771</v>
       </c>
       <c r="H140">
-        <v>0.99855193</v>
+        <v>0.9987999999999999</v>
       </c>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="1">
-        <v>46156</v>
+        <v>46184</v>
       </c>
       <c r="B141" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C141">
-        <v>36.14451597805883</v>
+        <v>61.41553176023326</v>
       </c>
       <c r="D141">
-        <v>18.86297660538653</v>
+        <v>23.99650204363438</v>
       </c>
       <c r="E141">
-        <v>0.9996563399999999</v>
+        <v>0.9986000000000002</v>
       </c>
       <c r="F141">
-        <v>0.9996563399999999</v>
+        <v>0.9986000000000002</v>
       </c>
       <c r="G141">
-        <v>0.2362110061840785</v>
+        <v>0.8722037562794076</v>
       </c>
       <c r="H141">
-        <v>0.99857265</v>
+        <v>0.9986000000000002</v>
       </c>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="1">
-        <v>46157</v>
+        <v>46185</v>
       </c>
       <c r="B142" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C142">
-        <v>35.32805803135546</v>
+        <v>60.84374742307179</v>
       </c>
       <c r="D142">
-        <v>18.35643242381478</v>
+        <v>24.14439702225977</v>
       </c>
       <c r="E142">
-        <v>0.9997415800000001</v>
+        <v>0.9988000000000001</v>
       </c>
       <c r="F142">
-        <v>0.9997415800000001</v>
+        <v>0.9988000000000001</v>
       </c>
       <c r="G142">
-        <v>0.2023559161375383</v>
+        <v>0.9019329453457305</v>
       </c>
       <c r="H142">
-        <v>0.9986639900000002</v>
+        <v>0.9988000000000001</v>
       </c>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="1">
-        <v>46160</v>
+        <v>46188</v>
       </c>
       <c r="B143" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C143">
-        <v>34.83995455757461</v>
+        <v>62.28063575842661</v>
       </c>
       <c r="D143">
-        <v>18.02301281718857</v>
+        <v>25.91936377587703</v>
       </c>
       <c r="E143">
-        <v>0.9996851299999999</v>
+        <v>0.9986</v>
       </c>
       <c r="F143">
-        <v>0.9996851299999999</v>
+        <v>0.9986</v>
       </c>
       <c r="G143">
-        <v>0.1850932291737926</v>
+        <v>1.004645337894305</v>
       </c>
       <c r="H143">
-        <v>0.99857724</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="1">
-        <v>46161</v>
+        <v>46153</v>
       </c>
       <c r="B144" t="s">
         <v>14</v>
       </c>
       <c r="C144">
-        <v>34.45479308705605</v>
+        <v>35.78646526282436</v>
       </c>
       <c r="D144">
-        <v>18.09576834566068</v>
+        <v>18.96635091925032</v>
       </c>
       <c r="E144">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="F144">
-        <v>0.9996803099999999</v>
+        <v>0.9996491399999999</v>
       </c>
       <c r="G144">
-        <v>0.1784731209386736</v>
+        <v>0.2240600969213613</v>
       </c>
       <c r="H144">
-        <v>0.9985337599999999</v>
+        <v>0.9985614899999999</v>
       </c>
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="1">
-        <v>46162</v>
+        <v>46154</v>
       </c>
       <c r="B145" t="s">
         <v>14</v>
       </c>
       <c r="C145">
-        <v>34.96336277390787</v>
+        <v>35.71584102184062</v>
       </c>
       <c r="D145">
-        <v>18.34938420029253</v>
+        <v>18.62432950231353</v>
       </c>
       <c r="E145">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="F145">
-        <v>0.99963413</v>
+        <v>0.99965481</v>
       </c>
       <c r="G145">
-        <v>0.2009313391215752</v>
+        <v>0.2104844827747143</v>
       </c>
       <c r="H145">
-        <v>0.99848777</v>
+        <v>0.9985622199999999</v>
       </c>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="1">
-        <v>46163</v>
+        <v>46155</v>
       </c>
       <c r="B146" t="s">
         <v>14</v>
       </c>
       <c r="C146">
-        <v>34.44616924817128</v>
+        <v>35.95182028203252</v>
       </c>
       <c r="D146">
-        <v>18.60085625074367</v>
+        <v>18.95670796791552</v>
       </c>
       <c r="E146">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="F146">
-        <v>0.9996355900000001</v>
+        <v>0.9996515200000001</v>
       </c>
       <c r="G146">
-        <v>0.2124957180214682</v>
+        <v>0.2259035693959275</v>
       </c>
       <c r="H146">
-        <v>0.9985085200000001</v>
+        <v>0.99855193</v>
       </c>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="1">
-        <v>46164</v>
+        <v>46156</v>
       </c>
       <c r="B147" t="s">
         <v>14</v>
       </c>
       <c r="C147">
-        <v>34.62137220937314</v>
+        <v>36.14451597805883</v>
       </c>
       <c r="D147">
-        <v>18.28780484745949</v>
+        <v>18.86297660538653</v>
       </c>
       <c r="E147">
-        <v>0.9996106299999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="F147">
-        <v>0.9996106299999999</v>
+        <v>0.9996563399999999</v>
       </c>
       <c r="G147">
-        <v>0.2145907067863493</v>
+        <v>0.2362110061840785</v>
       </c>
       <c r="H147">
-        <v>0.9932939299999999</v>
+        <v>0.99857265</v>
       </c>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="1">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="B148" t="s">
         <v>14</v>
       </c>
       <c r="C148">
-        <v>34.6540695486741</v>
+        <v>35.32805803135546</v>
       </c>
       <c r="D148">
-        <v>18.36409048915342</v>
+        <v>18.35643242381478</v>
       </c>
       <c r="E148">
-        <v>0.9995448900000001</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="F148">
-        <v>0.9995448900000001</v>
+        <v>0.9997415800000001</v>
       </c>
       <c r="G148">
-        <v>0.2145907067863493</v>
+        <v>0.2023559161375383</v>
       </c>
       <c r="H148">
-        <v>0.9984302600000001</v>
+        <v>0.9986639900000002</v>
       </c>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="1">
-        <v>46168</v>
+        <v>46160</v>
       </c>
       <c r="B149" t="s">
         <v>14</v>
       </c>
       <c r="C149">
-        <v>35.4820130509417</v>
+        <v>34.83995455757461</v>
       </c>
       <c r="D149">
-        <v>19.20292041814603</v>
+        <v>18.02301281718857</v>
       </c>
       <c r="E149">
-        <v>0.9995448900000001</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="F149">
-        <v>0.9995448900000001</v>
+        <v>0.9996851299999999</v>
       </c>
       <c r="G149">
-        <v>0.2553172934903569</v>
+        <v>0.1850932291737926</v>
       </c>
       <c r="H149">
-        <v>0.9984302600000001</v>
+        <v>0.99857724</v>
       </c>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" s="1">
-        <v>46169</v>
+        <v>46161</v>
       </c>
       <c r="B150" t="s">
         <v>14</v>
       </c>
       <c r="C150">
-        <v>35.71913468603401</v>
+        <v>34.45479308705605</v>
       </c>
       <c r="D150">
-        <v>18.96318693998171</v>
+        <v>18.09576834566068</v>
       </c>
       <c r="E150">
-        <v>0.99955466</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="F150">
-        <v>0.99955466</v>
+        <v>0.9996803099999999</v>
       </c>
       <c r="G150">
-        <v>0.2536413280520453</v>
+        <v>0.1784731209386736</v>
       </c>
       <c r="H150">
-        <v>0.9984700500000001</v>
+        <v>0.9985337599999999</v>
       </c>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="1">
-        <v>46170</v>
+        <v>46162</v>
       </c>
       <c r="B151" t="s">
         <v>14</v>
       </c>
       <c r="C151">
-        <v>35.76226417354731</v>
+        <v>34.96336277390787</v>
       </c>
       <c r="D151">
-        <v>18.89050847207122</v>
+        <v>18.34938420029253</v>
       </c>
       <c r="E151">
-        <v>0.9995525399999999</v>
+        <v>0.99963413</v>
       </c>
       <c r="F151">
-        <v>0.9995525399999999</v>
+        <v>0.99963413</v>
       </c>
       <c r="G151">
-        <v>0.2580826940041561</v>
+        <v>0.2009313391215752</v>
       </c>
       <c r="H151">
-        <v>0.99847732</v>
+        <v>0.99848777</v>
       </c>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="1">
-        <v>46171</v>
+        <v>46163</v>
       </c>
       <c r="B152" t="s">
         <v>14</v>
       </c>
       <c r="C152">
-        <v>35.84309020154227</v>
+        <v>34.44616924817128</v>
       </c>
       <c r="D152">
-        <v>19.06511612333149</v>
+        <v>18.60085625074367</v>
       </c>
       <c r="E152">
-        <v>0.9995533299999999</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="F152">
-        <v>0.9995533299999999</v>
+        <v>0.9996355900000001</v>
       </c>
       <c r="G152">
-        <v>0.2619374017254759</v>
+        <v>0.2124957180214682</v>
       </c>
       <c r="H152">
-        <v>0.99849382</v>
+        <v>0.9985085200000001</v>
       </c>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" s="1">
-        <v>46174</v>
+        <v>46164</v>
       </c>
       <c r="B153" t="s">
         <v>14</v>
       </c>
       <c r="C153">
-        <v>36.27022125574057</v>
+        <v>34.62137220937314</v>
       </c>
       <c r="D153">
-        <v>19.32711369104533</v>
+        <v>18.28780484745949</v>
       </c>
       <c r="E153">
-        <v>0.9995550400000001</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="F153">
-        <v>0.9995550400000001</v>
+        <v>0.9996106299999999</v>
       </c>
       <c r="G153">
-        <v>0.2764348160433892</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H153">
-        <v>0.9985177199999999</v>
+        <v>0.9932939299999999</v>
       </c>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" s="1">
-        <v>46175</v>
+        <v>46167</v>
       </c>
       <c r="B154" t="s">
         <v>14</v>
       </c>
       <c r="C154">
-        <v>36.57133692946976</v>
+        <v>34.6540695486741</v>
       </c>
       <c r="D154">
-        <v>19.33857330565742</v>
+        <v>18.36409048915342</v>
       </c>
       <c r="E154">
-        <v>0.9994989200000002</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="F154">
-        <v>0.9994989200000002</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="G154">
-        <v>0.2931947261624381</v>
+        <v>0.2145907067863493</v>
       </c>
       <c r="H154">
-        <v>0.9984577800000001</v>
+        <v>0.9984302600000001</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" s="1">
-        <v>46176</v>
+        <v>46168</v>
       </c>
       <c r="B155" t="s">
         <v>14</v>
       </c>
       <c r="C155">
-        <v>36.8289666508657</v>
+        <v>35.4820130509417</v>
       </c>
       <c r="D155">
-        <v>19.43137154505686</v>
+        <v>19.20292041814603</v>
       </c>
       <c r="E155">
-        <v>0.9994838199999998</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="F155">
-        <v>0.9994838199999998</v>
+        <v>0.9995448900000001</v>
       </c>
       <c r="G155">
-        <v>0.2996471994933361</v>
+        <v>0.2553172934903569</v>
       </c>
       <c r="H155">
-        <v>0.9984549499999998</v>
+        <v>0.9984302600000001</v>
       </c>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" s="1">
-        <v>46177</v>
+        <v>46169</v>
       </c>
       <c r="B156" t="s">
         <v>14</v>
       </c>
       <c r="C156">
-        <v>36.76760036565858</v>
+        <v>35.71913468603401</v>
       </c>
       <c r="D156">
-        <v>18.98774474764188</v>
+        <v>18.96318693998171</v>
       </c>
       <c r="E156">
-        <v>0.99948384</v>
+        <v>0.99955466</v>
       </c>
       <c r="F156">
-        <v>0.99948384</v>
+        <v>0.99955466</v>
       </c>
       <c r="G156">
-        <v>0.2807085470912787</v>
+        <v>0.2536413280520453</v>
       </c>
       <c r="H156">
-        <v>0.9984696899999999</v>
+        <v>0.9984700500000001</v>
       </c>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" s="1">
-        <v>46178</v>
+        <v>46170</v>
       </c>
       <c r="B157" t="s">
         <v>14</v>
       </c>
       <c r="C157">
-        <v>34.71533981972338</v>
+        <v>35.76226417354731</v>
       </c>
       <c r="D157">
-        <v>17.87291658642534</v>
+        <v>18.89050847207122</v>
       </c>
       <c r="E157">
-        <v>0.9994584900000001</v>
+        <v>0.9995525399999999</v>
       </c>
       <c r="F157">
-        <v>0.9994584900000001</v>
+        <v>0.9995525399999999</v>
       </c>
       <c r="G157">
-        <v>0.2090599057587512</v>
+        <v>0.2580826940041561</v>
       </c>
       <c r="H157">
-        <v>0.9984184600000001</v>
+        <v>0.99847732</v>
       </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="1">
-        <v>46182</v>
+        <v>46171</v>
       </c>
       <c r="B158" t="s">
         <v>14</v>
       </c>
       <c r="C158">
-        <v>35.03764279648938</v>
+        <v>35.84309020154227</v>
       </c>
       <c r="D158">
-        <v>18.26945792236365</v>
+        <v>19.06511612333149</v>
       </c>
       <c r="E158">
-        <v>0.9994212399999999</v>
+        <v>0.9995533299999999</v>
       </c>
       <c r="F158">
-        <v>0.9994212399999999</v>
+        <v>0.9995533299999999</v>
       </c>
       <c r="G158">
-        <v>0.2361271247979846</v>
+        <v>0.2619374017254759</v>
       </c>
       <c r="H158">
-        <v>0.99833116</v>
+        <v>0.99849382</v>
       </c>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" s="1">
-        <v>46183</v>
+        <v>46174</v>
       </c>
       <c r="B159" t="s">
         <v>14</v>
       </c>
       <c r="C159">
-        <v>34.21862503455022</v>
+        <v>36.27022125574057</v>
       </c>
       <c r="D159">
-        <v>17.67576313213109</v>
+        <v>19.32711369104533</v>
       </c>
       <c r="E159">
-        <v>0.9991916599999998</v>
+        <v>0.9995550400000001</v>
       </c>
       <c r="F159">
-        <v>0.9991916599999998</v>
+        <v>0.9995550400000001</v>
       </c>
       <c r="G159">
-        <v>0.2040318815758499</v>
+        <v>0.2764348160433892</v>
       </c>
       <c r="H159">
-        <v>0.99808951</v>
+        <v>0.9985177199999999</v>
       </c>
     </row>
     <row r="160" spans="1:8">
       <c r="A160" s="1">
-        <v>46184</v>
+        <v>46175</v>
       </c>
       <c r="B160" t="s">
         <v>14</v>
       </c>
       <c r="C160">
-        <v>35.57723814348832</v>
+        <v>36.57133692946976</v>
       </c>
       <c r="D160">
-        <v>18.6194204925492</v>
+        <v>19.33857330565742</v>
       </c>
       <c r="E160">
-        <v>0.9989294799999999</v>
+        <v>0.9994989200000002</v>
       </c>
       <c r="F160">
-        <v>0.9989294799999999</v>
+        <v>0.9994989200000002</v>
       </c>
       <c r="G160">
-        <v>0.2618536482073486</v>
+        <v>0.2931947261624381</v>
       </c>
       <c r="H160">
-        <v>0.9977895699999999</v>
+        <v>0.9984577800000001</v>
       </c>
     </row>
     <row r="161" spans="1:8">
       <c r="A161" s="1">
-        <v>46185</v>
+        <v>46176</v>
       </c>
       <c r="B161" t="s">
         <v>14</v>
       </c>
       <c r="C161">
-        <v>36.1035128450924</v>
+        <v>36.8289666508657</v>
       </c>
       <c r="D161">
-        <v>18.65667517843299</v>
+        <v>19.43137154505686</v>
       </c>
       <c r="E161">
-        <v>0.9988909800000001</v>
+        <v>0.9994838199999998</v>
       </c>
       <c r="F161">
-        <v>0.9988909800000001</v>
+        <v>0.9994838199999998</v>
       </c>
       <c r="G161">
-        <v>0.2777755116732585</v>
+        <v>0.2996471994933361</v>
       </c>
       <c r="H161">
-        <v>0.9978056500000002</v>
+        <v>0.9984549499999998</v>
       </c>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" s="1">
-        <v>46153</v>
+        <v>46177</v>
       </c>
       <c r="B162" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C162">
-        <v>28.12253390077671</v>
+        <v>36.76760036565858</v>
       </c>
       <c r="D162">
-        <v>23.58699683751922</v>
+        <v>18.98774474764188</v>
       </c>
       <c r="E162">
-        <v>0.9997295369999999</v>
+        <v>0.99948384</v>
       </c>
       <c r="F162">
-        <v>0.9997295369999999</v>
+        <v>0.99948384</v>
       </c>
       <c r="G162">
-        <v>0.03368732240295347</v>
+        <v>0.2807085470912787</v>
       </c>
       <c r="H162">
-        <v>0.9997295369999999</v>
+        <v>0.9984696899999999</v>
       </c>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" s="1">
-        <v>46154</v>
+        <v>46178</v>
       </c>
       <c r="B163" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C163">
-        <v>28.17715727830483</v>
+        <v>34.71533981972338</v>
       </c>
       <c r="D163">
-        <v>23.63894513078866</v>
+        <v>17.87291658642534</v>
       </c>
       <c r="E163">
-        <v>1.000319473</v>
+        <v>0.9994584900000001</v>
       </c>
       <c r="F163">
-        <v>1.000319473</v>
+        <v>0.9994584900000001</v>
       </c>
       <c r="G163">
-        <v>0.03515547182056333</v>
+        <v>0.2090599057587512</v>
       </c>
       <c r="H163">
-        <v>1.000319473</v>
+        <v>0.9984184600000001</v>
       </c>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" s="1">
-        <v>46155</v>
+        <v>46182</v>
       </c>
       <c r="B164" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C164">
-        <v>28.59002627414054</v>
+        <v>35.03764279648938</v>
       </c>
       <c r="D164">
-        <v>23.96230704059692</v>
+        <v>18.26945792236365</v>
       </c>
       <c r="E164">
-        <v>0.9999999989999999</v>
+        <v>0.9994212399999999</v>
       </c>
       <c r="F164">
-        <v>0.9999999989999999</v>
+        <v>0.9994212399999999</v>
       </c>
       <c r="G164">
-        <v>0.05179637495949674</v>
+        <v>0.2361271247979846</v>
       </c>
       <c r="H164">
-        <v>0.9999999989999999</v>
+        <v>0.99833116</v>
       </c>
     </row>
     <row r="165" spans="1:8">
       <c r="A165" s="1">
-        <v>46156</v>
+        <v>46183</v>
       </c>
       <c r="B165" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C165">
-        <v>28.56217859389523</v>
+        <v>34.21862503455022</v>
       </c>
       <c r="D165">
-        <v>23.9411987302529</v>
+        <v>17.67576313213109</v>
       </c>
       <c r="E165">
-        <v>1</v>
+        <v>0.9991916599999998</v>
       </c>
       <c r="F165">
-        <v>1</v>
+        <v>0.9991916599999998</v>
       </c>
       <c r="G165">
-        <v>0.04837024516756849</v>
+        <v>0.2040318815758499</v>
       </c>
       <c r="H165">
-        <v>1</v>
+        <v>0.99808951</v>
       </c>
     </row>
     <row r="166" spans="1:8">
       <c r="A166" s="1">
-        <v>46157</v>
+        <v>46184</v>
       </c>
       <c r="B166" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C166">
-        <v>28.57618675936338</v>
+        <v>35.57723814348832</v>
       </c>
       <c r="D166">
-        <v>23.9576220541054</v>
+        <v>18.6194204925492</v>
       </c>
       <c r="E166">
-        <v>0.999503249</v>
+        <v>0.9989294799999999</v>
       </c>
       <c r="F166">
-        <v>0.999503249</v>
+        <v>0.9989294799999999</v>
       </c>
       <c r="G166">
-        <v>0.04983868243960732</v>
+        <v>0.2618536482073486</v>
       </c>
       <c r="H166">
-        <v>0.999503249</v>
+        <v>0.9977895699999999</v>
       </c>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" s="1">
-        <v>46160</v>
+        <v>46185</v>
       </c>
       <c r="B167" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C167">
-        <v>28.68951918518517</v>
+        <v>36.1035128450924</v>
       </c>
       <c r="D167">
-        <v>24.06134728453882</v>
+        <v>18.65667517843299</v>
       </c>
       <c r="E167">
-        <v>0.999503249</v>
+        <v>0.9988909800000001</v>
       </c>
       <c r="F167">
-        <v>0.999503249</v>
+        <v>0.9988909800000001</v>
       </c>
       <c r="G167">
-        <v>0.04983868243960732</v>
+        <v>0.2777755116732585</v>
       </c>
       <c r="H167">
-        <v>0.999503249</v>
+        <v>0.9978056500000002</v>
       </c>
     </row>
     <row r="168" spans="1:8">
       <c r="A168" s="1">
-        <v>46161</v>
+        <v>46188</v>
       </c>
       <c r="B168" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C168">
-        <v>28.31167386654059</v>
+        <v>36.38577501752614</v>
       </c>
       <c r="D168">
-        <v>23.75157719455474</v>
+        <v>19.49200979016929</v>
       </c>
       <c r="E168">
-        <v>1.000177331</v>
+        <v>0.99898177</v>
       </c>
       <c r="F168">
-        <v>1.000177331</v>
+        <v>0.99898177</v>
       </c>
       <c r="G168">
-        <v>0.04053938625111919</v>
+        <v>0.3226920759070282</v>
       </c>
       <c r="H168">
-        <v>1.000177331</v>
+        <v>0.9979181100000001</v>
       </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" s="1">
-        <v>46162</v>
+        <v>46153</v>
       </c>
       <c r="B169" t="s">
         <v>15</v>
       </c>
       <c r="C169">
-        <v>28.57911382310097</v>
+        <v>28.12253390077671</v>
       </c>
       <c r="D169">
-        <v>23.89431741541233</v>
+        <v>23.58699683751922</v>
       </c>
       <c r="E169">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="F169">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
       <c r="G169">
-        <v>0.04690190590044785</v>
+        <v>0.03368732240295347</v>
       </c>
       <c r="H169">
-        <v>0.999503734</v>
+        <v>0.9997295369999999</v>
       </c>
     </row>
     <row r="170" spans="1:8">
       <c r="A170" s="1">
-        <v>46163</v>
+        <v>46154</v>
       </c>
       <c r="B170" t="s">
         <v>15</v>
       </c>
       <c r="C170">
-        <v>28.55785065378643</v>
+        <v>28.17715727830483</v>
       </c>
       <c r="D170">
-        <v>24.04274714970193</v>
+        <v>23.63894513078866</v>
       </c>
       <c r="E170">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="F170">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
       <c r="G170">
-        <v>0.05228572319419666</v>
+        <v>0.03515547182056333</v>
       </c>
       <c r="H170">
-        <v>1.000229282</v>
+        <v>1.000319473</v>
       </c>
     </row>
     <row r="171" spans="1:8">
       <c r="A171" s="1">
-        <v>46164</v>
+        <v>46155</v>
       </c>
       <c r="B171" t="s">
         <v>15</v>
       </c>
       <c r="C171">
-        <v>28.50194638163107</v>
+        <v>28.59002627414054</v>
       </c>
       <c r="D171">
-        <v>23.99272397156045</v>
+        <v>23.96230704059692</v>
       </c>
       <c r="E171">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F171">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G171">
-        <v>0.04934923597154284</v>
+        <v>0.05179637495949674</v>
       </c>
       <c r="H171">
-        <v>1</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="172" spans="1:8">
       <c r="A172" s="1">
-        <v>46167</v>
+        <v>46156</v>
       </c>
       <c r="B172" t="s">
         <v>15</v>
       </c>
       <c r="C172">
-        <v>28.55106858744498</v>
+        <v>28.56217859389523</v>
       </c>
       <c r="D172">
-        <v>23.9768329565351</v>
+        <v>23.9411987302529</v>
       </c>
       <c r="E172">
         <v>1</v>
@@ -4869,7 +4869,7 @@
         <v>1</v>
       </c>
       <c r="G172">
-        <v>0.05571185335164408</v>
+        <v>0.04837024516756849</v>
       </c>
       <c r="H172">
         <v>1</v>
@@ -4877,964 +4877,1198 @@
     </row>
     <row r="173" spans="1:8">
       <c r="A173" s="1">
-        <v>46168</v>
+        <v>46157</v>
       </c>
       <c r="B173" t="s">
         <v>15</v>
       </c>
       <c r="C173">
-        <v>28.54681541456266</v>
+        <v>28.57618675936338</v>
       </c>
       <c r="D173">
-        <v>23.97386168967948</v>
+        <v>23.9576220541054</v>
       </c>
       <c r="E173">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="F173">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="G173">
-        <v>0.04837034303541388</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H173">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="174" spans="1:8">
       <c r="A174" s="1">
-        <v>46169</v>
+        <v>46160</v>
       </c>
       <c r="B174" t="s">
         <v>15</v>
       </c>
       <c r="C174">
-        <v>28.83672936868491</v>
+        <v>28.68951918518517</v>
       </c>
       <c r="D174">
-        <v>24.203511281145</v>
+        <v>24.06134728453882</v>
       </c>
       <c r="E174">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="F174">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
       <c r="G174">
-        <v>0.05962723282507953</v>
+        <v>0.04983868243960732</v>
       </c>
       <c r="H174">
-        <v>1</v>
+        <v>0.999503249</v>
       </c>
     </row>
     <row r="175" spans="1:8">
       <c r="A175" s="1">
-        <v>46170</v>
+        <v>46161</v>
       </c>
       <c r="B175" t="s">
         <v>15</v>
       </c>
       <c r="C175">
-        <v>28.88109630394224</v>
+        <v>28.31167386654059</v>
       </c>
       <c r="D175">
-        <v>24.34085451035401</v>
+        <v>23.75157719455474</v>
       </c>
       <c r="E175">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
       <c r="F175">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
       <c r="G175">
-        <v>0.06647938938594877</v>
+        <v>0.04053938625111919</v>
       </c>
       <c r="H175">
-        <v>0.9999999999999999</v>
+        <v>1.000177331</v>
       </c>
     </row>
     <row r="176" spans="1:8">
       <c r="A176" s="1">
-        <v>46171</v>
+        <v>46162</v>
       </c>
       <c r="B176" t="s">
         <v>15</v>
       </c>
       <c r="C176">
-        <v>28.92588622185229</v>
+        <v>28.57911382310097</v>
       </c>
       <c r="D176">
-        <v>24.37463012178961</v>
+        <v>23.89431741541233</v>
       </c>
       <c r="E176">
-        <v>0.9999999989999999</v>
+        <v>0.999503734</v>
       </c>
       <c r="F176">
-        <v>0.9999999989999999</v>
+        <v>0.999503734</v>
       </c>
       <c r="G176">
-        <v>0.0669687424559624</v>
+        <v>0.04690190590044785</v>
       </c>
       <c r="H176">
-        <v>0.9999999989999999</v>
+        <v>0.999503734</v>
       </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177" s="1">
-        <v>46174</v>
+        <v>46163</v>
       </c>
       <c r="B177" t="s">
         <v>15</v>
       </c>
       <c r="C177">
-        <v>28.479823472488</v>
+        <v>28.55785065378643</v>
       </c>
       <c r="D177">
-        <v>23.940843604634</v>
+        <v>24.04274714970193</v>
       </c>
       <c r="E177">
-        <v>0.9999999999999999</v>
+        <v>1.000229282</v>
       </c>
       <c r="F177">
-        <v>0.9999999999999999</v>
+        <v>1.000229282</v>
       </c>
       <c r="G177">
-        <v>0.05385076946675693</v>
+        <v>0.05228572319419666</v>
       </c>
       <c r="H177">
-        <v>0.9999999999999999</v>
+        <v>1.000229282</v>
       </c>
     </row>
     <row r="178" spans="1:8">
       <c r="A178" s="1">
-        <v>46175</v>
+        <v>46164</v>
       </c>
       <c r="B178" t="s">
         <v>15</v>
       </c>
       <c r="C178">
-        <v>28.11501250979268</v>
+        <v>28.50194638163107</v>
       </c>
       <c r="D178">
-        <v>23.53470929078268</v>
+        <v>23.99272397156045</v>
       </c>
       <c r="E178">
-        <v>0.9999999989999999</v>
+        <v>1</v>
       </c>
       <c r="F178">
-        <v>0.9999999989999999</v>
+        <v>1</v>
       </c>
       <c r="G178">
-        <v>0.03476107722835287</v>
+        <v>0.04934923597154284</v>
       </c>
       <c r="H178">
-        <v>0.9999999989999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179" spans="1:8">
       <c r="A179" s="1">
-        <v>46176</v>
+        <v>46167</v>
       </c>
       <c r="B179" t="s">
         <v>15</v>
       </c>
       <c r="C179">
-        <v>28.0115884668485</v>
+        <v>28.55106858744498</v>
       </c>
       <c r="D179">
-        <v>23.38620815625822</v>
+        <v>23.9768329565351</v>
       </c>
       <c r="E179">
-        <v>0.9993115890000001</v>
+        <v>1</v>
       </c>
       <c r="F179">
-        <v>0.9993115890000001</v>
+        <v>1</v>
       </c>
       <c r="G179">
-        <v>0.02105569185214828</v>
+        <v>0.05571185335164408</v>
       </c>
       <c r="H179">
-        <v>0.9993115890000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180" spans="1:8">
       <c r="A180" s="1">
-        <v>46177</v>
+        <v>46168</v>
       </c>
       <c r="B180" t="s">
         <v>15</v>
       </c>
       <c r="C180">
-        <v>28.38208530418455</v>
+        <v>28.54681541456266</v>
       </c>
       <c r="D180">
-        <v>23.57230416238753</v>
+        <v>23.97386168967948</v>
       </c>
       <c r="E180">
-        <v>1.000774061</v>
+        <v>1</v>
       </c>
       <c r="F180">
-        <v>1.000774061</v>
+        <v>1</v>
       </c>
       <c r="G180">
-        <v>0.03133473088430172</v>
+        <v>0.04837034303541388</v>
       </c>
       <c r="H180">
-        <v>1.000774061</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181" spans="1:8">
       <c r="A181" s="1">
-        <v>46178</v>
+        <v>46169</v>
       </c>
       <c r="B181" t="s">
         <v>15</v>
       </c>
       <c r="C181">
-        <v>27.67379569436247</v>
+        <v>28.83672936868491</v>
       </c>
       <c r="D181">
-        <v>23.02577481291606</v>
+        <v>24.203511281145</v>
       </c>
       <c r="E181">
-        <v>1.000106056</v>
+        <v>1</v>
       </c>
       <c r="F181">
-        <v>1.000106056</v>
+        <v>1</v>
       </c>
       <c r="G181">
-        <v>0.01248973263108488</v>
+        <v>0.05962723282507953</v>
       </c>
       <c r="H181">
-        <v>1.000106056</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182" spans="1:8">
       <c r="A182" s="1">
-        <v>46182</v>
+        <v>46170</v>
       </c>
       <c r="B182" t="s">
         <v>15</v>
       </c>
       <c r="C182">
-        <v>27.45237632057606</v>
+        <v>28.88109630394224</v>
       </c>
       <c r="D182">
-        <v>22.58943922039682</v>
+        <v>24.34085451035401</v>
       </c>
       <c r="E182">
-        <v>0.9999738310000001</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F182">
-        <v>0.9999738310000001</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G182">
-        <v>-0.01076068709534461</v>
+        <v>0.06647938938594877</v>
       </c>
       <c r="H182">
-        <v>0.9999738310000001</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="183" spans="1:8">
       <c r="A183" s="1">
-        <v>46183</v>
+        <v>46171</v>
       </c>
       <c r="B183" t="s">
         <v>15</v>
       </c>
       <c r="C183">
-        <v>26.87898580194432</v>
+        <v>28.92588622185229</v>
       </c>
       <c r="D183">
-        <v>22.24994492425726</v>
+        <v>24.37463012178961</v>
       </c>
       <c r="E183">
-        <v>1.000000001</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F183">
-        <v>1.000000001</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G183">
-        <v>-0.02299778174457945</v>
+        <v>0.0669687424559624</v>
       </c>
       <c r="H183">
-        <v>1.000000001</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="184" spans="1:8">
       <c r="A184" s="1">
-        <v>46184</v>
+        <v>46174</v>
       </c>
       <c r="B184" t="s">
         <v>15</v>
       </c>
       <c r="C184">
-        <v>26.963842509069</v>
+        <v>28.479823472488</v>
       </c>
       <c r="D184">
-        <v>22.26031265264148</v>
+        <v>23.940843604634</v>
       </c>
       <c r="E184">
-        <v>0.9996853900000001</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F184">
-        <v>0.9996853900000001</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="G184">
-        <v>-0.02299759931689671</v>
+        <v>0.05385076946675693</v>
       </c>
       <c r="H184">
-        <v>0.9996853900000001</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="185" spans="1:8">
       <c r="A185" s="1">
-        <v>46185</v>
+        <v>46175</v>
       </c>
       <c r="B185" t="s">
         <v>15</v>
       </c>
       <c r="C185">
-        <v>26.83840329983722</v>
+        <v>28.11501250979268</v>
       </c>
       <c r="D185">
-        <v>22.18026196156466</v>
+        <v>23.53470929078268</v>
       </c>
       <c r="E185">
-        <v>1.000030945</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="F185">
-        <v>1.000030945</v>
+        <v>0.9999999989999999</v>
       </c>
       <c r="G185">
-        <v>-0.02985038257907502</v>
+        <v>0.03476107722835287</v>
       </c>
       <c r="H185">
-        <v>1.000030945</v>
+        <v>0.9999999989999999</v>
       </c>
     </row>
     <row r="186" spans="1:8">
       <c r="A186" s="1">
-        <v>46153</v>
+        <v>46176</v>
       </c>
       <c r="B186" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C186">
-        <v>40.68830633303975</v>
+        <v>28.0115884668485</v>
       </c>
       <c r="D186">
-        <v>21.50431773660198</v>
+        <v>23.38620815625822</v>
       </c>
       <c r="E186">
-        <v>0.99909852</v>
+        <v>0.9993115890000001</v>
       </c>
       <c r="F186">
-        <v>0.99909852</v>
+        <v>0.9993115890000001</v>
       </c>
       <c r="G186">
-        <v>0.2342423866086769</v>
+        <v>0.02105569185214828</v>
       </c>
       <c r="H186">
-        <v>0.9974930900000001</v>
+        <v>0.9993115890000001</v>
       </c>
     </row>
     <row r="187" spans="1:8">
       <c r="A187" s="1">
-        <v>46154</v>
+        <v>46177</v>
       </c>
       <c r="B187" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C187">
-        <v>40.32854894972581</v>
+        <v>28.38208530418455</v>
       </c>
       <c r="D187">
-        <v>21.09133998298594</v>
+        <v>23.57230416238753</v>
       </c>
       <c r="E187">
-        <v>0.9990972199999999</v>
+        <v>1.000774061</v>
       </c>
       <c r="F187">
-        <v>0.9990972199999999</v>
+        <v>1.000774061</v>
       </c>
       <c r="G187">
-        <v>0.2156468205051487</v>
+        <v>0.03133473088430172</v>
       </c>
       <c r="H187">
-        <v>0.99752223</v>
+        <v>1.000774061</v>
       </c>
     </row>
     <row r="188" spans="1:8">
       <c r="A188" s="1">
-        <v>46155</v>
+        <v>46178</v>
       </c>
       <c r="B188" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C188">
-        <v>40.47987921095815</v>
+        <v>27.67379569436247</v>
       </c>
       <c r="D188">
-        <v>21.35995364434454</v>
+        <v>23.02577481291606</v>
       </c>
       <c r="E188">
-        <v>0.9991780100000001</v>
+        <v>1.000106056</v>
       </c>
       <c r="F188">
-        <v>0.9991780100000001</v>
+        <v>1.000106056</v>
       </c>
       <c r="G188">
-        <v>0.2270956128473374</v>
+        <v>0.01248973263108488</v>
       </c>
       <c r="H188">
-        <v>0.9975825700000001</v>
+        <v>1.000106056</v>
       </c>
     </row>
     <row r="189" spans="1:8">
       <c r="A189" s="1">
-        <v>46156</v>
+        <v>46182</v>
       </c>
       <c r="B189" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C189">
-        <v>41.20436574895244</v>
+        <v>27.45237632057606</v>
       </c>
       <c r="D189">
-        <v>21.48149674387778</v>
+        <v>22.58943922039682</v>
       </c>
       <c r="E189">
-        <v>0.9991793299999999</v>
+        <v>0.9999738310000001</v>
       </c>
       <c r="F189">
-        <v>0.9991793299999999</v>
+        <v>0.9999738310000001</v>
       </c>
       <c r="G189">
-        <v>0.2454829228401052</v>
+        <v>-0.01076068709534461</v>
       </c>
       <c r="H189">
-        <v>0.99754722</v>
+        <v>0.9999738310000001</v>
       </c>
     </row>
     <row r="190" spans="1:8">
       <c r="A190" s="1">
-        <v>46157</v>
+        <v>46183</v>
       </c>
       <c r="B190" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C190">
-        <v>40.80613062958688</v>
+        <v>26.87898580194432</v>
       </c>
       <c r="D190">
-        <v>21.08912555803936</v>
+        <v>22.24994492425726</v>
       </c>
       <c r="E190">
-        <v>0.9991790600000001</v>
+        <v>1.000000001</v>
       </c>
       <c r="F190">
-        <v>0.9991790600000001</v>
+        <v>1.000000001</v>
       </c>
       <c r="G190">
-        <v>0.2230017445022556</v>
+        <v>-0.02299778174457945</v>
       </c>
       <c r="H190">
-        <v>0.9975824700000002</v>
+        <v>1.000000001</v>
       </c>
     </row>
     <row r="191" spans="1:8">
       <c r="A191" s="1">
-        <v>46160</v>
+        <v>46184</v>
       </c>
       <c r="B191" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C191">
-        <v>40.11672876026724</v>
+        <v>26.963842509069</v>
       </c>
       <c r="D191">
-        <v>20.79541439916316</v>
+        <v>22.26031265264148</v>
       </c>
       <c r="E191">
-        <v>0.999152</v>
+        <v>0.9996853900000001</v>
       </c>
       <c r="F191">
-        <v>0.999152</v>
+        <v>0.9996853900000001</v>
       </c>
       <c r="G191">
-        <v>0.2098184021536666</v>
+        <v>-0.02299759931689671</v>
       </c>
       <c r="H191">
-        <v>0.9975007899999999</v>
+        <v>0.9996853900000001</v>
       </c>
     </row>
     <row r="192" spans="1:8">
       <c r="A192" s="1">
-        <v>46161</v>
+        <v>46185</v>
       </c>
       <c r="B192" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C192">
-        <v>39.69086941528401</v>
+        <v>26.83840329983722</v>
       </c>
       <c r="D192">
-        <v>20.74924328599426</v>
+        <v>22.18026196156466</v>
       </c>
       <c r="E192">
-        <v>0.99914989</v>
+        <v>1.000030945</v>
       </c>
       <c r="F192">
-        <v>0.99914989</v>
+        <v>1.000030945</v>
       </c>
       <c r="G192">
-        <v>0.2020471776850241</v>
+        <v>-0.02985038257907502</v>
       </c>
       <c r="H192">
-        <v>0.9974417</v>
+        <v>1.000030945</v>
       </c>
     </row>
     <row r="193" spans="1:8">
       <c r="A193" s="1">
-        <v>46162</v>
+        <v>46188</v>
       </c>
       <c r="B193" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C193">
-        <v>40.37836787855562</v>
+        <v>27.39043294650222</v>
       </c>
       <c r="D193">
-        <v>21.11271132314188</v>
+        <v>22.77851469735379</v>
       </c>
       <c r="E193">
-        <v>0.99915058</v>
+        <v>1.000836146</v>
       </c>
       <c r="F193">
-        <v>0.99915058</v>
+        <v>1.000836146</v>
       </c>
       <c r="G193">
-        <v>0.2291077670847563</v>
+        <v>-0.001460445118800835</v>
       </c>
       <c r="H193">
-        <v>0.9974415600000001</v>
+        <v>1.000836146</v>
       </c>
     </row>
     <row r="194" spans="1:8">
       <c r="A194" s="1">
-        <v>46163</v>
+        <v>46153</v>
       </c>
       <c r="B194" t="s">
         <v>16</v>
       </c>
       <c r="C194">
-        <v>38.9123066967842</v>
+        <v>40.68830633303975</v>
       </c>
       <c r="D194">
-        <v>21.28910644207464</v>
+        <v>21.50431773660198</v>
       </c>
       <c r="E194">
-        <v>0.9989350699999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="F194">
-        <v>0.9989350699999999</v>
+        <v>0.99909852</v>
       </c>
       <c r="G194">
-        <v>0.2392382040170877</v>
+        <v>0.2342423866086769</v>
       </c>
       <c r="H194">
-        <v>0.99726191</v>
+        <v>0.9974930900000001</v>
       </c>
     </row>
     <row r="195" spans="1:8">
       <c r="A195" s="1">
-        <v>46164</v>
+        <v>46154</v>
       </c>
       <c r="B195" t="s">
         <v>16</v>
       </c>
       <c r="C195">
-        <v>39.43913909150694</v>
+        <v>40.32854894972581</v>
       </c>
       <c r="D195">
-        <v>21.05297617141148</v>
+        <v>21.09133998298594</v>
       </c>
       <c r="E195">
-        <v>0.999144</v>
+        <v>0.9990972199999999</v>
       </c>
       <c r="F195">
-        <v>0.999144</v>
+        <v>0.9990972199999999</v>
       </c>
       <c r="G195">
-        <v>0.2516582935428642</v>
+        <v>0.2156468205051487</v>
       </c>
       <c r="H195">
-        <v>0.9974678400000001</v>
+        <v>0.99752223</v>
       </c>
     </row>
     <row r="196" spans="1:8">
       <c r="A196" s="1">
-        <v>46167</v>
+        <v>46155</v>
       </c>
       <c r="B196" t="s">
         <v>16</v>
       </c>
       <c r="C196">
-        <v>39.45782844313628</v>
+        <v>40.47987921095815</v>
       </c>
       <c r="D196">
-        <v>21.0518901572272</v>
+        <v>21.35995364434454</v>
       </c>
       <c r="E196">
-        <v>0.999144</v>
+        <v>0.9991780100000001</v>
       </c>
       <c r="F196">
-        <v>0.999144</v>
+        <v>0.9991780100000001</v>
       </c>
       <c r="G196">
-        <v>0.2516582935428642</v>
+        <v>0.2270956128473374</v>
       </c>
       <c r="H196">
-        <v>0.9974678400000001</v>
+        <v>0.9975825700000001</v>
       </c>
     </row>
     <row r="197" spans="1:8">
       <c r="A197" s="1">
-        <v>46168</v>
+        <v>46156</v>
       </c>
       <c r="B197" t="s">
         <v>16</v>
       </c>
       <c r="C197">
-        <v>40.20219297984542</v>
+        <v>41.20436574895244</v>
       </c>
       <c r="D197">
-        <v>21.93106024403281</v>
+        <v>21.48149674387778</v>
       </c>
       <c r="E197">
-        <v>0.9991421799999999</v>
+        <v>0.9991793299999999</v>
       </c>
       <c r="F197">
-        <v>0.9991421799999999</v>
+        <v>0.9991793299999999</v>
       </c>
       <c r="G197">
-        <v>0.2846167552893293</v>
+        <v>0.2454829228401052</v>
       </c>
       <c r="H197">
-        <v>0.9974609800000001</v>
+        <v>0.99754722</v>
       </c>
     </row>
     <row r="198" spans="1:8">
       <c r="A198" s="1">
-        <v>46169</v>
+        <v>46157</v>
       </c>
       <c r="B198" t="s">
         <v>16</v>
       </c>
       <c r="C198">
-        <v>40.34993865302093</v>
+        <v>40.80613062958688</v>
       </c>
       <c r="D198">
-        <v>21.65366031776487</v>
+        <v>21.08912555803936</v>
       </c>
       <c r="E198">
-        <v>0.9991434600000001</v>
+        <v>0.9991790600000001</v>
       </c>
       <c r="F198">
-        <v>0.9991434600000001</v>
+        <v>0.9991790600000001</v>
       </c>
       <c r="G198">
-        <v>0.2796902860011767</v>
+        <v>0.2230017445022556</v>
       </c>
       <c r="H198">
-        <v>0.9991434600000001</v>
+        <v>0.9975824700000002</v>
       </c>
     </row>
     <row r="199" spans="1:8">
       <c r="A199" s="1">
-        <v>46170</v>
+        <v>46160</v>
       </c>
       <c r="B199" t="s">
         <v>16</v>
       </c>
       <c r="C199">
-        <v>40.5850485390846</v>
+        <v>40.11672876026724</v>
       </c>
       <c r="D199">
-        <v>21.75450977746074</v>
+        <v>20.79541439916316</v>
       </c>
       <c r="E199">
-        <v>0.99914592</v>
+        <v>0.999152</v>
       </c>
       <c r="F199">
-        <v>0.99914592</v>
+        <v>0.999152</v>
       </c>
       <c r="G199">
-        <v>0.2964818481030536</v>
+        <v>0.2098184021536666</v>
       </c>
       <c r="H199">
-        <v>0.99914592</v>
+        <v>0.9975007899999999</v>
       </c>
     </row>
     <row r="200" spans="1:8">
       <c r="A200" s="1">
-        <v>46171</v>
+        <v>46161</v>
       </c>
       <c r="B200" t="s">
         <v>16</v>
       </c>
       <c r="C200">
-        <v>41.86785805184477</v>
+        <v>39.69086941528401</v>
       </c>
       <c r="D200">
-        <v>22.33589392797469</v>
+        <v>20.74924328599426</v>
       </c>
       <c r="E200">
-        <v>0.9991336999999999</v>
+        <v>0.99914989</v>
       </c>
       <c r="F200">
-        <v>0.9991336999999999</v>
+        <v>0.99914989</v>
       </c>
       <c r="G200">
-        <v>0.3254158954996882</v>
+        <v>0.2020471776850241</v>
       </c>
       <c r="H200">
-        <v>0.9991336999999999</v>
+        <v>0.9974417</v>
       </c>
     </row>
     <row r="201" spans="1:8">
       <c r="A201" s="1">
-        <v>46174</v>
+        <v>46162</v>
       </c>
       <c r="B201" t="s">
         <v>16</v>
       </c>
       <c r="C201">
-        <v>42.82932322850974</v>
+        <v>40.37836787855562</v>
       </c>
       <c r="D201">
-        <v>22.98998911430362</v>
+        <v>21.11271132314188</v>
       </c>
       <c r="E201">
-        <v>0.99914238</v>
+        <v>0.99915058</v>
       </c>
       <c r="F201">
-        <v>0.99914238</v>
+        <v>0.99915058</v>
       </c>
       <c r="G201">
-        <v>0.3583049032509023</v>
+        <v>0.2291077670847563</v>
       </c>
       <c r="H201">
-        <v>0.99914238</v>
+        <v>0.9974415600000001</v>
       </c>
     </row>
     <row r="202" spans="1:8">
       <c r="A202" s="1">
-        <v>46175</v>
+        <v>46163</v>
       </c>
       <c r="B202" t="s">
         <v>16</v>
       </c>
       <c r="C202">
-        <v>43.11872937189534</v>
+        <v>38.9123066967842</v>
       </c>
       <c r="D202">
-        <v>22.90628380907704</v>
+        <v>21.28910644207464</v>
       </c>
       <c r="E202">
-        <v>0.9990972800000002</v>
+        <v>0.9989350699999999</v>
       </c>
       <c r="F202">
-        <v>0.9990972800000002</v>
+        <v>0.9989350699999999</v>
       </c>
       <c r="G202">
-        <v>0.3753046155885469</v>
+        <v>0.2392382040170877</v>
       </c>
       <c r="H202">
-        <v>0.9990972800000002</v>
+        <v>0.99726191</v>
       </c>
     </row>
     <row r="203" spans="1:8">
       <c r="A203" s="1">
-        <v>46176</v>
+        <v>46164</v>
       </c>
       <c r="B203" t="s">
         <v>16</v>
       </c>
       <c r="C203">
-        <v>42.86143001679577</v>
+        <v>39.43913909150694</v>
       </c>
       <c r="D203">
-        <v>22.72053012591219</v>
+        <v>21.05297617141148</v>
       </c>
       <c r="E203">
-        <v>0.9990984299999999</v>
+        <v>0.999144</v>
       </c>
       <c r="F203">
-        <v>0.9990984299999999</v>
+        <v>0.999144</v>
       </c>
       <c r="G203">
-        <v>0.3615660647779204</v>
+        <v>0.2516582935428642</v>
       </c>
       <c r="H203">
-        <v>0.9990984299999999</v>
+        <v>0.9974678400000001</v>
       </c>
     </row>
     <row r="204" spans="1:8">
       <c r="A204" s="1">
-        <v>46177</v>
+        <v>46167</v>
       </c>
       <c r="B204" t="s">
         <v>16</v>
       </c>
       <c r="C204">
-        <v>42.57902095847519</v>
+        <v>39.45782844313628</v>
       </c>
       <c r="D204">
-        <v>22.20304338566557</v>
+        <v>21.0518901572272</v>
       </c>
       <c r="E204">
-        <v>0.9990006900000001</v>
+        <v>0.999144</v>
       </c>
       <c r="F204">
-        <v>0.9990006900000001</v>
+        <v>0.999144</v>
       </c>
       <c r="G204">
-        <v>0.34033389372967</v>
+        <v>0.2516582935428642</v>
       </c>
       <c r="H204">
-        <v>0.9990006900000001</v>
+        <v>0.9974678400000001</v>
       </c>
     </row>
     <row r="205" spans="1:8">
       <c r="A205" s="1">
-        <v>46178</v>
+        <v>46168</v>
       </c>
       <c r="B205" t="s">
         <v>16</v>
       </c>
       <c r="C205">
-        <v>39.64354477595148</v>
+        <v>40.20219297984542</v>
       </c>
       <c r="D205">
-        <v>20.69555521363093</v>
+        <v>21.93106024403281</v>
       </c>
       <c r="E205">
-        <v>0.9992026399999999</v>
+        <v>0.9991421799999999</v>
       </c>
       <c r="F205">
-        <v>0.9992026399999999</v>
+        <v>0.9991421799999999</v>
       </c>
       <c r="G205">
-        <v>0.251033842835561</v>
+        <v>0.2846167552893293</v>
       </c>
       <c r="H205">
-        <v>0.9992026399999999</v>
+        <v>0.9974609800000001</v>
       </c>
     </row>
     <row r="206" spans="1:8">
       <c r="A206" s="1">
-        <v>46182</v>
+        <v>46169</v>
       </c>
       <c r="B206" t="s">
         <v>16</v>
       </c>
       <c r="C206">
-        <v>39.7656886466531</v>
+        <v>40.34993865302093</v>
       </c>
       <c r="D206">
-        <v>20.79148740795913</v>
+        <v>21.65366031776487</v>
       </c>
       <c r="E206">
-        <v>0.9992145899999999</v>
+        <v>0.9991434600000001</v>
       </c>
       <c r="F206">
-        <v>0.9992145899999999</v>
+        <v>0.9991434600000001</v>
       </c>
       <c r="G206">
-        <v>0.2542950043625791</v>
+        <v>0.2796902860011767</v>
       </c>
       <c r="H206">
-        <v>0.9992145899999999</v>
+        <v>0.9991434600000001</v>
       </c>
     </row>
     <row r="207" spans="1:8">
       <c r="A207" s="1">
-        <v>46183</v>
+        <v>46170</v>
       </c>
       <c r="B207" t="s">
         <v>16</v>
       </c>
       <c r="C207">
-        <v>38.48800295288941</v>
+        <v>40.5850485390846</v>
       </c>
       <c r="D207">
-        <v>20.05492629580107</v>
+        <v>21.75450977746074</v>
       </c>
       <c r="E207">
-        <v>0.9992031100000001</v>
+        <v>0.99914592</v>
       </c>
       <c r="F207">
-        <v>0.9992031100000001</v>
+        <v>0.99914592</v>
       </c>
       <c r="G207">
-        <v>0.2255691072017123</v>
+        <v>0.2964818481030536</v>
       </c>
       <c r="H207">
-        <v>0.9992031100000001</v>
+        <v>0.99914592</v>
       </c>
     </row>
     <row r="208" spans="1:8">
       <c r="A208" s="1">
-        <v>46184</v>
+        <v>46171</v>
       </c>
       <c r="B208" t="s">
         <v>16</v>
       </c>
       <c r="C208">
-        <v>39.71404813715499</v>
+        <v>41.86785805184477</v>
       </c>
       <c r="D208">
-        <v>20.78057418129766</v>
+        <v>22.33589392797469</v>
       </c>
       <c r="E208">
-        <v>0.9991764899999999</v>
+        <v>0.9991336999999999</v>
       </c>
       <c r="F208">
-        <v>0.9991764899999999</v>
+        <v>0.9991336999999999</v>
       </c>
       <c r="G208">
-        <v>0.2712252627049727</v>
+        <v>0.3254158954996882</v>
       </c>
       <c r="H208">
-        <v>0.9991764899999999</v>
+        <v>0.9991336999999999</v>
       </c>
     </row>
     <row r="209" spans="1:8">
       <c r="A209" s="1">
-        <v>46185</v>
+        <v>46174</v>
       </c>
       <c r="B209" t="s">
         <v>16</v>
       </c>
       <c r="C209">
+        <v>42.82932322850974</v>
+      </c>
+      <c r="D209">
+        <v>22.98998911430362</v>
+      </c>
+      <c r="E209">
+        <v>0.99914238</v>
+      </c>
+      <c r="F209">
+        <v>0.99914238</v>
+      </c>
+      <c r="G209">
+        <v>0.3583049032509023</v>
+      </c>
+      <c r="H209">
+        <v>0.99914238</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8">
+      <c r="A210" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B210" t="s">
+        <v>16</v>
+      </c>
+      <c r="C210">
+        <v>43.11872937189534</v>
+      </c>
+      <c r="D210">
+        <v>22.90628380907704</v>
+      </c>
+      <c r="E210">
+        <v>0.9990972800000002</v>
+      </c>
+      <c r="F210">
+        <v>0.9990972800000002</v>
+      </c>
+      <c r="G210">
+        <v>0.3753046155885469</v>
+      </c>
+      <c r="H210">
+        <v>0.9990972800000002</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8">
+      <c r="A211" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B211" t="s">
+        <v>16</v>
+      </c>
+      <c r="C211">
+        <v>42.86143001679577</v>
+      </c>
+      <c r="D211">
+        <v>22.72053012591219</v>
+      </c>
+      <c r="E211">
+        <v>0.9990984299999999</v>
+      </c>
+      <c r="F211">
+        <v>0.9990984299999999</v>
+      </c>
+      <c r="G211">
+        <v>0.3615660647779204</v>
+      </c>
+      <c r="H211">
+        <v>0.9990984299999999</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8">
+      <c r="A212" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B212" t="s">
+        <v>16</v>
+      </c>
+      <c r="C212">
+        <v>42.57902095847519</v>
+      </c>
+      <c r="D212">
+        <v>22.20304338566557</v>
+      </c>
+      <c r="E212">
+        <v>0.9990006900000001</v>
+      </c>
+      <c r="F212">
+        <v>0.9990006900000001</v>
+      </c>
+      <c r="G212">
+        <v>0.34033389372967</v>
+      </c>
+      <c r="H212">
+        <v>0.9990006900000001</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8">
+      <c r="A213" s="1">
+        <v>46178</v>
+      </c>
+      <c r="B213" t="s">
+        <v>16</v>
+      </c>
+      <c r="C213">
+        <v>39.64354477595148</v>
+      </c>
+      <c r="D213">
+        <v>20.69555521363093</v>
+      </c>
+      <c r="E213">
+        <v>0.9992026399999999</v>
+      </c>
+      <c r="F213">
+        <v>0.9992026399999999</v>
+      </c>
+      <c r="G213">
+        <v>0.251033842835561</v>
+      </c>
+      <c r="H213">
+        <v>0.9992026399999999</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8">
+      <c r="A214" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B214" t="s">
+        <v>16</v>
+      </c>
+      <c r="C214">
+        <v>39.7656886466531</v>
+      </c>
+      <c r="D214">
+        <v>20.79148740795913</v>
+      </c>
+      <c r="E214">
+        <v>0.9992145899999999</v>
+      </c>
+      <c r="F214">
+        <v>0.9992145899999999</v>
+      </c>
+      <c r="G214">
+        <v>0.2542950043625791</v>
+      </c>
+      <c r="H214">
+        <v>0.9992145899999999</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8">
+      <c r="A215" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B215" t="s">
+        <v>16</v>
+      </c>
+      <c r="C215">
+        <v>38.48800295288941</v>
+      </c>
+      <c r="D215">
+        <v>20.05492629580107</v>
+      </c>
+      <c r="E215">
+        <v>0.9992031100000001</v>
+      </c>
+      <c r="F215">
+        <v>0.9992031100000001</v>
+      </c>
+      <c r="G215">
+        <v>0.2255691072017123</v>
+      </c>
+      <c r="H215">
+        <v>0.9992031100000001</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8">
+      <c r="A216" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B216" t="s">
+        <v>16</v>
+      </c>
+      <c r="C216">
+        <v>39.71404813715499</v>
+      </c>
+      <c r="D216">
+        <v>20.78057418129766</v>
+      </c>
+      <c r="E216">
+        <v>0.9991764899999999</v>
+      </c>
+      <c r="F216">
+        <v>0.9991764899999999</v>
+      </c>
+      <c r="G216">
+        <v>0.2712252627049727</v>
+      </c>
+      <c r="H216">
+        <v>0.9991764899999999</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8">
+      <c r="A217" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B217" t="s">
+        <v>16</v>
+      </c>
+      <c r="C217">
         <v>40.05042651208108</v>
       </c>
-      <c r="D209">
+      <c r="D217">
         <v>20.84207512811844</v>
       </c>
-      <c r="E209">
+      <c r="E217">
         <v>0.9991762200000001</v>
       </c>
-      <c r="F209">
+      <c r="F217">
         <v>0.9991762200000001</v>
       </c>
-      <c r="G209">
+      <c r="G217">
         <v>0.2822576487006332</v>
       </c>
-      <c r="H209">
+      <c r="H217">
         <v>0.9991762200000001</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8">
+      <c r="A218" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B218" t="s">
+        <v>16</v>
+      </c>
+      <c r="C218">
+        <v>40.72250762932357</v>
+      </c>
+      <c r="D218">
+        <v>21.81434247841182</v>
+      </c>
+      <c r="E218">
+        <v>0.9991819499999999</v>
+      </c>
+      <c r="F218">
+        <v>0.9991819499999999</v>
+      </c>
+      <c r="G218">
+        <v>0.3307585593843836</v>
+      </c>
+      <c r="H218">
+        <v>0.9991819499999999</v>
       </c>
     </row>
   </sheetData>

--- a/etf_analyst_target_outputs/ETF_PE_history.xlsx
+++ b/etf_analyst_target_outputs/ETF_PE_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="17">
   <si>
     <t>Date</t>
   </si>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H218"/>
+  <dimension ref="A1:H227"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -899,42 +899,42 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1">
-        <v>46153</v>
+        <v>46189</v>
       </c>
       <c r="B20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20">
-        <v>53.14833755912058</v>
+        <v>27.41151837950002</v>
       </c>
       <c r="D20">
-        <v>25.84885448407537</v>
+        <v>17.66496991340819</v>
       </c>
       <c r="E20">
-        <v>0.9262</v>
+        <v>0.8732000000000001</v>
       </c>
       <c r="F20">
-        <v>0.9262</v>
+        <v>0.8732000000000001</v>
       </c>
       <c r="G20">
-        <v>0.3839084462043663</v>
+        <v>0.5843682939592225</v>
       </c>
       <c r="H20">
-        <v>0.9262</v>
+        <v>0.9353</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B21" t="s">
         <v>9</v>
       </c>
       <c r="C21">
-        <v>51.82921169635205</v>
+        <v>53.14833755912058</v>
       </c>
       <c r="D21">
-        <v>2